--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -1558,18 +1558,32 @@
       </c>
       <c r="U2" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V2" s="24" t="n"/>
-      <c r="W2" s="26" t="n"/>
-      <c r="X2" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n"/>
-      <c r="AD2" s="24" t="n"/>
+      <c r="AC2" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:43.225807Z</t>
+        </is>
+      </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.4900 (aec-mlb-cws-tor-2026-07-19).</t>
@@ -1582,7 +1596,7 @@
       </c>
       <c r="AG2" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH2" s="24" t="n"/>
@@ -1807,18 +1821,32 @@
       </c>
       <c r="U3" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V3" s="24" t="n"/>
-      <c r="W3" s="26" t="n"/>
-      <c r="X3" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W3" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="X3" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n"/>
-      <c r="AD3" s="24" t="n"/>
+      <c r="AC3" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:43.477592Z</t>
+        </is>
+      </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.4600 (aec-mlb-nym-phi-2026-07-19).</t>
@@ -1831,7 +1859,7 @@
       </c>
       <c r="AG3" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH3" s="24" t="n"/>
@@ -2056,18 +2084,32 @@
       </c>
       <c r="U4" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V4" s="24" t="n"/>
-      <c r="W4" s="26" t="n"/>
-      <c r="X4" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="26" t="n">
+        <v>6</v>
+      </c>
       <c r="Y4" s="25" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n"/>
-      <c r="AD4" s="24" t="n"/>
+      <c r="AC4" s="30" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="AD4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:43.720828Z</t>
+        </is>
+      </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.5400 (aec-mlb-tb-bos-2026-07-19).</t>
@@ -2305,18 +2347,32 @@
       </c>
       <c r="U5" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V5" s="24" t="n"/>
-      <c r="W5" s="26" t="n"/>
-      <c r="X5" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X5" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="24" t="n"/>
+      <c r="AC5" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:43.966052Z</t>
+        </is>
+      </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.4600 (aec-mlb-pit-cle-2026-07-19).</t>
@@ -2329,7 +2385,7 @@
       </c>
       <c r="AG5" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH5" s="24" t="n"/>
@@ -2554,18 +2610,32 @@
       </c>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="n"/>
-      <c r="W6" s="26" t="n"/>
-      <c r="X6" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="24" t="n"/>
+      <c r="AC6" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:44.208798Z</t>
+        </is>
+      </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.5150 (aec-mlb-bal-hou-2026-07-19).</t>
@@ -2578,7 +2648,7 @@
       </c>
       <c r="AG6" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH6" s="24" t="n"/>
@@ -2803,18 +2873,32 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>1.4344</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:44.452287Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.5500 (aec-mlb-mia-mil-2026-07-19).</t>
@@ -3052,18 +3136,32 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="AC8" s="30" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:44.698613Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.4650 (aec-mlb-sd-kc-2026-07-19).</t>
@@ -3301,18 +3399,32 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>10</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:44.944082Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.6000 (aec-mlb-min-chc-2026-07-19).</t>
@@ -3550,18 +3662,32 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:45.192018Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.5850 (aec-mlb-det-laa-2026-07-19).</t>
@@ -3574,7 +3700,7 @@
       </c>
       <c r="AG10" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH10" s="24" t="n"/>
@@ -3799,18 +3925,32 @@
       </c>
       <c r="U11" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>6</v>
+      </c>
       <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
+      <c r="AC11" s="30" t="n">
+        <v>0.9202</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:45.440735Z</t>
+        </is>
+      </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.6200 (aec-mlb-sf-sea-2026-07-19).</t>
@@ -4546,18 +4686,32 @@
       </c>
       <c r="U14" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>90</v>
+      </c>
       <c r="Y14" s="25" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
+      <c r="AC14" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:45.958826Z</t>
+        </is>
+      </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5000; executable ask 0.8000 (aec-wnba-la-dal-2026-07-19).</t>
@@ -4795,18 +4949,32 @@
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>91</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>93</v>
+      </c>
       <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
+      <c r="AC15" s="30" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:46.205387Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5000; executable ask 0.8100 (aec-wnba-chi-atl-2026-07-19).</t>
@@ -5268,17 +5436,17 @@
         <v>-354</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.282</v>
+        <v>1.282486</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.78</v>
+        <v>0.779736</v>
       </c>
       <c r="O17" s="28" t="n">
         <v>0.6207</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>-0.1593</v>
+        <v>-0.159036</v>
       </c>
       <c r="R17" s="26" t="n"/>
       <c r="S17" s="29" t="n">
@@ -5310,7 +5478,7 @@
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
       <c r="AC17" s="30" t="n">
-        <v>0.4936</v>
+        <v>0.4944</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
         <is>
@@ -5375,13 +5543,13 @@
         <v>-354</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.282</v>
+        <v>1.282486</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.78</v>
+        <v>0.779736</v>
       </c>
       <c r="BN17" s="28" t="n">
-        <v>0.78</v>
+        <v>0.779736</v>
       </c>
       <c r="BO17" s="28" t="n"/>
       <c r="BP17" s="25" t="n"/>
@@ -5453,10 +5621,10 @@
         <v>-194</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>1.515152</v>
+        <v>1.515464</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.66</v>
+        <v>0.659864</v>
       </c>
       <c r="O18" s="28" t="n">
         <v>0.577396</v>
@@ -5465,7 +5633,7 @@
         <v>0.05</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>-0.082604</v>
+        <v>-0.082468</v>
       </c>
       <c r="R18" s="26" t="n"/>
       <c r="S18" s="29" t="n">
@@ -5486,14 +5654,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
+      <c r="W18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>15</v>
+      </c>
       <c r="Y18" s="25" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
       <c r="AC18" s="30" t="n">
-        <v>0.6439</v>
+        <v>0.6443</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
         <is>
@@ -5544,10 +5716,10 @@
         <v>-194</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>1.515152</v>
+        <v>1.515464</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.66</v>
+        <v>0.659864</v>
       </c>
       <c r="BN18" s="28" t="n">
         <v>0.656716</v>
@@ -5622,10 +5794,10 @@
         <v>-122</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>1.818182</v>
+        <v>1.819672</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.55</v>
+        <v>0.54955</v>
       </c>
       <c r="O19" s="28" t="n">
         <v>0.551581</v>
@@ -5634,7 +5806,7 @@
         <v>0.05</v>
       </c>
       <c r="Q19" s="28" t="n">
-        <v>0.001581</v>
+        <v>0.002031</v>
       </c>
       <c r="R19" s="26" t="n"/>
       <c r="S19" s="29" t="n">
@@ -5655,8 +5827,12 @@
           <t>loss</t>
         </is>
       </c>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
+      <c r="W19" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
@@ -5713,10 +5889,10 @@
         <v>-122</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>1.818182</v>
+        <v>1.819672</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.55</v>
+        <v>0.54955</v>
       </c>
       <c r="BN19" s="28" t="n">
         <v>0.547264</v>
@@ -5791,10 +5967,10 @@
         <v>-113</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.886792</v>
+        <v>1.884956</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.53</v>
+        <v>0.530516</v>
       </c>
       <c r="O20" s="28" t="n">
         <v>0.521172</v>
@@ -5803,7 +5979,7 @@
         <v>0.05</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>-0.008828000000000001</v>
+        <v>-0.009344</v>
       </c>
       <c r="R20" s="26" t="n"/>
       <c r="S20" s="29" t="n">
@@ -5824,8 +6000,12 @@
           <t>loss</t>
         </is>
       </c>
-      <c r="W20" s="26" t="n"/>
-      <c r="X20" s="26" t="n"/>
+      <c r="W20" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>7</v>
+      </c>
       <c r="Y20" s="25" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
@@ -5882,10 +6062,10 @@
         <v>-113</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.886792</v>
+        <v>1.884956</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.53</v>
+        <v>0.530516</v>
       </c>
       <c r="BN20" s="28" t="n">
         <v>0.527363</v>
@@ -5960,10 +6140,10 @@
         <v>-106</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.941748</v>
+        <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.515</v>
+        <v>0.514563</v>
       </c>
       <c r="O21" s="28" t="n">
         <v>0.524624</v>
@@ -5972,7 +6152,7 @@
         <v>0.05</v>
       </c>
       <c r="Q21" s="28" t="n">
-        <v>0.009624000000000001</v>
+        <v>0.010061</v>
       </c>
       <c r="R21" s="26" t="n"/>
       <c r="S21" s="29" t="n">
@@ -5993,8 +6173,12 @@
           <t>loss</t>
         </is>
       </c>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
+      <c r="W21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y21" s="25" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
@@ -6051,10 +6235,10 @@
         <v>-106</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.941748</v>
+        <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.515</v>
+        <v>0.514563</v>
       </c>
       <c r="BN21" s="28" t="n">
         <v>0.5124379999999999</v>
@@ -6129,10 +6313,10 @@
         <v>-174</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>1.574803</v>
+        <v>1.574713</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.635</v>
+        <v>0.635036</v>
       </c>
       <c r="O22" s="28" t="n">
         <v>0.597575</v>
@@ -6141,7 +6325,7 @@
         <v>0.05</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>-0.037425</v>
+        <v>-0.037461</v>
       </c>
       <c r="R22" s="26" t="n"/>
       <c r="S22" s="29" t="n">
@@ -6162,8 +6346,12 @@
           <t>loss</t>
         </is>
       </c>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
+      <c r="W22" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y22" s="25" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
@@ -6220,10 +6408,10 @@
         <v>-174</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>1.574803</v>
+        <v>1.574713</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.635</v>
+        <v>0.635036</v>
       </c>
       <c r="BN22" s="28" t="n">
         <v>0.631841</v>
@@ -6298,10 +6486,10 @@
         <v>-376</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>1.265823</v>
+        <v>1.265957</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.79</v>
+        <v>0.789916</v>
       </c>
       <c r="O23" s="28" t="n">
         <v>0.534506</v>
@@ -6310,7 +6498,7 @@
         <v>0.05</v>
       </c>
       <c r="Q23" s="28" t="n">
-        <v>-0.255494</v>
+        <v>-0.25541</v>
       </c>
       <c r="R23" s="26" t="n"/>
       <c r="S23" s="29" t="n">
@@ -6331,14 +6519,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
+      <c r="W23" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>92</v>
+      </c>
       <c r="Y23" s="25" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
       <c r="AC23" s="30" t="n">
-        <v>0.1994</v>
+        <v>0.1995</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
         <is>
@@ -6389,10 +6581,10 @@
         <v>-376</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>1.265823</v>
+        <v>1.265957</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.79</v>
+        <v>0.789916</v>
       </c>
       <c r="BN23" s="28" t="n">
         <v>0.782178</v>
@@ -6467,10 +6659,10 @@
         <v>-113</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.886792</v>
+        <v>1.884956</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.53</v>
+        <v>0.530516</v>
       </c>
       <c r="O24" s="28" t="n">
         <v>0.505358</v>
@@ -6479,7 +6671,7 @@
         <v>0.05</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>-0.024642</v>
+        <v>-0.025158</v>
       </c>
       <c r="R24" s="26" t="n"/>
       <c r="S24" s="29" t="n">
@@ -6500,14 +6692,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
+      <c r="W24" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>96</v>
+      </c>
       <c r="Y24" s="25" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
       <c r="AC24" s="30" t="n">
-        <v>0.4434</v>
+        <v>0.4425</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
         <is>
@@ -6558,10 +6754,10 @@
         <v>-113</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.886792</v>
+        <v>1.884956</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.53</v>
+        <v>0.530516</v>
       </c>
       <c r="BN24" s="28" t="n">
         <v>0.524752</v>
@@ -6636,10 +6832,10 @@
         <v>-178</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.5625</v>
+        <v>1.561798</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.64</v>
+        <v>0.640288</v>
       </c>
       <c r="O25" s="28" t="n">
         <v>0.637935</v>
@@ -6648,7 +6844,7 @@
         <v>0.05</v>
       </c>
       <c r="Q25" s="28" t="n">
-        <v>-0.002065</v>
+        <v>-0.002353</v>
       </c>
       <c r="R25" s="26" t="n"/>
       <c r="S25" s="29" t="n">
@@ -6669,8 +6865,12 @@
           <t>loss</t>
         </is>
       </c>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
+      <c r="W25" s="26" t="n">
+        <v>96</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>83</v>
+      </c>
       <c r="Y25" s="25" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
@@ -6727,10 +6927,10 @@
         <v>-178</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>1.5625</v>
+        <v>1.561798</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.64</v>
+        <v>0.640288</v>
       </c>
       <c r="BN25" s="28" t="n">
         <v>0.633663</v>
@@ -6805,10 +7005,10 @@
         <v>-163</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1.612903</v>
+        <v>1.613497</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.62</v>
+        <v>0.619772</v>
       </c>
       <c r="O26" s="28" t="n">
         <v>0.611768</v>
@@ -6817,7 +7017,7 @@
         <v>0.05</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>-0.008232</v>
+        <v>-0.008004000000000001</v>
       </c>
       <c r="R26" s="26" t="n"/>
       <c r="S26" s="29" t="n">
@@ -6838,14 +7038,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
+      <c r="W26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>6</v>
+      </c>
       <c r="Y26" s="25" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
       <c r="AC26" s="30" t="n">
-        <v>0.9194</v>
+        <v>0.9202</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
         <is>
@@ -6896,10 +7100,10 @@
         <v>-163</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>1.612903</v>
+        <v>1.613497</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.62</v>
+        <v>0.619772</v>
       </c>
       <c r="BN26" s="28" t="n">
         <v>0.616915</v>
@@ -6974,10 +7178,10 @@
         <v>-111</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.904762</v>
+        <v>1.900901</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.525</v>
+        <v>0.526066</v>
       </c>
       <c r="O27" s="28" t="n">
         <v>0.525388</v>
@@ -6986,7 +7190,7 @@
         <v>0.05</v>
       </c>
       <c r="Q27" s="28" t="n">
-        <v>0.000388</v>
+        <v>-0.000678</v>
       </c>
       <c r="R27" s="26" t="n"/>
       <c r="S27" s="29" t="n">
@@ -7007,14 +7211,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
+      <c r="W27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>5</v>
+      </c>
       <c r="Y27" s="25" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
       <c r="AC27" s="30" t="n">
-        <v>0.6786</v>
+        <v>0.6757</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
         <is>
@@ -7065,10 +7273,10 @@
         <v>-111</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.904762</v>
+        <v>1.900901</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.525</v>
+        <v>0.526066</v>
       </c>
       <c r="BN27" s="28" t="n">
         <v>0.522388</v>
@@ -7143,10 +7351,10 @@
         <v>-138</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>1.724138</v>
+        <v>1.724638</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.58</v>
+        <v>0.579832</v>
       </c>
       <c r="O28" s="28" t="n">
         <v>0.597575</v>
@@ -7155,7 +7363,7 @@
         <v>0.05</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>0.017575</v>
+        <v>0.017743</v>
       </c>
       <c r="R28" s="26" t="n"/>
       <c r="S28" s="29" t="n">
@@ -7176,14 +7384,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
+      <c r="W28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
       <c r="AC28" s="30" t="n">
-        <v>1.0862</v>
+        <v>1.087</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
         <is>
@@ -7234,10 +7446,10 @@
         <v>-138</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>1.724138</v>
+        <v>1.724638</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.58</v>
+        <v>0.579832</v>
       </c>
       <c r="BN28" s="28" t="n">
         <v>0.577114</v>
@@ -7312,10 +7524,10 @@
         <v>-178</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>1.5625</v>
+        <v>1.561798</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.64</v>
+        <v>0.640288</v>
       </c>
       <c r="O29" s="28" t="n">
         <v>0.550233</v>
@@ -7324,7 +7536,7 @@
         <v>0.05</v>
       </c>
       <c r="Q29" s="28" t="n">
-        <v>-0.089767</v>
+        <v>-0.090055</v>
       </c>
       <c r="R29" s="26" t="n"/>
       <c r="S29" s="29" t="n">
@@ -7345,14 +7557,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
+      <c r="W29" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
       <c r="AC29" s="30" t="n">
-        <v>0.5625</v>
+        <v>0.5618</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
         <is>
@@ -7403,10 +7619,10 @@
         <v>-178</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>1.5625</v>
+        <v>1.561798</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.64</v>
+        <v>0.640288</v>
       </c>
       <c r="BN29" s="28" t="n">
         <v>0.636816</v>
@@ -7481,10 +7697,10 @@
         <v>-669</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>1.149425</v>
+        <v>1.149477</v>
       </c>
       <c r="N30" s="28" t="n">
-        <v>0.87</v>
+        <v>0.869961</v>
       </c>
       <c r="O30" s="28" t="n">
         <v>0.741703</v>
@@ -7493,7 +7709,7 @@
         <v>0.05</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>-0.128297</v>
+        <v>-0.128258</v>
       </c>
       <c r="R30" s="26" t="n"/>
       <c r="S30" s="29" t="n">
@@ -7514,14 +7730,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
+      <c r="W30" s="26" t="n">
+        <v>93</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>101</v>
+      </c>
       <c r="Y30" s="25" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
       <c r="AC30" s="30" t="n">
-        <v>0.2989</v>
+        <v>0.299</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
         <is>
@@ -7572,10 +7792,10 @@
         <v>-669</v>
       </c>
       <c r="BL30" s="27" t="n">
-        <v>1.149425</v>
+        <v>1.149477</v>
       </c>
       <c r="BM30" s="28" t="n">
-        <v>0.87</v>
+        <v>0.869961</v>
       </c>
       <c r="BN30" s="28" t="n">
         <v>0.861386</v>
@@ -7650,10 +7870,10 @@
         <v>-355</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>1.282051</v>
+        <v>1.28169</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.78</v>
+        <v>0.78022</v>
       </c>
       <c r="O31" s="28" t="n">
         <v>0.743891</v>
@@ -7662,7 +7882,7 @@
         <v>0.05</v>
       </c>
       <c r="Q31" s="28" t="n">
-        <v>-0.036109</v>
+        <v>-0.036329</v>
       </c>
       <c r="R31" s="26" t="n"/>
       <c r="S31" s="29" t="n">
@@ -7683,14 +7903,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W31" s="26" t="n"/>
-      <c r="X31" s="26" t="n"/>
+      <c r="W31" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <v>74</v>
+      </c>
       <c r="Y31" s="25" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
       <c r="AC31" s="30" t="n">
-        <v>0.5641</v>
+        <v>0.5634</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
         <is>
@@ -7741,10 +7965,10 @@
         <v>-355</v>
       </c>
       <c r="BL31" s="27" t="n">
-        <v>1.282051</v>
+        <v>1.28169</v>
       </c>
       <c r="BM31" s="28" t="n">
-        <v>0.78</v>
+        <v>0.78022</v>
       </c>
       <c r="BN31" s="28" t="n">
         <v>0.772277</v>
@@ -10844,10 +11068,10 @@
         <v>-106</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>1.941748</v>
+        <v>1.943396</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.515</v>
+        <v>0.514563</v>
       </c>
       <c r="O43" s="28" t="n">
         <v>0.550333</v>
@@ -10856,7 +11080,7 @@
         <v>0.05</v>
       </c>
       <c r="Q43" s="28" t="n">
-        <v>0.035333</v>
+        <v>0.03577</v>
       </c>
       <c r="R43" s="26" t="n"/>
       <c r="S43" s="29" t="n">
@@ -10877,14 +11101,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W43" s="26" t="n"/>
-      <c r="X43" s="26" t="n"/>
+      <c r="W43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="26" t="n">
+        <v>10</v>
+      </c>
       <c r="Y43" s="25" t="n"/>
       <c r="Z43" s="26" t="n"/>
       <c r="AA43" s="28" t="n"/>
       <c r="AB43" s="28" t="n"/>
       <c r="AC43" s="30" t="n">
-        <v>0.9417</v>
+        <v>0.9434</v>
       </c>
       <c r="AD43" s="24" t="inlineStr">
         <is>
@@ -10935,10 +11163,10 @@
         <v>-106</v>
       </c>
       <c r="BL43" s="27" t="n">
-        <v>1.941748</v>
+        <v>1.943396</v>
       </c>
       <c r="BM43" s="28" t="n">
-        <v>0.515</v>
+        <v>0.514563</v>
       </c>
       <c r="BN43" s="28" t="n">
         <v>0.5124379999999999</v>
@@ -11013,10 +11241,10 @@
         <v>-141</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>1.709402</v>
+        <v>1.70922</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.585</v>
+        <v>0.585062</v>
       </c>
       <c r="O44" s="28" t="n">
         <v>0.616198</v>
@@ -11025,7 +11253,7 @@
         <v>0.05</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>0.031198</v>
+        <v>0.031136</v>
       </c>
       <c r="R44" s="26" t="n"/>
       <c r="S44" s="29" t="n">
@@ -11046,14 +11274,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W44" s="26" t="n"/>
-      <c r="X44" s="26" t="n"/>
+      <c r="W44" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y44" s="25" t="n"/>
       <c r="Z44" s="26" t="n"/>
       <c r="AA44" s="28" t="n"/>
       <c r="AB44" s="28" t="n"/>
       <c r="AC44" s="30" t="n">
-        <v>1.2415</v>
+        <v>1.2411</v>
       </c>
       <c r="AD44" s="24" t="inlineStr">
         <is>
@@ -11104,10 +11336,10 @@
         <v>-141</v>
       </c>
       <c r="BL44" s="27" t="n">
-        <v>1.709402</v>
+        <v>1.70922</v>
       </c>
       <c r="BM44" s="28" t="n">
-        <v>0.585</v>
+        <v>0.585062</v>
       </c>
       <c r="BN44" s="28" t="n">
         <v>0.58209</v>
@@ -11182,10 +11414,10 @@
         <v>-133</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>1.754386</v>
+        <v>1.75188</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.57</v>
+        <v>0.570815</v>
       </c>
       <c r="O45" s="28" t="n">
         <v>0.60271</v>
@@ -11194,7 +11426,7 @@
         <v>0.05</v>
       </c>
       <c r="Q45" s="28" t="n">
-        <v>0.03271</v>
+        <v>0.031895</v>
       </c>
       <c r="R45" s="26" t="n"/>
       <c r="S45" s="29" t="n">
@@ -11215,8 +11447,12 @@
           <t>loss</t>
         </is>
       </c>
-      <c r="W45" s="26" t="n"/>
-      <c r="X45" s="26" t="n"/>
+      <c r="W45" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X45" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y45" s="25" t="n"/>
       <c r="Z45" s="26" t="n"/>
       <c r="AA45" s="28" t="n"/>
@@ -11273,10 +11509,10 @@
         <v>-133</v>
       </c>
       <c r="BL45" s="27" t="n">
-        <v>1.754386</v>
+        <v>1.75188</v>
       </c>
       <c r="BM45" s="28" t="n">
-        <v>0.57</v>
+        <v>0.570815</v>
       </c>
       <c r="BN45" s="28" t="n">
         <v>0.567164</v>
@@ -11351,10 +11587,10 @@
         <v>104</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>2.040816</v>
+        <v>2.04</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.49</v>
+        <v>0.490196</v>
       </c>
       <c r="O46" s="28" t="n">
         <v>0.582862</v>
@@ -11363,7 +11599,7 @@
         <v>0.05</v>
       </c>
       <c r="Q46" s="28" t="n">
-        <v>0.092862</v>
+        <v>0.092666</v>
       </c>
       <c r="R46" s="26" t="n"/>
       <c r="S46" s="29" t="n">
@@ -11384,14 +11620,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W46" s="26" t="n"/>
-      <c r="X46" s="26" t="n"/>
+      <c r="W46" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X46" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y46" s="25" t="n"/>
       <c r="Z46" s="26" t="n"/>
       <c r="AA46" s="28" t="n"/>
       <c r="AB46" s="28" t="n"/>
       <c r="AC46" s="30" t="n">
-        <v>1.301</v>
+        <v>1.3</v>
       </c>
       <c r="AD46" s="24" t="inlineStr">
         <is>
@@ -11442,10 +11682,10 @@
         <v>104</v>
       </c>
       <c r="BL46" s="27" t="n">
-        <v>2.040816</v>
+        <v>2.04</v>
       </c>
       <c r="BM46" s="28" t="n">
-        <v>0.49</v>
+        <v>0.490196</v>
       </c>
       <c r="BN46" s="28" t="n">
         <v>0.487562</v>
@@ -11520,10 +11760,10 @@
         <v>-104</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>1.960784</v>
+        <v>1.961538</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.51</v>
+        <v>0.509804</v>
       </c>
       <c r="O47" s="28" t="n">
         <v>0.550233</v>
@@ -11532,7 +11772,7 @@
         <v>0.05</v>
       </c>
       <c r="Q47" s="28" t="n">
-        <v>0.040233</v>
+        <v>0.040429</v>
       </c>
       <c r="R47" s="26" t="n"/>
       <c r="S47" s="29" t="n">
@@ -11553,14 +11793,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W47" s="26" t="n"/>
-      <c r="X47" s="26" t="n"/>
+      <c r="W47" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X47" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y47" s="25" t="n"/>
       <c r="Z47" s="26" t="n"/>
       <c r="AA47" s="28" t="n"/>
       <c r="AB47" s="28" t="n"/>
       <c r="AC47" s="30" t="n">
-        <v>0.9608</v>
+        <v>0.9615</v>
       </c>
       <c r="AD47" s="24" t="inlineStr">
         <is>
@@ -11611,10 +11855,10 @@
         <v>-104</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>1.960784</v>
+        <v>1.961538</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.51</v>
+        <v>0.509804</v>
       </c>
       <c r="BN47" s="28" t="n">
         <v>0.507463</v>
@@ -11689,10 +11933,10 @@
         <v>120</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>2.197802</v>
+        <v>2.2</v>
       </c>
       <c r="N48" s="28" t="n">
-        <v>0.455</v>
+        <v>0.454545</v>
       </c>
       <c r="O48" s="28" t="n">
         <v>0.530299</v>
@@ -11701,7 +11945,7 @@
         <v>0.05</v>
       </c>
       <c r="Q48" s="28" t="n">
-        <v>0.075299</v>
+        <v>0.075754</v>
       </c>
       <c r="R48" s="26" t="n"/>
       <c r="S48" s="29" t="n">
@@ -11722,8 +11966,12 @@
           <t>loss</t>
         </is>
       </c>
-      <c r="W48" s="26" t="n"/>
-      <c r="X48" s="26" t="n"/>
+      <c r="W48" s="26" t="n">
+        <v>23</v>
+      </c>
+      <c r="X48" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y48" s="25" t="n"/>
       <c r="Z48" s="26" t="n"/>
       <c r="AA48" s="28" t="n"/>
@@ -11780,10 +12028,10 @@
         <v>120</v>
       </c>
       <c r="BL48" s="27" t="n">
-        <v>2.197802</v>
+        <v>2.2</v>
       </c>
       <c r="BM48" s="28" t="n">
-        <v>0.455</v>
+        <v>0.454545</v>
       </c>
       <c r="BN48" s="28" t="n">
         <v>0.452736</v>
@@ -11891,8 +12139,12 @@
           <t>loss</t>
         </is>
       </c>
-      <c r="W49" s="26" t="n"/>
-      <c r="X49" s="26" t="n"/>
+      <c r="W49" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X49" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y49" s="25" t="n"/>
       <c r="Z49" s="26" t="n"/>
       <c r="AA49" s="28" t="n"/>
@@ -12052,18 +12304,32 @@
       </c>
       <c r="U50" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V50" s="24" t="n"/>
-      <c r="W50" s="26" t="n"/>
-      <c r="X50" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V50" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W50" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X50" s="26" t="n">
+        <v>8</v>
+      </c>
       <c r="Y50" s="25" t="n"/>
       <c r="Z50" s="26" t="n"/>
       <c r="AA50" s="28" t="n"/>
       <c r="AB50" s="28" t="n"/>
-      <c r="AC50" s="30" t="n"/>
-      <c r="AD50" s="24" t="n"/>
+      <c r="AC50" s="30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD50" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:46.455580Z</t>
+        </is>
+      </c>
       <c r="AE50" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.4800 (aec-mlb-tex-atl-2026-07-19).</t>
@@ -12301,18 +12567,32 @@
       </c>
       <c r="U51" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V51" s="24" t="n"/>
-      <c r="W51" s="26" t="n"/>
-      <c r="X51" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V51" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W51" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="X51" s="26" t="n">
+        <v>6</v>
+      </c>
       <c r="Y51" s="25" t="n"/>
       <c r="Z51" s="26" t="n"/>
       <c r="AA51" s="28" t="n"/>
       <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="30" t="n"/>
-      <c r="AD51" s="24" t="n"/>
+      <c r="AC51" s="30" t="n">
+        <v>1.1278</v>
+      </c>
+      <c r="AD51" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:46.701705Z</t>
+        </is>
+      </c>
       <c r="AE51" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.5700 (aec-mlb-cin-col-2026-07-19).</t>
@@ -12550,18 +12830,32 @@
       </c>
       <c r="U52" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V52" s="24" t="n"/>
-      <c r="W52" s="26" t="n"/>
-      <c r="X52" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V52" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W52" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X52" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y52" s="25" t="n"/>
       <c r="Z52" s="26" t="n"/>
       <c r="AA52" s="28" t="n"/>
       <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="30" t="n"/>
-      <c r="AD52" s="24" t="n"/>
+      <c r="AC52" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD52" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:12:46.998281Z</t>
+        </is>
+      </c>
       <c r="AE52" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.4350 (aec-mlb-wsh-ath-2026-07-19).</t>
@@ -12574,7 +12868,7 @@
       </c>
       <c r="AG52" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH52" s="24" t="n"/>

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0###"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0###"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,11 +217,38 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -300,8 +327,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA52" headerRowCount="1">
-  <autoFilter ref="A1:CA52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA69" headerRowCount="1">
+  <autoFilter ref="A1:CA69"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -738,22 +765,23 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$52)</f>
+        <f>COUNTA('Picks'!$A$2:$A$69)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$52,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$69,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$69,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")+COUNTIFS('Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$69,"settled",'Picks'!$V$2:$V$69,"win")+COUNTIFS('Picks'!$U$2:$U$69,"settled",'Picks'!$V$2:$V$69,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -778,22 +806,23 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$52,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$69,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$69,"&gt;0",'Picks'!$V$2:$V$69,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$69,"&gt;0",'Picks'!$V$2:$V$69,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")/(COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")+COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"loss")),0)</f>
+      <c r="E7" s="32">
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$69,"&gt;0",'Picks'!$V$2:$V$69,"win")/(COUNTIFS('Picks'!$BX$2:$BX$69,"&gt;0",'Picks'!$V$2:$V$69,"win")+COUNTIFS('Picks'!$BX$2:$BX$69,"&gt;0",'Picks'!$V$2:$V$69,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$52)/SUM('Picks'!$BX$2:$BX$52),0)</f>
+      <c r="G7" s="32">
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$69)/SUM('Picks'!$BX$2:$BX$69),0)</f>
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -817,23 +846,24 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$52)</f>
+      <c r="A10" s="33">
+        <f>SUM('Picks'!$BY$2:$BY$69)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$52,"&lt;&gt;",'Picks'!$AB$2:$AB$52),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$69,"&lt;&gt;",'Picks'!$AB$2:$AB$69),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$52,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$69,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$69,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$52,'Picks'!$AM$2:$AM$52,"QUALIFIED_SHADOW_CALL")</f>
+      <c r="G10" s="33">
+        <f>SUMIFS('Picks'!$AC$2:$AC$69,'Picks'!$AM$2:$AM$69,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -885,27 +915,27 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$69,$A14,'Picks'!$U$2:$U$69,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$69,$A14,'Picks'!$U$2:$U$69,"settled",'Picks'!$V$2:$V$69,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$69,$A14,'Picks'!$U$2:$U$69,"settled",'Picks'!$V$2:$V$69,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="34">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A14)</f>
+      <c r="F14" s="35">
+        <f>SUMIFS('Picks'!$BY$2:$BY$69,'Picks'!$H$2:$H$69,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$69,'Picks'!$H$2:$H$69,$A14,'Picks'!$U$2:$U$69,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -916,27 +946,27 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$69,$A15,'Picks'!$U$2:$U$69,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$69,$A15,'Picks'!$U$2:$U$69,"settled",'Picks'!$V$2:$V$69,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$69,$A15,'Picks'!$U$2:$U$69,"settled",'Picks'!$V$2:$V$69,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="36">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A15)</f>
+      <c r="F15" s="37">
+        <f>SUMIFS('Picks'!$BY$2:$BY$69,'Picks'!$H$2:$H$69,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$69,'Picks'!$H$2:$H$69,$A15,'Picks'!$U$2:$U$69,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -947,30 +977,31 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$69,$A16,'Picks'!$U$2:$U$69,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$69,$A16,'Picks'!$U$2:$U$69,"settled",'Picks'!$V$2:$V$69,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$69,$A16,'Picks'!$U$2:$U$69,"settled",'Picks'!$V$2:$V$69,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="34">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A16)</f>
+      <c r="F16" s="35">
+        <f>SUMIFS('Picks'!$BY$2:$BY$69,'Picks'!$H$2:$H$69,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$69,'Picks'!$H$2:$H$69,$A16,'Picks'!$U$2:$U$69,"settled"),0)</f>
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
@@ -996,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA52"/>
+  <dimension ref="A1:CA69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1523,7 +1554,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="25" t="n"/>
+      <c r="J2" s="38" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1532,7 +1563,7 @@
       <c r="L2" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M2" s="27" t="n">
+      <c r="M2" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1572,11 +1603,11 @@
       <c r="X2" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y2" s="25" t="n"/>
+      <c r="Y2" s="38" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n">
+      <c r="AC2" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1713,11 +1744,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="25" t="n"/>
+      <c r="BJ2" s="38" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL2" s="27" t="n">
+      <c r="BL2" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1727,16 +1758,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n"/>
+      <c r="BP2" s="38" t="n"/>
+      <c r="BQ2" s="39" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="25" t="n"/>
+      <c r="BU2" s="38" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="30" t="n"/>
-      <c r="BY2" s="27" t="n"/>
+      <c r="BX2" s="40" t="n"/>
+      <c r="BY2" s="39" t="n"/>
       <c r="BZ2" s="24" t="n"/>
       <c r="CA2" s="31" t="n"/>
     </row>
@@ -1786,7 +1817,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="25" t="n"/>
+      <c r="J3" s="38" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1795,7 +1826,7 @@
       <c r="L3" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M3" s="27" t="n">
+      <c r="M3" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1835,11 +1866,11 @@
       <c r="X3" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y3" s="25" t="n"/>
+      <c r="Y3" s="38" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n">
+      <c r="AC3" s="40" t="n">
         <v>-1.75</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -1976,11 +2007,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="25" t="n"/>
+      <c r="BJ3" s="38" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL3" s="27" t="n">
+      <c r="BL3" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -1990,16 +2021,16 @@
         <v>0.457711</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
+      <c r="BP3" s="38" t="n"/>
+      <c r="BQ3" s="39" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="25" t="n"/>
+      <c r="BU3" s="38" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="30" t="n"/>
-      <c r="BY3" s="27" t="n"/>
+      <c r="BX3" s="40" t="n"/>
+      <c r="BY3" s="39" t="n"/>
       <c r="BZ3" s="24" t="n"/>
       <c r="CA3" s="31" t="n"/>
     </row>
@@ -2049,7 +2080,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n"/>
+      <c r="J4" s="38" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2058,7 +2089,7 @@
       <c r="L4" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="M4" s="27" t="n">
+      <c r="M4" s="39" t="n">
         <v>1.854701</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2098,11 +2129,11 @@
       <c r="X4" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y4" s="25" t="n"/>
+      <c r="Y4" s="38" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n">
+      <c r="AC4" s="40" t="n">
         <v>0.8547</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2239,11 +2270,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="25" t="n"/>
+      <c r="BJ4" s="38" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="BL4" s="27" t="n">
+      <c r="BL4" s="39" t="n">
         <v>1.854701</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2253,16 +2284,16 @@
         <v>0.537313</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n"/>
+      <c r="BP4" s="38" t="n"/>
+      <c r="BQ4" s="39" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="25" t="n"/>
+      <c r="BU4" s="38" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="30" t="n"/>
-      <c r="BY4" s="27" t="n"/>
+      <c r="BX4" s="40" t="n"/>
+      <c r="BY4" s="39" t="n"/>
       <c r="BZ4" s="24" t="n"/>
       <c r="CA4" s="31" t="n"/>
     </row>
@@ -2312,7 +2343,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="25" t="n"/>
+      <c r="J5" s="38" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2321,7 +2352,7 @@
       <c r="L5" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M5" s="27" t="n">
+      <c r="M5" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2361,11 +2392,11 @@
       <c r="X5" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" s="25" t="n"/>
+      <c r="Y5" s="38" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n">
+      <c r="AC5" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2502,11 +2533,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="25" t="n"/>
+      <c r="BJ5" s="38" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL5" s="27" t="n">
+      <c r="BL5" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2516,16 +2547,16 @@
         <v>0.457711</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
+      <c r="BP5" s="38" t="n"/>
+      <c r="BQ5" s="39" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="25" t="n"/>
+      <c r="BU5" s="38" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="30" t="n"/>
-      <c r="BY5" s="27" t="n"/>
+      <c r="BX5" s="40" t="n"/>
+      <c r="BY5" s="39" t="n"/>
       <c r="BZ5" s="24" t="n"/>
       <c r="CA5" s="31" t="n"/>
     </row>
@@ -2575,7 +2606,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="25" t="n"/>
+      <c r="J6" s="38" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2584,7 +2615,7 @@
       <c r="L6" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M6" s="27" t="n">
+      <c r="M6" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2624,11 +2655,11 @@
       <c r="X6" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y6" s="25" t="n"/>
+      <c r="Y6" s="38" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n">
+      <c r="AC6" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2765,11 +2796,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="25" t="n"/>
+      <c r="BJ6" s="38" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL6" s="27" t="n">
+      <c r="BL6" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2779,16 +2810,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
+      <c r="BP6" s="38" t="n"/>
+      <c r="BQ6" s="39" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="25" t="n"/>
+      <c r="BU6" s="38" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n"/>
-      <c r="BY6" s="27" t="n"/>
+      <c r="BX6" s="40" t="n"/>
+      <c r="BY6" s="39" t="n"/>
       <c r="BZ6" s="24" t="n"/>
       <c r="CA6" s="31" t="n"/>
     </row>
@@ -2838,7 +2869,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J7" s="25" t="n"/>
+      <c r="J7" s="38" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2847,7 +2878,7 @@
       <c r="L7" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="M7" s="27" t="n">
+      <c r="M7" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2887,11 +2918,11 @@
       <c r="X7" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y7" s="25" t="n"/>
+      <c r="Y7" s="38" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n">
+      <c r="AC7" s="40" t="n">
         <v>1.4344</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3028,11 +3059,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="25" t="n"/>
+      <c r="BJ7" s="38" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="BL7" s="27" t="n">
+      <c r="BL7" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3042,16 +3073,16 @@
         <v>0.547264</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
+      <c r="BP7" s="38" t="n"/>
+      <c r="BQ7" s="39" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="25" t="n"/>
+      <c r="BU7" s="38" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="30" t="n"/>
-      <c r="BY7" s="27" t="n"/>
+      <c r="BX7" s="40" t="n"/>
+      <c r="BY7" s="39" t="n"/>
       <c r="BZ7" s="24" t="n"/>
       <c r="CA7" s="31" t="n"/>
     </row>
@@ -3101,7 +3132,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J8" s="25" t="n"/>
+      <c r="J8" s="38" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3110,7 +3141,7 @@
       <c r="L8" s="26" t="n">
         <v>115</v>
       </c>
-      <c r="M8" s="27" t="n">
+      <c r="M8" s="39" t="n">
         <v>2.15</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3150,11 +3181,11 @@
       <c r="X8" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y8" s="25" t="n"/>
+      <c r="Y8" s="38" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n">
+      <c r="AC8" s="40" t="n">
         <v>0.8625</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3291,11 +3322,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="25" t="n"/>
+      <c r="BJ8" s="38" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>115</v>
       </c>
-      <c r="BL8" s="27" t="n">
+      <c r="BL8" s="39" t="n">
         <v>2.15</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3305,16 +3336,16 @@
         <v>0.462687</v>
       </c>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
+      <c r="BP8" s="38" t="n"/>
+      <c r="BQ8" s="39" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="25" t="n"/>
+      <c r="BU8" s="38" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n"/>
-      <c r="BY8" s="27" t="n"/>
+      <c r="BX8" s="40" t="n"/>
+      <c r="BY8" s="39" t="n"/>
       <c r="BZ8" s="24" t="n"/>
       <c r="CA8" s="31" t="n"/>
     </row>
@@ -3364,7 +3395,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J9" s="25" t="n"/>
+      <c r="J9" s="38" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3373,7 +3404,7 @@
       <c r="L9" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M9" s="39" t="n">
         <v>1.666667</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3413,11 +3444,11 @@
       <c r="X9" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y9" s="25" t="n"/>
+      <c r="Y9" s="38" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n">
+      <c r="AC9" s="40" t="n">
         <v>1</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
@@ -3554,11 +3585,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="25" t="n"/>
+      <c r="BJ9" s="38" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="BL9" s="27" t="n">
+      <c r="BL9" s="39" t="n">
         <v>1.666667</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3568,16 +3599,16 @@
         <v>0.597015</v>
       </c>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
+      <c r="BP9" s="38" t="n"/>
+      <c r="BQ9" s="39" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
+      <c r="BU9" s="38" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n"/>
-      <c r="BY9" s="27" t="n"/>
+      <c r="BX9" s="40" t="n"/>
+      <c r="BY9" s="39" t="n"/>
       <c r="BZ9" s="24" t="n"/>
       <c r="CA9" s="31" t="n"/>
     </row>
@@ -3627,7 +3658,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J10" s="25" t="n"/>
+      <c r="J10" s="38" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3636,7 +3667,7 @@
       <c r="L10" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M10" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3676,11 +3707,11 @@
       <c r="X10" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y10" s="25" t="n"/>
+      <c r="Y10" s="38" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n">
+      <c r="AC10" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -3817,11 +3848,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="25" t="n"/>
+      <c r="BJ10" s="38" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL10" s="27" t="n">
+      <c r="BL10" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -3831,16 +3862,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
+      <c r="BP10" s="38" t="n"/>
+      <c r="BQ10" s="39" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
+      <c r="BU10" s="38" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n"/>
-      <c r="BY10" s="27" t="n"/>
+      <c r="BX10" s="40" t="n"/>
+      <c r="BY10" s="39" t="n"/>
       <c r="BZ10" s="24" t="n"/>
       <c r="CA10" s="31" t="n"/>
     </row>
@@ -3890,7 +3921,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J11" s="25" t="n"/>
+      <c r="J11" s="38" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3899,7 +3930,7 @@
       <c r="L11" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="M11" s="27" t="n">
+      <c r="M11" s="39" t="n">
         <v>1.613497</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -3939,11 +3970,11 @@
       <c r="X11" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y11" s="25" t="n"/>
+      <c r="Y11" s="38" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n">
+      <c r="AC11" s="40" t="n">
         <v>0.9202</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4080,11 +4111,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="25" t="n"/>
+      <c r="BJ11" s="38" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="BL11" s="27" t="n">
+      <c r="BL11" s="39" t="n">
         <v>1.613497</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4094,16 +4125,16 @@
         <v>0.616915</v>
       </c>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
+      <c r="BP11" s="38" t="n"/>
+      <c r="BQ11" s="39" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
+      <c r="BU11" s="38" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n"/>
-      <c r="BY11" s="27" t="n"/>
+      <c r="BX11" s="40" t="n"/>
+      <c r="BY11" s="39" t="n"/>
       <c r="BZ11" s="24" t="n"/>
       <c r="CA11" s="31" t="n"/>
     </row>
@@ -4153,7 +4184,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="25" t="n"/>
+      <c r="J12" s="38" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4162,7 +4193,7 @@
       <c r="L12" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M12" s="27" t="n">
+      <c r="M12" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4188,18 +4219,32 @@
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
-      <c r="Y12" s="25" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="38" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="AC12" s="40" t="n">
+        <v>0.6757</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:51:12.968396Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.5250 (aec-mlb-stl-az-2026-07-19).</t>
@@ -4329,11 +4374,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="25" t="n"/>
+      <c r="BJ12" s="38" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL12" s="27" t="n">
+      <c r="BL12" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4343,16 +4388,16 @@
         <v>0.522388</v>
       </c>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
+      <c r="BP12" s="38" t="n"/>
+      <c r="BQ12" s="39" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
+      <c r="BU12" s="38" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n"/>
-      <c r="BY12" s="27" t="n"/>
+      <c r="BX12" s="40" t="n"/>
+      <c r="BY12" s="39" t="n"/>
       <c r="BZ12" s="24" t="n"/>
       <c r="CA12" s="31" t="n"/>
     </row>
@@ -4402,7 +4447,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J13" s="25" t="n"/>
+      <c r="J13" s="38" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4411,7 +4456,7 @@
       <c r="L13" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M13" s="27" t="n">
+      <c r="M13" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4437,18 +4482,32 @@
       </c>
       <c r="U13" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
-      <c r="Y13" s="25" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" s="38" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
+      <c r="AC13" s="40" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:21.588181Z</t>
+        </is>
+      </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.5200 (aec-mlb-lad-nyy-2026-07-19).</t>
@@ -4461,7 +4520,7 @@
       </c>
       <c r="AG13" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH13" s="24" t="n"/>
@@ -4578,11 +4637,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="25" t="n"/>
+      <c r="BJ13" s="38" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL13" s="27" t="n">
+      <c r="BL13" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4592,16 +4651,16 @@
         <v>0.517413</v>
       </c>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
+      <c r="BP13" s="38" t="n"/>
+      <c r="BQ13" s="39" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
+      <c r="BU13" s="38" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n"/>
-      <c r="BY13" s="27" t="n"/>
+      <c r="BX13" s="40" t="n"/>
+      <c r="BY13" s="39" t="n"/>
       <c r="BZ13" s="24" t="n"/>
       <c r="CA13" s="31" t="n"/>
     </row>
@@ -4651,7 +4710,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n"/>
+      <c r="J14" s="38" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4660,7 +4719,7 @@
       <c r="L14" s="26" t="n">
         <v>-400</v>
       </c>
-      <c r="M14" s="27" t="n">
+      <c r="M14" s="39" t="n">
         <v>1.25</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -4700,11 +4759,11 @@
       <c r="X14" s="26" t="n">
         <v>90</v>
       </c>
-      <c r="Y14" s="25" t="n"/>
+      <c r="Y14" s="38" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n">
+      <c r="AC14" s="40" t="n">
         <v>0.5</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -4841,11 +4900,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="25" t="n"/>
+      <c r="BJ14" s="38" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-400</v>
       </c>
-      <c r="BL14" s="27" t="n">
+      <c r="BL14" s="39" t="n">
         <v>1.25</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -4855,16 +4914,16 @@
         <v>0.792079</v>
       </c>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
+      <c r="BP14" s="38" t="n"/>
+      <c r="BQ14" s="39" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="25" t="n"/>
+      <c r="BU14" s="38" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n"/>
-      <c r="BY14" s="27" t="n"/>
+      <c r="BX14" s="40" t="n"/>
+      <c r="BY14" s="39" t="n"/>
       <c r="BZ14" s="24" t="n"/>
       <c r="CA14" s="31" t="n"/>
     </row>
@@ -4914,7 +4973,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="25" t="n"/>
+      <c r="J15" s="38" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4923,7 +4982,7 @@
       <c r="L15" s="26" t="n">
         <v>-426</v>
       </c>
-      <c r="M15" s="27" t="n">
+      <c r="M15" s="39" t="n">
         <v>1.234742</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -4963,11 +5022,11 @@
       <c r="X15" s="26" t="n">
         <v>93</v>
       </c>
-      <c r="Y15" s="25" t="n"/>
+      <c r="Y15" s="38" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n">
+      <c r="AC15" s="40" t="n">
         <v>0.4695</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
@@ -5104,11 +5163,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="25" t="n"/>
+      <c r="BJ15" s="38" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-426</v>
       </c>
-      <c r="BL15" s="27" t="n">
+      <c r="BL15" s="39" t="n">
         <v>1.234742</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5118,16 +5177,16 @@
         <v>0.80198</v>
       </c>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
+      <c r="BP15" s="38" t="n"/>
+      <c r="BQ15" s="39" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
+      <c r="BU15" s="38" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n"/>
-      <c r="BY15" s="27" t="n"/>
+      <c r="BX15" s="40" t="n"/>
+      <c r="BY15" s="39" t="n"/>
       <c r="BZ15" s="24" t="n"/>
       <c r="CA15" s="31" t="n"/>
     </row>
@@ -5177,7 +5236,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n"/>
+      <c r="J16" s="38" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5186,7 +5245,7 @@
       <c r="L16" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="M16" s="27" t="n">
+      <c r="M16" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5212,18 +5271,32 @@
       </c>
       <c r="U16" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
-      <c r="Y16" s="25" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>63</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>72</v>
+      </c>
+      <c r="Y16" s="38" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
+      <c r="AC16" s="40" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:22.185310Z</t>
+        </is>
+      </c>
       <c r="AE16" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5000; executable ask 0.6100 (aec-wnba-conn-phx-2026-07-19).</t>
@@ -5353,11 +5426,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="25" t="n"/>
+      <c r="BJ16" s="38" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="BL16" s="27" t="n">
+      <c r="BL16" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5367,16 +5440,16 @@
         <v>0.6039600000000001</v>
       </c>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
+      <c r="BP16" s="38" t="n"/>
+      <c r="BQ16" s="39" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
+      <c r="BU16" s="38" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n"/>
-      <c r="BY16" s="27" t="n"/>
+      <c r="BX16" s="40" t="n"/>
+      <c r="BY16" s="39" t="n"/>
       <c r="BZ16" s="24" t="n"/>
       <c r="CA16" s="31" t="n"/>
     </row>
@@ -5426,7 +5499,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n"/>
+      <c r="J17" s="38" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5435,7 +5508,7 @@
       <c r="L17" s="26" t="n">
         <v>-354</v>
       </c>
-      <c r="M17" s="27" t="n">
+      <c r="M17" s="39" t="n">
         <v>1.282486</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5473,11 +5546,11 @@
       <c r="X17" s="26" t="n">
         <v>110</v>
       </c>
-      <c r="Y17" s="25" t="n"/>
+      <c r="Y17" s="38" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n">
+      <c r="AC17" s="40" t="n">
         <v>0.4944</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
@@ -5538,11 +5611,11 @@
       <c r="BG17" s="24" t="n"/>
       <c r="BH17" s="24" t="n"/>
       <c r="BI17" s="24" t="n"/>
-      <c r="BJ17" s="25" t="n"/>
+      <c r="BJ17" s="38" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-354</v>
       </c>
-      <c r="BL17" s="27" t="n">
+      <c r="BL17" s="39" t="n">
         <v>1.282486</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -5552,16 +5625,16 @@
         <v>0.779736</v>
       </c>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
+      <c r="BP17" s="38" t="n"/>
+      <c r="BQ17" s="39" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
+      <c r="BU17" s="38" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n"/>
-      <c r="BY17" s="27" t="n"/>
+      <c r="BX17" s="40" t="n"/>
+      <c r="BY17" s="39" t="n"/>
       <c r="BZ17" s="24" t="n"/>
       <c r="CA17" s="31" t="n"/>
     </row>
@@ -5611,7 +5684,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n"/>
+      <c r="J18" s="38" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -5620,7 +5693,7 @@
       <c r="L18" s="26" t="n">
         <v>-194</v>
       </c>
-      <c r="M18" s="27" t="n">
+      <c r="M18" s="39" t="n">
         <v>1.515464</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -5660,11 +5733,11 @@
       <c r="X18" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y18" s="25" t="n"/>
+      <c r="Y18" s="38" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n">
+      <c r="AC18" s="40" t="n">
         <v>0.6443</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
@@ -5711,11 +5784,11 @@
         </is>
       </c>
       <c r="BI18" s="24" t="n"/>
-      <c r="BJ18" s="25" t="n"/>
+      <c r="BJ18" s="38" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>-194</v>
       </c>
-      <c r="BL18" s="27" t="n">
+      <c r="BL18" s="39" t="n">
         <v>1.515464</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -5725,16 +5798,16 @@
         <v>0.656716</v>
       </c>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
+      <c r="BP18" s="38" t="n"/>
+      <c r="BQ18" s="39" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
+      <c r="BU18" s="38" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n"/>
-      <c r="BY18" s="27" t="n"/>
+      <c r="BX18" s="40" t="n"/>
+      <c r="BY18" s="39" t="n"/>
       <c r="BZ18" s="24" t="n"/>
       <c r="CA18" s="31" t="n"/>
     </row>
@@ -5784,7 +5857,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n"/>
+      <c r="J19" s="38" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -5793,7 +5866,7 @@
       <c r="L19" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="M19" s="27" t="n">
+      <c r="M19" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -5833,11 +5906,11 @@
       <c r="X19" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y19" s="25" t="n"/>
+      <c r="Y19" s="38" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n">
+      <c r="AC19" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
@@ -5884,11 +5957,11 @@
         </is>
       </c>
       <c r="BI19" s="24" t="n"/>
-      <c r="BJ19" s="25" t="n"/>
+      <c r="BJ19" s="38" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="BL19" s="27" t="n">
+      <c r="BL19" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -5898,16 +5971,16 @@
         <v>0.547264</v>
       </c>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
+      <c r="BP19" s="38" t="n"/>
+      <c r="BQ19" s="39" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="25" t="n"/>
+      <c r="BU19" s="38" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="30" t="n"/>
-      <c r="BY19" s="27" t="n"/>
+      <c r="BX19" s="40" t="n"/>
+      <c r="BY19" s="39" t="n"/>
       <c r="BZ19" s="24" t="n"/>
       <c r="CA19" s="31" t="n"/>
     </row>
@@ -5957,7 +6030,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J20" s="25" t="n"/>
+      <c r="J20" s="38" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -5966,7 +6039,7 @@
       <c r="L20" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M20" s="27" t="n">
+      <c r="M20" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6006,11 +6079,11 @@
       <c r="X20" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y20" s="25" t="n"/>
+      <c r="Y20" s="38" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n">
+      <c r="AC20" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
@@ -6057,11 +6130,11 @@
         </is>
       </c>
       <c r="BI20" s="24" t="n"/>
-      <c r="BJ20" s="25" t="n"/>
+      <c r="BJ20" s="38" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL20" s="27" t="n">
+      <c r="BL20" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -6071,16 +6144,16 @@
         <v>0.527363</v>
       </c>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
+      <c r="BP20" s="38" t="n"/>
+      <c r="BQ20" s="39" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="25" t="n"/>
+      <c r="BU20" s="38" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="30" t="n"/>
-      <c r="BY20" s="27" t="n"/>
+      <c r="BX20" s="40" t="n"/>
+      <c r="BY20" s="39" t="n"/>
       <c r="BZ20" s="24" t="n"/>
       <c r="CA20" s="31" t="n"/>
     </row>
@@ -6130,7 +6203,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J21" s="25" t="n"/>
+      <c r="J21" s="38" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6139,7 +6212,7 @@
       <c r="L21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M21" s="27" t="n">
+      <c r="M21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
@@ -6179,11 +6252,11 @@
       <c r="X21" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y21" s="25" t="n"/>
+      <c r="Y21" s="38" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n">
+      <c r="AC21" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
@@ -6230,11 +6303,11 @@
         </is>
       </c>
       <c r="BI21" s="24" t="n"/>
-      <c r="BJ21" s="25" t="n"/>
+      <c r="BJ21" s="38" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL21" s="27" t="n">
+      <c r="BL21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
@@ -6244,16 +6317,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
+      <c r="BP21" s="38" t="n"/>
+      <c r="BQ21" s="39" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
+      <c r="BU21" s="38" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
+      <c r="BX21" s="40" t="n"/>
+      <c r="BY21" s="39" t="n"/>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
     </row>
@@ -6303,7 +6376,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="25" t="n"/>
+      <c r="J22" s="38" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6312,7 +6385,7 @@
       <c r="L22" s="26" t="n">
         <v>-174</v>
       </c>
-      <c r="M22" s="27" t="n">
+      <c r="M22" s="39" t="n">
         <v>1.574713</v>
       </c>
       <c r="N22" s="28" t="n">
@@ -6352,11 +6425,11 @@
       <c r="X22" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y22" s="25" t="n"/>
+      <c r="Y22" s="38" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n">
+      <c r="AC22" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
@@ -6403,11 +6476,11 @@
         </is>
       </c>
       <c r="BI22" s="24" t="n"/>
-      <c r="BJ22" s="25" t="n"/>
+      <c r="BJ22" s="38" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-174</v>
       </c>
-      <c r="BL22" s="27" t="n">
+      <c r="BL22" s="39" t="n">
         <v>1.574713</v>
       </c>
       <c r="BM22" s="28" t="n">
@@ -6417,16 +6490,16 @@
         <v>0.631841</v>
       </c>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
+      <c r="BP22" s="38" t="n"/>
+      <c r="BQ22" s="39" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
+      <c r="BU22" s="38" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
+      <c r="BX22" s="40" t="n"/>
+      <c r="BY22" s="39" t="n"/>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
     </row>
@@ -6476,7 +6549,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J23" s="25" t="n"/>
+      <c r="J23" s="38" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6485,7 +6558,7 @@
       <c r="L23" s="26" t="n">
         <v>-376</v>
       </c>
-      <c r="M23" s="27" t="n">
+      <c r="M23" s="39" t="n">
         <v>1.265957</v>
       </c>
       <c r="N23" s="28" t="n">
@@ -6525,11 +6598,11 @@
       <c r="X23" s="26" t="n">
         <v>92</v>
       </c>
-      <c r="Y23" s="25" t="n"/>
+      <c r="Y23" s="38" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n">
+      <c r="AC23" s="40" t="n">
         <v>0.1995</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
@@ -6576,11 +6649,11 @@
         </is>
       </c>
       <c r="BI23" s="24" t="n"/>
-      <c r="BJ23" s="25" t="n"/>
+      <c r="BJ23" s="38" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-376</v>
       </c>
-      <c r="BL23" s="27" t="n">
+      <c r="BL23" s="39" t="n">
         <v>1.265957</v>
       </c>
       <c r="BM23" s="28" t="n">
@@ -6590,16 +6663,16 @@
         <v>0.782178</v>
       </c>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
+      <c r="BP23" s="38" t="n"/>
+      <c r="BQ23" s="39" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
+      <c r="BU23" s="38" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
+      <c r="BX23" s="40" t="n"/>
+      <c r="BY23" s="39" t="n"/>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
     </row>
@@ -6649,7 +6722,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="25" t="n"/>
+      <c r="J24" s="38" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6658,7 +6731,7 @@
       <c r="L24" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M24" s="27" t="n">
+      <c r="M24" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="N24" s="28" t="n">
@@ -6698,11 +6771,11 @@
       <c r="X24" s="26" t="n">
         <v>96</v>
       </c>
-      <c r="Y24" s="25" t="n"/>
+      <c r="Y24" s="38" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n">
+      <c r="AC24" s="40" t="n">
         <v>0.4425</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -6749,11 +6822,11 @@
         </is>
       </c>
       <c r="BI24" s="24" t="n"/>
-      <c r="BJ24" s="25" t="n"/>
+      <c r="BJ24" s="38" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL24" s="27" t="n">
+      <c r="BL24" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM24" s="28" t="n">
@@ -6763,16 +6836,16 @@
         <v>0.524752</v>
       </c>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
+      <c r="BP24" s="38" t="n"/>
+      <c r="BQ24" s="39" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="25" t="n"/>
+      <c r="BU24" s="38" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="30" t="n"/>
-      <c r="BY24" s="27" t="n"/>
+      <c r="BX24" s="40" t="n"/>
+      <c r="BY24" s="39" t="n"/>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
     </row>
@@ -6822,7 +6895,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J25" s="25" t="n"/>
+      <c r="J25" s="38" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6831,7 +6904,7 @@
       <c r="L25" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="M25" s="27" t="n">
+      <c r="M25" s="39" t="n">
         <v>1.561798</v>
       </c>
       <c r="N25" s="28" t="n">
@@ -6871,11 +6944,11 @@
       <c r="X25" s="26" t="n">
         <v>83</v>
       </c>
-      <c r="Y25" s="25" t="n"/>
+      <c r="Y25" s="38" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n">
+      <c r="AC25" s="40" t="n">
         <v>-2</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
@@ -6922,11 +6995,11 @@
         </is>
       </c>
       <c r="BI25" s="24" t="n"/>
-      <c r="BJ25" s="25" t="n"/>
+      <c r="BJ25" s="38" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="BL25" s="27" t="n">
+      <c r="BL25" s="39" t="n">
         <v>1.561798</v>
       </c>
       <c r="BM25" s="28" t="n">
@@ -6936,16 +7009,16 @@
         <v>0.633663</v>
       </c>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
+      <c r="BP25" s="38" t="n"/>
+      <c r="BQ25" s="39" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="25" t="n"/>
+      <c r="BU25" s="38" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="30" t="n"/>
-      <c r="BY25" s="27" t="n"/>
+      <c r="BX25" s="40" t="n"/>
+      <c r="BY25" s="39" t="n"/>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
     </row>
@@ -6995,7 +7068,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J26" s="25" t="n"/>
+      <c r="J26" s="38" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7004,7 +7077,7 @@
       <c r="L26" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="M26" s="27" t="n">
+      <c r="M26" s="39" t="n">
         <v>1.613497</v>
       </c>
       <c r="N26" s="28" t="n">
@@ -7044,11 +7117,11 @@
       <c r="X26" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y26" s="25" t="n"/>
+      <c r="Y26" s="38" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n">
+      <c r="AC26" s="40" t="n">
         <v>0.9202</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
@@ -7095,11 +7168,11 @@
         </is>
       </c>
       <c r="BI26" s="24" t="n"/>
-      <c r="BJ26" s="25" t="n"/>
+      <c r="BJ26" s="38" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="BL26" s="27" t="n">
+      <c r="BL26" s="39" t="n">
         <v>1.613497</v>
       </c>
       <c r="BM26" s="28" t="n">
@@ -7109,16 +7182,16 @@
         <v>0.616915</v>
       </c>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
+      <c r="BP26" s="38" t="n"/>
+      <c r="BQ26" s="39" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="25" t="n"/>
+      <c r="BU26" s="38" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="30" t="n"/>
-      <c r="BY26" s="27" t="n"/>
+      <c r="BX26" s="40" t="n"/>
+      <c r="BY26" s="39" t="n"/>
       <c r="BZ26" s="24" t="n"/>
       <c r="CA26" s="31" t="n"/>
     </row>
@@ -7168,7 +7241,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="25" t="n"/>
+      <c r="J27" s="38" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7177,7 +7250,7 @@
       <c r="L27" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M27" s="27" t="n">
+      <c r="M27" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="N27" s="28" t="n">
@@ -7217,11 +7290,11 @@
       <c r="X27" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y27" s="25" t="n"/>
+      <c r="Y27" s="38" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n">
+      <c r="AC27" s="40" t="n">
         <v>0.6757</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
@@ -7268,11 +7341,11 @@
         </is>
       </c>
       <c r="BI27" s="24" t="n"/>
-      <c r="BJ27" s="25" t="n"/>
+      <c r="BJ27" s="38" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL27" s="27" t="n">
+      <c r="BL27" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM27" s="28" t="n">
@@ -7282,16 +7355,16 @@
         <v>0.522388</v>
       </c>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
+      <c r="BP27" s="38" t="n"/>
+      <c r="BQ27" s="39" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="25" t="n"/>
+      <c r="BU27" s="38" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="30" t="n"/>
-      <c r="BY27" s="27" t="n"/>
+      <c r="BX27" s="40" t="n"/>
+      <c r="BY27" s="39" t="n"/>
       <c r="BZ27" s="24" t="n"/>
       <c r="CA27" s="31" t="n"/>
     </row>
@@ -7341,7 +7414,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="25" t="n"/>
+      <c r="J28" s="38" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7350,7 +7423,7 @@
       <c r="L28" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M28" s="27" t="n">
+      <c r="M28" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -7390,11 +7463,11 @@
       <c r="X28" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="25" t="n"/>
+      <c r="Y28" s="38" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n">
+      <c r="AC28" s="40" t="n">
         <v>1.087</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
@@ -7441,11 +7514,11 @@
         </is>
       </c>
       <c r="BI28" s="24" t="n"/>
-      <c r="BJ28" s="25" t="n"/>
+      <c r="BJ28" s="38" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL28" s="27" t="n">
+      <c r="BL28" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -7455,16 +7528,16 @@
         <v>0.577114</v>
       </c>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
+      <c r="BP28" s="38" t="n"/>
+      <c r="BQ28" s="39" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="25" t="n"/>
+      <c r="BU28" s="38" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="30" t="n"/>
-      <c r="BY28" s="27" t="n"/>
+      <c r="BX28" s="40" t="n"/>
+      <c r="BY28" s="39" t="n"/>
       <c r="BZ28" s="24" t="n"/>
       <c r="CA28" s="31" t="n"/>
     </row>
@@ -7514,7 +7587,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J29" s="25" t="n"/>
+      <c r="J29" s="38" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7523,7 +7596,7 @@
       <c r="L29" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="M29" s="27" t="n">
+      <c r="M29" s="39" t="n">
         <v>1.561798</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -7563,11 +7636,11 @@
       <c r="X29" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y29" s="25" t="n"/>
+      <c r="Y29" s="38" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n">
+      <c r="AC29" s="40" t="n">
         <v>0.5618</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
@@ -7614,11 +7687,11 @@
         </is>
       </c>
       <c r="BI29" s="24" t="n"/>
-      <c r="BJ29" s="25" t="n"/>
+      <c r="BJ29" s="38" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="BL29" s="27" t="n">
+      <c r="BL29" s="39" t="n">
         <v>1.561798</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -7628,16 +7701,16 @@
         <v>0.636816</v>
       </c>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="25" t="n"/>
-      <c r="BQ29" s="27" t="n"/>
+      <c r="BP29" s="38" t="n"/>
+      <c r="BQ29" s="39" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="25" t="n"/>
+      <c r="BU29" s="38" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="30" t="n"/>
-      <c r="BY29" s="27" t="n"/>
+      <c r="BX29" s="40" t="n"/>
+      <c r="BY29" s="39" t="n"/>
       <c r="BZ29" s="24" t="n"/>
       <c r="CA29" s="31" t="n"/>
     </row>
@@ -7687,7 +7760,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J30" s="25" t="n"/>
+      <c r="J30" s="38" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7696,7 +7769,7 @@
       <c r="L30" s="26" t="n">
         <v>-669</v>
       </c>
-      <c r="M30" s="27" t="n">
+      <c r="M30" s="39" t="n">
         <v>1.149477</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -7736,11 +7809,11 @@
       <c r="X30" s="26" t="n">
         <v>101</v>
       </c>
-      <c r="Y30" s="25" t="n"/>
+      <c r="Y30" s="38" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n">
+      <c r="AC30" s="40" t="n">
         <v>0.299</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
@@ -7787,11 +7860,11 @@
         </is>
       </c>
       <c r="BI30" s="24" t="n"/>
-      <c r="BJ30" s="25" t="n"/>
+      <c r="BJ30" s="38" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-669</v>
       </c>
-      <c r="BL30" s="27" t="n">
+      <c r="BL30" s="39" t="n">
         <v>1.149477</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -7801,16 +7874,16 @@
         <v>0.861386</v>
       </c>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
+      <c r="BP30" s="38" t="n"/>
+      <c r="BQ30" s="39" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="25" t="n"/>
+      <c r="BU30" s="38" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="30" t="n"/>
-      <c r="BY30" s="27" t="n"/>
+      <c r="BX30" s="40" t="n"/>
+      <c r="BY30" s="39" t="n"/>
       <c r="BZ30" s="24" t="n"/>
       <c r="CA30" s="31" t="n"/>
     </row>
@@ -7860,7 +7933,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="25" t="n"/>
+      <c r="J31" s="38" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7869,7 +7942,7 @@
       <c r="L31" s="26" t="n">
         <v>-355</v>
       </c>
-      <c r="M31" s="27" t="n">
+      <c r="M31" s="39" t="n">
         <v>1.28169</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -7909,11 +7982,11 @@
       <c r="X31" s="26" t="n">
         <v>74</v>
       </c>
-      <c r="Y31" s="25" t="n"/>
+      <c r="Y31" s="38" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n">
+      <c r="AC31" s="40" t="n">
         <v>0.5634</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
@@ -7960,11 +8033,11 @@
         </is>
       </c>
       <c r="BI31" s="24" t="n"/>
-      <c r="BJ31" s="25" t="n"/>
+      <c r="BJ31" s="38" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>-355</v>
       </c>
-      <c r="BL31" s="27" t="n">
+      <c r="BL31" s="39" t="n">
         <v>1.28169</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -7974,16 +8047,16 @@
         <v>0.772277</v>
       </c>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="25" t="n"/>
-      <c r="BQ31" s="27" t="n"/>
+      <c r="BP31" s="38" t="n"/>
+      <c r="BQ31" s="39" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="25" t="n"/>
+      <c r="BU31" s="38" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="30" t="n"/>
-      <c r="BY31" s="27" t="n"/>
+      <c r="BX31" s="40" t="n"/>
+      <c r="BY31" s="39" t="n"/>
       <c r="BZ31" s="24" t="n"/>
       <c r="CA31" s="31" t="n"/>
     </row>
@@ -8033,7 +8106,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J32" s="25" t="n"/>
+      <c r="J32" s="38" t="n"/>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8042,7 +8115,7 @@
       <c r="L32" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M32" s="27" t="n">
+      <c r="M32" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="N32" s="28" t="n">
@@ -8082,11 +8155,11 @@
       <c r="X32" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="Y32" s="25" t="n"/>
+      <c r="Y32" s="38" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n">
+      <c r="AC32" s="40" t="n">
         <v>1.755</v>
       </c>
       <c r="AD32" s="24" t="inlineStr">
@@ -8223,11 +8296,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ32" s="25" t="n"/>
+      <c r="BJ32" s="38" t="n"/>
       <c r="BK32" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL32" s="27" t="n">
+      <c r="BL32" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="BM32" s="28" t="n">
@@ -8237,18 +8310,18 @@
         <v>0.455446</v>
       </c>
       <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="25" t="n"/>
-      <c r="BQ32" s="27" t="n"/>
+      <c r="BP32" s="38" t="n"/>
+      <c r="BQ32" s="39" t="n"/>
       <c r="BR32" s="28" t="n"/>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="25" t="n"/>
+      <c r="BU32" s="38" t="n"/>
       <c r="BV32" s="29" t="n"/>
       <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="30" t="n">
+      <c r="BX32" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY32" s="27" t="n">
+      <c r="BY32" s="39" t="n">
         <v>1.17</v>
       </c>
       <c r="BZ32" s="24" t="inlineStr">
@@ -8308,7 +8381,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J33" s="25" t="n"/>
+      <c r="J33" s="38" t="n"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8317,7 +8390,7 @@
       <c r="L33" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M33" s="27" t="n">
+      <c r="M33" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N33" s="28" t="n">
@@ -8357,11 +8430,11 @@
       <c r="X33" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y33" s="25" t="n"/>
+      <c r="Y33" s="38" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="30" t="n">
+      <c r="AC33" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD33" s="24" t="inlineStr">
@@ -8498,11 +8571,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ33" s="25" t="n"/>
+      <c r="BJ33" s="38" t="n"/>
       <c r="BK33" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL33" s="27" t="n">
+      <c r="BL33" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM33" s="28" t="n">
@@ -8512,18 +8585,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="25" t="n"/>
-      <c r="BQ33" s="27" t="n"/>
+      <c r="BP33" s="38" t="n"/>
+      <c r="BQ33" s="39" t="n"/>
       <c r="BR33" s="28" t="n"/>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="25" t="n"/>
+      <c r="BU33" s="38" t="n"/>
       <c r="BV33" s="29" t="n"/>
       <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="30" t="n">
+      <c r="BX33" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY33" s="27" t="n">
+      <c r="BY33" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ33" s="24" t="inlineStr">
@@ -8583,7 +8656,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J34" s="25" t="n"/>
+      <c r="J34" s="38" t="n"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8592,7 +8665,7 @@
       <c r="L34" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M34" s="27" t="n">
+      <c r="M34" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N34" s="28" t="n">
@@ -8632,11 +8705,11 @@
       <c r="X34" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y34" s="25" t="n"/>
+      <c r="Y34" s="38" t="n"/>
       <c r="Z34" s="26" t="n"/>
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="30" t="n">
+      <c r="AC34" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD34" s="24" t="inlineStr">
@@ -8773,11 +8846,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ34" s="25" t="n"/>
+      <c r="BJ34" s="38" t="n"/>
       <c r="BK34" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL34" s="27" t="n">
+      <c r="BL34" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM34" s="28" t="n">
@@ -8787,18 +8860,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="25" t="n"/>
-      <c r="BQ34" s="27" t="n"/>
+      <c r="BP34" s="38" t="n"/>
+      <c r="BQ34" s="39" t="n"/>
       <c r="BR34" s="28" t="n"/>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="25" t="n"/>
+      <c r="BU34" s="38" t="n"/>
       <c r="BV34" s="29" t="n"/>
       <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="30" t="n">
+      <c r="BX34" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY34" s="27" t="n">
+      <c r="BY34" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ34" s="24" t="inlineStr">
@@ -8858,7 +8931,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J35" s="25" t="n"/>
+      <c r="J35" s="38" t="n"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8867,7 +8940,7 @@
       <c r="L35" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M35" s="27" t="n">
+      <c r="M35" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N35" s="28" t="n">
@@ -8907,11 +8980,11 @@
       <c r="X35" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y35" s="25" t="n"/>
+      <c r="Y35" s="38" t="n"/>
       <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="30" t="n">
+      <c r="AC35" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD35" s="24" t="inlineStr">
@@ -9048,11 +9121,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ35" s="25" t="n"/>
+      <c r="BJ35" s="38" t="n"/>
       <c r="BK35" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL35" s="27" t="n">
+      <c r="BL35" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM35" s="28" t="n">
@@ -9062,18 +9135,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="25" t="n"/>
-      <c r="BQ35" s="27" t="n"/>
+      <c r="BP35" s="38" t="n"/>
+      <c r="BQ35" s="39" t="n"/>
       <c r="BR35" s="28" t="n"/>
       <c r="BS35" s="28" t="n"/>
       <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="25" t="n"/>
+      <c r="BU35" s="38" t="n"/>
       <c r="BV35" s="29" t="n"/>
       <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="30" t="n">
+      <c r="BX35" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY35" s="27" t="n">
+      <c r="BY35" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ35" s="24" t="inlineStr">
@@ -9133,7 +9206,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J36" s="25" t="n"/>
+      <c r="J36" s="38" t="n"/>
       <c r="K36" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9142,7 +9215,7 @@
       <c r="L36" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M36" s="27" t="n">
+      <c r="M36" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N36" s="28" t="n">
@@ -9182,11 +9255,11 @@
       <c r="X36" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y36" s="25" t="n"/>
+      <c r="Y36" s="38" t="n"/>
       <c r="Z36" s="26" t="n"/>
       <c r="AA36" s="28" t="n"/>
       <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="30" t="n">
+      <c r="AC36" s="40" t="n">
         <v>1.2019</v>
       </c>
       <c r="AD36" s="24" t="inlineStr">
@@ -9323,11 +9396,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ36" s="25" t="n"/>
+      <c r="BJ36" s="38" t="n"/>
       <c r="BK36" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL36" s="27" t="n">
+      <c r="BL36" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM36" s="28" t="n">
@@ -9337,18 +9410,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="25" t="n"/>
-      <c r="BQ36" s="27" t="n"/>
+      <c r="BP36" s="38" t="n"/>
+      <c r="BQ36" s="39" t="n"/>
       <c r="BR36" s="28" t="n"/>
       <c r="BS36" s="28" t="n"/>
       <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="25" t="n"/>
+      <c r="BU36" s="38" t="n"/>
       <c r="BV36" s="29" t="n"/>
       <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="30" t="n">
+      <c r="BX36" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY36" s="27" t="n">
+      <c r="BY36" s="39" t="n">
         <v>0.961538</v>
       </c>
       <c r="BZ36" s="24" t="inlineStr">
@@ -9408,7 +9481,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J37" s="25" t="n"/>
+      <c r="J37" s="38" t="n"/>
       <c r="K37" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9417,7 +9490,7 @@
       <c r="L37" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M37" s="27" t="n">
+      <c r="M37" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N37" s="28" t="n">
@@ -9457,11 +9530,11 @@
       <c r="X37" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y37" s="25" t="n"/>
+      <c r="Y37" s="38" t="n"/>
       <c r="Z37" s="26" t="n"/>
       <c r="AA37" s="28" t="n"/>
       <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="30" t="n">
+      <c r="AC37" s="40" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD37" s="24" t="inlineStr">
@@ -9598,11 +9671,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ37" s="25" t="n"/>
+      <c r="BJ37" s="38" t="n"/>
       <c r="BK37" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL37" s="27" t="n">
+      <c r="BL37" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM37" s="28" t="n">
@@ -9612,18 +9685,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="25" t="n"/>
-      <c r="BQ37" s="27" t="n"/>
+      <c r="BP37" s="38" t="n"/>
+      <c r="BQ37" s="39" t="n"/>
       <c r="BR37" s="28" t="n"/>
       <c r="BS37" s="28" t="n"/>
       <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="25" t="n"/>
+      <c r="BU37" s="38" t="n"/>
       <c r="BV37" s="29" t="n"/>
       <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="30" t="n">
+      <c r="BX37" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY37" s="27" t="n">
+      <c r="BY37" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ37" s="24" t="inlineStr">
@@ -9683,7 +9756,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J38" s="25" t="n"/>
+      <c r="J38" s="38" t="n"/>
       <c r="K38" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9692,7 +9765,7 @@
       <c r="L38" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M38" s="27" t="n">
+      <c r="M38" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N38" s="28" t="n">
@@ -9732,11 +9805,11 @@
       <c r="X38" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y38" s="25" t="n"/>
+      <c r="Y38" s="38" t="n"/>
       <c r="Z38" s="26" t="n"/>
       <c r="AA38" s="28" t="n"/>
       <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="30" t="n">
+      <c r="AC38" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD38" s="24" t="inlineStr">
@@ -9873,11 +9946,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ38" s="25" t="n"/>
+      <c r="BJ38" s="38" t="n"/>
       <c r="BK38" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL38" s="27" t="n">
+      <c r="BL38" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM38" s="28" t="n">
@@ -9887,18 +9960,18 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="25" t="n"/>
-      <c r="BQ38" s="27" t="n"/>
+      <c r="BP38" s="38" t="n"/>
+      <c r="BQ38" s="39" t="n"/>
       <c r="BR38" s="28" t="n"/>
       <c r="BS38" s="28" t="n"/>
       <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="25" t="n"/>
+      <c r="BU38" s="38" t="n"/>
       <c r="BV38" s="29" t="n"/>
       <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="30" t="n">
+      <c r="BX38" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY38" s="27" t="n">
+      <c r="BY38" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ38" s="24" t="inlineStr">
@@ -9958,7 +10031,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J39" s="25" t="n"/>
+      <c r="J39" s="38" t="n"/>
       <c r="K39" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9967,7 +10040,7 @@
       <c r="L39" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M39" s="27" t="n">
+      <c r="M39" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="N39" s="28" t="n">
@@ -10007,11 +10080,11 @@
       <c r="X39" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y39" s="25" t="n"/>
+      <c r="Y39" s="38" t="n"/>
       <c r="Z39" s="26" t="n"/>
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="30" t="n">
+      <c r="AC39" s="40" t="n">
         <v>1.275</v>
       </c>
       <c r="AD39" s="24" t="inlineStr">
@@ -10148,11 +10221,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ39" s="25" t="n"/>
+      <c r="BJ39" s="38" t="n"/>
       <c r="BK39" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL39" s="27" t="n">
+      <c r="BL39" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="BM39" s="28" t="n">
@@ -10162,18 +10235,18 @@
         <v>0.492537</v>
       </c>
       <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="25" t="n"/>
-      <c r="BQ39" s="27" t="n"/>
+      <c r="BP39" s="38" t="n"/>
+      <c r="BQ39" s="39" t="n"/>
       <c r="BR39" s="28" t="n"/>
       <c r="BS39" s="28" t="n"/>
       <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="25" t="n"/>
+      <c r="BU39" s="38" t="n"/>
       <c r="BV39" s="29" t="n"/>
       <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="30" t="n">
+      <c r="BX39" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY39" s="27" t="n">
+      <c r="BY39" s="39" t="n">
         <v>1.02</v>
       </c>
       <c r="BZ39" s="24" t="inlineStr">
@@ -10233,7 +10306,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J40" s="25" t="n"/>
+      <c r="J40" s="38" t="n"/>
       <c r="K40" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10242,7 +10315,7 @@
       <c r="L40" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M40" s="27" t="n">
+      <c r="M40" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N40" s="28" t="n">
@@ -10282,11 +10355,11 @@
       <c r="X40" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y40" s="25" t="n"/>
+      <c r="Y40" s="38" t="n"/>
       <c r="Z40" s="26" t="n"/>
       <c r="AA40" s="28" t="n"/>
       <c r="AB40" s="28" t="n"/>
-      <c r="AC40" s="30" t="n">
+      <c r="AC40" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD40" s="24" t="inlineStr">
@@ -10423,11 +10496,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ40" s="25" t="n"/>
+      <c r="BJ40" s="38" t="n"/>
       <c r="BK40" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL40" s="27" t="n">
+      <c r="BL40" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM40" s="28" t="n">
@@ -10437,18 +10510,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO40" s="28" t="n"/>
-      <c r="BP40" s="25" t="n"/>
-      <c r="BQ40" s="27" t="n"/>
+      <c r="BP40" s="38" t="n"/>
+      <c r="BQ40" s="39" t="n"/>
       <c r="BR40" s="28" t="n"/>
       <c r="BS40" s="28" t="n"/>
       <c r="BT40" s="28" t="n"/>
-      <c r="BU40" s="25" t="n"/>
+      <c r="BU40" s="38" t="n"/>
       <c r="BV40" s="29" t="n"/>
       <c r="BW40" s="24" t="n"/>
-      <c r="BX40" s="30" t="n">
+      <c r="BX40" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY40" s="27" t="n">
+      <c r="BY40" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ40" s="24" t="inlineStr">
@@ -10508,7 +10581,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J41" s="25" t="n"/>
+      <c r="J41" s="38" t="n"/>
       <c r="K41" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10517,7 +10590,7 @@
       <c r="L41" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M41" s="27" t="n">
+      <c r="M41" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N41" s="28" t="n">
@@ -10557,11 +10630,11 @@
       <c r="X41" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y41" s="25" t="n"/>
+      <c r="Y41" s="38" t="n"/>
       <c r="Z41" s="26" t="n"/>
       <c r="AA41" s="28" t="n"/>
       <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="30" t="n">
+      <c r="AC41" s="40" t="n">
         <v>1.2255</v>
       </c>
       <c r="AD41" s="24" t="inlineStr">
@@ -10698,11 +10771,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ41" s="25" t="n"/>
+      <c r="BJ41" s="38" t="n"/>
       <c r="BK41" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL41" s="27" t="n">
+      <c r="BL41" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM41" s="28" t="n">
@@ -10712,18 +10785,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO41" s="28" t="n"/>
-      <c r="BP41" s="25" t="n"/>
-      <c r="BQ41" s="27" t="n"/>
+      <c r="BP41" s="38" t="n"/>
+      <c r="BQ41" s="39" t="n"/>
       <c r="BR41" s="28" t="n"/>
       <c r="BS41" s="28" t="n"/>
       <c r="BT41" s="28" t="n"/>
-      <c r="BU41" s="25" t="n"/>
+      <c r="BU41" s="38" t="n"/>
       <c r="BV41" s="29" t="n"/>
       <c r="BW41" s="24" t="n"/>
-      <c r="BX41" s="30" t="n">
+      <c r="BX41" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY41" s="27" t="n">
+      <c r="BY41" s="39" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ41" s="24" t="inlineStr">
@@ -10783,7 +10856,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J42" s="25" t="n"/>
+      <c r="J42" s="38" t="n"/>
       <c r="K42" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10792,7 +10865,7 @@
       <c r="L42" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M42" s="27" t="n">
+      <c r="M42" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N42" s="28" t="n">
@@ -10832,11 +10905,11 @@
       <c r="X42" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y42" s="25" t="n"/>
+      <c r="Y42" s="38" t="n"/>
       <c r="Z42" s="26" t="n"/>
       <c r="AA42" s="28" t="n"/>
       <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="30" t="n">
+      <c r="AC42" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD42" s="24" t="inlineStr">
@@ -10973,11 +11046,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ42" s="25" t="n"/>
+      <c r="BJ42" s="38" t="n"/>
       <c r="BK42" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL42" s="27" t="n">
+      <c r="BL42" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM42" s="28" t="n">
@@ -10987,18 +11060,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO42" s="28" t="n"/>
-      <c r="BP42" s="25" t="n"/>
-      <c r="BQ42" s="27" t="n"/>
+      <c r="BP42" s="38" t="n"/>
+      <c r="BQ42" s="39" t="n"/>
       <c r="BR42" s="28" t="n"/>
       <c r="BS42" s="28" t="n"/>
       <c r="BT42" s="28" t="n"/>
-      <c r="BU42" s="25" t="n"/>
+      <c r="BU42" s="38" t="n"/>
       <c r="BV42" s="29" t="n"/>
       <c r="BW42" s="24" t="n"/>
-      <c r="BX42" s="30" t="n">
+      <c r="BX42" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY42" s="27" t="n">
+      <c r="BY42" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ42" s="24" t="inlineStr">
@@ -11058,7 +11131,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J43" s="25" t="n"/>
+      <c r="J43" s="38" t="n"/>
       <c r="K43" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -11067,7 +11140,7 @@
       <c r="L43" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M43" s="27" t="n">
+      <c r="M43" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N43" s="28" t="n">
@@ -11107,11 +11180,11 @@
       <c r="X43" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y43" s="25" t="n"/>
+      <c r="Y43" s="38" t="n"/>
       <c r="Z43" s="26" t="n"/>
       <c r="AA43" s="28" t="n"/>
       <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="30" t="n">
+      <c r="AC43" s="40" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD43" s="24" t="inlineStr">
@@ -11158,11 +11231,11 @@
         </is>
       </c>
       <c r="BI43" s="24" t="n"/>
-      <c r="BJ43" s="25" t="n"/>
+      <c r="BJ43" s="38" t="n"/>
       <c r="BK43" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL43" s="27" t="n">
+      <c r="BL43" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM43" s="28" t="n">
@@ -11172,16 +11245,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO43" s="28" t="n"/>
-      <c r="BP43" s="25" t="n"/>
-      <c r="BQ43" s="27" t="n"/>
+      <c r="BP43" s="38" t="n"/>
+      <c r="BQ43" s="39" t="n"/>
       <c r="BR43" s="28" t="n"/>
       <c r="BS43" s="28" t="n"/>
       <c r="BT43" s="28" t="n"/>
-      <c r="BU43" s="25" t="n"/>
+      <c r="BU43" s="38" t="n"/>
       <c r="BV43" s="29" t="n"/>
       <c r="BW43" s="24" t="n"/>
-      <c r="BX43" s="30" t="n"/>
-      <c r="BY43" s="27" t="n"/>
+      <c r="BX43" s="40" t="n"/>
+      <c r="BY43" s="39" t="n"/>
       <c r="BZ43" s="24" t="n"/>
       <c r="CA43" s="31" t="n"/>
     </row>
@@ -11231,7 +11304,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J44" s="25" t="n"/>
+      <c r="J44" s="38" t="n"/>
       <c r="K44" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -11240,7 +11313,7 @@
       <c r="L44" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M44" s="27" t="n">
+      <c r="M44" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="N44" s="28" t="n">
@@ -11280,11 +11353,11 @@
       <c r="X44" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y44" s="25" t="n"/>
+      <c r="Y44" s="38" t="n"/>
       <c r="Z44" s="26" t="n"/>
       <c r="AA44" s="28" t="n"/>
       <c r="AB44" s="28" t="n"/>
-      <c r="AC44" s="30" t="n">
+      <c r="AC44" s="40" t="n">
         <v>1.2411</v>
       </c>
       <c r="AD44" s="24" t="inlineStr">
@@ -11331,11 +11404,11 @@
         </is>
       </c>
       <c r="BI44" s="24" t="n"/>
-      <c r="BJ44" s="25" t="n"/>
+      <c r="BJ44" s="38" t="n"/>
       <c r="BK44" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL44" s="27" t="n">
+      <c r="BL44" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM44" s="28" t="n">
@@ -11345,16 +11418,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO44" s="28" t="n"/>
-      <c r="BP44" s="25" t="n"/>
-      <c r="BQ44" s="27" t="n"/>
+      <c r="BP44" s="38" t="n"/>
+      <c r="BQ44" s="39" t="n"/>
       <c r="BR44" s="28" t="n"/>
       <c r="BS44" s="28" t="n"/>
       <c r="BT44" s="28" t="n"/>
-      <c r="BU44" s="25" t="n"/>
+      <c r="BU44" s="38" t="n"/>
       <c r="BV44" s="29" t="n"/>
       <c r="BW44" s="24" t="n"/>
-      <c r="BX44" s="30" t="n"/>
-      <c r="BY44" s="27" t="n"/>
+      <c r="BX44" s="40" t="n"/>
+      <c r="BY44" s="39" t="n"/>
       <c r="BZ44" s="24" t="n"/>
       <c r="CA44" s="31" t="n"/>
     </row>
@@ -11404,7 +11477,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J45" s="25" t="n"/>
+      <c r="J45" s="38" t="n"/>
       <c r="K45" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -11413,7 +11486,7 @@
       <c r="L45" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M45" s="27" t="n">
+      <c r="M45" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N45" s="28" t="n">
@@ -11453,11 +11526,11 @@
       <c r="X45" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y45" s="25" t="n"/>
+      <c r="Y45" s="38" t="n"/>
       <c r="Z45" s="26" t="n"/>
       <c r="AA45" s="28" t="n"/>
       <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="30" t="n">
+      <c r="AC45" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD45" s="24" t="inlineStr">
@@ -11504,11 +11577,11 @@
         </is>
       </c>
       <c r="BI45" s="24" t="n"/>
-      <c r="BJ45" s="25" t="n"/>
+      <c r="BJ45" s="38" t="n"/>
       <c r="BK45" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL45" s="27" t="n">
+      <c r="BL45" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM45" s="28" t="n">
@@ -11518,16 +11591,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO45" s="28" t="n"/>
-      <c r="BP45" s="25" t="n"/>
-      <c r="BQ45" s="27" t="n"/>
+      <c r="BP45" s="38" t="n"/>
+      <c r="BQ45" s="39" t="n"/>
       <c r="BR45" s="28" t="n"/>
       <c r="BS45" s="28" t="n"/>
       <c r="BT45" s="28" t="n"/>
-      <c r="BU45" s="25" t="n"/>
+      <c r="BU45" s="38" t="n"/>
       <c r="BV45" s="29" t="n"/>
       <c r="BW45" s="24" t="n"/>
-      <c r="BX45" s="30" t="n"/>
-      <c r="BY45" s="27" t="n"/>
+      <c r="BX45" s="40" t="n"/>
+      <c r="BY45" s="39" t="n"/>
       <c r="BZ45" s="24" t="n"/>
       <c r="CA45" s="31" t="n"/>
     </row>
@@ -11577,7 +11650,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J46" s="25" t="n"/>
+      <c r="J46" s="38" t="n"/>
       <c r="K46" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -11586,7 +11659,7 @@
       <c r="L46" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M46" s="27" t="n">
+      <c r="M46" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="N46" s="28" t="n">
@@ -11626,11 +11699,11 @@
       <c r="X46" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y46" s="25" t="n"/>
+      <c r="Y46" s="38" t="n"/>
       <c r="Z46" s="26" t="n"/>
       <c r="AA46" s="28" t="n"/>
       <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="30" t="n">
+      <c r="AC46" s="40" t="n">
         <v>1.3</v>
       </c>
       <c r="AD46" s="24" t="inlineStr">
@@ -11677,11 +11750,11 @@
         </is>
       </c>
       <c r="BI46" s="24" t="n"/>
-      <c r="BJ46" s="25" t="n"/>
+      <c r="BJ46" s="38" t="n"/>
       <c r="BK46" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL46" s="27" t="n">
+      <c r="BL46" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="BM46" s="28" t="n">
@@ -11691,16 +11764,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO46" s="28" t="n"/>
-      <c r="BP46" s="25" t="n"/>
-      <c r="BQ46" s="27" t="n"/>
+      <c r="BP46" s="38" t="n"/>
+      <c r="BQ46" s="39" t="n"/>
       <c r="BR46" s="28" t="n"/>
       <c r="BS46" s="28" t="n"/>
       <c r="BT46" s="28" t="n"/>
-      <c r="BU46" s="25" t="n"/>
+      <c r="BU46" s="38" t="n"/>
       <c r="BV46" s="29" t="n"/>
       <c r="BW46" s="24" t="n"/>
-      <c r="BX46" s="30" t="n"/>
-      <c r="BY46" s="27" t="n"/>
+      <c r="BX46" s="40" t="n"/>
+      <c r="BY46" s="39" t="n"/>
       <c r="BZ46" s="24" t="n"/>
       <c r="CA46" s="31" t="n"/>
     </row>
@@ -11750,7 +11823,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J47" s="25" t="n"/>
+      <c r="J47" s="38" t="n"/>
       <c r="K47" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -11759,7 +11832,7 @@
       <c r="L47" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M47" s="27" t="n">
+      <c r="M47" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N47" s="28" t="n">
@@ -11799,11 +11872,11 @@
       <c r="X47" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y47" s="25" t="n"/>
+      <c r="Y47" s="38" t="n"/>
       <c r="Z47" s="26" t="n"/>
       <c r="AA47" s="28" t="n"/>
       <c r="AB47" s="28" t="n"/>
-      <c r="AC47" s="30" t="n">
+      <c r="AC47" s="40" t="n">
         <v>0.9615</v>
       </c>
       <c r="AD47" s="24" t="inlineStr">
@@ -11850,11 +11923,11 @@
         </is>
       </c>
       <c r="BI47" s="24" t="n"/>
-      <c r="BJ47" s="25" t="n"/>
+      <c r="BJ47" s="38" t="n"/>
       <c r="BK47" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL47" s="27" t="n">
+      <c r="BL47" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM47" s="28" t="n">
@@ -11864,16 +11937,16 @@
         <v>0.507463</v>
       </c>
       <c r="BO47" s="28" t="n"/>
-      <c r="BP47" s="25" t="n"/>
-      <c r="BQ47" s="27" t="n"/>
+      <c r="BP47" s="38" t="n"/>
+      <c r="BQ47" s="39" t="n"/>
       <c r="BR47" s="28" t="n"/>
       <c r="BS47" s="28" t="n"/>
       <c r="BT47" s="28" t="n"/>
-      <c r="BU47" s="25" t="n"/>
+      <c r="BU47" s="38" t="n"/>
       <c r="BV47" s="29" t="n"/>
       <c r="BW47" s="24" t="n"/>
-      <c r="BX47" s="30" t="n"/>
-      <c r="BY47" s="27" t="n"/>
+      <c r="BX47" s="40" t="n"/>
+      <c r="BY47" s="39" t="n"/>
       <c r="BZ47" s="24" t="n"/>
       <c r="CA47" s="31" t="n"/>
     </row>
@@ -11923,7 +11996,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J48" s="25" t="n"/>
+      <c r="J48" s="38" t="n"/>
       <c r="K48" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -11932,7 +12005,7 @@
       <c r="L48" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="M48" s="27" t="n">
+      <c r="M48" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="N48" s="28" t="n">
@@ -11972,11 +12045,11 @@
       <c r="X48" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y48" s="25" t="n"/>
+      <c r="Y48" s="38" t="n"/>
       <c r="Z48" s="26" t="n"/>
       <c r="AA48" s="28" t="n"/>
       <c r="AB48" s="28" t="n"/>
-      <c r="AC48" s="30" t="n">
+      <c r="AC48" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD48" s="24" t="inlineStr">
@@ -12023,11 +12096,11 @@
         </is>
       </c>
       <c r="BI48" s="24" t="n"/>
-      <c r="BJ48" s="25" t="n"/>
+      <c r="BJ48" s="38" t="n"/>
       <c r="BK48" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="BL48" s="27" t="n">
+      <c r="BL48" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="BM48" s="28" t="n">
@@ -12037,16 +12110,16 @@
         <v>0.452736</v>
       </c>
       <c r="BO48" s="28" t="n"/>
-      <c r="BP48" s="25" t="n"/>
-      <c r="BQ48" s="27" t="n"/>
+      <c r="BP48" s="38" t="n"/>
+      <c r="BQ48" s="39" t="n"/>
       <c r="BR48" s="28" t="n"/>
       <c r="BS48" s="28" t="n"/>
       <c r="BT48" s="28" t="n"/>
-      <c r="BU48" s="25" t="n"/>
+      <c r="BU48" s="38" t="n"/>
       <c r="BV48" s="29" t="n"/>
       <c r="BW48" s="24" t="n"/>
-      <c r="BX48" s="30" t="n"/>
-      <c r="BY48" s="27" t="n"/>
+      <c r="BX48" s="40" t="n"/>
+      <c r="BY48" s="39" t="n"/>
       <c r="BZ48" s="24" t="n"/>
       <c r="CA48" s="31" t="n"/>
     </row>
@@ -12096,7 +12169,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J49" s="25" t="n"/>
+      <c r="J49" s="38" t="n"/>
       <c r="K49" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -12105,7 +12178,7 @@
       <c r="L49" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M49" s="27" t="n">
+      <c r="M49" s="39" t="n">
         <v>2</v>
       </c>
       <c r="N49" s="28" t="n">
@@ -12145,11 +12218,11 @@
       <c r="X49" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y49" s="25" t="n"/>
+      <c r="Y49" s="38" t="n"/>
       <c r="Z49" s="26" t="n"/>
       <c r="AA49" s="28" t="n"/>
       <c r="AB49" s="28" t="n"/>
-      <c r="AC49" s="30" t="n">
+      <c r="AC49" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD49" s="24" t="inlineStr">
@@ -12196,11 +12269,11 @@
         </is>
       </c>
       <c r="BI49" s="24" t="n"/>
-      <c r="BJ49" s="25" t="n"/>
+      <c r="BJ49" s="38" t="n"/>
       <c r="BK49" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL49" s="27" t="n">
+      <c r="BL49" s="39" t="n">
         <v>2</v>
       </c>
       <c r="BM49" s="28" t="n">
@@ -12210,16 +12283,16 @@
         <v>0.497512</v>
       </c>
       <c r="BO49" s="28" t="n"/>
-      <c r="BP49" s="25" t="n"/>
-      <c r="BQ49" s="27" t="n"/>
+      <c r="BP49" s="38" t="n"/>
+      <c r="BQ49" s="39" t="n"/>
       <c r="BR49" s="28" t="n"/>
       <c r="BS49" s="28" t="n"/>
       <c r="BT49" s="28" t="n"/>
-      <c r="BU49" s="25" t="n"/>
+      <c r="BU49" s="38" t="n"/>
       <c r="BV49" s="29" t="n"/>
       <c r="BW49" s="24" t="n"/>
-      <c r="BX49" s="30" t="n"/>
-      <c r="BY49" s="27" t="n"/>
+      <c r="BX49" s="40" t="n"/>
+      <c r="BY49" s="39" t="n"/>
       <c r="BZ49" s="24" t="n"/>
       <c r="CA49" s="31" t="n"/>
     </row>
@@ -12269,7 +12342,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J50" s="25" t="n"/>
+      <c r="J50" s="38" t="n"/>
       <c r="K50" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12278,7 +12351,7 @@
       <c r="L50" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M50" s="27" t="n">
+      <c r="M50" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="N50" s="28" t="n">
@@ -12318,11 +12391,11 @@
       <c r="X50" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y50" s="25" t="n"/>
+      <c r="Y50" s="38" t="n"/>
       <c r="Z50" s="26" t="n"/>
       <c r="AA50" s="28" t="n"/>
       <c r="AB50" s="28" t="n"/>
-      <c r="AC50" s="30" t="n">
+      <c r="AC50" s="40" t="n">
         <v>1.35</v>
       </c>
       <c r="AD50" s="24" t="inlineStr">
@@ -12459,11 +12532,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ50" s="25" t="n"/>
+      <c r="BJ50" s="38" t="n"/>
       <c r="BK50" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL50" s="27" t="n">
+      <c r="BL50" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="BM50" s="28" t="n">
@@ -12473,16 +12546,16 @@
         <v>0.477612</v>
       </c>
       <c r="BO50" s="28" t="n"/>
-      <c r="BP50" s="25" t="n"/>
-      <c r="BQ50" s="27" t="n"/>
+      <c r="BP50" s="38" t="n"/>
+      <c r="BQ50" s="39" t="n"/>
       <c r="BR50" s="28" t="n"/>
       <c r="BS50" s="28" t="n"/>
       <c r="BT50" s="28" t="n"/>
-      <c r="BU50" s="25" t="n"/>
+      <c r="BU50" s="38" t="n"/>
       <c r="BV50" s="29" t="n"/>
       <c r="BW50" s="24" t="n"/>
-      <c r="BX50" s="30" t="n"/>
-      <c r="BY50" s="27" t="n"/>
+      <c r="BX50" s="40" t="n"/>
+      <c r="BY50" s="39" t="n"/>
       <c r="BZ50" s="24" t="n"/>
       <c r="CA50" s="31" t="n"/>
     </row>
@@ -12532,7 +12605,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J51" s="25" t="n"/>
+      <c r="J51" s="38" t="n"/>
       <c r="K51" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12541,7 +12614,7 @@
       <c r="L51" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M51" s="27" t="n">
+      <c r="M51" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N51" s="28" t="n">
@@ -12581,11 +12654,11 @@
       <c r="X51" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y51" s="25" t="n"/>
+      <c r="Y51" s="38" t="n"/>
       <c r="Z51" s="26" t="n"/>
       <c r="AA51" s="28" t="n"/>
       <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="30" t="n">
+      <c r="AC51" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD51" s="24" t="inlineStr">
@@ -12722,11 +12795,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ51" s="25" t="n"/>
+      <c r="BJ51" s="38" t="n"/>
       <c r="BK51" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL51" s="27" t="n">
+      <c r="BL51" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM51" s="28" t="n">
@@ -12736,16 +12809,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO51" s="28" t="n"/>
-      <c r="BP51" s="25" t="n"/>
-      <c r="BQ51" s="27" t="n"/>
+      <c r="BP51" s="38" t="n"/>
+      <c r="BQ51" s="39" t="n"/>
       <c r="BR51" s="28" t="n"/>
       <c r="BS51" s="28" t="n"/>
       <c r="BT51" s="28" t="n"/>
-      <c r="BU51" s="25" t="n"/>
+      <c r="BU51" s="38" t="n"/>
       <c r="BV51" s="29" t="n"/>
       <c r="BW51" s="24" t="n"/>
-      <c r="BX51" s="30" t="n"/>
-      <c r="BY51" s="27" t="n"/>
+      <c r="BX51" s="40" t="n"/>
+      <c r="BY51" s="39" t="n"/>
       <c r="BZ51" s="24" t="n"/>
       <c r="CA51" s="31" t="n"/>
     </row>
@@ -12795,7 +12868,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J52" s="25" t="n"/>
+      <c r="J52" s="38" t="n"/>
       <c r="K52" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12804,7 +12877,7 @@
       <c r="L52" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="M52" s="27" t="n">
+      <c r="M52" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="N52" s="28" t="n">
@@ -12844,11 +12917,11 @@
       <c r="X52" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y52" s="25" t="n"/>
+      <c r="Y52" s="38" t="n"/>
       <c r="Z52" s="26" t="n"/>
       <c r="AA52" s="28" t="n"/>
       <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="30" t="n">
+      <c r="AC52" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD52" s="24" t="inlineStr">
@@ -12985,11 +13058,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ52" s="25" t="n"/>
+      <c r="BJ52" s="38" t="n"/>
       <c r="BK52" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="BL52" s="27" t="n">
+      <c r="BL52" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="BM52" s="28" t="n">
@@ -12999,18 +13072,4251 @@
         <v>0.432836</v>
       </c>
       <c r="BO52" s="28" t="n"/>
-      <c r="BP52" s="25" t="n"/>
-      <c r="BQ52" s="27" t="n"/>
+      <c r="BP52" s="38" t="n"/>
+      <c r="BQ52" s="39" t="n"/>
       <c r="BR52" s="28" t="n"/>
       <c r="BS52" s="28" t="n"/>
       <c r="BT52" s="28" t="n"/>
-      <c r="BU52" s="25" t="n"/>
+      <c r="BU52" s="38" t="n"/>
       <c r="BV52" s="29" t="n"/>
       <c r="BW52" s="24" t="n"/>
-      <c r="BX52" s="30" t="n"/>
-      <c r="BY52" s="27" t="n"/>
+      <c r="BX52" s="40" t="n"/>
+      <c r="BY52" s="39" t="n"/>
       <c r="BZ52" s="24" t="n"/>
       <c r="CA52" s="31" t="n"/>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>39f07dbdee044f92</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:09.837629Z</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>401816188</t>
+        </is>
+      </c>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="H53" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J53" s="38" t="n"/>
+      <c r="K53" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L53" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M53" s="39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N53" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O53" s="28" t="n">
+        <v>0.585152</v>
+      </c>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="28" t="n">
+        <v>0.104383</v>
+      </c>
+      <c r="R53" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S53" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T53" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U53" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V53" s="24" t="n"/>
+      <c r="W53" s="26" t="n"/>
+      <c r="X53" s="26" t="n"/>
+      <c r="Y53" s="38" t="n"/>
+      <c r="Z53" s="26" t="n"/>
+      <c r="AA53" s="28" t="n"/>
+      <c r="AB53" s="28" t="n"/>
+      <c r="AC53" s="40" t="n"/>
+      <c r="AD53" s="24" t="n"/>
+      <c r="AE53" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.4800 (aec-mlb-min-cle-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF53" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG53" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH53" s="24" t="n"/>
+      <c r="AI53" s="31" t="n"/>
+      <c r="AJ53" s="31" t="n"/>
+      <c r="AK53" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL53" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM53" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN53" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO53" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP53" s="24" t="inlineStr">
+        <is>
+          <t>mlb-min</t>
+        </is>
+      </c>
+      <c r="AQ53" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AR53" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AS53" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cle</t>
+        </is>
+      </c>
+      <c r="AT53" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AU53" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AV53" s="24" t="n"/>
+      <c r="AW53" s="24" t="n"/>
+      <c r="AX53" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY53" s="24" t="n"/>
+      <c r="AZ53" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA53" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB53" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC53" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD53" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE53" s="24" t="inlineStr">
+        <is>
+          <t>bcb6462455cdfab4</t>
+        </is>
+      </c>
+      <c r="BF53" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG53" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH53" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:25:43.922504Z</t>
+        </is>
+      </c>
+      <c r="BI53" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ53" s="38" t="n"/>
+      <c r="BK53" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL53" s="39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM53" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN53" s="28" t="n">
+        <v>0.477612</v>
+      </c>
+      <c r="BO53" s="28" t="n"/>
+      <c r="BP53" s="38" t="n"/>
+      <c r="BQ53" s="39" t="n"/>
+      <c r="BR53" s="28" t="n"/>
+      <c r="BS53" s="28" t="n"/>
+      <c r="BT53" s="28" t="n"/>
+      <c r="BU53" s="38" t="n"/>
+      <c r="BV53" s="29" t="n"/>
+      <c r="BW53" s="24" t="n"/>
+      <c r="BX53" s="40" t="n"/>
+      <c r="BY53" s="39" t="n"/>
+      <c r="BZ53" s="24" t="n"/>
+      <c r="CA53" s="31" t="n"/>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>25fe08e3be954adb</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:09.837629Z</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>401816187</t>
+        </is>
+      </c>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="G54" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="H54" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J54" s="38" t="n"/>
+      <c r="K54" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L54" s="26" t="n">
+        <v>125</v>
+      </c>
+      <c r="M54" s="39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N54" s="28" t="n">
+        <v>0.444444</v>
+      </c>
+      <c r="O54" s="28" t="n">
+        <v>0.534274</v>
+      </c>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="28" t="n">
+        <v>0.08982999999999999</v>
+      </c>
+      <c r="R54" s="26" t="n">
+        <v>65</v>
+      </c>
+      <c r="S54" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T54" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U54" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V54" s="24" t="n"/>
+      <c r="W54" s="26" t="n"/>
+      <c r="X54" s="26" t="n"/>
+      <c r="Y54" s="38" t="n"/>
+      <c r="Z54" s="26" t="n"/>
+      <c r="AA54" s="28" t="n"/>
+      <c r="AB54" s="28" t="n"/>
+      <c r="AC54" s="40" t="n"/>
+      <c r="AD54" s="24" t="n"/>
+      <c r="AE54" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.4450 (aec-mlb-lad-phi-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF54" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG54" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH54" s="24" t="n"/>
+      <c r="AI54" s="31" t="n"/>
+      <c r="AJ54" s="31" t="n"/>
+      <c r="AK54" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL54" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM54" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN54" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO54" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP54" s="24" t="inlineStr">
+        <is>
+          <t>mlb-lad</t>
+        </is>
+      </c>
+      <c r="AQ54" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AR54" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AS54" s="24" t="inlineStr">
+        <is>
+          <t>mlb-phi</t>
+        </is>
+      </c>
+      <c r="AT54" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="AU54" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="AV54" s="24" t="n"/>
+      <c r="AW54" s="24" t="n"/>
+      <c r="AX54" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY54" s="24" t="n"/>
+      <c r="AZ54" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA54" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB54" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC54" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD54" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE54" s="24" t="inlineStr">
+        <is>
+          <t>f54ac71be1a765d8</t>
+        </is>
+      </c>
+      <c r="BF54" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG54" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH54" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:25:49.234179Z</t>
+        </is>
+      </c>
+      <c r="BI54" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ54" s="38" t="n"/>
+      <c r="BK54" s="26" t="n">
+        <v>125</v>
+      </c>
+      <c r="BL54" s="39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM54" s="28" t="n">
+        <v>0.444444</v>
+      </c>
+      <c r="BN54" s="28" t="n">
+        <v>0.442786</v>
+      </c>
+      <c r="BO54" s="28" t="n"/>
+      <c r="BP54" s="38" t="n"/>
+      <c r="BQ54" s="39" t="n"/>
+      <c r="BR54" s="28" t="n"/>
+      <c r="BS54" s="28" t="n"/>
+      <c r="BT54" s="28" t="n"/>
+      <c r="BU54" s="38" t="n"/>
+      <c r="BV54" s="29" t="n"/>
+      <c r="BW54" s="24" t="n"/>
+      <c r="BX54" s="40" t="n"/>
+      <c r="BY54" s="39" t="n"/>
+      <c r="BZ54" s="24" t="n"/>
+      <c r="CA54" s="31" t="n"/>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>043f9b9799c44ad4</t>
+        </is>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:09.837629Z</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>401816189</t>
+        </is>
+      </c>
+      <c r="E55" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="H55" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I55" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J55" s="38" t="n"/>
+      <c r="K55" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L55" s="26" t="n">
+        <v>-111</v>
+      </c>
+      <c r="M55" s="39" t="n">
+        <v>1.900901</v>
+      </c>
+      <c r="N55" s="28" t="n">
+        <v>0.526066</v>
+      </c>
+      <c r="O55" s="28" t="n">
+        <v>0.588959</v>
+      </c>
+      <c r="P55" s="28" t="n"/>
+      <c r="Q55" s="28" t="n">
+        <v>0.062893</v>
+      </c>
+      <c r="R55" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="S55" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T55" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U55" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V55" s="24" t="n"/>
+      <c r="W55" s="26" t="n"/>
+      <c r="X55" s="26" t="n"/>
+      <c r="Y55" s="38" t="n"/>
+      <c r="Z55" s="26" t="n"/>
+      <c r="AA55" s="28" t="n"/>
+      <c r="AB55" s="28" t="n"/>
+      <c r="AC55" s="40" t="n"/>
+      <c r="AD55" s="24" t="n"/>
+      <c r="AE55" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5250 (aec-mlb-pit-nyy-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF55" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG55" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH55" s="24" t="n"/>
+      <c r="AI55" s="31" t="n"/>
+      <c r="AJ55" s="31" t="n"/>
+      <c r="AK55" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL55" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM55" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN55" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO55" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP55" s="24" t="inlineStr">
+        <is>
+          <t>mlb-pit</t>
+        </is>
+      </c>
+      <c r="AQ55" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AR55" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AS55" s="24" t="inlineStr">
+        <is>
+          <t>mlb-nyy</t>
+        </is>
+      </c>
+      <c r="AT55" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AU55" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AV55" s="24" t="n"/>
+      <c r="AW55" s="24" t="n"/>
+      <c r="AX55" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY55" s="24" t="n"/>
+      <c r="AZ55" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA55" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB55" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC55" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD55" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE55" s="24" t="inlineStr">
+        <is>
+          <t>847c7c728fdb87de</t>
+        </is>
+      </c>
+      <c r="BF55" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG55" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH55" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:25:45.280685Z</t>
+        </is>
+      </c>
+      <c r="BI55" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ55" s="38" t="n"/>
+      <c r="BK55" s="26" t="n">
+        <v>-111</v>
+      </c>
+      <c r="BL55" s="39" t="n">
+        <v>1.900901</v>
+      </c>
+      <c r="BM55" s="28" t="n">
+        <v>0.526066</v>
+      </c>
+      <c r="BN55" s="28" t="n">
+        <v>0.522388</v>
+      </c>
+      <c r="BO55" s="28" t="n"/>
+      <c r="BP55" s="38" t="n"/>
+      <c r="BQ55" s="39" t="n"/>
+      <c r="BR55" s="28" t="n"/>
+      <c r="BS55" s="28" t="n"/>
+      <c r="BT55" s="28" t="n"/>
+      <c r="BU55" s="38" t="n"/>
+      <c r="BV55" s="29" t="n"/>
+      <c r="BW55" s="24" t="n"/>
+      <c r="BX55" s="40" t="n"/>
+      <c r="BY55" s="39" t="n"/>
+      <c r="BZ55" s="24" t="n"/>
+      <c r="CA55" s="31" t="n"/>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="24" t="inlineStr">
+        <is>
+          <t>75cf9949602a4c17</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:09.837629Z</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:07:00-0400</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>401816191</t>
+        </is>
+      </c>
+      <c r="E56" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="G56" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="H56" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I56" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J56" s="38" t="n"/>
+      <c r="K56" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L56" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M56" s="39" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N56" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O56" s="28" t="n">
+        <v>0.528636</v>
+      </c>
+      <c r="P56" s="28" t="n"/>
+      <c r="Q56" s="28" t="n">
+        <v>-0.051196</v>
+      </c>
+      <c r="R56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T56" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U56" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V56" s="24" t="n"/>
+      <c r="W56" s="26" t="n"/>
+      <c r="X56" s="26" t="n"/>
+      <c r="Y56" s="38" t="n"/>
+      <c r="Z56" s="26" t="n"/>
+      <c r="AA56" s="28" t="n"/>
+      <c r="AB56" s="28" t="n"/>
+      <c r="AC56" s="40" t="n"/>
+      <c r="AD56" s="24" t="n"/>
+      <c r="AE56" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5800 (aec-mlb-tb-tor-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF56" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG56" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH56" s="24" t="n"/>
+      <c r="AI56" s="31" t="n"/>
+      <c r="AJ56" s="31" t="n"/>
+      <c r="AK56" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL56" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM56" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN56" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO56" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP56" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tb</t>
+        </is>
+      </c>
+      <c r="AQ56" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AR56" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AS56" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tor</t>
+        </is>
+      </c>
+      <c r="AT56" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="AU56" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="AV56" s="24" t="n"/>
+      <c r="AW56" s="24" t="n"/>
+      <c r="AX56" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY56" s="24" t="n"/>
+      <c r="AZ56" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA56" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB56" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC56" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD56" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE56" s="24" t="inlineStr">
+        <is>
+          <t>83a50acec79889d1</t>
+        </is>
+      </c>
+      <c r="BF56" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG56" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH56" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:25:46.631829Z</t>
+        </is>
+      </c>
+      <c r="BI56" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ56" s="38" t="n"/>
+      <c r="BK56" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL56" s="39" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM56" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN56" s="28" t="n">
+        <v>0.577114</v>
+      </c>
+      <c r="BO56" s="28" t="n"/>
+      <c r="BP56" s="38" t="n"/>
+      <c r="BQ56" s="39" t="n"/>
+      <c r="BR56" s="28" t="n"/>
+      <c r="BS56" s="28" t="n"/>
+      <c r="BT56" s="28" t="n"/>
+      <c r="BU56" s="38" t="n"/>
+      <c r="BV56" s="29" t="n"/>
+      <c r="BW56" s="24" t="n"/>
+      <c r="BX56" s="40" t="n"/>
+      <c r="BY56" s="39" t="n"/>
+      <c r="BZ56" s="24" t="n"/>
+      <c r="CA56" s="31" t="n"/>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>bd769f5d72db48bb</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:09.837629Z</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>401816186</t>
+        </is>
+      </c>
+      <c r="E57" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="G57" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="H57" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I57" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J57" s="38" t="n"/>
+      <c r="K57" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L57" s="26" t="n">
+        <v>-135</v>
+      </c>
+      <c r="M57" s="39" t="n">
+        <v>1.740741</v>
+      </c>
+      <c r="N57" s="28" t="n">
+        <v>0.574468</v>
+      </c>
+      <c r="O57" s="28" t="n">
+        <v>0.565634</v>
+      </c>
+      <c r="P57" s="28" t="n"/>
+      <c r="Q57" s="28" t="n">
+        <v>-0.008834</v>
+      </c>
+      <c r="R57" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="S57" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T57" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U57" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V57" s="24" t="n"/>
+      <c r="W57" s="26" t="n"/>
+      <c r="X57" s="26" t="n"/>
+      <c r="Y57" s="38" t="n"/>
+      <c r="Z57" s="26" t="n"/>
+      <c r="AA57" s="28" t="n"/>
+      <c r="AB57" s="28" t="n"/>
+      <c r="AC57" s="40" t="n"/>
+      <c r="AD57" s="24" t="n"/>
+      <c r="AE57" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5750 (aec-mlb-bal-bos-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF57" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG57" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH57" s="24" t="n"/>
+      <c r="AI57" s="31" t="n"/>
+      <c r="AJ57" s="31" t="n"/>
+      <c r="AK57" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL57" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM57" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN57" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO57" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP57" s="24" t="inlineStr">
+        <is>
+          <t>mlb-bal</t>
+        </is>
+      </c>
+      <c r="AQ57" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="AR57" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="AS57" s="24" t="inlineStr">
+        <is>
+          <t>mlb-bos</t>
+        </is>
+      </c>
+      <c r="AT57" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AU57" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AV57" s="24" t="n"/>
+      <c r="AW57" s="24" t="n"/>
+      <c r="AX57" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY57" s="24" t="n"/>
+      <c r="AZ57" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA57" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB57" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC57" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD57" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE57" s="24" t="inlineStr">
+        <is>
+          <t>f90d77bcf90af7a6</t>
+        </is>
+      </c>
+      <c r="BF57" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG57" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH57" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:25:48.021174Z</t>
+        </is>
+      </c>
+      <c r="BI57" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ57" s="38" t="n"/>
+      <c r="BK57" s="26" t="n">
+        <v>-135</v>
+      </c>
+      <c r="BL57" s="39" t="n">
+        <v>1.740741</v>
+      </c>
+      <c r="BM57" s="28" t="n">
+        <v>0.574468</v>
+      </c>
+      <c r="BN57" s="28" t="n">
+        <v>0.572139</v>
+      </c>
+      <c r="BO57" s="28" t="n"/>
+      <c r="BP57" s="38" t="n"/>
+      <c r="BQ57" s="39" t="n"/>
+      <c r="BR57" s="28" t="n"/>
+      <c r="BS57" s="28" t="n"/>
+      <c r="BT57" s="28" t="n"/>
+      <c r="BU57" s="38" t="n"/>
+      <c r="BV57" s="29" t="n"/>
+      <c r="BW57" s="24" t="n"/>
+      <c r="BX57" s="40" t="n"/>
+      <c r="BY57" s="39" t="n"/>
+      <c r="BZ57" s="24" t="n"/>
+      <c r="CA57" s="31" t="n"/>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>6f908cfbb4fb4660</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:09.837629Z</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>401816190</t>
+        </is>
+      </c>
+      <c r="E58" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F58" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="G58" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="H58" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I58" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J58" s="38" t="n"/>
+      <c r="K58" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L58" s="26" t="n">
+        <v>-135</v>
+      </c>
+      <c r="M58" s="39" t="n">
+        <v>1.740741</v>
+      </c>
+      <c r="N58" s="28" t="n">
+        <v>0.574468</v>
+      </c>
+      <c r="O58" s="28" t="n">
+        <v>0.5478730000000001</v>
+      </c>
+      <c r="P58" s="28" t="n"/>
+      <c r="Q58" s="28" t="n">
+        <v>-0.026595</v>
+      </c>
+      <c r="R58" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S58" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U58" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V58" s="24" t="n"/>
+      <c r="W58" s="26" t="n"/>
+      <c r="X58" s="26" t="n"/>
+      <c r="Y58" s="38" t="n"/>
+      <c r="Z58" s="26" t="n"/>
+      <c r="AA58" s="28" t="n"/>
+      <c r="AB58" s="28" t="n"/>
+      <c r="AC58" s="40" t="n"/>
+      <c r="AD58" s="24" t="n"/>
+      <c r="AE58" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5750 (aec-mlb-sd-atl-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF58" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG58" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH58" s="24" t="n"/>
+      <c r="AI58" s="31" t="n"/>
+      <c r="AJ58" s="31" t="n"/>
+      <c r="AK58" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL58" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM58" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN58" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO58" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP58" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sd</t>
+        </is>
+      </c>
+      <c r="AQ58" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AR58" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AS58" s="24" t="inlineStr">
+        <is>
+          <t>mlb-atl</t>
+        </is>
+      </c>
+      <c r="AT58" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AU58" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AV58" s="24" t="n"/>
+      <c r="AW58" s="24" t="n"/>
+      <c r="AX58" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY58" s="24" t="n"/>
+      <c r="AZ58" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA58" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB58" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC58" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD58" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE58" s="24" t="inlineStr">
+        <is>
+          <t>dcaf75f7da769912</t>
+        </is>
+      </c>
+      <c r="BF58" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG58" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH58" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:25:50.370060Z</t>
+        </is>
+      </c>
+      <c r="BI58" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ58" s="38" t="n"/>
+      <c r="BK58" s="26" t="n">
+        <v>-135</v>
+      </c>
+      <c r="BL58" s="39" t="n">
+        <v>1.740741</v>
+      </c>
+      <c r="BM58" s="28" t="n">
+        <v>0.574468</v>
+      </c>
+      <c r="BN58" s="28" t="n">
+        <v>0.572139</v>
+      </c>
+      <c r="BO58" s="28" t="n"/>
+      <c r="BP58" s="38" t="n"/>
+      <c r="BQ58" s="39" t="n"/>
+      <c r="BR58" s="28" t="n"/>
+      <c r="BS58" s="28" t="n"/>
+      <c r="BT58" s="28" t="n"/>
+      <c r="BU58" s="38" t="n"/>
+      <c r="BV58" s="29" t="n"/>
+      <c r="BW58" s="24" t="n"/>
+      <c r="BX58" s="40" t="n"/>
+      <c r="BY58" s="39" t="n"/>
+      <c r="BZ58" s="24" t="n"/>
+      <c r="CA58" s="31" t="n"/>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>b3d04af2bb2445ec</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:09.837629Z</t>
+        </is>
+      </c>
+      <c r="C59" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>401816195</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F59" s="24" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="G59" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="H59" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I59" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J59" s="38" t="n"/>
+      <c r="K59" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L59" s="26" t="n">
+        <v>-190</v>
+      </c>
+      <c r="M59" s="39" t="n">
+        <v>1.526316</v>
+      </c>
+      <c r="N59" s="28" t="n">
+        <v>0.655172</v>
+      </c>
+      <c r="O59" s="28" t="n">
+        <v>0.6384</v>
+      </c>
+      <c r="P59" s="28" t="n"/>
+      <c r="Q59" s="28" t="n">
+        <v>-0.016772</v>
+      </c>
+      <c r="R59" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="S59" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T59" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U59" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V59" s="24" t="n"/>
+      <c r="W59" s="26" t="n"/>
+      <c r="X59" s="26" t="n"/>
+      <c r="Y59" s="38" t="n"/>
+      <c r="Z59" s="26" t="n"/>
+      <c r="AA59" s="28" t="n"/>
+      <c r="AB59" s="28" t="n"/>
+      <c r="AC59" s="40" t="n"/>
+      <c r="AD59" s="24" t="n"/>
+      <c r="AE59" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.6550 (aec-mlb-nym-mil-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF59" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG59" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH59" s="24" t="n"/>
+      <c r="AI59" s="31" t="n"/>
+      <c r="AJ59" s="31" t="n"/>
+      <c r="AK59" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL59" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM59" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN59" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO59" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP59" s="24" t="inlineStr">
+        <is>
+          <t>mlb-nym</t>
+        </is>
+      </c>
+      <c r="AQ59" s="24" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="AR59" s="24" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="AS59" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AT59" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AU59" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AV59" s="24" t="n"/>
+      <c r="AW59" s="24" t="n"/>
+      <c r="AX59" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY59" s="24" t="n"/>
+      <c r="AZ59" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA59" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB59" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC59" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD59" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE59" s="24" t="inlineStr">
+        <is>
+          <t>08844b1e52756e6a</t>
+        </is>
+      </c>
+      <c r="BF59" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG59" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH59" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:25:51.762171Z</t>
+        </is>
+      </c>
+      <c r="BI59" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ59" s="38" t="n"/>
+      <c r="BK59" s="26" t="n">
+        <v>-190</v>
+      </c>
+      <c r="BL59" s="39" t="n">
+        <v>1.526316</v>
+      </c>
+      <c r="BM59" s="28" t="n">
+        <v>0.655172</v>
+      </c>
+      <c r="BN59" s="28" t="n">
+        <v>0.651741</v>
+      </c>
+      <c r="BO59" s="28" t="n"/>
+      <c r="BP59" s="38" t="n"/>
+      <c r="BQ59" s="39" t="n"/>
+      <c r="BR59" s="28" t="n"/>
+      <c r="BS59" s="28" t="n"/>
+      <c r="BT59" s="28" t="n"/>
+      <c r="BU59" s="38" t="n"/>
+      <c r="BV59" s="29" t="n"/>
+      <c r="BW59" s="24" t="n"/>
+      <c r="BX59" s="40" t="n"/>
+      <c r="BY59" s="39" t="n"/>
+      <c r="BZ59" s="24" t="n"/>
+      <c r="CA59" s="31" t="n"/>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>07c094e50e3443bc</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:09.837629Z</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>401816192</t>
+        </is>
+      </c>
+      <c r="E60" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F60" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="G60" s="24" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="H60" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I60" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J60" s="38" t="n"/>
+      <c r="K60" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L60" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M60" s="39" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N60" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O60" s="28" t="n">
+        <v>0.518942</v>
+      </c>
+      <c r="P60" s="28" t="n"/>
+      <c r="Q60" s="28" t="n">
+        <v>-0.090433</v>
+      </c>
+      <c r="R60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T60" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U60" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V60" s="24" t="n"/>
+      <c r="W60" s="26" t="n"/>
+      <c r="X60" s="26" t="n"/>
+      <c r="Y60" s="38" t="n"/>
+      <c r="Z60" s="26" t="n"/>
+      <c r="AA60" s="28" t="n"/>
+      <c r="AB60" s="28" t="n"/>
+      <c r="AC60" s="40" t="n"/>
+      <c r="AD60" s="24" t="n"/>
+      <c r="AE60" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.6100 (aec-mlb-cws-tex-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF60" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG60" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH60" s="24" t="n"/>
+      <c r="AI60" s="31" t="n"/>
+      <c r="AJ60" s="31" t="n"/>
+      <c r="AK60" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL60" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM60" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN60" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO60" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP60" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cws</t>
+        </is>
+      </c>
+      <c r="AQ60" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AR60" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AS60" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tex</t>
+        </is>
+      </c>
+      <c r="AT60" s="24" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="AU60" s="24" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="AV60" s="24" t="n"/>
+      <c r="AW60" s="24" t="n"/>
+      <c r="AX60" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY60" s="24" t="n"/>
+      <c r="AZ60" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA60" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB60" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC60" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD60" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE60" s="24" t="inlineStr">
+        <is>
+          <t>99c414db5594aff2</t>
+        </is>
+      </c>
+      <c r="BF60" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG60" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH60" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:25:54.352994Z</t>
+        </is>
+      </c>
+      <c r="BI60" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ60" s="38" t="n"/>
+      <c r="BK60" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL60" s="39" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM60" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN60" s="28" t="n">
+        <v>0.606965</v>
+      </c>
+      <c r="BO60" s="28" t="n"/>
+      <c r="BP60" s="38" t="n"/>
+      <c r="BQ60" s="39" t="n"/>
+      <c r="BR60" s="28" t="n"/>
+      <c r="BS60" s="28" t="n"/>
+      <c r="BT60" s="28" t="n"/>
+      <c r="BU60" s="38" t="n"/>
+      <c r="BV60" s="29" t="n"/>
+      <c r="BW60" s="24" t="n"/>
+      <c r="BX60" s="40" t="n"/>
+      <c r="BY60" s="39" t="n"/>
+      <c r="BZ60" s="24" t="n"/>
+      <c r="CA60" s="31" t="n"/>
+    </row>
+    <row r="61" ht="36" customHeight="1">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>fe1acb3bd59e41b3</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:09.837629Z</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>401816193</t>
+        </is>
+      </c>
+      <c r="E61" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F61" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="G61" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="H61" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I61" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J61" s="38" t="n"/>
+      <c r="K61" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L61" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M61" s="39" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N61" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O61" s="28" t="n">
+        <v>0.576624</v>
+      </c>
+      <c r="P61" s="28" t="n"/>
+      <c r="Q61" s="28" t="n">
+        <v>0.057393</v>
+      </c>
+      <c r="R61" s="26" t="n">
+        <v>49</v>
+      </c>
+      <c r="S61" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T61" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U61" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V61" s="24" t="n"/>
+      <c r="W61" s="26" t="n"/>
+      <c r="X61" s="26" t="n"/>
+      <c r="Y61" s="38" t="n"/>
+      <c r="Z61" s="26" t="n"/>
+      <c r="AA61" s="28" t="n"/>
+      <c r="AB61" s="28" t="n"/>
+      <c r="AC61" s="40" t="n"/>
+      <c r="AD61" s="24" t="n"/>
+      <c r="AE61" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5200 (aec-mlb-det-chc-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF61" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG61" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH61" s="24" t="n"/>
+      <c r="AI61" s="31" t="n"/>
+      <c r="AJ61" s="31" t="n"/>
+      <c r="AK61" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL61" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM61" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN61" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO61" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP61" s="24" t="inlineStr">
+        <is>
+          <t>mlb-det</t>
+        </is>
+      </c>
+      <c r="AQ61" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AR61" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AS61" s="24" t="inlineStr">
+        <is>
+          <t>mlb-chc</t>
+        </is>
+      </c>
+      <c r="AT61" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AU61" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AV61" s="24" t="n"/>
+      <c r="AW61" s="24" t="n"/>
+      <c r="AX61" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY61" s="24" t="n"/>
+      <c r="AZ61" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA61" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB61" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC61" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD61" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE61" s="24" t="inlineStr">
+        <is>
+          <t>cc155e3ebbdaf924</t>
+        </is>
+      </c>
+      <c r="BF61" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG61" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH61" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:25:55.980853Z</t>
+        </is>
+      </c>
+      <c r="BI61" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ61" s="38" t="n"/>
+      <c r="BK61" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL61" s="39" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM61" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN61" s="28" t="n">
+        <v>0.517413</v>
+      </c>
+      <c r="BO61" s="28" t="n"/>
+      <c r="BP61" s="38" t="n"/>
+      <c r="BQ61" s="39" t="n"/>
+      <c r="BR61" s="28" t="n"/>
+      <c r="BS61" s="28" t="n"/>
+      <c r="BT61" s="28" t="n"/>
+      <c r="BU61" s="38" t="n"/>
+      <c r="BV61" s="29" t="n"/>
+      <c r="BW61" s="24" t="n"/>
+      <c r="BX61" s="40" t="n"/>
+      <c r="BY61" s="39" t="n"/>
+      <c r="BZ61" s="24" t="n"/>
+      <c r="CA61" s="31" t="n"/>
+    </row>
+    <row r="62" ht="36" customHeight="1">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>41914e723f8545e3</t>
+        </is>
+      </c>
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:09.837629Z</t>
+        </is>
+      </c>
+      <c r="C62" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D62" s="24" t="inlineStr">
+        <is>
+          <t>401816197</t>
+        </is>
+      </c>
+      <c r="E62" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F62" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="G62" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="H62" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I62" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J62" s="38" t="n"/>
+      <c r="K62" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L62" s="26" t="n">
+        <v>-115</v>
+      </c>
+      <c r="M62" s="39" t="n">
+        <v>1.869565</v>
+      </c>
+      <c r="N62" s="28" t="n">
+        <v>0.534884</v>
+      </c>
+      <c r="O62" s="28" t="n">
+        <v>0.547691</v>
+      </c>
+      <c r="P62" s="28" t="n"/>
+      <c r="Q62" s="28" t="n">
+        <v>0.012807</v>
+      </c>
+      <c r="R62" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="S62" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U62" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V62" s="24" t="n"/>
+      <c r="W62" s="26" t="n"/>
+      <c r="X62" s="26" t="n"/>
+      <c r="Y62" s="38" t="n"/>
+      <c r="Z62" s="26" t="n"/>
+      <c r="AA62" s="28" t="n"/>
+      <c r="AB62" s="28" t="n"/>
+      <c r="AC62" s="40" t="n"/>
+      <c r="AD62" s="24" t="n"/>
+      <c r="AE62" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5350 (aec-mlb-wsh-col-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF62" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG62" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH62" s="24" t="n"/>
+      <c r="AI62" s="31" t="n"/>
+      <c r="AJ62" s="31" t="n"/>
+      <c r="AK62" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL62" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM62" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN62" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO62" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP62" s="24" t="inlineStr">
+        <is>
+          <t>mlb-wsh</t>
+        </is>
+      </c>
+      <c r="AQ62" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="AR62" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="AS62" s="24" t="inlineStr">
+        <is>
+          <t>mlb-col</t>
+        </is>
+      </c>
+      <c r="AT62" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AU62" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AV62" s="24" t="n"/>
+      <c r="AW62" s="24" t="n"/>
+      <c r="AX62" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY62" s="24" t="n"/>
+      <c r="AZ62" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA62" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB62" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC62" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD62" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE62" s="24" t="inlineStr">
+        <is>
+          <t>c4e9d6e5adabb27c</t>
+        </is>
+      </c>
+      <c r="BF62" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG62" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH62" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:25:57.709954Z</t>
+        </is>
+      </c>
+      <c r="BI62" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ62" s="38" t="n"/>
+      <c r="BK62" s="26" t="n">
+        <v>-115</v>
+      </c>
+      <c r="BL62" s="39" t="n">
+        <v>1.869565</v>
+      </c>
+      <c r="BM62" s="28" t="n">
+        <v>0.534884</v>
+      </c>
+      <c r="BN62" s="28" t="n">
+        <v>0.532338</v>
+      </c>
+      <c r="BO62" s="28" t="n"/>
+      <c r="BP62" s="38" t="n"/>
+      <c r="BQ62" s="39" t="n"/>
+      <c r="BR62" s="28" t="n"/>
+      <c r="BS62" s="28" t="n"/>
+      <c r="BT62" s="28" t="n"/>
+      <c r="BU62" s="38" t="n"/>
+      <c r="BV62" s="29" t="n"/>
+      <c r="BW62" s="24" t="n"/>
+      <c r="BX62" s="40" t="n"/>
+      <c r="BY62" s="39" t="n"/>
+      <c r="BZ62" s="24" t="n"/>
+      <c r="CA62" s="31" t="n"/>
+    </row>
+    <row r="63" ht="36" customHeight="1">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>226f56cb020a4d72</t>
+        </is>
+      </c>
+      <c r="B63" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:09.837629Z</t>
+        </is>
+      </c>
+      <c r="C63" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D63" s="24" t="inlineStr">
+        <is>
+          <t>401816198</t>
+        </is>
+      </c>
+      <c r="E63" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F63" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="G63" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="H63" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I63" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J63" s="38" t="n"/>
+      <c r="K63" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L63" s="26" t="n">
+        <v>-147</v>
+      </c>
+      <c r="M63" s="39" t="n">
+        <v>1.680272</v>
+      </c>
+      <c r="N63" s="28" t="n">
+        <v>0.5951419999999999</v>
+      </c>
+      <c r="O63" s="28" t="n">
+        <v>0.589249</v>
+      </c>
+      <c r="P63" s="28" t="n"/>
+      <c r="Q63" s="28" t="n">
+        <v>-0.005893</v>
+      </c>
+      <c r="R63" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="S63" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T63" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U63" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V63" s="24" t="n"/>
+      <c r="W63" s="26" t="n"/>
+      <c r="X63" s="26" t="n"/>
+      <c r="Y63" s="38" t="n"/>
+      <c r="Z63" s="26" t="n"/>
+      <c r="AA63" s="28" t="n"/>
+      <c r="AB63" s="28" t="n"/>
+      <c r="AC63" s="40" t="n"/>
+      <c r="AD63" s="24" t="n"/>
+      <c r="AE63" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5950 (aec-mlb-ath-az-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF63" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG63" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH63" s="24" t="n"/>
+      <c r="AI63" s="31" t="n"/>
+      <c r="AJ63" s="31" t="n"/>
+      <c r="AK63" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL63" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM63" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN63" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO63" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP63" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ath</t>
+        </is>
+      </c>
+      <c r="AQ63" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AR63" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AS63" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ari</t>
+        </is>
+      </c>
+      <c r="AT63" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AU63" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AV63" s="24" t="n"/>
+      <c r="AW63" s="24" t="n"/>
+      <c r="AX63" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY63" s="24" t="n"/>
+      <c r="AZ63" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA63" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB63" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC63" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD63" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE63" s="24" t="inlineStr">
+        <is>
+          <t>202c6fbc367f9e59</t>
+        </is>
+      </c>
+      <c r="BF63" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG63" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH63" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:25:58.909244Z</t>
+        </is>
+      </c>
+      <c r="BI63" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ63" s="38" t="n"/>
+      <c r="BK63" s="26" t="n">
+        <v>-147</v>
+      </c>
+      <c r="BL63" s="39" t="n">
+        <v>1.680272</v>
+      </c>
+      <c r="BM63" s="28" t="n">
+        <v>0.5951419999999999</v>
+      </c>
+      <c r="BN63" s="28" t="n">
+        <v>0.59204</v>
+      </c>
+      <c r="BO63" s="28" t="n"/>
+      <c r="BP63" s="38" t="n"/>
+      <c r="BQ63" s="39" t="n"/>
+      <c r="BR63" s="28" t="n"/>
+      <c r="BS63" s="28" t="n"/>
+      <c r="BT63" s="28" t="n"/>
+      <c r="BU63" s="38" t="n"/>
+      <c r="BV63" s="29" t="n"/>
+      <c r="BW63" s="24" t="n"/>
+      <c r="BX63" s="40" t="n"/>
+      <c r="BY63" s="39" t="n"/>
+      <c r="BZ63" s="24" t="n"/>
+      <c r="CA63" s="31" t="n"/>
+    </row>
+    <row r="64" ht="36" customHeight="1">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>a9cd87c83dca4e08</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:09.837629Z</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D64" s="24" t="inlineStr">
+        <is>
+          <t>401816199</t>
+        </is>
+      </c>
+      <c r="E64" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F64" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="G64" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="H64" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I64" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J64" s="38" t="n"/>
+      <c r="K64" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L64" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M64" s="39" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N64" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O64" s="28" t="n">
+        <v>0.597509</v>
+      </c>
+      <c r="P64" s="28" t="n"/>
+      <c r="Q64" s="28" t="n">
+        <v>0.007345</v>
+      </c>
+      <c r="R64" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="S64" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T64" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U64" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V64" s="24" t="n"/>
+      <c r="W64" s="26" t="n"/>
+      <c r="X64" s="26" t="n"/>
+      <c r="Y64" s="38" t="n"/>
+      <c r="Z64" s="26" t="n"/>
+      <c r="AA64" s="28" t="n"/>
+      <c r="AB64" s="28" t="n"/>
+      <c r="AC64" s="40" t="n"/>
+      <c r="AD64" s="24" t="n"/>
+      <c r="AE64" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5900 (aec-mlb-cin-sea-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF64" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG64" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH64" s="24" t="n"/>
+      <c r="AI64" s="31" t="n"/>
+      <c r="AJ64" s="31" t="n"/>
+      <c r="AK64" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL64" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM64" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN64" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO64" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP64" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cin</t>
+        </is>
+      </c>
+      <c r="AQ64" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AR64" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AS64" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sea</t>
+        </is>
+      </c>
+      <c r="AT64" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AU64" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AV64" s="24" t="n"/>
+      <c r="AW64" s="24" t="n"/>
+      <c r="AX64" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY64" s="24" t="n"/>
+      <c r="AZ64" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA64" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB64" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC64" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD64" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE64" s="24" t="inlineStr">
+        <is>
+          <t>982d73638d70c45b</t>
+        </is>
+      </c>
+      <c r="BF64" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG64" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH64" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:26:01.154096Z</t>
+        </is>
+      </c>
+      <c r="BI64" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ64" s="38" t="n"/>
+      <c r="BK64" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL64" s="39" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM64" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN64" s="28" t="n">
+        <v>0.5870649999999999</v>
+      </c>
+      <c r="BO64" s="28" t="n"/>
+      <c r="BP64" s="38" t="n"/>
+      <c r="BQ64" s="39" t="n"/>
+      <c r="BR64" s="28" t="n"/>
+      <c r="BS64" s="28" t="n"/>
+      <c r="BT64" s="28" t="n"/>
+      <c r="BU64" s="38" t="n"/>
+      <c r="BV64" s="29" t="n"/>
+      <c r="BW64" s="24" t="n"/>
+      <c r="BX64" s="40" t="n"/>
+      <c r="BY64" s="39" t="n"/>
+      <c r="BZ64" s="24" t="n"/>
+      <c r="CA64" s="31" t="n"/>
+    </row>
+    <row r="65" ht="36" customHeight="1">
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>8e420714a95e4d9c</t>
+        </is>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:09.837629Z</t>
+        </is>
+      </c>
+      <c r="C65" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D65" s="24" t="inlineStr">
+        <is>
+          <t>401816200</t>
+        </is>
+      </c>
+      <c r="E65" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F65" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="G65" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="H65" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I65" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J65" s="38" t="n"/>
+      <c r="K65" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L65" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M65" s="39" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N65" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O65" s="28" t="n">
+        <v>0.5411280000000001</v>
+      </c>
+      <c r="P65" s="28" t="n"/>
+      <c r="Q65" s="28" t="n">
+        <v>0.050932</v>
+      </c>
+      <c r="R65" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S65" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U65" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V65" s="24" t="n"/>
+      <c r="W65" s="26" t="n"/>
+      <c r="X65" s="26" t="n"/>
+      <c r="Y65" s="38" t="n"/>
+      <c r="Z65" s="26" t="n"/>
+      <c r="AA65" s="28" t="n"/>
+      <c r="AB65" s="28" t="n"/>
+      <c r="AC65" s="40" t="n"/>
+      <c r="AD65" s="24" t="n"/>
+      <c r="AE65" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.4900 (aec-mlb-stl-laa-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF65" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG65" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH65" s="24" t="n"/>
+      <c r="AI65" s="31" t="n"/>
+      <c r="AJ65" s="31" t="n"/>
+      <c r="AK65" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL65" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM65" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN65" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO65" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP65" s="24" t="inlineStr">
+        <is>
+          <t>mlb-stl</t>
+        </is>
+      </c>
+      <c r="AQ65" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="AR65" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="AS65" s="24" t="inlineStr">
+        <is>
+          <t>mlb-laa</t>
+        </is>
+      </c>
+      <c r="AT65" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="AU65" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="AV65" s="24" t="n"/>
+      <c r="AW65" s="24" t="n"/>
+      <c r="AX65" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY65" s="24" t="n"/>
+      <c r="AZ65" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA65" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB65" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC65" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD65" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE65" s="24" t="inlineStr">
+        <is>
+          <t>84a60e91d728d400</t>
+        </is>
+      </c>
+      <c r="BF65" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG65" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH65" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:26:01.325929Z</t>
+        </is>
+      </c>
+      <c r="BI65" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ65" s="38" t="n"/>
+      <c r="BK65" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL65" s="39" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM65" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN65" s="28" t="n">
+        <v>0.487562</v>
+      </c>
+      <c r="BO65" s="28" t="n"/>
+      <c r="BP65" s="38" t="n"/>
+      <c r="BQ65" s="39" t="n"/>
+      <c r="BR65" s="28" t="n"/>
+      <c r="BS65" s="28" t="n"/>
+      <c r="BT65" s="28" t="n"/>
+      <c r="BU65" s="38" t="n"/>
+      <c r="BV65" s="29" t="n"/>
+      <c r="BW65" s="24" t="n"/>
+      <c r="BX65" s="40" t="n"/>
+      <c r="BY65" s="39" t="n"/>
+      <c r="BZ65" s="24" t="n"/>
+      <c r="CA65" s="31" t="n"/>
+    </row>
+    <row r="66" ht="36" customHeight="1">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>e35a217d64aa4265</t>
+        </is>
+      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:15.488547Z</t>
+        </is>
+      </c>
+      <c r="C66" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D66" s="24" t="inlineStr">
+        <is>
+          <t>401857083</t>
+        </is>
+      </c>
+      <c r="E66" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F66" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="G66" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="H66" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I66" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J66" s="38" t="n"/>
+      <c r="K66" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L66" s="26" t="n">
+        <v>-488</v>
+      </c>
+      <c r="M66" s="39" t="n">
+        <v>1.204918</v>
+      </c>
+      <c r="N66" s="28" t="n">
+        <v>0.829932</v>
+      </c>
+      <c r="O66" s="28" t="n">
+        <v>0.657294</v>
+      </c>
+      <c r="P66" s="28" t="n"/>
+      <c r="Q66" s="28" t="n">
+        <v>-0.172638</v>
+      </c>
+      <c r="R66" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T66" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U66" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V66" s="24" t="n"/>
+      <c r="W66" s="26" t="n"/>
+      <c r="X66" s="26" t="n"/>
+      <c r="Y66" s="38" t="n"/>
+      <c r="Z66" s="26" t="n"/>
+      <c r="AA66" s="28" t="n"/>
+      <c r="AB66" s="28" t="n"/>
+      <c r="AC66" s="40" t="n"/>
+      <c r="AD66" s="24" t="n"/>
+      <c r="AE66" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5000; executable ask 0.8300 (aec-wnba-lv-tor-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF66" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG66" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH66" s="24" t="n"/>
+      <c r="AI66" s="31" t="n"/>
+      <c r="AJ66" s="31" t="n"/>
+      <c r="AK66" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL66" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM66" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN66" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO66" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP66" s="24" t="inlineStr">
+        <is>
+          <t>wnba-lva</t>
+        </is>
+      </c>
+      <c r="AQ66" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AR66" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AS66" s="24" t="inlineStr">
+        <is>
+          <t>wnba-tor</t>
+        </is>
+      </c>
+      <c r="AT66" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AU66" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AV66" s="24" t="n"/>
+      <c r="AW66" s="24" t="n"/>
+      <c r="AX66" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY66" s="24" t="n"/>
+      <c r="AZ66" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA66" s="24" t="inlineStr">
+        <is>
+          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+        </is>
+      </c>
+      <c r="BB66" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC66" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD66" s="24" t="inlineStr">
+        <is>
+          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+        </is>
+      </c>
+      <c r="BE66" s="24" t="inlineStr">
+        <is>
+          <t>b239d28861d5b74d</t>
+        </is>
+      </c>
+      <c r="BF66" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG66" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH66" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:26:02.605954Z</t>
+        </is>
+      </c>
+      <c r="BI66" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ66" s="38" t="n"/>
+      <c r="BK66" s="26" t="n">
+        <v>-488</v>
+      </c>
+      <c r="BL66" s="39" t="n">
+        <v>1.204918</v>
+      </c>
+      <c r="BM66" s="28" t="n">
+        <v>0.829932</v>
+      </c>
+      <c r="BN66" s="28" t="n">
+        <v>0.821782</v>
+      </c>
+      <c r="BO66" s="28" t="n"/>
+      <c r="BP66" s="38" t="n"/>
+      <c r="BQ66" s="39" t="n"/>
+      <c r="BR66" s="28" t="n"/>
+      <c r="BS66" s="28" t="n"/>
+      <c r="BT66" s="28" t="n"/>
+      <c r="BU66" s="38" t="n"/>
+      <c r="BV66" s="29" t="n"/>
+      <c r="BW66" s="24" t="n"/>
+      <c r="BX66" s="40" t="n"/>
+      <c r="BY66" s="39" t="n"/>
+      <c r="BZ66" s="24" t="n"/>
+      <c r="CA66" s="31" t="n"/>
+    </row>
+    <row r="67" ht="36" customHeight="1">
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>6c42d2d2436849c1</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:15.488547Z</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D67" s="24" t="inlineStr">
+        <is>
+          <t>401892393</t>
+        </is>
+      </c>
+      <c r="E67" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F67" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="G67" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="H67" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I67" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J67" s="38" t="n"/>
+      <c r="K67" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L67" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M67" s="39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N67" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O67" s="28" t="n">
+        <v>0.6787840000000001</v>
+      </c>
+      <c r="P67" s="28" t="n"/>
+      <c r="Q67" s="28" t="n">
+        <v>0.278784</v>
+      </c>
+      <c r="R67" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S67" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T67" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U67" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V67" s="24" t="n"/>
+      <c r="W67" s="26" t="n"/>
+      <c r="X67" s="26" t="n"/>
+      <c r="Y67" s="38" t="n"/>
+      <c r="Z67" s="26" t="n"/>
+      <c r="AA67" s="28" t="n"/>
+      <c r="AB67" s="28" t="n"/>
+      <c r="AC67" s="40" t="n"/>
+      <c r="AD67" s="24" t="n"/>
+      <c r="AE67" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5000; executable ask 0.4000 (aec-wnba-ny-dal-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF67" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG67" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH67" s="24" t="n"/>
+      <c r="AI67" s="31" t="n"/>
+      <c r="AJ67" s="31" t="n"/>
+      <c r="AK67" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL67" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM67" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN67" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO67" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP67" s="24" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AQ67" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AR67" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AS67" s="24" t="inlineStr">
+        <is>
+          <t>wnba-dal</t>
+        </is>
+      </c>
+      <c r="AT67" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AU67" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AV67" s="24" t="n"/>
+      <c r="AW67" s="24" t="n"/>
+      <c r="AX67" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY67" s="24" t="n"/>
+      <c r="AZ67" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA67" s="24" t="inlineStr">
+        <is>
+          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+        </is>
+      </c>
+      <c r="BB67" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC67" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD67" s="24" t="inlineStr">
+        <is>
+          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+        </is>
+      </c>
+      <c r="BE67" s="24" t="inlineStr">
+        <is>
+          <t>1c6f45e72b2d1f80</t>
+        </is>
+      </c>
+      <c r="BF67" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG67" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH67" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:26:04.731909Z</t>
+        </is>
+      </c>
+      <c r="BI67" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ67" s="38" t="n"/>
+      <c r="BK67" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL67" s="39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM67" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN67" s="28" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="BO67" s="28" t="n"/>
+      <c r="BP67" s="38" t="n"/>
+      <c r="BQ67" s="39" t="n"/>
+      <c r="BR67" s="28" t="n"/>
+      <c r="BS67" s="28" t="n"/>
+      <c r="BT67" s="28" t="n"/>
+      <c r="BU67" s="38" t="n"/>
+      <c r="BV67" s="29" t="n"/>
+      <c r="BW67" s="24" t="n"/>
+      <c r="BX67" s="40" t="n"/>
+      <c r="BY67" s="39" t="n"/>
+      <c r="BZ67" s="24" t="n"/>
+      <c r="CA67" s="31" t="n"/>
+    </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>0da50dc88c9649b8</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:15.488547Z</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>401857084</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="G68" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="H68" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I68" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J68" s="38" t="n"/>
+      <c r="K68" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L68" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="M68" s="39" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="N68" s="28" t="n">
+        <v>0.760192</v>
+      </c>
+      <c r="O68" s="28" t="n">
+        <v>0.750444</v>
+      </c>
+      <c r="P68" s="28" t="n"/>
+      <c r="Q68" s="28" t="n">
+        <v>-0.009748</v>
+      </c>
+      <c r="R68" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="S68" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T68" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U68" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V68" s="24" t="n"/>
+      <c r="W68" s="26" t="n"/>
+      <c r="X68" s="26" t="n"/>
+      <c r="Y68" s="38" t="n"/>
+      <c r="Z68" s="26" t="n"/>
+      <c r="AA68" s="28" t="n"/>
+      <c r="AB68" s="28" t="n"/>
+      <c r="AC68" s="40" t="n"/>
+      <c r="AD68" s="24" t="n"/>
+      <c r="AE68" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5000; executable ask 0.7600 (aec-wnba-wsh-gsv-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF68" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG68" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH68" s="24" t="n"/>
+      <c r="AI68" s="31" t="n"/>
+      <c r="AJ68" s="31" t="n"/>
+      <c r="AK68" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL68" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM68" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN68" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO68" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP68" s="24" t="inlineStr">
+        <is>
+          <t>wnba-was</t>
+        </is>
+      </c>
+      <c r="AQ68" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AR68" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AS68" s="24" t="inlineStr">
+        <is>
+          <t>wnba-gsv</t>
+        </is>
+      </c>
+      <c r="AT68" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AU68" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AV68" s="24" t="n"/>
+      <c r="AW68" s="24" t="n"/>
+      <c r="AX68" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY68" s="24" t="n"/>
+      <c r="AZ68" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA68" s="24" t="inlineStr">
+        <is>
+          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+        </is>
+      </c>
+      <c r="BB68" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC68" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD68" s="24" t="inlineStr">
+        <is>
+          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+        </is>
+      </c>
+      <c r="BE68" s="24" t="inlineStr">
+        <is>
+          <t>46de7d71a35c9491</t>
+        </is>
+      </c>
+      <c r="BF68" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG68" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH68" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:26:06.455979Z</t>
+        </is>
+      </c>
+      <c r="BI68" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ68" s="38" t="n"/>
+      <c r="BK68" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="BL68" s="39" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="BM68" s="28" t="n">
+        <v>0.760192</v>
+      </c>
+      <c r="BN68" s="28" t="n">
+        <v>0.752475</v>
+      </c>
+      <c r="BO68" s="28" t="n"/>
+      <c r="BP68" s="38" t="n"/>
+      <c r="BQ68" s="39" t="n"/>
+      <c r="BR68" s="28" t="n"/>
+      <c r="BS68" s="28" t="n"/>
+      <c r="BT68" s="28" t="n"/>
+      <c r="BU68" s="38" t="n"/>
+      <c r="BV68" s="29" t="n"/>
+      <c r="BW68" s="24" t="n"/>
+      <c r="BX68" s="40" t="n"/>
+      <c r="BY68" s="39" t="n"/>
+      <c r="BZ68" s="24" t="n"/>
+      <c r="CA68" s="31" t="n"/>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>2d184773492d4263</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:27:15.488547Z</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="inlineStr">
+        <is>
+          <t>401857085</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F69" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="G69" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="H69" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I69" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J69" s="38" t="n"/>
+      <c r="K69" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L69" s="26" t="n">
+        <v>-488</v>
+      </c>
+      <c r="M69" s="39" t="n">
+        <v>1.204918</v>
+      </c>
+      <c r="N69" s="28" t="n">
+        <v>0.829932</v>
+      </c>
+      <c r="O69" s="28" t="n">
+        <v>0.739042</v>
+      </c>
+      <c r="P69" s="28" t="n"/>
+      <c r="Q69" s="28" t="n">
+        <v>-0.09089</v>
+      </c>
+      <c r="R69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T69" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U69" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V69" s="24" t="n"/>
+      <c r="W69" s="26" t="n"/>
+      <c r="X69" s="26" t="n"/>
+      <c r="Y69" s="38" t="n"/>
+      <c r="Z69" s="26" t="n"/>
+      <c r="AA69" s="28" t="n"/>
+      <c r="AB69" s="28" t="n"/>
+      <c r="AC69" s="40" t="n"/>
+      <c r="AD69" s="24" t="n"/>
+      <c r="AE69" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5000; executable ask 0.8300 (aec-wnba-min-sea-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF69" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG69" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH69" s="24" t="n"/>
+      <c r="AI69" s="31" t="n"/>
+      <c r="AJ69" s="31" t="n"/>
+      <c r="AK69" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL69" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM69" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN69" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO69" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP69" s="24" t="inlineStr">
+        <is>
+          <t>wnba-min</t>
+        </is>
+      </c>
+      <c r="AQ69" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AR69" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AS69" s="24" t="inlineStr">
+        <is>
+          <t>wnba-sea</t>
+        </is>
+      </c>
+      <c r="AT69" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AU69" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AV69" s="24" t="n"/>
+      <c r="AW69" s="24" t="n"/>
+      <c r="AX69" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY69" s="24" t="n"/>
+      <c r="AZ69" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA69" s="24" t="inlineStr">
+        <is>
+          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+        </is>
+      </c>
+      <c r="BB69" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC69" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD69" s="24" t="inlineStr">
+        <is>
+          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+        </is>
+      </c>
+      <c r="BE69" s="24" t="inlineStr">
+        <is>
+          <t>9e3cecf68c87303d</t>
+        </is>
+      </c>
+      <c r="BF69" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG69" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH69" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:26:06.846002Z</t>
+        </is>
+      </c>
+      <c r="BI69" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ69" s="38" t="n"/>
+      <c r="BK69" s="26" t="n">
+        <v>-488</v>
+      </c>
+      <c r="BL69" s="39" t="n">
+        <v>1.204918</v>
+      </c>
+      <c r="BM69" s="28" t="n">
+        <v>0.829932</v>
+      </c>
+      <c r="BN69" s="28" t="n">
+        <v>0.821782</v>
+      </c>
+      <c r="BO69" s="28" t="n"/>
+      <c r="BP69" s="38" t="n"/>
+      <c r="BQ69" s="39" t="n"/>
+      <c r="BR69" s="28" t="n"/>
+      <c r="BS69" s="28" t="n"/>
+      <c r="BT69" s="28" t="n"/>
+      <c r="BU69" s="38" t="n"/>
+      <c r="BV69" s="29" t="n"/>
+      <c r="BW69" s="24" t="n"/>
+      <c r="BX69" s="40" t="n"/>
+      <c r="BY69" s="39" t="n"/>
+      <c r="BZ69" s="24" t="n"/>
+      <c r="CA69" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -327,8 +327,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA81" headerRowCount="1">
-  <autoFilter ref="A1:CA81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA90" headerRowCount="1">
+  <autoFilter ref="A1:CA90"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -765,19 +765,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$81)</f>
+        <f>COUNTA('Picks'!$A$2:$A$90)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$81,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$90,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$81,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$90,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$81,"settled",'Picks'!$V$2:$V$81,"win")+COUNTIFS('Picks'!$U$2:$U$81,"settled",'Picks'!$V$2:$V$81,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")+COUNTIFS('Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -806,19 +806,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$81,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$90,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$81,"&gt;0",'Picks'!$V$2:$V$81,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$81,"&gt;0",'Picks'!$V$2:$V$81,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="32">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$81,"&gt;0",'Picks'!$V$2:$V$81,"win")/(COUNTIFS('Picks'!$BX$2:$BX$81,"&gt;0",'Picks'!$V$2:$V$81,"win")+COUNTIFS('Picks'!$BX$2:$BX$81,"&gt;0",'Picks'!$V$2:$V$81,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"win")/(COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"win")+COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="32">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$81)/SUM('Picks'!$BX$2:$BX$81),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$90)/SUM('Picks'!$BX$2:$BX$90),0)</f>
         <v/>
       </c>
     </row>
@@ -847,19 +847,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="33">
-        <f>SUM('Picks'!$BY$2:$BY$81)</f>
+        <f>SUM('Picks'!$BY$2:$BY$90)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$81,"&lt;&gt;",'Picks'!$AB$2:$AB$81),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$90,"&lt;&gt;",'Picks'!$AB$2:$AB$90),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$81,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$81,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$90,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$90,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="33">
-        <f>SUMIFS('Picks'!$AC$2:$AC$81,'Picks'!$AM$2:$AM$81,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$90,'Picks'!$AM$2:$AM$90,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -915,15 +915,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$81,$A14,'Picks'!$U$2:$U$81,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$81,$A14,'Picks'!$U$2:$U$81,"settled",'Picks'!$V$2:$V$81,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$81,$A14,'Picks'!$U$2:$U$81,"settled",'Picks'!$V$2:$V$81,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="34">
@@ -931,11 +931,11 @@
         <v/>
       </c>
       <c r="F14" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$81,'Picks'!$H$2:$H$81,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$90,'Picks'!$H$2:$H$90,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$81,'Picks'!$H$2:$H$81,$A14,'Picks'!$U$2:$U$81,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$90,'Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -946,15 +946,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$81,$A15,'Picks'!$U$2:$U$81,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$81,$A15,'Picks'!$U$2:$U$81,"settled",'Picks'!$V$2:$V$81,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$81,$A15,'Picks'!$U$2:$U$81,"settled",'Picks'!$V$2:$V$81,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="36">
@@ -962,11 +962,11 @@
         <v/>
       </c>
       <c r="F15" s="37">
-        <f>SUMIFS('Picks'!$BY$2:$BY$81,'Picks'!$H$2:$H$81,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$90,'Picks'!$H$2:$H$90,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$81,'Picks'!$H$2:$H$81,$A15,'Picks'!$U$2:$U$81,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$90,'Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -977,15 +977,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$81,$A16,'Picks'!$U$2:$U$81,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$81,$A16,'Picks'!$U$2:$U$81,"settled",'Picks'!$V$2:$V$81,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$81,$A16,'Picks'!$U$2:$U$81,"settled",'Picks'!$V$2:$V$81,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="34">
@@ -993,11 +993,11 @@
         <v/>
       </c>
       <c r="F16" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$81,'Picks'!$H$2:$H$81,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$90,'Picks'!$H$2:$H$90,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$81,'Picks'!$H$2:$H$81,$A16,'Picks'!$U$2:$U$81,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$90,'Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA81"/>
+  <dimension ref="A1:CA90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20474,6 +20474,2247 @@
       <c r="BZ81" s="24" t="n"/>
       <c r="CA81" s="31" t="n"/>
     </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>aaf1b4b6ac094ac8</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:58:34.322674Z</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D82" s="24" t="inlineStr">
+        <is>
+          <t>401816188</t>
+        </is>
+      </c>
+      <c r="E82" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F82" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="G82" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="H82" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I82" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J82" s="38" t="n"/>
+      <c r="K82" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L82" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="M82" s="39" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N82" s="28" t="n">
+        <v>0.473934</v>
+      </c>
+      <c r="O82" s="28" t="n">
+        <v>0.5726869999999999</v>
+      </c>
+      <c r="P82" s="28" t="n"/>
+      <c r="Q82" s="28" t="n">
+        <v>0.09875299999999999</v>
+      </c>
+      <c r="R82" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="S82" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T82" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U82" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V82" s="24" t="n"/>
+      <c r="W82" s="26" t="n"/>
+      <c r="X82" s="26" t="n"/>
+      <c r="Y82" s="38" t="n"/>
+      <c r="Z82" s="26" t="n"/>
+      <c r="AA82" s="28" t="n"/>
+      <c r="AB82" s="28" t="n"/>
+      <c r="AC82" s="40" t="n"/>
+      <c r="AD82" s="24" t="n"/>
+      <c r="AE82" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.4750 (aec-mlb-min-cle-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF82" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG82" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH82" s="24" t="n"/>
+      <c r="AI82" s="31" t="n"/>
+      <c r="AJ82" s="31" t="n"/>
+      <c r="AK82" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL82" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM82" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN82" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO82" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP82" s="24" t="inlineStr">
+        <is>
+          <t>mlb-min</t>
+        </is>
+      </c>
+      <c r="AQ82" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AR82" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AS82" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cle</t>
+        </is>
+      </c>
+      <c r="AT82" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AU82" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AV82" s="24" t="n"/>
+      <c r="AW82" s="24" t="n"/>
+      <c r="AX82" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY82" s="24" t="n"/>
+      <c r="AZ82" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA82" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB82" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC82" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD82" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE82" s="24" t="inlineStr">
+        <is>
+          <t>2170ac399ced5417</t>
+        </is>
+      </c>
+      <c r="BF82" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG82" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH82" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:57:32.219947Z</t>
+        </is>
+      </c>
+      <c r="BI82" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ82" s="38" t="n"/>
+      <c r="BK82" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="BL82" s="39" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM82" s="28" t="n">
+        <v>0.473934</v>
+      </c>
+      <c r="BN82" s="28" t="n">
+        <v>0.472637</v>
+      </c>
+      <c r="BO82" s="28" t="n"/>
+      <c r="BP82" s="38" t="n"/>
+      <c r="BQ82" s="39" t="n"/>
+      <c r="BR82" s="28" t="n"/>
+      <c r="BS82" s="28" t="n"/>
+      <c r="BT82" s="28" t="n"/>
+      <c r="BU82" s="38" t="n"/>
+      <c r="BV82" s="29" t="n"/>
+      <c r="BW82" s="24" t="n"/>
+      <c r="BX82" s="40" t="n"/>
+      <c r="BY82" s="39" t="n"/>
+      <c r="BZ82" s="24" t="n"/>
+      <c r="CA82" s="31" t="n"/>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>14a96af3a7654557</t>
+        </is>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:58:34.322674Z</t>
+        </is>
+      </c>
+      <c r="C83" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>401816189</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F83" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J83" s="38" t="n"/>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L83" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M83" s="39" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N83" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O83" s="28" t="n">
+        <v>0.578558</v>
+      </c>
+      <c r="P83" s="28" t="n"/>
+      <c r="Q83" s="28" t="n">
+        <v>0.059327</v>
+      </c>
+      <c r="R83" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="S83" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T83" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U83" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V83" s="24" t="n"/>
+      <c r="W83" s="26" t="n"/>
+      <c r="X83" s="26" t="n"/>
+      <c r="Y83" s="38" t="n"/>
+      <c r="Z83" s="26" t="n"/>
+      <c r="AA83" s="28" t="n"/>
+      <c r="AB83" s="28" t="n"/>
+      <c r="AC83" s="40" t="n"/>
+      <c r="AD83" s="24" t="n"/>
+      <c r="AE83" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-pit-nyy-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF83" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG83" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH83" s="24" t="n"/>
+      <c r="AI83" s="31" t="n"/>
+      <c r="AJ83" s="31" t="n"/>
+      <c r="AK83" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL83" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM83" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN83" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO83" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP83" s="24" t="inlineStr">
+        <is>
+          <t>mlb-pit</t>
+        </is>
+      </c>
+      <c r="AQ83" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AR83" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AS83" s="24" t="inlineStr">
+        <is>
+          <t>mlb-nyy</t>
+        </is>
+      </c>
+      <c r="AT83" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AU83" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AV83" s="24" t="n"/>
+      <c r="AW83" s="24" t="n"/>
+      <c r="AX83" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY83" s="24" t="n"/>
+      <c r="AZ83" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA83" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB83" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC83" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD83" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE83" s="24" t="inlineStr">
+        <is>
+          <t>38ab7db5a3798f0c</t>
+        </is>
+      </c>
+      <c r="BF83" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG83" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH83" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:57:35.056972Z</t>
+        </is>
+      </c>
+      <c r="BI83" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ83" s="38" t="n"/>
+      <c r="BK83" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL83" s="39" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM83" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN83" s="28" t="n">
+        <v>0.517413</v>
+      </c>
+      <c r="BO83" s="28" t="n"/>
+      <c r="BP83" s="38" t="n"/>
+      <c r="BQ83" s="39" t="n"/>
+      <c r="BR83" s="28" t="n"/>
+      <c r="BS83" s="28" t="n"/>
+      <c r="BT83" s="28" t="n"/>
+      <c r="BU83" s="38" t="n"/>
+      <c r="BV83" s="29" t="n"/>
+      <c r="BW83" s="24" t="n"/>
+      <c r="BX83" s="40" t="n"/>
+      <c r="BY83" s="39" t="n"/>
+      <c r="BZ83" s="24" t="n"/>
+      <c r="CA83" s="31" t="n"/>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>4859b2be84c249d7</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:58:34.322674Z</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="inlineStr">
+        <is>
+          <t>401816186</t>
+        </is>
+      </c>
+      <c r="E84" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="G84" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="H84" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I84" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J84" s="38" t="n"/>
+      <c r="K84" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L84" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M84" s="39" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N84" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O84" s="28" t="n">
+        <v>0.565797</v>
+      </c>
+      <c r="P84" s="28" t="n"/>
+      <c r="Q84" s="28" t="n">
+        <v>-0.014035</v>
+      </c>
+      <c r="R84" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="S84" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T84" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U84" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V84" s="24" t="n"/>
+      <c r="W84" s="26" t="n"/>
+      <c r="X84" s="26" t="n"/>
+      <c r="Y84" s="38" t="n"/>
+      <c r="Z84" s="26" t="n"/>
+      <c r="AA84" s="28" t="n"/>
+      <c r="AB84" s="28" t="n"/>
+      <c r="AC84" s="40" t="n"/>
+      <c r="AD84" s="24" t="n"/>
+      <c r="AE84" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5800 (aec-mlb-bal-bos-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF84" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG84" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH84" s="24" t="n"/>
+      <c r="AI84" s="31" t="n"/>
+      <c r="AJ84" s="31" t="n"/>
+      <c r="AK84" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL84" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM84" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN84" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO84" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP84" s="24" t="inlineStr">
+        <is>
+          <t>mlb-bal</t>
+        </is>
+      </c>
+      <c r="AQ84" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="AR84" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="AS84" s="24" t="inlineStr">
+        <is>
+          <t>mlb-bos</t>
+        </is>
+      </c>
+      <c r="AT84" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AU84" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AV84" s="24" t="n"/>
+      <c r="AW84" s="24" t="n"/>
+      <c r="AX84" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY84" s="24" t="n"/>
+      <c r="AZ84" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA84" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB84" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC84" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD84" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE84" s="24" t="inlineStr">
+        <is>
+          <t>9fe2d27778a72dfe</t>
+        </is>
+      </c>
+      <c r="BF84" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG84" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH84" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:57:37.354484Z</t>
+        </is>
+      </c>
+      <c r="BI84" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ84" s="38" t="n"/>
+      <c r="BK84" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL84" s="39" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM84" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN84" s="28" t="n">
+        <v>0.577114</v>
+      </c>
+      <c r="BO84" s="28" t="n"/>
+      <c r="BP84" s="38" t="n"/>
+      <c r="BQ84" s="39" t="n"/>
+      <c r="BR84" s="28" t="n"/>
+      <c r="BS84" s="28" t="n"/>
+      <c r="BT84" s="28" t="n"/>
+      <c r="BU84" s="38" t="n"/>
+      <c r="BV84" s="29" t="n"/>
+      <c r="BW84" s="24" t="n"/>
+      <c r="BX84" s="40" t="n"/>
+      <c r="BY84" s="39" t="n"/>
+      <c r="BZ84" s="24" t="n"/>
+      <c r="CA84" s="31" t="n"/>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>41f811ccac474792</t>
+        </is>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:58:34.322674Z</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:15:00-0400</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>401816190</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J85" s="38" t="n"/>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L85" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M85" s="39" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N85" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O85" s="28" t="n">
+        <v>0.550915</v>
+      </c>
+      <c r="P85" s="28" t="n"/>
+      <c r="Q85" s="28" t="n">
+        <v>-0.0199</v>
+      </c>
+      <c r="R85" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="S85" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U85" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V85" s="24" t="n"/>
+      <c r="W85" s="26" t="n"/>
+      <c r="X85" s="26" t="n"/>
+      <c r="Y85" s="38" t="n"/>
+      <c r="Z85" s="26" t="n"/>
+      <c r="AA85" s="28" t="n"/>
+      <c r="AB85" s="28" t="n"/>
+      <c r="AC85" s="40" t="n"/>
+      <c r="AD85" s="24" t="n"/>
+      <c r="AE85" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5700 (aec-mlb-sd-atl-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF85" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG85" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH85" s="24" t="n"/>
+      <c r="AI85" s="31" t="n"/>
+      <c r="AJ85" s="31" t="n"/>
+      <c r="AK85" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL85" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM85" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN85" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO85" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP85" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sd</t>
+        </is>
+      </c>
+      <c r="AQ85" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AR85" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AS85" s="24" t="inlineStr">
+        <is>
+          <t>mlb-atl</t>
+        </is>
+      </c>
+      <c r="AT85" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AU85" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AV85" s="24" t="n"/>
+      <c r="AW85" s="24" t="n"/>
+      <c r="AX85" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY85" s="24" t="n"/>
+      <c r="AZ85" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA85" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB85" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC85" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD85" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE85" s="24" t="inlineStr">
+        <is>
+          <t>f0b5eac7c97d1146</t>
+        </is>
+      </c>
+      <c r="BF85" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG85" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH85" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:57:40.909749Z</t>
+        </is>
+      </c>
+      <c r="BI85" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ85" s="38" t="n"/>
+      <c r="BK85" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL85" s="39" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM85" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN85" s="28" t="n">
+        <v>0.567164</v>
+      </c>
+      <c r="BO85" s="28" t="n"/>
+      <c r="BP85" s="38" t="n"/>
+      <c r="BQ85" s="39" t="n"/>
+      <c r="BR85" s="28" t="n"/>
+      <c r="BS85" s="28" t="n"/>
+      <c r="BT85" s="28" t="n"/>
+      <c r="BU85" s="38" t="n"/>
+      <c r="BV85" s="29" t="n"/>
+      <c r="BW85" s="24" t="n"/>
+      <c r="BX85" s="40" t="n"/>
+      <c r="BY85" s="39" t="n"/>
+      <c r="BZ85" s="24" t="n"/>
+      <c r="CA85" s="31" t="n"/>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="24" t="inlineStr">
+        <is>
+          <t>e68eefc9610e4621</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:58:34.322674Z</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="inlineStr">
+        <is>
+          <t>401816195</t>
+        </is>
+      </c>
+      <c r="E86" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F86" s="24" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="G86" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="H86" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I86" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J86" s="38" t="n"/>
+      <c r="K86" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L86" s="26" t="n">
+        <v>-199</v>
+      </c>
+      <c r="M86" s="39" t="n">
+        <v>1.502513</v>
+      </c>
+      <c r="N86" s="28" t="n">
+        <v>0.665552</v>
+      </c>
+      <c r="O86" s="28" t="n">
+        <v>0.640995</v>
+      </c>
+      <c r="P86" s="28" t="n"/>
+      <c r="Q86" s="28" t="n">
+        <v>-0.024557</v>
+      </c>
+      <c r="R86" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="S86" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T86" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U86" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V86" s="24" t="n"/>
+      <c r="W86" s="26" t="n"/>
+      <c r="X86" s="26" t="n"/>
+      <c r="Y86" s="38" t="n"/>
+      <c r="Z86" s="26" t="n"/>
+      <c r="AA86" s="28" t="n"/>
+      <c r="AB86" s="28" t="n"/>
+      <c r="AC86" s="40" t="n"/>
+      <c r="AD86" s="24" t="n"/>
+      <c r="AE86" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.6650 (aec-mlb-nym-mil-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF86" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG86" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH86" s="24" t="n"/>
+      <c r="AI86" s="31" t="n"/>
+      <c r="AJ86" s="31" t="n"/>
+      <c r="AK86" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL86" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM86" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN86" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO86" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP86" s="24" t="inlineStr">
+        <is>
+          <t>mlb-nym</t>
+        </is>
+      </c>
+      <c r="AQ86" s="24" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="AR86" s="24" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="AS86" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AT86" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AU86" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AV86" s="24" t="n"/>
+      <c r="AW86" s="24" t="n"/>
+      <c r="AX86" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY86" s="24" t="n"/>
+      <c r="AZ86" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA86" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB86" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC86" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD86" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE86" s="24" t="inlineStr">
+        <is>
+          <t>6d5f3f5e8f75cb2b</t>
+        </is>
+      </c>
+      <c r="BF86" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG86" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH86" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:57:42.879792Z</t>
+        </is>
+      </c>
+      <c r="BI86" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ86" s="38" t="n"/>
+      <c r="BK86" s="26" t="n">
+        <v>-199</v>
+      </c>
+      <c r="BL86" s="39" t="n">
+        <v>1.502513</v>
+      </c>
+      <c r="BM86" s="28" t="n">
+        <v>0.665552</v>
+      </c>
+      <c r="BN86" s="28" t="n">
+        <v>0.6616919999999999</v>
+      </c>
+      <c r="BO86" s="28" t="n"/>
+      <c r="BP86" s="38" t="n"/>
+      <c r="BQ86" s="39" t="n"/>
+      <c r="BR86" s="28" t="n"/>
+      <c r="BS86" s="28" t="n"/>
+      <c r="BT86" s="28" t="n"/>
+      <c r="BU86" s="38" t="n"/>
+      <c r="BV86" s="29" t="n"/>
+      <c r="BW86" s="24" t="n"/>
+      <c r="BX86" s="40" t="n"/>
+      <c r="BY86" s="39" t="n"/>
+      <c r="BZ86" s="24" t="n"/>
+      <c r="CA86" s="31" t="n"/>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>8db3a8d8a90f4145</t>
+        </is>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:58:34.322674Z</t>
+        </is>
+      </c>
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>401816193</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F87" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="H87" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I87" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J87" s="38" t="n"/>
+      <c r="K87" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L87" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M87" s="39" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N87" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O87" s="28" t="n">
+        <v>0.566967</v>
+      </c>
+      <c r="P87" s="28" t="n"/>
+      <c r="Q87" s="28" t="n">
+        <v>0.047736</v>
+      </c>
+      <c r="R87" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="S87" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T87" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U87" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V87" s="24" t="n"/>
+      <c r="W87" s="26" t="n"/>
+      <c r="X87" s="26" t="n"/>
+      <c r="Y87" s="38" t="n"/>
+      <c r="Z87" s="26" t="n"/>
+      <c r="AA87" s="28" t="n"/>
+      <c r="AB87" s="28" t="n"/>
+      <c r="AC87" s="40" t="n"/>
+      <c r="AD87" s="24" t="n"/>
+      <c r="AE87" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-det-chc-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF87" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG87" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH87" s="24" t="n"/>
+      <c r="AI87" s="31" t="n"/>
+      <c r="AJ87" s="31" t="n"/>
+      <c r="AK87" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL87" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM87" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN87" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO87" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP87" s="24" t="inlineStr">
+        <is>
+          <t>mlb-det</t>
+        </is>
+      </c>
+      <c r="AQ87" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AR87" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AS87" s="24" t="inlineStr">
+        <is>
+          <t>mlb-chc</t>
+        </is>
+      </c>
+      <c r="AT87" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AU87" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AV87" s="24" t="n"/>
+      <c r="AW87" s="24" t="n"/>
+      <c r="AX87" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY87" s="24" t="n"/>
+      <c r="AZ87" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA87" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB87" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC87" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD87" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE87" s="24" t="inlineStr">
+        <is>
+          <t>b84afb2c70e14d93</t>
+        </is>
+      </c>
+      <c r="BF87" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG87" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH87" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:57:46.871986Z</t>
+        </is>
+      </c>
+      <c r="BI87" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ87" s="38" t="n"/>
+      <c r="BK87" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL87" s="39" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM87" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN87" s="28" t="n">
+        <v>0.517413</v>
+      </c>
+      <c r="BO87" s="28" t="n"/>
+      <c r="BP87" s="38" t="n"/>
+      <c r="BQ87" s="39" t="n"/>
+      <c r="BR87" s="28" t="n"/>
+      <c r="BS87" s="28" t="n"/>
+      <c r="BT87" s="28" t="n"/>
+      <c r="BU87" s="38" t="n"/>
+      <c r="BV87" s="29" t="n"/>
+      <c r="BW87" s="24" t="n"/>
+      <c r="BX87" s="40" t="n"/>
+      <c r="BY87" s="39" t="n"/>
+      <c r="BZ87" s="24" t="n"/>
+      <c r="CA87" s="31" t="n"/>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="A88" s="24" t="inlineStr">
+        <is>
+          <t>63c8de42843a46c9</t>
+        </is>
+      </c>
+      <c r="B88" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:58:34.322674Z</t>
+        </is>
+      </c>
+      <c r="C88" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D88" s="24" t="inlineStr">
+        <is>
+          <t>401816197</t>
+        </is>
+      </c>
+      <c r="E88" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F88" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="G88" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="H88" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I88" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J88" s="38" t="n"/>
+      <c r="K88" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L88" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M88" s="39" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N88" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O88" s="28" t="n">
+        <v>0.5563709999999999</v>
+      </c>
+      <c r="P88" s="28" t="n"/>
+      <c r="Q88" s="28" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="R88" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="S88" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T88" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U88" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V88" s="24" t="n"/>
+      <c r="W88" s="26" t="n"/>
+      <c r="X88" s="26" t="n"/>
+      <c r="Y88" s="38" t="n"/>
+      <c r="Z88" s="26" t="n"/>
+      <c r="AA88" s="28" t="n"/>
+      <c r="AB88" s="28" t="n"/>
+      <c r="AC88" s="40" t="n"/>
+      <c r="AD88" s="24" t="n"/>
+      <c r="AE88" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5400 (aec-mlb-wsh-col-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF88" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG88" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH88" s="24" t="n"/>
+      <c r="AI88" s="31" t="n"/>
+      <c r="AJ88" s="31" t="n"/>
+      <c r="AK88" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL88" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM88" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN88" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO88" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP88" s="24" t="inlineStr">
+        <is>
+          <t>mlb-wsh</t>
+        </is>
+      </c>
+      <c r="AQ88" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="AR88" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="AS88" s="24" t="inlineStr">
+        <is>
+          <t>mlb-col</t>
+        </is>
+      </c>
+      <c r="AT88" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AU88" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AV88" s="24" t="n"/>
+      <c r="AW88" s="24" t="n"/>
+      <c r="AX88" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY88" s="24" t="n"/>
+      <c r="AZ88" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA88" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB88" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC88" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD88" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE88" s="24" t="inlineStr">
+        <is>
+          <t>a2f336c1cee8c92e</t>
+        </is>
+      </c>
+      <c r="BF88" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG88" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH88" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:57:49.897394Z</t>
+        </is>
+      </c>
+      <c r="BI88" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ88" s="38" t="n"/>
+      <c r="BK88" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL88" s="39" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM88" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN88" s="28" t="n">
+        <v>0.537313</v>
+      </c>
+      <c r="BO88" s="28" t="n"/>
+      <c r="BP88" s="38" t="n"/>
+      <c r="BQ88" s="39" t="n"/>
+      <c r="BR88" s="28" t="n"/>
+      <c r="BS88" s="28" t="n"/>
+      <c r="BT88" s="28" t="n"/>
+      <c r="BU88" s="38" t="n"/>
+      <c r="BV88" s="29" t="n"/>
+      <c r="BW88" s="24" t="n"/>
+      <c r="BX88" s="40" t="n"/>
+      <c r="BY88" s="39" t="n"/>
+      <c r="BZ88" s="24" t="n"/>
+      <c r="CA88" s="31" t="n"/>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="A89" s="24" t="inlineStr">
+        <is>
+          <t>21876b0ffe164cd7</t>
+        </is>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:58:34.322674Z</t>
+        </is>
+      </c>
+      <c r="C89" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>401816198</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F89" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="H89" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I89" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J89" s="38" t="n"/>
+      <c r="K89" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L89" s="26" t="n">
+        <v>-147</v>
+      </c>
+      <c r="M89" s="39" t="n">
+        <v>1.680272</v>
+      </c>
+      <c r="N89" s="28" t="n">
+        <v>0.5951419999999999</v>
+      </c>
+      <c r="O89" s="28" t="n">
+        <v>0.58189</v>
+      </c>
+      <c r="P89" s="28" t="n"/>
+      <c r="Q89" s="28" t="n">
+        <v>-0.013252</v>
+      </c>
+      <c r="R89" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="S89" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T89" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U89" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V89" s="24" t="n"/>
+      <c r="W89" s="26" t="n"/>
+      <c r="X89" s="26" t="n"/>
+      <c r="Y89" s="38" t="n"/>
+      <c r="Z89" s="26" t="n"/>
+      <c r="AA89" s="28" t="n"/>
+      <c r="AB89" s="28" t="n"/>
+      <c r="AC89" s="40" t="n"/>
+      <c r="AD89" s="24" t="n"/>
+      <c r="AE89" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5950 (aec-mlb-ath-az-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF89" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG89" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH89" s="24" t="n"/>
+      <c r="AI89" s="31" t="n"/>
+      <c r="AJ89" s="31" t="n"/>
+      <c r="AK89" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL89" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM89" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN89" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO89" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP89" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ath</t>
+        </is>
+      </c>
+      <c r="AQ89" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AR89" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AS89" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ari</t>
+        </is>
+      </c>
+      <c r="AT89" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AU89" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AV89" s="24" t="n"/>
+      <c r="AW89" s="24" t="n"/>
+      <c r="AX89" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY89" s="24" t="n"/>
+      <c r="AZ89" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA89" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB89" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC89" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD89" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE89" s="24" t="inlineStr">
+        <is>
+          <t>7b682aa5da86e2a4</t>
+        </is>
+      </c>
+      <c r="BF89" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG89" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH89" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:57:51.339273Z</t>
+        </is>
+      </c>
+      <c r="BI89" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ89" s="38" t="n"/>
+      <c r="BK89" s="26" t="n">
+        <v>-147</v>
+      </c>
+      <c r="BL89" s="39" t="n">
+        <v>1.680272</v>
+      </c>
+      <c r="BM89" s="28" t="n">
+        <v>0.5951419999999999</v>
+      </c>
+      <c r="BN89" s="28" t="n">
+        <v>0.59204</v>
+      </c>
+      <c r="BO89" s="28" t="n"/>
+      <c r="BP89" s="38" t="n"/>
+      <c r="BQ89" s="39" t="n"/>
+      <c r="BR89" s="28" t="n"/>
+      <c r="BS89" s="28" t="n"/>
+      <c r="BT89" s="28" t="n"/>
+      <c r="BU89" s="38" t="n"/>
+      <c r="BV89" s="29" t="n"/>
+      <c r="BW89" s="24" t="n"/>
+      <c r="BX89" s="40" t="n"/>
+      <c r="BY89" s="39" t="n"/>
+      <c r="BZ89" s="24" t="n"/>
+      <c r="CA89" s="31" t="n"/>
+    </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t>7df4ed647cfb43ef</t>
+        </is>
+      </c>
+      <c r="B90" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:58:34.322674Z</t>
+        </is>
+      </c>
+      <c r="C90" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D90" s="24" t="inlineStr">
+        <is>
+          <t>401816199</t>
+        </is>
+      </c>
+      <c r="E90" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F90" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="G90" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="H90" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I90" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J90" s="38" t="n"/>
+      <c r="K90" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L90" s="26" t="n">
+        <v>-141</v>
+      </c>
+      <c r="M90" s="39" t="n">
+        <v>1.70922</v>
+      </c>
+      <c r="N90" s="28" t="n">
+        <v>0.585062</v>
+      </c>
+      <c r="O90" s="28" t="n">
+        <v>0.592852</v>
+      </c>
+      <c r="P90" s="28" t="n"/>
+      <c r="Q90" s="28" t="n">
+        <v>0.00779</v>
+      </c>
+      <c r="R90" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="S90" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T90" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U90" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V90" s="24" t="n"/>
+      <c r="W90" s="26" t="n"/>
+      <c r="X90" s="26" t="n"/>
+      <c r="Y90" s="38" t="n"/>
+      <c r="Z90" s="26" t="n"/>
+      <c r="AA90" s="28" t="n"/>
+      <c r="AB90" s="28" t="n"/>
+      <c r="AC90" s="40" t="n"/>
+      <c r="AD90" s="24" t="n"/>
+      <c r="AE90" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5850 (aec-mlb-cin-sea-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF90" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG90" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH90" s="24" t="n"/>
+      <c r="AI90" s="31" t="n"/>
+      <c r="AJ90" s="31" t="n"/>
+      <c r="AK90" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL90" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM90" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN90" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO90" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP90" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cin</t>
+        </is>
+      </c>
+      <c r="AQ90" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AR90" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AS90" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sea</t>
+        </is>
+      </c>
+      <c r="AT90" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AU90" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AV90" s="24" t="n"/>
+      <c r="AW90" s="24" t="n"/>
+      <c r="AX90" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY90" s="24" t="n"/>
+      <c r="AZ90" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA90" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB90" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC90" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD90" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE90" s="24" t="inlineStr">
+        <is>
+          <t>af7ccafcacf69681</t>
+        </is>
+      </c>
+      <c r="BF90" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG90" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH90" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T14:57:52.831217Z</t>
+        </is>
+      </c>
+      <c r="BI90" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ90" s="38" t="n"/>
+      <c r="BK90" s="26" t="n">
+        <v>-141</v>
+      </c>
+      <c r="BL90" s="39" t="n">
+        <v>1.70922</v>
+      </c>
+      <c r="BM90" s="28" t="n">
+        <v>0.585062</v>
+      </c>
+      <c r="BN90" s="28" t="n">
+        <v>0.58209</v>
+      </c>
+      <c r="BO90" s="28" t="n"/>
+      <c r="BP90" s="38" t="n"/>
+      <c r="BQ90" s="39" t="n"/>
+      <c r="BR90" s="28" t="n"/>
+      <c r="BS90" s="28" t="n"/>
+      <c r="BT90" s="28" t="n"/>
+      <c r="BU90" s="38" t="n"/>
+      <c r="BV90" s="29" t="n"/>
+      <c r="BW90" s="24" t="n"/>
+      <c r="BX90" s="40" t="n"/>
+      <c r="BY90" s="39" t="n"/>
+      <c r="BZ90" s="24" t="n"/>
+      <c r="CA90" s="31" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -327,8 +327,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA90" headerRowCount="1">
-  <autoFilter ref="A1:CA90"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA74" headerRowCount="1">
+  <autoFilter ref="A1:CA74"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -765,19 +765,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$90)</f>
+        <f>COUNTA('Picks'!$A$2:$A$74)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$90,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$74,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$90,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$74,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")+COUNTIFS('Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")+COUNTIFS('Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -806,19 +806,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$90,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$74,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="32">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"win")/(COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"win")+COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"win")/(COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"win")+COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="32">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$90)/SUM('Picks'!$BX$2:$BX$90),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$74)/SUM('Picks'!$BX$2:$BX$74),0)</f>
         <v/>
       </c>
     </row>
@@ -847,19 +847,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="33">
-        <f>SUM('Picks'!$BY$2:$BY$90)</f>
+        <f>SUM('Picks'!$BY$2:$BY$74)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$90,"&lt;&gt;",'Picks'!$AB$2:$AB$90),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$74,"&lt;&gt;",'Picks'!$AB$2:$AB$74),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$90,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$90,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$74,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$74,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="33">
-        <f>SUMIFS('Picks'!$AC$2:$AC$90,'Picks'!$AM$2:$AM$90,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$74,'Picks'!$AM$2:$AM$74,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -915,15 +915,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="34">
@@ -931,11 +931,11 @@
         <v/>
       </c>
       <c r="F14" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$90,'Picks'!$H$2:$H$90,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$74,'Picks'!$H$2:$H$74,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$90,'Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$74,'Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -946,15 +946,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="36">
@@ -962,11 +962,11 @@
         <v/>
       </c>
       <c r="F15" s="37">
-        <f>SUMIFS('Picks'!$BY$2:$BY$90,'Picks'!$H$2:$H$90,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$74,'Picks'!$H$2:$H$74,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$90,'Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$74,'Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -977,15 +977,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="34">
@@ -993,11 +993,11 @@
         <v/>
       </c>
       <c r="F16" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$90,'Picks'!$H$2:$H$90,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$74,'Picks'!$H$2:$H$74,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$90,'Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$74,'Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA90"/>
+  <dimension ref="A1:CA74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1852,14 +1852,14 @@
         <v>0.037938</v>
       </c>
       <c r="R3" s="26" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="S3" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T3" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U3" s="24" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="BA3" s="24" t="inlineStr">
         <is>
-          <t>117c03794b1d1031deec3bd4cce88c9158bebd0622c621defd0aab3eb37c0a6e</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB3" s="24" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="BC3" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD3" s="24" t="inlineStr">
         <is>
-          <t>117c03794b1d1031deec3bd4cce88c9158bebd0622c621defd0aab3eb37c0a6e</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE3" s="24" t="inlineStr">
@@ -2127,14 +2127,14 @@
         <v>0.049134</v>
       </c>
       <c r="R4" s="26" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="S4" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T4" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U4" s="24" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="BA4" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB4" s="24" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="BC4" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD4" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE4" s="24" t="inlineStr">
@@ -2402,14 +2402,14 @@
         <v>0.037548</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="S5" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T5" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U5" s="24" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="BA5" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB5" s="24" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="BC5" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD5" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE5" s="24" t="inlineStr">
@@ -2677,14 +2677,14 @@
         <v>0.066964</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="S6" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T6" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U6" s="24" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="BC6" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2952,14 +2952,14 @@
         <v>0.072563</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="S7" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T7" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U7" s="24" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="BC7" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3227,14 +3227,14 @@
         <v>0.035734</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="S8" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T8" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U8" s="24" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BC8" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3502,14 +3502,14 @@
         <v>0.049134</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="S9" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T9" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U9" s="24" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="BC9" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3777,14 +3777,14 @@
         <v>0.047926</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="S10" s="29" t="n">
         <v>1.75</v>
       </c>
       <c r="T10" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U10" s="24" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3911,12 +3911,12 @@
       </c>
       <c r="BC10" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4052,14 +4052,14 @@
         <v>0.074685</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="S11" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T11" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U11" s="24" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="BC11" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4327,14 +4327,14 @@
         <v>0.040217</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="S12" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U12" s="24" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>40e5d70a6fae1347ad85569354088d9df4f2d6970f7d7c2f9d4924d65efd0c19</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="BC12" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>40e5d70a6fae1347ad85569354088d9df4f2d6970f7d7c2f9d4924d65efd0c19</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4602,14 +4602,14 @@
         <v>0.06776799999999999</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="S13" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T13" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U13" s="24" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4736,12 +4736,12 @@
       </c>
       <c r="BC13" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4877,14 +4877,14 @@
         <v>0.020811</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="S14" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U14" s="24" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="BC14" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5152,14 +5152,14 @@
         <v>0.039772</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="S15" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U15" s="24" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="BC15" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5427,14 +5427,14 @@
         <v>0.079943</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S16" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T16" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U16" s="24" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="BC16" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5702,14 +5702,14 @@
         <v>0.031345</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="S17" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U17" s="24" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="BC17" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -5977,14 +5977,14 @@
         <v>0.090138</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="S18" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T18" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U18" s="24" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="BC18" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6252,14 +6252,14 @@
         <v>0.051613</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="S19" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T19" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U19" s="24" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="BC19" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6527,14 +6527,14 @@
         <v>0.035428</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="S20" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U20" s="24" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="BC20" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6803,13 +6803,15 @@
       <c r="Q21" s="28" t="n">
         <v>0.03577</v>
       </c>
-      <c r="R21" s="26" t="n"/>
+      <c r="R21" s="26" t="n">
+        <v>35</v>
+      </c>
       <c r="S21" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U21" s="24" t="inlineStr">
@@ -6866,10 +6868,22 @@
       <c r="AX21" s="24" t="n"/>
       <c r="AY21" s="24" t="n"/>
       <c r="AZ21" s="24" t="n"/>
-      <c r="BA21" s="24" t="n"/>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB21" s="24" t="n"/>
-      <c r="BC21" s="24" t="n"/>
-      <c r="BD21" s="24" t="n"/>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE21" s="24" t="n"/>
       <c r="BF21" s="24" t="n"/>
       <c r="BG21" s="24" t="n"/>
@@ -6976,13 +6990,15 @@
       <c r="Q22" s="28" t="n">
         <v>0.03577</v>
       </c>
-      <c r="R22" s="26" t="n"/>
+      <c r="R22" s="26" t="n">
+        <v>35</v>
+      </c>
       <c r="S22" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T22" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U22" s="24" t="inlineStr">
@@ -7039,10 +7055,22 @@
       <c r="AX22" s="24" t="n"/>
       <c r="AY22" s="24" t="n"/>
       <c r="AZ22" s="24" t="n"/>
-      <c r="BA22" s="24" t="n"/>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB22" s="24" t="n"/>
-      <c r="BC22" s="24" t="n"/>
-      <c r="BD22" s="24" t="n"/>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE22" s="24" t="n"/>
       <c r="BF22" s="24" t="n"/>
       <c r="BG22" s="24" t="n"/>
@@ -7149,13 +7177,15 @@
       <c r="Q23" s="28" t="n">
         <v>0.031136</v>
       </c>
-      <c r="R23" s="26" t="n"/>
+      <c r="R23" s="26" t="n">
+        <v>31</v>
+      </c>
       <c r="S23" s="29" t="n">
         <v>1.75</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U23" s="24" t="inlineStr">
@@ -7212,10 +7242,22 @@
       <c r="AX23" s="24" t="n"/>
       <c r="AY23" s="24" t="n"/>
       <c r="AZ23" s="24" t="n"/>
-      <c r="BA23" s="24" t="n"/>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB23" s="24" t="n"/>
-      <c r="BC23" s="24" t="n"/>
-      <c r="BD23" s="24" t="n"/>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE23" s="24" t="n"/>
       <c r="BF23" s="24" t="n"/>
       <c r="BG23" s="24" t="n"/>
@@ -7322,13 +7364,15 @@
       <c r="Q24" s="28" t="n">
         <v>0.031895</v>
       </c>
-      <c r="R24" s="26" t="n"/>
+      <c r="R24" s="26" t="n">
+        <v>31</v>
+      </c>
       <c r="S24" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T24" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U24" s="24" t="inlineStr">
@@ -7385,10 +7429,22 @@
       <c r="AX24" s="24" t="n"/>
       <c r="AY24" s="24" t="n"/>
       <c r="AZ24" s="24" t="n"/>
-      <c r="BA24" s="24" t="n"/>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB24" s="24" t="n"/>
-      <c r="BC24" s="24" t="n"/>
-      <c r="BD24" s="24" t="n"/>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE24" s="24" t="n"/>
       <c r="BF24" s="24" t="n"/>
       <c r="BG24" s="24" t="n"/>
@@ -7495,13 +7551,15 @@
       <c r="Q25" s="28" t="n">
         <v>0.092666</v>
       </c>
-      <c r="R25" s="26" t="n"/>
+      <c r="R25" s="26" t="n">
+        <v>92</v>
+      </c>
       <c r="S25" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U25" s="24" t="inlineStr">
@@ -7558,10 +7616,22 @@
       <c r="AX25" s="24" t="n"/>
       <c r="AY25" s="24" t="n"/>
       <c r="AZ25" s="24" t="n"/>
-      <c r="BA25" s="24" t="n"/>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB25" s="24" t="n"/>
-      <c r="BC25" s="24" t="n"/>
-      <c r="BD25" s="24" t="n"/>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE25" s="24" t="n"/>
       <c r="BF25" s="24" t="n"/>
       <c r="BG25" s="24" t="n"/>
@@ -7668,13 +7738,15 @@
       <c r="Q26" s="28" t="n">
         <v>0.040429</v>
       </c>
-      <c r="R26" s="26" t="n"/>
+      <c r="R26" s="26" t="n">
+        <v>40</v>
+      </c>
       <c r="S26" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U26" s="24" t="inlineStr">
@@ -7731,10 +7803,22 @@
       <c r="AX26" s="24" t="n"/>
       <c r="AY26" s="24" t="n"/>
       <c r="AZ26" s="24" t="n"/>
-      <c r="BA26" s="24" t="n"/>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB26" s="24" t="n"/>
-      <c r="BC26" s="24" t="n"/>
-      <c r="BD26" s="24" t="n"/>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE26" s="24" t="n"/>
       <c r="BF26" s="24" t="n"/>
       <c r="BG26" s="24" t="n"/>
@@ -7841,13 +7925,15 @@
       <c r="Q27" s="28" t="n">
         <v>0.075754</v>
       </c>
-      <c r="R27" s="26" t="n"/>
+      <c r="R27" s="26" t="n">
+        <v>75</v>
+      </c>
       <c r="S27" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T27" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U27" s="24" t="inlineStr">
@@ -7904,10 +7990,22 @@
       <c r="AX27" s="24" t="n"/>
       <c r="AY27" s="24" t="n"/>
       <c r="AZ27" s="24" t="n"/>
-      <c r="BA27" s="24" t="n"/>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB27" s="24" t="n"/>
-      <c r="BC27" s="24" t="n"/>
-      <c r="BD27" s="24" t="n"/>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE27" s="24" t="n"/>
       <c r="BF27" s="24" t="n"/>
       <c r="BG27" s="24" t="n"/>
@@ -8014,13 +8112,15 @@
       <c r="Q28" s="28" t="n">
         <v>0.025388</v>
       </c>
-      <c r="R28" s="26" t="n"/>
+      <c r="R28" s="26" t="n">
+        <v>25</v>
+      </c>
       <c r="S28" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T28" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U28" s="24" t="inlineStr">
@@ -8077,10 +8177,22 @@
       <c r="AX28" s="24" t="n"/>
       <c r="AY28" s="24" t="n"/>
       <c r="AZ28" s="24" t="n"/>
-      <c r="BA28" s="24" t="n"/>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB28" s="24" t="n"/>
-      <c r="BC28" s="24" t="n"/>
-      <c r="BD28" s="24" t="n"/>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE28" s="24" t="n"/>
       <c r="BF28" s="24" t="n"/>
       <c r="BG28" s="24" t="n"/>
@@ -8186,14 +8298,14 @@
         <v>0.085969</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="S29" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T29" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U29" s="24" t="inlineStr">
@@ -8310,7 +8422,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -8320,12 +8432,12 @@
       </c>
       <c r="BC29" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -8461,14 +8573,14 @@
         <v>0.02961</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="S30" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T30" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U30" s="24" t="inlineStr">
@@ -8585,7 +8697,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -8595,12 +8707,12 @@
       </c>
       <c r="BC30" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD30" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE30" s="24" t="inlineStr">
@@ -8743,7 +8855,7 @@
       </c>
       <c r="T31" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U31" s="24" t="inlineStr">
@@ -8860,7 +8972,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -8870,12 +8982,12 @@
       </c>
       <c r="BC31" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -9011,14 +9123,14 @@
         <v>0.061817</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="S32" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T32" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U32" s="24" t="inlineStr">
@@ -9135,7 +9247,7 @@
       </c>
       <c r="BA32" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB32" s="24" t="inlineStr">
@@ -9145,12 +9257,12 @@
       </c>
       <c r="BC32" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD32" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE32" s="24" t="inlineStr">
@@ -9281,7 +9393,7 @@
       </c>
       <c r="T33" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U33" s="24" t="inlineStr">
@@ -9398,7 +9510,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -9408,12 +9520,12 @@
       </c>
       <c r="BC33" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
@@ -9537,14 +9649,14 @@
         <v>0.013837</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="S34" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T34" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U34" s="24" t="inlineStr">
@@ -9661,7 +9773,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -9671,12 +9783,12 @@
       </c>
       <c r="BC34" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
@@ -9800,14 +9912,14 @@
         <v>0.09975299999999999</v>
       </c>
       <c r="R35" s="26" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S35" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T35" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U35" s="24" t="inlineStr">
@@ -9924,7 +10036,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -9934,12 +10046,12 @@
       </c>
       <c r="BC35" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -10063,14 +10175,14 @@
         <v>0.004261</v>
       </c>
       <c r="R36" s="26" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="S36" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T36" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U36" s="24" t="inlineStr">
@@ -10187,7 +10299,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -10197,12 +10309,12 @@
       </c>
       <c r="BC36" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
@@ -10326,14 +10438,14 @@
         <v>0.08122</v>
       </c>
       <c r="R37" s="26" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="S37" s="29" t="n">
         <v>1.75</v>
       </c>
       <c r="T37" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U37" s="24" t="inlineStr">
@@ -10450,7 +10562,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -10460,12 +10572,12 @@
       </c>
       <c r="BC37" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -10589,14 +10701,14 @@
         <v>0.055602</v>
       </c>
       <c r="R38" s="26" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="S38" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T38" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U38" s="24" t="inlineStr">
@@ -10713,7 +10825,7 @@
       </c>
       <c r="BA38" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB38" s="24" t="inlineStr">
@@ -10723,12 +10835,12 @@
       </c>
       <c r="BC38" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD38" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE38" s="24" t="inlineStr">
@@ -10852,14 +10964,14 @@
         <v>-0.000953</v>
       </c>
       <c r="R39" s="26" t="n">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="S39" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T39" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U39" s="24" t="inlineStr">
@@ -10976,7 +11088,7 @@
       </c>
       <c r="BA39" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB39" s="24" t="inlineStr">
@@ -10986,12 +11098,12 @@
       </c>
       <c r="BC39" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD39" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE39" s="24" t="inlineStr">
@@ -11115,14 +11227,14 @@
         <v>-0.05821</v>
       </c>
       <c r="R40" s="26" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="S40" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T40" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U40" s="24" t="inlineStr">
@@ -11239,7 +11351,7 @@
       </c>
       <c r="BA40" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB40" s="24" t="inlineStr">
@@ -11249,12 +11361,12 @@
       </c>
       <c r="BC40" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD40" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE40" s="24" t="inlineStr">
@@ -11378,14 +11490,14 @@
         <v>-0.024303</v>
       </c>
       <c r="R41" s="26" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="S41" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T41" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U41" s="24" t="inlineStr">
@@ -11502,7 +11614,7 @@
       </c>
       <c r="BA41" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB41" s="24" t="inlineStr">
@@ -11512,12 +11624,12 @@
       </c>
       <c r="BC41" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD41" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE41" s="24" t="inlineStr">
@@ -11641,14 +11753,14 @@
         <v>-0.007549</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="S42" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T42" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U42" s="24" t="inlineStr">
@@ -11765,7 +11877,7 @@
       </c>
       <c r="BA42" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB42" s="24" t="inlineStr">
@@ -11775,12 +11887,12 @@
       </c>
       <c r="BC42" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD42" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE42" s="24" t="inlineStr">
@@ -11904,14 +12016,14 @@
         <v>-0.000995</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="S43" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T43" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U43" s="24" t="inlineStr">
@@ -12028,7 +12140,7 @@
       </c>
       <c r="BA43" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB43" s="24" t="inlineStr">
@@ -12038,12 +12150,12 @@
       </c>
       <c r="BC43" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD43" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE43" s="24" t="inlineStr">
@@ -13142,13 +13254,15 @@
       <c r="Q48" s="28" t="n">
         <v>-0.082468</v>
       </c>
-      <c r="R48" s="26" t="n"/>
+      <c r="R48" s="26" t="n">
+        <v>17</v>
+      </c>
       <c r="S48" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U48" s="24" t="inlineStr">
@@ -13205,10 +13319,22 @@
       <c r="AX48" s="24" t="n"/>
       <c r="AY48" s="24" t="n"/>
       <c r="AZ48" s="24" t="n"/>
-      <c r="BA48" s="24" t="n"/>
+      <c r="BA48" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB48" s="24" t="n"/>
-      <c r="BC48" s="24" t="n"/>
-      <c r="BD48" s="24" t="n"/>
+      <c r="BC48" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD48" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE48" s="24" t="n"/>
       <c r="BF48" s="24" t="n"/>
       <c r="BG48" s="24" t="n"/>
@@ -13315,13 +13441,15 @@
       <c r="Q49" s="28" t="n">
         <v>0.002031</v>
       </c>
-      <c r="R49" s="26" t="n"/>
+      <c r="R49" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="S49" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T49" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U49" s="24" t="inlineStr">
@@ -13378,10 +13506,22 @@
       <c r="AX49" s="24" t="n"/>
       <c r="AY49" s="24" t="n"/>
       <c r="AZ49" s="24" t="n"/>
-      <c r="BA49" s="24" t="n"/>
+      <c r="BA49" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB49" s="24" t="n"/>
-      <c r="BC49" s="24" t="n"/>
-      <c r="BD49" s="24" t="n"/>
+      <c r="BC49" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD49" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE49" s="24" t="n"/>
       <c r="BF49" s="24" t="n"/>
       <c r="BG49" s="24" t="n"/>
@@ -13488,13 +13628,15 @@
       <c r="Q50" s="28" t="n">
         <v>-0.009344</v>
       </c>
-      <c r="R50" s="26" t="n"/>
+      <c r="R50" s="26" t="n">
+        <v>90</v>
+      </c>
       <c r="S50" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T50" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U50" s="24" t="inlineStr">
@@ -13551,10 +13693,22 @@
       <c r="AX50" s="24" t="n"/>
       <c r="AY50" s="24" t="n"/>
       <c r="AZ50" s="24" t="n"/>
-      <c r="BA50" s="24" t="n"/>
+      <c r="BA50" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB50" s="24" t="n"/>
-      <c r="BC50" s="24" t="n"/>
-      <c r="BD50" s="24" t="n"/>
+      <c r="BC50" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD50" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE50" s="24" t="n"/>
       <c r="BF50" s="24" t="n"/>
       <c r="BG50" s="24" t="n"/>
@@ -13661,13 +13815,15 @@
       <c r="Q51" s="28" t="n">
         <v>0.010061</v>
       </c>
-      <c r="R51" s="26" t="n"/>
+      <c r="R51" s="26" t="n">
+        <v>10</v>
+      </c>
       <c r="S51" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T51" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U51" s="24" t="inlineStr">
@@ -13724,10 +13880,22 @@
       <c r="AX51" s="24" t="n"/>
       <c r="AY51" s="24" t="n"/>
       <c r="AZ51" s="24" t="n"/>
-      <c r="BA51" s="24" t="n"/>
+      <c r="BA51" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB51" s="24" t="n"/>
-      <c r="BC51" s="24" t="n"/>
-      <c r="BD51" s="24" t="n"/>
+      <c r="BC51" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD51" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE51" s="24" t="n"/>
       <c r="BF51" s="24" t="n"/>
       <c r="BG51" s="24" t="n"/>
@@ -13834,13 +14002,15 @@
       <c r="Q52" s="28" t="n">
         <v>-0.037461</v>
       </c>
-      <c r="R52" s="26" t="n"/>
+      <c r="R52" s="26" t="n">
+        <v>62</v>
+      </c>
       <c r="S52" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T52" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U52" s="24" t="inlineStr">
@@ -13897,10 +14067,22 @@
       <c r="AX52" s="24" t="n"/>
       <c r="AY52" s="24" t="n"/>
       <c r="AZ52" s="24" t="n"/>
-      <c r="BA52" s="24" t="n"/>
+      <c r="BA52" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB52" s="24" t="n"/>
-      <c r="BC52" s="24" t="n"/>
-      <c r="BD52" s="24" t="n"/>
+      <c r="BC52" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD52" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE52" s="24" t="n"/>
       <c r="BF52" s="24" t="n"/>
       <c r="BG52" s="24" t="n"/>
@@ -14526,13 +14708,15 @@
       <c r="Q56" s="28" t="n">
         <v>-0.008004000000000001</v>
       </c>
-      <c r="R56" s="26" t="n"/>
+      <c r="R56" s="26" t="n">
+        <v>91</v>
+      </c>
       <c r="S56" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T56" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U56" s="24" t="inlineStr">
@@ -14589,10 +14773,22 @@
       <c r="AX56" s="24" t="n"/>
       <c r="AY56" s="24" t="n"/>
       <c r="AZ56" s="24" t="n"/>
-      <c r="BA56" s="24" t="n"/>
+      <c r="BA56" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB56" s="24" t="n"/>
-      <c r="BC56" s="24" t="n"/>
-      <c r="BD56" s="24" t="n"/>
+      <c r="BC56" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD56" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE56" s="24" t="n"/>
       <c r="BF56" s="24" t="n"/>
       <c r="BG56" s="24" t="n"/>
@@ -14699,13 +14895,15 @@
       <c r="Q57" s="28" t="n">
         <v>-0.000678</v>
       </c>
-      <c r="R57" s="26" t="n"/>
+      <c r="R57" s="26" t="n">
+        <v>99</v>
+      </c>
       <c r="S57" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T57" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U57" s="24" t="inlineStr">
@@ -14762,10 +14960,22 @@
       <c r="AX57" s="24" t="n"/>
       <c r="AY57" s="24" t="n"/>
       <c r="AZ57" s="24" t="n"/>
-      <c r="BA57" s="24" t="n"/>
+      <c r="BA57" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB57" s="24" t="n"/>
-      <c r="BC57" s="24" t="n"/>
-      <c r="BD57" s="24" t="n"/>
+      <c r="BC57" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD57" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE57" s="24" t="n"/>
       <c r="BF57" s="24" t="n"/>
       <c r="BG57" s="24" t="n"/>
@@ -14872,13 +15082,15 @@
       <c r="Q58" s="28" t="n">
         <v>0.017743</v>
       </c>
-      <c r="R58" s="26" t="n"/>
+      <c r="R58" s="26" t="n">
+        <v>17</v>
+      </c>
       <c r="S58" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T58" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U58" s="24" t="inlineStr">
@@ -14935,10 +15147,22 @@
       <c r="AX58" s="24" t="n"/>
       <c r="AY58" s="24" t="n"/>
       <c r="AZ58" s="24" t="n"/>
-      <c r="BA58" s="24" t="n"/>
+      <c r="BA58" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB58" s="24" t="n"/>
-      <c r="BC58" s="24" t="n"/>
-      <c r="BD58" s="24" t="n"/>
+      <c r="BC58" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD58" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE58" s="24" t="n"/>
       <c r="BF58" s="24" t="n"/>
       <c r="BG58" s="24" t="n"/>
@@ -15045,13 +15269,15 @@
       <c r="Q59" s="28" t="n">
         <v>-0.090055</v>
       </c>
-      <c r="R59" s="26" t="n"/>
+      <c r="R59" s="26" t="n">
+        <v>9</v>
+      </c>
       <c r="S59" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T59" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U59" s="24" t="inlineStr">
@@ -15108,10 +15334,22 @@
       <c r="AX59" s="24" t="n"/>
       <c r="AY59" s="24" t="n"/>
       <c r="AZ59" s="24" t="n"/>
-      <c r="BA59" s="24" t="n"/>
+      <c r="BA59" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB59" s="24" t="n"/>
-      <c r="BC59" s="24" t="n"/>
-      <c r="BD59" s="24" t="n"/>
+      <c r="BC59" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD59" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE59" s="24" t="n"/>
       <c r="BF59" s="24" t="n"/>
       <c r="BG59" s="24" t="n"/>
@@ -15497,12 +15735,12 @@
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>39f07dbdee044f92</t>
+          <t>bbf4c446926f4a96</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:27:09.837629Z</t>
+          <t>2026-07-20T15:22:41.782177Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
@@ -15547,30 +15785,30 @@
         </is>
       </c>
       <c r="L62" s="26" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M62" s="39" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="N62" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.473934</v>
       </c>
       <c r="O62" s="28" t="n">
-        <v>0.585152</v>
+        <v>0.5726869999999999</v>
       </c>
       <c r="P62" s="28" t="n"/>
       <c r="Q62" s="28" t="n">
-        <v>0.104383</v>
+        <v>0.09875299999999999</v>
       </c>
       <c r="R62" s="26" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S62" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T62" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U62" s="24" t="inlineStr">
@@ -15589,7 +15827,7 @@
       <c r="AD62" s="24" t="n"/>
       <c r="AE62" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.4800 (aec-mlb-min-cle-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.4750 (aec-mlb-min-cle-2026-07-20).</t>
         </is>
       </c>
       <c r="AF62" s="31" t="inlineStr">
@@ -15673,7 +15911,7 @@
       </c>
       <c r="BA62" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB62" s="24" t="inlineStr">
@@ -15683,17 +15921,17 @@
       </c>
       <c r="BC62" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD62" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE62" s="24" t="inlineStr">
         <is>
-          <t>bcb6462455cdfab4</t>
+          <t>2170ac399ced5417</t>
         </is>
       </c>
       <c r="BF62" s="24" t="inlineStr">
@@ -15703,12 +15941,12 @@
       </c>
       <c r="BG62" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:25:43.922504Z</t>
+          <t>2026-07-20T14:57:32.219947Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -15718,16 +15956,16 @@
       </c>
       <c r="BJ62" s="38" t="n"/>
       <c r="BK62" s="26" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BL62" s="39" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="BM62" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.473934</v>
       </c>
       <c r="BN62" s="28" t="n">
-        <v>0.477612</v>
+        <v>0.472637</v>
       </c>
       <c r="BO62" s="28" t="n"/>
       <c r="BP62" s="38" t="n"/>
@@ -15746,22 +15984,22 @@
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>25fe08e3be954adb</t>
+          <t>1506b66a3b294539</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:27:09.837629Z</t>
+          <t>2026-07-20T15:22:41.782177Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:00:00-0400</t>
+          <t>2026-07-20T19:05:00-0400</t>
         </is>
       </c>
       <c r="D63" s="24" t="inlineStr">
         <is>
-          <t>401816187</t>
+          <t>401816189</t>
         </is>
       </c>
       <c r="E63" s="24" t="inlineStr">
@@ -15771,12 +16009,12 @@
       </c>
       <c r="F63" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="G63" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="H63" s="24" t="inlineStr">
@@ -15786,7 +16024,7 @@
       </c>
       <c r="I63" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J63" s="38" t="n"/>
@@ -15796,30 +16034,30 @@
         </is>
       </c>
       <c r="L63" s="26" t="n">
-        <v>125</v>
+        <v>-108</v>
       </c>
       <c r="M63" s="39" t="n">
-        <v>2.25</v>
+        <v>1.925926</v>
       </c>
       <c r="N63" s="28" t="n">
-        <v>0.444444</v>
+        <v>0.519231</v>
       </c>
       <c r="O63" s="28" t="n">
-        <v>0.534274</v>
+        <v>0.578558</v>
       </c>
       <c r="P63" s="28" t="n"/>
       <c r="Q63" s="28" t="n">
-        <v>0.08982999999999999</v>
+        <v>0.059327</v>
       </c>
       <c r="R63" s="26" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="S63" s="29" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="T63" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U63" s="24" t="inlineStr">
@@ -15838,7 +16076,7 @@
       <c r="AD63" s="24" t="n"/>
       <c r="AE63" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.4450 (aec-mlb-lad-phi-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-pit-nyy-2026-07-20).</t>
         </is>
       </c>
       <c r="AF63" s="31" t="inlineStr">
@@ -15856,7 +16094,7 @@
       <c r="AJ63" s="31" t="n"/>
       <c r="AK63" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL63" s="26" t="n">
@@ -15864,47 +16102,47 @@
       </c>
       <c r="AM63" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN63" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO63" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP63" s="24" t="inlineStr">
         <is>
-          <t>mlb-lad</t>
+          <t>mlb-pit</t>
         </is>
       </c>
       <c r="AQ63" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AR63" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AS63" s="24" t="inlineStr">
         <is>
-          <t>mlb-phi</t>
+          <t>mlb-nyy</t>
         </is>
       </c>
       <c r="AT63" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AU63" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AV63" s="24" t="n"/>
@@ -15922,7 +16160,7 @@
       </c>
       <c r="BA63" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB63" s="24" t="inlineStr">
@@ -15932,17 +16170,17 @@
       </c>
       <c r="BC63" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD63" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE63" s="24" t="inlineStr">
         <is>
-          <t>f54ac71be1a765d8</t>
+          <t>38ab7db5a3798f0c</t>
         </is>
       </c>
       <c r="BF63" s="24" t="inlineStr">
@@ -15952,12 +16190,12 @@
       </c>
       <c r="BG63" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:25:49.234179Z</t>
+          <t>2026-07-20T14:57:35.056972Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -15967,16 +16205,16 @@
       </c>
       <c r="BJ63" s="38" t="n"/>
       <c r="BK63" s="26" t="n">
-        <v>125</v>
+        <v>-108</v>
       </c>
       <c r="BL63" s="39" t="n">
-        <v>2.25</v>
+        <v>1.925926</v>
       </c>
       <c r="BM63" s="28" t="n">
-        <v>0.444444</v>
+        <v>0.519231</v>
       </c>
       <c r="BN63" s="28" t="n">
-        <v>0.442786</v>
+        <v>0.517413</v>
       </c>
       <c r="BO63" s="28" t="n"/>
       <c r="BP63" s="38" t="n"/>
@@ -15995,22 +16233,22 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>043f9b9799c44ad4</t>
+          <t>540e168c7d8c4ba0</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:27:09.837629Z</t>
+          <t>2026-07-20T15:22:41.782177Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:05:00-0400</t>
+          <t>2026-07-20T19:10:00-0400</t>
         </is>
       </c>
       <c r="D64" s="24" t="inlineStr">
         <is>
-          <t>401816189</t>
+          <t>401816186</t>
         </is>
       </c>
       <c r="E64" s="24" t="inlineStr">
@@ -16020,12 +16258,12 @@
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="G64" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr">
@@ -16045,30 +16283,30 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>-111</v>
+        <v>-138</v>
       </c>
       <c r="M64" s="39" t="n">
-        <v>1.900901</v>
+        <v>1.724638</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.579832</v>
       </c>
       <c r="O64" s="28" t="n">
-        <v>0.588959</v>
+        <v>0.565797</v>
       </c>
       <c r="P64" s="28" t="n"/>
       <c r="Q64" s="28" t="n">
-        <v>0.062893</v>
+        <v>-0.014035</v>
       </c>
       <c r="R64" s="26" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="S64" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T64" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U64" s="24" t="inlineStr">
@@ -16087,7 +16325,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5250 (aec-mlb-pit-nyy-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5800 (aec-mlb-bal-bos-2026-07-20).</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -16128,32 +16366,32 @@
       </c>
       <c r="AP64" s="24" t="inlineStr">
         <is>
-          <t>mlb-pit</t>
+          <t>mlb-bal</t>
         </is>
       </c>
       <c r="AQ64" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AR64" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AS64" s="24" t="inlineStr">
         <is>
-          <t>mlb-nyy</t>
+          <t>mlb-bos</t>
         </is>
       </c>
       <c r="AT64" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="AU64" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="AV64" s="24" t="n"/>
@@ -16171,7 +16409,7 @@
       </c>
       <c r="BA64" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB64" s="24" t="inlineStr">
@@ -16181,17 +16419,17 @@
       </c>
       <c r="BC64" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD64" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE64" s="24" t="inlineStr">
         <is>
-          <t>847c7c728fdb87de</t>
+          <t>9fe2d27778a72dfe</t>
         </is>
       </c>
       <c r="BF64" s="24" t="inlineStr">
@@ -16201,12 +16439,12 @@
       </c>
       <c r="BG64" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:25:45.280685Z</t>
+          <t>2026-07-20T14:57:37.354484Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -16216,16 +16454,16 @@
       </c>
       <c r="BJ64" s="38" t="n"/>
       <c r="BK64" s="26" t="n">
-        <v>-111</v>
+        <v>-138</v>
       </c>
       <c r="BL64" s="39" t="n">
-        <v>1.900901</v>
+        <v>1.724638</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.579832</v>
       </c>
       <c r="BN64" s="28" t="n">
-        <v>0.522388</v>
+        <v>0.577114</v>
       </c>
       <c r="BO64" s="28" t="n"/>
       <c r="BP64" s="38" t="n"/>
@@ -16244,22 +16482,22 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>75cf9949602a4c17</t>
+          <t>f4dc16b93ff64092</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:27:09.837629Z</t>
+          <t>2026-07-20T15:22:41.782177Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:07:00-0400</t>
+          <t>2026-07-20T19:15:00-0400</t>
         </is>
       </c>
       <c r="D65" s="24" t="inlineStr">
         <is>
-          <t>401816191</t>
+          <t>401816190</t>
         </is>
       </c>
       <c r="E65" s="24" t="inlineStr">
@@ -16269,12 +16507,12 @@
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="G65" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="H65" s="24" t="inlineStr">
@@ -16294,30 +16532,30 @@
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="M65" s="39" t="n">
-        <v>1.724638</v>
+        <v>1.75188</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.570815</v>
       </c>
       <c r="O65" s="28" t="n">
-        <v>0.528636</v>
+        <v>0.550915</v>
       </c>
       <c r="P65" s="28" t="n"/>
       <c r="Q65" s="28" t="n">
-        <v>-0.051196</v>
+        <v>-0.0199</v>
       </c>
       <c r="R65" s="26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S65" s="29" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="T65" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U65" s="24" t="inlineStr">
@@ -16336,7 +16574,7 @@
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5800 (aec-mlb-tb-tor-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5700 (aec-mlb-sd-atl-2026-07-20).</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -16377,32 +16615,32 @@
       </c>
       <c r="AP65" s="24" t="inlineStr">
         <is>
-          <t>mlb-tb</t>
+          <t>mlb-sd</t>
         </is>
       </c>
       <c r="AQ65" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AR65" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AS65" s="24" t="inlineStr">
         <is>
-          <t>mlb-tor</t>
+          <t>mlb-atl</t>
         </is>
       </c>
       <c r="AT65" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="AU65" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="AV65" s="24" t="n"/>
@@ -16420,7 +16658,7 @@
       </c>
       <c r="BA65" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB65" s="24" t="inlineStr">
@@ -16430,17 +16668,17 @@
       </c>
       <c r="BC65" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD65" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE65" s="24" t="inlineStr">
         <is>
-          <t>83a50acec79889d1</t>
+          <t>f0b5eac7c97d1146</t>
         </is>
       </c>
       <c r="BF65" s="24" t="inlineStr">
@@ -16450,12 +16688,12 @@
       </c>
       <c r="BG65" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:25:46.631829Z</t>
+          <t>2026-07-20T14:57:40.909749Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -16465,16 +16703,16 @@
       </c>
       <c r="BJ65" s="38" t="n"/>
       <c r="BK65" s="26" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="BL65" s="39" t="n">
-        <v>1.724638</v>
+        <v>1.75188</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.570815</v>
       </c>
       <c r="BN65" s="28" t="n">
-        <v>0.577114</v>
+        <v>0.567164</v>
       </c>
       <c r="BO65" s="28" t="n"/>
       <c r="BP65" s="38" t="n"/>
@@ -16493,22 +16731,22 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>bd769f5d72db48bb</t>
+          <t>c08b803127a54cd0</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:27:09.837629Z</t>
+          <t>2026-07-20T15:22:41.782177Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:10:00-0400</t>
+          <t>2026-07-20T19:40:00-0400</t>
         </is>
       </c>
       <c r="D66" s="24" t="inlineStr">
         <is>
-          <t>401816186</t>
+          <t>401816195</t>
         </is>
       </c>
       <c r="E66" s="24" t="inlineStr">
@@ -16518,12 +16756,12 @@
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="G66" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="H66" s="24" t="inlineStr">
@@ -16543,30 +16781,30 @@
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>-135</v>
+        <v>-199</v>
       </c>
       <c r="M66" s="39" t="n">
-        <v>1.740741</v>
+        <v>1.502513</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.574468</v>
+        <v>0.665552</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.565634</v>
+        <v>0.640995</v>
       </c>
       <c r="P66" s="28" t="n"/>
       <c r="Q66" s="28" t="n">
-        <v>-0.008834</v>
+        <v>-0.024557</v>
       </c>
       <c r="R66" s="26" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S66" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T66" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U66" s="24" t="inlineStr">
@@ -16585,7 +16823,7 @@
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5750 (aec-mlb-bal-bos-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.6650 (aec-mlb-nym-mil-2026-07-20).</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -16626,32 +16864,32 @@
       </c>
       <c r="AP66" s="24" t="inlineStr">
         <is>
-          <t>mlb-bal</t>
+          <t>mlb-nym</t>
         </is>
       </c>
       <c r="AQ66" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AR66" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AS66" s="24" t="inlineStr">
         <is>
-          <t>mlb-bos</t>
+          <t>mlb-mil</t>
         </is>
       </c>
       <c r="AT66" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AU66" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AV66" s="24" t="n"/>
@@ -16669,7 +16907,7 @@
       </c>
       <c r="BA66" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB66" s="24" t="inlineStr">
@@ -16679,17 +16917,17 @@
       </c>
       <c r="BC66" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD66" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE66" s="24" t="inlineStr">
         <is>
-          <t>f90d77bcf90af7a6</t>
+          <t>6d5f3f5e8f75cb2b</t>
         </is>
       </c>
       <c r="BF66" s="24" t="inlineStr">
@@ -16699,12 +16937,12 @@
       </c>
       <c r="BG66" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:25:48.021174Z</t>
+          <t>2026-07-20T14:57:42.879792Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -16714,16 +16952,16 @@
       </c>
       <c r="BJ66" s="38" t="n"/>
       <c r="BK66" s="26" t="n">
-        <v>-135</v>
+        <v>-199</v>
       </c>
       <c r="BL66" s="39" t="n">
-        <v>1.740741</v>
+        <v>1.502513</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.574468</v>
+        <v>0.665552</v>
       </c>
       <c r="BN66" s="28" t="n">
-        <v>0.572139</v>
+        <v>0.6616919999999999</v>
       </c>
       <c r="BO66" s="28" t="n"/>
       <c r="BP66" s="38" t="n"/>
@@ -16742,22 +16980,22 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>6f908cfbb4fb4660</t>
+          <t>6e9b235e0abe4f38</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:27:09.837629Z</t>
+          <t>2026-07-20T15:22:41.782177Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:15:00-0400</t>
+          <t>2026-07-20T20:05:00-0400</t>
         </is>
       </c>
       <c r="D67" s="24" t="inlineStr">
         <is>
-          <t>401816190</t>
+          <t>401816193</t>
         </is>
       </c>
       <c r="E67" s="24" t="inlineStr">
@@ -16767,12 +17005,12 @@
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="G67" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr">
@@ -16792,30 +17030,30 @@
         </is>
       </c>
       <c r="L67" s="26" t="n">
-        <v>-135</v>
+        <v>-108</v>
       </c>
       <c r="M67" s="39" t="n">
-        <v>1.740741</v>
+        <v>1.925926</v>
       </c>
       <c r="N67" s="28" t="n">
-        <v>0.574468</v>
+        <v>0.519231</v>
       </c>
       <c r="O67" s="28" t="n">
-        <v>0.5478730000000001</v>
+        <v>0.566967</v>
       </c>
       <c r="P67" s="28" t="n"/>
       <c r="Q67" s="28" t="n">
-        <v>-0.026595</v>
+        <v>0.047736</v>
       </c>
       <c r="R67" s="26" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="S67" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T67" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U67" s="24" t="inlineStr">
@@ -16834,7 +17072,7 @@
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5750 (aec-mlb-sd-atl-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-det-chc-2026-07-20).</t>
         </is>
       </c>
       <c r="AF67" s="31" t="inlineStr">
@@ -16875,32 +17113,32 @@
       </c>
       <c r="AP67" s="24" t="inlineStr">
         <is>
-          <t>mlb-sd</t>
+          <t>mlb-det</t>
         </is>
       </c>
       <c r="AQ67" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AR67" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AS67" s="24" t="inlineStr">
         <is>
-          <t>mlb-atl</t>
+          <t>mlb-chc</t>
         </is>
       </c>
       <c r="AT67" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AU67" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AV67" s="24" t="n"/>
@@ -16918,7 +17156,7 @@
       </c>
       <c r="BA67" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB67" s="24" t="inlineStr">
@@ -16928,17 +17166,17 @@
       </c>
       <c r="BC67" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD67" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE67" s="24" t="inlineStr">
         <is>
-          <t>dcaf75f7da769912</t>
+          <t>b84afb2c70e14d93</t>
         </is>
       </c>
       <c r="BF67" s="24" t="inlineStr">
@@ -16948,12 +17186,12 @@
       </c>
       <c r="BG67" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:25:50.370060Z</t>
+          <t>2026-07-20T14:57:46.871986Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -16963,16 +17201,16 @@
       </c>
       <c r="BJ67" s="38" t="n"/>
       <c r="BK67" s="26" t="n">
-        <v>-135</v>
+        <v>-108</v>
       </c>
       <c r="BL67" s="39" t="n">
-        <v>1.740741</v>
+        <v>1.925926</v>
       </c>
       <c r="BM67" s="28" t="n">
-        <v>0.574468</v>
+        <v>0.519231</v>
       </c>
       <c r="BN67" s="28" t="n">
-        <v>0.572139</v>
+        <v>0.517413</v>
       </c>
       <c r="BO67" s="28" t="n"/>
       <c r="BP67" s="38" t="n"/>
@@ -16991,22 +17229,22 @@
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
         <is>
-          <t>b3d04af2bb2445ec</t>
+          <t>bf8728673bd4485f</t>
         </is>
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:27:09.837629Z</t>
+          <t>2026-07-20T15:22:41.782177Z</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:40:00-0400</t>
+          <t>2026-07-20T20:40:00-0400</t>
         </is>
       </c>
       <c r="D68" s="24" t="inlineStr">
         <is>
-          <t>401816195</t>
+          <t>401816197</t>
         </is>
       </c>
       <c r="E68" s="24" t="inlineStr">
@@ -17016,12 +17254,12 @@
       </c>
       <c r="F68" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="G68" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="H68" s="24" t="inlineStr">
@@ -17031,7 +17269,7 @@
       </c>
       <c r="I68" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J68" s="38" t="n"/>
@@ -17041,30 +17279,30 @@
         </is>
       </c>
       <c r="L68" s="26" t="n">
-        <v>-190</v>
+        <v>-117</v>
       </c>
       <c r="M68" s="39" t="n">
-        <v>1.526316</v>
+        <v>1.854701</v>
       </c>
       <c r="N68" s="28" t="n">
-        <v>0.655172</v>
+        <v>0.539171</v>
       </c>
       <c r="O68" s="28" t="n">
-        <v>0.6384</v>
+        <v>0.5563709999999999</v>
       </c>
       <c r="P68" s="28" t="n"/>
       <c r="Q68" s="28" t="n">
-        <v>-0.016772</v>
+        <v>0.0172</v>
       </c>
       <c r="R68" s="26" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="S68" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T68" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U68" s="24" t="inlineStr">
@@ -17083,7 +17321,7 @@
       <c r="AD68" s="24" t="n"/>
       <c r="AE68" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.6550 (aec-mlb-nym-mil-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5400 (aec-mlb-wsh-col-2026-07-20).</t>
         </is>
       </c>
       <c r="AF68" s="31" t="inlineStr">
@@ -17124,32 +17362,32 @@
       </c>
       <c r="AP68" s="24" t="inlineStr">
         <is>
-          <t>mlb-nym</t>
+          <t>mlb-wsh</t>
         </is>
       </c>
       <c r="AQ68" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="AR68" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="AS68" s="24" t="inlineStr">
         <is>
-          <t>mlb-mil</t>
+          <t>mlb-col</t>
         </is>
       </c>
       <c r="AT68" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AU68" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AV68" s="24" t="n"/>
@@ -17167,7 +17405,7 @@
       </c>
       <c r="BA68" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB68" s="24" t="inlineStr">
@@ -17177,17 +17415,17 @@
       </c>
       <c r="BC68" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD68" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE68" s="24" t="inlineStr">
         <is>
-          <t>08844b1e52756e6a</t>
+          <t>a2f336c1cee8c92e</t>
         </is>
       </c>
       <c r="BF68" s="24" t="inlineStr">
@@ -17197,12 +17435,12 @@
       </c>
       <c r="BG68" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH68" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:25:51.762171Z</t>
+          <t>2026-07-20T14:57:49.897394Z</t>
         </is>
       </c>
       <c r="BI68" s="24" t="inlineStr">
@@ -17212,16 +17450,16 @@
       </c>
       <c r="BJ68" s="38" t="n"/>
       <c r="BK68" s="26" t="n">
-        <v>-190</v>
+        <v>-117</v>
       </c>
       <c r="BL68" s="39" t="n">
-        <v>1.526316</v>
+        <v>1.854701</v>
       </c>
       <c r="BM68" s="28" t="n">
-        <v>0.655172</v>
+        <v>0.539171</v>
       </c>
       <c r="BN68" s="28" t="n">
-        <v>0.651741</v>
+        <v>0.537313</v>
       </c>
       <c r="BO68" s="28" t="n"/>
       <c r="BP68" s="38" t="n"/>
@@ -17240,22 +17478,22 @@
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>07c094e50e3443bc</t>
+          <t>aefbe47ff16045f2</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:27:09.837629Z</t>
+          <t>2026-07-20T15:22:41.782177Z</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T20:05:00-0400</t>
+          <t>2026-07-20T21:40:00-0400</t>
         </is>
       </c>
       <c r="D69" s="24" t="inlineStr">
         <is>
-          <t>401816192</t>
+          <t>401816198</t>
         </is>
       </c>
       <c r="E69" s="24" t="inlineStr">
@@ -17265,12 +17503,12 @@
       </c>
       <c r="F69" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="G69" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="H69" s="24" t="inlineStr">
@@ -17290,30 +17528,30 @@
         </is>
       </c>
       <c r="L69" s="26" t="n">
-        <v>-156</v>
+        <v>-147</v>
       </c>
       <c r="M69" s="39" t="n">
-        <v>1.641026</v>
+        <v>1.680272</v>
       </c>
       <c r="N69" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.5951419999999999</v>
       </c>
       <c r="O69" s="28" t="n">
-        <v>0.518942</v>
+        <v>0.58189</v>
       </c>
       <c r="P69" s="28" t="n"/>
       <c r="Q69" s="28" t="n">
-        <v>-0.090433</v>
+        <v>-0.013252</v>
       </c>
       <c r="R69" s="26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S69" s="29" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="T69" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U69" s="24" t="inlineStr">
@@ -17332,7 +17570,7 @@
       <c r="AD69" s="24" t="n"/>
       <c r="AE69" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.6100 (aec-mlb-cws-tex-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5950 (aec-mlb-ath-az-2026-07-20).</t>
         </is>
       </c>
       <c r="AF69" s="31" t="inlineStr">
@@ -17373,32 +17611,32 @@
       </c>
       <c r="AP69" s="24" t="inlineStr">
         <is>
-          <t>mlb-cws</t>
+          <t>mlb-ath</t>
         </is>
       </c>
       <c r="AQ69" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="AR69" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="AS69" s="24" t="inlineStr">
         <is>
-          <t>mlb-tex</t>
+          <t>mlb-ari</t>
         </is>
       </c>
       <c r="AT69" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AU69" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AV69" s="24" t="n"/>
@@ -17416,7 +17654,7 @@
       </c>
       <c r="BA69" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB69" s="24" t="inlineStr">
@@ -17426,17 +17664,17 @@
       </c>
       <c r="BC69" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD69" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE69" s="24" t="inlineStr">
         <is>
-          <t>99c414db5594aff2</t>
+          <t>7b682aa5da86e2a4</t>
         </is>
       </c>
       <c r="BF69" s="24" t="inlineStr">
@@ -17446,12 +17684,12 @@
       </c>
       <c r="BG69" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH69" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:25:54.352994Z</t>
+          <t>2026-07-20T14:57:51.339273Z</t>
         </is>
       </c>
       <c r="BI69" s="24" t="inlineStr">
@@ -17461,16 +17699,16 @@
       </c>
       <c r="BJ69" s="38" t="n"/>
       <c r="BK69" s="26" t="n">
-        <v>-156</v>
+        <v>-147</v>
       </c>
       <c r="BL69" s="39" t="n">
-        <v>1.641026</v>
+        <v>1.680272</v>
       </c>
       <c r="BM69" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.5951419999999999</v>
       </c>
       <c r="BN69" s="28" t="n">
-        <v>0.606965</v>
+        <v>0.59204</v>
       </c>
       <c r="BO69" s="28" t="n"/>
       <c r="BP69" s="38" t="n"/>
@@ -17489,22 +17727,22 @@
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>fe1acb3bd59e41b3</t>
+          <t>b9692cb20ec34d5d</t>
         </is>
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:27:09.837629Z</t>
+          <t>2026-07-20T15:22:41.782177Z</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T20:05:00-0400</t>
+          <t>2026-07-20T21:40:00-0400</t>
         </is>
       </c>
       <c r="D70" s="24" t="inlineStr">
         <is>
-          <t>401816193</t>
+          <t>401816199</t>
         </is>
       </c>
       <c r="E70" s="24" t="inlineStr">
@@ -17514,12 +17752,12 @@
       </c>
       <c r="F70" s="24" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="G70" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="H70" s="24" t="inlineStr">
@@ -17539,30 +17777,30 @@
         </is>
       </c>
       <c r="L70" s="26" t="n">
-        <v>-108</v>
+        <v>-141</v>
       </c>
       <c r="M70" s="39" t="n">
-        <v>1.925926</v>
+        <v>1.70922</v>
       </c>
       <c r="N70" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.585062</v>
       </c>
       <c r="O70" s="28" t="n">
-        <v>0.576624</v>
+        <v>0.592852</v>
       </c>
       <c r="P70" s="28" t="n"/>
       <c r="Q70" s="28" t="n">
-        <v>0.057393</v>
+        <v>0.00779</v>
       </c>
       <c r="R70" s="26" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="S70" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T70" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U70" s="24" t="inlineStr">
@@ -17581,7 +17819,7 @@
       <c r="AD70" s="24" t="n"/>
       <c r="AE70" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5200 (aec-mlb-det-chc-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5850 (aec-mlb-cin-sea-2026-07-20).</t>
         </is>
       </c>
       <c r="AF70" s="31" t="inlineStr">
@@ -17622,32 +17860,32 @@
       </c>
       <c r="AP70" s="24" t="inlineStr">
         <is>
-          <t>mlb-det</t>
+          <t>mlb-cin</t>
         </is>
       </c>
       <c r="AQ70" s="24" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="AR70" s="24" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="AS70" s="24" t="inlineStr">
         <is>
-          <t>mlb-chc</t>
+          <t>mlb-sea</t>
         </is>
       </c>
       <c r="AT70" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="AU70" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="AV70" s="24" t="n"/>
@@ -17665,7 +17903,7 @@
       </c>
       <c r="BA70" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB70" s="24" t="inlineStr">
@@ -17675,17 +17913,17 @@
       </c>
       <c r="BC70" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD70" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE70" s="24" t="inlineStr">
         <is>
-          <t>cc155e3ebbdaf924</t>
+          <t>af7ccafcacf69681</t>
         </is>
       </c>
       <c r="BF70" s="24" t="inlineStr">
@@ -17695,12 +17933,12 @@
       </c>
       <c r="BG70" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH70" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:25:55.980853Z</t>
+          <t>2026-07-20T14:57:52.831217Z</t>
         </is>
       </c>
       <c r="BI70" s="24" t="inlineStr">
@@ -17710,16 +17948,16 @@
       </c>
       <c r="BJ70" s="38" t="n"/>
       <c r="BK70" s="26" t="n">
-        <v>-108</v>
+        <v>-141</v>
       </c>
       <c r="BL70" s="39" t="n">
-        <v>1.925926</v>
+        <v>1.70922</v>
       </c>
       <c r="BM70" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.585062</v>
       </c>
       <c r="BN70" s="28" t="n">
-        <v>0.517413</v>
+        <v>0.58209</v>
       </c>
       <c r="BO70" s="28" t="n"/>
       <c r="BP70" s="38" t="n"/>
@@ -17738,37 +17976,37 @@
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>41914e723f8545e3</t>
+          <t>11f48fe641c040f7</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:27:09.837629Z</t>
+          <t>2026-07-20T15:28:55.067840Z</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T20:40:00-0400</t>
+          <t>2026-07-20T20:00:00-0400</t>
         </is>
       </c>
       <c r="D71" s="24" t="inlineStr">
         <is>
-          <t>401816197</t>
+          <t>401857083</t>
         </is>
       </c>
       <c r="E71" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>WNBA</t>
         </is>
       </c>
       <c r="F71" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Las Vegas Aces</t>
         </is>
       </c>
       <c r="G71" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Toronto Tempo</t>
         </is>
       </c>
       <c r="H71" s="24" t="inlineStr">
@@ -17788,30 +18026,30 @@
         </is>
       </c>
       <c r="L71" s="26" t="n">
-        <v>-115</v>
+        <v>-488</v>
       </c>
       <c r="M71" s="39" t="n">
-        <v>1.869565</v>
+        <v>1.204918</v>
       </c>
       <c r="N71" s="28" t="n">
-        <v>0.534884</v>
+        <v>0.829932</v>
       </c>
       <c r="O71" s="28" t="n">
-        <v>0.547691</v>
+        <v>0.6572210000000001</v>
       </c>
       <c r="P71" s="28" t="n"/>
       <c r="Q71" s="28" t="n">
-        <v>0.012807</v>
+        <v>-0.172711</v>
       </c>
       <c r="R71" s="26" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S71" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T71" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="U71" s="24" t="inlineStr">
@@ -17830,7 +18068,7 @@
       <c r="AD71" s="24" t="n"/>
       <c r="AE71" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5350 (aec-mlb-wsh-col-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5051; executable ask 0.8300 (aec-wnba-lv-tor-2026-07-20).</t>
         </is>
       </c>
       <c r="AF71" s="31" t="inlineStr">
@@ -17866,37 +18104,37 @@
       </c>
       <c r="AO71" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
         </is>
       </c>
       <c r="AP71" s="24" t="inlineStr">
         <is>
-          <t>mlb-wsh</t>
+          <t>wnba-lva</t>
         </is>
       </c>
       <c r="AQ71" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Las Vegas Aces</t>
         </is>
       </c>
       <c r="AR71" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Las Vegas Aces</t>
         </is>
       </c>
       <c r="AS71" s="24" t="inlineStr">
         <is>
-          <t>mlb-col</t>
+          <t>wnba-tor</t>
         </is>
       </c>
       <c r="AT71" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Toronto Tempo</t>
         </is>
       </c>
       <c r="AU71" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Toronto Tempo</t>
         </is>
       </c>
       <c r="AV71" s="24" t="n"/>
@@ -17914,7 +18152,7 @@
       </c>
       <c r="BA71" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
         </is>
       </c>
       <c r="BB71" s="24" t="inlineStr">
@@ -17924,17 +18162,17 @@
       </c>
       <c r="BC71" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BD71" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
         </is>
       </c>
       <c r="BE71" s="24" t="inlineStr">
         <is>
-          <t>c4e9d6e5adabb27c</t>
+          <t>32740a9f4976946d</t>
         </is>
       </c>
       <c r="BF71" s="24" t="inlineStr">
@@ -17944,12 +18182,12 @@
       </c>
       <c r="BG71" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BH71" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:25:57.709954Z</t>
+          <t>2026-07-20T14:57:56.867039Z</t>
         </is>
       </c>
       <c r="BI71" s="24" t="inlineStr">
@@ -17959,16 +18197,16 @@
       </c>
       <c r="BJ71" s="38" t="n"/>
       <c r="BK71" s="26" t="n">
-        <v>-115</v>
+        <v>-488</v>
       </c>
       <c r="BL71" s="39" t="n">
-        <v>1.869565</v>
+        <v>1.204918</v>
       </c>
       <c r="BM71" s="28" t="n">
-        <v>0.534884</v>
+        <v>0.829932</v>
       </c>
       <c r="BN71" s="28" t="n">
-        <v>0.532338</v>
+        <v>0.821782</v>
       </c>
       <c r="BO71" s="28" t="n"/>
       <c r="BP71" s="38" t="n"/>
@@ -17987,37 +18225,37 @@
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
         <is>
-          <t>226f56cb020a4d72</t>
+          <t>18e861041a484fd5</t>
         </is>
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:27:09.837629Z</t>
+          <t>2026-07-20T15:28:55.067840Z</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T21:40:00-0400</t>
+          <t>2026-07-20T20:00:00-0400</t>
         </is>
       </c>
       <c r="D72" s="24" t="inlineStr">
         <is>
-          <t>401816198</t>
+          <t>401892393</t>
         </is>
       </c>
       <c r="E72" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>WNBA</t>
         </is>
       </c>
       <c r="F72" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="G72" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="H72" s="24" t="inlineStr">
@@ -18037,30 +18275,30 @@
         </is>
       </c>
       <c r="L72" s="26" t="n">
-        <v>-147</v>
+        <v>156</v>
       </c>
       <c r="M72" s="39" t="n">
-        <v>1.680272</v>
+        <v>2.56</v>
       </c>
       <c r="N72" s="28" t="n">
-        <v>0.5951419999999999</v>
+        <v>0.390625</v>
       </c>
       <c r="O72" s="28" t="n">
-        <v>0.589249</v>
+        <v>0.688998</v>
       </c>
       <c r="P72" s="28" t="n"/>
       <c r="Q72" s="28" t="n">
-        <v>-0.005893</v>
+        <v>0.298373</v>
       </c>
       <c r="R72" s="26" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="S72" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T72" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="U72" s="24" t="inlineStr">
@@ -18079,7 +18317,7 @@
       <c r="AD72" s="24" t="n"/>
       <c r="AE72" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5950 (aec-mlb-ath-az-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5051; executable ask 0.3900 (aec-wnba-ny-dal-2026-07-20).</t>
         </is>
       </c>
       <c r="AF72" s="31" t="inlineStr">
@@ -18115,37 +18353,37 @@
       </c>
       <c r="AO72" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
         </is>
       </c>
       <c r="AP72" s="24" t="inlineStr">
         <is>
-          <t>mlb-ath</t>
+          <t>wnba-nyl</t>
         </is>
       </c>
       <c r="AQ72" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="AR72" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="AS72" s="24" t="inlineStr">
         <is>
-          <t>mlb-ari</t>
+          <t>wnba-dal</t>
         </is>
       </c>
       <c r="AT72" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="AU72" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="AV72" s="24" t="n"/>
@@ -18163,7 +18401,7 @@
       </c>
       <c r="BA72" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
         </is>
       </c>
       <c r="BB72" s="24" t="inlineStr">
@@ -18173,17 +18411,17 @@
       </c>
       <c r="BC72" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BD72" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
         </is>
       </c>
       <c r="BE72" s="24" t="inlineStr">
         <is>
-          <t>202c6fbc367f9e59</t>
+          <t>c20bbb99f1fff741</t>
         </is>
       </c>
       <c r="BF72" s="24" t="inlineStr">
@@ -18193,12 +18431,12 @@
       </c>
       <c r="BG72" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BH72" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:25:58.909244Z</t>
+          <t>2026-07-20T14:57:58.731031Z</t>
         </is>
       </c>
       <c r="BI72" s="24" t="inlineStr">
@@ -18208,16 +18446,16 @@
       </c>
       <c r="BJ72" s="38" t="n"/>
       <c r="BK72" s="26" t="n">
-        <v>-147</v>
+        <v>156</v>
       </c>
       <c r="BL72" s="39" t="n">
-        <v>1.680272</v>
+        <v>2.56</v>
       </c>
       <c r="BM72" s="28" t="n">
-        <v>0.5951419999999999</v>
+        <v>0.390625</v>
       </c>
       <c r="BN72" s="28" t="n">
-        <v>0.59204</v>
+        <v>0.386139</v>
       </c>
       <c r="BO72" s="28" t="n"/>
       <c r="BP72" s="38" t="n"/>
@@ -18236,37 +18474,37 @@
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>a9cd87c83dca4e08</t>
+          <t>195c4a9c3ce44e1b</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:27:09.837629Z</t>
+          <t>2026-07-20T15:28:55.067840Z</t>
         </is>
       </c>
       <c r="C73" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T21:40:00-0400</t>
+          <t>2026-07-20T22:00:00-0400</t>
         </is>
       </c>
       <c r="D73" s="24" t="inlineStr">
         <is>
-          <t>401816199</t>
+          <t>401857084</t>
         </is>
       </c>
       <c r="E73" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>WNBA</t>
         </is>
       </c>
       <c r="F73" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="G73" s="24" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Golden State Valkyries</t>
         </is>
       </c>
       <c r="H73" s="24" t="inlineStr">
@@ -18286,30 +18524,30 @@
         </is>
       </c>
       <c r="L73" s="26" t="n">
-        <v>-144</v>
+        <v>-317</v>
       </c>
       <c r="M73" s="39" t="n">
-        <v>1.694444</v>
+        <v>1.315457</v>
       </c>
       <c r="N73" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.760192</v>
       </c>
       <c r="O73" s="28" t="n">
-        <v>0.597509</v>
+        <v>0.750463</v>
       </c>
       <c r="P73" s="28" t="n"/>
       <c r="Q73" s="28" t="n">
-        <v>0.007345</v>
+        <v>-0.009729</v>
       </c>
       <c r="R73" s="26" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="S73" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T73" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="U73" s="24" t="inlineStr">
@@ -18328,7 +18566,7 @@
       <c r="AD73" s="24" t="n"/>
       <c r="AE73" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5900 (aec-mlb-cin-sea-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5051; executable ask 0.7600 (aec-wnba-wsh-gsv-2026-07-20).</t>
         </is>
       </c>
       <c r="AF73" s="31" t="inlineStr">
@@ -18369,32 +18607,32 @@
       </c>
       <c r="AP73" s="24" t="inlineStr">
         <is>
-          <t>mlb-cin</t>
+          <t>wnba-was</t>
         </is>
       </c>
       <c r="AQ73" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="AR73" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="AS73" s="24" t="inlineStr">
         <is>
-          <t>mlb-sea</t>
+          <t>wnba-gsv</t>
         </is>
       </c>
       <c r="AT73" s="24" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Golden State Valkyries</t>
         </is>
       </c>
       <c r="AU73" s="24" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Golden State Valkyries</t>
         </is>
       </c>
       <c r="AV73" s="24" t="n"/>
@@ -18412,7 +18650,7 @@
       </c>
       <c r="BA73" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
         </is>
       </c>
       <c r="BB73" s="24" t="inlineStr">
@@ -18422,17 +18660,17 @@
       </c>
       <c r="BC73" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BD73" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
         </is>
       </c>
       <c r="BE73" s="24" t="inlineStr">
         <is>
-          <t>982d73638d70c45b</t>
+          <t>a82314f65618b567</t>
         </is>
       </c>
       <c r="BF73" s="24" t="inlineStr">
@@ -18442,12 +18680,12 @@
       </c>
       <c r="BG73" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BH73" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:26:01.154096Z</t>
+          <t>2026-07-20T14:58:01.293707Z</t>
         </is>
       </c>
       <c r="BI73" s="24" t="inlineStr">
@@ -18457,16 +18695,16 @@
       </c>
       <c r="BJ73" s="38" t="n"/>
       <c r="BK73" s="26" t="n">
-        <v>-144</v>
+        <v>-317</v>
       </c>
       <c r="BL73" s="39" t="n">
-        <v>1.694444</v>
+        <v>1.315457</v>
       </c>
       <c r="BM73" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.760192</v>
       </c>
       <c r="BN73" s="28" t="n">
-        <v>0.5870649999999999</v>
+        <v>0.752475</v>
       </c>
       <c r="BO73" s="28" t="n"/>
       <c r="BP73" s="38" t="n"/>
@@ -18485,12 +18723,12 @@
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
         <is>
-          <t>8e420714a95e4d9c</t>
+          <t>555b6295ce3941e7</t>
         </is>
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:27:09.837629Z</t>
+          <t>2026-07-20T15:28:55.067840Z</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
@@ -18500,22 +18738,22 @@
       </c>
       <c r="D74" s="24" t="inlineStr">
         <is>
-          <t>401816200</t>
+          <t>401857085</t>
         </is>
       </c>
       <c r="E74" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>WNBA</t>
         </is>
       </c>
       <c r="F74" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="G74" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="H74" s="24" t="inlineStr">
@@ -18535,30 +18773,30 @@
         </is>
       </c>
       <c r="L74" s="26" t="n">
-        <v>104</v>
+        <v>-456</v>
       </c>
       <c r="M74" s="39" t="n">
-        <v>2.04</v>
+        <v>1.219298</v>
       </c>
       <c r="N74" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.820144</v>
       </c>
       <c r="O74" s="28" t="n">
-        <v>0.5411280000000001</v>
+        <v>0.738843</v>
       </c>
       <c r="P74" s="28" t="n"/>
       <c r="Q74" s="28" t="n">
-        <v>0.050932</v>
+        <v>-0.081301</v>
       </c>
       <c r="R74" s="26" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="S74" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T74" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="U74" s="24" t="inlineStr">
@@ -18577,7 +18815,7 @@
       <c r="AD74" s="24" t="n"/>
       <c r="AE74" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.4900 (aec-mlb-stl-laa-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5051; executable ask 0.8200 (aec-wnba-min-sea-2026-07-20).</t>
         </is>
       </c>
       <c r="AF74" s="31" t="inlineStr">
@@ -18618,32 +18856,32 @@
       </c>
       <c r="AP74" s="24" t="inlineStr">
         <is>
-          <t>mlb-stl</t>
+          <t>wnba-min</t>
         </is>
       </c>
       <c r="AQ74" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="AR74" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="AS74" s="24" t="inlineStr">
         <is>
-          <t>mlb-laa</t>
+          <t>wnba-sea</t>
         </is>
       </c>
       <c r="AT74" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="AU74" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="AV74" s="24" t="n"/>
@@ -18661,7 +18899,7 @@
       </c>
       <c r="BA74" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
         </is>
       </c>
       <c r="BB74" s="24" t="inlineStr">
@@ -18671,17 +18909,17 @@
       </c>
       <c r="BC74" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BD74" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
         </is>
       </c>
       <c r="BE74" s="24" t="inlineStr">
         <is>
-          <t>84a60e91d728d400</t>
+          <t>c7928758cc04b6e5</t>
         </is>
       </c>
       <c r="BF74" s="24" t="inlineStr">
@@ -18691,12 +18929,12 @@
       </c>
       <c r="BG74" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BH74" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T07:26:01.325929Z</t>
+          <t>2026-07-20T14:58:02.052718Z</t>
         </is>
       </c>
       <c r="BI74" s="24" t="inlineStr">
@@ -18706,16 +18944,16 @@
       </c>
       <c r="BJ74" s="38" t="n"/>
       <c r="BK74" s="26" t="n">
-        <v>104</v>
+        <v>-456</v>
       </c>
       <c r="BL74" s="39" t="n">
-        <v>2.04</v>
+        <v>1.219298</v>
       </c>
       <c r="BM74" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.820144</v>
       </c>
       <c r="BN74" s="28" t="n">
-        <v>0.487562</v>
+        <v>0.811881</v>
       </c>
       <c r="BO74" s="28" t="n"/>
       <c r="BP74" s="38" t="n"/>
@@ -18731,3990 +18969,6 @@
       <c r="BZ74" s="24" t="n"/>
       <c r="CA74" s="31" t="n"/>
     </row>
-    <row r="75" ht="36" customHeight="1">
-      <c r="A75" s="24" t="inlineStr">
-        <is>
-          <t>e35a217d64aa4265</t>
-        </is>
-      </c>
-      <c r="B75" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T07:27:15.488547Z</t>
-        </is>
-      </c>
-      <c r="C75" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T20:00:00-0400</t>
-        </is>
-      </c>
-      <c r="D75" s="24" t="inlineStr">
-        <is>
-          <t>401857083</t>
-        </is>
-      </c>
-      <c r="E75" s="24" t="inlineStr">
-        <is>
-          <t>WNBA</t>
-        </is>
-      </c>
-      <c r="F75" s="24" t="inlineStr">
-        <is>
-          <t>Las Vegas Aces</t>
-        </is>
-      </c>
-      <c r="G75" s="24" t="inlineStr">
-        <is>
-          <t>Toronto Tempo</t>
-        </is>
-      </c>
-      <c r="H75" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I75" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J75" s="38" t="n"/>
-      <c r="K75" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L75" s="26" t="n">
-        <v>-488</v>
-      </c>
-      <c r="M75" s="39" t="n">
-        <v>1.204918</v>
-      </c>
-      <c r="N75" s="28" t="n">
-        <v>0.829932</v>
-      </c>
-      <c r="O75" s="28" t="n">
-        <v>0.657294</v>
-      </c>
-      <c r="P75" s="28" t="n"/>
-      <c r="Q75" s="28" t="n">
-        <v>-0.172638</v>
-      </c>
-      <c r="R75" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T75" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U75" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V75" s="24" t="n"/>
-      <c r="W75" s="26" t="n"/>
-      <c r="X75" s="26" t="n"/>
-      <c r="Y75" s="38" t="n"/>
-      <c r="Z75" s="26" t="n"/>
-      <c r="AA75" s="28" t="n"/>
-      <c r="AB75" s="28" t="n"/>
-      <c r="AC75" s="40" t="n"/>
-      <c r="AD75" s="24" t="n"/>
-      <c r="AE75" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5000; executable ask 0.8300 (aec-wnba-lv-tor-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF75" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG75" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH75" s="24" t="n"/>
-      <c r="AI75" s="31" t="n"/>
-      <c r="AJ75" s="31" t="n"/>
-      <c r="AK75" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL75" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM75" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN75" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO75" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP75" s="24" t="inlineStr">
-        <is>
-          <t>wnba-lva</t>
-        </is>
-      </c>
-      <c r="AQ75" s="24" t="inlineStr">
-        <is>
-          <t>Las Vegas Aces</t>
-        </is>
-      </c>
-      <c r="AR75" s="24" t="inlineStr">
-        <is>
-          <t>Las Vegas Aces</t>
-        </is>
-      </c>
-      <c r="AS75" s="24" t="inlineStr">
-        <is>
-          <t>wnba-tor</t>
-        </is>
-      </c>
-      <c r="AT75" s="24" t="inlineStr">
-        <is>
-          <t>Toronto Tempo</t>
-        </is>
-      </c>
-      <c r="AU75" s="24" t="inlineStr">
-        <is>
-          <t>Toronto Tempo</t>
-        </is>
-      </c>
-      <c r="AV75" s="24" t="n"/>
-      <c r="AW75" s="24" t="n"/>
-      <c r="AX75" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY75" s="24" t="n"/>
-      <c r="AZ75" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA75" s="24" t="inlineStr">
-        <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
-        </is>
-      </c>
-      <c r="BB75" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC75" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD75" s="24" t="inlineStr">
-        <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
-        </is>
-      </c>
-      <c r="BE75" s="24" t="inlineStr">
-        <is>
-          <t>b239d28861d5b74d</t>
-        </is>
-      </c>
-      <c r="BF75" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG75" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH75" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T07:26:02.605954Z</t>
-        </is>
-      </c>
-      <c r="BI75" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ75" s="38" t="n"/>
-      <c r="BK75" s="26" t="n">
-        <v>-488</v>
-      </c>
-      <c r="BL75" s="39" t="n">
-        <v>1.204918</v>
-      </c>
-      <c r="BM75" s="28" t="n">
-        <v>0.829932</v>
-      </c>
-      <c r="BN75" s="28" t="n">
-        <v>0.821782</v>
-      </c>
-      <c r="BO75" s="28" t="n"/>
-      <c r="BP75" s="38" t="n"/>
-      <c r="BQ75" s="39" t="n"/>
-      <c r="BR75" s="28" t="n"/>
-      <c r="BS75" s="28" t="n"/>
-      <c r="BT75" s="28" t="n"/>
-      <c r="BU75" s="38" t="n"/>
-      <c r="BV75" s="29" t="n"/>
-      <c r="BW75" s="24" t="n"/>
-      <c r="BX75" s="40" t="n"/>
-      <c r="BY75" s="39" t="n"/>
-      <c r="BZ75" s="24" t="n"/>
-      <c r="CA75" s="31" t="n"/>
-    </row>
-    <row r="76" ht="36" customHeight="1">
-      <c r="A76" s="24" t="inlineStr">
-        <is>
-          <t>6c42d2d2436849c1</t>
-        </is>
-      </c>
-      <c r="B76" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T07:27:15.488547Z</t>
-        </is>
-      </c>
-      <c r="C76" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T20:00:00-0400</t>
-        </is>
-      </c>
-      <c r="D76" s="24" t="inlineStr">
-        <is>
-          <t>401892393</t>
-        </is>
-      </c>
-      <c r="E76" s="24" t="inlineStr">
-        <is>
-          <t>WNBA</t>
-        </is>
-      </c>
-      <c r="F76" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="G76" s="24" t="inlineStr">
-        <is>
-          <t>Dallas Wings</t>
-        </is>
-      </c>
-      <c r="H76" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I76" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J76" s="38" t="n"/>
-      <c r="K76" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L76" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="M76" s="39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N76" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O76" s="28" t="n">
-        <v>0.6787840000000001</v>
-      </c>
-      <c r="P76" s="28" t="n"/>
-      <c r="Q76" s="28" t="n">
-        <v>0.278784</v>
-      </c>
-      <c r="R76" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S76" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T76" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U76" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V76" s="24" t="n"/>
-      <c r="W76" s="26" t="n"/>
-      <c r="X76" s="26" t="n"/>
-      <c r="Y76" s="38" t="n"/>
-      <c r="Z76" s="26" t="n"/>
-      <c r="AA76" s="28" t="n"/>
-      <c r="AB76" s="28" t="n"/>
-      <c r="AC76" s="40" t="n"/>
-      <c r="AD76" s="24" t="n"/>
-      <c r="AE76" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5000; executable ask 0.4000 (aec-wnba-ny-dal-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF76" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG76" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH76" s="24" t="n"/>
-      <c r="AI76" s="31" t="n"/>
-      <c r="AJ76" s="31" t="n"/>
-      <c r="AK76" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL76" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM76" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN76" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO76" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP76" s="24" t="inlineStr">
-        <is>
-          <t>wnba-nyl</t>
-        </is>
-      </c>
-      <c r="AQ76" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="AR76" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="AS76" s="24" t="inlineStr">
-        <is>
-          <t>wnba-dal</t>
-        </is>
-      </c>
-      <c r="AT76" s="24" t="inlineStr">
-        <is>
-          <t>Dallas Wings</t>
-        </is>
-      </c>
-      <c r="AU76" s="24" t="inlineStr">
-        <is>
-          <t>Dallas Wings</t>
-        </is>
-      </c>
-      <c r="AV76" s="24" t="n"/>
-      <c r="AW76" s="24" t="n"/>
-      <c r="AX76" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY76" s="24" t="n"/>
-      <c r="AZ76" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA76" s="24" t="inlineStr">
-        <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
-        </is>
-      </c>
-      <c r="BB76" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC76" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD76" s="24" t="inlineStr">
-        <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
-        </is>
-      </c>
-      <c r="BE76" s="24" t="inlineStr">
-        <is>
-          <t>1c6f45e72b2d1f80</t>
-        </is>
-      </c>
-      <c r="BF76" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG76" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH76" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T07:26:04.731909Z</t>
-        </is>
-      </c>
-      <c r="BI76" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ76" s="38" t="n"/>
-      <c r="BK76" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="BL76" s="39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BM76" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BN76" s="28" t="n">
-        <v>0.39604</v>
-      </c>
-      <c r="BO76" s="28" t="n"/>
-      <c r="BP76" s="38" t="n"/>
-      <c r="BQ76" s="39" t="n"/>
-      <c r="BR76" s="28" t="n"/>
-      <c r="BS76" s="28" t="n"/>
-      <c r="BT76" s="28" t="n"/>
-      <c r="BU76" s="38" t="n"/>
-      <c r="BV76" s="29" t="n"/>
-      <c r="BW76" s="24" t="n"/>
-      <c r="BX76" s="40" t="n"/>
-      <c r="BY76" s="39" t="n"/>
-      <c r="BZ76" s="24" t="n"/>
-      <c r="CA76" s="31" t="n"/>
-    </row>
-    <row r="77" ht="36" customHeight="1">
-      <c r="A77" s="24" t="inlineStr">
-        <is>
-          <t>0da50dc88c9649b8</t>
-        </is>
-      </c>
-      <c r="B77" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T07:27:15.488547Z</t>
-        </is>
-      </c>
-      <c r="C77" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T22:00:00-0400</t>
-        </is>
-      </c>
-      <c r="D77" s="24" t="inlineStr">
-        <is>
-          <t>401857084</t>
-        </is>
-      </c>
-      <c r="E77" s="24" t="inlineStr">
-        <is>
-          <t>WNBA</t>
-        </is>
-      </c>
-      <c r="F77" s="24" t="inlineStr">
-        <is>
-          <t>Washington Mystics</t>
-        </is>
-      </c>
-      <c r="G77" s="24" t="inlineStr">
-        <is>
-          <t>Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="H77" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I77" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J77" s="38" t="n"/>
-      <c r="K77" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L77" s="26" t="n">
-        <v>-317</v>
-      </c>
-      <c r="M77" s="39" t="n">
-        <v>1.315457</v>
-      </c>
-      <c r="N77" s="28" t="n">
-        <v>0.760192</v>
-      </c>
-      <c r="O77" s="28" t="n">
-        <v>0.750444</v>
-      </c>
-      <c r="P77" s="28" t="n"/>
-      <c r="Q77" s="28" t="n">
-        <v>-0.009748</v>
-      </c>
-      <c r="R77" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="S77" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T77" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U77" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V77" s="24" t="n"/>
-      <c r="W77" s="26" t="n"/>
-      <c r="X77" s="26" t="n"/>
-      <c r="Y77" s="38" t="n"/>
-      <c r="Z77" s="26" t="n"/>
-      <c r="AA77" s="28" t="n"/>
-      <c r="AB77" s="28" t="n"/>
-      <c r="AC77" s="40" t="n"/>
-      <c r="AD77" s="24" t="n"/>
-      <c r="AE77" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5000; executable ask 0.7600 (aec-wnba-wsh-gsv-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF77" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG77" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH77" s="24" t="n"/>
-      <c r="AI77" s="31" t="n"/>
-      <c r="AJ77" s="31" t="n"/>
-      <c r="AK77" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL77" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM77" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN77" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO77" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP77" s="24" t="inlineStr">
-        <is>
-          <t>wnba-was</t>
-        </is>
-      </c>
-      <c r="AQ77" s="24" t="inlineStr">
-        <is>
-          <t>Washington Mystics</t>
-        </is>
-      </c>
-      <c r="AR77" s="24" t="inlineStr">
-        <is>
-          <t>Washington Mystics</t>
-        </is>
-      </c>
-      <c r="AS77" s="24" t="inlineStr">
-        <is>
-          <t>wnba-gsv</t>
-        </is>
-      </c>
-      <c r="AT77" s="24" t="inlineStr">
-        <is>
-          <t>Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="AU77" s="24" t="inlineStr">
-        <is>
-          <t>Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="AV77" s="24" t="n"/>
-      <c r="AW77" s="24" t="n"/>
-      <c r="AX77" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY77" s="24" t="n"/>
-      <c r="AZ77" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA77" s="24" t="inlineStr">
-        <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
-        </is>
-      </c>
-      <c r="BB77" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC77" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD77" s="24" t="inlineStr">
-        <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
-        </is>
-      </c>
-      <c r="BE77" s="24" t="inlineStr">
-        <is>
-          <t>46de7d71a35c9491</t>
-        </is>
-      </c>
-      <c r="BF77" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG77" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH77" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T07:26:06.455979Z</t>
-        </is>
-      </c>
-      <c r="BI77" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ77" s="38" t="n"/>
-      <c r="BK77" s="26" t="n">
-        <v>-317</v>
-      </c>
-      <c r="BL77" s="39" t="n">
-        <v>1.315457</v>
-      </c>
-      <c r="BM77" s="28" t="n">
-        <v>0.760192</v>
-      </c>
-      <c r="BN77" s="28" t="n">
-        <v>0.752475</v>
-      </c>
-      <c r="BO77" s="28" t="n"/>
-      <c r="BP77" s="38" t="n"/>
-      <c r="BQ77" s="39" t="n"/>
-      <c r="BR77" s="28" t="n"/>
-      <c r="BS77" s="28" t="n"/>
-      <c r="BT77" s="28" t="n"/>
-      <c r="BU77" s="38" t="n"/>
-      <c r="BV77" s="29" t="n"/>
-      <c r="BW77" s="24" t="n"/>
-      <c r="BX77" s="40" t="n"/>
-      <c r="BY77" s="39" t="n"/>
-      <c r="BZ77" s="24" t="n"/>
-      <c r="CA77" s="31" t="n"/>
-    </row>
-    <row r="78" ht="36" customHeight="1">
-      <c r="A78" s="24" t="inlineStr">
-        <is>
-          <t>2d184773492d4263</t>
-        </is>
-      </c>
-      <c r="B78" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T07:27:15.488547Z</t>
-        </is>
-      </c>
-      <c r="C78" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T22:00:00-0400</t>
-        </is>
-      </c>
-      <c r="D78" s="24" t="inlineStr">
-        <is>
-          <t>401857085</t>
-        </is>
-      </c>
-      <c r="E78" s="24" t="inlineStr">
-        <is>
-          <t>WNBA</t>
-        </is>
-      </c>
-      <c r="F78" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="G78" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Storm</t>
-        </is>
-      </c>
-      <c r="H78" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I78" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J78" s="38" t="n"/>
-      <c r="K78" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L78" s="26" t="n">
-        <v>-488</v>
-      </c>
-      <c r="M78" s="39" t="n">
-        <v>1.204918</v>
-      </c>
-      <c r="N78" s="28" t="n">
-        <v>0.829932</v>
-      </c>
-      <c r="O78" s="28" t="n">
-        <v>0.739042</v>
-      </c>
-      <c r="P78" s="28" t="n"/>
-      <c r="Q78" s="28" t="n">
-        <v>-0.09089</v>
-      </c>
-      <c r="R78" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T78" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U78" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V78" s="24" t="n"/>
-      <c r="W78" s="26" t="n"/>
-      <c r="X78" s="26" t="n"/>
-      <c r="Y78" s="38" t="n"/>
-      <c r="Z78" s="26" t="n"/>
-      <c r="AA78" s="28" t="n"/>
-      <c r="AB78" s="28" t="n"/>
-      <c r="AC78" s="40" t="n"/>
-      <c r="AD78" s="24" t="n"/>
-      <c r="AE78" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5000; executable ask 0.8300 (aec-wnba-min-sea-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF78" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG78" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH78" s="24" t="n"/>
-      <c r="AI78" s="31" t="n"/>
-      <c r="AJ78" s="31" t="n"/>
-      <c r="AK78" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL78" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM78" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN78" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO78" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP78" s="24" t="inlineStr">
-        <is>
-          <t>wnba-min</t>
-        </is>
-      </c>
-      <c r="AQ78" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="AR78" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="AS78" s="24" t="inlineStr">
-        <is>
-          <t>wnba-sea</t>
-        </is>
-      </c>
-      <c r="AT78" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Storm</t>
-        </is>
-      </c>
-      <c r="AU78" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Storm</t>
-        </is>
-      </c>
-      <c r="AV78" s="24" t="n"/>
-      <c r="AW78" s="24" t="n"/>
-      <c r="AX78" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY78" s="24" t="n"/>
-      <c r="AZ78" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA78" s="24" t="inlineStr">
-        <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
-        </is>
-      </c>
-      <c r="BB78" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC78" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD78" s="24" t="inlineStr">
-        <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
-        </is>
-      </c>
-      <c r="BE78" s="24" t="inlineStr">
-        <is>
-          <t>9e3cecf68c87303d</t>
-        </is>
-      </c>
-      <c r="BF78" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG78" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH78" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T07:26:06.846002Z</t>
-        </is>
-      </c>
-      <c r="BI78" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ78" s="38" t="n"/>
-      <c r="BK78" s="26" t="n">
-        <v>-488</v>
-      </c>
-      <c r="BL78" s="39" t="n">
-        <v>1.204918</v>
-      </c>
-      <c r="BM78" s="28" t="n">
-        <v>0.829932</v>
-      </c>
-      <c r="BN78" s="28" t="n">
-        <v>0.821782</v>
-      </c>
-      <c r="BO78" s="28" t="n"/>
-      <c r="BP78" s="38" t="n"/>
-      <c r="BQ78" s="39" t="n"/>
-      <c r="BR78" s="28" t="n"/>
-      <c r="BS78" s="28" t="n"/>
-      <c r="BT78" s="28" t="n"/>
-      <c r="BU78" s="38" t="n"/>
-      <c r="BV78" s="29" t="n"/>
-      <c r="BW78" s="24" t="n"/>
-      <c r="BX78" s="40" t="n"/>
-      <c r="BY78" s="39" t="n"/>
-      <c r="BZ78" s="24" t="n"/>
-      <c r="CA78" s="31" t="n"/>
-    </row>
-    <row r="79" ht="36" customHeight="1">
-      <c r="A79" s="24" t="inlineStr">
-        <is>
-          <t>369b925b172f4b6a</t>
-        </is>
-      </c>
-      <c r="B79" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-19T17:18:24.670965Z</t>
-        </is>
-      </c>
-      <c r="C79" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-21T01:40Z</t>
-        </is>
-      </c>
-      <c r="D79" s="24" t="inlineStr">
-        <is>
-          <t>401816199</t>
-        </is>
-      </c>
-      <c r="E79" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F79" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="G79" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="H79" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I79" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J79" s="38" t="n"/>
-      <c r="K79" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L79" s="26" t="n">
-        <v>-125</v>
-      </c>
-      <c r="M79" s="39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N79" s="28" t="n">
-        <v>0.555556</v>
-      </c>
-      <c r="O79" s="28" t="n">
-        <v>0.597509</v>
-      </c>
-      <c r="P79" s="28" t="n"/>
-      <c r="Q79" s="28" t="n">
-        <v>0.041953</v>
-      </c>
-      <c r="R79" s="26" t="n">
-        <v>41</v>
-      </c>
-      <c r="S79" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T79" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U79" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V79" s="24" t="n"/>
-      <c r="W79" s="26" t="n"/>
-      <c r="X79" s="26" t="n"/>
-      <c r="Y79" s="38" t="n"/>
-      <c r="Z79" s="26" t="n"/>
-      <c r="AA79" s="28" t="n"/>
-      <c r="AB79" s="28" t="n"/>
-      <c r="AC79" s="40" t="n"/>
-      <c r="AD79" s="24" t="n"/>
-      <c r="AE79" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5550 (aec-mlb-cin-sea-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF79" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG79" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH79" s="24" t="n"/>
-      <c r="AI79" s="31" t="n"/>
-      <c r="AJ79" s="31" t="n"/>
-      <c r="AK79" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL79" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM79" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN79" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO79" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP79" s="24" t="inlineStr">
-        <is>
-          <t>mlb-cin</t>
-        </is>
-      </c>
-      <c r="AQ79" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="AR79" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="AS79" s="24" t="inlineStr">
-        <is>
-          <t>mlb-sea</t>
-        </is>
-      </c>
-      <c r="AT79" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="AU79" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="AV79" s="24" t="n"/>
-      <c r="AW79" s="24" t="n"/>
-      <c r="AX79" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY79" s="24" t="n"/>
-      <c r="AZ79" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA79" s="24" t="inlineStr">
-        <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
-        </is>
-      </c>
-      <c r="BB79" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC79" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD79" s="24" t="inlineStr">
-        <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
-        </is>
-      </c>
-      <c r="BE79" s="24" t="inlineStr">
-        <is>
-          <t>982d73638d70c45b</t>
-        </is>
-      </c>
-      <c r="BF79" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG79" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH79" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-19T17:17:46.849555Z</t>
-        </is>
-      </c>
-      <c r="BI79" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ79" s="38" t="n"/>
-      <c r="BK79" s="26" t="n">
-        <v>-125</v>
-      </c>
-      <c r="BL79" s="39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BM79" s="28" t="n">
-        <v>0.555556</v>
-      </c>
-      <c r="BN79" s="28" t="n">
-        <v>0.552239</v>
-      </c>
-      <c r="BO79" s="28" t="n"/>
-      <c r="BP79" s="38" t="n"/>
-      <c r="BQ79" s="39" t="n"/>
-      <c r="BR79" s="28" t="n"/>
-      <c r="BS79" s="28" t="n"/>
-      <c r="BT79" s="28" t="n"/>
-      <c r="BU79" s="38" t="n"/>
-      <c r="BV79" s="29" t="n"/>
-      <c r="BW79" s="24" t="n"/>
-      <c r="BX79" s="40" t="n"/>
-      <c r="BY79" s="39" t="n"/>
-      <c r="BZ79" s="24" t="n"/>
-      <c r="CA79" s="31" t="n"/>
-    </row>
-    <row r="80" ht="36" customHeight="1">
-      <c r="A80" s="24" t="inlineStr">
-        <is>
-          <t>c7a1577522fb4d37</t>
-        </is>
-      </c>
-      <c r="B80" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-19T17:18:24.670965Z</t>
-        </is>
-      </c>
-      <c r="C80" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-21T02:00Z</t>
-        </is>
-      </c>
-      <c r="D80" s="24" t="inlineStr">
-        <is>
-          <t>401816200</t>
-        </is>
-      </c>
-      <c r="E80" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F80" s="24" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="G80" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="H80" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I80" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J80" s="38" t="n"/>
-      <c r="K80" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L80" s="26" t="n">
-        <v>-102</v>
-      </c>
-      <c r="M80" s="39" t="n">
-        <v>1.980392</v>
-      </c>
-      <c r="N80" s="28" t="n">
-        <v>0.50495</v>
-      </c>
-      <c r="O80" s="28" t="n">
-        <v>0.541942</v>
-      </c>
-      <c r="P80" s="28" t="n"/>
-      <c r="Q80" s="28" t="n">
-        <v>0.036992</v>
-      </c>
-      <c r="R80" s="26" t="n">
-        <v>38</v>
-      </c>
-      <c r="S80" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T80" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U80" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V80" s="24" t="n"/>
-      <c r="W80" s="26" t="n"/>
-      <c r="X80" s="26" t="n"/>
-      <c r="Y80" s="38" t="n"/>
-      <c r="Z80" s="26" t="n"/>
-      <c r="AA80" s="28" t="n"/>
-      <c r="AB80" s="28" t="n"/>
-      <c r="AC80" s="40" t="n"/>
-      <c r="AD80" s="24" t="n"/>
-      <c r="AE80" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5050 (aec-mlb-stl-laa-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF80" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG80" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH80" s="24" t="n"/>
-      <c r="AI80" s="31" t="n"/>
-      <c r="AJ80" s="31" t="n"/>
-      <c r="AK80" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL80" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM80" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN80" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO80" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP80" s="24" t="inlineStr">
-        <is>
-          <t>mlb-stl</t>
-        </is>
-      </c>
-      <c r="AQ80" s="24" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="AR80" s="24" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="AS80" s="24" t="inlineStr">
-        <is>
-          <t>mlb-laa</t>
-        </is>
-      </c>
-      <c r="AT80" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="AU80" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="AV80" s="24" t="n"/>
-      <c r="AW80" s="24" t="n"/>
-      <c r="AX80" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY80" s="24" t="n"/>
-      <c r="AZ80" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA80" s="24" t="inlineStr">
-        <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
-        </is>
-      </c>
-      <c r="BB80" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC80" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD80" s="24" t="inlineStr">
-        <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
-        </is>
-      </c>
-      <c r="BE80" s="24" t="inlineStr">
-        <is>
-          <t>83613a19346b831e</t>
-        </is>
-      </c>
-      <c r="BF80" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG80" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH80" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-19T17:17:47.727344Z</t>
-        </is>
-      </c>
-      <c r="BI80" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ80" s="38" t="n"/>
-      <c r="BK80" s="26" t="n">
-        <v>-102</v>
-      </c>
-      <c r="BL80" s="39" t="n">
-        <v>1.980392</v>
-      </c>
-      <c r="BM80" s="28" t="n">
-        <v>0.50495</v>
-      </c>
-      <c r="BN80" s="28" t="n">
-        <v>0.502488</v>
-      </c>
-      <c r="BO80" s="28" t="n"/>
-      <c r="BP80" s="38" t="n"/>
-      <c r="BQ80" s="39" t="n"/>
-      <c r="BR80" s="28" t="n"/>
-      <c r="BS80" s="28" t="n"/>
-      <c r="BT80" s="28" t="n"/>
-      <c r="BU80" s="38" t="n"/>
-      <c r="BV80" s="29" t="n"/>
-      <c r="BW80" s="24" t="n"/>
-      <c r="BX80" s="40" t="n"/>
-      <c r="BY80" s="39" t="n"/>
-      <c r="BZ80" s="24" t="n"/>
-      <c r="CA80" s="31" t="n"/>
-    </row>
-    <row r="81" ht="36" customHeight="1">
-      <c r="A81" s="24" t="inlineStr">
-        <is>
-          <t>5ddbae8d805944cb</t>
-        </is>
-      </c>
-      <c r="B81" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-19T17:18:29.371620Z</t>
-        </is>
-      </c>
-      <c r="C81" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-21T00:00Z</t>
-        </is>
-      </c>
-      <c r="D81" s="24" t="inlineStr">
-        <is>
-          <t>401892393</t>
-        </is>
-      </c>
-      <c r="E81" s="24" t="inlineStr">
-        <is>
-          <t>WNBA</t>
-        </is>
-      </c>
-      <c r="F81" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="G81" s="24" t="inlineStr">
-        <is>
-          <t>Dallas Wings</t>
-        </is>
-      </c>
-      <c r="H81" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I81" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J81" s="38" t="n"/>
-      <c r="K81" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L81" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="M81" s="39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="N81" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="O81" s="28" t="n">
-        <v>0.6787840000000001</v>
-      </c>
-      <c r="P81" s="28" t="n"/>
-      <c r="Q81" s="28" t="n">
-        <v>0.198015</v>
-      </c>
-      <c r="R81" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S81" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T81" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U81" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V81" s="24" t="n"/>
-      <c r="W81" s="26" t="n"/>
-      <c r="X81" s="26" t="n"/>
-      <c r="Y81" s="38" t="n"/>
-      <c r="Z81" s="26" t="n"/>
-      <c r="AA81" s="28" t="n"/>
-      <c r="AB81" s="28" t="n"/>
-      <c r="AC81" s="40" t="n"/>
-      <c r="AD81" s="24" t="n"/>
-      <c r="AE81" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5000; executable ask 0.4800 (aec-wnba-ny-dal-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF81" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG81" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH81" s="24" t="n"/>
-      <c r="AI81" s="31" t="n"/>
-      <c r="AJ81" s="31" t="n"/>
-      <c r="AK81" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL81" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM81" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN81" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO81" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP81" s="24" t="inlineStr">
-        <is>
-          <t>wnba-nyl</t>
-        </is>
-      </c>
-      <c r="AQ81" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="AR81" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="AS81" s="24" t="inlineStr">
-        <is>
-          <t>wnba-dal</t>
-        </is>
-      </c>
-      <c r="AT81" s="24" t="inlineStr">
-        <is>
-          <t>Dallas Wings</t>
-        </is>
-      </c>
-      <c r="AU81" s="24" t="inlineStr">
-        <is>
-          <t>Dallas Wings</t>
-        </is>
-      </c>
-      <c r="AV81" s="24" t="n"/>
-      <c r="AW81" s="24" t="n"/>
-      <c r="AX81" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY81" s="24" t="n"/>
-      <c r="AZ81" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA81" s="24" t="inlineStr">
-        <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
-        </is>
-      </c>
-      <c r="BB81" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC81" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD81" s="24" t="inlineStr">
-        <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
-        </is>
-      </c>
-      <c r="BE81" s="24" t="inlineStr">
-        <is>
-          <t>1c6f45e72b2d1f80</t>
-        </is>
-      </c>
-      <c r="BF81" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG81" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH81" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-19T17:17:49.472621Z</t>
-        </is>
-      </c>
-      <c r="BI81" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ81" s="38" t="n"/>
-      <c r="BK81" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="BL81" s="39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BM81" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="BN81" s="28" t="n">
-        <v>0.475248</v>
-      </c>
-      <c r="BO81" s="28" t="n"/>
-      <c r="BP81" s="38" t="n"/>
-      <c r="BQ81" s="39" t="n"/>
-      <c r="BR81" s="28" t="n"/>
-      <c r="BS81" s="28" t="n"/>
-      <c r="BT81" s="28" t="n"/>
-      <c r="BU81" s="38" t="n"/>
-      <c r="BV81" s="29" t="n"/>
-      <c r="BW81" s="24" t="n"/>
-      <c r="BX81" s="40" t="n"/>
-      <c r="BY81" s="39" t="n"/>
-      <c r="BZ81" s="24" t="n"/>
-      <c r="CA81" s="31" t="n"/>
-    </row>
-    <row r="82" ht="36" customHeight="1">
-      <c r="A82" s="24" t="inlineStr">
-        <is>
-          <t>aaf1b4b6ac094ac8</t>
-        </is>
-      </c>
-      <c r="B82" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:58:34.322674Z</t>
-        </is>
-      </c>
-      <c r="C82" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T18:40:00-0400</t>
-        </is>
-      </c>
-      <c r="D82" s="24" t="inlineStr">
-        <is>
-          <t>401816188</t>
-        </is>
-      </c>
-      <c r="E82" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F82" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="G82" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="H82" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I82" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J82" s="38" t="n"/>
-      <c r="K82" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L82" s="26" t="n">
-        <v>111</v>
-      </c>
-      <c r="M82" s="39" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="N82" s="28" t="n">
-        <v>0.473934</v>
-      </c>
-      <c r="O82" s="28" t="n">
-        <v>0.5726869999999999</v>
-      </c>
-      <c r="P82" s="28" t="n"/>
-      <c r="Q82" s="28" t="n">
-        <v>0.09875299999999999</v>
-      </c>
-      <c r="R82" s="26" t="n">
-        <v>99</v>
-      </c>
-      <c r="S82" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T82" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U82" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V82" s="24" t="n"/>
-      <c r="W82" s="26" t="n"/>
-      <c r="X82" s="26" t="n"/>
-      <c r="Y82" s="38" t="n"/>
-      <c r="Z82" s="26" t="n"/>
-      <c r="AA82" s="28" t="n"/>
-      <c r="AB82" s="28" t="n"/>
-      <c r="AC82" s="40" t="n"/>
-      <c r="AD82" s="24" t="n"/>
-      <c r="AE82" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.4750 (aec-mlb-min-cle-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF82" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG82" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH82" s="24" t="n"/>
-      <c r="AI82" s="31" t="n"/>
-      <c r="AJ82" s="31" t="n"/>
-      <c r="AK82" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL82" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM82" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN82" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO82" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP82" s="24" t="inlineStr">
-        <is>
-          <t>mlb-min</t>
-        </is>
-      </c>
-      <c r="AQ82" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AR82" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AS82" s="24" t="inlineStr">
-        <is>
-          <t>mlb-cle</t>
-        </is>
-      </c>
-      <c r="AT82" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="AU82" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="AV82" s="24" t="n"/>
-      <c r="AW82" s="24" t="n"/>
-      <c r="AX82" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY82" s="24" t="n"/>
-      <c r="AZ82" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA82" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BB82" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC82" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD82" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BE82" s="24" t="inlineStr">
-        <is>
-          <t>2170ac399ced5417</t>
-        </is>
-      </c>
-      <c r="BF82" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG82" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH82" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:57:32.219947Z</t>
-        </is>
-      </c>
-      <c r="BI82" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ82" s="38" t="n"/>
-      <c r="BK82" s="26" t="n">
-        <v>111</v>
-      </c>
-      <c r="BL82" s="39" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BM82" s="28" t="n">
-        <v>0.473934</v>
-      </c>
-      <c r="BN82" s="28" t="n">
-        <v>0.472637</v>
-      </c>
-      <c r="BO82" s="28" t="n"/>
-      <c r="BP82" s="38" t="n"/>
-      <c r="BQ82" s="39" t="n"/>
-      <c r="BR82" s="28" t="n"/>
-      <c r="BS82" s="28" t="n"/>
-      <c r="BT82" s="28" t="n"/>
-      <c r="BU82" s="38" t="n"/>
-      <c r="BV82" s="29" t="n"/>
-      <c r="BW82" s="24" t="n"/>
-      <c r="BX82" s="40" t="n"/>
-      <c r="BY82" s="39" t="n"/>
-      <c r="BZ82" s="24" t="n"/>
-      <c r="CA82" s="31" t="n"/>
-    </row>
-    <row r="83" ht="36" customHeight="1">
-      <c r="A83" s="24" t="inlineStr">
-        <is>
-          <t>14a96af3a7654557</t>
-        </is>
-      </c>
-      <c r="B83" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:58:34.322674Z</t>
-        </is>
-      </c>
-      <c r="C83" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T19:05:00-0400</t>
-        </is>
-      </c>
-      <c r="D83" s="24" t="inlineStr">
-        <is>
-          <t>401816189</t>
-        </is>
-      </c>
-      <c r="E83" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F83" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="G83" s="24" t="inlineStr">
-        <is>
-          <t>New York Yankees</t>
-        </is>
-      </c>
-      <c r="H83" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I83" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J83" s="38" t="n"/>
-      <c r="K83" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L83" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="M83" s="39" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="N83" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="O83" s="28" t="n">
-        <v>0.578558</v>
-      </c>
-      <c r="P83" s="28" t="n"/>
-      <c r="Q83" s="28" t="n">
-        <v>0.059327</v>
-      </c>
-      <c r="R83" s="26" t="n">
-        <v>50</v>
-      </c>
-      <c r="S83" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T83" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U83" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V83" s="24" t="n"/>
-      <c r="W83" s="26" t="n"/>
-      <c r="X83" s="26" t="n"/>
-      <c r="Y83" s="38" t="n"/>
-      <c r="Z83" s="26" t="n"/>
-      <c r="AA83" s="28" t="n"/>
-      <c r="AB83" s="28" t="n"/>
-      <c r="AC83" s="40" t="n"/>
-      <c r="AD83" s="24" t="n"/>
-      <c r="AE83" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-pit-nyy-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF83" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG83" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH83" s="24" t="n"/>
-      <c r="AI83" s="31" t="n"/>
-      <c r="AJ83" s="31" t="n"/>
-      <c r="AK83" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL83" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM83" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN83" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO83" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP83" s="24" t="inlineStr">
-        <is>
-          <t>mlb-pit</t>
-        </is>
-      </c>
-      <c r="AQ83" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="AR83" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="AS83" s="24" t="inlineStr">
-        <is>
-          <t>mlb-nyy</t>
-        </is>
-      </c>
-      <c r="AT83" s="24" t="inlineStr">
-        <is>
-          <t>New York Yankees</t>
-        </is>
-      </c>
-      <c r="AU83" s="24" t="inlineStr">
-        <is>
-          <t>New York Yankees</t>
-        </is>
-      </c>
-      <c r="AV83" s="24" t="n"/>
-      <c r="AW83" s="24" t="n"/>
-      <c r="AX83" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY83" s="24" t="n"/>
-      <c r="AZ83" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA83" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BB83" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC83" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD83" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BE83" s="24" t="inlineStr">
-        <is>
-          <t>38ab7db5a3798f0c</t>
-        </is>
-      </c>
-      <c r="BF83" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG83" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH83" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:57:35.056972Z</t>
-        </is>
-      </c>
-      <c r="BI83" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ83" s="38" t="n"/>
-      <c r="BK83" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="BL83" s="39" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="BM83" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="BN83" s="28" t="n">
-        <v>0.517413</v>
-      </c>
-      <c r="BO83" s="28" t="n"/>
-      <c r="BP83" s="38" t="n"/>
-      <c r="BQ83" s="39" t="n"/>
-      <c r="BR83" s="28" t="n"/>
-      <c r="BS83" s="28" t="n"/>
-      <c r="BT83" s="28" t="n"/>
-      <c r="BU83" s="38" t="n"/>
-      <c r="BV83" s="29" t="n"/>
-      <c r="BW83" s="24" t="n"/>
-      <c r="BX83" s="40" t="n"/>
-      <c r="BY83" s="39" t="n"/>
-      <c r="BZ83" s="24" t="n"/>
-      <c r="CA83" s="31" t="n"/>
-    </row>
-    <row r="84" ht="36" customHeight="1">
-      <c r="A84" s="24" t="inlineStr">
-        <is>
-          <t>4859b2be84c249d7</t>
-        </is>
-      </c>
-      <c r="B84" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:58:34.322674Z</t>
-        </is>
-      </c>
-      <c r="C84" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T19:10:00-0400</t>
-        </is>
-      </c>
-      <c r="D84" s="24" t="inlineStr">
-        <is>
-          <t>401816186</t>
-        </is>
-      </c>
-      <c r="E84" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F84" s="24" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="G84" s="24" t="inlineStr">
-        <is>
-          <t>Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="H84" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I84" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J84" s="38" t="n"/>
-      <c r="K84" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L84" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="M84" s="39" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="N84" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="O84" s="28" t="n">
-        <v>0.565797</v>
-      </c>
-      <c r="P84" s="28" t="n"/>
-      <c r="Q84" s="28" t="n">
-        <v>-0.014035</v>
-      </c>
-      <c r="R84" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="S84" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T84" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U84" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V84" s="24" t="n"/>
-      <c r="W84" s="26" t="n"/>
-      <c r="X84" s="26" t="n"/>
-      <c r="Y84" s="38" t="n"/>
-      <c r="Z84" s="26" t="n"/>
-      <c r="AA84" s="28" t="n"/>
-      <c r="AB84" s="28" t="n"/>
-      <c r="AC84" s="40" t="n"/>
-      <c r="AD84" s="24" t="n"/>
-      <c r="AE84" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5800 (aec-mlb-bal-bos-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF84" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG84" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH84" s="24" t="n"/>
-      <c r="AI84" s="31" t="n"/>
-      <c r="AJ84" s="31" t="n"/>
-      <c r="AK84" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL84" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM84" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN84" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO84" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP84" s="24" t="inlineStr">
-        <is>
-          <t>mlb-bal</t>
-        </is>
-      </c>
-      <c r="AQ84" s="24" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="AR84" s="24" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="AS84" s="24" t="inlineStr">
-        <is>
-          <t>mlb-bos</t>
-        </is>
-      </c>
-      <c r="AT84" s="24" t="inlineStr">
-        <is>
-          <t>Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="AU84" s="24" t="inlineStr">
-        <is>
-          <t>Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="AV84" s="24" t="n"/>
-      <c r="AW84" s="24" t="n"/>
-      <c r="AX84" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY84" s="24" t="n"/>
-      <c r="AZ84" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA84" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BB84" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC84" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD84" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BE84" s="24" t="inlineStr">
-        <is>
-          <t>9fe2d27778a72dfe</t>
-        </is>
-      </c>
-      <c r="BF84" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG84" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH84" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:57:37.354484Z</t>
-        </is>
-      </c>
-      <c r="BI84" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ84" s="38" t="n"/>
-      <c r="BK84" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="BL84" s="39" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="BM84" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="BN84" s="28" t="n">
-        <v>0.577114</v>
-      </c>
-      <c r="BO84" s="28" t="n"/>
-      <c r="BP84" s="38" t="n"/>
-      <c r="BQ84" s="39" t="n"/>
-      <c r="BR84" s="28" t="n"/>
-      <c r="BS84" s="28" t="n"/>
-      <c r="BT84" s="28" t="n"/>
-      <c r="BU84" s="38" t="n"/>
-      <c r="BV84" s="29" t="n"/>
-      <c r="BW84" s="24" t="n"/>
-      <c r="BX84" s="40" t="n"/>
-      <c r="BY84" s="39" t="n"/>
-      <c r="BZ84" s="24" t="n"/>
-      <c r="CA84" s="31" t="n"/>
-    </row>
-    <row r="85" ht="36" customHeight="1">
-      <c r="A85" s="24" t="inlineStr">
-        <is>
-          <t>41f811ccac474792</t>
-        </is>
-      </c>
-      <c r="B85" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:58:34.322674Z</t>
-        </is>
-      </c>
-      <c r="C85" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T19:15:00-0400</t>
-        </is>
-      </c>
-      <c r="D85" s="24" t="inlineStr">
-        <is>
-          <t>401816190</t>
-        </is>
-      </c>
-      <c r="E85" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F85" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="G85" s="24" t="inlineStr">
-        <is>
-          <t>Atlanta Braves</t>
-        </is>
-      </c>
-      <c r="H85" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I85" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J85" s="38" t="n"/>
-      <c r="K85" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L85" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="M85" s="39" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="N85" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="O85" s="28" t="n">
-        <v>0.550915</v>
-      </c>
-      <c r="P85" s="28" t="n"/>
-      <c r="Q85" s="28" t="n">
-        <v>-0.0199</v>
-      </c>
-      <c r="R85" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="S85" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T85" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U85" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V85" s="24" t="n"/>
-      <c r="W85" s="26" t="n"/>
-      <c r="X85" s="26" t="n"/>
-      <c r="Y85" s="38" t="n"/>
-      <c r="Z85" s="26" t="n"/>
-      <c r="AA85" s="28" t="n"/>
-      <c r="AB85" s="28" t="n"/>
-      <c r="AC85" s="40" t="n"/>
-      <c r="AD85" s="24" t="n"/>
-      <c r="AE85" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5700 (aec-mlb-sd-atl-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF85" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG85" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH85" s="24" t="n"/>
-      <c r="AI85" s="31" t="n"/>
-      <c r="AJ85" s="31" t="n"/>
-      <c r="AK85" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL85" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM85" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN85" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO85" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP85" s="24" t="inlineStr">
-        <is>
-          <t>mlb-sd</t>
-        </is>
-      </c>
-      <c r="AQ85" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="AR85" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="AS85" s="24" t="inlineStr">
-        <is>
-          <t>mlb-atl</t>
-        </is>
-      </c>
-      <c r="AT85" s="24" t="inlineStr">
-        <is>
-          <t>Atlanta Braves</t>
-        </is>
-      </c>
-      <c r="AU85" s="24" t="inlineStr">
-        <is>
-          <t>Atlanta Braves</t>
-        </is>
-      </c>
-      <c r="AV85" s="24" t="n"/>
-      <c r="AW85" s="24" t="n"/>
-      <c r="AX85" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY85" s="24" t="n"/>
-      <c r="AZ85" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA85" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BB85" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC85" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD85" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BE85" s="24" t="inlineStr">
-        <is>
-          <t>f0b5eac7c97d1146</t>
-        </is>
-      </c>
-      <c r="BF85" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG85" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH85" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:57:40.909749Z</t>
-        </is>
-      </c>
-      <c r="BI85" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ85" s="38" t="n"/>
-      <c r="BK85" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="BL85" s="39" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="BM85" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="BN85" s="28" t="n">
-        <v>0.567164</v>
-      </c>
-      <c r="BO85" s="28" t="n"/>
-      <c r="BP85" s="38" t="n"/>
-      <c r="BQ85" s="39" t="n"/>
-      <c r="BR85" s="28" t="n"/>
-      <c r="BS85" s="28" t="n"/>
-      <c r="BT85" s="28" t="n"/>
-      <c r="BU85" s="38" t="n"/>
-      <c r="BV85" s="29" t="n"/>
-      <c r="BW85" s="24" t="n"/>
-      <c r="BX85" s="40" t="n"/>
-      <c r="BY85" s="39" t="n"/>
-      <c r="BZ85" s="24" t="n"/>
-      <c r="CA85" s="31" t="n"/>
-    </row>
-    <row r="86" ht="36" customHeight="1">
-      <c r="A86" s="24" t="inlineStr">
-        <is>
-          <t>e68eefc9610e4621</t>
-        </is>
-      </c>
-      <c r="B86" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:58:34.322674Z</t>
-        </is>
-      </c>
-      <c r="C86" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T19:40:00-0400</t>
-        </is>
-      </c>
-      <c r="D86" s="24" t="inlineStr">
-        <is>
-          <t>401816195</t>
-        </is>
-      </c>
-      <c r="E86" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F86" s="24" t="inlineStr">
-        <is>
-          <t>New York Mets</t>
-        </is>
-      </c>
-      <c r="G86" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="H86" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I86" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J86" s="38" t="n"/>
-      <c r="K86" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L86" s="26" t="n">
-        <v>-199</v>
-      </c>
-      <c r="M86" s="39" t="n">
-        <v>1.502513</v>
-      </c>
-      <c r="N86" s="28" t="n">
-        <v>0.665552</v>
-      </c>
-      <c r="O86" s="28" t="n">
-        <v>0.640995</v>
-      </c>
-      <c r="P86" s="28" t="n"/>
-      <c r="Q86" s="28" t="n">
-        <v>-0.024557</v>
-      </c>
-      <c r="R86" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="S86" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T86" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U86" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V86" s="24" t="n"/>
-      <c r="W86" s="26" t="n"/>
-      <c r="X86" s="26" t="n"/>
-      <c r="Y86" s="38" t="n"/>
-      <c r="Z86" s="26" t="n"/>
-      <c r="AA86" s="28" t="n"/>
-      <c r="AB86" s="28" t="n"/>
-      <c r="AC86" s="40" t="n"/>
-      <c r="AD86" s="24" t="n"/>
-      <c r="AE86" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.6650 (aec-mlb-nym-mil-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF86" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG86" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH86" s="24" t="n"/>
-      <c r="AI86" s="31" t="n"/>
-      <c r="AJ86" s="31" t="n"/>
-      <c r="AK86" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL86" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM86" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN86" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO86" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP86" s="24" t="inlineStr">
-        <is>
-          <t>mlb-nym</t>
-        </is>
-      </c>
-      <c r="AQ86" s="24" t="inlineStr">
-        <is>
-          <t>New York Mets</t>
-        </is>
-      </c>
-      <c r="AR86" s="24" t="inlineStr">
-        <is>
-          <t>New York Mets</t>
-        </is>
-      </c>
-      <c r="AS86" s="24" t="inlineStr">
-        <is>
-          <t>mlb-mil</t>
-        </is>
-      </c>
-      <c r="AT86" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="AU86" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="AV86" s="24" t="n"/>
-      <c r="AW86" s="24" t="n"/>
-      <c r="AX86" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY86" s="24" t="n"/>
-      <c r="AZ86" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA86" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BB86" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC86" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD86" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BE86" s="24" t="inlineStr">
-        <is>
-          <t>6d5f3f5e8f75cb2b</t>
-        </is>
-      </c>
-      <c r="BF86" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG86" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH86" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:57:42.879792Z</t>
-        </is>
-      </c>
-      <c r="BI86" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ86" s="38" t="n"/>
-      <c r="BK86" s="26" t="n">
-        <v>-199</v>
-      </c>
-      <c r="BL86" s="39" t="n">
-        <v>1.502513</v>
-      </c>
-      <c r="BM86" s="28" t="n">
-        <v>0.665552</v>
-      </c>
-      <c r="BN86" s="28" t="n">
-        <v>0.6616919999999999</v>
-      </c>
-      <c r="BO86" s="28" t="n"/>
-      <c r="BP86" s="38" t="n"/>
-      <c r="BQ86" s="39" t="n"/>
-      <c r="BR86" s="28" t="n"/>
-      <c r="BS86" s="28" t="n"/>
-      <c r="BT86" s="28" t="n"/>
-      <c r="BU86" s="38" t="n"/>
-      <c r="BV86" s="29" t="n"/>
-      <c r="BW86" s="24" t="n"/>
-      <c r="BX86" s="40" t="n"/>
-      <c r="BY86" s="39" t="n"/>
-      <c r="BZ86" s="24" t="n"/>
-      <c r="CA86" s="31" t="n"/>
-    </row>
-    <row r="87" ht="36" customHeight="1">
-      <c r="A87" s="24" t="inlineStr">
-        <is>
-          <t>8db3a8d8a90f4145</t>
-        </is>
-      </c>
-      <c r="B87" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:58:34.322674Z</t>
-        </is>
-      </c>
-      <c r="C87" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T20:05:00-0400</t>
-        </is>
-      </c>
-      <c r="D87" s="24" t="inlineStr">
-        <is>
-          <t>401816193</t>
-        </is>
-      </c>
-      <c r="E87" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F87" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="G87" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="H87" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I87" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J87" s="38" t="n"/>
-      <c r="K87" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L87" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="M87" s="39" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="N87" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="O87" s="28" t="n">
-        <v>0.566967</v>
-      </c>
-      <c r="P87" s="28" t="n"/>
-      <c r="Q87" s="28" t="n">
-        <v>0.047736</v>
-      </c>
-      <c r="R87" s="26" t="n">
-        <v>44</v>
-      </c>
-      <c r="S87" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T87" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U87" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V87" s="24" t="n"/>
-      <c r="W87" s="26" t="n"/>
-      <c r="X87" s="26" t="n"/>
-      <c r="Y87" s="38" t="n"/>
-      <c r="Z87" s="26" t="n"/>
-      <c r="AA87" s="28" t="n"/>
-      <c r="AB87" s="28" t="n"/>
-      <c r="AC87" s="40" t="n"/>
-      <c r="AD87" s="24" t="n"/>
-      <c r="AE87" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-det-chc-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF87" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG87" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH87" s="24" t="n"/>
-      <c r="AI87" s="31" t="n"/>
-      <c r="AJ87" s="31" t="n"/>
-      <c r="AK87" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL87" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM87" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN87" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO87" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP87" s="24" t="inlineStr">
-        <is>
-          <t>mlb-det</t>
-        </is>
-      </c>
-      <c r="AQ87" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="AR87" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="AS87" s="24" t="inlineStr">
-        <is>
-          <t>mlb-chc</t>
-        </is>
-      </c>
-      <c r="AT87" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AU87" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AV87" s="24" t="n"/>
-      <c r="AW87" s="24" t="n"/>
-      <c r="AX87" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY87" s="24" t="n"/>
-      <c r="AZ87" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA87" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BB87" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC87" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD87" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BE87" s="24" t="inlineStr">
-        <is>
-          <t>b84afb2c70e14d93</t>
-        </is>
-      </c>
-      <c r="BF87" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG87" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH87" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:57:46.871986Z</t>
-        </is>
-      </c>
-      <c r="BI87" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ87" s="38" t="n"/>
-      <c r="BK87" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="BL87" s="39" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="BM87" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="BN87" s="28" t="n">
-        <v>0.517413</v>
-      </c>
-      <c r="BO87" s="28" t="n"/>
-      <c r="BP87" s="38" t="n"/>
-      <c r="BQ87" s="39" t="n"/>
-      <c r="BR87" s="28" t="n"/>
-      <c r="BS87" s="28" t="n"/>
-      <c r="BT87" s="28" t="n"/>
-      <c r="BU87" s="38" t="n"/>
-      <c r="BV87" s="29" t="n"/>
-      <c r="BW87" s="24" t="n"/>
-      <c r="BX87" s="40" t="n"/>
-      <c r="BY87" s="39" t="n"/>
-      <c r="BZ87" s="24" t="n"/>
-      <c r="CA87" s="31" t="n"/>
-    </row>
-    <row r="88" ht="36" customHeight="1">
-      <c r="A88" s="24" t="inlineStr">
-        <is>
-          <t>63c8de42843a46c9</t>
-        </is>
-      </c>
-      <c r="B88" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:58:34.322674Z</t>
-        </is>
-      </c>
-      <c r="C88" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T20:40:00-0400</t>
-        </is>
-      </c>
-      <c r="D88" s="24" t="inlineStr">
-        <is>
-          <t>401816197</t>
-        </is>
-      </c>
-      <c r="E88" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F88" s="24" t="inlineStr">
-        <is>
-          <t>Washington Nationals</t>
-        </is>
-      </c>
-      <c r="G88" s="24" t="inlineStr">
-        <is>
-          <t>Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="H88" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I88" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J88" s="38" t="n"/>
-      <c r="K88" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L88" s="26" t="n">
-        <v>-117</v>
-      </c>
-      <c r="M88" s="39" t="n">
-        <v>1.854701</v>
-      </c>
-      <c r="N88" s="28" t="n">
-        <v>0.539171</v>
-      </c>
-      <c r="O88" s="28" t="n">
-        <v>0.5563709999999999</v>
-      </c>
-      <c r="P88" s="28" t="n"/>
-      <c r="Q88" s="28" t="n">
-        <v>0.0172</v>
-      </c>
-      <c r="R88" s="26" t="n">
-        <v>29</v>
-      </c>
-      <c r="S88" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T88" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U88" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V88" s="24" t="n"/>
-      <c r="W88" s="26" t="n"/>
-      <c r="X88" s="26" t="n"/>
-      <c r="Y88" s="38" t="n"/>
-      <c r="Z88" s="26" t="n"/>
-      <c r="AA88" s="28" t="n"/>
-      <c r="AB88" s="28" t="n"/>
-      <c r="AC88" s="40" t="n"/>
-      <c r="AD88" s="24" t="n"/>
-      <c r="AE88" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5400 (aec-mlb-wsh-col-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF88" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG88" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH88" s="24" t="n"/>
-      <c r="AI88" s="31" t="n"/>
-      <c r="AJ88" s="31" t="n"/>
-      <c r="AK88" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL88" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM88" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN88" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO88" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP88" s="24" t="inlineStr">
-        <is>
-          <t>mlb-wsh</t>
-        </is>
-      </c>
-      <c r="AQ88" s="24" t="inlineStr">
-        <is>
-          <t>Washington Nationals</t>
-        </is>
-      </c>
-      <c r="AR88" s="24" t="inlineStr">
-        <is>
-          <t>Washington Nationals</t>
-        </is>
-      </c>
-      <c r="AS88" s="24" t="inlineStr">
-        <is>
-          <t>mlb-col</t>
-        </is>
-      </c>
-      <c r="AT88" s="24" t="inlineStr">
-        <is>
-          <t>Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="AU88" s="24" t="inlineStr">
-        <is>
-          <t>Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="AV88" s="24" t="n"/>
-      <c r="AW88" s="24" t="n"/>
-      <c r="AX88" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY88" s="24" t="n"/>
-      <c r="AZ88" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA88" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BB88" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC88" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD88" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BE88" s="24" t="inlineStr">
-        <is>
-          <t>a2f336c1cee8c92e</t>
-        </is>
-      </c>
-      <c r="BF88" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG88" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH88" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:57:49.897394Z</t>
-        </is>
-      </c>
-      <c r="BI88" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ88" s="38" t="n"/>
-      <c r="BK88" s="26" t="n">
-        <v>-117</v>
-      </c>
-      <c r="BL88" s="39" t="n">
-        <v>1.854701</v>
-      </c>
-      <c r="BM88" s="28" t="n">
-        <v>0.539171</v>
-      </c>
-      <c r="BN88" s="28" t="n">
-        <v>0.537313</v>
-      </c>
-      <c r="BO88" s="28" t="n"/>
-      <c r="BP88" s="38" t="n"/>
-      <c r="BQ88" s="39" t="n"/>
-      <c r="BR88" s="28" t="n"/>
-      <c r="BS88" s="28" t="n"/>
-      <c r="BT88" s="28" t="n"/>
-      <c r="BU88" s="38" t="n"/>
-      <c r="BV88" s="29" t="n"/>
-      <c r="BW88" s="24" t="n"/>
-      <c r="BX88" s="40" t="n"/>
-      <c r="BY88" s="39" t="n"/>
-      <c r="BZ88" s="24" t="n"/>
-      <c r="CA88" s="31" t="n"/>
-    </row>
-    <row r="89" ht="36" customHeight="1">
-      <c r="A89" s="24" t="inlineStr">
-        <is>
-          <t>21876b0ffe164cd7</t>
-        </is>
-      </c>
-      <c r="B89" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:58:34.322674Z</t>
-        </is>
-      </c>
-      <c r="C89" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T21:40:00-0400</t>
-        </is>
-      </c>
-      <c r="D89" s="24" t="inlineStr">
-        <is>
-          <t>401816198</t>
-        </is>
-      </c>
-      <c r="E89" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F89" s="24" t="inlineStr">
-        <is>
-          <t>Athletics</t>
-        </is>
-      </c>
-      <c r="G89" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="H89" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I89" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J89" s="38" t="n"/>
-      <c r="K89" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L89" s="26" t="n">
-        <v>-147</v>
-      </c>
-      <c r="M89" s="39" t="n">
-        <v>1.680272</v>
-      </c>
-      <c r="N89" s="28" t="n">
-        <v>0.5951419999999999</v>
-      </c>
-      <c r="O89" s="28" t="n">
-        <v>0.58189</v>
-      </c>
-      <c r="P89" s="28" t="n"/>
-      <c r="Q89" s="28" t="n">
-        <v>-0.013252</v>
-      </c>
-      <c r="R89" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="S89" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T89" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U89" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V89" s="24" t="n"/>
-      <c r="W89" s="26" t="n"/>
-      <c r="X89" s="26" t="n"/>
-      <c r="Y89" s="38" t="n"/>
-      <c r="Z89" s="26" t="n"/>
-      <c r="AA89" s="28" t="n"/>
-      <c r="AB89" s="28" t="n"/>
-      <c r="AC89" s="40" t="n"/>
-      <c r="AD89" s="24" t="n"/>
-      <c r="AE89" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5950 (aec-mlb-ath-az-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF89" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG89" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH89" s="24" t="n"/>
-      <c r="AI89" s="31" t="n"/>
-      <c r="AJ89" s="31" t="n"/>
-      <c r="AK89" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL89" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM89" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN89" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO89" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP89" s="24" t="inlineStr">
-        <is>
-          <t>mlb-ath</t>
-        </is>
-      </c>
-      <c r="AQ89" s="24" t="inlineStr">
-        <is>
-          <t>Athletics</t>
-        </is>
-      </c>
-      <c r="AR89" s="24" t="inlineStr">
-        <is>
-          <t>Athletics</t>
-        </is>
-      </c>
-      <c r="AS89" s="24" t="inlineStr">
-        <is>
-          <t>mlb-ari</t>
-        </is>
-      </c>
-      <c r="AT89" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="AU89" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="AV89" s="24" t="n"/>
-      <c r="AW89" s="24" t="n"/>
-      <c r="AX89" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY89" s="24" t="n"/>
-      <c r="AZ89" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA89" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BB89" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC89" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD89" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BE89" s="24" t="inlineStr">
-        <is>
-          <t>7b682aa5da86e2a4</t>
-        </is>
-      </c>
-      <c r="BF89" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG89" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH89" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:57:51.339273Z</t>
-        </is>
-      </c>
-      <c r="BI89" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ89" s="38" t="n"/>
-      <c r="BK89" s="26" t="n">
-        <v>-147</v>
-      </c>
-      <c r="BL89" s="39" t="n">
-        <v>1.680272</v>
-      </c>
-      <c r="BM89" s="28" t="n">
-        <v>0.5951419999999999</v>
-      </c>
-      <c r="BN89" s="28" t="n">
-        <v>0.59204</v>
-      </c>
-      <c r="BO89" s="28" t="n"/>
-      <c r="BP89" s="38" t="n"/>
-      <c r="BQ89" s="39" t="n"/>
-      <c r="BR89" s="28" t="n"/>
-      <c r="BS89" s="28" t="n"/>
-      <c r="BT89" s="28" t="n"/>
-      <c r="BU89" s="38" t="n"/>
-      <c r="BV89" s="29" t="n"/>
-      <c r="BW89" s="24" t="n"/>
-      <c r="BX89" s="40" t="n"/>
-      <c r="BY89" s="39" t="n"/>
-      <c r="BZ89" s="24" t="n"/>
-      <c r="CA89" s="31" t="n"/>
-    </row>
-    <row r="90" ht="36" customHeight="1">
-      <c r="A90" s="24" t="inlineStr">
-        <is>
-          <t>7df4ed647cfb43ef</t>
-        </is>
-      </c>
-      <c r="B90" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:58:34.322674Z</t>
-        </is>
-      </c>
-      <c r="C90" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T21:40:00-0400</t>
-        </is>
-      </c>
-      <c r="D90" s="24" t="inlineStr">
-        <is>
-          <t>401816199</t>
-        </is>
-      </c>
-      <c r="E90" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F90" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="G90" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="H90" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I90" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J90" s="38" t="n"/>
-      <c r="K90" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L90" s="26" t="n">
-        <v>-141</v>
-      </c>
-      <c r="M90" s="39" t="n">
-        <v>1.70922</v>
-      </c>
-      <c r="N90" s="28" t="n">
-        <v>0.585062</v>
-      </c>
-      <c r="O90" s="28" t="n">
-        <v>0.592852</v>
-      </c>
-      <c r="P90" s="28" t="n"/>
-      <c r="Q90" s="28" t="n">
-        <v>0.00779</v>
-      </c>
-      <c r="R90" s="26" t="n">
-        <v>24</v>
-      </c>
-      <c r="S90" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T90" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U90" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V90" s="24" t="n"/>
-      <c r="W90" s="26" t="n"/>
-      <c r="X90" s="26" t="n"/>
-      <c r="Y90" s="38" t="n"/>
-      <c r="Z90" s="26" t="n"/>
-      <c r="AA90" s="28" t="n"/>
-      <c r="AB90" s="28" t="n"/>
-      <c r="AC90" s="40" t="n"/>
-      <c r="AD90" s="24" t="n"/>
-      <c r="AE90" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5850 (aec-mlb-cin-sea-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF90" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG90" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH90" s="24" t="n"/>
-      <c r="AI90" s="31" t="n"/>
-      <c r="AJ90" s="31" t="n"/>
-      <c r="AK90" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL90" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM90" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN90" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO90" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP90" s="24" t="inlineStr">
-        <is>
-          <t>mlb-cin</t>
-        </is>
-      </c>
-      <c r="AQ90" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="AR90" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="AS90" s="24" t="inlineStr">
-        <is>
-          <t>mlb-sea</t>
-        </is>
-      </c>
-      <c r="AT90" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="AU90" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="AV90" s="24" t="n"/>
-      <c r="AW90" s="24" t="n"/>
-      <c r="AX90" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY90" s="24" t="n"/>
-      <c r="AZ90" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA90" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BB90" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC90" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD90" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BE90" s="24" t="inlineStr">
-        <is>
-          <t>af7ccafcacf69681</t>
-        </is>
-      </c>
-      <c r="BF90" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG90" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH90" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:57:52.831217Z</t>
-        </is>
-      </c>
-      <c r="BI90" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ90" s="38" t="n"/>
-      <c r="BK90" s="26" t="n">
-        <v>-141</v>
-      </c>
-      <c r="BL90" s="39" t="n">
-        <v>1.70922</v>
-      </c>
-      <c r="BM90" s="28" t="n">
-        <v>0.585062</v>
-      </c>
-      <c r="BN90" s="28" t="n">
-        <v>0.58209</v>
-      </c>
-      <c r="BO90" s="28" t="n"/>
-      <c r="BP90" s="38" t="n"/>
-      <c r="BQ90" s="39" t="n"/>
-      <c r="BR90" s="28" t="n"/>
-      <c r="BS90" s="28" t="n"/>
-      <c r="BT90" s="28" t="n"/>
-      <c r="BU90" s="38" t="n"/>
-      <c r="BV90" s="29" t="n"/>
-      <c r="BW90" s="24" t="n"/>
-      <c r="BX90" s="40" t="n"/>
-      <c r="BY90" s="39" t="n"/>
-      <c r="BZ90" s="24" t="n"/>
-      <c r="CA90" s="31" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -327,8 +327,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA74" headerRowCount="1">
-  <autoFilter ref="A1:CA74"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA80" headerRowCount="1">
+  <autoFilter ref="A1:CA80"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -765,19 +765,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$74)</f>
+        <f>COUNTA('Picks'!$A$2:$A$80)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$74,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$80,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$74,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$80,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")+COUNTIFS('Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"win")+COUNTIFS('Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -806,19 +806,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$74,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$80,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$80,"&gt;0",'Picks'!$V$2:$V$80,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$80,"&gt;0",'Picks'!$V$2:$V$80,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="32">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"win")/(COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"win")+COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$80,"&gt;0",'Picks'!$V$2:$V$80,"win")/(COUNTIFS('Picks'!$BX$2:$BX$80,"&gt;0",'Picks'!$V$2:$V$80,"win")+COUNTIFS('Picks'!$BX$2:$BX$80,"&gt;0",'Picks'!$V$2:$V$80,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="32">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$74)/SUM('Picks'!$BX$2:$BX$74),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$80)/SUM('Picks'!$BX$2:$BX$80),0)</f>
         <v/>
       </c>
     </row>
@@ -847,19 +847,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="33">
-        <f>SUM('Picks'!$BY$2:$BY$74)</f>
+        <f>SUM('Picks'!$BY$2:$BY$80)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$74,"&lt;&gt;",'Picks'!$AB$2:$AB$74),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$80,"&lt;&gt;",'Picks'!$AB$2:$AB$80),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$74,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$74,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$80,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$80,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="33">
-        <f>SUMIFS('Picks'!$AC$2:$AC$74,'Picks'!$AM$2:$AM$74,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$80,'Picks'!$AM$2:$AM$80,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -915,15 +915,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$80,$A14,'Picks'!$U$2:$U$80,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$80,$A14,'Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$80,$A14,'Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="34">
@@ -931,11 +931,11 @@
         <v/>
       </c>
       <c r="F14" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$74,'Picks'!$H$2:$H$74,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$80,'Picks'!$H$2:$H$80,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$74,'Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$80,'Picks'!$H$2:$H$80,$A14,'Picks'!$U$2:$U$80,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -946,15 +946,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$80,$A15,'Picks'!$U$2:$U$80,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$80,$A15,'Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$80,$A15,'Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="36">
@@ -962,11 +962,11 @@
         <v/>
       </c>
       <c r="F15" s="37">
-        <f>SUMIFS('Picks'!$BY$2:$BY$74,'Picks'!$H$2:$H$74,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$80,'Picks'!$H$2:$H$80,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$74,'Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$80,'Picks'!$H$2:$H$80,$A15,'Picks'!$U$2:$U$80,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -977,15 +977,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$80,$A16,'Picks'!$U$2:$U$80,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$80,$A16,'Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$80,$A16,'Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="34">
@@ -993,11 +993,11 @@
         <v/>
       </c>
       <c r="F16" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$74,'Picks'!$H$2:$H$74,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$80,'Picks'!$H$2:$H$80,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$74,'Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$80,'Picks'!$H$2:$H$80,$A16,'Picks'!$U$2:$U$80,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA74"/>
+  <dimension ref="A1:CA80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15735,12 +15735,12 @@
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>bbf4c446926f4a96</t>
+          <t>e00add3bfe2446db</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:22:41.782177Z</t>
+          <t>2026-07-20T15:38:55.511243Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
@@ -15946,7 +15946,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:32.219947Z</t>
+          <t>2026-07-20T15:33:34.083345Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -15965,7 +15965,7 @@
         <v>0.473934</v>
       </c>
       <c r="BN62" s="28" t="n">
-        <v>0.472637</v>
+        <v>0.470297</v>
       </c>
       <c r="BO62" s="28" t="n"/>
       <c r="BP62" s="38" t="n"/>
@@ -15984,22 +15984,22 @@
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>1506b66a3b294539</t>
+          <t>7a7171ebb07c44d9</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:22:41.782177Z</t>
+          <t>2026-07-20T15:38:55.511243Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:05:00-0400</t>
+          <t>2026-07-20T19:00:00-0400</t>
         </is>
       </c>
       <c r="D63" s="24" t="inlineStr">
         <is>
-          <t>401816189</t>
+          <t>401816187</t>
         </is>
       </c>
       <c r="E63" s="24" t="inlineStr">
@@ -16009,12 +16009,12 @@
       </c>
       <c r="F63" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="G63" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="H63" s="24" t="inlineStr">
@@ -16024,7 +16024,7 @@
       </c>
       <c r="I63" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J63" s="38" t="n"/>
@@ -16034,26 +16034,26 @@
         </is>
       </c>
       <c r="L63" s="26" t="n">
-        <v>-108</v>
+        <v>125</v>
       </c>
       <c r="M63" s="39" t="n">
-        <v>1.925926</v>
+        <v>2.25</v>
       </c>
       <c r="N63" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.444444</v>
       </c>
       <c r="O63" s="28" t="n">
-        <v>0.578558</v>
+        <v>0.513332</v>
       </c>
       <c r="P63" s="28" t="n"/>
       <c r="Q63" s="28" t="n">
-        <v>0.059327</v>
+        <v>0.068888</v>
       </c>
       <c r="R63" s="26" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="S63" s="29" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="T63" s="24" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
       <c r="AD63" s="24" t="n"/>
       <c r="AE63" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-pit-nyy-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.4450 (aec-mlb-lad-phi-2026-07-20).</t>
         </is>
       </c>
       <c r="AF63" s="31" t="inlineStr">
@@ -16117,32 +16117,32 @@
       </c>
       <c r="AP63" s="24" t="inlineStr">
         <is>
-          <t>mlb-pit</t>
+          <t>mlb-lad</t>
         </is>
       </c>
       <c r="AQ63" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AR63" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AS63" s="24" t="inlineStr">
         <is>
-          <t>mlb-nyy</t>
+          <t>mlb-phi</t>
         </is>
       </c>
       <c r="AT63" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AU63" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AV63" s="24" t="n"/>
@@ -16180,7 +16180,7 @@
       </c>
       <c r="BE63" s="24" t="inlineStr">
         <is>
-          <t>38ab7db5a3798f0c</t>
+          <t>bac520e15b938e92</t>
         </is>
       </c>
       <c r="BF63" s="24" t="inlineStr">
@@ -16195,7 +16195,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:35.056972Z</t>
+          <t>2026-07-20T15:33:40.881321Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -16205,16 +16205,16 @@
       </c>
       <c r="BJ63" s="38" t="n"/>
       <c r="BK63" s="26" t="n">
-        <v>-108</v>
+        <v>125</v>
       </c>
       <c r="BL63" s="39" t="n">
-        <v>1.925926</v>
+        <v>2.25</v>
       </c>
       <c r="BM63" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.444444</v>
       </c>
       <c r="BN63" s="28" t="n">
-        <v>0.517413</v>
+        <v>0.442786</v>
       </c>
       <c r="BO63" s="28" t="n"/>
       <c r="BP63" s="38" t="n"/>
@@ -16233,22 +16233,22 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>540e168c7d8c4ba0</t>
+          <t>0e08e82b6c5e41de</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:22:41.782177Z</t>
+          <t>2026-07-20T15:38:55.511243Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:10:00-0400</t>
+          <t>2026-07-20T19:05:00-0400</t>
         </is>
       </c>
       <c r="D64" s="24" t="inlineStr">
         <is>
-          <t>401816186</t>
+          <t>401816189</t>
         </is>
       </c>
       <c r="E64" s="24" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="G64" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr">
@@ -16283,23 +16283,23 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>-138</v>
+        <v>-108</v>
       </c>
       <c r="M64" s="39" t="n">
-        <v>1.724638</v>
+        <v>1.925926</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.519231</v>
       </c>
       <c r="O64" s="28" t="n">
-        <v>0.565797</v>
+        <v>0.578558</v>
       </c>
       <c r="P64" s="28" t="n"/>
       <c r="Q64" s="28" t="n">
-        <v>-0.014035</v>
+        <v>0.059327</v>
       </c>
       <c r="R64" s="26" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="S64" s="29" t="n">
         <v>1.25</v>
@@ -16325,7 +16325,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5800 (aec-mlb-bal-bos-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-pit-nyy-2026-07-20).</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -16366,32 +16366,32 @@
       </c>
       <c r="AP64" s="24" t="inlineStr">
         <is>
-          <t>mlb-bal</t>
+          <t>mlb-pit</t>
         </is>
       </c>
       <c r="AQ64" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AR64" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AS64" s="24" t="inlineStr">
         <is>
-          <t>mlb-bos</t>
+          <t>mlb-nyy</t>
         </is>
       </c>
       <c r="AT64" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AU64" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AV64" s="24" t="n"/>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="BE64" s="24" t="inlineStr">
         <is>
-          <t>9fe2d27778a72dfe</t>
+          <t>38ab7db5a3798f0c</t>
         </is>
       </c>
       <c r="BF64" s="24" t="inlineStr">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:37.354484Z</t>
+          <t>2026-07-20T15:33:36.050461Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -16454,16 +16454,16 @@
       </c>
       <c r="BJ64" s="38" t="n"/>
       <c r="BK64" s="26" t="n">
-        <v>-138</v>
+        <v>-108</v>
       </c>
       <c r="BL64" s="39" t="n">
-        <v>1.724638</v>
+        <v>1.925926</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.519231</v>
       </c>
       <c r="BN64" s="28" t="n">
-        <v>0.577114</v>
+        <v>0.517413</v>
       </c>
       <c r="BO64" s="28" t="n"/>
       <c r="BP64" s="38" t="n"/>
@@ -16482,22 +16482,22 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>f4dc16b93ff64092</t>
+          <t>764b59e974874df1</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:22:41.782177Z</t>
+          <t>2026-07-20T15:38:55.511243Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:15:00-0400</t>
+          <t>2026-07-20T19:07:00-0400</t>
         </is>
       </c>
       <c r="D65" s="24" t="inlineStr">
         <is>
-          <t>401816190</t>
+          <t>401816191</t>
         </is>
       </c>
       <c r="E65" s="24" t="inlineStr">
@@ -16507,12 +16507,12 @@
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="G65" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="H65" s="24" t="inlineStr">
@@ -16532,26 +16532,26 @@
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>-133</v>
+        <v>-144</v>
       </c>
       <c r="M65" s="39" t="n">
-        <v>1.75188</v>
+        <v>1.694444</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.590164</v>
       </c>
       <c r="O65" s="28" t="n">
-        <v>0.550915</v>
+        <v>0.530206</v>
       </c>
       <c r="P65" s="28" t="n"/>
       <c r="Q65" s="28" t="n">
-        <v>-0.0199</v>
+        <v>-0.059958</v>
       </c>
       <c r="R65" s="26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S65" s="29" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="T65" s="24" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5700 (aec-mlb-sd-atl-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5900 (aec-mlb-tb-tor-2026-07-20).</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -16615,32 +16615,32 @@
       </c>
       <c r="AP65" s="24" t="inlineStr">
         <is>
-          <t>mlb-sd</t>
+          <t>mlb-tb</t>
         </is>
       </c>
       <c r="AQ65" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="AR65" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="AS65" s="24" t="inlineStr">
         <is>
-          <t>mlb-atl</t>
+          <t>mlb-tor</t>
         </is>
       </c>
       <c r="AT65" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="AU65" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="AV65" s="24" t="n"/>
@@ -16678,7 +16678,7 @@
       </c>
       <c r="BE65" s="24" t="inlineStr">
         <is>
-          <t>f0b5eac7c97d1146</t>
+          <t>78559912fe10ab9f</t>
         </is>
       </c>
       <c r="BF65" s="24" t="inlineStr">
@@ -16693,7 +16693,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:40.909749Z</t>
+          <t>2026-07-20T15:33:37.942740Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -16703,16 +16703,16 @@
       </c>
       <c r="BJ65" s="38" t="n"/>
       <c r="BK65" s="26" t="n">
-        <v>-133</v>
+        <v>-144</v>
       </c>
       <c r="BL65" s="39" t="n">
-        <v>1.75188</v>
+        <v>1.694444</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.590164</v>
       </c>
       <c r="BN65" s="28" t="n">
-        <v>0.567164</v>
+        <v>0.5870649999999999</v>
       </c>
       <c r="BO65" s="28" t="n"/>
       <c r="BP65" s="38" t="n"/>
@@ -16731,22 +16731,22 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>c08b803127a54cd0</t>
+          <t>03845491b26c4e30</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:22:41.782177Z</t>
+          <t>2026-07-20T15:38:55.511243Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:40:00-0400</t>
+          <t>2026-07-20T19:10:00-0400</t>
         </is>
       </c>
       <c r="D66" s="24" t="inlineStr">
         <is>
-          <t>401816195</t>
+          <t>401816186</t>
         </is>
       </c>
       <c r="E66" s="24" t="inlineStr">
@@ -16756,12 +16756,12 @@
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="G66" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="H66" s="24" t="inlineStr">
@@ -16781,26 +16781,26 @@
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>-199</v>
+        <v>-138</v>
       </c>
       <c r="M66" s="39" t="n">
-        <v>1.502513</v>
+        <v>1.724638</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.665552</v>
+        <v>0.579832</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.640995</v>
+        <v>0.565797</v>
       </c>
       <c r="P66" s="28" t="n"/>
       <c r="Q66" s="28" t="n">
-        <v>-0.024557</v>
+        <v>-0.014035</v>
       </c>
       <c r="R66" s="26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="S66" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T66" s="24" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.6650 (aec-mlb-nym-mil-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5800 (aec-mlb-bal-bos-2026-07-20).</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -16864,32 +16864,32 @@
       </c>
       <c r="AP66" s="24" t="inlineStr">
         <is>
-          <t>mlb-nym</t>
+          <t>mlb-bal</t>
         </is>
       </c>
       <c r="AQ66" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AR66" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AS66" s="24" t="inlineStr">
         <is>
-          <t>mlb-mil</t>
+          <t>mlb-bos</t>
         </is>
       </c>
       <c r="AT66" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="AU66" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="AV66" s="24" t="n"/>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="BE66" s="24" t="inlineStr">
         <is>
-          <t>6d5f3f5e8f75cb2b</t>
+          <t>9fe2d27778a72dfe</t>
         </is>
       </c>
       <c r="BF66" s="24" t="inlineStr">
@@ -16942,7 +16942,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:42.879792Z</t>
+          <t>2026-07-20T15:33:39.422286Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -16952,16 +16952,16 @@
       </c>
       <c r="BJ66" s="38" t="n"/>
       <c r="BK66" s="26" t="n">
-        <v>-199</v>
+        <v>-138</v>
       </c>
       <c r="BL66" s="39" t="n">
-        <v>1.502513</v>
+        <v>1.724638</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.665552</v>
+        <v>0.579832</v>
       </c>
       <c r="BN66" s="28" t="n">
-        <v>0.6616919999999999</v>
+        <v>0.577114</v>
       </c>
       <c r="BO66" s="28" t="n"/>
       <c r="BP66" s="38" t="n"/>
@@ -16980,22 +16980,22 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>6e9b235e0abe4f38</t>
+          <t>8fe8dba867db4326</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:22:41.782177Z</t>
+          <t>2026-07-20T15:38:55.511243Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T20:05:00-0400</t>
+          <t>2026-07-20T19:15:00-0400</t>
         </is>
       </c>
       <c r="D67" s="24" t="inlineStr">
         <is>
-          <t>401816193</t>
+          <t>401816190</t>
         </is>
       </c>
       <c r="E67" s="24" t="inlineStr">
@@ -17005,12 +17005,12 @@
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="G67" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr">
@@ -17030,26 +17030,26 @@
         </is>
       </c>
       <c r="L67" s="26" t="n">
-        <v>-108</v>
+        <v>-133</v>
       </c>
       <c r="M67" s="39" t="n">
-        <v>1.925926</v>
+        <v>1.75188</v>
       </c>
       <c r="N67" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.570815</v>
       </c>
       <c r="O67" s="28" t="n">
-        <v>0.566967</v>
+        <v>0.550915</v>
       </c>
       <c r="P67" s="28" t="n"/>
       <c r="Q67" s="28" t="n">
-        <v>0.047736</v>
+        <v>-0.0199</v>
       </c>
       <c r="R67" s="26" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="S67" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T67" s="24" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-det-chc-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5700 (aec-mlb-sd-atl-2026-07-20).</t>
         </is>
       </c>
       <c r="AF67" s="31" t="inlineStr">
@@ -17113,32 +17113,32 @@
       </c>
       <c r="AP67" s="24" t="inlineStr">
         <is>
-          <t>mlb-det</t>
+          <t>mlb-sd</t>
         </is>
       </c>
       <c r="AQ67" s="24" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AR67" s="24" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AS67" s="24" t="inlineStr">
         <is>
-          <t>mlb-chc</t>
+          <t>mlb-atl</t>
         </is>
       </c>
       <c r="AT67" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="AU67" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="AV67" s="24" t="n"/>
@@ -17176,7 +17176,7 @@
       </c>
       <c r="BE67" s="24" t="inlineStr">
         <is>
-          <t>b84afb2c70e14d93</t>
+          <t>f0b5eac7c97d1146</t>
         </is>
       </c>
       <c r="BF67" s="24" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:46.871986Z</t>
+          <t>2026-07-20T15:33:42.141054Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -17201,16 +17201,16 @@
       </c>
       <c r="BJ67" s="38" t="n"/>
       <c r="BK67" s="26" t="n">
-        <v>-108</v>
+        <v>-133</v>
       </c>
       <c r="BL67" s="39" t="n">
-        <v>1.925926</v>
+        <v>1.75188</v>
       </c>
       <c r="BM67" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.570815</v>
       </c>
       <c r="BN67" s="28" t="n">
-        <v>0.517413</v>
+        <v>0.567164</v>
       </c>
       <c r="BO67" s="28" t="n"/>
       <c r="BP67" s="38" t="n"/>
@@ -17229,22 +17229,22 @@
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
         <is>
-          <t>bf8728673bd4485f</t>
+          <t>de587015be8044d0</t>
         </is>
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:22:41.782177Z</t>
+          <t>2026-07-20T15:38:55.511243Z</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T20:40:00-0400</t>
+          <t>2026-07-20T19:40:00-0400</t>
         </is>
       </c>
       <c r="D68" s="24" t="inlineStr">
         <is>
-          <t>401816197</t>
+          <t>401816195</t>
         </is>
       </c>
       <c r="E68" s="24" t="inlineStr">
@@ -17254,12 +17254,12 @@
       </c>
       <c r="F68" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="G68" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="H68" s="24" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="I68" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J68" s="38" t="n"/>
@@ -17279,26 +17279,26 @@
         </is>
       </c>
       <c r="L68" s="26" t="n">
-        <v>-117</v>
+        <v>-199</v>
       </c>
       <c r="M68" s="39" t="n">
-        <v>1.854701</v>
+        <v>1.502513</v>
       </c>
       <c r="N68" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.665552</v>
       </c>
       <c r="O68" s="28" t="n">
-        <v>0.5563709999999999</v>
+        <v>0.640995</v>
       </c>
       <c r="P68" s="28" t="n"/>
       <c r="Q68" s="28" t="n">
-        <v>0.0172</v>
+        <v>-0.024557</v>
       </c>
       <c r="R68" s="26" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="S68" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T68" s="24" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
       <c r="AD68" s="24" t="n"/>
       <c r="AE68" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5400 (aec-mlb-wsh-col-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.6650 (aec-mlb-nym-mil-2026-07-20).</t>
         </is>
       </c>
       <c r="AF68" s="31" t="inlineStr">
@@ -17362,32 +17362,32 @@
       </c>
       <c r="AP68" s="24" t="inlineStr">
         <is>
-          <t>mlb-wsh</t>
+          <t>mlb-nym</t>
         </is>
       </c>
       <c r="AQ68" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AR68" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AS68" s="24" t="inlineStr">
         <is>
-          <t>mlb-col</t>
+          <t>mlb-mil</t>
         </is>
       </c>
       <c r="AT68" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AU68" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AV68" s="24" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="BE68" s="24" t="inlineStr">
         <is>
-          <t>a2f336c1cee8c92e</t>
+          <t>6d5f3f5e8f75cb2b</t>
         </is>
       </c>
       <c r="BF68" s="24" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="BH68" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:49.897394Z</t>
+          <t>2026-07-20T15:33:44.122845Z</t>
         </is>
       </c>
       <c r="BI68" s="24" t="inlineStr">
@@ -17450,16 +17450,16 @@
       </c>
       <c r="BJ68" s="38" t="n"/>
       <c r="BK68" s="26" t="n">
-        <v>-117</v>
+        <v>-199</v>
       </c>
       <c r="BL68" s="39" t="n">
-        <v>1.854701</v>
+        <v>1.502513</v>
       </c>
       <c r="BM68" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.665552</v>
       </c>
       <c r="BN68" s="28" t="n">
-        <v>0.537313</v>
+        <v>0.6616919999999999</v>
       </c>
       <c r="BO68" s="28" t="n"/>
       <c r="BP68" s="38" t="n"/>
@@ -17478,22 +17478,22 @@
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>aefbe47ff16045f2</t>
+          <t>f30c4f4411454bcb</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:22:41.782177Z</t>
+          <t>2026-07-20T15:38:55.511243Z</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T21:40:00-0400</t>
+          <t>2026-07-20T19:40:00-0400</t>
         </is>
       </c>
       <c r="D69" s="24" t="inlineStr">
         <is>
-          <t>401816198</t>
+          <t>401816196</t>
         </is>
       </c>
       <c r="E69" s="24" t="inlineStr">
@@ -17503,12 +17503,12 @@
       </c>
       <c r="F69" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="G69" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="H69" s="24" t="inlineStr">
@@ -17528,26 +17528,26 @@
         </is>
       </c>
       <c r="L69" s="26" t="n">
-        <v>-147</v>
+        <v>-111</v>
       </c>
       <c r="M69" s="39" t="n">
-        <v>1.680272</v>
+        <v>1.900901</v>
       </c>
       <c r="N69" s="28" t="n">
-        <v>0.5951419999999999</v>
+        <v>0.526066</v>
       </c>
       <c r="O69" s="28" t="n">
-        <v>0.58189</v>
+        <v>0.514213</v>
       </c>
       <c r="P69" s="28" t="n"/>
       <c r="Q69" s="28" t="n">
-        <v>-0.013252</v>
+        <v>-0.011853</v>
       </c>
       <c r="R69" s="26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S69" s="29" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="T69" s="24" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
       <c r="AD69" s="24" t="n"/>
       <c r="AE69" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5950 (aec-mlb-ath-az-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5250 (aec-mlb-sf-kc-2026-07-20).</t>
         </is>
       </c>
       <c r="AF69" s="31" t="inlineStr">
@@ -17611,32 +17611,32 @@
       </c>
       <c r="AP69" s="24" t="inlineStr">
         <is>
-          <t>mlb-ath</t>
+          <t>mlb-sf</t>
         </is>
       </c>
       <c r="AQ69" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="AR69" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="AS69" s="24" t="inlineStr">
         <is>
-          <t>mlb-ari</t>
+          <t>mlb-kc</t>
         </is>
       </c>
       <c r="AT69" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="AU69" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="AV69" s="24" t="n"/>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="BE69" s="24" t="inlineStr">
         <is>
-          <t>7b682aa5da86e2a4</t>
+          <t>9c457d5cc4752804</t>
         </is>
       </c>
       <c r="BF69" s="24" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="BH69" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:51.339273Z</t>
+          <t>2026-07-20T15:33:44.852438Z</t>
         </is>
       </c>
       <c r="BI69" s="24" t="inlineStr">
@@ -17699,16 +17699,16 @@
       </c>
       <c r="BJ69" s="38" t="n"/>
       <c r="BK69" s="26" t="n">
-        <v>-147</v>
+        <v>-111</v>
       </c>
       <c r="BL69" s="39" t="n">
-        <v>1.680272</v>
+        <v>1.900901</v>
       </c>
       <c r="BM69" s="28" t="n">
-        <v>0.5951419999999999</v>
+        <v>0.526066</v>
       </c>
       <c r="BN69" s="28" t="n">
-        <v>0.59204</v>
+        <v>0.522388</v>
       </c>
       <c r="BO69" s="28" t="n"/>
       <c r="BP69" s="38" t="n"/>
@@ -17727,22 +17727,22 @@
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>b9692cb20ec34d5d</t>
+          <t>9d32e3b580bb4d9e</t>
         </is>
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:22:41.782177Z</t>
+          <t>2026-07-20T15:38:55.511243Z</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T21:40:00-0400</t>
+          <t>2026-07-20T20:05:00-0400</t>
         </is>
       </c>
       <c r="D70" s="24" t="inlineStr">
         <is>
-          <t>401816199</t>
+          <t>401816192</t>
         </is>
       </c>
       <c r="E70" s="24" t="inlineStr">
@@ -17752,12 +17752,12 @@
       </c>
       <c r="F70" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="G70" s="24" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="H70" s="24" t="inlineStr">
@@ -17777,26 +17777,26 @@
         </is>
       </c>
       <c r="L70" s="26" t="n">
-        <v>-141</v>
+        <v>-160</v>
       </c>
       <c r="M70" s="39" t="n">
-        <v>1.70922</v>
+        <v>1.625</v>
       </c>
       <c r="N70" s="28" t="n">
-        <v>0.585062</v>
+        <v>0.615385</v>
       </c>
       <c r="O70" s="28" t="n">
-        <v>0.592852</v>
+        <v>0.524518</v>
       </c>
       <c r="P70" s="28" t="n"/>
       <c r="Q70" s="28" t="n">
-        <v>0.00779</v>
+        <v>-0.090867</v>
       </c>
       <c r="R70" s="26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="S70" s="29" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="T70" s="24" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
       <c r="AD70" s="24" t="n"/>
       <c r="AE70" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5850 (aec-mlb-cin-sea-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.6150 (aec-mlb-cws-tex-2026-07-20).</t>
         </is>
       </c>
       <c r="AF70" s="31" t="inlineStr">
@@ -17860,32 +17860,32 @@
       </c>
       <c r="AP70" s="24" t="inlineStr">
         <is>
-          <t>mlb-cin</t>
+          <t>mlb-cws</t>
         </is>
       </c>
       <c r="AQ70" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="AR70" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="AS70" s="24" t="inlineStr">
         <is>
-          <t>mlb-sea</t>
+          <t>mlb-tex</t>
         </is>
       </c>
       <c r="AT70" s="24" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AU70" s="24" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AV70" s="24" t="n"/>
@@ -17923,7 +17923,7 @@
       </c>
       <c r="BE70" s="24" t="inlineStr">
         <is>
-          <t>af7ccafcacf69681</t>
+          <t>87e15ff2f82f8974</t>
         </is>
       </c>
       <c r="BF70" s="24" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="BH70" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:52.831217Z</t>
+          <t>2026-07-20T15:33:47.582533Z</t>
         </is>
       </c>
       <c r="BI70" s="24" t="inlineStr">
@@ -17948,16 +17948,16 @@
       </c>
       <c r="BJ70" s="38" t="n"/>
       <c r="BK70" s="26" t="n">
-        <v>-141</v>
+        <v>-160</v>
       </c>
       <c r="BL70" s="39" t="n">
-        <v>1.70922</v>
+        <v>1.625</v>
       </c>
       <c r="BM70" s="28" t="n">
-        <v>0.585062</v>
+        <v>0.615385</v>
       </c>
       <c r="BN70" s="28" t="n">
-        <v>0.58209</v>
+        <v>0.61194</v>
       </c>
       <c r="BO70" s="28" t="n"/>
       <c r="BP70" s="38" t="n"/>
@@ -17976,37 +17976,37 @@
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>11f48fe641c040f7</t>
+          <t>d4d115be002c47d3</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:28:55.067840Z</t>
+          <t>2026-07-20T15:38:55.511243Z</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T20:00:00-0400</t>
+          <t>2026-07-20T20:05:00-0400</t>
         </is>
       </c>
       <c r="D71" s="24" t="inlineStr">
         <is>
-          <t>401857083</t>
+          <t>401816193</t>
         </is>
       </c>
       <c r="E71" s="24" t="inlineStr">
         <is>
-          <t>WNBA</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="F71" s="24" t="inlineStr">
         <is>
-          <t>Las Vegas Aces</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="G71" s="24" t="inlineStr">
         <is>
-          <t>Toronto Tempo</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="H71" s="24" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="I71" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J71" s="38" t="n"/>
@@ -18026,30 +18026,30 @@
         </is>
       </c>
       <c r="L71" s="26" t="n">
-        <v>-488</v>
+        <v>-108</v>
       </c>
       <c r="M71" s="39" t="n">
-        <v>1.204918</v>
+        <v>1.925926</v>
       </c>
       <c r="N71" s="28" t="n">
-        <v>0.829932</v>
+        <v>0.519231</v>
       </c>
       <c r="O71" s="28" t="n">
-        <v>0.6572210000000001</v>
+        <v>0.566967</v>
       </c>
       <c r="P71" s="28" t="n"/>
       <c r="Q71" s="28" t="n">
-        <v>-0.172711</v>
+        <v>0.047736</v>
       </c>
       <c r="R71" s="26" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="S71" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T71" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U71" s="24" t="inlineStr">
@@ -18068,7 +18068,7 @@
       <c r="AD71" s="24" t="n"/>
       <c r="AE71" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5051; executable ask 0.8300 (aec-wnba-lv-tor-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-det-chc-2026-07-20).</t>
         </is>
       </c>
       <c r="AF71" s="31" t="inlineStr">
@@ -18104,37 +18104,37 @@
       </c>
       <c r="AO71" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP71" s="24" t="inlineStr">
         <is>
-          <t>wnba-lva</t>
+          <t>mlb-det</t>
         </is>
       </c>
       <c r="AQ71" s="24" t="inlineStr">
         <is>
-          <t>Las Vegas Aces</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AR71" s="24" t="inlineStr">
         <is>
-          <t>Las Vegas Aces</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AS71" s="24" t="inlineStr">
         <is>
-          <t>wnba-tor</t>
+          <t>mlb-chc</t>
         </is>
       </c>
       <c r="AT71" s="24" t="inlineStr">
         <is>
-          <t>Toronto Tempo</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AU71" s="24" t="inlineStr">
         <is>
-          <t>Toronto Tempo</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AV71" s="24" t="n"/>
@@ -18152,7 +18152,7 @@
       </c>
       <c r="BA71" s="24" t="inlineStr">
         <is>
-          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB71" s="24" t="inlineStr">
@@ -18162,17 +18162,17 @@
       </c>
       <c r="BC71" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD71" s="24" t="inlineStr">
         <is>
-          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE71" s="24" t="inlineStr">
         <is>
-          <t>32740a9f4976946d</t>
+          <t>b84afb2c70e14d93</t>
         </is>
       </c>
       <c r="BF71" s="24" t="inlineStr">
@@ -18182,12 +18182,12 @@
       </c>
       <c r="BG71" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH71" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:56.867039Z</t>
+          <t>2026-07-20T15:33:47.761585Z</t>
         </is>
       </c>
       <c r="BI71" s="24" t="inlineStr">
@@ -18197,16 +18197,16 @@
       </c>
       <c r="BJ71" s="38" t="n"/>
       <c r="BK71" s="26" t="n">
-        <v>-488</v>
+        <v>-108</v>
       </c>
       <c r="BL71" s="39" t="n">
-        <v>1.204918</v>
+        <v>1.925926</v>
       </c>
       <c r="BM71" s="28" t="n">
-        <v>0.829932</v>
+        <v>0.519231</v>
       </c>
       <c r="BN71" s="28" t="n">
-        <v>0.821782</v>
+        <v>0.5148509999999999</v>
       </c>
       <c r="BO71" s="28" t="n"/>
       <c r="BP71" s="38" t="n"/>
@@ -18225,37 +18225,37 @@
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
         <is>
-          <t>18e861041a484fd5</t>
+          <t>5ac11ebb449b4b54</t>
         </is>
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:28:55.067840Z</t>
+          <t>2026-07-20T15:38:55.511243Z</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T20:00:00-0400</t>
+          <t>2026-07-20T20:10:00-0400</t>
         </is>
       </c>
       <c r="D72" s="24" t="inlineStr">
         <is>
-          <t>401892393</t>
+          <t>401816194</t>
         </is>
       </c>
       <c r="E72" s="24" t="inlineStr">
         <is>
-          <t>WNBA</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="F72" s="24" t="inlineStr">
         <is>
-          <t>New York Liberty</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="G72" s="24" t="inlineStr">
         <is>
-          <t>Dallas Wings</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="H72" s="24" t="inlineStr">
@@ -18275,30 +18275,30 @@
         </is>
       </c>
       <c r="L72" s="26" t="n">
-        <v>156</v>
+        <v>-115</v>
       </c>
       <c r="M72" s="39" t="n">
-        <v>2.56</v>
+        <v>1.869565</v>
       </c>
       <c r="N72" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.534884</v>
       </c>
       <c r="O72" s="28" t="n">
-        <v>0.688998</v>
+        <v>0.512555</v>
       </c>
       <c r="P72" s="28" t="n"/>
       <c r="Q72" s="28" t="n">
-        <v>0.298373</v>
+        <v>-0.022329</v>
       </c>
       <c r="R72" s="26" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="S72" s="29" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="T72" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U72" s="24" t="inlineStr">
@@ -18317,7 +18317,7 @@
       <c r="AD72" s="24" t="n"/>
       <c r="AE72" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5051; executable ask 0.3900 (aec-wnba-ny-dal-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5350 (aec-mlb-mia-hou-2026-07-20).</t>
         </is>
       </c>
       <c r="AF72" s="31" t="inlineStr">
@@ -18353,37 +18353,37 @@
       </c>
       <c r="AO72" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP72" s="24" t="inlineStr">
         <is>
-          <t>wnba-nyl</t>
+          <t>mlb-mia</t>
         </is>
       </c>
       <c r="AQ72" s="24" t="inlineStr">
         <is>
-          <t>New York Liberty</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="AR72" s="24" t="inlineStr">
         <is>
-          <t>New York Liberty</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="AS72" s="24" t="inlineStr">
         <is>
-          <t>wnba-dal</t>
+          <t>mlb-hou</t>
         </is>
       </c>
       <c r="AT72" s="24" t="inlineStr">
         <is>
-          <t>Dallas Wings</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="AU72" s="24" t="inlineStr">
         <is>
-          <t>Dallas Wings</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="AV72" s="24" t="n"/>
@@ -18401,7 +18401,7 @@
       </c>
       <c r="BA72" s="24" t="inlineStr">
         <is>
-          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB72" s="24" t="inlineStr">
@@ -18411,17 +18411,17 @@
       </c>
       <c r="BC72" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD72" s="24" t="inlineStr">
         <is>
-          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE72" s="24" t="inlineStr">
         <is>
-          <t>c20bbb99f1fff741</t>
+          <t>ba8ef6f8648f77b7</t>
         </is>
       </c>
       <c r="BF72" s="24" t="inlineStr">
@@ -18431,12 +18431,12 @@
       </c>
       <c r="BG72" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH72" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:58.731031Z</t>
+          <t>2026-07-20T15:33:49.597715Z</t>
         </is>
       </c>
       <c r="BI72" s="24" t="inlineStr">
@@ -18446,16 +18446,16 @@
       </c>
       <c r="BJ72" s="38" t="n"/>
       <c r="BK72" s="26" t="n">
-        <v>156</v>
+        <v>-115</v>
       </c>
       <c r="BL72" s="39" t="n">
-        <v>2.56</v>
+        <v>1.869565</v>
       </c>
       <c r="BM72" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.534884</v>
       </c>
       <c r="BN72" s="28" t="n">
-        <v>0.386139</v>
+        <v>0.532338</v>
       </c>
       <c r="BO72" s="28" t="n"/>
       <c r="BP72" s="38" t="n"/>
@@ -18474,37 +18474,37 @@
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>195c4a9c3ce44e1b</t>
+          <t>3faaea8e908f4dff</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:28:55.067840Z</t>
+          <t>2026-07-20T15:38:55.511243Z</t>
         </is>
       </c>
       <c r="C73" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T22:00:00-0400</t>
+          <t>2026-07-20T20:40:00-0400</t>
         </is>
       </c>
       <c r="D73" s="24" t="inlineStr">
         <is>
-          <t>401857084</t>
+          <t>401816197</t>
         </is>
       </c>
       <c r="E73" s="24" t="inlineStr">
         <is>
-          <t>WNBA</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="F73" s="24" t="inlineStr">
         <is>
-          <t>Washington Mystics</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="G73" s="24" t="inlineStr">
         <is>
-          <t>Golden State Valkyries</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="H73" s="24" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="I73" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J73" s="38" t="n"/>
@@ -18524,30 +18524,30 @@
         </is>
       </c>
       <c r="L73" s="26" t="n">
-        <v>-317</v>
+        <v>-117</v>
       </c>
       <c r="M73" s="39" t="n">
-        <v>1.315457</v>
+        <v>1.854701</v>
       </c>
       <c r="N73" s="28" t="n">
-        <v>0.760192</v>
+        <v>0.539171</v>
       </c>
       <c r="O73" s="28" t="n">
-        <v>0.750463</v>
+        <v>0.5563709999999999</v>
       </c>
       <c r="P73" s="28" t="n"/>
       <c r="Q73" s="28" t="n">
-        <v>-0.009729</v>
+        <v>0.0172</v>
       </c>
       <c r="R73" s="26" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="S73" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T73" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U73" s="24" t="inlineStr">
@@ -18566,7 +18566,7 @@
       <c r="AD73" s="24" t="n"/>
       <c r="AE73" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5051; executable ask 0.7600 (aec-wnba-wsh-gsv-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5400 (aec-mlb-wsh-col-2026-07-20).</t>
         </is>
       </c>
       <c r="AF73" s="31" t="inlineStr">
@@ -18607,32 +18607,32 @@
       </c>
       <c r="AP73" s="24" t="inlineStr">
         <is>
-          <t>wnba-was</t>
+          <t>mlb-wsh</t>
         </is>
       </c>
       <c r="AQ73" s="24" t="inlineStr">
         <is>
-          <t>Washington Mystics</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="AR73" s="24" t="inlineStr">
         <is>
-          <t>Washington Mystics</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="AS73" s="24" t="inlineStr">
         <is>
-          <t>wnba-gsv</t>
+          <t>mlb-col</t>
         </is>
       </c>
       <c r="AT73" s="24" t="inlineStr">
         <is>
-          <t>Golden State Valkyries</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AU73" s="24" t="inlineStr">
         <is>
-          <t>Golden State Valkyries</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AV73" s="24" t="n"/>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="BA73" s="24" t="inlineStr">
         <is>
-          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB73" s="24" t="inlineStr">
@@ -18660,17 +18660,17 @@
       </c>
       <c r="BC73" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD73" s="24" t="inlineStr">
         <is>
-          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE73" s="24" t="inlineStr">
         <is>
-          <t>a82314f65618b567</t>
+          <t>a2f336c1cee8c92e</t>
         </is>
       </c>
       <c r="BF73" s="24" t="inlineStr">
@@ -18680,12 +18680,12 @@
       </c>
       <c r="BG73" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH73" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:58:01.293707Z</t>
+          <t>2026-07-20T15:33:51.548954Z</t>
         </is>
       </c>
       <c r="BI73" s="24" t="inlineStr">
@@ -18695,16 +18695,16 @@
       </c>
       <c r="BJ73" s="38" t="n"/>
       <c r="BK73" s="26" t="n">
-        <v>-317</v>
+        <v>-117</v>
       </c>
       <c r="BL73" s="39" t="n">
-        <v>1.315457</v>
+        <v>1.854701</v>
       </c>
       <c r="BM73" s="28" t="n">
-        <v>0.760192</v>
+        <v>0.539171</v>
       </c>
       <c r="BN73" s="28" t="n">
-        <v>0.752475</v>
+        <v>0.537313</v>
       </c>
       <c r="BO73" s="28" t="n"/>
       <c r="BP73" s="38" t="n"/>
@@ -18723,37 +18723,37 @@
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
         <is>
-          <t>555b6295ce3941e7</t>
+          <t>ce60c51f7f4d4503</t>
         </is>
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:28:55.067840Z</t>
+          <t>2026-07-20T15:38:55.511243Z</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T22:00:00-0400</t>
+          <t>2026-07-20T21:40:00-0400</t>
         </is>
       </c>
       <c r="D74" s="24" t="inlineStr">
         <is>
-          <t>401857085</t>
+          <t>401816198</t>
         </is>
       </c>
       <c r="E74" s="24" t="inlineStr">
         <is>
-          <t>WNBA</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="F74" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="G74" s="24" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="H74" s="24" t="inlineStr">
@@ -18763,7 +18763,7 @@
       </c>
       <c r="I74" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J74" s="38" t="n"/>
@@ -18773,30 +18773,30 @@
         </is>
       </c>
       <c r="L74" s="26" t="n">
-        <v>-456</v>
+        <v>-144</v>
       </c>
       <c r="M74" s="39" t="n">
-        <v>1.219298</v>
+        <v>1.694444</v>
       </c>
       <c r="N74" s="28" t="n">
-        <v>0.820144</v>
+        <v>0.590164</v>
       </c>
       <c r="O74" s="28" t="n">
-        <v>0.738843</v>
+        <v>0.58189</v>
       </c>
       <c r="P74" s="28" t="n"/>
       <c r="Q74" s="28" t="n">
-        <v>-0.081301</v>
+        <v>-0.008274</v>
       </c>
       <c r="R74" s="26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S74" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T74" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U74" s="24" t="inlineStr">
@@ -18815,7 +18815,7 @@
       <c r="AD74" s="24" t="n"/>
       <c r="AE74" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5051; executable ask 0.8200 (aec-wnba-min-sea-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5900 (aec-mlb-ath-az-2026-07-20).</t>
         </is>
       </c>
       <c r="AF74" s="31" t="inlineStr">
@@ -18856,32 +18856,32 @@
       </c>
       <c r="AP74" s="24" t="inlineStr">
         <is>
-          <t>wnba-min</t>
+          <t>mlb-ath</t>
         </is>
       </c>
       <c r="AQ74" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="AR74" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="AS74" s="24" t="inlineStr">
         <is>
-          <t>wnba-sea</t>
+          <t>mlb-ari</t>
         </is>
       </c>
       <c r="AT74" s="24" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AU74" s="24" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AV74" s="24" t="n"/>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="BA74" s="24" t="inlineStr">
         <is>
-          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB74" s="24" t="inlineStr">
@@ -18909,17 +18909,17 @@
       </c>
       <c r="BC74" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD74" s="24" t="inlineStr">
         <is>
-          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE74" s="24" t="inlineStr">
         <is>
-          <t>c7928758cc04b6e5</t>
+          <t>7b682aa5da86e2a4</t>
         </is>
       </c>
       <c r="BF74" s="24" t="inlineStr">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="BG74" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH74" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:58:02.052718Z</t>
+          <t>2026-07-20T15:33:52.295961Z</t>
         </is>
       </c>
       <c r="BI74" s="24" t="inlineStr">
@@ -18944,16 +18944,16 @@
       </c>
       <c r="BJ74" s="38" t="n"/>
       <c r="BK74" s="26" t="n">
-        <v>-456</v>
+        <v>-144</v>
       </c>
       <c r="BL74" s="39" t="n">
-        <v>1.219298</v>
+        <v>1.694444</v>
       </c>
       <c r="BM74" s="28" t="n">
-        <v>0.820144</v>
+        <v>0.590164</v>
       </c>
       <c r="BN74" s="28" t="n">
-        <v>0.811881</v>
+        <v>0.5870649999999999</v>
       </c>
       <c r="BO74" s="28" t="n"/>
       <c r="BP74" s="38" t="n"/>
@@ -18969,6 +18969,1500 @@
       <c r="BZ74" s="24" t="n"/>
       <c r="CA74" s="31" t="n"/>
     </row>
+    <row r="75" ht="36" customHeight="1">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>adfd7bf912a84989</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:38:55.511243Z</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D75" s="24" t="inlineStr">
+        <is>
+          <t>401816199</t>
+        </is>
+      </c>
+      <c r="E75" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F75" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="G75" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="H75" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I75" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J75" s="38" t="n"/>
+      <c r="K75" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L75" s="26" t="n">
+        <v>-141</v>
+      </c>
+      <c r="M75" s="39" t="n">
+        <v>1.70922</v>
+      </c>
+      <c r="N75" s="28" t="n">
+        <v>0.585062</v>
+      </c>
+      <c r="O75" s="28" t="n">
+        <v>0.592852</v>
+      </c>
+      <c r="P75" s="28" t="n"/>
+      <c r="Q75" s="28" t="n">
+        <v>0.00779</v>
+      </c>
+      <c r="R75" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="S75" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T75" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U75" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V75" s="24" t="n"/>
+      <c r="W75" s="26" t="n"/>
+      <c r="X75" s="26" t="n"/>
+      <c r="Y75" s="38" t="n"/>
+      <c r="Z75" s="26" t="n"/>
+      <c r="AA75" s="28" t="n"/>
+      <c r="AB75" s="28" t="n"/>
+      <c r="AC75" s="40" t="n"/>
+      <c r="AD75" s="24" t="n"/>
+      <c r="AE75" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5850 (aec-mlb-cin-sea-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF75" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG75" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH75" s="24" t="n"/>
+      <c r="AI75" s="31" t="n"/>
+      <c r="AJ75" s="31" t="n"/>
+      <c r="AK75" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL75" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM75" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN75" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO75" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP75" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cin</t>
+        </is>
+      </c>
+      <c r="AQ75" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AR75" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AS75" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sea</t>
+        </is>
+      </c>
+      <c r="AT75" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AU75" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AV75" s="24" t="n"/>
+      <c r="AW75" s="24" t="n"/>
+      <c r="AX75" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY75" s="24" t="n"/>
+      <c r="AZ75" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA75" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB75" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC75" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD75" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE75" s="24" t="inlineStr">
+        <is>
+          <t>af7ccafcacf69681</t>
+        </is>
+      </c>
+      <c r="BF75" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG75" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH75" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:33:53.701471Z</t>
+        </is>
+      </c>
+      <c r="BI75" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ75" s="38" t="n"/>
+      <c r="BK75" s="26" t="n">
+        <v>-141</v>
+      </c>
+      <c r="BL75" s="39" t="n">
+        <v>1.70922</v>
+      </c>
+      <c r="BM75" s="28" t="n">
+        <v>0.585062</v>
+      </c>
+      <c r="BN75" s="28" t="n">
+        <v>0.58209</v>
+      </c>
+      <c r="BO75" s="28" t="n"/>
+      <c r="BP75" s="38" t="n"/>
+      <c r="BQ75" s="39" t="n"/>
+      <c r="BR75" s="28" t="n"/>
+      <c r="BS75" s="28" t="n"/>
+      <c r="BT75" s="28" t="n"/>
+      <c r="BU75" s="38" t="n"/>
+      <c r="BV75" s="29" t="n"/>
+      <c r="BW75" s="24" t="n"/>
+      <c r="BX75" s="40" t="n"/>
+      <c r="BY75" s="39" t="n"/>
+      <c r="BZ75" s="24" t="n"/>
+      <c r="CA75" s="31" t="n"/>
+    </row>
+    <row r="76" ht="36" customHeight="1">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>e912f9cec2ac4e02</t>
+        </is>
+      </c>
+      <c r="B76" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:38:55.511243Z</t>
+        </is>
+      </c>
+      <c r="C76" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D76" s="24" t="inlineStr">
+        <is>
+          <t>401816200</t>
+        </is>
+      </c>
+      <c r="E76" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F76" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="G76" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="H76" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I76" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J76" s="38" t="n"/>
+      <c r="K76" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L76" s="26" t="n">
+        <v>102</v>
+      </c>
+      <c r="M76" s="39" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N76" s="28" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="O76" s="28" t="n">
+        <v>0.52919</v>
+      </c>
+      <c r="P76" s="28" t="n"/>
+      <c r="Q76" s="28" t="n">
+        <v>0.03414</v>
+      </c>
+      <c r="R76" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="S76" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T76" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U76" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V76" s="24" t="n"/>
+      <c r="W76" s="26" t="n"/>
+      <c r="X76" s="26" t="n"/>
+      <c r="Y76" s="38" t="n"/>
+      <c r="Z76" s="26" t="n"/>
+      <c r="AA76" s="28" t="n"/>
+      <c r="AB76" s="28" t="n"/>
+      <c r="AC76" s="40" t="n"/>
+      <c r="AD76" s="24" t="n"/>
+      <c r="AE76" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.4950 (aec-mlb-stl-laa-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF76" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG76" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH76" s="24" t="n"/>
+      <c r="AI76" s="31" t="n"/>
+      <c r="AJ76" s="31" t="n"/>
+      <c r="AK76" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL76" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM76" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN76" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO76" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP76" s="24" t="inlineStr">
+        <is>
+          <t>mlb-stl</t>
+        </is>
+      </c>
+      <c r="AQ76" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="AR76" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="AS76" s="24" t="inlineStr">
+        <is>
+          <t>mlb-laa</t>
+        </is>
+      </c>
+      <c r="AT76" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="AU76" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="AV76" s="24" t="n"/>
+      <c r="AW76" s="24" t="n"/>
+      <c r="AX76" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY76" s="24" t="n"/>
+      <c r="AZ76" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA76" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB76" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC76" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD76" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE76" s="24" t="inlineStr">
+        <is>
+          <t>e8de503e18ea775f</t>
+        </is>
+      </c>
+      <c r="BF76" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG76" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH76" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:33:54.984623Z</t>
+        </is>
+      </c>
+      <c r="BI76" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ76" s="38" t="n"/>
+      <c r="BK76" s="26" t="n">
+        <v>102</v>
+      </c>
+      <c r="BL76" s="39" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM76" s="28" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="BN76" s="28" t="n">
+        <v>0.492537</v>
+      </c>
+      <c r="BO76" s="28" t="n"/>
+      <c r="BP76" s="38" t="n"/>
+      <c r="BQ76" s="39" t="n"/>
+      <c r="BR76" s="28" t="n"/>
+      <c r="BS76" s="28" t="n"/>
+      <c r="BT76" s="28" t="n"/>
+      <c r="BU76" s="38" t="n"/>
+      <c r="BV76" s="29" t="n"/>
+      <c r="BW76" s="24" t="n"/>
+      <c r="BX76" s="40" t="n"/>
+      <c r="BY76" s="39" t="n"/>
+      <c r="BZ76" s="24" t="n"/>
+      <c r="CA76" s="31" t="n"/>
+    </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t>e9767a845c794040</t>
+        </is>
+      </c>
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:39:03.207125Z</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>401857083</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F77" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J77" s="38" t="n"/>
+      <c r="K77" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L77" s="26" t="n">
+        <v>-488</v>
+      </c>
+      <c r="M77" s="39" t="n">
+        <v>1.204918</v>
+      </c>
+      <c r="N77" s="28" t="n">
+        <v>0.829932</v>
+      </c>
+      <c r="O77" s="28" t="n">
+        <v>0.6572210000000001</v>
+      </c>
+      <c r="P77" s="28" t="n"/>
+      <c r="Q77" s="28" t="n">
+        <v>-0.172711</v>
+      </c>
+      <c r="R77" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T77" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U77" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V77" s="24" t="n"/>
+      <c r="W77" s="26" t="n"/>
+      <c r="X77" s="26" t="n"/>
+      <c r="Y77" s="38" t="n"/>
+      <c r="Z77" s="26" t="n"/>
+      <c r="AA77" s="28" t="n"/>
+      <c r="AB77" s="28" t="n"/>
+      <c r="AC77" s="40" t="n"/>
+      <c r="AD77" s="24" t="n"/>
+      <c r="AE77" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5051; executable ask 0.8300 (aec-wnba-lv-tor-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF77" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG77" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH77" s="24" t="n"/>
+      <c r="AI77" s="31" t="n"/>
+      <c r="AJ77" s="31" t="n"/>
+      <c r="AK77" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL77" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM77" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN77" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO77" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP77" s="24" t="inlineStr">
+        <is>
+          <t>wnba-lva</t>
+        </is>
+      </c>
+      <c r="AQ77" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AR77" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AS77" s="24" t="inlineStr">
+        <is>
+          <t>wnba-tor</t>
+        </is>
+      </c>
+      <c r="AT77" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AU77" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AV77" s="24" t="n"/>
+      <c r="AW77" s="24" t="n"/>
+      <c r="AX77" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY77" s="24" t="n"/>
+      <c r="AZ77" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA77" s="24" t="inlineStr">
+        <is>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+        </is>
+      </c>
+      <c r="BB77" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC77" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD77" s="24" t="inlineStr">
+        <is>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+        </is>
+      </c>
+      <c r="BE77" s="24" t="inlineStr">
+        <is>
+          <t>32740a9f4976946d</t>
+        </is>
+      </c>
+      <c r="BF77" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG77" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH77" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:33:56.676680Z</t>
+        </is>
+      </c>
+      <c r="BI77" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ77" s="38" t="n"/>
+      <c r="BK77" s="26" t="n">
+        <v>-488</v>
+      </c>
+      <c r="BL77" s="39" t="n">
+        <v>1.204918</v>
+      </c>
+      <c r="BM77" s="28" t="n">
+        <v>0.829932</v>
+      </c>
+      <c r="BN77" s="28" t="n">
+        <v>0.821782</v>
+      </c>
+      <c r="BO77" s="28" t="n"/>
+      <c r="BP77" s="38" t="n"/>
+      <c r="BQ77" s="39" t="n"/>
+      <c r="BR77" s="28" t="n"/>
+      <c r="BS77" s="28" t="n"/>
+      <c r="BT77" s="28" t="n"/>
+      <c r="BU77" s="38" t="n"/>
+      <c r="BV77" s="29" t="n"/>
+      <c r="BW77" s="24" t="n"/>
+      <c r="BX77" s="40" t="n"/>
+      <c r="BY77" s="39" t="n"/>
+      <c r="BZ77" s="24" t="n"/>
+      <c r="CA77" s="31" t="n"/>
+    </row>
+    <row r="78" ht="36" customHeight="1">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>8e2265c74515471f</t>
+        </is>
+      </c>
+      <c r="B78" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:39:03.207125Z</t>
+        </is>
+      </c>
+      <c r="C78" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D78" s="24" t="inlineStr">
+        <is>
+          <t>401892393</t>
+        </is>
+      </c>
+      <c r="E78" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F78" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="G78" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="H78" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I78" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J78" s="38" t="n"/>
+      <c r="K78" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L78" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M78" s="39" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N78" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O78" s="28" t="n">
+        <v>0.688998</v>
+      </c>
+      <c r="P78" s="28" t="n"/>
+      <c r="Q78" s="28" t="n">
+        <v>0.298373</v>
+      </c>
+      <c r="R78" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S78" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T78" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U78" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V78" s="24" t="n"/>
+      <c r="W78" s="26" t="n"/>
+      <c r="X78" s="26" t="n"/>
+      <c r="Y78" s="38" t="n"/>
+      <c r="Z78" s="26" t="n"/>
+      <c r="AA78" s="28" t="n"/>
+      <c r="AB78" s="28" t="n"/>
+      <c r="AC78" s="40" t="n"/>
+      <c r="AD78" s="24" t="n"/>
+      <c r="AE78" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5051; executable ask 0.3900 (aec-wnba-ny-dal-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF78" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG78" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH78" s="24" t="n"/>
+      <c r="AI78" s="31" t="n"/>
+      <c r="AJ78" s="31" t="n"/>
+      <c r="AK78" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL78" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM78" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN78" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO78" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP78" s="24" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AQ78" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AR78" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AS78" s="24" t="inlineStr">
+        <is>
+          <t>wnba-dal</t>
+        </is>
+      </c>
+      <c r="AT78" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AU78" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AV78" s="24" t="n"/>
+      <c r="AW78" s="24" t="n"/>
+      <c r="AX78" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY78" s="24" t="n"/>
+      <c r="AZ78" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA78" s="24" t="inlineStr">
+        <is>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+        </is>
+      </c>
+      <c r="BB78" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC78" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD78" s="24" t="inlineStr">
+        <is>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+        </is>
+      </c>
+      <c r="BE78" s="24" t="inlineStr">
+        <is>
+          <t>c20bbb99f1fff741</t>
+        </is>
+      </c>
+      <c r="BF78" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG78" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH78" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:33:58.690931Z</t>
+        </is>
+      </c>
+      <c r="BI78" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ78" s="38" t="n"/>
+      <c r="BK78" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL78" s="39" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM78" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN78" s="28" t="n">
+        <v>0.386139</v>
+      </c>
+      <c r="BO78" s="28" t="n"/>
+      <c r="BP78" s="38" t="n"/>
+      <c r="BQ78" s="39" t="n"/>
+      <c r="BR78" s="28" t="n"/>
+      <c r="BS78" s="28" t="n"/>
+      <c r="BT78" s="28" t="n"/>
+      <c r="BU78" s="38" t="n"/>
+      <c r="BV78" s="29" t="n"/>
+      <c r="BW78" s="24" t="n"/>
+      <c r="BX78" s="40" t="n"/>
+      <c r="BY78" s="39" t="n"/>
+      <c r="BZ78" s="24" t="n"/>
+      <c r="CA78" s="31" t="n"/>
+    </row>
+    <row r="79" ht="36" customHeight="1">
+      <c r="A79" s="24" t="inlineStr">
+        <is>
+          <t>a4f324e828eb4cee</t>
+        </is>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:39:03.207125Z</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>401857084</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F79" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="H79" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J79" s="38" t="n"/>
+      <c r="K79" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L79" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="M79" s="39" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="N79" s="28" t="n">
+        <v>0.760192</v>
+      </c>
+      <c r="O79" s="28" t="n">
+        <v>0.750463</v>
+      </c>
+      <c r="P79" s="28" t="n"/>
+      <c r="Q79" s="28" t="n">
+        <v>-0.009729</v>
+      </c>
+      <c r="R79" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="S79" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T79" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U79" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V79" s="24" t="n"/>
+      <c r="W79" s="26" t="n"/>
+      <c r="X79" s="26" t="n"/>
+      <c r="Y79" s="38" t="n"/>
+      <c r="Z79" s="26" t="n"/>
+      <c r="AA79" s="28" t="n"/>
+      <c r="AB79" s="28" t="n"/>
+      <c r="AC79" s="40" t="n"/>
+      <c r="AD79" s="24" t="n"/>
+      <c r="AE79" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5051; executable ask 0.7600 (aec-wnba-wsh-gsv-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF79" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG79" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH79" s="24" t="n"/>
+      <c r="AI79" s="31" t="n"/>
+      <c r="AJ79" s="31" t="n"/>
+      <c r="AK79" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL79" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM79" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN79" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO79" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP79" s="24" t="inlineStr">
+        <is>
+          <t>wnba-was</t>
+        </is>
+      </c>
+      <c r="AQ79" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AR79" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AS79" s="24" t="inlineStr">
+        <is>
+          <t>wnba-gsv</t>
+        </is>
+      </c>
+      <c r="AT79" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AU79" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AV79" s="24" t="n"/>
+      <c r="AW79" s="24" t="n"/>
+      <c r="AX79" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY79" s="24" t="n"/>
+      <c r="AZ79" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA79" s="24" t="inlineStr">
+        <is>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+        </is>
+      </c>
+      <c r="BB79" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC79" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD79" s="24" t="inlineStr">
+        <is>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+        </is>
+      </c>
+      <c r="BE79" s="24" t="inlineStr">
+        <is>
+          <t>a82314f65618b567</t>
+        </is>
+      </c>
+      <c r="BF79" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG79" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH79" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:34:00.890171Z</t>
+        </is>
+      </c>
+      <c r="BI79" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ79" s="38" t="n"/>
+      <c r="BK79" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="BL79" s="39" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="BM79" s="28" t="n">
+        <v>0.760192</v>
+      </c>
+      <c r="BN79" s="28" t="n">
+        <v>0.752475</v>
+      </c>
+      <c r="BO79" s="28" t="n"/>
+      <c r="BP79" s="38" t="n"/>
+      <c r="BQ79" s="39" t="n"/>
+      <c r="BR79" s="28" t="n"/>
+      <c r="BS79" s="28" t="n"/>
+      <c r="BT79" s="28" t="n"/>
+      <c r="BU79" s="38" t="n"/>
+      <c r="BV79" s="29" t="n"/>
+      <c r="BW79" s="24" t="n"/>
+      <c r="BX79" s="40" t="n"/>
+      <c r="BY79" s="39" t="n"/>
+      <c r="BZ79" s="24" t="n"/>
+      <c r="CA79" s="31" t="n"/>
+    </row>
+    <row r="80" ht="36" customHeight="1">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>e010b6ed614649a7</t>
+        </is>
+      </c>
+      <c r="B80" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:39:03.207125Z</t>
+        </is>
+      </c>
+      <c r="C80" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D80" s="24" t="inlineStr">
+        <is>
+          <t>401857085</t>
+        </is>
+      </c>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F80" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="G80" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="H80" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I80" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J80" s="38" t="n"/>
+      <c r="K80" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L80" s="26" t="n">
+        <v>-456</v>
+      </c>
+      <c r="M80" s="39" t="n">
+        <v>1.219298</v>
+      </c>
+      <c r="N80" s="28" t="n">
+        <v>0.820144</v>
+      </c>
+      <c r="O80" s="28" t="n">
+        <v>0.738843</v>
+      </c>
+      <c r="P80" s="28" t="n"/>
+      <c r="Q80" s="28" t="n">
+        <v>-0.081301</v>
+      </c>
+      <c r="R80" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T80" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U80" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V80" s="24" t="n"/>
+      <c r="W80" s="26" t="n"/>
+      <c r="X80" s="26" t="n"/>
+      <c r="Y80" s="38" t="n"/>
+      <c r="Z80" s="26" t="n"/>
+      <c r="AA80" s="28" t="n"/>
+      <c r="AB80" s="28" t="n"/>
+      <c r="AC80" s="40" t="n"/>
+      <c r="AD80" s="24" t="n"/>
+      <c r="AE80" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5051; executable ask 0.8200 (aec-wnba-min-sea-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF80" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG80" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH80" s="24" t="n"/>
+      <c r="AI80" s="31" t="n"/>
+      <c r="AJ80" s="31" t="n"/>
+      <c r="AK80" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL80" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM80" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN80" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO80" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP80" s="24" t="inlineStr">
+        <is>
+          <t>wnba-min</t>
+        </is>
+      </c>
+      <c r="AQ80" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AR80" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AS80" s="24" t="inlineStr">
+        <is>
+          <t>wnba-sea</t>
+        </is>
+      </c>
+      <c r="AT80" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AU80" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AV80" s="24" t="n"/>
+      <c r="AW80" s="24" t="n"/>
+      <c r="AX80" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY80" s="24" t="n"/>
+      <c r="AZ80" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA80" s="24" t="inlineStr">
+        <is>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+        </is>
+      </c>
+      <c r="BB80" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC80" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD80" s="24" t="inlineStr">
+        <is>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+        </is>
+      </c>
+      <c r="BE80" s="24" t="inlineStr">
+        <is>
+          <t>c7928758cc04b6e5</t>
+        </is>
+      </c>
+      <c r="BF80" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG80" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH80" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T15:34:01.619683Z</t>
+        </is>
+      </c>
+      <c r="BI80" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ80" s="38" t="n"/>
+      <c r="BK80" s="26" t="n">
+        <v>-456</v>
+      </c>
+      <c r="BL80" s="39" t="n">
+        <v>1.219298</v>
+      </c>
+      <c r="BM80" s="28" t="n">
+        <v>0.820144</v>
+      </c>
+      <c r="BN80" s="28" t="n">
+        <v>0.811881</v>
+      </c>
+      <c r="BO80" s="28" t="n"/>
+      <c r="BP80" s="38" t="n"/>
+      <c r="BQ80" s="39" t="n"/>
+      <c r="BR80" s="28" t="n"/>
+      <c r="BS80" s="28" t="n"/>
+      <c r="BT80" s="28" t="n"/>
+      <c r="BU80" s="38" t="n"/>
+      <c r="BV80" s="29" t="n"/>
+      <c r="BW80" s="24" t="n"/>
+      <c r="BX80" s="40" t="n"/>
+      <c r="BY80" s="39" t="n"/>
+      <c r="BZ80" s="24" t="n"/>
+      <c r="CA80" s="31" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0###"/>
-    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,38 +217,11 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -327,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA80" headerRowCount="1">
-  <autoFilter ref="A1:CA80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA90" headerRowCount="1">
+  <autoFilter ref="A1:CA90"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -765,23 +738,22 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$80)</f>
+        <f>COUNTA('Picks'!$A$2:$A$90)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$80,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$90,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$80,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$90,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"win")+COUNTIFS('Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")+COUNTIFS('Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -806,23 +778,22 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$80,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$90,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$80,"&gt;0",'Picks'!$V$2:$V$80,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$80,"&gt;0",'Picks'!$V$2:$V$80,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="32">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$80,"&gt;0",'Picks'!$V$2:$V$80,"win")/(COUNTIFS('Picks'!$BX$2:$BX$80,"&gt;0",'Picks'!$V$2:$V$80,"win")+COUNTIFS('Picks'!$BX$2:$BX$80,"&gt;0",'Picks'!$V$2:$V$80,"loss")),0)</f>
+      <c r="E7" s="7">
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"win")/(COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"win")+COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="32">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$80)/SUM('Picks'!$BX$2:$BX$80),0)</f>
+      <c r="G7" s="7">
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$90)/SUM('Picks'!$BX$2:$BX$90),0)</f>
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -846,24 +817,23 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="33">
-        <f>SUM('Picks'!$BY$2:$BY$80)</f>
+      <c r="A10" s="8">
+        <f>SUM('Picks'!$BY$2:$BY$90)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$80,"&lt;&gt;",'Picks'!$AB$2:$AB$80),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$90,"&lt;&gt;",'Picks'!$AB$2:$AB$90),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$80,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$80,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$90,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$90,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="33">
-        <f>SUMIFS('Picks'!$AC$2:$AC$80,'Picks'!$AM$2:$AM$80,"QUALIFIED_SHADOW_CALL")</f>
+      <c r="G10" s="8">
+        <f>SUMIFS('Picks'!$AC$2:$AC$90,'Picks'!$AM$2:$AM$90,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -915,27 +885,27 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$80,$A14,'Picks'!$U$2:$U$80,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$80,$A14,'Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$80,$A14,'Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="14">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$80,'Picks'!$H$2:$H$80,$A14)</f>
+      <c r="F14" s="15">
+        <f>SUMIFS('Picks'!$BY$2:$BY$90,'Picks'!$H$2:$H$90,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$80,'Picks'!$H$2:$H$80,$A14,'Picks'!$U$2:$U$80,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$90,'Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -946,27 +916,27 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$80,$A15,'Picks'!$U$2:$U$80,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$80,$A15,'Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$80,$A15,'Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="19">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="37">
-        <f>SUMIFS('Picks'!$BY$2:$BY$80,'Picks'!$H$2:$H$80,$A15)</f>
+      <c r="F15" s="20">
+        <f>SUMIFS('Picks'!$BY$2:$BY$90,'Picks'!$H$2:$H$90,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$80,'Picks'!$H$2:$H$80,$A15,'Picks'!$U$2:$U$80,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$90,'Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -977,31 +947,30 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$80,$A16,'Picks'!$U$2:$U$80,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$80,$A16,'Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$80,$A16,'Picks'!$U$2:$U$80,"settled",'Picks'!$V$2:$V$80,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="14">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$80,'Picks'!$H$2:$H$80,$A16)</f>
+      <c r="F16" s="15">
+        <f>SUMIFS('Picks'!$BY$2:$BY$90,'Picks'!$H$2:$H$90,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$80,'Picks'!$H$2:$H$80,$A16,'Picks'!$U$2:$U$80,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$90,'Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled"),0)</f>
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
@@ -1027,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA80"/>
+  <dimension ref="A1:CA90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1554,7 +1523,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="38" t="n"/>
+      <c r="J2" s="25" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1563,7 +1532,7 @@
       <c r="L2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M2" s="39" t="n">
+      <c r="M2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1603,11 +1572,11 @@
       <c r="X2" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="Y2" s="38" t="n"/>
+      <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="40" t="n">
+      <c r="AC2" s="30" t="n">
         <v>1.755</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1744,11 +1713,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="38" t="n"/>
+      <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL2" s="39" t="n">
+      <c r="BL2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1758,18 +1727,18 @@
         <v>0.455446</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="38" t="n"/>
-      <c r="BQ2" s="39" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="38" t="n"/>
+      <c r="BU2" s="25" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="40" t="n">
+      <c r="BX2" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="39" t="n">
+      <c r="BY2" s="27" t="n">
         <v>1.17</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1829,7 +1798,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="38" t="n"/>
+      <c r="J3" s="25" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1838,7 +1807,7 @@
       <c r="L3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M3" s="39" t="n">
+      <c r="M3" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1878,11 +1847,11 @@
       <c r="X3" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y3" s="38" t="n"/>
+      <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="40" t="n">
+      <c r="AC3" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -2019,11 +1988,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="38" t="n"/>
+      <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL3" s="39" t="n">
+      <c r="BL3" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2033,18 +2002,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="38" t="n"/>
-      <c r="BQ3" s="39" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="38" t="n"/>
+      <c r="BU3" s="25" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="40" t="n">
+      <c r="BX3" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="39" t="n">
+      <c r="BY3" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2104,7 +2073,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="25" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2113,7 +2082,7 @@
       <c r="L4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M4" s="39" t="n">
+      <c r="M4" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2153,11 +2122,11 @@
       <c r="X4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="38" t="n"/>
+      <c r="Y4" s="25" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="40" t="n">
+      <c r="AC4" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2294,11 +2263,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="38" t="n"/>
+      <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL4" s="39" t="n">
+      <c r="BL4" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2308,18 +2277,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="38" t="n"/>
-      <c r="BQ4" s="39" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="38" t="n"/>
+      <c r="BU4" s="25" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="40" t="n">
+      <c r="BX4" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" s="39" t="n">
+      <c r="BY4" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
@@ -2379,7 +2348,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="25" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2388,7 +2357,7 @@
       <c r="L5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M5" s="39" t="n">
+      <c r="M5" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2428,11 +2397,11 @@
       <c r="X5" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y5" s="38" t="n"/>
+      <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="40" t="n">
+      <c r="AC5" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2569,11 +2538,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="38" t="n"/>
+      <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL5" s="39" t="n">
+      <c r="BL5" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2583,18 +2552,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="38" t="n"/>
-      <c r="BQ5" s="39" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="38" t="n"/>
+      <c r="BU5" s="25" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="40" t="n">
+      <c r="BX5" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" s="39" t="n">
+      <c r="BY5" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
@@ -2654,7 +2623,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="25" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2663,7 +2632,7 @@
       <c r="L6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M6" s="39" t="n">
+      <c r="M6" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2703,11 +2672,11 @@
       <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="38" t="n"/>
+      <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="40" t="n">
+      <c r="AC6" s="30" t="n">
         <v>1.2019</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2844,11 +2813,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="38" t="n"/>
+      <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL6" s="39" t="n">
+      <c r="BL6" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2858,18 +2827,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="38" t="n"/>
-      <c r="BQ6" s="39" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="38" t="n"/>
+      <c r="BU6" s="25" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="40" t="n">
+      <c r="BX6" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" s="39" t="n">
+      <c r="BY6" s="27" t="n">
         <v>0.961538</v>
       </c>
       <c r="BZ6" s="24" t="inlineStr">
@@ -2929,7 +2898,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="25" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2938,7 +2907,7 @@
       <c r="L7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M7" s="39" t="n">
+      <c r="M7" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2978,11 +2947,11 @@
       <c r="X7" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" s="38" t="n"/>
+      <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="40" t="n">
+      <c r="AC7" s="30" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3119,11 +3088,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="38" t="n"/>
+      <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL7" s="39" t="n">
+      <c r="BL7" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3133,18 +3102,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="38" t="n"/>
-      <c r="BQ7" s="39" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="38" t="n"/>
+      <c r="BU7" s="25" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="40" t="n">
+      <c r="BX7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" s="39" t="n">
+      <c r="BY7" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ7" s="24" t="inlineStr">
@@ -3204,7 +3173,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="25" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3213,7 +3182,7 @@
       <c r="L8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M8" s="39" t="n">
+      <c r="M8" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3253,11 +3222,11 @@
       <c r="X8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y8" s="38" t="n"/>
+      <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="40" t="n">
+      <c r="AC8" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3394,11 +3363,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="38" t="n"/>
+      <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL8" s="39" t="n">
+      <c r="BL8" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3408,18 +3377,18 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="38" t="n"/>
-      <c r="BQ8" s="39" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="38" t="n"/>
+      <c r="BU8" s="25" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="40" t="n">
+      <c r="BX8" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" s="39" t="n">
+      <c r="BY8" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ8" s="24" t="inlineStr">
@@ -3479,7 +3448,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="25" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3488,7 +3457,7 @@
       <c r="L9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M9" s="39" t="n">
+      <c r="M9" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3528,11 +3497,11 @@
       <c r="X9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="38" t="n"/>
+      <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="40" t="n">
+      <c r="AC9" s="30" t="n">
         <v>0.9804</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
@@ -3669,11 +3638,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="38" t="n"/>
+      <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL9" s="39" t="n">
+      <c r="BL9" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3683,18 +3652,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="38" t="n"/>
-      <c r="BQ9" s="39" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="38" t="n"/>
+      <c r="BU9" s="25" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="40" t="n">
+      <c r="BX9" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" s="39" t="n">
+      <c r="BY9" s="27" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ9" s="24" t="inlineStr">
@@ -3754,7 +3723,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J10" s="38" t="n"/>
+      <c r="J10" s="25" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3763,7 +3732,7 @@
       <c r="L10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M10" s="39" t="n">
+      <c r="M10" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3803,11 +3772,11 @@
       <c r="X10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y10" s="38" t="n"/>
+      <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="40" t="n">
+      <c r="AC10" s="30" t="n">
         <v>1.2681</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -3944,11 +3913,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="38" t="n"/>
+      <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL10" s="39" t="n">
+      <c r="BL10" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -3958,18 +3927,18 @@
         <v>0.577114</v>
       </c>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="38" t="n"/>
-      <c r="BQ10" s="39" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="38" t="n"/>
+      <c r="BU10" s="25" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="40" t="n">
+      <c r="BX10" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" s="39" t="n">
+      <c r="BY10" s="27" t="n">
         <v>0.724638</v>
       </c>
       <c r="BZ10" s="24" t="inlineStr">
@@ -4029,7 +3998,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="25" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4038,7 +4007,7 @@
       <c r="L11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M11" s="39" t="n">
+      <c r="M11" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -4078,11 +4047,11 @@
       <c r="X11" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="38" t="n"/>
+      <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="40" t="n">
+      <c r="AC11" s="30" t="n">
         <v>1.275</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4219,11 +4188,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="38" t="n"/>
+      <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL11" s="39" t="n">
+      <c r="BL11" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4233,18 +4202,18 @@
         <v>0.492537</v>
       </c>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="38" t="n"/>
-      <c r="BQ11" s="39" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="38" t="n"/>
+      <c r="BU11" s="25" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="40" t="n">
+      <c r="BX11" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" s="39" t="n">
+      <c r="BY11" s="27" t="n">
         <v>1.02</v>
       </c>
       <c r="BZ11" s="24" t="inlineStr">
@@ -4304,7 +4273,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="25" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4313,7 +4282,7 @@
       <c r="L12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M12" s="39" t="n">
+      <c r="M12" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4353,11 +4322,11 @@
       <c r="X12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" s="38" t="n"/>
+      <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="40" t="n">
+      <c r="AC12" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
@@ -4494,11 +4463,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="38" t="n"/>
+      <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL12" s="39" t="n">
+      <c r="BL12" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4508,18 +4477,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="38" t="n"/>
-      <c r="BQ12" s="39" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="38" t="n"/>
+      <c r="BU12" s="25" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="40" t="n">
+      <c r="BX12" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" s="39" t="n">
+      <c r="BY12" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ12" s="24" t="inlineStr">
@@ -4579,7 +4548,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J13" s="38" t="n"/>
+      <c r="J13" s="25" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4588,7 +4557,7 @@
       <c r="L13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M13" s="39" t="n">
+      <c r="M13" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4628,11 +4597,11 @@
       <c r="X13" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" s="38" t="n"/>
+      <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="40" t="n">
+      <c r="AC13" s="30" t="n">
         <v>1.2255</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
@@ -4769,11 +4738,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="38" t="n"/>
+      <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL13" s="39" t="n">
+      <c r="BL13" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4783,18 +4752,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="38" t="n"/>
-      <c r="BQ13" s="39" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="38" t="n"/>
+      <c r="BU13" s="25" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="40" t="n">
+      <c r="BX13" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY13" s="39" t="n">
+      <c r="BY13" s="27" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ13" s="24" t="inlineStr">
@@ -4854,7 +4823,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J14" s="38" t="n"/>
+      <c r="J14" s="25" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4863,7 +4832,7 @@
       <c r="L14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M14" s="39" t="n">
+      <c r="M14" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -4903,11 +4872,11 @@
       <c r="X14" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="38" t="n"/>
+      <c r="Y14" s="25" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="40" t="n">
+      <c r="AC14" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -5044,11 +5013,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="38" t="n"/>
+      <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL14" s="39" t="n">
+      <c r="BL14" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -5058,18 +5027,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="38" t="n"/>
-      <c r="BQ14" s="39" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="38" t="n"/>
+      <c r="BU14" s="25" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="40" t="n">
+      <c r="BX14" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY14" s="39" t="n">
+      <c r="BY14" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ14" s="24" t="inlineStr">
@@ -5129,7 +5098,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="38" t="n"/>
+      <c r="J15" s="25" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5138,7 +5107,7 @@
       <c r="L15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M15" s="39" t="n">
+      <c r="M15" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -5178,11 +5147,11 @@
       <c r="X15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="38" t="n"/>
+      <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="40" t="n">
+      <c r="AC15" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
@@ -5319,11 +5288,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="38" t="n"/>
+      <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL15" s="39" t="n">
+      <c r="BL15" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5333,18 +5302,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="38" t="n"/>
-      <c r="BQ15" s="39" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="38" t="n"/>
+      <c r="BU15" s="25" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="40" t="n">
+      <c r="BX15" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY15" s="39" t="n">
+      <c r="BY15" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ15" s="24" t="inlineStr">
@@ -5404,7 +5373,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J16" s="38" t="n"/>
+      <c r="J16" s="25" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5413,7 +5382,7 @@
       <c r="L16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M16" s="39" t="n">
+      <c r="M16" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5453,11 +5422,11 @@
       <c r="X16" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" s="38" t="n"/>
+      <c r="Y16" s="25" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="40" t="n">
+      <c r="AC16" s="30" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
@@ -5594,11 +5563,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="38" t="n"/>
+      <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL16" s="39" t="n">
+      <c r="BL16" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5608,18 +5577,18 @@
         <v>0.522388</v>
       </c>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="38" t="n"/>
-      <c r="BQ16" s="39" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="38" t="n"/>
+      <c r="BU16" s="25" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="40" t="n">
+      <c r="BX16" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY16" s="39" t="n">
+      <c r="BY16" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ16" s="24" t="inlineStr">
@@ -5679,7 +5648,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="38" t="n"/>
+      <c r="J17" s="25" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5688,7 +5657,7 @@
       <c r="L17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M17" s="39" t="n">
+      <c r="M17" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5728,11 +5697,11 @@
       <c r="X17" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y17" s="38" t="n"/>
+      <c r="Y17" s="25" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="40" t="n">
+      <c r="AC17" s="30" t="n">
         <v>0.9258999999999999</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
@@ -5869,11 +5838,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ17" s="38" t="n"/>
+      <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL17" s="39" t="n">
+      <c r="BL17" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -5883,18 +5852,18 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="38" t="n"/>
-      <c r="BQ17" s="39" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="38" t="n"/>
+      <c r="BU17" s="25" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="40" t="n">
+      <c r="BX17" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY17" s="39" t="n">
+      <c r="BY17" s="27" t="n">
         <v>0.925926</v>
       </c>
       <c r="BZ17" s="24" t="inlineStr">
@@ -5954,7 +5923,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="38" t="n"/>
+      <c r="J18" s="25" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5963,7 +5932,7 @@
       <c r="L18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="M18" s="39" t="n">
+      <c r="M18" s="27" t="n">
         <v>2.11</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -6003,11 +5972,11 @@
       <c r="X18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y18" s="38" t="n"/>
+      <c r="Y18" s="25" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="40" t="n">
+      <c r="AC18" s="30" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
@@ -6144,11 +6113,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ18" s="38" t="n"/>
+      <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="BL18" s="39" t="n">
+      <c r="BL18" s="27" t="n">
         <v>2.11</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -6158,18 +6127,18 @@
         <v>0.472637</v>
       </c>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="38" t="n"/>
-      <c r="BQ18" s="39" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="38" t="n"/>
+      <c r="BU18" s="25" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="40" t="n">
+      <c r="BX18" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" s="39" t="n">
+      <c r="BY18" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ18" s="24" t="inlineStr">
@@ -6229,7 +6198,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="38" t="n"/>
+      <c r="J19" s="25" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6238,7 +6207,7 @@
       <c r="L19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M19" s="39" t="n">
+      <c r="M19" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -6278,11 +6247,11 @@
       <c r="X19" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y19" s="38" t="n"/>
+      <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="40" t="n">
+      <c r="AC19" s="30" t="n">
         <v>1.2</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
@@ -6419,11 +6388,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ19" s="38" t="n"/>
+      <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL19" s="39" t="n">
+      <c r="BL19" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -6433,18 +6402,18 @@
         <v>0.552239</v>
       </c>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="38" t="n"/>
-      <c r="BQ19" s="39" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="38" t="n"/>
+      <c r="BU19" s="25" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="40" t="n">
+      <c r="BX19" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY19" s="39" t="n">
+      <c r="BY19" s="27" t="n">
         <v>0.8</v>
       </c>
       <c r="BZ19" s="24" t="inlineStr">
@@ -6504,7 +6473,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J20" s="38" t="n"/>
+      <c r="J20" s="25" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6513,7 +6482,7 @@
       <c r="L20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="M20" s="39" t="n">
+      <c r="M20" s="27" t="n">
         <v>2.06</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6553,11 +6522,11 @@
       <c r="X20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y20" s="38" t="n"/>
+      <c r="Y20" s="25" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="40" t="n">
+      <c r="AC20" s="30" t="n">
         <v>0.795</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
@@ -6694,11 +6663,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ20" s="38" t="n"/>
+      <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="BL20" s="39" t="n">
+      <c r="BL20" s="27" t="n">
         <v>2.06</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -6708,18 +6677,18 @@
         <v>0.482587</v>
       </c>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="38" t="n"/>
-      <c r="BQ20" s="39" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="38" t="n"/>
+      <c r="BU20" s="25" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="40" t="n">
+      <c r="BX20" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" s="39" t="n">
+      <c r="BY20" s="27" t="n">
         <v>1.06</v>
       </c>
       <c r="BZ20" s="24" t="inlineStr">
@@ -6779,7 +6748,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J21" s="38" t="n"/>
+      <c r="J21" s="25" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6788,7 +6757,7 @@
       <c r="L21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M21" s="39" t="n">
+      <c r="M21" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
@@ -6830,11 +6799,11 @@
       <c r="X21" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y21" s="38" t="n"/>
+      <c r="Y21" s="25" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="40" t="n">
+      <c r="AC21" s="30" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
@@ -6893,11 +6862,11 @@
         </is>
       </c>
       <c r="BI21" s="24" t="n"/>
-      <c r="BJ21" s="38" t="n"/>
+      <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL21" s="39" t="n">
+      <c r="BL21" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
@@ -6907,16 +6876,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="38" t="n"/>
-      <c r="BQ21" s="39" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="38" t="n"/>
+      <c r="BU21" s="25" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="40" t="n"/>
-      <c r="BY21" s="39" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
     </row>
@@ -6966,7 +6935,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="38" t="n"/>
+      <c r="J22" s="25" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6975,7 +6944,7 @@
       <c r="L22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M22" s="39" t="n">
+      <c r="M22" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N22" s="28" t="n">
@@ -7017,11 +6986,11 @@
       <c r="X22" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y22" s="38" t="n"/>
+      <c r="Y22" s="25" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="40" t="n">
+      <c r="AC22" s="30" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
@@ -7080,11 +7049,11 @@
         </is>
       </c>
       <c r="BI22" s="24" t="n"/>
-      <c r="BJ22" s="38" t="n"/>
+      <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL22" s="39" t="n">
+      <c r="BL22" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM22" s="28" t="n">
@@ -7094,16 +7063,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="38" t="n"/>
-      <c r="BQ22" s="39" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="38" t="n"/>
+      <c r="BU22" s="25" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="40" t="n"/>
-      <c r="BY22" s="39" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
     </row>
@@ -7153,7 +7122,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J23" s="38" t="n"/>
+      <c r="J23" s="25" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7162,7 +7131,7 @@
       <c r="L23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M23" s="39" t="n">
+      <c r="M23" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="N23" s="28" t="n">
@@ -7204,11 +7173,11 @@
       <c r="X23" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y23" s="38" t="n"/>
+      <c r="Y23" s="25" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="40" t="n">
+      <c r="AC23" s="30" t="n">
         <v>1.2411</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
@@ -7267,11 +7236,11 @@
         </is>
       </c>
       <c r="BI23" s="24" t="n"/>
-      <c r="BJ23" s="38" t="n"/>
+      <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL23" s="39" t="n">
+      <c r="BL23" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM23" s="28" t="n">
@@ -7281,16 +7250,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="38" t="n"/>
-      <c r="BQ23" s="39" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="38" t="n"/>
+      <c r="BU23" s="25" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="40" t="n"/>
-      <c r="BY23" s="39" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
     </row>
@@ -7340,7 +7309,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="38" t="n"/>
+      <c r="J24" s="25" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7349,7 +7318,7 @@
       <c r="L24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M24" s="39" t="n">
+      <c r="M24" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N24" s="28" t="n">
@@ -7391,11 +7360,11 @@
       <c r="X24" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" s="38" t="n"/>
+      <c r="Y24" s="25" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="40" t="n">
+      <c r="AC24" s="30" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -7454,11 +7423,11 @@
         </is>
       </c>
       <c r="BI24" s="24" t="n"/>
-      <c r="BJ24" s="38" t="n"/>
+      <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL24" s="39" t="n">
+      <c r="BL24" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM24" s="28" t="n">
@@ -7468,16 +7437,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="38" t="n"/>
-      <c r="BQ24" s="39" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="38" t="n"/>
+      <c r="BU24" s="25" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="40" t="n"/>
-      <c r="BY24" s="39" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
     </row>
@@ -7527,7 +7496,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J25" s="38" t="n"/>
+      <c r="J25" s="25" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7536,7 +7505,7 @@
       <c r="L25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M25" s="39" t="n">
+      <c r="M25" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
@@ -7578,11 +7547,11 @@
       <c r="X25" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" s="38" t="n"/>
+      <c r="Y25" s="25" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="40" t="n">
+      <c r="AC25" s="30" t="n">
         <v>1.3</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
@@ -7641,11 +7610,11 @@
         </is>
       </c>
       <c r="BI25" s="24" t="n"/>
-      <c r="BJ25" s="38" t="n"/>
+      <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL25" s="39" t="n">
+      <c r="BL25" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
@@ -7655,16 +7624,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="38" t="n"/>
-      <c r="BQ25" s="39" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="38" t="n"/>
+      <c r="BU25" s="25" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="40" t="n"/>
-      <c r="BY25" s="39" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
     </row>
@@ -7714,7 +7683,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J26" s="38" t="n"/>
+      <c r="J26" s="25" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7723,7 +7692,7 @@
       <c r="L26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M26" s="39" t="n">
+      <c r="M26" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N26" s="28" t="n">
@@ -7765,11 +7734,11 @@
       <c r="X26" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26" s="38" t="n"/>
+      <c r="Y26" s="25" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="40" t="n">
+      <c r="AC26" s="30" t="n">
         <v>0.9615</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
@@ -7828,11 +7797,11 @@
         </is>
       </c>
       <c r="BI26" s="24" t="n"/>
-      <c r="BJ26" s="38" t="n"/>
+      <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL26" s="39" t="n">
+      <c r="BL26" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM26" s="28" t="n">
@@ -7842,16 +7811,16 @@
         <v>0.507463</v>
       </c>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="38" t="n"/>
-      <c r="BQ26" s="39" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="38" t="n"/>
+      <c r="BU26" s="25" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="40" t="n"/>
-      <c r="BY26" s="39" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
       <c r="BZ26" s="24" t="n"/>
       <c r="CA26" s="31" t="n"/>
     </row>
@@ -7901,7 +7870,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="38" t="n"/>
+      <c r="J27" s="25" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7910,7 +7879,7 @@
       <c r="L27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="M27" s="39" t="n">
+      <c r="M27" s="27" t="n">
         <v>2.2</v>
       </c>
       <c r="N27" s="28" t="n">
@@ -7952,11 +7921,11 @@
       <c r="X27" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" s="38" t="n"/>
+      <c r="Y27" s="25" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="40" t="n">
+      <c r="AC27" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
@@ -8015,11 +7984,11 @@
         </is>
       </c>
       <c r="BI27" s="24" t="n"/>
-      <c r="BJ27" s="38" t="n"/>
+      <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="BL27" s="39" t="n">
+      <c r="BL27" s="27" t="n">
         <v>2.2</v>
       </c>
       <c r="BM27" s="28" t="n">
@@ -8029,16 +7998,16 @@
         <v>0.452736</v>
       </c>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="38" t="n"/>
-      <c r="BQ27" s="39" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="38" t="n"/>
+      <c r="BU27" s="25" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="40" t="n"/>
-      <c r="BY27" s="39" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
       <c r="BZ27" s="24" t="n"/>
       <c r="CA27" s="31" t="n"/>
     </row>
@@ -8088,7 +8057,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="38" t="n"/>
+      <c r="J28" s="25" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -8097,7 +8066,7 @@
       <c r="L28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="39" t="n">
+      <c r="M28" s="27" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -8139,11 +8108,11 @@
       <c r="X28" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="38" t="n"/>
+      <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="40" t="n">
+      <c r="AC28" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
@@ -8202,11 +8171,11 @@
         </is>
       </c>
       <c r="BI28" s="24" t="n"/>
-      <c r="BJ28" s="38" t="n"/>
+      <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL28" s="39" t="n">
+      <c r="BL28" s="27" t="n">
         <v>2</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -8216,16 +8185,16 @@
         <v>0.497512</v>
       </c>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="38" t="n"/>
-      <c r="BQ28" s="39" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="38" t="n"/>
+      <c r="BU28" s="25" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="40" t="n"/>
-      <c r="BY28" s="39" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
       <c r="BZ28" s="24" t="n"/>
       <c r="CA28" s="31" t="n"/>
     </row>
@@ -8275,7 +8244,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J29" s="38" t="n"/>
+      <c r="J29" s="25" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8284,7 +8253,7 @@
       <c r="L29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M29" s="39" t="n">
+      <c r="M29" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -8324,11 +8293,11 @@
       <c r="X29" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y29" s="38" t="n"/>
+      <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="40" t="n">
+      <c r="AC29" s="30" t="n">
         <v>1.35</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
@@ -8465,11 +8434,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ29" s="38" t="n"/>
+      <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL29" s="39" t="n">
+      <c r="BL29" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -8479,18 +8448,18 @@
         <v>0.477612</v>
       </c>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="38" t="n"/>
-      <c r="BQ29" s="39" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="38" t="n"/>
+      <c r="BU29" s="25" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="40" t="n">
+      <c r="BX29" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY29" s="39" t="n">
+      <c r="BY29" s="27" t="n">
         <v>1.08</v>
       </c>
       <c r="BZ29" s="24" t="inlineStr">
@@ -8550,7 +8519,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J30" s="38" t="n"/>
+      <c r="J30" s="25" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8559,7 +8528,7 @@
       <c r="L30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M30" s="39" t="n">
+      <c r="M30" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -8599,11 +8568,11 @@
       <c r="X30" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y30" s="38" t="n"/>
+      <c r="Y30" s="25" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="40" t="n">
+      <c r="AC30" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
@@ -8740,11 +8709,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ30" s="38" t="n"/>
+      <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL30" s="39" t="n">
+      <c r="BL30" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -8754,18 +8723,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="38" t="n"/>
-      <c r="BQ30" s="39" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="38" t="n"/>
+      <c r="BU30" s="25" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="40" t="n">
+      <c r="BX30" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY30" s="39" t="n">
+      <c r="BY30" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ30" s="24" t="inlineStr">
@@ -8825,7 +8794,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="38" t="n"/>
+      <c r="J31" s="25" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8834,7 +8803,7 @@
       <c r="L31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="M31" s="39" t="n">
+      <c r="M31" s="27" t="n">
         <v>2.3</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -8874,11 +8843,11 @@
       <c r="X31" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y31" s="38" t="n"/>
+      <c r="Y31" s="25" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="40" t="n">
+      <c r="AC31" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
@@ -9015,11 +8984,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ31" s="38" t="n"/>
+      <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="BL31" s="39" t="n">
+      <c r="BL31" s="27" t="n">
         <v>2.3</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -9029,18 +8998,18 @@
         <v>0.432836</v>
       </c>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="38" t="n"/>
-      <c r="BQ31" s="39" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="38" t="n"/>
+      <c r="BU31" s="25" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="40" t="n">
+      <c r="BX31" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY31" s="39" t="n">
+      <c r="BY31" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ31" s="24" t="inlineStr">
@@ -9100,7 +9069,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J32" s="38" t="n"/>
+      <c r="J32" s="25" t="n"/>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9109,7 +9078,7 @@
       <c r="L32" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M32" s="39" t="n">
+      <c r="M32" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="N32" s="28" t="n">
@@ -9149,11 +9118,11 @@
       <c r="X32" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y32" s="38" t="n"/>
+      <c r="Y32" s="25" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="40" t="n">
+      <c r="AC32" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD32" s="24" t="inlineStr">
@@ -9290,11 +9259,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ32" s="38" t="n"/>
+      <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL32" s="39" t="n">
+      <c r="BL32" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="BM32" s="28" t="n">
@@ -9304,16 +9273,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="38" t="n"/>
-      <c r="BQ32" s="39" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
       <c r="BR32" s="28" t="n"/>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="38" t="n"/>
+      <c r="BU32" s="25" t="n"/>
       <c r="BV32" s="29" t="n"/>
       <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="40" t="n"/>
-      <c r="BY32" s="39" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
       <c r="BZ32" s="24" t="n"/>
       <c r="CA32" s="31" t="n"/>
     </row>
@@ -9363,7 +9332,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J33" s="38" t="n"/>
+      <c r="J33" s="25" t="n"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9372,7 +9341,7 @@
       <c r="L33" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M33" s="39" t="n">
+      <c r="M33" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="N33" s="28" t="n">
@@ -9412,11 +9381,11 @@
       <c r="X33" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y33" s="38" t="n"/>
+      <c r="Y33" s="25" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="40" t="n">
+      <c r="AC33" s="30" t="n">
         <v>-1.75</v>
       </c>
       <c r="AD33" s="24" t="inlineStr">
@@ -9553,11 +9522,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ33" s="38" t="n"/>
+      <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL33" s="39" t="n">
+      <c r="BL33" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="BM33" s="28" t="n">
@@ -9567,16 +9536,16 @@
         <v>0.457711</v>
       </c>
       <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="38" t="n"/>
-      <c r="BQ33" s="39" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
       <c r="BR33" s="28" t="n"/>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="38" t="n"/>
+      <c r="BU33" s="25" t="n"/>
       <c r="BV33" s="29" t="n"/>
       <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="40" t="n"/>
-      <c r="BY33" s="39" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
       <c r="BZ33" s="24" t="n"/>
       <c r="CA33" s="31" t="n"/>
     </row>
@@ -9626,7 +9595,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J34" s="38" t="n"/>
+      <c r="J34" s="25" t="n"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9635,7 +9604,7 @@
       <c r="L34" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="M34" s="39" t="n">
+      <c r="M34" s="27" t="n">
         <v>1.854701</v>
       </c>
       <c r="N34" s="28" t="n">
@@ -9675,11 +9644,11 @@
       <c r="X34" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y34" s="38" t="n"/>
+      <c r="Y34" s="25" t="n"/>
       <c r="Z34" s="26" t="n"/>
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="40" t="n">
+      <c r="AC34" s="30" t="n">
         <v>0.8547</v>
       </c>
       <c r="AD34" s="24" t="inlineStr">
@@ -9816,11 +9785,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ34" s="38" t="n"/>
+      <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="BL34" s="39" t="n">
+      <c r="BL34" s="27" t="n">
         <v>1.854701</v>
       </c>
       <c r="BM34" s="28" t="n">
@@ -9830,16 +9799,16 @@
         <v>0.537313</v>
       </c>
       <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="38" t="n"/>
-      <c r="BQ34" s="39" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
       <c r="BR34" s="28" t="n"/>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="38" t="n"/>
+      <c r="BU34" s="25" t="n"/>
       <c r="BV34" s="29" t="n"/>
       <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="40" t="n"/>
-      <c r="BY34" s="39" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
       <c r="BZ34" s="24" t="n"/>
       <c r="CA34" s="31" t="n"/>
     </row>
@@ -9889,7 +9858,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J35" s="38" t="n"/>
+      <c r="J35" s="25" t="n"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9898,7 +9867,7 @@
       <c r="L35" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M35" s="39" t="n">
+      <c r="M35" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="N35" s="28" t="n">
@@ -9938,11 +9907,11 @@
       <c r="X35" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y35" s="38" t="n"/>
+      <c r="Y35" s="25" t="n"/>
       <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="40" t="n">
+      <c r="AC35" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD35" s="24" t="inlineStr">
@@ -10079,11 +10048,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ35" s="38" t="n"/>
+      <c r="BJ35" s="25" t="n"/>
       <c r="BK35" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL35" s="39" t="n">
+      <c r="BL35" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="BM35" s="28" t="n">
@@ -10093,16 +10062,16 @@
         <v>0.457711</v>
       </c>
       <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="38" t="n"/>
-      <c r="BQ35" s="39" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
       <c r="BR35" s="28" t="n"/>
       <c r="BS35" s="28" t="n"/>
       <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="38" t="n"/>
+      <c r="BU35" s="25" t="n"/>
       <c r="BV35" s="29" t="n"/>
       <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="40" t="n"/>
-      <c r="BY35" s="39" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
       <c r="BZ35" s="24" t="n"/>
       <c r="CA35" s="31" t="n"/>
     </row>
@@ -10152,7 +10121,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J36" s="38" t="n"/>
+      <c r="J36" s="25" t="n"/>
       <c r="K36" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10161,7 +10130,7 @@
       <c r="L36" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M36" s="39" t="n">
+      <c r="M36" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N36" s="28" t="n">
@@ -10201,11 +10170,11 @@
       <c r="X36" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y36" s="38" t="n"/>
+      <c r="Y36" s="25" t="n"/>
       <c r="Z36" s="26" t="n"/>
       <c r="AA36" s="28" t="n"/>
       <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="40" t="n">
+      <c r="AC36" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD36" s="24" t="inlineStr">
@@ -10342,11 +10311,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ36" s="38" t="n"/>
+      <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL36" s="39" t="n">
+      <c r="BL36" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM36" s="28" t="n">
@@ -10356,16 +10325,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="38" t="n"/>
-      <c r="BQ36" s="39" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
       <c r="BR36" s="28" t="n"/>
       <c r="BS36" s="28" t="n"/>
       <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="38" t="n"/>
+      <c r="BU36" s="25" t="n"/>
       <c r="BV36" s="29" t="n"/>
       <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="40" t="n"/>
-      <c r="BY36" s="39" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
       <c r="BZ36" s="24" t="n"/>
       <c r="CA36" s="31" t="n"/>
     </row>
@@ -10415,7 +10384,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J37" s="38" t="n"/>
+      <c r="J37" s="25" t="n"/>
       <c r="K37" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10424,7 +10393,7 @@
       <c r="L37" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="M37" s="39" t="n">
+      <c r="M37" s="27" t="n">
         <v>1.819672</v>
       </c>
       <c r="N37" s="28" t="n">
@@ -10464,11 +10433,11 @@
       <c r="X37" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y37" s="38" t="n"/>
+      <c r="Y37" s="25" t="n"/>
       <c r="Z37" s="26" t="n"/>
       <c r="AA37" s="28" t="n"/>
       <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="40" t="n">
+      <c r="AC37" s="30" t="n">
         <v>1.4344</v>
       </c>
       <c r="AD37" s="24" t="inlineStr">
@@ -10605,11 +10574,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ37" s="38" t="n"/>
+      <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="BL37" s="39" t="n">
+      <c r="BL37" s="27" t="n">
         <v>1.819672</v>
       </c>
       <c r="BM37" s="28" t="n">
@@ -10619,16 +10588,16 @@
         <v>0.547264</v>
       </c>
       <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="38" t="n"/>
-      <c r="BQ37" s="39" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
       <c r="BR37" s="28" t="n"/>
       <c r="BS37" s="28" t="n"/>
       <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="38" t="n"/>
+      <c r="BU37" s="25" t="n"/>
       <c r="BV37" s="29" t="n"/>
       <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="40" t="n"/>
-      <c r="BY37" s="39" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
       <c r="BZ37" s="24" t="n"/>
       <c r="CA37" s="31" t="n"/>
     </row>
@@ -10678,7 +10647,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J38" s="38" t="n"/>
+      <c r="J38" s="25" t="n"/>
       <c r="K38" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10687,7 +10656,7 @@
       <c r="L38" s="26" t="n">
         <v>115</v>
       </c>
-      <c r="M38" s="39" t="n">
+      <c r="M38" s="27" t="n">
         <v>2.15</v>
       </c>
       <c r="N38" s="28" t="n">
@@ -10727,11 +10696,11 @@
       <c r="X38" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y38" s="38" t="n"/>
+      <c r="Y38" s="25" t="n"/>
       <c r="Z38" s="26" t="n"/>
       <c r="AA38" s="28" t="n"/>
       <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="40" t="n">
+      <c r="AC38" s="30" t="n">
         <v>0.8625</v>
       </c>
       <c r="AD38" s="24" t="inlineStr">
@@ -10868,11 +10837,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ38" s="38" t="n"/>
+      <c r="BJ38" s="25" t="n"/>
       <c r="BK38" s="26" t="n">
         <v>115</v>
       </c>
-      <c r="BL38" s="39" t="n">
+      <c r="BL38" s="27" t="n">
         <v>2.15</v>
       </c>
       <c r="BM38" s="28" t="n">
@@ -10882,16 +10851,16 @@
         <v>0.462687</v>
       </c>
       <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="38" t="n"/>
-      <c r="BQ38" s="39" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
       <c r="BR38" s="28" t="n"/>
       <c r="BS38" s="28" t="n"/>
       <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="38" t="n"/>
+      <c r="BU38" s="25" t="n"/>
       <c r="BV38" s="29" t="n"/>
       <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="40" t="n"/>
-      <c r="BY38" s="39" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
       <c r="BZ38" s="24" t="n"/>
       <c r="CA38" s="31" t="n"/>
     </row>
@@ -10941,7 +10910,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J39" s="38" t="n"/>
+      <c r="J39" s="25" t="n"/>
       <c r="K39" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10950,7 +10919,7 @@
       <c r="L39" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="M39" s="39" t="n">
+      <c r="M39" s="27" t="n">
         <v>1.666667</v>
       </c>
       <c r="N39" s="28" t="n">
@@ -10990,11 +10959,11 @@
       <c r="X39" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y39" s="38" t="n"/>
+      <c r="Y39" s="25" t="n"/>
       <c r="Z39" s="26" t="n"/>
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="40" t="n">
+      <c r="AC39" s="30" t="n">
         <v>1</v>
       </c>
       <c r="AD39" s="24" t="inlineStr">
@@ -11131,11 +11100,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ39" s="38" t="n"/>
+      <c r="BJ39" s="25" t="n"/>
       <c r="BK39" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="BL39" s="39" t="n">
+      <c r="BL39" s="27" t="n">
         <v>1.666667</v>
       </c>
       <c r="BM39" s="28" t="n">
@@ -11145,16 +11114,16 @@
         <v>0.597015</v>
       </c>
       <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="38" t="n"/>
-      <c r="BQ39" s="39" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n"/>
       <c r="BR39" s="28" t="n"/>
       <c r="BS39" s="28" t="n"/>
       <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="38" t="n"/>
+      <c r="BU39" s="25" t="n"/>
       <c r="BV39" s="29" t="n"/>
       <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="40" t="n"/>
-      <c r="BY39" s="39" t="n"/>
+      <c r="BX39" s="30" t="n"/>
+      <c r="BY39" s="27" t="n"/>
       <c r="BZ39" s="24" t="n"/>
       <c r="CA39" s="31" t="n"/>
     </row>
@@ -11204,7 +11173,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J40" s="38" t="n"/>
+      <c r="J40" s="25" t="n"/>
       <c r="K40" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11213,7 +11182,7 @@
       <c r="L40" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M40" s="39" t="n">
+      <c r="M40" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="N40" s="28" t="n">
@@ -11253,11 +11222,11 @@
       <c r="X40" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y40" s="38" t="n"/>
+      <c r="Y40" s="25" t="n"/>
       <c r="Z40" s="26" t="n"/>
       <c r="AA40" s="28" t="n"/>
       <c r="AB40" s="28" t="n"/>
-      <c r="AC40" s="40" t="n">
+      <c r="AC40" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD40" s="24" t="inlineStr">
@@ -11394,11 +11363,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ40" s="38" t="n"/>
+      <c r="BJ40" s="25" t="n"/>
       <c r="BK40" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL40" s="39" t="n">
+      <c r="BL40" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM40" s="28" t="n">
@@ -11408,16 +11377,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO40" s="28" t="n"/>
-      <c r="BP40" s="38" t="n"/>
-      <c r="BQ40" s="39" t="n"/>
+      <c r="BP40" s="25" t="n"/>
+      <c r="BQ40" s="27" t="n"/>
       <c r="BR40" s="28" t="n"/>
       <c r="BS40" s="28" t="n"/>
       <c r="BT40" s="28" t="n"/>
-      <c r="BU40" s="38" t="n"/>
+      <c r="BU40" s="25" t="n"/>
       <c r="BV40" s="29" t="n"/>
       <c r="BW40" s="24" t="n"/>
-      <c r="BX40" s="40" t="n"/>
-      <c r="BY40" s="39" t="n"/>
+      <c r="BX40" s="30" t="n"/>
+      <c r="BY40" s="27" t="n"/>
       <c r="BZ40" s="24" t="n"/>
       <c r="CA40" s="31" t="n"/>
     </row>
@@ -11467,7 +11436,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J41" s="38" t="n"/>
+      <c r="J41" s="25" t="n"/>
       <c r="K41" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11476,7 +11445,7 @@
       <c r="L41" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="M41" s="39" t="n">
+      <c r="M41" s="27" t="n">
         <v>1.613497</v>
       </c>
       <c r="N41" s="28" t="n">
@@ -11516,11 +11485,11 @@
       <c r="X41" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y41" s="38" t="n"/>
+      <c r="Y41" s="25" t="n"/>
       <c r="Z41" s="26" t="n"/>
       <c r="AA41" s="28" t="n"/>
       <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="40" t="n">
+      <c r="AC41" s="30" t="n">
         <v>0.9202</v>
       </c>
       <c r="AD41" s="24" t="inlineStr">
@@ -11657,11 +11626,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ41" s="38" t="n"/>
+      <c r="BJ41" s="25" t="n"/>
       <c r="BK41" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="BL41" s="39" t="n">
+      <c r="BL41" s="27" t="n">
         <v>1.613497</v>
       </c>
       <c r="BM41" s="28" t="n">
@@ -11671,16 +11640,16 @@
         <v>0.616915</v>
       </c>
       <c r="BO41" s="28" t="n"/>
-      <c r="BP41" s="38" t="n"/>
-      <c r="BQ41" s="39" t="n"/>
+      <c r="BP41" s="25" t="n"/>
+      <c r="BQ41" s="27" t="n"/>
       <c r="BR41" s="28" t="n"/>
       <c r="BS41" s="28" t="n"/>
       <c r="BT41" s="28" t="n"/>
-      <c r="BU41" s="38" t="n"/>
+      <c r="BU41" s="25" t="n"/>
       <c r="BV41" s="29" t="n"/>
       <c r="BW41" s="24" t="n"/>
-      <c r="BX41" s="40" t="n"/>
-      <c r="BY41" s="39" t="n"/>
+      <c r="BX41" s="30" t="n"/>
+      <c r="BY41" s="27" t="n"/>
       <c r="BZ41" s="24" t="n"/>
       <c r="CA41" s="31" t="n"/>
     </row>
@@ -11730,7 +11699,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J42" s="38" t="n"/>
+      <c r="J42" s="25" t="n"/>
       <c r="K42" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11739,7 +11708,7 @@
       <c r="L42" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M42" s="39" t="n">
+      <c r="M42" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="N42" s="28" t="n">
@@ -11779,11 +11748,11 @@
       <c r="X42" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y42" s="38" t="n"/>
+      <c r="Y42" s="25" t="n"/>
       <c r="Z42" s="26" t="n"/>
       <c r="AA42" s="28" t="n"/>
       <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="40" t="n">
+      <c r="AC42" s="30" t="n">
         <v>0.6757</v>
       </c>
       <c r="AD42" s="24" t="inlineStr">
@@ -11920,11 +11889,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ42" s="38" t="n"/>
+      <c r="BJ42" s="25" t="n"/>
       <c r="BK42" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL42" s="39" t="n">
+      <c r="BL42" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM42" s="28" t="n">
@@ -11934,16 +11903,16 @@
         <v>0.522388</v>
       </c>
       <c r="BO42" s="28" t="n"/>
-      <c r="BP42" s="38" t="n"/>
-      <c r="BQ42" s="39" t="n"/>
+      <c r="BP42" s="25" t="n"/>
+      <c r="BQ42" s="27" t="n"/>
       <c r="BR42" s="28" t="n"/>
       <c r="BS42" s="28" t="n"/>
       <c r="BT42" s="28" t="n"/>
-      <c r="BU42" s="38" t="n"/>
+      <c r="BU42" s="25" t="n"/>
       <c r="BV42" s="29" t="n"/>
       <c r="BW42" s="24" t="n"/>
-      <c r="BX42" s="40" t="n"/>
-      <c r="BY42" s="39" t="n"/>
+      <c r="BX42" s="30" t="n"/>
+      <c r="BY42" s="27" t="n"/>
       <c r="BZ42" s="24" t="n"/>
       <c r="CA42" s="31" t="n"/>
     </row>
@@ -11993,7 +11962,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J43" s="38" t="n"/>
+      <c r="J43" s="25" t="n"/>
       <c r="K43" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12002,7 +11971,7 @@
       <c r="L43" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M43" s="39" t="n">
+      <c r="M43" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N43" s="28" t="n">
@@ -12042,11 +12011,11 @@
       <c r="X43" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y43" s="38" t="n"/>
+      <c r="Y43" s="25" t="n"/>
       <c r="Z43" s="26" t="n"/>
       <c r="AA43" s="28" t="n"/>
       <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="40" t="n">
+      <c r="AC43" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD43" s="24" t="inlineStr">
@@ -12183,11 +12152,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ43" s="38" t="n"/>
+      <c r="BJ43" s="25" t="n"/>
       <c r="BK43" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL43" s="39" t="n">
+      <c r="BL43" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM43" s="28" t="n">
@@ -12197,16 +12166,16 @@
         <v>0.517413</v>
       </c>
       <c r="BO43" s="28" t="n"/>
-      <c r="BP43" s="38" t="n"/>
-      <c r="BQ43" s="39" t="n"/>
+      <c r="BP43" s="25" t="n"/>
+      <c r="BQ43" s="27" t="n"/>
       <c r="BR43" s="28" t="n"/>
       <c r="BS43" s="28" t="n"/>
       <c r="BT43" s="28" t="n"/>
-      <c r="BU43" s="38" t="n"/>
+      <c r="BU43" s="25" t="n"/>
       <c r="BV43" s="29" t="n"/>
       <c r="BW43" s="24" t="n"/>
-      <c r="BX43" s="40" t="n"/>
-      <c r="BY43" s="39" t="n"/>
+      <c r="BX43" s="30" t="n"/>
+      <c r="BY43" s="27" t="n"/>
       <c r="BZ43" s="24" t="n"/>
       <c r="CA43" s="31" t="n"/>
     </row>
@@ -12256,7 +12225,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J44" s="38" t="n"/>
+      <c r="J44" s="25" t="n"/>
       <c r="K44" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12265,7 +12234,7 @@
       <c r="L44" s="26" t="n">
         <v>-400</v>
       </c>
-      <c r="M44" s="39" t="n">
+      <c r="M44" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="N44" s="28" t="n">
@@ -12305,11 +12274,11 @@
       <c r="X44" s="26" t="n">
         <v>90</v>
       </c>
-      <c r="Y44" s="38" t="n"/>
+      <c r="Y44" s="25" t="n"/>
       <c r="Z44" s="26" t="n"/>
       <c r="AA44" s="28" t="n"/>
       <c r="AB44" s="28" t="n"/>
-      <c r="AC44" s="40" t="n">
+      <c r="AC44" s="30" t="n">
         <v>0.5</v>
       </c>
       <c r="AD44" s="24" t="inlineStr">
@@ -12446,11 +12415,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ44" s="38" t="n"/>
+      <c r="BJ44" s="25" t="n"/>
       <c r="BK44" s="26" t="n">
         <v>-400</v>
       </c>
-      <c r="BL44" s="39" t="n">
+      <c r="BL44" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="BM44" s="28" t="n">
@@ -12460,16 +12429,16 @@
         <v>0.792079</v>
       </c>
       <c r="BO44" s="28" t="n"/>
-      <c r="BP44" s="38" t="n"/>
-      <c r="BQ44" s="39" t="n"/>
+      <c r="BP44" s="25" t="n"/>
+      <c r="BQ44" s="27" t="n"/>
       <c r="BR44" s="28" t="n"/>
       <c r="BS44" s="28" t="n"/>
       <c r="BT44" s="28" t="n"/>
-      <c r="BU44" s="38" t="n"/>
+      <c r="BU44" s="25" t="n"/>
       <c r="BV44" s="29" t="n"/>
       <c r="BW44" s="24" t="n"/>
-      <c r="BX44" s="40" t="n"/>
-      <c r="BY44" s="39" t="n"/>
+      <c r="BX44" s="30" t="n"/>
+      <c r="BY44" s="27" t="n"/>
       <c r="BZ44" s="24" t="n"/>
       <c r="CA44" s="31" t="n"/>
     </row>
@@ -12519,7 +12488,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J45" s="38" t="n"/>
+      <c r="J45" s="25" t="n"/>
       <c r="K45" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12528,7 +12497,7 @@
       <c r="L45" s="26" t="n">
         <v>-426</v>
       </c>
-      <c r="M45" s="39" t="n">
+      <c r="M45" s="27" t="n">
         <v>1.234742</v>
       </c>
       <c r="N45" s="28" t="n">
@@ -12568,11 +12537,11 @@
       <c r="X45" s="26" t="n">
         <v>93</v>
       </c>
-      <c r="Y45" s="38" t="n"/>
+      <c r="Y45" s="25" t="n"/>
       <c r="Z45" s="26" t="n"/>
       <c r="AA45" s="28" t="n"/>
       <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="40" t="n">
+      <c r="AC45" s="30" t="n">
         <v>0.4695</v>
       </c>
       <c r="AD45" s="24" t="inlineStr">
@@ -12709,11 +12678,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ45" s="38" t="n"/>
+      <c r="BJ45" s="25" t="n"/>
       <c r="BK45" s="26" t="n">
         <v>-426</v>
       </c>
-      <c r="BL45" s="39" t="n">
+      <c r="BL45" s="27" t="n">
         <v>1.234742</v>
       </c>
       <c r="BM45" s="28" t="n">
@@ -12723,16 +12692,16 @@
         <v>0.80198</v>
       </c>
       <c r="BO45" s="28" t="n"/>
-      <c r="BP45" s="38" t="n"/>
-      <c r="BQ45" s="39" t="n"/>
+      <c r="BP45" s="25" t="n"/>
+      <c r="BQ45" s="27" t="n"/>
       <c r="BR45" s="28" t="n"/>
       <c r="BS45" s="28" t="n"/>
       <c r="BT45" s="28" t="n"/>
-      <c r="BU45" s="38" t="n"/>
+      <c r="BU45" s="25" t="n"/>
       <c r="BV45" s="29" t="n"/>
       <c r="BW45" s="24" t="n"/>
-      <c r="BX45" s="40" t="n"/>
-      <c r="BY45" s="39" t="n"/>
+      <c r="BX45" s="30" t="n"/>
+      <c r="BY45" s="27" t="n"/>
       <c r="BZ45" s="24" t="n"/>
       <c r="CA45" s="31" t="n"/>
     </row>
@@ -12782,7 +12751,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J46" s="38" t="n"/>
+      <c r="J46" s="25" t="n"/>
       <c r="K46" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12791,7 +12760,7 @@
       <c r="L46" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="M46" s="39" t="n">
+      <c r="M46" s="27" t="n">
         <v>1.641026</v>
       </c>
       <c r="N46" s="28" t="n">
@@ -12831,11 +12800,11 @@
       <c r="X46" s="26" t="n">
         <v>72</v>
       </c>
-      <c r="Y46" s="38" t="n"/>
+      <c r="Y46" s="25" t="n"/>
       <c r="Z46" s="26" t="n"/>
       <c r="AA46" s="28" t="n"/>
       <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="40" t="n">
+      <c r="AC46" s="30" t="n">
         <v>0.8013</v>
       </c>
       <c r="AD46" s="24" t="inlineStr">
@@ -12972,11 +12941,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ46" s="38" t="n"/>
+      <c r="BJ46" s="25" t="n"/>
       <c r="BK46" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="BL46" s="39" t="n">
+      <c r="BL46" s="27" t="n">
         <v>1.641026</v>
       </c>
       <c r="BM46" s="28" t="n">
@@ -12986,16 +12955,16 @@
         <v>0.6039600000000001</v>
       </c>
       <c r="BO46" s="28" t="n"/>
-      <c r="BP46" s="38" t="n"/>
-      <c r="BQ46" s="39" t="n"/>
+      <c r="BP46" s="25" t="n"/>
+      <c r="BQ46" s="27" t="n"/>
       <c r="BR46" s="28" t="n"/>
       <c r="BS46" s="28" t="n"/>
       <c r="BT46" s="28" t="n"/>
-      <c r="BU46" s="38" t="n"/>
+      <c r="BU46" s="25" t="n"/>
       <c r="BV46" s="29" t="n"/>
       <c r="BW46" s="24" t="n"/>
-      <c r="BX46" s="40" t="n"/>
-      <c r="BY46" s="39" t="n"/>
+      <c r="BX46" s="30" t="n"/>
+      <c r="BY46" s="27" t="n"/>
       <c r="BZ46" s="24" t="n"/>
       <c r="CA46" s="31" t="n"/>
     </row>
@@ -13045,7 +13014,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J47" s="38" t="n"/>
+      <c r="J47" s="25" t="n"/>
       <c r="K47" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -13054,7 +13023,7 @@
       <c r="L47" s="26" t="n">
         <v>-354</v>
       </c>
-      <c r="M47" s="39" t="n">
+      <c r="M47" s="27" t="n">
         <v>1.282486</v>
       </c>
       <c r="N47" s="28" t="n">
@@ -13092,11 +13061,11 @@
       <c r="X47" s="26" t="n">
         <v>110</v>
       </c>
-      <c r="Y47" s="38" t="n"/>
+      <c r="Y47" s="25" t="n"/>
       <c r="Z47" s="26" t="n"/>
       <c r="AA47" s="28" t="n"/>
       <c r="AB47" s="28" t="n"/>
-      <c r="AC47" s="40" t="n">
+      <c r="AC47" s="30" t="n">
         <v>0.4944</v>
       </c>
       <c r="AD47" s="24" t="inlineStr">
@@ -13157,11 +13126,11 @@
       <c r="BG47" s="24" t="n"/>
       <c r="BH47" s="24" t="n"/>
       <c r="BI47" s="24" t="n"/>
-      <c r="BJ47" s="38" t="n"/>
+      <c r="BJ47" s="25" t="n"/>
       <c r="BK47" s="26" t="n">
         <v>-354</v>
       </c>
-      <c r="BL47" s="39" t="n">
+      <c r="BL47" s="27" t="n">
         <v>1.282486</v>
       </c>
       <c r="BM47" s="28" t="n">
@@ -13171,16 +13140,16 @@
         <v>0.779736</v>
       </c>
       <c r="BO47" s="28" t="n"/>
-      <c r="BP47" s="38" t="n"/>
-      <c r="BQ47" s="39" t="n"/>
+      <c r="BP47" s="25" t="n"/>
+      <c r="BQ47" s="27" t="n"/>
       <c r="BR47" s="28" t="n"/>
       <c r="BS47" s="28" t="n"/>
       <c r="BT47" s="28" t="n"/>
-      <c r="BU47" s="38" t="n"/>
+      <c r="BU47" s="25" t="n"/>
       <c r="BV47" s="29" t="n"/>
       <c r="BW47" s="24" t="n"/>
-      <c r="BX47" s="40" t="n"/>
-      <c r="BY47" s="39" t="n"/>
+      <c r="BX47" s="30" t="n"/>
+      <c r="BY47" s="27" t="n"/>
       <c r="BZ47" s="24" t="n"/>
       <c r="CA47" s="31" t="n"/>
     </row>
@@ -13230,7 +13199,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J48" s="38" t="n"/>
+      <c r="J48" s="25" t="n"/>
       <c r="K48" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13239,7 +13208,7 @@
       <c r="L48" s="26" t="n">
         <v>-194</v>
       </c>
-      <c r="M48" s="39" t="n">
+      <c r="M48" s="27" t="n">
         <v>1.515464</v>
       </c>
       <c r="N48" s="28" t="n">
@@ -13281,11 +13250,11 @@
       <c r="X48" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y48" s="38" t="n"/>
+      <c r="Y48" s="25" t="n"/>
       <c r="Z48" s="26" t="n"/>
       <c r="AA48" s="28" t="n"/>
       <c r="AB48" s="28" t="n"/>
-      <c r="AC48" s="40" t="n">
+      <c r="AC48" s="30" t="n">
         <v>0.6443</v>
       </c>
       <c r="AD48" s="24" t="inlineStr">
@@ -13344,11 +13313,11 @@
         </is>
       </c>
       <c r="BI48" s="24" t="n"/>
-      <c r="BJ48" s="38" t="n"/>
+      <c r="BJ48" s="25" t="n"/>
       <c r="BK48" s="26" t="n">
         <v>-194</v>
       </c>
-      <c r="BL48" s="39" t="n">
+      <c r="BL48" s="27" t="n">
         <v>1.515464</v>
       </c>
       <c r="BM48" s="28" t="n">
@@ -13358,16 +13327,16 @@
         <v>0.656716</v>
       </c>
       <c r="BO48" s="28" t="n"/>
-      <c r="BP48" s="38" t="n"/>
-      <c r="BQ48" s="39" t="n"/>
+      <c r="BP48" s="25" t="n"/>
+      <c r="BQ48" s="27" t="n"/>
       <c r="BR48" s="28" t="n"/>
       <c r="BS48" s="28" t="n"/>
       <c r="BT48" s="28" t="n"/>
-      <c r="BU48" s="38" t="n"/>
+      <c r="BU48" s="25" t="n"/>
       <c r="BV48" s="29" t="n"/>
       <c r="BW48" s="24" t="n"/>
-      <c r="BX48" s="40" t="n"/>
-      <c r="BY48" s="39" t="n"/>
+      <c r="BX48" s="30" t="n"/>
+      <c r="BY48" s="27" t="n"/>
       <c r="BZ48" s="24" t="n"/>
       <c r="CA48" s="31" t="n"/>
     </row>
@@ -13417,7 +13386,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J49" s="38" t="n"/>
+      <c r="J49" s="25" t="n"/>
       <c r="K49" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13426,7 +13395,7 @@
       <c r="L49" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="M49" s="39" t="n">
+      <c r="M49" s="27" t="n">
         <v>1.819672</v>
       </c>
       <c r="N49" s="28" t="n">
@@ -13468,11 +13437,11 @@
       <c r="X49" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y49" s="38" t="n"/>
+      <c r="Y49" s="25" t="n"/>
       <c r="Z49" s="26" t="n"/>
       <c r="AA49" s="28" t="n"/>
       <c r="AB49" s="28" t="n"/>
-      <c r="AC49" s="40" t="n">
+      <c r="AC49" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD49" s="24" t="inlineStr">
@@ -13531,11 +13500,11 @@
         </is>
       </c>
       <c r="BI49" s="24" t="n"/>
-      <c r="BJ49" s="38" t="n"/>
+      <c r="BJ49" s="25" t="n"/>
       <c r="BK49" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="BL49" s="39" t="n">
+      <c r="BL49" s="27" t="n">
         <v>1.819672</v>
       </c>
       <c r="BM49" s="28" t="n">
@@ -13545,16 +13514,16 @@
         <v>0.547264</v>
       </c>
       <c r="BO49" s="28" t="n"/>
-      <c r="BP49" s="38" t="n"/>
-      <c r="BQ49" s="39" t="n"/>
+      <c r="BP49" s="25" t="n"/>
+      <c r="BQ49" s="27" t="n"/>
       <c r="BR49" s="28" t="n"/>
       <c r="BS49" s="28" t="n"/>
       <c r="BT49" s="28" t="n"/>
-      <c r="BU49" s="38" t="n"/>
+      <c r="BU49" s="25" t="n"/>
       <c r="BV49" s="29" t="n"/>
       <c r="BW49" s="24" t="n"/>
-      <c r="BX49" s="40" t="n"/>
-      <c r="BY49" s="39" t="n"/>
+      <c r="BX49" s="30" t="n"/>
+      <c r="BY49" s="27" t="n"/>
       <c r="BZ49" s="24" t="n"/>
       <c r="CA49" s="31" t="n"/>
     </row>
@@ -13604,7 +13573,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J50" s="38" t="n"/>
+      <c r="J50" s="25" t="n"/>
       <c r="K50" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13613,7 +13582,7 @@
       <c r="L50" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M50" s="39" t="n">
+      <c r="M50" s="27" t="n">
         <v>1.884956</v>
       </c>
       <c r="N50" s="28" t="n">
@@ -13655,11 +13624,11 @@
       <c r="X50" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y50" s="38" t="n"/>
+      <c r="Y50" s="25" t="n"/>
       <c r="Z50" s="26" t="n"/>
       <c r="AA50" s="28" t="n"/>
       <c r="AB50" s="28" t="n"/>
-      <c r="AC50" s="40" t="n">
+      <c r="AC50" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD50" s="24" t="inlineStr">
@@ -13718,11 +13687,11 @@
         </is>
       </c>
       <c r="BI50" s="24" t="n"/>
-      <c r="BJ50" s="38" t="n"/>
+      <c r="BJ50" s="25" t="n"/>
       <c r="BK50" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL50" s="39" t="n">
+      <c r="BL50" s="27" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM50" s="28" t="n">
@@ -13732,16 +13701,16 @@
         <v>0.527363</v>
       </c>
       <c r="BO50" s="28" t="n"/>
-      <c r="BP50" s="38" t="n"/>
-      <c r="BQ50" s="39" t="n"/>
+      <c r="BP50" s="25" t="n"/>
+      <c r="BQ50" s="27" t="n"/>
       <c r="BR50" s="28" t="n"/>
       <c r="BS50" s="28" t="n"/>
       <c r="BT50" s="28" t="n"/>
-      <c r="BU50" s="38" t="n"/>
+      <c r="BU50" s="25" t="n"/>
       <c r="BV50" s="29" t="n"/>
       <c r="BW50" s="24" t="n"/>
-      <c r="BX50" s="40" t="n"/>
-      <c r="BY50" s="39" t="n"/>
+      <c r="BX50" s="30" t="n"/>
+      <c r="BY50" s="27" t="n"/>
       <c r="BZ50" s="24" t="n"/>
       <c r="CA50" s="31" t="n"/>
     </row>
@@ -13791,7 +13760,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J51" s="38" t="n"/>
+      <c r="J51" s="25" t="n"/>
       <c r="K51" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13800,7 +13769,7 @@
       <c r="L51" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M51" s="39" t="n">
+      <c r="M51" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N51" s="28" t="n">
@@ -13842,11 +13811,11 @@
       <c r="X51" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y51" s="38" t="n"/>
+      <c r="Y51" s="25" t="n"/>
       <c r="Z51" s="26" t="n"/>
       <c r="AA51" s="28" t="n"/>
       <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="40" t="n">
+      <c r="AC51" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD51" s="24" t="inlineStr">
@@ -13905,11 +13874,11 @@
         </is>
       </c>
       <c r="BI51" s="24" t="n"/>
-      <c r="BJ51" s="38" t="n"/>
+      <c r="BJ51" s="25" t="n"/>
       <c r="BK51" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL51" s="39" t="n">
+      <c r="BL51" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM51" s="28" t="n">
@@ -13919,16 +13888,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO51" s="28" t="n"/>
-      <c r="BP51" s="38" t="n"/>
-      <c r="BQ51" s="39" t="n"/>
+      <c r="BP51" s="25" t="n"/>
+      <c r="BQ51" s="27" t="n"/>
       <c r="BR51" s="28" t="n"/>
       <c r="BS51" s="28" t="n"/>
       <c r="BT51" s="28" t="n"/>
-      <c r="BU51" s="38" t="n"/>
+      <c r="BU51" s="25" t="n"/>
       <c r="BV51" s="29" t="n"/>
       <c r="BW51" s="24" t="n"/>
-      <c r="BX51" s="40" t="n"/>
-      <c r="BY51" s="39" t="n"/>
+      <c r="BX51" s="30" t="n"/>
+      <c r="BY51" s="27" t="n"/>
       <c r="BZ51" s="24" t="n"/>
       <c r="CA51" s="31" t="n"/>
     </row>
@@ -13978,7 +13947,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J52" s="38" t="n"/>
+      <c r="J52" s="25" t="n"/>
       <c r="K52" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13987,7 +13956,7 @@
       <c r="L52" s="26" t="n">
         <v>-174</v>
       </c>
-      <c r="M52" s="39" t="n">
+      <c r="M52" s="27" t="n">
         <v>1.574713</v>
       </c>
       <c r="N52" s="28" t="n">
@@ -14029,11 +13998,11 @@
       <c r="X52" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y52" s="38" t="n"/>
+      <c r="Y52" s="25" t="n"/>
       <c r="Z52" s="26" t="n"/>
       <c r="AA52" s="28" t="n"/>
       <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="40" t="n">
+      <c r="AC52" s="30" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD52" s="24" t="inlineStr">
@@ -14092,11 +14061,11 @@
         </is>
       </c>
       <c r="BI52" s="24" t="n"/>
-      <c r="BJ52" s="38" t="n"/>
+      <c r="BJ52" s="25" t="n"/>
       <c r="BK52" s="26" t="n">
         <v>-174</v>
       </c>
-      <c r="BL52" s="39" t="n">
+      <c r="BL52" s="27" t="n">
         <v>1.574713</v>
       </c>
       <c r="BM52" s="28" t="n">
@@ -14106,16 +14075,16 @@
         <v>0.631841</v>
       </c>
       <c r="BO52" s="28" t="n"/>
-      <c r="BP52" s="38" t="n"/>
-      <c r="BQ52" s="39" t="n"/>
+      <c r="BP52" s="25" t="n"/>
+      <c r="BQ52" s="27" t="n"/>
       <c r="BR52" s="28" t="n"/>
       <c r="BS52" s="28" t="n"/>
       <c r="BT52" s="28" t="n"/>
-      <c r="BU52" s="38" t="n"/>
+      <c r="BU52" s="25" t="n"/>
       <c r="BV52" s="29" t="n"/>
       <c r="BW52" s="24" t="n"/>
-      <c r="BX52" s="40" t="n"/>
-      <c r="BY52" s="39" t="n"/>
+      <c r="BX52" s="30" t="n"/>
+      <c r="BY52" s="27" t="n"/>
       <c r="BZ52" s="24" t="n"/>
       <c r="CA52" s="31" t="n"/>
     </row>
@@ -14165,7 +14134,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J53" s="38" t="n"/>
+      <c r="J53" s="25" t="n"/>
       <c r="K53" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14174,7 +14143,7 @@
       <c r="L53" s="26" t="n">
         <v>-376</v>
       </c>
-      <c r="M53" s="39" t="n">
+      <c r="M53" s="27" t="n">
         <v>1.265957</v>
       </c>
       <c r="N53" s="28" t="n">
@@ -14214,11 +14183,11 @@
       <c r="X53" s="26" t="n">
         <v>92</v>
       </c>
-      <c r="Y53" s="38" t="n"/>
+      <c r="Y53" s="25" t="n"/>
       <c r="Z53" s="26" t="n"/>
       <c r="AA53" s="28" t="n"/>
       <c r="AB53" s="28" t="n"/>
-      <c r="AC53" s="40" t="n">
+      <c r="AC53" s="30" t="n">
         <v>0.1995</v>
       </c>
       <c r="AD53" s="24" t="inlineStr">
@@ -14265,11 +14234,11 @@
         </is>
       </c>
       <c r="BI53" s="24" t="n"/>
-      <c r="BJ53" s="38" t="n"/>
+      <c r="BJ53" s="25" t="n"/>
       <c r="BK53" s="26" t="n">
         <v>-376</v>
       </c>
-      <c r="BL53" s="39" t="n">
+      <c r="BL53" s="27" t="n">
         <v>1.265957</v>
       </c>
       <c r="BM53" s="28" t="n">
@@ -14279,16 +14248,16 @@
         <v>0.782178</v>
       </c>
       <c r="BO53" s="28" t="n"/>
-      <c r="BP53" s="38" t="n"/>
-      <c r="BQ53" s="39" t="n"/>
+      <c r="BP53" s="25" t="n"/>
+      <c r="BQ53" s="27" t="n"/>
       <c r="BR53" s="28" t="n"/>
       <c r="BS53" s="28" t="n"/>
       <c r="BT53" s="28" t="n"/>
-      <c r="BU53" s="38" t="n"/>
+      <c r="BU53" s="25" t="n"/>
       <c r="BV53" s="29" t="n"/>
       <c r="BW53" s="24" t="n"/>
-      <c r="BX53" s="40" t="n"/>
-      <c r="BY53" s="39" t="n"/>
+      <c r="BX53" s="30" t="n"/>
+      <c r="BY53" s="27" t="n"/>
       <c r="BZ53" s="24" t="n"/>
       <c r="CA53" s="31" t="n"/>
     </row>
@@ -14338,7 +14307,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J54" s="38" t="n"/>
+      <c r="J54" s="25" t="n"/>
       <c r="K54" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14347,7 +14316,7 @@
       <c r="L54" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M54" s="39" t="n">
+      <c r="M54" s="27" t="n">
         <v>1.884956</v>
       </c>
       <c r="N54" s="28" t="n">
@@ -14387,11 +14356,11 @@
       <c r="X54" s="26" t="n">
         <v>96</v>
       </c>
-      <c r="Y54" s="38" t="n"/>
+      <c r="Y54" s="25" t="n"/>
       <c r="Z54" s="26" t="n"/>
       <c r="AA54" s="28" t="n"/>
       <c r="AB54" s="28" t="n"/>
-      <c r="AC54" s="40" t="n">
+      <c r="AC54" s="30" t="n">
         <v>0.4425</v>
       </c>
       <c r="AD54" s="24" t="inlineStr">
@@ -14438,11 +14407,11 @@
         </is>
       </c>
       <c r="BI54" s="24" t="n"/>
-      <c r="BJ54" s="38" t="n"/>
+      <c r="BJ54" s="25" t="n"/>
       <c r="BK54" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL54" s="39" t="n">
+      <c r="BL54" s="27" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM54" s="28" t="n">
@@ -14452,16 +14421,16 @@
         <v>0.524752</v>
       </c>
       <c r="BO54" s="28" t="n"/>
-      <c r="BP54" s="38" t="n"/>
-      <c r="BQ54" s="39" t="n"/>
+      <c r="BP54" s="25" t="n"/>
+      <c r="BQ54" s="27" t="n"/>
       <c r="BR54" s="28" t="n"/>
       <c r="BS54" s="28" t="n"/>
       <c r="BT54" s="28" t="n"/>
-      <c r="BU54" s="38" t="n"/>
+      <c r="BU54" s="25" t="n"/>
       <c r="BV54" s="29" t="n"/>
       <c r="BW54" s="24" t="n"/>
-      <c r="BX54" s="40" t="n"/>
-      <c r="BY54" s="39" t="n"/>
+      <c r="BX54" s="30" t="n"/>
+      <c r="BY54" s="27" t="n"/>
       <c r="BZ54" s="24" t="n"/>
       <c r="CA54" s="31" t="n"/>
     </row>
@@ -14511,7 +14480,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J55" s="38" t="n"/>
+      <c r="J55" s="25" t="n"/>
       <c r="K55" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14520,7 +14489,7 @@
       <c r="L55" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="M55" s="39" t="n">
+      <c r="M55" s="27" t="n">
         <v>1.561798</v>
       </c>
       <c r="N55" s="28" t="n">
@@ -14560,11 +14529,11 @@
       <c r="X55" s="26" t="n">
         <v>83</v>
       </c>
-      <c r="Y55" s="38" t="n"/>
+      <c r="Y55" s="25" t="n"/>
       <c r="Z55" s="26" t="n"/>
       <c r="AA55" s="28" t="n"/>
       <c r="AB55" s="28" t="n"/>
-      <c r="AC55" s="40" t="n">
+      <c r="AC55" s="30" t="n">
         <v>-2</v>
       </c>
       <c r="AD55" s="24" t="inlineStr">
@@ -14611,11 +14580,11 @@
         </is>
       </c>
       <c r="BI55" s="24" t="n"/>
-      <c r="BJ55" s="38" t="n"/>
+      <c r="BJ55" s="25" t="n"/>
       <c r="BK55" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="BL55" s="39" t="n">
+      <c r="BL55" s="27" t="n">
         <v>1.561798</v>
       </c>
       <c r="BM55" s="28" t="n">
@@ -14625,16 +14594,16 @@
         <v>0.633663</v>
       </c>
       <c r="BO55" s="28" t="n"/>
-      <c r="BP55" s="38" t="n"/>
-      <c r="BQ55" s="39" t="n"/>
+      <c r="BP55" s="25" t="n"/>
+      <c r="BQ55" s="27" t="n"/>
       <c r="BR55" s="28" t="n"/>
       <c r="BS55" s="28" t="n"/>
       <c r="BT55" s="28" t="n"/>
-      <c r="BU55" s="38" t="n"/>
+      <c r="BU55" s="25" t="n"/>
       <c r="BV55" s="29" t="n"/>
       <c r="BW55" s="24" t="n"/>
-      <c r="BX55" s="40" t="n"/>
-      <c r="BY55" s="39" t="n"/>
+      <c r="BX55" s="30" t="n"/>
+      <c r="BY55" s="27" t="n"/>
       <c r="BZ55" s="24" t="n"/>
       <c r="CA55" s="31" t="n"/>
     </row>
@@ -14684,7 +14653,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J56" s="38" t="n"/>
+      <c r="J56" s="25" t="n"/>
       <c r="K56" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14693,7 +14662,7 @@
       <c r="L56" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="M56" s="39" t="n">
+      <c r="M56" s="27" t="n">
         <v>1.613497</v>
       </c>
       <c r="N56" s="28" t="n">
@@ -14735,11 +14704,11 @@
       <c r="X56" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y56" s="38" t="n"/>
+      <c r="Y56" s="25" t="n"/>
       <c r="Z56" s="26" t="n"/>
       <c r="AA56" s="28" t="n"/>
       <c r="AB56" s="28" t="n"/>
-      <c r="AC56" s="40" t="n">
+      <c r="AC56" s="30" t="n">
         <v>0.9202</v>
       </c>
       <c r="AD56" s="24" t="inlineStr">
@@ -14798,11 +14767,11 @@
         </is>
       </c>
       <c r="BI56" s="24" t="n"/>
-      <c r="BJ56" s="38" t="n"/>
+      <c r="BJ56" s="25" t="n"/>
       <c r="BK56" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="BL56" s="39" t="n">
+      <c r="BL56" s="27" t="n">
         <v>1.613497</v>
       </c>
       <c r="BM56" s="28" t="n">
@@ -14812,16 +14781,16 @@
         <v>0.616915</v>
       </c>
       <c r="BO56" s="28" t="n"/>
-      <c r="BP56" s="38" t="n"/>
-      <c r="BQ56" s="39" t="n"/>
+      <c r="BP56" s="25" t="n"/>
+      <c r="BQ56" s="27" t="n"/>
       <c r="BR56" s="28" t="n"/>
       <c r="BS56" s="28" t="n"/>
       <c r="BT56" s="28" t="n"/>
-      <c r="BU56" s="38" t="n"/>
+      <c r="BU56" s="25" t="n"/>
       <c r="BV56" s="29" t="n"/>
       <c r="BW56" s="24" t="n"/>
-      <c r="BX56" s="40" t="n"/>
-      <c r="BY56" s="39" t="n"/>
+      <c r="BX56" s="30" t="n"/>
+      <c r="BY56" s="27" t="n"/>
       <c r="BZ56" s="24" t="n"/>
       <c r="CA56" s="31" t="n"/>
     </row>
@@ -14871,7 +14840,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J57" s="38" t="n"/>
+      <c r="J57" s="25" t="n"/>
       <c r="K57" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14880,7 +14849,7 @@
       <c r="L57" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M57" s="39" t="n">
+      <c r="M57" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="N57" s="28" t="n">
@@ -14922,11 +14891,11 @@
       <c r="X57" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y57" s="38" t="n"/>
+      <c r="Y57" s="25" t="n"/>
       <c r="Z57" s="26" t="n"/>
       <c r="AA57" s="28" t="n"/>
       <c r="AB57" s="28" t="n"/>
-      <c r="AC57" s="40" t="n">
+      <c r="AC57" s="30" t="n">
         <v>0.6757</v>
       </c>
       <c r="AD57" s="24" t="inlineStr">
@@ -14985,11 +14954,11 @@
         </is>
       </c>
       <c r="BI57" s="24" t="n"/>
-      <c r="BJ57" s="38" t="n"/>
+      <c r="BJ57" s="25" t="n"/>
       <c r="BK57" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL57" s="39" t="n">
+      <c r="BL57" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM57" s="28" t="n">
@@ -14999,16 +14968,16 @@
         <v>0.522388</v>
       </c>
       <c r="BO57" s="28" t="n"/>
-      <c r="BP57" s="38" t="n"/>
-      <c r="BQ57" s="39" t="n"/>
+      <c r="BP57" s="25" t="n"/>
+      <c r="BQ57" s="27" t="n"/>
       <c r="BR57" s="28" t="n"/>
       <c r="BS57" s="28" t="n"/>
       <c r="BT57" s="28" t="n"/>
-      <c r="BU57" s="38" t="n"/>
+      <c r="BU57" s="25" t="n"/>
       <c r="BV57" s="29" t="n"/>
       <c r="BW57" s="24" t="n"/>
-      <c r="BX57" s="40" t="n"/>
-      <c r="BY57" s="39" t="n"/>
+      <c r="BX57" s="30" t="n"/>
+      <c r="BY57" s="27" t="n"/>
       <c r="BZ57" s="24" t="n"/>
       <c r="CA57" s="31" t="n"/>
     </row>
@@ -15058,7 +15027,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J58" s="38" t="n"/>
+      <c r="J58" s="25" t="n"/>
       <c r="K58" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -15067,7 +15036,7 @@
       <c r="L58" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M58" s="39" t="n">
+      <c r="M58" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="N58" s="28" t="n">
@@ -15109,11 +15078,11 @@
       <c r="X58" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y58" s="38" t="n"/>
+      <c r="Y58" s="25" t="n"/>
       <c r="Z58" s="26" t="n"/>
       <c r="AA58" s="28" t="n"/>
       <c r="AB58" s="28" t="n"/>
-      <c r="AC58" s="40" t="n">
+      <c r="AC58" s="30" t="n">
         <v>1.087</v>
       </c>
       <c r="AD58" s="24" t="inlineStr">
@@ -15172,11 +15141,11 @@
         </is>
       </c>
       <c r="BI58" s="24" t="n"/>
-      <c r="BJ58" s="38" t="n"/>
+      <c r="BJ58" s="25" t="n"/>
       <c r="BK58" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL58" s="39" t="n">
+      <c r="BL58" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM58" s="28" t="n">
@@ -15186,16 +15155,16 @@
         <v>0.577114</v>
       </c>
       <c r="BO58" s="28" t="n"/>
-      <c r="BP58" s="38" t="n"/>
-      <c r="BQ58" s="39" t="n"/>
+      <c r="BP58" s="25" t="n"/>
+      <c r="BQ58" s="27" t="n"/>
       <c r="BR58" s="28" t="n"/>
       <c r="BS58" s="28" t="n"/>
       <c r="BT58" s="28" t="n"/>
-      <c r="BU58" s="38" t="n"/>
+      <c r="BU58" s="25" t="n"/>
       <c r="BV58" s="29" t="n"/>
       <c r="BW58" s="24" t="n"/>
-      <c r="BX58" s="40" t="n"/>
-      <c r="BY58" s="39" t="n"/>
+      <c r="BX58" s="30" t="n"/>
+      <c r="BY58" s="27" t="n"/>
       <c r="BZ58" s="24" t="n"/>
       <c r="CA58" s="31" t="n"/>
     </row>
@@ -15245,7 +15214,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J59" s="38" t="n"/>
+      <c r="J59" s="25" t="n"/>
       <c r="K59" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -15254,7 +15223,7 @@
       <c r="L59" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="M59" s="39" t="n">
+      <c r="M59" s="27" t="n">
         <v>1.561798</v>
       </c>
       <c r="N59" s="28" t="n">
@@ -15296,11 +15265,11 @@
       <c r="X59" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y59" s="38" t="n"/>
+      <c r="Y59" s="25" t="n"/>
       <c r="Z59" s="26" t="n"/>
       <c r="AA59" s="28" t="n"/>
       <c r="AB59" s="28" t="n"/>
-      <c r="AC59" s="40" t="n">
+      <c r="AC59" s="30" t="n">
         <v>0.5618</v>
       </c>
       <c r="AD59" s="24" t="inlineStr">
@@ -15359,11 +15328,11 @@
         </is>
       </c>
       <c r="BI59" s="24" t="n"/>
-      <c r="BJ59" s="38" t="n"/>
+      <c r="BJ59" s="25" t="n"/>
       <c r="BK59" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="BL59" s="39" t="n">
+      <c r="BL59" s="27" t="n">
         <v>1.561798</v>
       </c>
       <c r="BM59" s="28" t="n">
@@ -15373,16 +15342,16 @@
         <v>0.636816</v>
       </c>
       <c r="BO59" s="28" t="n"/>
-      <c r="BP59" s="38" t="n"/>
-      <c r="BQ59" s="39" t="n"/>
+      <c r="BP59" s="25" t="n"/>
+      <c r="BQ59" s="27" t="n"/>
       <c r="BR59" s="28" t="n"/>
       <c r="BS59" s="28" t="n"/>
       <c r="BT59" s="28" t="n"/>
-      <c r="BU59" s="38" t="n"/>
+      <c r="BU59" s="25" t="n"/>
       <c r="BV59" s="29" t="n"/>
       <c r="BW59" s="24" t="n"/>
-      <c r="BX59" s="40" t="n"/>
-      <c r="BY59" s="39" t="n"/>
+      <c r="BX59" s="30" t="n"/>
+      <c r="BY59" s="27" t="n"/>
       <c r="BZ59" s="24" t="n"/>
       <c r="CA59" s="31" t="n"/>
     </row>
@@ -15432,7 +15401,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J60" s="38" t="n"/>
+      <c r="J60" s="25" t="n"/>
       <c r="K60" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -15441,7 +15410,7 @@
       <c r="L60" s="26" t="n">
         <v>-669</v>
       </c>
-      <c r="M60" s="39" t="n">
+      <c r="M60" s="27" t="n">
         <v>1.149477</v>
       </c>
       <c r="N60" s="28" t="n">
@@ -15481,11 +15450,11 @@
       <c r="X60" s="26" t="n">
         <v>101</v>
       </c>
-      <c r="Y60" s="38" t="n"/>
+      <c r="Y60" s="25" t="n"/>
       <c r="Z60" s="26" t="n"/>
       <c r="AA60" s="28" t="n"/>
       <c r="AB60" s="28" t="n"/>
-      <c r="AC60" s="40" t="n">
+      <c r="AC60" s="30" t="n">
         <v>0.299</v>
       </c>
       <c r="AD60" s="24" t="inlineStr">
@@ -15532,11 +15501,11 @@
         </is>
       </c>
       <c r="BI60" s="24" t="n"/>
-      <c r="BJ60" s="38" t="n"/>
+      <c r="BJ60" s="25" t="n"/>
       <c r="BK60" s="26" t="n">
         <v>-669</v>
       </c>
-      <c r="BL60" s="39" t="n">
+      <c r="BL60" s="27" t="n">
         <v>1.149477</v>
       </c>
       <c r="BM60" s="28" t="n">
@@ -15546,16 +15515,16 @@
         <v>0.861386</v>
       </c>
       <c r="BO60" s="28" t="n"/>
-      <c r="BP60" s="38" t="n"/>
-      <c r="BQ60" s="39" t="n"/>
+      <c r="BP60" s="25" t="n"/>
+      <c r="BQ60" s="27" t="n"/>
       <c r="BR60" s="28" t="n"/>
       <c r="BS60" s="28" t="n"/>
       <c r="BT60" s="28" t="n"/>
-      <c r="BU60" s="38" t="n"/>
+      <c r="BU60" s="25" t="n"/>
       <c r="BV60" s="29" t="n"/>
       <c r="BW60" s="24" t="n"/>
-      <c r="BX60" s="40" t="n"/>
-      <c r="BY60" s="39" t="n"/>
+      <c r="BX60" s="30" t="n"/>
+      <c r="BY60" s="27" t="n"/>
       <c r="BZ60" s="24" t="n"/>
       <c r="CA60" s="31" t="n"/>
     </row>
@@ -15605,7 +15574,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J61" s="38" t="n"/>
+      <c r="J61" s="25" t="n"/>
       <c r="K61" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -15614,7 +15583,7 @@
       <c r="L61" s="26" t="n">
         <v>-355</v>
       </c>
-      <c r="M61" s="39" t="n">
+      <c r="M61" s="27" t="n">
         <v>1.28169</v>
       </c>
       <c r="N61" s="28" t="n">
@@ -15654,11 +15623,11 @@
       <c r="X61" s="26" t="n">
         <v>74</v>
       </c>
-      <c r="Y61" s="38" t="n"/>
+      <c r="Y61" s="25" t="n"/>
       <c r="Z61" s="26" t="n"/>
       <c r="AA61" s="28" t="n"/>
       <c r="AB61" s="28" t="n"/>
-      <c r="AC61" s="40" t="n">
+      <c r="AC61" s="30" t="n">
         <v>0.5634</v>
       </c>
       <c r="AD61" s="24" t="inlineStr">
@@ -15705,11 +15674,11 @@
         </is>
       </c>
       <c r="BI61" s="24" t="n"/>
-      <c r="BJ61" s="38" t="n"/>
+      <c r="BJ61" s="25" t="n"/>
       <c r="BK61" s="26" t="n">
         <v>-355</v>
       </c>
-      <c r="BL61" s="39" t="n">
+      <c r="BL61" s="27" t="n">
         <v>1.28169</v>
       </c>
       <c r="BM61" s="28" t="n">
@@ -15719,28 +15688,28 @@
         <v>0.772277</v>
       </c>
       <c r="BO61" s="28" t="n"/>
-      <c r="BP61" s="38" t="n"/>
-      <c r="BQ61" s="39" t="n"/>
+      <c r="BP61" s="25" t="n"/>
+      <c r="BQ61" s="27" t="n"/>
       <c r="BR61" s="28" t="n"/>
       <c r="BS61" s="28" t="n"/>
       <c r="BT61" s="28" t="n"/>
-      <c r="BU61" s="38" t="n"/>
+      <c r="BU61" s="25" t="n"/>
       <c r="BV61" s="29" t="n"/>
       <c r="BW61" s="24" t="n"/>
-      <c r="BX61" s="40" t="n"/>
-      <c r="BY61" s="39" t="n"/>
+      <c r="BX61" s="30" t="n"/>
+      <c r="BY61" s="27" t="n"/>
       <c r="BZ61" s="24" t="n"/>
       <c r="CA61" s="31" t="n"/>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>e00add3bfe2446db</t>
+          <t>5df3c9112e914547</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
@@ -15778,30 +15747,30 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J62" s="38" t="n"/>
+      <c r="J62" s="25" t="n"/>
       <c r="K62" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L62" s="26" t="n">
-        <v>111</v>
-      </c>
-      <c r="M62" s="39" t="n">
-        <v>2.11</v>
+        <v>113</v>
+      </c>
+      <c r="M62" s="27" t="n">
+        <v>2.13</v>
       </c>
       <c r="N62" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.469484</v>
       </c>
       <c r="O62" s="28" t="n">
         <v>0.5726869999999999</v>
       </c>
       <c r="P62" s="28" t="n"/>
       <c r="Q62" s="28" t="n">
-        <v>0.09875299999999999</v>
+        <v>0.103203</v>
       </c>
       <c r="R62" s="26" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S62" s="29" t="n">
         <v>1.25</v>
@@ -15819,15 +15788,15 @@
       <c r="V62" s="24" t="n"/>
       <c r="W62" s="26" t="n"/>
       <c r="X62" s="26" t="n"/>
-      <c r="Y62" s="38" t="n"/>
+      <c r="Y62" s="25" t="n"/>
       <c r="Z62" s="26" t="n"/>
       <c r="AA62" s="28" t="n"/>
       <c r="AB62" s="28" t="n"/>
-      <c r="AC62" s="40" t="n"/>
+      <c r="AC62" s="30" t="n"/>
       <c r="AD62" s="24" t="n"/>
       <c r="AE62" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.4750 (aec-mlb-min-cle-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.4700 (aec-mlb-min-cle-2026-07-20).</t>
         </is>
       </c>
       <c r="AF62" s="31" t="inlineStr">
@@ -15946,7 +15915,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:34.083345Z</t>
+          <t>2026-07-20T15:40:37.473344Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -15954,42 +15923,42 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ62" s="38" t="n"/>
+      <c r="BJ62" s="25" t="n"/>
       <c r="BK62" s="26" t="n">
-        <v>111</v>
-      </c>
-      <c r="BL62" s="39" t="n">
-        <v>2.11</v>
+        <v>113</v>
+      </c>
+      <c r="BL62" s="27" t="n">
+        <v>2.13</v>
       </c>
       <c r="BM62" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.469484</v>
       </c>
       <c r="BN62" s="28" t="n">
-        <v>0.470297</v>
+        <v>0.467662</v>
       </c>
       <c r="BO62" s="28" t="n"/>
-      <c r="BP62" s="38" t="n"/>
-      <c r="BQ62" s="39" t="n"/>
+      <c r="BP62" s="25" t="n"/>
+      <c r="BQ62" s="27" t="n"/>
       <c r="BR62" s="28" t="n"/>
       <c r="BS62" s="28" t="n"/>
       <c r="BT62" s="28" t="n"/>
-      <c r="BU62" s="38" t="n"/>
+      <c r="BU62" s="25" t="n"/>
       <c r="BV62" s="29" t="n"/>
       <c r="BW62" s="24" t="n"/>
-      <c r="BX62" s="40" t="n"/>
-      <c r="BY62" s="39" t="n"/>
+      <c r="BX62" s="30" t="n"/>
+      <c r="BY62" s="27" t="n"/>
       <c r="BZ62" s="24" t="n"/>
       <c r="CA62" s="31" t="n"/>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>7a7171ebb07c44d9</t>
+          <t>e598241db79c4dfb</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
@@ -16027,7 +15996,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J63" s="38" t="n"/>
+      <c r="J63" s="25" t="n"/>
       <c r="K63" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16036,7 +16005,7 @@
       <c r="L63" s="26" t="n">
         <v>125</v>
       </c>
-      <c r="M63" s="39" t="n">
+      <c r="M63" s="27" t="n">
         <v>2.25</v>
       </c>
       <c r="N63" s="28" t="n">
@@ -16068,11 +16037,11 @@
       <c r="V63" s="24" t="n"/>
       <c r="W63" s="26" t="n"/>
       <c r="X63" s="26" t="n"/>
-      <c r="Y63" s="38" t="n"/>
+      <c r="Y63" s="25" t="n"/>
       <c r="Z63" s="26" t="n"/>
       <c r="AA63" s="28" t="n"/>
       <c r="AB63" s="28" t="n"/>
-      <c r="AC63" s="40" t="n"/>
+      <c r="AC63" s="30" t="n"/>
       <c r="AD63" s="24" t="n"/>
       <c r="AE63" s="31" t="inlineStr">
         <is>
@@ -16195,7 +16164,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:40.881321Z</t>
+          <t>2026-07-20T15:40:44.245309Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -16203,11 +16172,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ63" s="38" t="n"/>
+      <c r="BJ63" s="25" t="n"/>
       <c r="BK63" s="26" t="n">
         <v>125</v>
       </c>
-      <c r="BL63" s="39" t="n">
+      <c r="BL63" s="27" t="n">
         <v>2.25</v>
       </c>
       <c r="BM63" s="28" t="n">
@@ -16217,28 +16186,28 @@
         <v>0.442786</v>
       </c>
       <c r="BO63" s="28" t="n"/>
-      <c r="BP63" s="38" t="n"/>
-      <c r="BQ63" s="39" t="n"/>
+      <c r="BP63" s="25" t="n"/>
+      <c r="BQ63" s="27" t="n"/>
       <c r="BR63" s="28" t="n"/>
       <c r="BS63" s="28" t="n"/>
       <c r="BT63" s="28" t="n"/>
-      <c r="BU63" s="38" t="n"/>
+      <c r="BU63" s="25" t="n"/>
       <c r="BV63" s="29" t="n"/>
       <c r="BW63" s="24" t="n"/>
-      <c r="BX63" s="40" t="n"/>
-      <c r="BY63" s="39" t="n"/>
+      <c r="BX63" s="30" t="n"/>
+      <c r="BY63" s="27" t="n"/>
       <c r="BZ63" s="24" t="n"/>
       <c r="CA63" s="31" t="n"/>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>0e08e82b6c5e41de</t>
+          <t>099694587c434b4a</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -16276,7 +16245,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J64" s="38" t="n"/>
+      <c r="J64" s="25" t="n"/>
       <c r="K64" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16285,7 +16254,7 @@
       <c r="L64" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M64" s="39" t="n">
+      <c r="M64" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N64" s="28" t="n">
@@ -16317,11 +16286,11 @@
       <c r="V64" s="24" t="n"/>
       <c r="W64" s="26" t="n"/>
       <c r="X64" s="26" t="n"/>
-      <c r="Y64" s="38" t="n"/>
+      <c r="Y64" s="25" t="n"/>
       <c r="Z64" s="26" t="n"/>
       <c r="AA64" s="28" t="n"/>
       <c r="AB64" s="28" t="n"/>
-      <c r="AC64" s="40" t="n"/>
+      <c r="AC64" s="30" t="n"/>
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
@@ -16444,7 +16413,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:36.050461Z</t>
+          <t>2026-07-20T15:40:38.983839Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -16452,11 +16421,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ64" s="38" t="n"/>
+      <c r="BJ64" s="25" t="n"/>
       <c r="BK64" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL64" s="39" t="n">
+      <c r="BL64" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM64" s="28" t="n">
@@ -16466,28 +16435,28 @@
         <v>0.517413</v>
       </c>
       <c r="BO64" s="28" t="n"/>
-      <c r="BP64" s="38" t="n"/>
-      <c r="BQ64" s="39" t="n"/>
+      <c r="BP64" s="25" t="n"/>
+      <c r="BQ64" s="27" t="n"/>
       <c r="BR64" s="28" t="n"/>
       <c r="BS64" s="28" t="n"/>
       <c r="BT64" s="28" t="n"/>
-      <c r="BU64" s="38" t="n"/>
+      <c r="BU64" s="25" t="n"/>
       <c r="BV64" s="29" t="n"/>
       <c r="BW64" s="24" t="n"/>
-      <c r="BX64" s="40" t="n"/>
-      <c r="BY64" s="39" t="n"/>
+      <c r="BX64" s="30" t="n"/>
+      <c r="BY64" s="27" t="n"/>
       <c r="BZ64" s="24" t="n"/>
       <c r="CA64" s="31" t="n"/>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>764b59e974874df1</t>
+          <t>6c1b1d290ce24d73</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -16525,27 +16494,27 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J65" s="38" t="n"/>
+      <c r="J65" s="25" t="n"/>
       <c r="K65" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M65" s="39" t="n">
-        <v>1.694444</v>
+        <v>-147</v>
+      </c>
+      <c r="M65" s="27" t="n">
+        <v>1.680272</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.5951419999999999</v>
       </c>
       <c r="O65" s="28" t="n">
         <v>0.530206</v>
       </c>
       <c r="P65" s="28" t="n"/>
       <c r="Q65" s="28" t="n">
-        <v>-0.059958</v>
+        <v>-0.06493599999999999</v>
       </c>
       <c r="R65" s="26" t="n">
         <v>0</v>
@@ -16566,15 +16535,15 @@
       <c r="V65" s="24" t="n"/>
       <c r="W65" s="26" t="n"/>
       <c r="X65" s="26" t="n"/>
-      <c r="Y65" s="38" t="n"/>
+      <c r="Y65" s="25" t="n"/>
       <c r="Z65" s="26" t="n"/>
       <c r="AA65" s="28" t="n"/>
       <c r="AB65" s="28" t="n"/>
-      <c r="AC65" s="40" t="n"/>
+      <c r="AC65" s="30" t="n"/>
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5900 (aec-mlb-tb-tor-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5950 (aec-mlb-tb-tor-2026-07-20).</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -16693,7 +16662,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:37.942740Z</t>
+          <t>2026-07-20T15:40:40.696549Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -16701,42 +16670,42 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ65" s="38" t="n"/>
+      <c r="BJ65" s="25" t="n"/>
       <c r="BK65" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL65" s="39" t="n">
-        <v>1.694444</v>
+        <v>-147</v>
+      </c>
+      <c r="BL65" s="27" t="n">
+        <v>1.680272</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.5951419999999999</v>
       </c>
       <c r="BN65" s="28" t="n">
-        <v>0.5870649999999999</v>
+        <v>0.59204</v>
       </c>
       <c r="BO65" s="28" t="n"/>
-      <c r="BP65" s="38" t="n"/>
-      <c r="BQ65" s="39" t="n"/>
+      <c r="BP65" s="25" t="n"/>
+      <c r="BQ65" s="27" t="n"/>
       <c r="BR65" s="28" t="n"/>
       <c r="BS65" s="28" t="n"/>
       <c r="BT65" s="28" t="n"/>
-      <c r="BU65" s="38" t="n"/>
+      <c r="BU65" s="25" t="n"/>
       <c r="BV65" s="29" t="n"/>
       <c r="BW65" s="24" t="n"/>
-      <c r="BX65" s="40" t="n"/>
-      <c r="BY65" s="39" t="n"/>
+      <c r="BX65" s="30" t="n"/>
+      <c r="BY65" s="27" t="n"/>
       <c r="BZ65" s="24" t="n"/>
       <c r="CA65" s="31" t="n"/>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>03845491b26c4e30</t>
+          <t>43b2ed970ab34f5f</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -16774,30 +16743,30 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J66" s="38" t="n"/>
+      <c r="J66" s="25" t="n"/>
       <c r="K66" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="M66" s="39" t="n">
-        <v>1.724638</v>
+        <v>-141</v>
+      </c>
+      <c r="M66" s="27" t="n">
+        <v>1.70922</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.585062</v>
       </c>
       <c r="O66" s="28" t="n">
         <v>0.565797</v>
       </c>
       <c r="P66" s="28" t="n"/>
       <c r="Q66" s="28" t="n">
-        <v>-0.014035</v>
+        <v>-0.019265</v>
       </c>
       <c r="R66" s="26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="S66" s="29" t="n">
         <v>1.25</v>
@@ -16815,15 +16784,15 @@
       <c r="V66" s="24" t="n"/>
       <c r="W66" s="26" t="n"/>
       <c r="X66" s="26" t="n"/>
-      <c r="Y66" s="38" t="n"/>
+      <c r="Y66" s="25" t="n"/>
       <c r="Z66" s="26" t="n"/>
       <c r="AA66" s="28" t="n"/>
       <c r="AB66" s="28" t="n"/>
-      <c r="AC66" s="40" t="n"/>
+      <c r="AC66" s="30" t="n"/>
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5800 (aec-mlb-bal-bos-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5850 (aec-mlb-bal-bos-2026-07-20).</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -16942,7 +16911,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:39.422286Z</t>
+          <t>2026-07-20T15:40:42.945575Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -16950,42 +16919,42 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ66" s="38" t="n"/>
+      <c r="BJ66" s="25" t="n"/>
       <c r="BK66" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="BL66" s="39" t="n">
-        <v>1.724638</v>
+        <v>-141</v>
+      </c>
+      <c r="BL66" s="27" t="n">
+        <v>1.70922</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.585062</v>
       </c>
       <c r="BN66" s="28" t="n">
-        <v>0.577114</v>
+        <v>0.58209</v>
       </c>
       <c r="BO66" s="28" t="n"/>
-      <c r="BP66" s="38" t="n"/>
-      <c r="BQ66" s="39" t="n"/>
+      <c r="BP66" s="25" t="n"/>
+      <c r="BQ66" s="27" t="n"/>
       <c r="BR66" s="28" t="n"/>
       <c r="BS66" s="28" t="n"/>
       <c r="BT66" s="28" t="n"/>
-      <c r="BU66" s="38" t="n"/>
+      <c r="BU66" s="25" t="n"/>
       <c r="BV66" s="29" t="n"/>
       <c r="BW66" s="24" t="n"/>
-      <c r="BX66" s="40" t="n"/>
-      <c r="BY66" s="39" t="n"/>
+      <c r="BX66" s="30" t="n"/>
+      <c r="BY66" s="27" t="n"/>
       <c r="BZ66" s="24" t="n"/>
       <c r="CA66" s="31" t="n"/>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>8fe8dba867db4326</t>
+          <t>556a298369cf47bd</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -17023,7 +16992,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J67" s="38" t="n"/>
+      <c r="J67" s="25" t="n"/>
       <c r="K67" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17032,7 +17001,7 @@
       <c r="L67" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M67" s="39" t="n">
+      <c r="M67" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N67" s="28" t="n">
@@ -17064,11 +17033,11 @@
       <c r="V67" s="24" t="n"/>
       <c r="W67" s="26" t="n"/>
       <c r="X67" s="26" t="n"/>
-      <c r="Y67" s="38" t="n"/>
+      <c r="Y67" s="25" t="n"/>
       <c r="Z67" s="26" t="n"/>
       <c r="AA67" s="28" t="n"/>
       <c r="AB67" s="28" t="n"/>
-      <c r="AC67" s="40" t="n"/>
+      <c r="AC67" s="30" t="n"/>
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
@@ -17191,7 +17160,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:42.141054Z</t>
+          <t>2026-07-20T15:40:45.418635Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -17199,11 +17168,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ67" s="38" t="n"/>
+      <c r="BJ67" s="25" t="n"/>
       <c r="BK67" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL67" s="39" t="n">
+      <c r="BL67" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM67" s="28" t="n">
@@ -17213,28 +17182,28 @@
         <v>0.567164</v>
       </c>
       <c r="BO67" s="28" t="n"/>
-      <c r="BP67" s="38" t="n"/>
-      <c r="BQ67" s="39" t="n"/>
+      <c r="BP67" s="25" t="n"/>
+      <c r="BQ67" s="27" t="n"/>
       <c r="BR67" s="28" t="n"/>
       <c r="BS67" s="28" t="n"/>
       <c r="BT67" s="28" t="n"/>
-      <c r="BU67" s="38" t="n"/>
+      <c r="BU67" s="25" t="n"/>
       <c r="BV67" s="29" t="n"/>
       <c r="BW67" s="24" t="n"/>
-      <c r="BX67" s="40" t="n"/>
-      <c r="BY67" s="39" t="n"/>
+      <c r="BX67" s="30" t="n"/>
+      <c r="BY67" s="27" t="n"/>
       <c r="BZ67" s="24" t="n"/>
       <c r="CA67" s="31" t="n"/>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
         <is>
-          <t>de587015be8044d0</t>
+          <t>1ca3aac02ee1494c</t>
         </is>
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -17272,7 +17241,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J68" s="38" t="n"/>
+      <c r="J68" s="25" t="n"/>
       <c r="K68" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17281,7 +17250,7 @@
       <c r="L68" s="26" t="n">
         <v>-199</v>
       </c>
-      <c r="M68" s="39" t="n">
+      <c r="M68" s="27" t="n">
         <v>1.502513</v>
       </c>
       <c r="N68" s="28" t="n">
@@ -17313,11 +17282,11 @@
       <c r="V68" s="24" t="n"/>
       <c r="W68" s="26" t="n"/>
       <c r="X68" s="26" t="n"/>
-      <c r="Y68" s="38" t="n"/>
+      <c r="Y68" s="25" t="n"/>
       <c r="Z68" s="26" t="n"/>
       <c r="AA68" s="28" t="n"/>
       <c r="AB68" s="28" t="n"/>
-      <c r="AC68" s="40" t="n"/>
+      <c r="AC68" s="30" t="n"/>
       <c r="AD68" s="24" t="n"/>
       <c r="AE68" s="31" t="inlineStr">
         <is>
@@ -17440,7 +17409,7 @@
       </c>
       <c r="BH68" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:44.122845Z</t>
+          <t>2026-07-20T15:40:46.730850Z</t>
         </is>
       </c>
       <c r="BI68" s="24" t="inlineStr">
@@ -17448,11 +17417,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ68" s="38" t="n"/>
+      <c r="BJ68" s="25" t="n"/>
       <c r="BK68" s="26" t="n">
         <v>-199</v>
       </c>
-      <c r="BL68" s="39" t="n">
+      <c r="BL68" s="27" t="n">
         <v>1.502513</v>
       </c>
       <c r="BM68" s="28" t="n">
@@ -17462,28 +17431,28 @@
         <v>0.6616919999999999</v>
       </c>
       <c r="BO68" s="28" t="n"/>
-      <c r="BP68" s="38" t="n"/>
-      <c r="BQ68" s="39" t="n"/>
+      <c r="BP68" s="25" t="n"/>
+      <c r="BQ68" s="27" t="n"/>
       <c r="BR68" s="28" t="n"/>
       <c r="BS68" s="28" t="n"/>
       <c r="BT68" s="28" t="n"/>
-      <c r="BU68" s="38" t="n"/>
+      <c r="BU68" s="25" t="n"/>
       <c r="BV68" s="29" t="n"/>
       <c r="BW68" s="24" t="n"/>
-      <c r="BX68" s="40" t="n"/>
-      <c r="BY68" s="39" t="n"/>
+      <c r="BX68" s="30" t="n"/>
+      <c r="BY68" s="27" t="n"/>
       <c r="BZ68" s="24" t="n"/>
       <c r="CA68" s="31" t="n"/>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>f30c4f4411454bcb</t>
+          <t>8d7ca0ea971a4878</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
@@ -17521,7 +17490,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J69" s="38" t="n"/>
+      <c r="J69" s="25" t="n"/>
       <c r="K69" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17530,7 +17499,7 @@
       <c r="L69" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M69" s="39" t="n">
+      <c r="M69" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="N69" s="28" t="n">
@@ -17562,11 +17531,11 @@
       <c r="V69" s="24" t="n"/>
       <c r="W69" s="26" t="n"/>
       <c r="X69" s="26" t="n"/>
-      <c r="Y69" s="38" t="n"/>
+      <c r="Y69" s="25" t="n"/>
       <c r="Z69" s="26" t="n"/>
       <c r="AA69" s="28" t="n"/>
       <c r="AB69" s="28" t="n"/>
-      <c r="AC69" s="40" t="n"/>
+      <c r="AC69" s="30" t="n"/>
       <c r="AD69" s="24" t="n"/>
       <c r="AE69" s="31" t="inlineStr">
         <is>
@@ -17689,7 +17658,7 @@
       </c>
       <c r="BH69" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:44.852438Z</t>
+          <t>2026-07-20T15:40:47.694396Z</t>
         </is>
       </c>
       <c r="BI69" s="24" t="inlineStr">
@@ -17697,11 +17666,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ69" s="38" t="n"/>
+      <c r="BJ69" s="25" t="n"/>
       <c r="BK69" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL69" s="39" t="n">
+      <c r="BL69" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM69" s="28" t="n">
@@ -17711,28 +17680,28 @@
         <v>0.522388</v>
       </c>
       <c r="BO69" s="28" t="n"/>
-      <c r="BP69" s="38" t="n"/>
-      <c r="BQ69" s="39" t="n"/>
+      <c r="BP69" s="25" t="n"/>
+      <c r="BQ69" s="27" t="n"/>
       <c r="BR69" s="28" t="n"/>
       <c r="BS69" s="28" t="n"/>
       <c r="BT69" s="28" t="n"/>
-      <c r="BU69" s="38" t="n"/>
+      <c r="BU69" s="25" t="n"/>
       <c r="BV69" s="29" t="n"/>
       <c r="BW69" s="24" t="n"/>
-      <c r="BX69" s="40" t="n"/>
-      <c r="BY69" s="39" t="n"/>
+      <c r="BX69" s="30" t="n"/>
+      <c r="BY69" s="27" t="n"/>
       <c r="BZ69" s="24" t="n"/>
       <c r="CA69" s="31" t="n"/>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>9d32e3b580bb4d9e</t>
+          <t>40fd1303ee5c40bc</t>
         </is>
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
@@ -17770,7 +17739,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J70" s="38" t="n"/>
+      <c r="J70" s="25" t="n"/>
       <c r="K70" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17779,7 +17748,7 @@
       <c r="L70" s="26" t="n">
         <v>-160</v>
       </c>
-      <c r="M70" s="39" t="n">
+      <c r="M70" s="27" t="n">
         <v>1.625</v>
       </c>
       <c r="N70" s="28" t="n">
@@ -17811,11 +17780,11 @@
       <c r="V70" s="24" t="n"/>
       <c r="W70" s="26" t="n"/>
       <c r="X70" s="26" t="n"/>
-      <c r="Y70" s="38" t="n"/>
+      <c r="Y70" s="25" t="n"/>
       <c r="Z70" s="26" t="n"/>
       <c r="AA70" s="28" t="n"/>
       <c r="AB70" s="28" t="n"/>
-      <c r="AC70" s="40" t="n"/>
+      <c r="AC70" s="30" t="n"/>
       <c r="AD70" s="24" t="n"/>
       <c r="AE70" s="31" t="inlineStr">
         <is>
@@ -17938,7 +17907,7 @@
       </c>
       <c r="BH70" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:47.582533Z</t>
+          <t>2026-07-20T15:40:49.845471Z</t>
         </is>
       </c>
       <c r="BI70" s="24" t="inlineStr">
@@ -17946,11 +17915,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ70" s="38" t="n"/>
+      <c r="BJ70" s="25" t="n"/>
       <c r="BK70" s="26" t="n">
         <v>-160</v>
       </c>
-      <c r="BL70" s="39" t="n">
+      <c r="BL70" s="27" t="n">
         <v>1.625</v>
       </c>
       <c r="BM70" s="28" t="n">
@@ -17960,28 +17929,28 @@
         <v>0.61194</v>
       </c>
       <c r="BO70" s="28" t="n"/>
-      <c r="BP70" s="38" t="n"/>
-      <c r="BQ70" s="39" t="n"/>
+      <c r="BP70" s="25" t="n"/>
+      <c r="BQ70" s="27" t="n"/>
       <c r="BR70" s="28" t="n"/>
       <c r="BS70" s="28" t="n"/>
       <c r="BT70" s="28" t="n"/>
-      <c r="BU70" s="38" t="n"/>
+      <c r="BU70" s="25" t="n"/>
       <c r="BV70" s="29" t="n"/>
       <c r="BW70" s="24" t="n"/>
-      <c r="BX70" s="40" t="n"/>
-      <c r="BY70" s="39" t="n"/>
+      <c r="BX70" s="30" t="n"/>
+      <c r="BY70" s="27" t="n"/>
       <c r="BZ70" s="24" t="n"/>
       <c r="CA70" s="31" t="n"/>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>d4d115be002c47d3</t>
+          <t>f140b8e744fa42a4</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
@@ -18019,7 +17988,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J71" s="38" t="n"/>
+      <c r="J71" s="25" t="n"/>
       <c r="K71" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -18028,7 +17997,7 @@
       <c r="L71" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M71" s="39" t="n">
+      <c r="M71" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N71" s="28" t="n">
@@ -18060,11 +18029,11 @@
       <c r="V71" s="24" t="n"/>
       <c r="W71" s="26" t="n"/>
       <c r="X71" s="26" t="n"/>
-      <c r="Y71" s="38" t="n"/>
+      <c r="Y71" s="25" t="n"/>
       <c r="Z71" s="26" t="n"/>
       <c r="AA71" s="28" t="n"/>
       <c r="AB71" s="28" t="n"/>
-      <c r="AC71" s="40" t="n"/>
+      <c r="AC71" s="30" t="n"/>
       <c r="AD71" s="24" t="n"/>
       <c r="AE71" s="31" t="inlineStr">
         <is>
@@ -18187,7 +18156,7 @@
       </c>
       <c r="BH71" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:47.761585Z</t>
+          <t>2026-07-20T15:40:51.564498Z</t>
         </is>
       </c>
       <c r="BI71" s="24" t="inlineStr">
@@ -18195,11 +18164,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ71" s="38" t="n"/>
+      <c r="BJ71" s="25" t="n"/>
       <c r="BK71" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL71" s="39" t="n">
+      <c r="BL71" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM71" s="28" t="n">
@@ -18209,28 +18178,28 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO71" s="28" t="n"/>
-      <c r="BP71" s="38" t="n"/>
-      <c r="BQ71" s="39" t="n"/>
+      <c r="BP71" s="25" t="n"/>
+      <c r="BQ71" s="27" t="n"/>
       <c r="BR71" s="28" t="n"/>
       <c r="BS71" s="28" t="n"/>
       <c r="BT71" s="28" t="n"/>
-      <c r="BU71" s="38" t="n"/>
+      <c r="BU71" s="25" t="n"/>
       <c r="BV71" s="29" t="n"/>
       <c r="BW71" s="24" t="n"/>
-      <c r="BX71" s="40" t="n"/>
-      <c r="BY71" s="39" t="n"/>
+      <c r="BX71" s="30" t="n"/>
+      <c r="BY71" s="27" t="n"/>
       <c r="BZ71" s="24" t="n"/>
       <c r="CA71" s="31" t="n"/>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
         <is>
-          <t>5ac11ebb449b4b54</t>
+          <t>e2d3732e917242c3</t>
         </is>
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
@@ -18268,7 +18237,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J72" s="38" t="n"/>
+      <c r="J72" s="25" t="n"/>
       <c r="K72" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -18277,7 +18246,7 @@
       <c r="L72" s="26" t="n">
         <v>-115</v>
       </c>
-      <c r="M72" s="39" t="n">
+      <c r="M72" s="27" t="n">
         <v>1.869565</v>
       </c>
       <c r="N72" s="28" t="n">
@@ -18309,11 +18278,11 @@
       <c r="V72" s="24" t="n"/>
       <c r="W72" s="26" t="n"/>
       <c r="X72" s="26" t="n"/>
-      <c r="Y72" s="38" t="n"/>
+      <c r="Y72" s="25" t="n"/>
       <c r="Z72" s="26" t="n"/>
       <c r="AA72" s="28" t="n"/>
       <c r="AB72" s="28" t="n"/>
-      <c r="AC72" s="40" t="n"/>
+      <c r="AC72" s="30" t="n"/>
       <c r="AD72" s="24" t="n"/>
       <c r="AE72" s="31" t="inlineStr">
         <is>
@@ -18436,7 +18405,7 @@
       </c>
       <c r="BH72" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:49.597715Z</t>
+          <t>2026-07-20T15:40:52.975565Z</t>
         </is>
       </c>
       <c r="BI72" s="24" t="inlineStr">
@@ -18444,11 +18413,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ72" s="38" t="n"/>
+      <c r="BJ72" s="25" t="n"/>
       <c r="BK72" s="26" t="n">
         <v>-115</v>
       </c>
-      <c r="BL72" s="39" t="n">
+      <c r="BL72" s="27" t="n">
         <v>1.869565</v>
       </c>
       <c r="BM72" s="28" t="n">
@@ -18458,28 +18427,28 @@
         <v>0.532338</v>
       </c>
       <c r="BO72" s="28" t="n"/>
-      <c r="BP72" s="38" t="n"/>
-      <c r="BQ72" s="39" t="n"/>
+      <c r="BP72" s="25" t="n"/>
+      <c r="BQ72" s="27" t="n"/>
       <c r="BR72" s="28" t="n"/>
       <c r="BS72" s="28" t="n"/>
       <c r="BT72" s="28" t="n"/>
-      <c r="BU72" s="38" t="n"/>
+      <c r="BU72" s="25" t="n"/>
       <c r="BV72" s="29" t="n"/>
       <c r="BW72" s="24" t="n"/>
-      <c r="BX72" s="40" t="n"/>
-      <c r="BY72" s="39" t="n"/>
+      <c r="BX72" s="30" t="n"/>
+      <c r="BY72" s="27" t="n"/>
       <c r="BZ72" s="24" t="n"/>
       <c r="CA72" s="31" t="n"/>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>3faaea8e908f4dff</t>
+          <t>7088516dc8f442f0</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C73" s="24" t="inlineStr">
@@ -18517,7 +18486,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J73" s="38" t="n"/>
+      <c r="J73" s="25" t="n"/>
       <c r="K73" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -18526,7 +18495,7 @@
       <c r="L73" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="M73" s="39" t="n">
+      <c r="M73" s="27" t="n">
         <v>1.854701</v>
       </c>
       <c r="N73" s="28" t="n">
@@ -18558,11 +18527,11 @@
       <c r="V73" s="24" t="n"/>
       <c r="W73" s="26" t="n"/>
       <c r="X73" s="26" t="n"/>
-      <c r="Y73" s="38" t="n"/>
+      <c r="Y73" s="25" t="n"/>
       <c r="Z73" s="26" t="n"/>
       <c r="AA73" s="28" t="n"/>
       <c r="AB73" s="28" t="n"/>
-      <c r="AC73" s="40" t="n"/>
+      <c r="AC73" s="30" t="n"/>
       <c r="AD73" s="24" t="n"/>
       <c r="AE73" s="31" t="inlineStr">
         <is>
@@ -18685,7 +18654,7 @@
       </c>
       <c r="BH73" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:51.548954Z</t>
+          <t>2026-07-20T15:40:55.296261Z</t>
         </is>
       </c>
       <c r="BI73" s="24" t="inlineStr">
@@ -18693,11 +18662,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ73" s="38" t="n"/>
+      <c r="BJ73" s="25" t="n"/>
       <c r="BK73" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="BL73" s="39" t="n">
+      <c r="BL73" s="27" t="n">
         <v>1.854701</v>
       </c>
       <c r="BM73" s="28" t="n">
@@ -18707,28 +18676,28 @@
         <v>0.537313</v>
       </c>
       <c r="BO73" s="28" t="n"/>
-      <c r="BP73" s="38" t="n"/>
-      <c r="BQ73" s="39" t="n"/>
+      <c r="BP73" s="25" t="n"/>
+      <c r="BQ73" s="27" t="n"/>
       <c r="BR73" s="28" t="n"/>
       <c r="BS73" s="28" t="n"/>
       <c r="BT73" s="28" t="n"/>
-      <c r="BU73" s="38" t="n"/>
+      <c r="BU73" s="25" t="n"/>
       <c r="BV73" s="29" t="n"/>
       <c r="BW73" s="24" t="n"/>
-      <c r="BX73" s="40" t="n"/>
-      <c r="BY73" s="39" t="n"/>
+      <c r="BX73" s="30" t="n"/>
+      <c r="BY73" s="27" t="n"/>
       <c r="BZ73" s="24" t="n"/>
       <c r="CA73" s="31" t="n"/>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
         <is>
-          <t>ce60c51f7f4d4503</t>
+          <t>cbd07a2b3b254a5a</t>
         </is>
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
@@ -18766,7 +18735,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J74" s="38" t="n"/>
+      <c r="J74" s="25" t="n"/>
       <c r="K74" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -18775,7 +18744,7 @@
       <c r="L74" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="M74" s="39" t="n">
+      <c r="M74" s="27" t="n">
         <v>1.694444</v>
       </c>
       <c r="N74" s="28" t="n">
@@ -18807,11 +18776,11 @@
       <c r="V74" s="24" t="n"/>
       <c r="W74" s="26" t="n"/>
       <c r="X74" s="26" t="n"/>
-      <c r="Y74" s="38" t="n"/>
+      <c r="Y74" s="25" t="n"/>
       <c r="Z74" s="26" t="n"/>
       <c r="AA74" s="28" t="n"/>
       <c r="AB74" s="28" t="n"/>
-      <c r="AC74" s="40" t="n"/>
+      <c r="AC74" s="30" t="n"/>
       <c r="AD74" s="24" t="n"/>
       <c r="AE74" s="31" t="inlineStr">
         <is>
@@ -18934,7 +18903,7 @@
       </c>
       <c r="BH74" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:52.295961Z</t>
+          <t>2026-07-20T15:40:57.666402Z</t>
         </is>
       </c>
       <c r="BI74" s="24" t="inlineStr">
@@ -18942,11 +18911,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ74" s="38" t="n"/>
+      <c r="BJ74" s="25" t="n"/>
       <c r="BK74" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="BL74" s="39" t="n">
+      <c r="BL74" s="27" t="n">
         <v>1.694444</v>
       </c>
       <c r="BM74" s="28" t="n">
@@ -18956,28 +18925,28 @@
         <v>0.5870649999999999</v>
       </c>
       <c r="BO74" s="28" t="n"/>
-      <c r="BP74" s="38" t="n"/>
-      <c r="BQ74" s="39" t="n"/>
+      <c r="BP74" s="25" t="n"/>
+      <c r="BQ74" s="27" t="n"/>
       <c r="BR74" s="28" t="n"/>
       <c r="BS74" s="28" t="n"/>
       <c r="BT74" s="28" t="n"/>
-      <c r="BU74" s="38" t="n"/>
+      <c r="BU74" s="25" t="n"/>
       <c r="BV74" s="29" t="n"/>
       <c r="BW74" s="24" t="n"/>
-      <c r="BX74" s="40" t="n"/>
-      <c r="BY74" s="39" t="n"/>
+      <c r="BX74" s="30" t="n"/>
+      <c r="BY74" s="27" t="n"/>
       <c r="BZ74" s="24" t="n"/>
       <c r="CA74" s="31" t="n"/>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>adfd7bf912a84989</t>
+          <t>3f1ba5855ae540e0</t>
         </is>
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C75" s="24" t="inlineStr">
@@ -19015,7 +18984,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J75" s="38" t="n"/>
+      <c r="J75" s="25" t="n"/>
       <c r="K75" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -19024,7 +18993,7 @@
       <c r="L75" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M75" s="39" t="n">
+      <c r="M75" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="N75" s="28" t="n">
@@ -19056,11 +19025,11 @@
       <c r="V75" s="24" t="n"/>
       <c r="W75" s="26" t="n"/>
       <c r="X75" s="26" t="n"/>
-      <c r="Y75" s="38" t="n"/>
+      <c r="Y75" s="25" t="n"/>
       <c r="Z75" s="26" t="n"/>
       <c r="AA75" s="28" t="n"/>
       <c r="AB75" s="28" t="n"/>
-      <c r="AC75" s="40" t="n"/>
+      <c r="AC75" s="30" t="n"/>
       <c r="AD75" s="24" t="n"/>
       <c r="AE75" s="31" t="inlineStr">
         <is>
@@ -19183,7 +19152,7 @@
       </c>
       <c r="BH75" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:53.701471Z</t>
+          <t>2026-07-20T15:40:58.875708Z</t>
         </is>
       </c>
       <c r="BI75" s="24" t="inlineStr">
@@ -19191,11 +19160,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ75" s="38" t="n"/>
+      <c r="BJ75" s="25" t="n"/>
       <c r="BK75" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL75" s="39" t="n">
+      <c r="BL75" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM75" s="28" t="n">
@@ -19205,28 +19174,28 @@
         <v>0.58209</v>
       </c>
       <c r="BO75" s="28" t="n"/>
-      <c r="BP75" s="38" t="n"/>
-      <c r="BQ75" s="39" t="n"/>
+      <c r="BP75" s="25" t="n"/>
+      <c r="BQ75" s="27" t="n"/>
       <c r="BR75" s="28" t="n"/>
       <c r="BS75" s="28" t="n"/>
       <c r="BT75" s="28" t="n"/>
-      <c r="BU75" s="38" t="n"/>
+      <c r="BU75" s="25" t="n"/>
       <c r="BV75" s="29" t="n"/>
       <c r="BW75" s="24" t="n"/>
-      <c r="BX75" s="40" t="n"/>
-      <c r="BY75" s="39" t="n"/>
+      <c r="BX75" s="30" t="n"/>
+      <c r="BY75" s="27" t="n"/>
       <c r="BZ75" s="24" t="n"/>
       <c r="CA75" s="31" t="n"/>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
         <is>
-          <t>e912f9cec2ac4e02</t>
+          <t>2bd291e543c748bf</t>
         </is>
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:38:55.511243Z</t>
+          <t>2026-07-20T15:44:31.508407Z</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
@@ -19264,7 +19233,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J76" s="38" t="n"/>
+      <c r="J76" s="25" t="n"/>
       <c r="K76" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -19273,7 +19242,7 @@
       <c r="L76" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M76" s="39" t="n">
+      <c r="M76" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="N76" s="28" t="n">
@@ -19305,11 +19274,11 @@
       <c r="V76" s="24" t="n"/>
       <c r="W76" s="26" t="n"/>
       <c r="X76" s="26" t="n"/>
-      <c r="Y76" s="38" t="n"/>
+      <c r="Y76" s="25" t="n"/>
       <c r="Z76" s="26" t="n"/>
       <c r="AA76" s="28" t="n"/>
       <c r="AB76" s="28" t="n"/>
-      <c r="AC76" s="40" t="n"/>
+      <c r="AC76" s="30" t="n"/>
       <c r="AD76" s="24" t="n"/>
       <c r="AE76" s="31" t="inlineStr">
         <is>
@@ -19432,7 +19401,7 @@
       </c>
       <c r="BH76" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:54.984623Z</t>
+          <t>2026-07-20T15:40:59.475543Z</t>
         </is>
       </c>
       <c r="BI76" s="24" t="inlineStr">
@@ -19440,11 +19409,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ76" s="38" t="n"/>
+      <c r="BJ76" s="25" t="n"/>
       <c r="BK76" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL76" s="39" t="n">
+      <c r="BL76" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="BM76" s="28" t="n">
@@ -19454,28 +19423,28 @@
         <v>0.492537</v>
       </c>
       <c r="BO76" s="28" t="n"/>
-      <c r="BP76" s="38" t="n"/>
-      <c r="BQ76" s="39" t="n"/>
+      <c r="BP76" s="25" t="n"/>
+      <c r="BQ76" s="27" t="n"/>
       <c r="BR76" s="28" t="n"/>
       <c r="BS76" s="28" t="n"/>
       <c r="BT76" s="28" t="n"/>
-      <c r="BU76" s="38" t="n"/>
+      <c r="BU76" s="25" t="n"/>
       <c r="BV76" s="29" t="n"/>
       <c r="BW76" s="24" t="n"/>
-      <c r="BX76" s="40" t="n"/>
-      <c r="BY76" s="39" t="n"/>
+      <c r="BX76" s="30" t="n"/>
+      <c r="BY76" s="27" t="n"/>
       <c r="BZ76" s="24" t="n"/>
       <c r="CA76" s="31" t="n"/>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>e9767a845c794040</t>
+          <t>4f41d18dabd545ca</t>
         </is>
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:39:03.207125Z</t>
+          <t>2026-07-20T15:44:38.792804Z</t>
         </is>
       </c>
       <c r="C77" s="24" t="inlineStr">
@@ -19513,7 +19482,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J77" s="38" t="n"/>
+      <c r="J77" s="25" t="n"/>
       <c r="K77" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -19522,7 +19491,7 @@
       <c r="L77" s="26" t="n">
         <v>-488</v>
       </c>
-      <c r="M77" s="39" t="n">
+      <c r="M77" s="27" t="n">
         <v>1.204918</v>
       </c>
       <c r="N77" s="28" t="n">
@@ -19554,11 +19523,11 @@
       <c r="V77" s="24" t="n"/>
       <c r="W77" s="26" t="n"/>
       <c r="X77" s="26" t="n"/>
-      <c r="Y77" s="38" t="n"/>
+      <c r="Y77" s="25" t="n"/>
       <c r="Z77" s="26" t="n"/>
       <c r="AA77" s="28" t="n"/>
       <c r="AB77" s="28" t="n"/>
-      <c r="AC77" s="40" t="n"/>
+      <c r="AC77" s="30" t="n"/>
       <c r="AD77" s="24" t="n"/>
       <c r="AE77" s="31" t="inlineStr">
         <is>
@@ -19681,7 +19650,7 @@
       </c>
       <c r="BH77" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:56.676680Z</t>
+          <t>2026-07-20T15:41:02.063056Z</t>
         </is>
       </c>
       <c r="BI77" s="24" t="inlineStr">
@@ -19689,11 +19658,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ77" s="38" t="n"/>
+      <c r="BJ77" s="25" t="n"/>
       <c r="BK77" s="26" t="n">
         <v>-488</v>
       </c>
-      <c r="BL77" s="39" t="n">
+      <c r="BL77" s="27" t="n">
         <v>1.204918</v>
       </c>
       <c r="BM77" s="28" t="n">
@@ -19703,28 +19672,28 @@
         <v>0.821782</v>
       </c>
       <c r="BO77" s="28" t="n"/>
-      <c r="BP77" s="38" t="n"/>
-      <c r="BQ77" s="39" t="n"/>
+      <c r="BP77" s="25" t="n"/>
+      <c r="BQ77" s="27" t="n"/>
       <c r="BR77" s="28" t="n"/>
       <c r="BS77" s="28" t="n"/>
       <c r="BT77" s="28" t="n"/>
-      <c r="BU77" s="38" t="n"/>
+      <c r="BU77" s="25" t="n"/>
       <c r="BV77" s="29" t="n"/>
       <c r="BW77" s="24" t="n"/>
-      <c r="BX77" s="40" t="n"/>
-      <c r="BY77" s="39" t="n"/>
+      <c r="BX77" s="30" t="n"/>
+      <c r="BY77" s="27" t="n"/>
       <c r="BZ77" s="24" t="n"/>
       <c r="CA77" s="31" t="n"/>
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="24" t="inlineStr">
         <is>
-          <t>8e2265c74515471f</t>
+          <t>bf6f6152e282469c</t>
         </is>
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:39:03.207125Z</t>
+          <t>2026-07-20T15:44:38.792804Z</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
@@ -19762,27 +19731,27 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J78" s="38" t="n"/>
+      <c r="J78" s="25" t="n"/>
       <c r="K78" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L78" s="26" t="n">
-        <v>156</v>
-      </c>
-      <c r="M78" s="39" t="n">
-        <v>2.56</v>
+        <v>150</v>
+      </c>
+      <c r="M78" s="27" t="n">
+        <v>2.5</v>
       </c>
       <c r="N78" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.4</v>
       </c>
       <c r="O78" s="28" t="n">
         <v>0.688998</v>
       </c>
       <c r="P78" s="28" t="n"/>
       <c r="Q78" s="28" t="n">
-        <v>0.298373</v>
+        <v>0.288998</v>
       </c>
       <c r="R78" s="26" t="n">
         <v>100</v>
@@ -19803,15 +19772,15 @@
       <c r="V78" s="24" t="n"/>
       <c r="W78" s="26" t="n"/>
       <c r="X78" s="26" t="n"/>
-      <c r="Y78" s="38" t="n"/>
+      <c r="Y78" s="25" t="n"/>
       <c r="Z78" s="26" t="n"/>
       <c r="AA78" s="28" t="n"/>
       <c r="AB78" s="28" t="n"/>
-      <c r="AC78" s="40" t="n"/>
+      <c r="AC78" s="30" t="n"/>
       <c r="AD78" s="24" t="n"/>
       <c r="AE78" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5051; executable ask 0.3900 (aec-wnba-ny-dal-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5051; executable ask 0.4000 (aec-wnba-ny-dal-2026-07-20).</t>
         </is>
       </c>
       <c r="AF78" s="31" t="inlineStr">
@@ -19930,7 +19899,7 @@
       </c>
       <c r="BH78" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:33:58.690931Z</t>
+          <t>2026-07-20T15:41:03.863692Z</t>
         </is>
       </c>
       <c r="BI78" s="24" t="inlineStr">
@@ -19938,42 +19907,42 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ78" s="38" t="n"/>
+      <c r="BJ78" s="25" t="n"/>
       <c r="BK78" s="26" t="n">
-        <v>156</v>
-      </c>
-      <c r="BL78" s="39" t="n">
-        <v>2.56</v>
+        <v>150</v>
+      </c>
+      <c r="BL78" s="27" t="n">
+        <v>2.5</v>
       </c>
       <c r="BM78" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.4</v>
       </c>
       <c r="BN78" s="28" t="n">
-        <v>0.386139</v>
+        <v>0.39604</v>
       </c>
       <c r="BO78" s="28" t="n"/>
-      <c r="BP78" s="38" t="n"/>
-      <c r="BQ78" s="39" t="n"/>
+      <c r="BP78" s="25" t="n"/>
+      <c r="BQ78" s="27" t="n"/>
       <c r="BR78" s="28" t="n"/>
       <c r="BS78" s="28" t="n"/>
       <c r="BT78" s="28" t="n"/>
-      <c r="BU78" s="38" t="n"/>
+      <c r="BU78" s="25" t="n"/>
       <c r="BV78" s="29" t="n"/>
       <c r="BW78" s="24" t="n"/>
-      <c r="BX78" s="40" t="n"/>
-      <c r="BY78" s="39" t="n"/>
+      <c r="BX78" s="30" t="n"/>
+      <c r="BY78" s="27" t="n"/>
       <c r="BZ78" s="24" t="n"/>
       <c r="CA78" s="31" t="n"/>
     </row>
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>a4f324e828eb4cee</t>
+          <t>afaf853c69284bb6</t>
         </is>
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:39:03.207125Z</t>
+          <t>2026-07-20T15:44:38.792804Z</t>
         </is>
       </c>
       <c r="C79" s="24" t="inlineStr">
@@ -20011,7 +19980,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J79" s="38" t="n"/>
+      <c r="J79" s="25" t="n"/>
       <c r="K79" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -20020,7 +19989,7 @@
       <c r="L79" s="26" t="n">
         <v>-317</v>
       </c>
-      <c r="M79" s="39" t="n">
+      <c r="M79" s="27" t="n">
         <v>1.315457</v>
       </c>
       <c r="N79" s="28" t="n">
@@ -20052,11 +20021,11 @@
       <c r="V79" s="24" t="n"/>
       <c r="W79" s="26" t="n"/>
       <c r="X79" s="26" t="n"/>
-      <c r="Y79" s="38" t="n"/>
+      <c r="Y79" s="25" t="n"/>
       <c r="Z79" s="26" t="n"/>
       <c r="AA79" s="28" t="n"/>
       <c r="AB79" s="28" t="n"/>
-      <c r="AC79" s="40" t="n"/>
+      <c r="AC79" s="30" t="n"/>
       <c r="AD79" s="24" t="n"/>
       <c r="AE79" s="31" t="inlineStr">
         <is>
@@ -20179,7 +20148,7 @@
       </c>
       <c r="BH79" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:34:00.890171Z</t>
+          <t>2026-07-20T15:41:06.249047Z</t>
         </is>
       </c>
       <c r="BI79" s="24" t="inlineStr">
@@ -20187,11 +20156,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ79" s="38" t="n"/>
+      <c r="BJ79" s="25" t="n"/>
       <c r="BK79" s="26" t="n">
         <v>-317</v>
       </c>
-      <c r="BL79" s="39" t="n">
+      <c r="BL79" s="27" t="n">
         <v>1.315457</v>
       </c>
       <c r="BM79" s="28" t="n">
@@ -20201,28 +20170,28 @@
         <v>0.752475</v>
       </c>
       <c r="BO79" s="28" t="n"/>
-      <c r="BP79" s="38" t="n"/>
-      <c r="BQ79" s="39" t="n"/>
+      <c r="BP79" s="25" t="n"/>
+      <c r="BQ79" s="27" t="n"/>
       <c r="BR79" s="28" t="n"/>
       <c r="BS79" s="28" t="n"/>
       <c r="BT79" s="28" t="n"/>
-      <c r="BU79" s="38" t="n"/>
+      <c r="BU79" s="25" t="n"/>
       <c r="BV79" s="29" t="n"/>
       <c r="BW79" s="24" t="n"/>
-      <c r="BX79" s="40" t="n"/>
-      <c r="BY79" s="39" t="n"/>
+      <c r="BX79" s="30" t="n"/>
+      <c r="BY79" s="27" t="n"/>
       <c r="BZ79" s="24" t="n"/>
       <c r="CA79" s="31" t="n"/>
     </row>
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="24" t="inlineStr">
         <is>
-          <t>e010b6ed614649a7</t>
+          <t>23aad3907b4640b1</t>
         </is>
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:39:03.207125Z</t>
+          <t>2026-07-20T15:44:38.792804Z</t>
         </is>
       </c>
       <c r="C80" s="24" t="inlineStr">
@@ -20260,7 +20229,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J80" s="38" t="n"/>
+      <c r="J80" s="25" t="n"/>
       <c r="K80" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -20269,7 +20238,7 @@
       <c r="L80" s="26" t="n">
         <v>-456</v>
       </c>
-      <c r="M80" s="39" t="n">
+      <c r="M80" s="27" t="n">
         <v>1.219298</v>
       </c>
       <c r="N80" s="28" t="n">
@@ -20301,11 +20270,11 @@
       <c r="V80" s="24" t="n"/>
       <c r="W80" s="26" t="n"/>
       <c r="X80" s="26" t="n"/>
-      <c r="Y80" s="38" t="n"/>
+      <c r="Y80" s="25" t="n"/>
       <c r="Z80" s="26" t="n"/>
       <c r="AA80" s="28" t="n"/>
       <c r="AB80" s="28" t="n"/>
-      <c r="AC80" s="40" t="n"/>
+      <c r="AC80" s="30" t="n"/>
       <c r="AD80" s="24" t="n"/>
       <c r="AE80" s="31" t="inlineStr">
         <is>
@@ -20428,7 +20397,7 @@
       </c>
       <c r="BH80" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:34:01.619683Z</t>
+          <t>2026-07-20T15:41:07.394583Z</t>
         </is>
       </c>
       <c r="BI80" s="24" t="inlineStr">
@@ -20436,11 +20405,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ80" s="38" t="n"/>
+      <c r="BJ80" s="25" t="n"/>
       <c r="BK80" s="26" t="n">
         <v>-456</v>
       </c>
-      <c r="BL80" s="39" t="n">
+      <c r="BL80" s="27" t="n">
         <v>1.219298</v>
       </c>
       <c r="BM80" s="28" t="n">
@@ -20450,18 +20419,2488 @@
         <v>0.811881</v>
       </c>
       <c r="BO80" s="28" t="n"/>
-      <c r="BP80" s="38" t="n"/>
-      <c r="BQ80" s="39" t="n"/>
+      <c r="BP80" s="25" t="n"/>
+      <c r="BQ80" s="27" t="n"/>
       <c r="BR80" s="28" t="n"/>
       <c r="BS80" s="28" t="n"/>
       <c r="BT80" s="28" t="n"/>
-      <c r="BU80" s="38" t="n"/>
+      <c r="BU80" s="25" t="n"/>
       <c r="BV80" s="29" t="n"/>
       <c r="BW80" s="24" t="n"/>
-      <c r="BX80" s="40" t="n"/>
-      <c r="BY80" s="39" t="n"/>
+      <c r="BX80" s="30" t="n"/>
+      <c r="BY80" s="27" t="n"/>
       <c r="BZ80" s="24" t="n"/>
       <c r="CA80" s="31" t="n"/>
+    </row>
+    <row r="81" ht="36" customHeight="1">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>5b6cb66aed1b43a7</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:04.119469Z</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>54491</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F81" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J81" s="25" t="n"/>
+      <c r="K81" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L81" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M81" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N81" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O81" s="28" t="n">
+        <v>0.555003</v>
+      </c>
+      <c r="P81" s="28" t="n"/>
+      <c r="Q81" s="28" t="n">
+        <v>0.145003</v>
+      </c>
+      <c r="R81" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S81" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U81" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V81" s="24" t="n"/>
+      <c r="W81" s="26" t="n"/>
+      <c r="X81" s="26" t="n"/>
+      <c r="Y81" s="25" t="n"/>
+      <c r="Z81" s="26" t="n"/>
+      <c r="AA81" s="28" t="n"/>
+      <c r="AB81" s="28" t="n"/>
+      <c r="AC81" s="30" t="n"/>
+      <c r="AD81" s="24" t="n"/>
+      <c r="AE81" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (aec-lol-vksa-kbm-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF81" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG81" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH81" s="24" t="n"/>
+      <c r="AI81" s="31" t="n"/>
+      <c r="AJ81" s="31" t="n"/>
+      <c r="AK81" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL81" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM81" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN81" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO81" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP81" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AQ81" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AR81" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AS81" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AT81" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AU81" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AV81" s="24" t="n"/>
+      <c r="AW81" s="24" t="n"/>
+      <c r="AX81" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY81" s="24" t="n"/>
+      <c r="AZ81" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA81" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BB81" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC81" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD81" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BE81" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF81" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG81" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH81" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:04.119469Z</t>
+        </is>
+      </c>
+      <c r="BI81" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ81" s="25" t="n"/>
+      <c r="BK81" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL81" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM81" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN81" s="28" t="n"/>
+      <c r="BO81" s="28" t="n"/>
+      <c r="BP81" s="25" t="n"/>
+      <c r="BQ81" s="27" t="n"/>
+      <c r="BR81" s="28" t="n"/>
+      <c r="BS81" s="28" t="n"/>
+      <c r="BT81" s="28" t="n"/>
+      <c r="BU81" s="25" t="n"/>
+      <c r="BV81" s="29" t="n"/>
+      <c r="BW81" s="24" t="n"/>
+      <c r="BX81" s="30" t="n"/>
+      <c r="BY81" s="27" t="n"/>
+      <c r="BZ81" s="24" t="n"/>
+      <c r="CA81" s="31" t="n"/>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>6daddbd69a464322</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:04.354854Z</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D82" s="24" t="inlineStr">
+        <is>
+          <t>54670</t>
+        </is>
+      </c>
+      <c r="E82" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F82" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="G82" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="H82" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I82" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J82" s="25" t="n"/>
+      <c r="K82" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L82" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M82" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N82" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O82" s="28" t="n">
+        <v>0.567918</v>
+      </c>
+      <c r="P82" s="28" t="n"/>
+      <c r="Q82" s="28" t="n">
+        <v>0.217918</v>
+      </c>
+      <c r="R82" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S82" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T82" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U82" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V82" s="24" t="n"/>
+      <c r="W82" s="26" t="n"/>
+      <c r="X82" s="26" t="n"/>
+      <c r="Y82" s="25" t="n"/>
+      <c r="Z82" s="26" t="n"/>
+      <c r="AA82" s="28" t="n"/>
+      <c r="AB82" s="28" t="n"/>
+      <c r="AC82" s="30" t="n"/>
+      <c r="AD82" s="24" t="n"/>
+      <c r="AE82" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (aec-lol-itz-7rex-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF82" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG82" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH82" s="24" t="n"/>
+      <c r="AI82" s="31" t="n"/>
+      <c r="AJ82" s="31" t="n"/>
+      <c r="AK82" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL82" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM82" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN82" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO82" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP82" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AQ82" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AR82" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AS82" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AT82" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AU82" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AV82" s="24" t="n"/>
+      <c r="AW82" s="24" t="n"/>
+      <c r="AX82" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY82" s="24" t="n"/>
+      <c r="AZ82" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA82" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BB82" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC82" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD82" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BE82" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF82" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG82" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH82" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:04.354854Z</t>
+        </is>
+      </c>
+      <c r="BI82" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ82" s="25" t="n"/>
+      <c r="BK82" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL82" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM82" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN82" s="28" t="n"/>
+      <c r="BO82" s="28" t="n"/>
+      <c r="BP82" s="25" t="n"/>
+      <c r="BQ82" s="27" t="n"/>
+      <c r="BR82" s="28" t="n"/>
+      <c r="BS82" s="28" t="n"/>
+      <c r="BT82" s="28" t="n"/>
+      <c r="BU82" s="25" t="n"/>
+      <c r="BV82" s="29" t="n"/>
+      <c r="BW82" s="24" t="n"/>
+      <c r="BX82" s="30" t="n"/>
+      <c r="BY82" s="27" t="n"/>
+      <c r="BZ82" s="24" t="n"/>
+      <c r="CA82" s="31" t="n"/>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>a90c13efd4db44fa</t>
+        </is>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:04.555914Z</t>
+        </is>
+      </c>
+      <c r="C83" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>54693</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F83" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>RED Academy</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J83" s="25" t="n"/>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L83" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="M83" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N83" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O83" s="28" t="n">
+        <v>0.674654</v>
+      </c>
+      <c r="P83" s="28" t="n"/>
+      <c r="Q83" s="28" t="n">
+        <v>0.424654</v>
+      </c>
+      <c r="R83" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S83" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T83" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U83" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V83" s="24" t="n"/>
+      <c r="W83" s="26" t="n"/>
+      <c r="X83" s="26" t="n"/>
+      <c r="Y83" s="25" t="n"/>
+      <c r="Z83" s="26" t="n"/>
+      <c r="AA83" s="28" t="n"/>
+      <c r="AB83" s="28" t="n"/>
+      <c r="AC83" s="30" t="n"/>
+      <c r="AD83" s="24" t="n"/>
+      <c r="AE83" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.2500 (aec-lol-reda-nerd-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF83" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG83" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH83" s="24" t="n"/>
+      <c r="AI83" s="31" t="n"/>
+      <c r="AJ83" s="31" t="n"/>
+      <c r="AK83" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL83" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM83" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN83" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO83" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP83" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AQ83" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AR83" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AS83" s="24" t="inlineStr">
+        <is>
+          <t>RED Academy</t>
+        </is>
+      </c>
+      <c r="AT83" s="24" t="inlineStr">
+        <is>
+          <t>RED Academy</t>
+        </is>
+      </c>
+      <c r="AU83" s="24" t="inlineStr">
+        <is>
+          <t>RED Academy</t>
+        </is>
+      </c>
+      <c r="AV83" s="24" t="n"/>
+      <c r="AW83" s="24" t="n"/>
+      <c r="AX83" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY83" s="24" t="n"/>
+      <c r="AZ83" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA83" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BB83" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC83" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD83" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BE83" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF83" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG83" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH83" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:04.555914Z</t>
+        </is>
+      </c>
+      <c r="BI83" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ83" s="25" t="n"/>
+      <c r="BK83" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="BL83" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM83" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BN83" s="28" t="n"/>
+      <c r="BO83" s="28" t="n"/>
+      <c r="BP83" s="25" t="n"/>
+      <c r="BQ83" s="27" t="n"/>
+      <c r="BR83" s="28" t="n"/>
+      <c r="BS83" s="28" t="n"/>
+      <c r="BT83" s="28" t="n"/>
+      <c r="BU83" s="25" t="n"/>
+      <c r="BV83" s="29" t="n"/>
+      <c r="BW83" s="24" t="n"/>
+      <c r="BX83" s="30" t="n"/>
+      <c r="BY83" s="27" t="n"/>
+      <c r="BZ83" s="24" t="n"/>
+      <c r="CA83" s="31" t="n"/>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>3a2bf877040d4609</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:04.750645Z</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="inlineStr">
+        <is>
+          <t>54724</t>
+        </is>
+      </c>
+      <c r="E84" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="G84" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="H84" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I84" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J84" s="25" t="n"/>
+      <c r="K84" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L84" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M84" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N84" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O84" s="28" t="n">
+        <v>0.54815</v>
+      </c>
+      <c r="P84" s="28" t="n"/>
+      <c r="Q84" s="28" t="n">
+        <v>-0.04185</v>
+      </c>
+      <c r="R84" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U84" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V84" s="24" t="n"/>
+      <c r="W84" s="26" t="n"/>
+      <c r="X84" s="26" t="n"/>
+      <c r="Y84" s="25" t="n"/>
+      <c r="Z84" s="26" t="n"/>
+      <c r="AA84" s="28" t="n"/>
+      <c r="AB84" s="28" t="n"/>
+      <c r="AC84" s="30" t="n"/>
+      <c r="AD84" s="24" t="n"/>
+      <c r="AE84" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (aec-lol-tse-rmd-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF84" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG84" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH84" s="24" t="n"/>
+      <c r="AI84" s="31" t="n"/>
+      <c r="AJ84" s="31" t="n"/>
+      <c r="AK84" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL84" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM84" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN84" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO84" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP84" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AQ84" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AR84" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AS84" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AT84" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AU84" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AV84" s="24" t="n"/>
+      <c r="AW84" s="24" t="n"/>
+      <c r="AX84" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY84" s="24" t="n"/>
+      <c r="AZ84" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA84" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BB84" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC84" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD84" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BE84" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF84" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG84" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH84" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:04.750645Z</t>
+        </is>
+      </c>
+      <c r="BI84" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ84" s="25" t="n"/>
+      <c r="BK84" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL84" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM84" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN84" s="28" t="n"/>
+      <c r="BO84" s="28" t="n"/>
+      <c r="BP84" s="25" t="n"/>
+      <c r="BQ84" s="27" t="n"/>
+      <c r="BR84" s="28" t="n"/>
+      <c r="BS84" s="28" t="n"/>
+      <c r="BT84" s="28" t="n"/>
+      <c r="BU84" s="25" t="n"/>
+      <c r="BV84" s="29" t="n"/>
+      <c r="BW84" s="24" t="n"/>
+      <c r="BX84" s="30" t="n"/>
+      <c r="BY84" s="27" t="n"/>
+      <c r="BZ84" s="24" t="n"/>
+      <c r="CA84" s="31" t="n"/>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>f15dccef86584b5d</t>
+        </is>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:04.952889Z</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>54745</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J85" s="25" t="n"/>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L85" s="26" t="n">
+        <v>245</v>
+      </c>
+      <c r="M85" s="27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N85" s="28" t="n">
+        <v>0.289855</v>
+      </c>
+      <c r="O85" s="28" t="n">
+        <v>0.586418</v>
+      </c>
+      <c r="P85" s="28" t="n"/>
+      <c r="Q85" s="28" t="n">
+        <v>0.296418</v>
+      </c>
+      <c r="R85" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S85" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T85" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U85" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V85" s="24" t="n"/>
+      <c r="W85" s="26" t="n"/>
+      <c r="X85" s="26" t="n"/>
+      <c r="Y85" s="25" t="n"/>
+      <c r="Z85" s="26" t="n"/>
+      <c r="AA85" s="28" t="n"/>
+      <c r="AB85" s="28" t="n"/>
+      <c r="AC85" s="30" t="n"/>
+      <c r="AD85" s="24" t="n"/>
+      <c r="AE85" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.2900 (aec-lol-est-pnga-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF85" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG85" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH85" s="24" t="n"/>
+      <c r="AI85" s="31" t="n"/>
+      <c r="AJ85" s="31" t="n"/>
+      <c r="AK85" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL85" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM85" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN85" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO85" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP85" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AQ85" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AR85" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AS85" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AT85" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AU85" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AV85" s="24" t="n"/>
+      <c r="AW85" s="24" t="n"/>
+      <c r="AX85" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY85" s="24" t="n"/>
+      <c r="AZ85" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA85" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BB85" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC85" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD85" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BE85" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF85" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG85" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH85" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:04.952889Z</t>
+        </is>
+      </c>
+      <c r="BI85" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ85" s="25" t="n"/>
+      <c r="BK85" s="26" t="n">
+        <v>245</v>
+      </c>
+      <c r="BL85" s="27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BM85" s="28" t="n">
+        <v>0.289855</v>
+      </c>
+      <c r="BN85" s="28" t="n"/>
+      <c r="BO85" s="28" t="n"/>
+      <c r="BP85" s="25" t="n"/>
+      <c r="BQ85" s="27" t="n"/>
+      <c r="BR85" s="28" t="n"/>
+      <c r="BS85" s="28" t="n"/>
+      <c r="BT85" s="28" t="n"/>
+      <c r="BU85" s="25" t="n"/>
+      <c r="BV85" s="29" t="n"/>
+      <c r="BW85" s="24" t="n"/>
+      <c r="BX85" s="30" t="n"/>
+      <c r="BY85" s="27" t="n"/>
+      <c r="BZ85" s="24" t="n"/>
+      <c r="CA85" s="31" t="n"/>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="24" t="inlineStr">
+        <is>
+          <t>26f5ce8f779549de</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:44.609761Z</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="inlineStr">
+        <is>
+          <t>56113</t>
+        </is>
+      </c>
+      <c r="E86" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F86" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="G86" s="24" t="inlineStr">
+        <is>
+          <t>Endless Journey</t>
+        </is>
+      </c>
+      <c r="H86" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I86" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J86" s="25" t="n"/>
+      <c r="K86" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L86" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M86" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N86" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O86" s="28" t="n">
+        <v>0.652434</v>
+      </c>
+      <c r="P86" s="28" t="n"/>
+      <c r="Q86" s="28" t="n">
+        <v>0.132434</v>
+      </c>
+      <c r="R86" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S86" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T86" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U86" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V86" s="24" t="n"/>
+      <c r="W86" s="26" t="n"/>
+      <c r="X86" s="26" t="n"/>
+      <c r="Y86" s="25" t="n"/>
+      <c r="Z86" s="26" t="n"/>
+      <c r="AA86" s="28" t="n"/>
+      <c r="AB86" s="28" t="n"/>
+      <c r="AC86" s="30" t="n"/>
+      <c r="AD86" s="24" t="n"/>
+      <c r="AE86" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (aec-cs2-ica-ej-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF86" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG86" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH86" s="24" t="n"/>
+      <c r="AI86" s="31" t="n"/>
+      <c r="AJ86" s="31" t="n"/>
+      <c r="AK86" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL86" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM86" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN86" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO86" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP86" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AQ86" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AR86" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AS86" s="24" t="inlineStr">
+        <is>
+          <t>Endless Journey</t>
+        </is>
+      </c>
+      <c r="AT86" s="24" t="inlineStr">
+        <is>
+          <t>Endless Journey</t>
+        </is>
+      </c>
+      <c r="AU86" s="24" t="inlineStr">
+        <is>
+          <t>Endless Journey</t>
+        </is>
+      </c>
+      <c r="AV86" s="24" t="n"/>
+      <c r="AW86" s="24" t="n"/>
+      <c r="AX86" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY86" s="24" t="n"/>
+      <c r="AZ86" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA86" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BB86" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC86" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD86" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BE86" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF86" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG86" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH86" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:44.609761Z</t>
+        </is>
+      </c>
+      <c r="BI86" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ86" s="25" t="n"/>
+      <c r="BK86" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL86" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM86" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN86" s="28" t="n"/>
+      <c r="BO86" s="28" t="n"/>
+      <c r="BP86" s="25" t="n"/>
+      <c r="BQ86" s="27" t="n"/>
+      <c r="BR86" s="28" t="n"/>
+      <c r="BS86" s="28" t="n"/>
+      <c r="BT86" s="28" t="n"/>
+      <c r="BU86" s="25" t="n"/>
+      <c r="BV86" s="29" t="n"/>
+      <c r="BW86" s="24" t="n"/>
+      <c r="BX86" s="30" t="n"/>
+      <c r="BY86" s="27" t="n"/>
+      <c r="BZ86" s="24" t="n"/>
+      <c r="CA86" s="31" t="n"/>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>56fd16b43e1349fc</t>
+        </is>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:44.830487Z</t>
+        </is>
+      </c>
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>56757</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F87" s="24" t="inlineStr">
+        <is>
+          <t>MAGICOS</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>Blitzkrieg</t>
+        </is>
+      </c>
+      <c r="H87" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I87" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J87" s="25" t="n"/>
+      <c r="K87" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L87" s="26" t="n">
+        <v>669</v>
+      </c>
+      <c r="M87" s="27" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="N87" s="28" t="n">
+        <v>0.130039</v>
+      </c>
+      <c r="O87" s="28" t="n">
+        <v>0.598244</v>
+      </c>
+      <c r="P87" s="28" t="n"/>
+      <c r="Q87" s="28" t="n">
+        <v>0.468244</v>
+      </c>
+      <c r="R87" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S87" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T87" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U87" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V87" s="24" t="n"/>
+      <c r="W87" s="26" t="n"/>
+      <c r="X87" s="26" t="n"/>
+      <c r="Y87" s="25" t="n"/>
+      <c r="Z87" s="26" t="n"/>
+      <c r="AA87" s="28" t="n"/>
+      <c r="AB87" s="28" t="n"/>
+      <c r="AC87" s="30" t="n"/>
+      <c r="AD87" s="24" t="n"/>
+      <c r="AE87" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.1300 (aec-cs2-mag-bk-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF87" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG87" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH87" s="24" t="n"/>
+      <c r="AI87" s="31" t="n"/>
+      <c r="AJ87" s="31" t="n"/>
+      <c r="AK87" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL87" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM87" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN87" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO87" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP87" s="24" t="inlineStr">
+        <is>
+          <t>MAGICOS</t>
+        </is>
+      </c>
+      <c r="AQ87" s="24" t="inlineStr">
+        <is>
+          <t>MAGICOS</t>
+        </is>
+      </c>
+      <c r="AR87" s="24" t="inlineStr">
+        <is>
+          <t>MAGICOS</t>
+        </is>
+      </c>
+      <c r="AS87" s="24" t="inlineStr">
+        <is>
+          <t>Blitzkrieg</t>
+        </is>
+      </c>
+      <c r="AT87" s="24" t="inlineStr">
+        <is>
+          <t>Blitzkrieg</t>
+        </is>
+      </c>
+      <c r="AU87" s="24" t="inlineStr">
+        <is>
+          <t>Blitzkrieg</t>
+        </is>
+      </c>
+      <c r="AV87" s="24" t="n"/>
+      <c r="AW87" s="24" t="n"/>
+      <c r="AX87" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY87" s="24" t="n"/>
+      <c r="AZ87" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA87" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BB87" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC87" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD87" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BE87" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF87" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG87" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH87" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:44.830487Z</t>
+        </is>
+      </c>
+      <c r="BI87" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ87" s="25" t="n"/>
+      <c r="BK87" s="26" t="n">
+        <v>669</v>
+      </c>
+      <c r="BL87" s="27" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="BM87" s="28" t="n">
+        <v>0.130039</v>
+      </c>
+      <c r="BN87" s="28" t="n"/>
+      <c r="BO87" s="28" t="n"/>
+      <c r="BP87" s="25" t="n"/>
+      <c r="BQ87" s="27" t="n"/>
+      <c r="BR87" s="28" t="n"/>
+      <c r="BS87" s="28" t="n"/>
+      <c r="BT87" s="28" t="n"/>
+      <c r="BU87" s="25" t="n"/>
+      <c r="BV87" s="29" t="n"/>
+      <c r="BW87" s="24" t="n"/>
+      <c r="BX87" s="30" t="n"/>
+      <c r="BY87" s="27" t="n"/>
+      <c r="BZ87" s="24" t="n"/>
+      <c r="CA87" s="31" t="n"/>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="A88" s="24" t="inlineStr">
+        <is>
+          <t>016345fa98e04c4d</t>
+        </is>
+      </c>
+      <c r="B88" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:45.030222Z</t>
+        </is>
+      </c>
+      <c r="C88" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D88" s="24" t="inlineStr">
+        <is>
+          <t>54667</t>
+        </is>
+      </c>
+      <c r="E88" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F88" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="G88" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="H88" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I88" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J88" s="25" t="n"/>
+      <c r="K88" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L88" s="26" t="n">
+        <v>335</v>
+      </c>
+      <c r="M88" s="27" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="N88" s="28" t="n">
+        <v>0.229885</v>
+      </c>
+      <c r="O88" s="28" t="n">
+        <v>0.558097</v>
+      </c>
+      <c r="P88" s="28" t="n"/>
+      <c r="Q88" s="28" t="n">
+        <v>0.328097</v>
+      </c>
+      <c r="R88" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S88" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T88" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U88" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V88" s="24" t="n"/>
+      <c r="W88" s="26" t="n"/>
+      <c r="X88" s="26" t="n"/>
+      <c r="Y88" s="25" t="n"/>
+      <c r="Z88" s="26" t="n"/>
+      <c r="AA88" s="28" t="n"/>
+      <c r="AB88" s="28" t="n"/>
+      <c r="AC88" s="30" t="n"/>
+      <c r="AD88" s="24" t="n"/>
+      <c r="AE88" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.2300 (aec-cs2-hat-paina-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF88" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG88" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH88" s="24" t="n"/>
+      <c r="AI88" s="31" t="n"/>
+      <c r="AJ88" s="31" t="n"/>
+      <c r="AK88" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL88" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM88" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN88" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO88" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP88" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AQ88" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AR88" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AS88" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="AT88" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="AU88" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="AV88" s="24" t="n"/>
+      <c r="AW88" s="24" t="n"/>
+      <c r="AX88" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY88" s="24" t="n"/>
+      <c r="AZ88" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA88" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BB88" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC88" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD88" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BE88" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF88" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG88" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH88" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:45.030222Z</t>
+        </is>
+      </c>
+      <c r="BI88" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ88" s="25" t="n"/>
+      <c r="BK88" s="26" t="n">
+        <v>335</v>
+      </c>
+      <c r="BL88" s="27" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BM88" s="28" t="n">
+        <v>0.229885</v>
+      </c>
+      <c r="BN88" s="28" t="n"/>
+      <c r="BO88" s="28" t="n"/>
+      <c r="BP88" s="25" t="n"/>
+      <c r="BQ88" s="27" t="n"/>
+      <c r="BR88" s="28" t="n"/>
+      <c r="BS88" s="28" t="n"/>
+      <c r="BT88" s="28" t="n"/>
+      <c r="BU88" s="25" t="n"/>
+      <c r="BV88" s="29" t="n"/>
+      <c r="BW88" s="24" t="n"/>
+      <c r="BX88" s="30" t="n"/>
+      <c r="BY88" s="27" t="n"/>
+      <c r="BZ88" s="24" t="n"/>
+      <c r="CA88" s="31" t="n"/>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="A89" s="24" t="inlineStr">
+        <is>
+          <t>817f81c59de8400e</t>
+        </is>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:45.236193Z</t>
+        </is>
+      </c>
+      <c r="C89" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>54669</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F89" s="24" t="inlineStr">
+        <is>
+          <t>QUINTESSÊNCIA</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="inlineStr">
+        <is>
+          <t>MIBR Academy</t>
+        </is>
+      </c>
+      <c r="H89" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I89" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J89" s="25" t="n"/>
+      <c r="K89" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L89" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M89" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N89" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O89" s="28" t="n">
+        <v>0.660032</v>
+      </c>
+      <c r="P89" s="28" t="n"/>
+      <c r="Q89" s="28" t="n">
+        <v>-0.029968</v>
+      </c>
+      <c r="R89" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T89" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U89" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V89" s="24" t="n"/>
+      <c r="W89" s="26" t="n"/>
+      <c r="X89" s="26" t="n"/>
+      <c r="Y89" s="25" t="n"/>
+      <c r="Z89" s="26" t="n"/>
+      <c r="AA89" s="28" t="n"/>
+      <c r="AB89" s="28" t="n"/>
+      <c r="AC89" s="30" t="n"/>
+      <c r="AD89" s="24" t="n"/>
+      <c r="AE89" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (aec-cs2-mibra-quin-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF89" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG89" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH89" s="24" t="n"/>
+      <c r="AI89" s="31" t="n"/>
+      <c r="AJ89" s="31" t="n"/>
+      <c r="AK89" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL89" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM89" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN89" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO89" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP89" s="24" t="inlineStr">
+        <is>
+          <t>QUINTESSÊNCIA</t>
+        </is>
+      </c>
+      <c r="AQ89" s="24" t="inlineStr">
+        <is>
+          <t>QUINTESSÊNCIA</t>
+        </is>
+      </c>
+      <c r="AR89" s="24" t="inlineStr">
+        <is>
+          <t>QUINTESSÊNCIA</t>
+        </is>
+      </c>
+      <c r="AS89" s="24" t="inlineStr">
+        <is>
+          <t>MIBR Academy</t>
+        </is>
+      </c>
+      <c r="AT89" s="24" t="inlineStr">
+        <is>
+          <t>MIBR Academy</t>
+        </is>
+      </c>
+      <c r="AU89" s="24" t="inlineStr">
+        <is>
+          <t>MIBR Academy</t>
+        </is>
+      </c>
+      <c r="AV89" s="24" t="n"/>
+      <c r="AW89" s="24" t="n"/>
+      <c r="AX89" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY89" s="24" t="n"/>
+      <c r="AZ89" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA89" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BB89" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC89" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD89" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BE89" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF89" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG89" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH89" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:45.236193Z</t>
+        </is>
+      </c>
+      <c r="BI89" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ89" s="25" t="n"/>
+      <c r="BK89" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL89" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM89" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN89" s="28" t="n"/>
+      <c r="BO89" s="28" t="n"/>
+      <c r="BP89" s="25" t="n"/>
+      <c r="BQ89" s="27" t="n"/>
+      <c r="BR89" s="28" t="n"/>
+      <c r="BS89" s="28" t="n"/>
+      <c r="BT89" s="28" t="n"/>
+      <c r="BU89" s="25" t="n"/>
+      <c r="BV89" s="29" t="n"/>
+      <c r="BW89" s="24" t="n"/>
+      <c r="BX89" s="30" t="n"/>
+      <c r="BY89" s="27" t="n"/>
+      <c r="BZ89" s="24" t="n"/>
+      <c r="CA89" s="31" t="n"/>
+    </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t>14ea1c3a676f493a</t>
+        </is>
+      </c>
+      <c r="B90" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:45.443663Z</t>
+        </is>
+      </c>
+      <c r="C90" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D90" s="24" t="inlineStr">
+        <is>
+          <t>54672</t>
+        </is>
+      </c>
+      <c r="E90" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F90" s="24" t="inlineStr">
+        <is>
+          <t>METANOIA WOLVES</t>
+        </is>
+      </c>
+      <c r="G90" s="24" t="inlineStr">
+        <is>
+          <t>RED Canids Academy</t>
+        </is>
+      </c>
+      <c r="H90" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I90" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J90" s="25" t="n"/>
+      <c r="K90" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L90" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M90" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N90" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O90" s="28" t="n">
+        <v>0.885084</v>
+      </c>
+      <c r="P90" s="28" t="n"/>
+      <c r="Q90" s="28" t="n">
+        <v>0.295084</v>
+      </c>
+      <c r="R90" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S90" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T90" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U90" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V90" s="24" t="n"/>
+      <c r="W90" s="26" t="n"/>
+      <c r="X90" s="26" t="n"/>
+      <c r="Y90" s="25" t="n"/>
+      <c r="Z90" s="26" t="n"/>
+      <c r="AA90" s="28" t="n"/>
+      <c r="AB90" s="28" t="n"/>
+      <c r="AC90" s="30" t="n"/>
+      <c r="AD90" s="24" t="n"/>
+      <c r="AE90" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (aec-cs2-reda-mw-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF90" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG90" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH90" s="24" t="n"/>
+      <c r="AI90" s="31" t="n"/>
+      <c r="AJ90" s="31" t="n"/>
+      <c r="AK90" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL90" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM90" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN90" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO90" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP90" s="24" t="inlineStr">
+        <is>
+          <t>METANOIA WOLVES</t>
+        </is>
+      </c>
+      <c r="AQ90" s="24" t="inlineStr">
+        <is>
+          <t>METANOIA WOLVES</t>
+        </is>
+      </c>
+      <c r="AR90" s="24" t="inlineStr">
+        <is>
+          <t>METANOIA WOLVES</t>
+        </is>
+      </c>
+      <c r="AS90" s="24" t="inlineStr">
+        <is>
+          <t>RED Canids Academy</t>
+        </is>
+      </c>
+      <c r="AT90" s="24" t="inlineStr">
+        <is>
+          <t>RED Canids Academy</t>
+        </is>
+      </c>
+      <c r="AU90" s="24" t="inlineStr">
+        <is>
+          <t>RED Canids Academy</t>
+        </is>
+      </c>
+      <c r="AV90" s="24" t="n"/>
+      <c r="AW90" s="24" t="n"/>
+      <c r="AX90" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY90" s="24" t="n"/>
+      <c r="AZ90" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA90" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BB90" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC90" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD90" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BE90" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF90" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG90" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH90" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:45.443663Z</t>
+        </is>
+      </c>
+      <c r="BI90" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ90" s="25" t="n"/>
+      <c r="BK90" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL90" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM90" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN90" s="28" t="n"/>
+      <c r="BO90" s="28" t="n"/>
+      <c r="BP90" s="25" t="n"/>
+      <c r="BQ90" s="27" t="n"/>
+      <c r="BR90" s="28" t="n"/>
+      <c r="BS90" s="28" t="n"/>
+      <c r="BT90" s="28" t="n"/>
+      <c r="BU90" s="25" t="n"/>
+      <c r="BV90" s="29" t="n"/>
+      <c r="BW90" s="24" t="n"/>
+      <c r="BX90" s="30" t="n"/>
+      <c r="BY90" s="27" t="n"/>
+      <c r="BZ90" s="24" t="n"/>
+      <c r="CA90" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0###"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0###"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,11 +217,38 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -300,8 +327,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA90" headerRowCount="1">
-  <autoFilter ref="A1:CA90"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA86" headerRowCount="1">
+  <autoFilter ref="A1:CA86"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -738,22 +765,23 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$90)</f>
+        <f>COUNTA('Picks'!$A$2:$A$86)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$90,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$86,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$90,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$86,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")+COUNTIFS('Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"win")+COUNTIFS('Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -778,22 +806,23 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$90,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$86,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"win")/(COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"win")+COUNTIFS('Picks'!$BX$2:$BX$90,"&gt;0",'Picks'!$V$2:$V$90,"loss")),0)</f>
+      <c r="E7" s="32">
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"win")/(COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"win")+COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$90)/SUM('Picks'!$BX$2:$BX$90),0)</f>
+      <c r="G7" s="32">
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$86)/SUM('Picks'!$BX$2:$BX$86),0)</f>
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -817,23 +846,24 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$90)</f>
+      <c r="A10" s="33">
+        <f>SUM('Picks'!$BY$2:$BY$86)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$90,"&lt;&gt;",'Picks'!$AB$2:$AB$90),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$86,"&lt;&gt;",'Picks'!$AB$2:$AB$86),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$90,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$90,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$86,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$86,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$90,'Picks'!$AM$2:$AM$90,"QUALIFIED_SHADOW_CALL")</f>
+      <c r="G10" s="33">
+        <f>SUMIFS('Picks'!$AC$2:$AC$86,'Picks'!$AM$2:$AM$86,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -885,27 +915,27 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A14,'Picks'!$U$2:$U$86,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A14,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A14,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="34">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$90,'Picks'!$H$2:$H$90,$A14)</f>
+      <c r="F14" s="35">
+        <f>SUMIFS('Picks'!$BY$2:$BY$86,'Picks'!$H$2:$H$86,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$90,'Picks'!$H$2:$H$90,$A14,'Picks'!$U$2:$U$90,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$86,'Picks'!$H$2:$H$86,$A14,'Picks'!$U$2:$U$86,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -916,27 +946,27 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A15,'Picks'!$U$2:$U$86,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A15,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A15,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="36">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$90,'Picks'!$H$2:$H$90,$A15)</f>
+      <c r="F15" s="37">
+        <f>SUMIFS('Picks'!$BY$2:$BY$86,'Picks'!$H$2:$H$86,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$90,'Picks'!$H$2:$H$90,$A15,'Picks'!$U$2:$U$90,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$86,'Picks'!$H$2:$H$86,$A15,'Picks'!$U$2:$U$86,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -947,30 +977,31 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A16,'Picks'!$U$2:$U$86,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A16,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled",'Picks'!$V$2:$V$90,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A16,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="34">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$90,'Picks'!$H$2:$H$90,$A16)</f>
+      <c r="F16" s="35">
+        <f>SUMIFS('Picks'!$BY$2:$BY$86,'Picks'!$H$2:$H$86,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$90,'Picks'!$H$2:$H$90,$A16,'Picks'!$U$2:$U$90,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$86,'Picks'!$H$2:$H$86,$A16,'Picks'!$U$2:$U$86,"settled"),0)</f>
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
@@ -996,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA90"/>
+  <dimension ref="A1:CA86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1523,7 +1554,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="25" t="n"/>
+      <c r="J2" s="38" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1532,7 +1563,7 @@
       <c r="L2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M2" s="27" t="n">
+      <c r="M2" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1572,11 +1603,11 @@
       <c r="X2" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="Y2" s="25" t="n"/>
+      <c r="Y2" s="38" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n">
+      <c r="AC2" s="40" t="n">
         <v>1.755</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1713,11 +1744,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="25" t="n"/>
+      <c r="BJ2" s="38" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL2" s="27" t="n">
+      <c r="BL2" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1727,18 +1758,18 @@
         <v>0.455446</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n"/>
+      <c r="BP2" s="38" t="n"/>
+      <c r="BQ2" s="39" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="25" t="n"/>
+      <c r="BU2" s="38" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="30" t="n">
+      <c r="BX2" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="27" t="n">
+      <c r="BY2" s="39" t="n">
         <v>1.17</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1798,7 +1829,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="25" t="n"/>
+      <c r="J3" s="38" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1807,7 +1838,7 @@
       <c r="L3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M3" s="27" t="n">
+      <c r="M3" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1847,11 +1878,11 @@
       <c r="X3" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y3" s="25" t="n"/>
+      <c r="Y3" s="38" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n">
+      <c r="AC3" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -1988,11 +2019,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="25" t="n"/>
+      <c r="BJ3" s="38" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL3" s="27" t="n">
+      <c r="BL3" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2002,18 +2033,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
+      <c r="BP3" s="38" t="n"/>
+      <c r="BQ3" s="39" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="25" t="n"/>
+      <c r="BU3" s="38" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="30" t="n">
+      <c r="BX3" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="27" t="n">
+      <c r="BY3" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2073,7 +2104,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n"/>
+      <c r="J4" s="38" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2082,7 +2113,7 @@
       <c r="L4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M4" s="27" t="n">
+      <c r="M4" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2122,11 +2153,11 @@
       <c r="X4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="25" t="n"/>
+      <c r="Y4" s="38" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n">
+      <c r="AC4" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2263,11 +2294,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="25" t="n"/>
+      <c r="BJ4" s="38" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL4" s="27" t="n">
+      <c r="BL4" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2277,18 +2308,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n"/>
+      <c r="BP4" s="38" t="n"/>
+      <c r="BQ4" s="39" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="25" t="n"/>
+      <c r="BU4" s="38" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="30" t="n">
+      <c r="BX4" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" s="27" t="n">
+      <c r="BY4" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
@@ -2348,7 +2379,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="25" t="n"/>
+      <c r="J5" s="38" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2357,7 +2388,7 @@
       <c r="L5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M5" s="27" t="n">
+      <c r="M5" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2397,11 +2428,11 @@
       <c r="X5" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y5" s="25" t="n"/>
+      <c r="Y5" s="38" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n">
+      <c r="AC5" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2538,11 +2569,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="25" t="n"/>
+      <c r="BJ5" s="38" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL5" s="27" t="n">
+      <c r="BL5" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2552,18 +2583,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
+      <c r="BP5" s="38" t="n"/>
+      <c r="BQ5" s="39" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="25" t="n"/>
+      <c r="BU5" s="38" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="30" t="n">
+      <c r="BX5" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" s="27" t="n">
+      <c r="BY5" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
@@ -2623,7 +2654,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="25" t="n"/>
+      <c r="J6" s="38" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2632,7 +2663,7 @@
       <c r="L6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M6" s="27" t="n">
+      <c r="M6" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2672,11 +2703,11 @@
       <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="25" t="n"/>
+      <c r="Y6" s="38" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n">
+      <c r="AC6" s="40" t="n">
         <v>1.2019</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2813,11 +2844,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="25" t="n"/>
+      <c r="BJ6" s="38" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL6" s="27" t="n">
+      <c r="BL6" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2827,18 +2858,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
+      <c r="BP6" s="38" t="n"/>
+      <c r="BQ6" s="39" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="25" t="n"/>
+      <c r="BU6" s="38" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n">
+      <c r="BX6" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" s="27" t="n">
+      <c r="BY6" s="39" t="n">
         <v>0.961538</v>
       </c>
       <c r="BZ6" s="24" t="inlineStr">
@@ -2898,7 +2929,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J7" s="25" t="n"/>
+      <c r="J7" s="38" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2907,7 +2938,7 @@
       <c r="L7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M7" s="27" t="n">
+      <c r="M7" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2947,11 +2978,11 @@
       <c r="X7" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" s="25" t="n"/>
+      <c r="Y7" s="38" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n">
+      <c r="AC7" s="40" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3088,11 +3119,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="25" t="n"/>
+      <c r="BJ7" s="38" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL7" s="27" t="n">
+      <c r="BL7" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3102,18 +3133,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
+      <c r="BP7" s="38" t="n"/>
+      <c r="BQ7" s="39" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="25" t="n"/>
+      <c r="BU7" s="38" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="30" t="n">
+      <c r="BX7" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" s="27" t="n">
+      <c r="BY7" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ7" s="24" t="inlineStr">
@@ -3173,7 +3204,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J8" s="25" t="n"/>
+      <c r="J8" s="38" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3182,7 +3213,7 @@
       <c r="L8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M8" s="27" t="n">
+      <c r="M8" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3222,11 +3253,11 @@
       <c r="X8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y8" s="25" t="n"/>
+      <c r="Y8" s="38" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n">
+      <c r="AC8" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3363,11 +3394,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="25" t="n"/>
+      <c r="BJ8" s="38" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL8" s="27" t="n">
+      <c r="BL8" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3377,18 +3408,18 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
+      <c r="BP8" s="38" t="n"/>
+      <c r="BQ8" s="39" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="25" t="n"/>
+      <c r="BU8" s="38" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n">
+      <c r="BX8" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" s="27" t="n">
+      <c r="BY8" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ8" s="24" t="inlineStr">
@@ -3448,7 +3479,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J9" s="25" t="n"/>
+      <c r="J9" s="38" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3457,7 +3488,7 @@
       <c r="L9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M9" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3497,11 +3528,11 @@
       <c r="X9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="25" t="n"/>
+      <c r="Y9" s="38" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n">
+      <c r="AC9" s="40" t="n">
         <v>0.9804</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
@@ -3638,11 +3669,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="25" t="n"/>
+      <c r="BJ9" s="38" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL9" s="27" t="n">
+      <c r="BL9" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3652,18 +3683,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
+      <c r="BP9" s="38" t="n"/>
+      <c r="BQ9" s="39" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
+      <c r="BU9" s="38" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n">
+      <c r="BX9" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" s="27" t="n">
+      <c r="BY9" s="39" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ9" s="24" t="inlineStr">
@@ -3723,7 +3754,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J10" s="25" t="n"/>
+      <c r="J10" s="38" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3732,7 +3763,7 @@
       <c r="L10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M10" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3772,11 +3803,11 @@
       <c r="X10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y10" s="25" t="n"/>
+      <c r="Y10" s="38" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n">
+      <c r="AC10" s="40" t="n">
         <v>1.2681</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -3913,11 +3944,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="25" t="n"/>
+      <c r="BJ10" s="38" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL10" s="27" t="n">
+      <c r="BL10" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -3927,18 +3958,18 @@
         <v>0.577114</v>
       </c>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
+      <c r="BP10" s="38" t="n"/>
+      <c r="BQ10" s="39" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
+      <c r="BU10" s="38" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n">
+      <c r="BX10" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" s="27" t="n">
+      <c r="BY10" s="39" t="n">
         <v>0.724638</v>
       </c>
       <c r="BZ10" s="24" t="inlineStr">
@@ -3998,7 +4029,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J11" s="25" t="n"/>
+      <c r="J11" s="38" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4007,7 +4038,7 @@
       <c r="L11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M11" s="27" t="n">
+      <c r="M11" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -4047,11 +4078,11 @@
       <c r="X11" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="25" t="n"/>
+      <c r="Y11" s="38" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n">
+      <c r="AC11" s="40" t="n">
         <v>1.275</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4188,11 +4219,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="25" t="n"/>
+      <c r="BJ11" s="38" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL11" s="27" t="n">
+      <c r="BL11" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4202,18 +4233,18 @@
         <v>0.492537</v>
       </c>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
+      <c r="BP11" s="38" t="n"/>
+      <c r="BQ11" s="39" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
+      <c r="BU11" s="38" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n">
+      <c r="BX11" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" s="27" t="n">
+      <c r="BY11" s="39" t="n">
         <v>1.02</v>
       </c>
       <c r="BZ11" s="24" t="inlineStr">
@@ -4273,7 +4304,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="25" t="n"/>
+      <c r="J12" s="38" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4282,7 +4313,7 @@
       <c r="L12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M12" s="27" t="n">
+      <c r="M12" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4322,11 +4353,11 @@
       <c r="X12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" s="25" t="n"/>
+      <c r="Y12" s="38" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n">
+      <c r="AC12" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
@@ -4463,11 +4494,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="25" t="n"/>
+      <c r="BJ12" s="38" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL12" s="27" t="n">
+      <c r="BL12" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4477,18 +4508,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
+      <c r="BP12" s="38" t="n"/>
+      <c r="BQ12" s="39" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
+      <c r="BU12" s="38" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n">
+      <c r="BX12" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" s="27" t="n">
+      <c r="BY12" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ12" s="24" t="inlineStr">
@@ -4548,7 +4579,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J13" s="25" t="n"/>
+      <c r="J13" s="38" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4557,7 +4588,7 @@
       <c r="L13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M13" s="27" t="n">
+      <c r="M13" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4597,11 +4628,11 @@
       <c r="X13" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" s="25" t="n"/>
+      <c r="Y13" s="38" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n">
+      <c r="AC13" s="40" t="n">
         <v>1.2255</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
@@ -4738,11 +4769,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="25" t="n"/>
+      <c r="BJ13" s="38" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL13" s="27" t="n">
+      <c r="BL13" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4752,18 +4783,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
+      <c r="BP13" s="38" t="n"/>
+      <c r="BQ13" s="39" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
+      <c r="BU13" s="38" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n">
+      <c r="BX13" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY13" s="27" t="n">
+      <c r="BY13" s="39" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ13" s="24" t="inlineStr">
@@ -4823,7 +4854,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n"/>
+      <c r="J14" s="38" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4832,7 +4863,7 @@
       <c r="L14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M14" s="27" t="n">
+      <c r="M14" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -4872,11 +4903,11 @@
       <c r="X14" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="25" t="n"/>
+      <c r="Y14" s="38" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n">
+      <c r="AC14" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -5013,11 +5044,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="25" t="n"/>
+      <c r="BJ14" s="38" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL14" s="27" t="n">
+      <c r="BL14" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -5027,18 +5058,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
+      <c r="BP14" s="38" t="n"/>
+      <c r="BQ14" s="39" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="25" t="n"/>
+      <c r="BU14" s="38" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n">
+      <c r="BX14" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY14" s="27" t="n">
+      <c r="BY14" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ14" s="24" t="inlineStr">
@@ -5098,7 +5129,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="25" t="n"/>
+      <c r="J15" s="38" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5107,7 +5138,7 @@
       <c r="L15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M15" s="27" t="n">
+      <c r="M15" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -5147,11 +5178,11 @@
       <c r="X15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="25" t="n"/>
+      <c r="Y15" s="38" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n">
+      <c r="AC15" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
@@ -5288,11 +5319,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="25" t="n"/>
+      <c r="BJ15" s="38" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL15" s="27" t="n">
+      <c r="BL15" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5302,18 +5333,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
+      <c r="BP15" s="38" t="n"/>
+      <c r="BQ15" s="39" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
+      <c r="BU15" s="38" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n">
+      <c r="BX15" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY15" s="27" t="n">
+      <c r="BY15" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ15" s="24" t="inlineStr">
@@ -5373,7 +5404,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n"/>
+      <c r="J16" s="38" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5382,7 +5413,7 @@
       <c r="L16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M16" s="27" t="n">
+      <c r="M16" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5422,11 +5453,11 @@
       <c r="X16" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" s="25" t="n"/>
+      <c r="Y16" s="38" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n">
+      <c r="AC16" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
@@ -5563,11 +5594,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="25" t="n"/>
+      <c r="BJ16" s="38" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL16" s="27" t="n">
+      <c r="BL16" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5577,18 +5608,18 @@
         <v>0.522388</v>
       </c>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
+      <c r="BP16" s="38" t="n"/>
+      <c r="BQ16" s="39" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
+      <c r="BU16" s="38" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n">
+      <c r="BX16" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY16" s="27" t="n">
+      <c r="BY16" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ16" s="24" t="inlineStr">
@@ -5648,7 +5679,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n"/>
+      <c r="J17" s="38" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5657,7 +5688,7 @@
       <c r="L17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M17" s="27" t="n">
+      <c r="M17" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5697,11 +5728,11 @@
       <c r="X17" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y17" s="25" t="n"/>
+      <c r="Y17" s="38" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n">
+      <c r="AC17" s="40" t="n">
         <v>0.9258999999999999</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
@@ -5838,11 +5869,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ17" s="25" t="n"/>
+      <c r="BJ17" s="38" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL17" s="27" t="n">
+      <c r="BL17" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -5852,18 +5883,18 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
+      <c r="BP17" s="38" t="n"/>
+      <c r="BQ17" s="39" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
+      <c r="BU17" s="38" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n">
+      <c r="BX17" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY17" s="27" t="n">
+      <c r="BY17" s="39" t="n">
         <v>0.925926</v>
       </c>
       <c r="BZ17" s="24" t="inlineStr">
@@ -5923,7 +5954,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n"/>
+      <c r="J18" s="38" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5932,7 +5963,7 @@
       <c r="L18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="M18" s="27" t="n">
+      <c r="M18" s="39" t="n">
         <v>2.11</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -5972,11 +6003,11 @@
       <c r="X18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y18" s="25" t="n"/>
+      <c r="Y18" s="38" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n">
+      <c r="AC18" s="40" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
@@ -6113,11 +6144,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ18" s="25" t="n"/>
+      <c r="BJ18" s="38" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="BL18" s="27" t="n">
+      <c r="BL18" s="39" t="n">
         <v>2.11</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -6127,18 +6158,18 @@
         <v>0.472637</v>
       </c>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
+      <c r="BP18" s="38" t="n"/>
+      <c r="BQ18" s="39" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
+      <c r="BU18" s="38" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n">
+      <c r="BX18" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" s="27" t="n">
+      <c r="BY18" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ18" s="24" t="inlineStr">
@@ -6198,7 +6229,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n"/>
+      <c r="J19" s="38" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6207,7 +6238,7 @@
       <c r="L19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M19" s="27" t="n">
+      <c r="M19" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -6247,11 +6278,11 @@
       <c r="X19" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y19" s="25" t="n"/>
+      <c r="Y19" s="38" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n">
+      <c r="AC19" s="40" t="n">
         <v>1.2</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
@@ -6388,11 +6419,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ19" s="25" t="n"/>
+      <c r="BJ19" s="38" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL19" s="27" t="n">
+      <c r="BL19" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -6402,18 +6433,18 @@
         <v>0.552239</v>
       </c>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
+      <c r="BP19" s="38" t="n"/>
+      <c r="BQ19" s="39" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="25" t="n"/>
+      <c r="BU19" s="38" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="30" t="n">
+      <c r="BX19" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY19" s="27" t="n">
+      <c r="BY19" s="39" t="n">
         <v>0.8</v>
       </c>
       <c r="BZ19" s="24" t="inlineStr">
@@ -6473,7 +6504,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J20" s="25" t="n"/>
+      <c r="J20" s="38" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6482,7 +6513,7 @@
       <c r="L20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="M20" s="27" t="n">
+      <c r="M20" s="39" t="n">
         <v>2.06</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6522,11 +6553,11 @@
       <c r="X20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y20" s="25" t="n"/>
+      <c r="Y20" s="38" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n">
+      <c r="AC20" s="40" t="n">
         <v>0.795</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
@@ -6663,11 +6694,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ20" s="25" t="n"/>
+      <c r="BJ20" s="38" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="BL20" s="27" t="n">
+      <c r="BL20" s="39" t="n">
         <v>2.06</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -6677,18 +6708,18 @@
         <v>0.482587</v>
       </c>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
+      <c r="BP20" s="38" t="n"/>
+      <c r="BQ20" s="39" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="25" t="n"/>
+      <c r="BU20" s="38" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="30" t="n">
+      <c r="BX20" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" s="27" t="n">
+      <c r="BY20" s="39" t="n">
         <v>1.06</v>
       </c>
       <c r="BZ20" s="24" t="inlineStr">
@@ -6748,7 +6779,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J21" s="25" t="n"/>
+      <c r="J21" s="38" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6757,7 +6788,7 @@
       <c r="L21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M21" s="27" t="n">
+      <c r="M21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
@@ -6799,11 +6830,11 @@
       <c r="X21" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y21" s="25" t="n"/>
+      <c r="Y21" s="38" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n">
+      <c r="AC21" s="40" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
@@ -6862,11 +6893,11 @@
         </is>
       </c>
       <c r="BI21" s="24" t="n"/>
-      <c r="BJ21" s="25" t="n"/>
+      <c r="BJ21" s="38" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL21" s="27" t="n">
+      <c r="BL21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
@@ -6876,16 +6907,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
+      <c r="BP21" s="38" t="n"/>
+      <c r="BQ21" s="39" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
+      <c r="BU21" s="38" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
+      <c r="BX21" s="40" t="n"/>
+      <c r="BY21" s="39" t="n"/>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
     </row>
@@ -6935,7 +6966,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="25" t="n"/>
+      <c r="J22" s="38" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6944,7 +6975,7 @@
       <c r="L22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M22" s="27" t="n">
+      <c r="M22" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N22" s="28" t="n">
@@ -6986,11 +7017,11 @@
       <c r="X22" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y22" s="25" t="n"/>
+      <c r="Y22" s="38" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n">
+      <c r="AC22" s="40" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
@@ -7049,11 +7080,11 @@
         </is>
       </c>
       <c r="BI22" s="24" t="n"/>
-      <c r="BJ22" s="25" t="n"/>
+      <c r="BJ22" s="38" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL22" s="27" t="n">
+      <c r="BL22" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM22" s="28" t="n">
@@ -7063,16 +7094,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
+      <c r="BP22" s="38" t="n"/>
+      <c r="BQ22" s="39" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
+      <c r="BU22" s="38" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
+      <c r="BX22" s="40" t="n"/>
+      <c r="BY22" s="39" t="n"/>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
     </row>
@@ -7122,7 +7153,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J23" s="25" t="n"/>
+      <c r="J23" s="38" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7131,7 +7162,7 @@
       <c r="L23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M23" s="27" t="n">
+      <c r="M23" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="N23" s="28" t="n">
@@ -7173,11 +7204,11 @@
       <c r="X23" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y23" s="25" t="n"/>
+      <c r="Y23" s="38" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n">
+      <c r="AC23" s="40" t="n">
         <v>1.2411</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
@@ -7236,11 +7267,11 @@
         </is>
       </c>
       <c r="BI23" s="24" t="n"/>
-      <c r="BJ23" s="25" t="n"/>
+      <c r="BJ23" s="38" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL23" s="27" t="n">
+      <c r="BL23" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM23" s="28" t="n">
@@ -7250,16 +7281,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
+      <c r="BP23" s="38" t="n"/>
+      <c r="BQ23" s="39" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
+      <c r="BU23" s="38" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
+      <c r="BX23" s="40" t="n"/>
+      <c r="BY23" s="39" t="n"/>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
     </row>
@@ -7309,7 +7340,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="25" t="n"/>
+      <c r="J24" s="38" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7318,7 +7349,7 @@
       <c r="L24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M24" s="27" t="n">
+      <c r="M24" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N24" s="28" t="n">
@@ -7360,11 +7391,11 @@
       <c r="X24" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" s="25" t="n"/>
+      <c r="Y24" s="38" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n">
+      <c r="AC24" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -7423,11 +7454,11 @@
         </is>
       </c>
       <c r="BI24" s="24" t="n"/>
-      <c r="BJ24" s="25" t="n"/>
+      <c r="BJ24" s="38" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL24" s="27" t="n">
+      <c r="BL24" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM24" s="28" t="n">
@@ -7437,16 +7468,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
+      <c r="BP24" s="38" t="n"/>
+      <c r="BQ24" s="39" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="25" t="n"/>
+      <c r="BU24" s="38" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="30" t="n"/>
-      <c r="BY24" s="27" t="n"/>
+      <c r="BX24" s="40" t="n"/>
+      <c r="BY24" s="39" t="n"/>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
     </row>
@@ -7496,7 +7527,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J25" s="25" t="n"/>
+      <c r="J25" s="38" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7505,7 +7536,7 @@
       <c r="L25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M25" s="27" t="n">
+      <c r="M25" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
@@ -7547,11 +7578,11 @@
       <c r="X25" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" s="25" t="n"/>
+      <c r="Y25" s="38" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n">
+      <c r="AC25" s="40" t="n">
         <v>1.3</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
@@ -7610,11 +7641,11 @@
         </is>
       </c>
       <c r="BI25" s="24" t="n"/>
-      <c r="BJ25" s="25" t="n"/>
+      <c r="BJ25" s="38" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL25" s="27" t="n">
+      <c r="BL25" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
@@ -7624,16 +7655,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
+      <c r="BP25" s="38" t="n"/>
+      <c r="BQ25" s="39" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="25" t="n"/>
+      <c r="BU25" s="38" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="30" t="n"/>
-      <c r="BY25" s="27" t="n"/>
+      <c r="BX25" s="40" t="n"/>
+      <c r="BY25" s="39" t="n"/>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
     </row>
@@ -7683,7 +7714,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J26" s="25" t="n"/>
+      <c r="J26" s="38" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7692,7 +7723,7 @@
       <c r="L26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M26" s="27" t="n">
+      <c r="M26" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N26" s="28" t="n">
@@ -7734,11 +7765,11 @@
       <c r="X26" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26" s="25" t="n"/>
+      <c r="Y26" s="38" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n">
+      <c r="AC26" s="40" t="n">
         <v>0.9615</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
@@ -7797,11 +7828,11 @@
         </is>
       </c>
       <c r="BI26" s="24" t="n"/>
-      <c r="BJ26" s="25" t="n"/>
+      <c r="BJ26" s="38" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL26" s="27" t="n">
+      <c r="BL26" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM26" s="28" t="n">
@@ -7811,16 +7842,16 @@
         <v>0.507463</v>
       </c>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
+      <c r="BP26" s="38" t="n"/>
+      <c r="BQ26" s="39" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="25" t="n"/>
+      <c r="BU26" s="38" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="30" t="n"/>
-      <c r="BY26" s="27" t="n"/>
+      <c r="BX26" s="40" t="n"/>
+      <c r="BY26" s="39" t="n"/>
       <c r="BZ26" s="24" t="n"/>
       <c r="CA26" s="31" t="n"/>
     </row>
@@ -7870,7 +7901,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="25" t="n"/>
+      <c r="J27" s="38" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7879,7 +7910,7 @@
       <c r="L27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="M27" s="27" t="n">
+      <c r="M27" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="N27" s="28" t="n">
@@ -7921,11 +7952,11 @@
       <c r="X27" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" s="25" t="n"/>
+      <c r="Y27" s="38" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n">
+      <c r="AC27" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
@@ -7984,11 +8015,11 @@
         </is>
       </c>
       <c r="BI27" s="24" t="n"/>
-      <c r="BJ27" s="25" t="n"/>
+      <c r="BJ27" s="38" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="BL27" s="27" t="n">
+      <c r="BL27" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="BM27" s="28" t="n">
@@ -7998,16 +8029,16 @@
         <v>0.452736</v>
       </c>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
+      <c r="BP27" s="38" t="n"/>
+      <c r="BQ27" s="39" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="25" t="n"/>
+      <c r="BU27" s="38" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="30" t="n"/>
-      <c r="BY27" s="27" t="n"/>
+      <c r="BX27" s="40" t="n"/>
+      <c r="BY27" s="39" t="n"/>
       <c r="BZ27" s="24" t="n"/>
       <c r="CA27" s="31" t="n"/>
     </row>
@@ -8057,7 +8088,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="25" t="n"/>
+      <c r="J28" s="38" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -8066,7 +8097,7 @@
       <c r="L28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="27" t="n">
+      <c r="M28" s="39" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -8108,11 +8139,11 @@
       <c r="X28" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="25" t="n"/>
+      <c r="Y28" s="38" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n">
+      <c r="AC28" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
@@ -8171,11 +8202,11 @@
         </is>
       </c>
       <c r="BI28" s="24" t="n"/>
-      <c r="BJ28" s="25" t="n"/>
+      <c r="BJ28" s="38" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL28" s="27" t="n">
+      <c r="BL28" s="39" t="n">
         <v>2</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -8185,16 +8216,16 @@
         <v>0.497512</v>
       </c>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
+      <c r="BP28" s="38" t="n"/>
+      <c r="BQ28" s="39" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="25" t="n"/>
+      <c r="BU28" s="38" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="30" t="n"/>
-      <c r="BY28" s="27" t="n"/>
+      <c r="BX28" s="40" t="n"/>
+      <c r="BY28" s="39" t="n"/>
       <c r="BZ28" s="24" t="n"/>
       <c r="CA28" s="31" t="n"/>
     </row>
@@ -8244,7 +8275,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J29" s="25" t="n"/>
+      <c r="J29" s="38" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8253,7 +8284,7 @@
       <c r="L29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M29" s="27" t="n">
+      <c r="M29" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -8293,11 +8324,11 @@
       <c r="X29" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y29" s="25" t="n"/>
+      <c r="Y29" s="38" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n">
+      <c r="AC29" s="40" t="n">
         <v>1.35</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
@@ -8434,11 +8465,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ29" s="25" t="n"/>
+      <c r="BJ29" s="38" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL29" s="27" t="n">
+      <c r="BL29" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -8448,18 +8479,18 @@
         <v>0.477612</v>
       </c>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="25" t="n"/>
-      <c r="BQ29" s="27" t="n"/>
+      <c r="BP29" s="38" t="n"/>
+      <c r="BQ29" s="39" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="25" t="n"/>
+      <c r="BU29" s="38" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="30" t="n">
+      <c r="BX29" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY29" s="27" t="n">
+      <c r="BY29" s="39" t="n">
         <v>1.08</v>
       </c>
       <c r="BZ29" s="24" t="inlineStr">
@@ -8519,7 +8550,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J30" s="25" t="n"/>
+      <c r="J30" s="38" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8528,7 +8559,7 @@
       <c r="L30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M30" s="27" t="n">
+      <c r="M30" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -8568,11 +8599,11 @@
       <c r="X30" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y30" s="25" t="n"/>
+      <c r="Y30" s="38" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n">
+      <c r="AC30" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
@@ -8709,11 +8740,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ30" s="25" t="n"/>
+      <c r="BJ30" s="38" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL30" s="27" t="n">
+      <c r="BL30" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -8723,18 +8754,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
+      <c r="BP30" s="38" t="n"/>
+      <c r="BQ30" s="39" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="25" t="n"/>
+      <c r="BU30" s="38" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="30" t="n">
+      <c r="BX30" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY30" s="27" t="n">
+      <c r="BY30" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ30" s="24" t="inlineStr">
@@ -8794,7 +8825,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="25" t="n"/>
+      <c r="J31" s="38" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8803,7 +8834,7 @@
       <c r="L31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="M31" s="27" t="n">
+      <c r="M31" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -8843,11 +8874,11 @@
       <c r="X31" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y31" s="25" t="n"/>
+      <c r="Y31" s="38" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n">
+      <c r="AC31" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
@@ -8984,11 +9015,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ31" s="25" t="n"/>
+      <c r="BJ31" s="38" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="BL31" s="27" t="n">
+      <c r="BL31" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -8998,18 +9029,18 @@
         <v>0.432836</v>
       </c>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="25" t="n"/>
-      <c r="BQ31" s="27" t="n"/>
+      <c r="BP31" s="38" t="n"/>
+      <c r="BQ31" s="39" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="25" t="n"/>
+      <c r="BU31" s="38" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="30" t="n">
+      <c r="BX31" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY31" s="27" t="n">
+      <c r="BY31" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ31" s="24" t="inlineStr">
@@ -9069,7 +9100,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J32" s="25" t="n"/>
+      <c r="J32" s="38" t="n"/>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9078,7 +9109,7 @@
       <c r="L32" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M32" s="27" t="n">
+      <c r="M32" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="N32" s="28" t="n">
@@ -9118,11 +9149,11 @@
       <c r="X32" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y32" s="25" t="n"/>
+      <c r="Y32" s="38" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n">
+      <c r="AC32" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD32" s="24" t="inlineStr">
@@ -9259,11 +9290,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ32" s="25" t="n"/>
+      <c r="BJ32" s="38" t="n"/>
       <c r="BK32" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL32" s="27" t="n">
+      <c r="BL32" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="BM32" s="28" t="n">
@@ -9273,16 +9304,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="25" t="n"/>
-      <c r="BQ32" s="27" t="n"/>
+      <c r="BP32" s="38" t="n"/>
+      <c r="BQ32" s="39" t="n"/>
       <c r="BR32" s="28" t="n"/>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="25" t="n"/>
+      <c r="BU32" s="38" t="n"/>
       <c r="BV32" s="29" t="n"/>
       <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="30" t="n"/>
-      <c r="BY32" s="27" t="n"/>
+      <c r="BX32" s="40" t="n"/>
+      <c r="BY32" s="39" t="n"/>
       <c r="BZ32" s="24" t="n"/>
       <c r="CA32" s="31" t="n"/>
     </row>
@@ -9332,7 +9363,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J33" s="25" t="n"/>
+      <c r="J33" s="38" t="n"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9341,7 +9372,7 @@
       <c r="L33" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M33" s="27" t="n">
+      <c r="M33" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="N33" s="28" t="n">
@@ -9381,11 +9412,11 @@
       <c r="X33" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y33" s="25" t="n"/>
+      <c r="Y33" s="38" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="30" t="n">
+      <c r="AC33" s="40" t="n">
         <v>-1.75</v>
       </c>
       <c r="AD33" s="24" t="inlineStr">
@@ -9522,11 +9553,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ33" s="25" t="n"/>
+      <c r="BJ33" s="38" t="n"/>
       <c r="BK33" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL33" s="27" t="n">
+      <c r="BL33" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="BM33" s="28" t="n">
@@ -9536,16 +9567,16 @@
         <v>0.457711</v>
       </c>
       <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="25" t="n"/>
-      <c r="BQ33" s="27" t="n"/>
+      <c r="BP33" s="38" t="n"/>
+      <c r="BQ33" s="39" t="n"/>
       <c r="BR33" s="28" t="n"/>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="25" t="n"/>
+      <c r="BU33" s="38" t="n"/>
       <c r="BV33" s="29" t="n"/>
       <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="30" t="n"/>
-      <c r="BY33" s="27" t="n"/>
+      <c r="BX33" s="40" t="n"/>
+      <c r="BY33" s="39" t="n"/>
       <c r="BZ33" s="24" t="n"/>
       <c r="CA33" s="31" t="n"/>
     </row>
@@ -9595,7 +9626,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J34" s="25" t="n"/>
+      <c r="J34" s="38" t="n"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9604,7 +9635,7 @@
       <c r="L34" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="M34" s="27" t="n">
+      <c r="M34" s="39" t="n">
         <v>1.854701</v>
       </c>
       <c r="N34" s="28" t="n">
@@ -9644,11 +9675,11 @@
       <c r="X34" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y34" s="25" t="n"/>
+      <c r="Y34" s="38" t="n"/>
       <c r="Z34" s="26" t="n"/>
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="30" t="n">
+      <c r="AC34" s="40" t="n">
         <v>0.8547</v>
       </c>
       <c r="AD34" s="24" t="inlineStr">
@@ -9785,11 +9816,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ34" s="25" t="n"/>
+      <c r="BJ34" s="38" t="n"/>
       <c r="BK34" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="BL34" s="27" t="n">
+      <c r="BL34" s="39" t="n">
         <v>1.854701</v>
       </c>
       <c r="BM34" s="28" t="n">
@@ -9799,16 +9830,16 @@
         <v>0.537313</v>
       </c>
       <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="25" t="n"/>
-      <c r="BQ34" s="27" t="n"/>
+      <c r="BP34" s="38" t="n"/>
+      <c r="BQ34" s="39" t="n"/>
       <c r="BR34" s="28" t="n"/>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="25" t="n"/>
+      <c r="BU34" s="38" t="n"/>
       <c r="BV34" s="29" t="n"/>
       <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="30" t="n"/>
-      <c r="BY34" s="27" t="n"/>
+      <c r="BX34" s="40" t="n"/>
+      <c r="BY34" s="39" t="n"/>
       <c r="BZ34" s="24" t="n"/>
       <c r="CA34" s="31" t="n"/>
     </row>
@@ -9858,7 +9889,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J35" s="25" t="n"/>
+      <c r="J35" s="38" t="n"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9867,7 +9898,7 @@
       <c r="L35" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M35" s="27" t="n">
+      <c r="M35" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="N35" s="28" t="n">
@@ -9907,11 +9938,11 @@
       <c r="X35" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y35" s="25" t="n"/>
+      <c r="Y35" s="38" t="n"/>
       <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="30" t="n">
+      <c r="AC35" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD35" s="24" t="inlineStr">
@@ -10048,11 +10079,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ35" s="25" t="n"/>
+      <c r="BJ35" s="38" t="n"/>
       <c r="BK35" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL35" s="27" t="n">
+      <c r="BL35" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="BM35" s="28" t="n">
@@ -10062,16 +10093,16 @@
         <v>0.457711</v>
       </c>
       <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="25" t="n"/>
-      <c r="BQ35" s="27" t="n"/>
+      <c r="BP35" s="38" t="n"/>
+      <c r="BQ35" s="39" t="n"/>
       <c r="BR35" s="28" t="n"/>
       <c r="BS35" s="28" t="n"/>
       <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="25" t="n"/>
+      <c r="BU35" s="38" t="n"/>
       <c r="BV35" s="29" t="n"/>
       <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="30" t="n"/>
-      <c r="BY35" s="27" t="n"/>
+      <c r="BX35" s="40" t="n"/>
+      <c r="BY35" s="39" t="n"/>
       <c r="BZ35" s="24" t="n"/>
       <c r="CA35" s="31" t="n"/>
     </row>
@@ -10121,7 +10152,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J36" s="25" t="n"/>
+      <c r="J36" s="38" t="n"/>
       <c r="K36" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10130,7 +10161,7 @@
       <c r="L36" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M36" s="27" t="n">
+      <c r="M36" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N36" s="28" t="n">
@@ -10170,11 +10201,11 @@
       <c r="X36" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y36" s="25" t="n"/>
+      <c r="Y36" s="38" t="n"/>
       <c r="Z36" s="26" t="n"/>
       <c r="AA36" s="28" t="n"/>
       <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="30" t="n">
+      <c r="AC36" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD36" s="24" t="inlineStr">
@@ -10311,11 +10342,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ36" s="25" t="n"/>
+      <c r="BJ36" s="38" t="n"/>
       <c r="BK36" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL36" s="27" t="n">
+      <c r="BL36" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM36" s="28" t="n">
@@ -10325,16 +10356,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="25" t="n"/>
-      <c r="BQ36" s="27" t="n"/>
+      <c r="BP36" s="38" t="n"/>
+      <c r="BQ36" s="39" t="n"/>
       <c r="BR36" s="28" t="n"/>
       <c r="BS36" s="28" t="n"/>
       <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="25" t="n"/>
+      <c r="BU36" s="38" t="n"/>
       <c r="BV36" s="29" t="n"/>
       <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="30" t="n"/>
-      <c r="BY36" s="27" t="n"/>
+      <c r="BX36" s="40" t="n"/>
+      <c r="BY36" s="39" t="n"/>
       <c r="BZ36" s="24" t="n"/>
       <c r="CA36" s="31" t="n"/>
     </row>
@@ -10384,7 +10415,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J37" s="25" t="n"/>
+      <c r="J37" s="38" t="n"/>
       <c r="K37" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10393,7 +10424,7 @@
       <c r="L37" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="M37" s="27" t="n">
+      <c r="M37" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="N37" s="28" t="n">
@@ -10433,11 +10464,11 @@
       <c r="X37" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y37" s="25" t="n"/>
+      <c r="Y37" s="38" t="n"/>
       <c r="Z37" s="26" t="n"/>
       <c r="AA37" s="28" t="n"/>
       <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="30" t="n">
+      <c r="AC37" s="40" t="n">
         <v>1.4344</v>
       </c>
       <c r="AD37" s="24" t="inlineStr">
@@ -10574,11 +10605,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ37" s="25" t="n"/>
+      <c r="BJ37" s="38" t="n"/>
       <c r="BK37" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="BL37" s="27" t="n">
+      <c r="BL37" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="BM37" s="28" t="n">
@@ -10588,16 +10619,16 @@
         <v>0.547264</v>
       </c>
       <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="25" t="n"/>
-      <c r="BQ37" s="27" t="n"/>
+      <c r="BP37" s="38" t="n"/>
+      <c r="BQ37" s="39" t="n"/>
       <c r="BR37" s="28" t="n"/>
       <c r="BS37" s="28" t="n"/>
       <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="25" t="n"/>
+      <c r="BU37" s="38" t="n"/>
       <c r="BV37" s="29" t="n"/>
       <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="30" t="n"/>
-      <c r="BY37" s="27" t="n"/>
+      <c r="BX37" s="40" t="n"/>
+      <c r="BY37" s="39" t="n"/>
       <c r="BZ37" s="24" t="n"/>
       <c r="CA37" s="31" t="n"/>
     </row>
@@ -10647,7 +10678,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J38" s="25" t="n"/>
+      <c r="J38" s="38" t="n"/>
       <c r="K38" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10656,7 +10687,7 @@
       <c r="L38" s="26" t="n">
         <v>115</v>
       </c>
-      <c r="M38" s="27" t="n">
+      <c r="M38" s="39" t="n">
         <v>2.15</v>
       </c>
       <c r="N38" s="28" t="n">
@@ -10696,11 +10727,11 @@
       <c r="X38" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y38" s="25" t="n"/>
+      <c r="Y38" s="38" t="n"/>
       <c r="Z38" s="26" t="n"/>
       <c r="AA38" s="28" t="n"/>
       <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="30" t="n">
+      <c r="AC38" s="40" t="n">
         <v>0.8625</v>
       </c>
       <c r="AD38" s="24" t="inlineStr">
@@ -10837,11 +10868,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ38" s="25" t="n"/>
+      <c r="BJ38" s="38" t="n"/>
       <c r="BK38" s="26" t="n">
         <v>115</v>
       </c>
-      <c r="BL38" s="27" t="n">
+      <c r="BL38" s="39" t="n">
         <v>2.15</v>
       </c>
       <c r="BM38" s="28" t="n">
@@ -10851,16 +10882,16 @@
         <v>0.462687</v>
       </c>
       <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="25" t="n"/>
-      <c r="BQ38" s="27" t="n"/>
+      <c r="BP38" s="38" t="n"/>
+      <c r="BQ38" s="39" t="n"/>
       <c r="BR38" s="28" t="n"/>
       <c r="BS38" s="28" t="n"/>
       <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="25" t="n"/>
+      <c r="BU38" s="38" t="n"/>
       <c r="BV38" s="29" t="n"/>
       <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="30" t="n"/>
-      <c r="BY38" s="27" t="n"/>
+      <c r="BX38" s="40" t="n"/>
+      <c r="BY38" s="39" t="n"/>
       <c r="BZ38" s="24" t="n"/>
       <c r="CA38" s="31" t="n"/>
     </row>
@@ -10910,7 +10941,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J39" s="25" t="n"/>
+      <c r="J39" s="38" t="n"/>
       <c r="K39" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10919,7 +10950,7 @@
       <c r="L39" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="M39" s="27" t="n">
+      <c r="M39" s="39" t="n">
         <v>1.666667</v>
       </c>
       <c r="N39" s="28" t="n">
@@ -10959,11 +10990,11 @@
       <c r="X39" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y39" s="25" t="n"/>
+      <c r="Y39" s="38" t="n"/>
       <c r="Z39" s="26" t="n"/>
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="30" t="n">
+      <c r="AC39" s="40" t="n">
         <v>1</v>
       </c>
       <c r="AD39" s="24" t="inlineStr">
@@ -11100,11 +11131,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ39" s="25" t="n"/>
+      <c r="BJ39" s="38" t="n"/>
       <c r="BK39" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="BL39" s="27" t="n">
+      <c r="BL39" s="39" t="n">
         <v>1.666667</v>
       </c>
       <c r="BM39" s="28" t="n">
@@ -11114,16 +11145,16 @@
         <v>0.597015</v>
       </c>
       <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="25" t="n"/>
-      <c r="BQ39" s="27" t="n"/>
+      <c r="BP39" s="38" t="n"/>
+      <c r="BQ39" s="39" t="n"/>
       <c r="BR39" s="28" t="n"/>
       <c r="BS39" s="28" t="n"/>
       <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="25" t="n"/>
+      <c r="BU39" s="38" t="n"/>
       <c r="BV39" s="29" t="n"/>
       <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="30" t="n"/>
-      <c r="BY39" s="27" t="n"/>
+      <c r="BX39" s="40" t="n"/>
+      <c r="BY39" s="39" t="n"/>
       <c r="BZ39" s="24" t="n"/>
       <c r="CA39" s="31" t="n"/>
     </row>
@@ -11173,7 +11204,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J40" s="25" t="n"/>
+      <c r="J40" s="38" t="n"/>
       <c r="K40" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11182,7 +11213,7 @@
       <c r="L40" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M40" s="27" t="n">
+      <c r="M40" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="N40" s="28" t="n">
@@ -11222,11 +11253,11 @@
       <c r="X40" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y40" s="25" t="n"/>
+      <c r="Y40" s="38" t="n"/>
       <c r="Z40" s="26" t="n"/>
       <c r="AA40" s="28" t="n"/>
       <c r="AB40" s="28" t="n"/>
-      <c r="AC40" s="30" t="n">
+      <c r="AC40" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD40" s="24" t="inlineStr">
@@ -11363,11 +11394,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ40" s="25" t="n"/>
+      <c r="BJ40" s="38" t="n"/>
       <c r="BK40" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL40" s="27" t="n">
+      <c r="BL40" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM40" s="28" t="n">
@@ -11377,16 +11408,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO40" s="28" t="n"/>
-      <c r="BP40" s="25" t="n"/>
-      <c r="BQ40" s="27" t="n"/>
+      <c r="BP40" s="38" t="n"/>
+      <c r="BQ40" s="39" t="n"/>
       <c r="BR40" s="28" t="n"/>
       <c r="BS40" s="28" t="n"/>
       <c r="BT40" s="28" t="n"/>
-      <c r="BU40" s="25" t="n"/>
+      <c r="BU40" s="38" t="n"/>
       <c r="BV40" s="29" t="n"/>
       <c r="BW40" s="24" t="n"/>
-      <c r="BX40" s="30" t="n"/>
-      <c r="BY40" s="27" t="n"/>
+      <c r="BX40" s="40" t="n"/>
+      <c r="BY40" s="39" t="n"/>
       <c r="BZ40" s="24" t="n"/>
       <c r="CA40" s="31" t="n"/>
     </row>
@@ -11436,7 +11467,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J41" s="25" t="n"/>
+      <c r="J41" s="38" t="n"/>
       <c r="K41" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11445,7 +11476,7 @@
       <c r="L41" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="M41" s="27" t="n">
+      <c r="M41" s="39" t="n">
         <v>1.613497</v>
       </c>
       <c r="N41" s="28" t="n">
@@ -11485,11 +11516,11 @@
       <c r="X41" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y41" s="25" t="n"/>
+      <c r="Y41" s="38" t="n"/>
       <c r="Z41" s="26" t="n"/>
       <c r="AA41" s="28" t="n"/>
       <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="30" t="n">
+      <c r="AC41" s="40" t="n">
         <v>0.9202</v>
       </c>
       <c r="AD41" s="24" t="inlineStr">
@@ -11626,11 +11657,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ41" s="25" t="n"/>
+      <c r="BJ41" s="38" t="n"/>
       <c r="BK41" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="BL41" s="27" t="n">
+      <c r="BL41" s="39" t="n">
         <v>1.613497</v>
       </c>
       <c r="BM41" s="28" t="n">
@@ -11640,16 +11671,16 @@
         <v>0.616915</v>
       </c>
       <c r="BO41" s="28" t="n"/>
-      <c r="BP41" s="25" t="n"/>
-      <c r="BQ41" s="27" t="n"/>
+      <c r="BP41" s="38" t="n"/>
+      <c r="BQ41" s="39" t="n"/>
       <c r="BR41" s="28" t="n"/>
       <c r="BS41" s="28" t="n"/>
       <c r="BT41" s="28" t="n"/>
-      <c r="BU41" s="25" t="n"/>
+      <c r="BU41" s="38" t="n"/>
       <c r="BV41" s="29" t="n"/>
       <c r="BW41" s="24" t="n"/>
-      <c r="BX41" s="30" t="n"/>
-      <c r="BY41" s="27" t="n"/>
+      <c r="BX41" s="40" t="n"/>
+      <c r="BY41" s="39" t="n"/>
       <c r="BZ41" s="24" t="n"/>
       <c r="CA41" s="31" t="n"/>
     </row>
@@ -11699,7 +11730,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J42" s="25" t="n"/>
+      <c r="J42" s="38" t="n"/>
       <c r="K42" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11708,7 +11739,7 @@
       <c r="L42" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M42" s="27" t="n">
+      <c r="M42" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="N42" s="28" t="n">
@@ -11748,11 +11779,11 @@
       <c r="X42" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y42" s="25" t="n"/>
+      <c r="Y42" s="38" t="n"/>
       <c r="Z42" s="26" t="n"/>
       <c r="AA42" s="28" t="n"/>
       <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="30" t="n">
+      <c r="AC42" s="40" t="n">
         <v>0.6757</v>
       </c>
       <c r="AD42" s="24" t="inlineStr">
@@ -11889,11 +11920,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ42" s="25" t="n"/>
+      <c r="BJ42" s="38" t="n"/>
       <c r="BK42" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL42" s="27" t="n">
+      <c r="BL42" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM42" s="28" t="n">
@@ -11903,16 +11934,16 @@
         <v>0.522388</v>
       </c>
       <c r="BO42" s="28" t="n"/>
-      <c r="BP42" s="25" t="n"/>
-      <c r="BQ42" s="27" t="n"/>
+      <c r="BP42" s="38" t="n"/>
+      <c r="BQ42" s="39" t="n"/>
       <c r="BR42" s="28" t="n"/>
       <c r="BS42" s="28" t="n"/>
       <c r="BT42" s="28" t="n"/>
-      <c r="BU42" s="25" t="n"/>
+      <c r="BU42" s="38" t="n"/>
       <c r="BV42" s="29" t="n"/>
       <c r="BW42" s="24" t="n"/>
-      <c r="BX42" s="30" t="n"/>
-      <c r="BY42" s="27" t="n"/>
+      <c r="BX42" s="40" t="n"/>
+      <c r="BY42" s="39" t="n"/>
       <c r="BZ42" s="24" t="n"/>
       <c r="CA42" s="31" t="n"/>
     </row>
@@ -11962,7 +11993,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J43" s="25" t="n"/>
+      <c r="J43" s="38" t="n"/>
       <c r="K43" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11971,7 +12002,7 @@
       <c r="L43" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M43" s="27" t="n">
+      <c r="M43" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N43" s="28" t="n">
@@ -12011,11 +12042,11 @@
       <c r="X43" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y43" s="25" t="n"/>
+      <c r="Y43" s="38" t="n"/>
       <c r="Z43" s="26" t="n"/>
       <c r="AA43" s="28" t="n"/>
       <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="30" t="n">
+      <c r="AC43" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD43" s="24" t="inlineStr">
@@ -12152,11 +12183,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ43" s="25" t="n"/>
+      <c r="BJ43" s="38" t="n"/>
       <c r="BK43" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL43" s="27" t="n">
+      <c r="BL43" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM43" s="28" t="n">
@@ -12166,16 +12197,16 @@
         <v>0.517413</v>
       </c>
       <c r="BO43" s="28" t="n"/>
-      <c r="BP43" s="25" t="n"/>
-      <c r="BQ43" s="27" t="n"/>
+      <c r="BP43" s="38" t="n"/>
+      <c r="BQ43" s="39" t="n"/>
       <c r="BR43" s="28" t="n"/>
       <c r="BS43" s="28" t="n"/>
       <c r="BT43" s="28" t="n"/>
-      <c r="BU43" s="25" t="n"/>
+      <c r="BU43" s="38" t="n"/>
       <c r="BV43" s="29" t="n"/>
       <c r="BW43" s="24" t="n"/>
-      <c r="BX43" s="30" t="n"/>
-      <c r="BY43" s="27" t="n"/>
+      <c r="BX43" s="40" t="n"/>
+      <c r="BY43" s="39" t="n"/>
       <c r="BZ43" s="24" t="n"/>
       <c r="CA43" s="31" t="n"/>
     </row>
@@ -12225,7 +12256,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J44" s="25" t="n"/>
+      <c r="J44" s="38" t="n"/>
       <c r="K44" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12234,7 +12265,7 @@
       <c r="L44" s="26" t="n">
         <v>-400</v>
       </c>
-      <c r="M44" s="27" t="n">
+      <c r="M44" s="39" t="n">
         <v>1.25</v>
       </c>
       <c r="N44" s="28" t="n">
@@ -12274,11 +12305,11 @@
       <c r="X44" s="26" t="n">
         <v>90</v>
       </c>
-      <c r="Y44" s="25" t="n"/>
+      <c r="Y44" s="38" t="n"/>
       <c r="Z44" s="26" t="n"/>
       <c r="AA44" s="28" t="n"/>
       <c r="AB44" s="28" t="n"/>
-      <c r="AC44" s="30" t="n">
+      <c r="AC44" s="40" t="n">
         <v>0.5</v>
       </c>
       <c r="AD44" s="24" t="inlineStr">
@@ -12415,11 +12446,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ44" s="25" t="n"/>
+      <c r="BJ44" s="38" t="n"/>
       <c r="BK44" s="26" t="n">
         <v>-400</v>
       </c>
-      <c r="BL44" s="27" t="n">
+      <c r="BL44" s="39" t="n">
         <v>1.25</v>
       </c>
       <c r="BM44" s="28" t="n">
@@ -12429,16 +12460,16 @@
         <v>0.792079</v>
       </c>
       <c r="BO44" s="28" t="n"/>
-      <c r="BP44" s="25" t="n"/>
-      <c r="BQ44" s="27" t="n"/>
+      <c r="BP44" s="38" t="n"/>
+      <c r="BQ44" s="39" t="n"/>
       <c r="BR44" s="28" t="n"/>
       <c r="BS44" s="28" t="n"/>
       <c r="BT44" s="28" t="n"/>
-      <c r="BU44" s="25" t="n"/>
+      <c r="BU44" s="38" t="n"/>
       <c r="BV44" s="29" t="n"/>
       <c r="BW44" s="24" t="n"/>
-      <c r="BX44" s="30" t="n"/>
-      <c r="BY44" s="27" t="n"/>
+      <c r="BX44" s="40" t="n"/>
+      <c r="BY44" s="39" t="n"/>
       <c r="BZ44" s="24" t="n"/>
       <c r="CA44" s="31" t="n"/>
     </row>
@@ -12488,7 +12519,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J45" s="25" t="n"/>
+      <c r="J45" s="38" t="n"/>
       <c r="K45" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12497,7 +12528,7 @@
       <c r="L45" s="26" t="n">
         <v>-426</v>
       </c>
-      <c r="M45" s="27" t="n">
+      <c r="M45" s="39" t="n">
         <v>1.234742</v>
       </c>
       <c r="N45" s="28" t="n">
@@ -12537,11 +12568,11 @@
       <c r="X45" s="26" t="n">
         <v>93</v>
       </c>
-      <c r="Y45" s="25" t="n"/>
+      <c r="Y45" s="38" t="n"/>
       <c r="Z45" s="26" t="n"/>
       <c r="AA45" s="28" t="n"/>
       <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="30" t="n">
+      <c r="AC45" s="40" t="n">
         <v>0.4695</v>
       </c>
       <c r="AD45" s="24" t="inlineStr">
@@ -12678,11 +12709,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ45" s="25" t="n"/>
+      <c r="BJ45" s="38" t="n"/>
       <c r="BK45" s="26" t="n">
         <v>-426</v>
       </c>
-      <c r="BL45" s="27" t="n">
+      <c r="BL45" s="39" t="n">
         <v>1.234742</v>
       </c>
       <c r="BM45" s="28" t="n">
@@ -12692,16 +12723,16 @@
         <v>0.80198</v>
       </c>
       <c r="BO45" s="28" t="n"/>
-      <c r="BP45" s="25" t="n"/>
-      <c r="BQ45" s="27" t="n"/>
+      <c r="BP45" s="38" t="n"/>
+      <c r="BQ45" s="39" t="n"/>
       <c r="BR45" s="28" t="n"/>
       <c r="BS45" s="28" t="n"/>
       <c r="BT45" s="28" t="n"/>
-      <c r="BU45" s="25" t="n"/>
+      <c r="BU45" s="38" t="n"/>
       <c r="BV45" s="29" t="n"/>
       <c r="BW45" s="24" t="n"/>
-      <c r="BX45" s="30" t="n"/>
-      <c r="BY45" s="27" t="n"/>
+      <c r="BX45" s="40" t="n"/>
+      <c r="BY45" s="39" t="n"/>
       <c r="BZ45" s="24" t="n"/>
       <c r="CA45" s="31" t="n"/>
     </row>
@@ -12751,7 +12782,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J46" s="25" t="n"/>
+      <c r="J46" s="38" t="n"/>
       <c r="K46" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12760,7 +12791,7 @@
       <c r="L46" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="M46" s="27" t="n">
+      <c r="M46" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="N46" s="28" t="n">
@@ -12800,11 +12831,11 @@
       <c r="X46" s="26" t="n">
         <v>72</v>
       </c>
-      <c r="Y46" s="25" t="n"/>
+      <c r="Y46" s="38" t="n"/>
       <c r="Z46" s="26" t="n"/>
       <c r="AA46" s="28" t="n"/>
       <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="30" t="n">
+      <c r="AC46" s="40" t="n">
         <v>0.8013</v>
       </c>
       <c r="AD46" s="24" t="inlineStr">
@@ -12941,11 +12972,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ46" s="25" t="n"/>
+      <c r="BJ46" s="38" t="n"/>
       <c r="BK46" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="BL46" s="27" t="n">
+      <c r="BL46" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="BM46" s="28" t="n">
@@ -12955,16 +12986,16 @@
         <v>0.6039600000000001</v>
       </c>
       <c r="BO46" s="28" t="n"/>
-      <c r="BP46" s="25" t="n"/>
-      <c r="BQ46" s="27" t="n"/>
+      <c r="BP46" s="38" t="n"/>
+      <c r="BQ46" s="39" t="n"/>
       <c r="BR46" s="28" t="n"/>
       <c r="BS46" s="28" t="n"/>
       <c r="BT46" s="28" t="n"/>
-      <c r="BU46" s="25" t="n"/>
+      <c r="BU46" s="38" t="n"/>
       <c r="BV46" s="29" t="n"/>
       <c r="BW46" s="24" t="n"/>
-      <c r="BX46" s="30" t="n"/>
-      <c r="BY46" s="27" t="n"/>
+      <c r="BX46" s="40" t="n"/>
+      <c r="BY46" s="39" t="n"/>
       <c r="BZ46" s="24" t="n"/>
       <c r="CA46" s="31" t="n"/>
     </row>
@@ -13014,7 +13045,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J47" s="25" t="n"/>
+      <c r="J47" s="38" t="n"/>
       <c r="K47" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -13023,7 +13054,7 @@
       <c r="L47" s="26" t="n">
         <v>-354</v>
       </c>
-      <c r="M47" s="27" t="n">
+      <c r="M47" s="39" t="n">
         <v>1.282486</v>
       </c>
       <c r="N47" s="28" t="n">
@@ -13061,11 +13092,11 @@
       <c r="X47" s="26" t="n">
         <v>110</v>
       </c>
-      <c r="Y47" s="25" t="n"/>
+      <c r="Y47" s="38" t="n"/>
       <c r="Z47" s="26" t="n"/>
       <c r="AA47" s="28" t="n"/>
       <c r="AB47" s="28" t="n"/>
-      <c r="AC47" s="30" t="n">
+      <c r="AC47" s="40" t="n">
         <v>0.4944</v>
       </c>
       <c r="AD47" s="24" t="inlineStr">
@@ -13126,11 +13157,11 @@
       <c r="BG47" s="24" t="n"/>
       <c r="BH47" s="24" t="n"/>
       <c r="BI47" s="24" t="n"/>
-      <c r="BJ47" s="25" t="n"/>
+      <c r="BJ47" s="38" t="n"/>
       <c r="BK47" s="26" t="n">
         <v>-354</v>
       </c>
-      <c r="BL47" s="27" t="n">
+      <c r="BL47" s="39" t="n">
         <v>1.282486</v>
       </c>
       <c r="BM47" s="28" t="n">
@@ -13140,16 +13171,16 @@
         <v>0.779736</v>
       </c>
       <c r="BO47" s="28" t="n"/>
-      <c r="BP47" s="25" t="n"/>
-      <c r="BQ47" s="27" t="n"/>
+      <c r="BP47" s="38" t="n"/>
+      <c r="BQ47" s="39" t="n"/>
       <c r="BR47" s="28" t="n"/>
       <c r="BS47" s="28" t="n"/>
       <c r="BT47" s="28" t="n"/>
-      <c r="BU47" s="25" t="n"/>
+      <c r="BU47" s="38" t="n"/>
       <c r="BV47" s="29" t="n"/>
       <c r="BW47" s="24" t="n"/>
-      <c r="BX47" s="30" t="n"/>
-      <c r="BY47" s="27" t="n"/>
+      <c r="BX47" s="40" t="n"/>
+      <c r="BY47" s="39" t="n"/>
       <c r="BZ47" s="24" t="n"/>
       <c r="CA47" s="31" t="n"/>
     </row>
@@ -13199,7 +13230,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J48" s="25" t="n"/>
+      <c r="J48" s="38" t="n"/>
       <c r="K48" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13208,7 +13239,7 @@
       <c r="L48" s="26" t="n">
         <v>-194</v>
       </c>
-      <c r="M48" s="27" t="n">
+      <c r="M48" s="39" t="n">
         <v>1.515464</v>
       </c>
       <c r="N48" s="28" t="n">
@@ -13250,11 +13281,11 @@
       <c r="X48" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y48" s="25" t="n"/>
+      <c r="Y48" s="38" t="n"/>
       <c r="Z48" s="26" t="n"/>
       <c r="AA48" s="28" t="n"/>
       <c r="AB48" s="28" t="n"/>
-      <c r="AC48" s="30" t="n">
+      <c r="AC48" s="40" t="n">
         <v>0.6443</v>
       </c>
       <c r="AD48" s="24" t="inlineStr">
@@ -13313,11 +13344,11 @@
         </is>
       </c>
       <c r="BI48" s="24" t="n"/>
-      <c r="BJ48" s="25" t="n"/>
+      <c r="BJ48" s="38" t="n"/>
       <c r="BK48" s="26" t="n">
         <v>-194</v>
       </c>
-      <c r="BL48" s="27" t="n">
+      <c r="BL48" s="39" t="n">
         <v>1.515464</v>
       </c>
       <c r="BM48" s="28" t="n">
@@ -13327,16 +13358,16 @@
         <v>0.656716</v>
       </c>
       <c r="BO48" s="28" t="n"/>
-      <c r="BP48" s="25" t="n"/>
-      <c r="BQ48" s="27" t="n"/>
+      <c r="BP48" s="38" t="n"/>
+      <c r="BQ48" s="39" t="n"/>
       <c r="BR48" s="28" t="n"/>
       <c r="BS48" s="28" t="n"/>
       <c r="BT48" s="28" t="n"/>
-      <c r="BU48" s="25" t="n"/>
+      <c r="BU48" s="38" t="n"/>
       <c r="BV48" s="29" t="n"/>
       <c r="BW48" s="24" t="n"/>
-      <c r="BX48" s="30" t="n"/>
-      <c r="BY48" s="27" t="n"/>
+      <c r="BX48" s="40" t="n"/>
+      <c r="BY48" s="39" t="n"/>
       <c r="BZ48" s="24" t="n"/>
       <c r="CA48" s="31" t="n"/>
     </row>
@@ -13386,7 +13417,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J49" s="25" t="n"/>
+      <c r="J49" s="38" t="n"/>
       <c r="K49" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13395,7 +13426,7 @@
       <c r="L49" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="M49" s="27" t="n">
+      <c r="M49" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="N49" s="28" t="n">
@@ -13437,11 +13468,11 @@
       <c r="X49" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y49" s="25" t="n"/>
+      <c r="Y49" s="38" t="n"/>
       <c r="Z49" s="26" t="n"/>
       <c r="AA49" s="28" t="n"/>
       <c r="AB49" s="28" t="n"/>
-      <c r="AC49" s="30" t="n">
+      <c r="AC49" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD49" s="24" t="inlineStr">
@@ -13500,11 +13531,11 @@
         </is>
       </c>
       <c r="BI49" s="24" t="n"/>
-      <c r="BJ49" s="25" t="n"/>
+      <c r="BJ49" s="38" t="n"/>
       <c r="BK49" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="BL49" s="27" t="n">
+      <c r="BL49" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="BM49" s="28" t="n">
@@ -13514,16 +13545,16 @@
         <v>0.547264</v>
       </c>
       <c r="BO49" s="28" t="n"/>
-      <c r="BP49" s="25" t="n"/>
-      <c r="BQ49" s="27" t="n"/>
+      <c r="BP49" s="38" t="n"/>
+      <c r="BQ49" s="39" t="n"/>
       <c r="BR49" s="28" t="n"/>
       <c r="BS49" s="28" t="n"/>
       <c r="BT49" s="28" t="n"/>
-      <c r="BU49" s="25" t="n"/>
+      <c r="BU49" s="38" t="n"/>
       <c r="BV49" s="29" t="n"/>
       <c r="BW49" s="24" t="n"/>
-      <c r="BX49" s="30" t="n"/>
-      <c r="BY49" s="27" t="n"/>
+      <c r="BX49" s="40" t="n"/>
+      <c r="BY49" s="39" t="n"/>
       <c r="BZ49" s="24" t="n"/>
       <c r="CA49" s="31" t="n"/>
     </row>
@@ -13573,7 +13604,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J50" s="25" t="n"/>
+      <c r="J50" s="38" t="n"/>
       <c r="K50" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13582,7 +13613,7 @@
       <c r="L50" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M50" s="27" t="n">
+      <c r="M50" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="N50" s="28" t="n">
@@ -13624,11 +13655,11 @@
       <c r="X50" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y50" s="25" t="n"/>
+      <c r="Y50" s="38" t="n"/>
       <c r="Z50" s="26" t="n"/>
       <c r="AA50" s="28" t="n"/>
       <c r="AB50" s="28" t="n"/>
-      <c r="AC50" s="30" t="n">
+      <c r="AC50" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD50" s="24" t="inlineStr">
@@ -13687,11 +13718,11 @@
         </is>
       </c>
       <c r="BI50" s="24" t="n"/>
-      <c r="BJ50" s="25" t="n"/>
+      <c r="BJ50" s="38" t="n"/>
       <c r="BK50" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL50" s="27" t="n">
+      <c r="BL50" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM50" s="28" t="n">
@@ -13701,16 +13732,16 @@
         <v>0.527363</v>
       </c>
       <c r="BO50" s="28" t="n"/>
-      <c r="BP50" s="25" t="n"/>
-      <c r="BQ50" s="27" t="n"/>
+      <c r="BP50" s="38" t="n"/>
+      <c r="BQ50" s="39" t="n"/>
       <c r="BR50" s="28" t="n"/>
       <c r="BS50" s="28" t="n"/>
       <c r="BT50" s="28" t="n"/>
-      <c r="BU50" s="25" t="n"/>
+      <c r="BU50" s="38" t="n"/>
       <c r="BV50" s="29" t="n"/>
       <c r="BW50" s="24" t="n"/>
-      <c r="BX50" s="30" t="n"/>
-      <c r="BY50" s="27" t="n"/>
+      <c r="BX50" s="40" t="n"/>
+      <c r="BY50" s="39" t="n"/>
       <c r="BZ50" s="24" t="n"/>
       <c r="CA50" s="31" t="n"/>
     </row>
@@ -13760,7 +13791,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J51" s="25" t="n"/>
+      <c r="J51" s="38" t="n"/>
       <c r="K51" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13769,7 +13800,7 @@
       <c r="L51" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M51" s="27" t="n">
+      <c r="M51" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N51" s="28" t="n">
@@ -13811,11 +13842,11 @@
       <c r="X51" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y51" s="25" t="n"/>
+      <c r="Y51" s="38" t="n"/>
       <c r="Z51" s="26" t="n"/>
       <c r="AA51" s="28" t="n"/>
       <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="30" t="n">
+      <c r="AC51" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD51" s="24" t="inlineStr">
@@ -13874,11 +13905,11 @@
         </is>
       </c>
       <c r="BI51" s="24" t="n"/>
-      <c r="BJ51" s="25" t="n"/>
+      <c r="BJ51" s="38" t="n"/>
       <c r="BK51" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL51" s="27" t="n">
+      <c r="BL51" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM51" s="28" t="n">
@@ -13888,16 +13919,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO51" s="28" t="n"/>
-      <c r="BP51" s="25" t="n"/>
-      <c r="BQ51" s="27" t="n"/>
+      <c r="BP51" s="38" t="n"/>
+      <c r="BQ51" s="39" t="n"/>
       <c r="BR51" s="28" t="n"/>
       <c r="BS51" s="28" t="n"/>
       <c r="BT51" s="28" t="n"/>
-      <c r="BU51" s="25" t="n"/>
+      <c r="BU51" s="38" t="n"/>
       <c r="BV51" s="29" t="n"/>
       <c r="BW51" s="24" t="n"/>
-      <c r="BX51" s="30" t="n"/>
-      <c r="BY51" s="27" t="n"/>
+      <c r="BX51" s="40" t="n"/>
+      <c r="BY51" s="39" t="n"/>
       <c r="BZ51" s="24" t="n"/>
       <c r="CA51" s="31" t="n"/>
     </row>
@@ -13947,7 +13978,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J52" s="25" t="n"/>
+      <c r="J52" s="38" t="n"/>
       <c r="K52" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13956,7 +13987,7 @@
       <c r="L52" s="26" t="n">
         <v>-174</v>
       </c>
-      <c r="M52" s="27" t="n">
+      <c r="M52" s="39" t="n">
         <v>1.574713</v>
       </c>
       <c r="N52" s="28" t="n">
@@ -13998,11 +14029,11 @@
       <c r="X52" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y52" s="25" t="n"/>
+      <c r="Y52" s="38" t="n"/>
       <c r="Z52" s="26" t="n"/>
       <c r="AA52" s="28" t="n"/>
       <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="30" t="n">
+      <c r="AC52" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD52" s="24" t="inlineStr">
@@ -14061,11 +14092,11 @@
         </is>
       </c>
       <c r="BI52" s="24" t="n"/>
-      <c r="BJ52" s="25" t="n"/>
+      <c r="BJ52" s="38" t="n"/>
       <c r="BK52" s="26" t="n">
         <v>-174</v>
       </c>
-      <c r="BL52" s="27" t="n">
+      <c r="BL52" s="39" t="n">
         <v>1.574713</v>
       </c>
       <c r="BM52" s="28" t="n">
@@ -14075,16 +14106,16 @@
         <v>0.631841</v>
       </c>
       <c r="BO52" s="28" t="n"/>
-      <c r="BP52" s="25" t="n"/>
-      <c r="BQ52" s="27" t="n"/>
+      <c r="BP52" s="38" t="n"/>
+      <c r="BQ52" s="39" t="n"/>
       <c r="BR52" s="28" t="n"/>
       <c r="BS52" s="28" t="n"/>
       <c r="BT52" s="28" t="n"/>
-      <c r="BU52" s="25" t="n"/>
+      <c r="BU52" s="38" t="n"/>
       <c r="BV52" s="29" t="n"/>
       <c r="BW52" s="24" t="n"/>
-      <c r="BX52" s="30" t="n"/>
-      <c r="BY52" s="27" t="n"/>
+      <c r="BX52" s="40" t="n"/>
+      <c r="BY52" s="39" t="n"/>
       <c r="BZ52" s="24" t="n"/>
       <c r="CA52" s="31" t="n"/>
     </row>
@@ -14134,7 +14165,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J53" s="25" t="n"/>
+      <c r="J53" s="38" t="n"/>
       <c r="K53" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14143,7 +14174,7 @@
       <c r="L53" s="26" t="n">
         <v>-376</v>
       </c>
-      <c r="M53" s="27" t="n">
+      <c r="M53" s="39" t="n">
         <v>1.265957</v>
       </c>
       <c r="N53" s="28" t="n">
@@ -14183,11 +14214,11 @@
       <c r="X53" s="26" t="n">
         <v>92</v>
       </c>
-      <c r="Y53" s="25" t="n"/>
+      <c r="Y53" s="38" t="n"/>
       <c r="Z53" s="26" t="n"/>
       <c r="AA53" s="28" t="n"/>
       <c r="AB53" s="28" t="n"/>
-      <c r="AC53" s="30" t="n">
+      <c r="AC53" s="40" t="n">
         <v>0.1995</v>
       </c>
       <c r="AD53" s="24" t="inlineStr">
@@ -14234,11 +14265,11 @@
         </is>
       </c>
       <c r="BI53" s="24" t="n"/>
-      <c r="BJ53" s="25" t="n"/>
+      <c r="BJ53" s="38" t="n"/>
       <c r="BK53" s="26" t="n">
         <v>-376</v>
       </c>
-      <c r="BL53" s="27" t="n">
+      <c r="BL53" s="39" t="n">
         <v>1.265957</v>
       </c>
       <c r="BM53" s="28" t="n">
@@ -14248,16 +14279,16 @@
         <v>0.782178</v>
       </c>
       <c r="BO53" s="28" t="n"/>
-      <c r="BP53" s="25" t="n"/>
-      <c r="BQ53" s="27" t="n"/>
+      <c r="BP53" s="38" t="n"/>
+      <c r="BQ53" s="39" t="n"/>
       <c r="BR53" s="28" t="n"/>
       <c r="BS53" s="28" t="n"/>
       <c r="BT53" s="28" t="n"/>
-      <c r="BU53" s="25" t="n"/>
+      <c r="BU53" s="38" t="n"/>
       <c r="BV53" s="29" t="n"/>
       <c r="BW53" s="24" t="n"/>
-      <c r="BX53" s="30" t="n"/>
-      <c r="BY53" s="27" t="n"/>
+      <c r="BX53" s="40" t="n"/>
+      <c r="BY53" s="39" t="n"/>
       <c r="BZ53" s="24" t="n"/>
       <c r="CA53" s="31" t="n"/>
     </row>
@@ -14307,7 +14338,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J54" s="25" t="n"/>
+      <c r="J54" s="38" t="n"/>
       <c r="K54" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14316,7 +14347,7 @@
       <c r="L54" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M54" s="27" t="n">
+      <c r="M54" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="N54" s="28" t="n">
@@ -14356,11 +14387,11 @@
       <c r="X54" s="26" t="n">
         <v>96</v>
       </c>
-      <c r="Y54" s="25" t="n"/>
+      <c r="Y54" s="38" t="n"/>
       <c r="Z54" s="26" t="n"/>
       <c r="AA54" s="28" t="n"/>
       <c r="AB54" s="28" t="n"/>
-      <c r="AC54" s="30" t="n">
+      <c r="AC54" s="40" t="n">
         <v>0.4425</v>
       </c>
       <c r="AD54" s="24" t="inlineStr">
@@ -14407,11 +14438,11 @@
         </is>
       </c>
       <c r="BI54" s="24" t="n"/>
-      <c r="BJ54" s="25" t="n"/>
+      <c r="BJ54" s="38" t="n"/>
       <c r="BK54" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL54" s="27" t="n">
+      <c r="BL54" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM54" s="28" t="n">
@@ -14421,16 +14452,16 @@
         <v>0.524752</v>
       </c>
       <c r="BO54" s="28" t="n"/>
-      <c r="BP54" s="25" t="n"/>
-      <c r="BQ54" s="27" t="n"/>
+      <c r="BP54" s="38" t="n"/>
+      <c r="BQ54" s="39" t="n"/>
       <c r="BR54" s="28" t="n"/>
       <c r="BS54" s="28" t="n"/>
       <c r="BT54" s="28" t="n"/>
-      <c r="BU54" s="25" t="n"/>
+      <c r="BU54" s="38" t="n"/>
       <c r="BV54" s="29" t="n"/>
       <c r="BW54" s="24" t="n"/>
-      <c r="BX54" s="30" t="n"/>
-      <c r="BY54" s="27" t="n"/>
+      <c r="BX54" s="40" t="n"/>
+      <c r="BY54" s="39" t="n"/>
       <c r="BZ54" s="24" t="n"/>
       <c r="CA54" s="31" t="n"/>
     </row>
@@ -14480,7 +14511,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J55" s="25" t="n"/>
+      <c r="J55" s="38" t="n"/>
       <c r="K55" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14489,7 +14520,7 @@
       <c r="L55" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="M55" s="27" t="n">
+      <c r="M55" s="39" t="n">
         <v>1.561798</v>
       </c>
       <c r="N55" s="28" t="n">
@@ -14529,11 +14560,11 @@
       <c r="X55" s="26" t="n">
         <v>83</v>
       </c>
-      <c r="Y55" s="25" t="n"/>
+      <c r="Y55" s="38" t="n"/>
       <c r="Z55" s="26" t="n"/>
       <c r="AA55" s="28" t="n"/>
       <c r="AB55" s="28" t="n"/>
-      <c r="AC55" s="30" t="n">
+      <c r="AC55" s="40" t="n">
         <v>-2</v>
       </c>
       <c r="AD55" s="24" t="inlineStr">
@@ -14580,11 +14611,11 @@
         </is>
       </c>
       <c r="BI55" s="24" t="n"/>
-      <c r="BJ55" s="25" t="n"/>
+      <c r="BJ55" s="38" t="n"/>
       <c r="BK55" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="BL55" s="27" t="n">
+      <c r="BL55" s="39" t="n">
         <v>1.561798</v>
       </c>
       <c r="BM55" s="28" t="n">
@@ -14594,16 +14625,16 @@
         <v>0.633663</v>
       </c>
       <c r="BO55" s="28" t="n"/>
-      <c r="BP55" s="25" t="n"/>
-      <c r="BQ55" s="27" t="n"/>
+      <c r="BP55" s="38" t="n"/>
+      <c r="BQ55" s="39" t="n"/>
       <c r="BR55" s="28" t="n"/>
       <c r="BS55" s="28" t="n"/>
       <c r="BT55" s="28" t="n"/>
-      <c r="BU55" s="25" t="n"/>
+      <c r="BU55" s="38" t="n"/>
       <c r="BV55" s="29" t="n"/>
       <c r="BW55" s="24" t="n"/>
-      <c r="BX55" s="30" t="n"/>
-      <c r="BY55" s="27" t="n"/>
+      <c r="BX55" s="40" t="n"/>
+      <c r="BY55" s="39" t="n"/>
       <c r="BZ55" s="24" t="n"/>
       <c r="CA55" s="31" t="n"/>
     </row>
@@ -14653,7 +14684,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J56" s="25" t="n"/>
+      <c r="J56" s="38" t="n"/>
       <c r="K56" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14662,7 +14693,7 @@
       <c r="L56" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="M56" s="27" t="n">
+      <c r="M56" s="39" t="n">
         <v>1.613497</v>
       </c>
       <c r="N56" s="28" t="n">
@@ -14704,11 +14735,11 @@
       <c r="X56" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y56" s="25" t="n"/>
+      <c r="Y56" s="38" t="n"/>
       <c r="Z56" s="26" t="n"/>
       <c r="AA56" s="28" t="n"/>
       <c r="AB56" s="28" t="n"/>
-      <c r="AC56" s="30" t="n">
+      <c r="AC56" s="40" t="n">
         <v>0.9202</v>
       </c>
       <c r="AD56" s="24" t="inlineStr">
@@ -14767,11 +14798,11 @@
         </is>
       </c>
       <c r="BI56" s="24" t="n"/>
-      <c r="BJ56" s="25" t="n"/>
+      <c r="BJ56" s="38" t="n"/>
       <c r="BK56" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="BL56" s="27" t="n">
+      <c r="BL56" s="39" t="n">
         <v>1.613497</v>
       </c>
       <c r="BM56" s="28" t="n">
@@ -14781,16 +14812,16 @@
         <v>0.616915</v>
       </c>
       <c r="BO56" s="28" t="n"/>
-      <c r="BP56" s="25" t="n"/>
-      <c r="BQ56" s="27" t="n"/>
+      <c r="BP56" s="38" t="n"/>
+      <c r="BQ56" s="39" t="n"/>
       <c r="BR56" s="28" t="n"/>
       <c r="BS56" s="28" t="n"/>
       <c r="BT56" s="28" t="n"/>
-      <c r="BU56" s="25" t="n"/>
+      <c r="BU56" s="38" t="n"/>
       <c r="BV56" s="29" t="n"/>
       <c r="BW56" s="24" t="n"/>
-      <c r="BX56" s="30" t="n"/>
-      <c r="BY56" s="27" t="n"/>
+      <c r="BX56" s="40" t="n"/>
+      <c r="BY56" s="39" t="n"/>
       <c r="BZ56" s="24" t="n"/>
       <c r="CA56" s="31" t="n"/>
     </row>
@@ -14840,7 +14871,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J57" s="25" t="n"/>
+      <c r="J57" s="38" t="n"/>
       <c r="K57" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14849,7 +14880,7 @@
       <c r="L57" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M57" s="27" t="n">
+      <c r="M57" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="N57" s="28" t="n">
@@ -14891,11 +14922,11 @@
       <c r="X57" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y57" s="25" t="n"/>
+      <c r="Y57" s="38" t="n"/>
       <c r="Z57" s="26" t="n"/>
       <c r="AA57" s="28" t="n"/>
       <c r="AB57" s="28" t="n"/>
-      <c r="AC57" s="30" t="n">
+      <c r="AC57" s="40" t="n">
         <v>0.6757</v>
       </c>
       <c r="AD57" s="24" t="inlineStr">
@@ -14954,11 +14985,11 @@
         </is>
       </c>
       <c r="BI57" s="24" t="n"/>
-      <c r="BJ57" s="25" t="n"/>
+      <c r="BJ57" s="38" t="n"/>
       <c r="BK57" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL57" s="27" t="n">
+      <c r="BL57" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM57" s="28" t="n">
@@ -14968,16 +14999,16 @@
         <v>0.522388</v>
       </c>
       <c r="BO57" s="28" t="n"/>
-      <c r="BP57" s="25" t="n"/>
-      <c r="BQ57" s="27" t="n"/>
+      <c r="BP57" s="38" t="n"/>
+      <c r="BQ57" s="39" t="n"/>
       <c r="BR57" s="28" t="n"/>
       <c r="BS57" s="28" t="n"/>
       <c r="BT57" s="28" t="n"/>
-      <c r="BU57" s="25" t="n"/>
+      <c r="BU57" s="38" t="n"/>
       <c r="BV57" s="29" t="n"/>
       <c r="BW57" s="24" t="n"/>
-      <c r="BX57" s="30" t="n"/>
-      <c r="BY57" s="27" t="n"/>
+      <c r="BX57" s="40" t="n"/>
+      <c r="BY57" s="39" t="n"/>
       <c r="BZ57" s="24" t="n"/>
       <c r="CA57" s="31" t="n"/>
     </row>
@@ -15027,7 +15058,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J58" s="25" t="n"/>
+      <c r="J58" s="38" t="n"/>
       <c r="K58" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -15036,7 +15067,7 @@
       <c r="L58" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M58" s="27" t="n">
+      <c r="M58" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="N58" s="28" t="n">
@@ -15078,11 +15109,11 @@
       <c r="X58" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y58" s="25" t="n"/>
+      <c r="Y58" s="38" t="n"/>
       <c r="Z58" s="26" t="n"/>
       <c r="AA58" s="28" t="n"/>
       <c r="AB58" s="28" t="n"/>
-      <c r="AC58" s="30" t="n">
+      <c r="AC58" s="40" t="n">
         <v>1.087</v>
       </c>
       <c r="AD58" s="24" t="inlineStr">
@@ -15141,11 +15172,11 @@
         </is>
       </c>
       <c r="BI58" s="24" t="n"/>
-      <c r="BJ58" s="25" t="n"/>
+      <c r="BJ58" s="38" t="n"/>
       <c r="BK58" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL58" s="27" t="n">
+      <c r="BL58" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM58" s="28" t="n">
@@ -15155,16 +15186,16 @@
         <v>0.577114</v>
       </c>
       <c r="BO58" s="28" t="n"/>
-      <c r="BP58" s="25" t="n"/>
-      <c r="BQ58" s="27" t="n"/>
+      <c r="BP58" s="38" t="n"/>
+      <c r="BQ58" s="39" t="n"/>
       <c r="BR58" s="28" t="n"/>
       <c r="BS58" s="28" t="n"/>
       <c r="BT58" s="28" t="n"/>
-      <c r="BU58" s="25" t="n"/>
+      <c r="BU58" s="38" t="n"/>
       <c r="BV58" s="29" t="n"/>
       <c r="BW58" s="24" t="n"/>
-      <c r="BX58" s="30" t="n"/>
-      <c r="BY58" s="27" t="n"/>
+      <c r="BX58" s="40" t="n"/>
+      <c r="BY58" s="39" t="n"/>
       <c r="BZ58" s="24" t="n"/>
       <c r="CA58" s="31" t="n"/>
     </row>
@@ -15214,7 +15245,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J59" s="25" t="n"/>
+      <c r="J59" s="38" t="n"/>
       <c r="K59" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -15223,7 +15254,7 @@
       <c r="L59" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="M59" s="27" t="n">
+      <c r="M59" s="39" t="n">
         <v>1.561798</v>
       </c>
       <c r="N59" s="28" t="n">
@@ -15265,11 +15296,11 @@
       <c r="X59" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y59" s="25" t="n"/>
+      <c r="Y59" s="38" t="n"/>
       <c r="Z59" s="26" t="n"/>
       <c r="AA59" s="28" t="n"/>
       <c r="AB59" s="28" t="n"/>
-      <c r="AC59" s="30" t="n">
+      <c r="AC59" s="40" t="n">
         <v>0.5618</v>
       </c>
       <c r="AD59" s="24" t="inlineStr">
@@ -15328,11 +15359,11 @@
         </is>
       </c>
       <c r="BI59" s="24" t="n"/>
-      <c r="BJ59" s="25" t="n"/>
+      <c r="BJ59" s="38" t="n"/>
       <c r="BK59" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="BL59" s="27" t="n">
+      <c r="BL59" s="39" t="n">
         <v>1.561798</v>
       </c>
       <c r="BM59" s="28" t="n">
@@ -15342,16 +15373,16 @@
         <v>0.636816</v>
       </c>
       <c r="BO59" s="28" t="n"/>
-      <c r="BP59" s="25" t="n"/>
-      <c r="BQ59" s="27" t="n"/>
+      <c r="BP59" s="38" t="n"/>
+      <c r="BQ59" s="39" t="n"/>
       <c r="BR59" s="28" t="n"/>
       <c r="BS59" s="28" t="n"/>
       <c r="BT59" s="28" t="n"/>
-      <c r="BU59" s="25" t="n"/>
+      <c r="BU59" s="38" t="n"/>
       <c r="BV59" s="29" t="n"/>
       <c r="BW59" s="24" t="n"/>
-      <c r="BX59" s="30" t="n"/>
-      <c r="BY59" s="27" t="n"/>
+      <c r="BX59" s="40" t="n"/>
+      <c r="BY59" s="39" t="n"/>
       <c r="BZ59" s="24" t="n"/>
       <c r="CA59" s="31" t="n"/>
     </row>
@@ -15401,7 +15432,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J60" s="25" t="n"/>
+      <c r="J60" s="38" t="n"/>
       <c r="K60" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -15410,7 +15441,7 @@
       <c r="L60" s="26" t="n">
         <v>-669</v>
       </c>
-      <c r="M60" s="27" t="n">
+      <c r="M60" s="39" t="n">
         <v>1.149477</v>
       </c>
       <c r="N60" s="28" t="n">
@@ -15450,11 +15481,11 @@
       <c r="X60" s="26" t="n">
         <v>101</v>
       </c>
-      <c r="Y60" s="25" t="n"/>
+      <c r="Y60" s="38" t="n"/>
       <c r="Z60" s="26" t="n"/>
       <c r="AA60" s="28" t="n"/>
       <c r="AB60" s="28" t="n"/>
-      <c r="AC60" s="30" t="n">
+      <c r="AC60" s="40" t="n">
         <v>0.299</v>
       </c>
       <c r="AD60" s="24" t="inlineStr">
@@ -15501,11 +15532,11 @@
         </is>
       </c>
       <c r="BI60" s="24" t="n"/>
-      <c r="BJ60" s="25" t="n"/>
+      <c r="BJ60" s="38" t="n"/>
       <c r="BK60" s="26" t="n">
         <v>-669</v>
       </c>
-      <c r="BL60" s="27" t="n">
+      <c r="BL60" s="39" t="n">
         <v>1.149477</v>
       </c>
       <c r="BM60" s="28" t="n">
@@ -15515,16 +15546,16 @@
         <v>0.861386</v>
       </c>
       <c r="BO60" s="28" t="n"/>
-      <c r="BP60" s="25" t="n"/>
-      <c r="BQ60" s="27" t="n"/>
+      <c r="BP60" s="38" t="n"/>
+      <c r="BQ60" s="39" t="n"/>
       <c r="BR60" s="28" t="n"/>
       <c r="BS60" s="28" t="n"/>
       <c r="BT60" s="28" t="n"/>
-      <c r="BU60" s="25" t="n"/>
+      <c r="BU60" s="38" t="n"/>
       <c r="BV60" s="29" t="n"/>
       <c r="BW60" s="24" t="n"/>
-      <c r="BX60" s="30" t="n"/>
-      <c r="BY60" s="27" t="n"/>
+      <c r="BX60" s="40" t="n"/>
+      <c r="BY60" s="39" t="n"/>
       <c r="BZ60" s="24" t="n"/>
       <c r="CA60" s="31" t="n"/>
     </row>
@@ -15574,7 +15605,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J61" s="25" t="n"/>
+      <c r="J61" s="38" t="n"/>
       <c r="K61" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -15583,7 +15614,7 @@
       <c r="L61" s="26" t="n">
         <v>-355</v>
       </c>
-      <c r="M61" s="27" t="n">
+      <c r="M61" s="39" t="n">
         <v>1.28169</v>
       </c>
       <c r="N61" s="28" t="n">
@@ -15623,11 +15654,11 @@
       <c r="X61" s="26" t="n">
         <v>74</v>
       </c>
-      <c r="Y61" s="25" t="n"/>
+      <c r="Y61" s="38" t="n"/>
       <c r="Z61" s="26" t="n"/>
       <c r="AA61" s="28" t="n"/>
       <c r="AB61" s="28" t="n"/>
-      <c r="AC61" s="30" t="n">
+      <c r="AC61" s="40" t="n">
         <v>0.5634</v>
       </c>
       <c r="AD61" s="24" t="inlineStr">
@@ -15674,11 +15705,11 @@
         </is>
       </c>
       <c r="BI61" s="24" t="n"/>
-      <c r="BJ61" s="25" t="n"/>
+      <c r="BJ61" s="38" t="n"/>
       <c r="BK61" s="26" t="n">
         <v>-355</v>
       </c>
-      <c r="BL61" s="27" t="n">
+      <c r="BL61" s="39" t="n">
         <v>1.28169</v>
       </c>
       <c r="BM61" s="28" t="n">
@@ -15688,16 +15719,16 @@
         <v>0.772277</v>
       </c>
       <c r="BO61" s="28" t="n"/>
-      <c r="BP61" s="25" t="n"/>
-      <c r="BQ61" s="27" t="n"/>
+      <c r="BP61" s="38" t="n"/>
+      <c r="BQ61" s="39" t="n"/>
       <c r="BR61" s="28" t="n"/>
       <c r="BS61" s="28" t="n"/>
       <c r="BT61" s="28" t="n"/>
-      <c r="BU61" s="25" t="n"/>
+      <c r="BU61" s="38" t="n"/>
       <c r="BV61" s="29" t="n"/>
       <c r="BW61" s="24" t="n"/>
-      <c r="BX61" s="30" t="n"/>
-      <c r="BY61" s="27" t="n"/>
+      <c r="BX61" s="40" t="n"/>
+      <c r="BY61" s="39" t="n"/>
       <c r="BZ61" s="24" t="n"/>
       <c r="CA61" s="31" t="n"/>
     </row>
@@ -15747,7 +15778,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J62" s="25" t="n"/>
+      <c r="J62" s="38" t="n"/>
       <c r="K62" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -15756,7 +15787,7 @@
       <c r="L62" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="M62" s="27" t="n">
+      <c r="M62" s="39" t="n">
         <v>2.13</v>
       </c>
       <c r="N62" s="28" t="n">
@@ -15788,11 +15819,11 @@
       <c r="V62" s="24" t="n"/>
       <c r="W62" s="26" t="n"/>
       <c r="X62" s="26" t="n"/>
-      <c r="Y62" s="25" t="n"/>
+      <c r="Y62" s="38" t="n"/>
       <c r="Z62" s="26" t="n"/>
       <c r="AA62" s="28" t="n"/>
       <c r="AB62" s="28" t="n"/>
-      <c r="AC62" s="30" t="n"/>
+      <c r="AC62" s="40" t="n"/>
       <c r="AD62" s="24" t="n"/>
       <c r="AE62" s="31" t="inlineStr">
         <is>
@@ -15923,11 +15954,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ62" s="25" t="n"/>
+      <c r="BJ62" s="38" t="n"/>
       <c r="BK62" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="BL62" s="27" t="n">
+      <c r="BL62" s="39" t="n">
         <v>2.13</v>
       </c>
       <c r="BM62" s="28" t="n">
@@ -15937,16 +15968,16 @@
         <v>0.467662</v>
       </c>
       <c r="BO62" s="28" t="n"/>
-      <c r="BP62" s="25" t="n"/>
-      <c r="BQ62" s="27" t="n"/>
+      <c r="BP62" s="38" t="n"/>
+      <c r="BQ62" s="39" t="n"/>
       <c r="BR62" s="28" t="n"/>
       <c r="BS62" s="28" t="n"/>
       <c r="BT62" s="28" t="n"/>
-      <c r="BU62" s="25" t="n"/>
+      <c r="BU62" s="38" t="n"/>
       <c r="BV62" s="29" t="n"/>
       <c r="BW62" s="24" t="n"/>
-      <c r="BX62" s="30" t="n"/>
-      <c r="BY62" s="27" t="n"/>
+      <c r="BX62" s="40" t="n"/>
+      <c r="BY62" s="39" t="n"/>
       <c r="BZ62" s="24" t="n"/>
       <c r="CA62" s="31" t="n"/>
     </row>
@@ -15996,7 +16027,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J63" s="25" t="n"/>
+      <c r="J63" s="38" t="n"/>
       <c r="K63" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16005,7 +16036,7 @@
       <c r="L63" s="26" t="n">
         <v>125</v>
       </c>
-      <c r="M63" s="27" t="n">
+      <c r="M63" s="39" t="n">
         <v>2.25</v>
       </c>
       <c r="N63" s="28" t="n">
@@ -16037,11 +16068,11 @@
       <c r="V63" s="24" t="n"/>
       <c r="W63" s="26" t="n"/>
       <c r="X63" s="26" t="n"/>
-      <c r="Y63" s="25" t="n"/>
+      <c r="Y63" s="38" t="n"/>
       <c r="Z63" s="26" t="n"/>
       <c r="AA63" s="28" t="n"/>
       <c r="AB63" s="28" t="n"/>
-      <c r="AC63" s="30" t="n"/>
+      <c r="AC63" s="40" t="n"/>
       <c r="AD63" s="24" t="n"/>
       <c r="AE63" s="31" t="inlineStr">
         <is>
@@ -16172,11 +16203,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ63" s="25" t="n"/>
+      <c r="BJ63" s="38" t="n"/>
       <c r="BK63" s="26" t="n">
         <v>125</v>
       </c>
-      <c r="BL63" s="27" t="n">
+      <c r="BL63" s="39" t="n">
         <v>2.25</v>
       </c>
       <c r="BM63" s="28" t="n">
@@ -16186,16 +16217,16 @@
         <v>0.442786</v>
       </c>
       <c r="BO63" s="28" t="n"/>
-      <c r="BP63" s="25" t="n"/>
-      <c r="BQ63" s="27" t="n"/>
+      <c r="BP63" s="38" t="n"/>
+      <c r="BQ63" s="39" t="n"/>
       <c r="BR63" s="28" t="n"/>
       <c r="BS63" s="28" t="n"/>
       <c r="BT63" s="28" t="n"/>
-      <c r="BU63" s="25" t="n"/>
+      <c r="BU63" s="38" t="n"/>
       <c r="BV63" s="29" t="n"/>
       <c r="BW63" s="24" t="n"/>
-      <c r="BX63" s="30" t="n"/>
-      <c r="BY63" s="27" t="n"/>
+      <c r="BX63" s="40" t="n"/>
+      <c r="BY63" s="39" t="n"/>
       <c r="BZ63" s="24" t="n"/>
       <c r="CA63" s="31" t="n"/>
     </row>
@@ -16245,7 +16276,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J64" s="25" t="n"/>
+      <c r="J64" s="38" t="n"/>
       <c r="K64" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16254,7 +16285,7 @@
       <c r="L64" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M64" s="27" t="n">
+      <c r="M64" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N64" s="28" t="n">
@@ -16286,11 +16317,11 @@
       <c r="V64" s="24" t="n"/>
       <c r="W64" s="26" t="n"/>
       <c r="X64" s="26" t="n"/>
-      <c r="Y64" s="25" t="n"/>
+      <c r="Y64" s="38" t="n"/>
       <c r="Z64" s="26" t="n"/>
       <c r="AA64" s="28" t="n"/>
       <c r="AB64" s="28" t="n"/>
-      <c r="AC64" s="30" t="n"/>
+      <c r="AC64" s="40" t="n"/>
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
@@ -16421,11 +16452,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ64" s="25" t="n"/>
+      <c r="BJ64" s="38" t="n"/>
       <c r="BK64" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL64" s="27" t="n">
+      <c r="BL64" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM64" s="28" t="n">
@@ -16435,16 +16466,16 @@
         <v>0.517413</v>
       </c>
       <c r="BO64" s="28" t="n"/>
-      <c r="BP64" s="25" t="n"/>
-      <c r="BQ64" s="27" t="n"/>
+      <c r="BP64" s="38" t="n"/>
+      <c r="BQ64" s="39" t="n"/>
       <c r="BR64" s="28" t="n"/>
       <c r="BS64" s="28" t="n"/>
       <c r="BT64" s="28" t="n"/>
-      <c r="BU64" s="25" t="n"/>
+      <c r="BU64" s="38" t="n"/>
       <c r="BV64" s="29" t="n"/>
       <c r="BW64" s="24" t="n"/>
-      <c r="BX64" s="30" t="n"/>
-      <c r="BY64" s="27" t="n"/>
+      <c r="BX64" s="40" t="n"/>
+      <c r="BY64" s="39" t="n"/>
       <c r="BZ64" s="24" t="n"/>
       <c r="CA64" s="31" t="n"/>
     </row>
@@ -16494,7 +16525,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J65" s="25" t="n"/>
+      <c r="J65" s="38" t="n"/>
       <c r="K65" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16503,7 +16534,7 @@
       <c r="L65" s="26" t="n">
         <v>-147</v>
       </c>
-      <c r="M65" s="27" t="n">
+      <c r="M65" s="39" t="n">
         <v>1.680272</v>
       </c>
       <c r="N65" s="28" t="n">
@@ -16535,11 +16566,11 @@
       <c r="V65" s="24" t="n"/>
       <c r="W65" s="26" t="n"/>
       <c r="X65" s="26" t="n"/>
-      <c r="Y65" s="25" t="n"/>
+      <c r="Y65" s="38" t="n"/>
       <c r="Z65" s="26" t="n"/>
       <c r="AA65" s="28" t="n"/>
       <c r="AB65" s="28" t="n"/>
-      <c r="AC65" s="30" t="n"/>
+      <c r="AC65" s="40" t="n"/>
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
@@ -16670,11 +16701,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ65" s="25" t="n"/>
+      <c r="BJ65" s="38" t="n"/>
       <c r="BK65" s="26" t="n">
         <v>-147</v>
       </c>
-      <c r="BL65" s="27" t="n">
+      <c r="BL65" s="39" t="n">
         <v>1.680272</v>
       </c>
       <c r="BM65" s="28" t="n">
@@ -16684,16 +16715,16 @@
         <v>0.59204</v>
       </c>
       <c r="BO65" s="28" t="n"/>
-      <c r="BP65" s="25" t="n"/>
-      <c r="BQ65" s="27" t="n"/>
+      <c r="BP65" s="38" t="n"/>
+      <c r="BQ65" s="39" t="n"/>
       <c r="BR65" s="28" t="n"/>
       <c r="BS65" s="28" t="n"/>
       <c r="BT65" s="28" t="n"/>
-      <c r="BU65" s="25" t="n"/>
+      <c r="BU65" s="38" t="n"/>
       <c r="BV65" s="29" t="n"/>
       <c r="BW65" s="24" t="n"/>
-      <c r="BX65" s="30" t="n"/>
-      <c r="BY65" s="27" t="n"/>
+      <c r="BX65" s="40" t="n"/>
+      <c r="BY65" s="39" t="n"/>
       <c r="BZ65" s="24" t="n"/>
       <c r="CA65" s="31" t="n"/>
     </row>
@@ -16743,7 +16774,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J66" s="25" t="n"/>
+      <c r="J66" s="38" t="n"/>
       <c r="K66" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16752,7 +16783,7 @@
       <c r="L66" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M66" s="27" t="n">
+      <c r="M66" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="N66" s="28" t="n">
@@ -16784,11 +16815,11 @@
       <c r="V66" s="24" t="n"/>
       <c r="W66" s="26" t="n"/>
       <c r="X66" s="26" t="n"/>
-      <c r="Y66" s="25" t="n"/>
+      <c r="Y66" s="38" t="n"/>
       <c r="Z66" s="26" t="n"/>
       <c r="AA66" s="28" t="n"/>
       <c r="AB66" s="28" t="n"/>
-      <c r="AC66" s="30" t="n"/>
+      <c r="AC66" s="40" t="n"/>
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
@@ -16919,11 +16950,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ66" s="25" t="n"/>
+      <c r="BJ66" s="38" t="n"/>
       <c r="BK66" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL66" s="27" t="n">
+      <c r="BL66" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM66" s="28" t="n">
@@ -16933,16 +16964,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO66" s="28" t="n"/>
-      <c r="BP66" s="25" t="n"/>
-      <c r="BQ66" s="27" t="n"/>
+      <c r="BP66" s="38" t="n"/>
+      <c r="BQ66" s="39" t="n"/>
       <c r="BR66" s="28" t="n"/>
       <c r="BS66" s="28" t="n"/>
       <c r="BT66" s="28" t="n"/>
-      <c r="BU66" s="25" t="n"/>
+      <c r="BU66" s="38" t="n"/>
       <c r="BV66" s="29" t="n"/>
       <c r="BW66" s="24" t="n"/>
-      <c r="BX66" s="30" t="n"/>
-      <c r="BY66" s="27" t="n"/>
+      <c r="BX66" s="40" t="n"/>
+      <c r="BY66" s="39" t="n"/>
       <c r="BZ66" s="24" t="n"/>
       <c r="CA66" s="31" t="n"/>
     </row>
@@ -16992,7 +17023,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J67" s="25" t="n"/>
+      <c r="J67" s="38" t="n"/>
       <c r="K67" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17001,7 +17032,7 @@
       <c r="L67" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M67" s="27" t="n">
+      <c r="M67" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N67" s="28" t="n">
@@ -17033,11 +17064,11 @@
       <c r="V67" s="24" t="n"/>
       <c r="W67" s="26" t="n"/>
       <c r="X67" s="26" t="n"/>
-      <c r="Y67" s="25" t="n"/>
+      <c r="Y67" s="38" t="n"/>
       <c r="Z67" s="26" t="n"/>
       <c r="AA67" s="28" t="n"/>
       <c r="AB67" s="28" t="n"/>
-      <c r="AC67" s="30" t="n"/>
+      <c r="AC67" s="40" t="n"/>
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
@@ -17168,11 +17199,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ67" s="25" t="n"/>
+      <c r="BJ67" s="38" t="n"/>
       <c r="BK67" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL67" s="27" t="n">
+      <c r="BL67" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM67" s="28" t="n">
@@ -17182,16 +17213,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO67" s="28" t="n"/>
-      <c r="BP67" s="25" t="n"/>
-      <c r="BQ67" s="27" t="n"/>
+      <c r="BP67" s="38" t="n"/>
+      <c r="BQ67" s="39" t="n"/>
       <c r="BR67" s="28" t="n"/>
       <c r="BS67" s="28" t="n"/>
       <c r="BT67" s="28" t="n"/>
-      <c r="BU67" s="25" t="n"/>
+      <c r="BU67" s="38" t="n"/>
       <c r="BV67" s="29" t="n"/>
       <c r="BW67" s="24" t="n"/>
-      <c r="BX67" s="30" t="n"/>
-      <c r="BY67" s="27" t="n"/>
+      <c r="BX67" s="40" t="n"/>
+      <c r="BY67" s="39" t="n"/>
       <c r="BZ67" s="24" t="n"/>
       <c r="CA67" s="31" t="n"/>
     </row>
@@ -17241,7 +17272,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J68" s="25" t="n"/>
+      <c r="J68" s="38" t="n"/>
       <c r="K68" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17250,7 +17281,7 @@
       <c r="L68" s="26" t="n">
         <v>-199</v>
       </c>
-      <c r="M68" s="27" t="n">
+      <c r="M68" s="39" t="n">
         <v>1.502513</v>
       </c>
       <c r="N68" s="28" t="n">
@@ -17282,11 +17313,11 @@
       <c r="V68" s="24" t="n"/>
       <c r="W68" s="26" t="n"/>
       <c r="X68" s="26" t="n"/>
-      <c r="Y68" s="25" t="n"/>
+      <c r="Y68" s="38" t="n"/>
       <c r="Z68" s="26" t="n"/>
       <c r="AA68" s="28" t="n"/>
       <c r="AB68" s="28" t="n"/>
-      <c r="AC68" s="30" t="n"/>
+      <c r="AC68" s="40" t="n"/>
       <c r="AD68" s="24" t="n"/>
       <c r="AE68" s="31" t="inlineStr">
         <is>
@@ -17417,11 +17448,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ68" s="25" t="n"/>
+      <c r="BJ68" s="38" t="n"/>
       <c r="BK68" s="26" t="n">
         <v>-199</v>
       </c>
-      <c r="BL68" s="27" t="n">
+      <c r="BL68" s="39" t="n">
         <v>1.502513</v>
       </c>
       <c r="BM68" s="28" t="n">
@@ -17431,16 +17462,16 @@
         <v>0.6616919999999999</v>
       </c>
       <c r="BO68" s="28" t="n"/>
-      <c r="BP68" s="25" t="n"/>
-      <c r="BQ68" s="27" t="n"/>
+      <c r="BP68" s="38" t="n"/>
+      <c r="BQ68" s="39" t="n"/>
       <c r="BR68" s="28" t="n"/>
       <c r="BS68" s="28" t="n"/>
       <c r="BT68" s="28" t="n"/>
-      <c r="BU68" s="25" t="n"/>
+      <c r="BU68" s="38" t="n"/>
       <c r="BV68" s="29" t="n"/>
       <c r="BW68" s="24" t="n"/>
-      <c r="BX68" s="30" t="n"/>
-      <c r="BY68" s="27" t="n"/>
+      <c r="BX68" s="40" t="n"/>
+      <c r="BY68" s="39" t="n"/>
       <c r="BZ68" s="24" t="n"/>
       <c r="CA68" s="31" t="n"/>
     </row>
@@ -17490,7 +17521,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J69" s="25" t="n"/>
+      <c r="J69" s="38" t="n"/>
       <c r="K69" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17499,7 +17530,7 @@
       <c r="L69" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M69" s="27" t="n">
+      <c r="M69" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="N69" s="28" t="n">
@@ -17531,11 +17562,11 @@
       <c r="V69" s="24" t="n"/>
       <c r="W69" s="26" t="n"/>
       <c r="X69" s="26" t="n"/>
-      <c r="Y69" s="25" t="n"/>
+      <c r="Y69" s="38" t="n"/>
       <c r="Z69" s="26" t="n"/>
       <c r="AA69" s="28" t="n"/>
       <c r="AB69" s="28" t="n"/>
-      <c r="AC69" s="30" t="n"/>
+      <c r="AC69" s="40" t="n"/>
       <c r="AD69" s="24" t="n"/>
       <c r="AE69" s="31" t="inlineStr">
         <is>
@@ -17666,11 +17697,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ69" s="25" t="n"/>
+      <c r="BJ69" s="38" t="n"/>
       <c r="BK69" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL69" s="27" t="n">
+      <c r="BL69" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM69" s="28" t="n">
@@ -17680,16 +17711,16 @@
         <v>0.522388</v>
       </c>
       <c r="BO69" s="28" t="n"/>
-      <c r="BP69" s="25" t="n"/>
-      <c r="BQ69" s="27" t="n"/>
+      <c r="BP69" s="38" t="n"/>
+      <c r="BQ69" s="39" t="n"/>
       <c r="BR69" s="28" t="n"/>
       <c r="BS69" s="28" t="n"/>
       <c r="BT69" s="28" t="n"/>
-      <c r="BU69" s="25" t="n"/>
+      <c r="BU69" s="38" t="n"/>
       <c r="BV69" s="29" t="n"/>
       <c r="BW69" s="24" t="n"/>
-      <c r="BX69" s="30" t="n"/>
-      <c r="BY69" s="27" t="n"/>
+      <c r="BX69" s="40" t="n"/>
+      <c r="BY69" s="39" t="n"/>
       <c r="BZ69" s="24" t="n"/>
       <c r="CA69" s="31" t="n"/>
     </row>
@@ -17739,7 +17770,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J70" s="25" t="n"/>
+      <c r="J70" s="38" t="n"/>
       <c r="K70" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17748,7 +17779,7 @@
       <c r="L70" s="26" t="n">
         <v>-160</v>
       </c>
-      <c r="M70" s="27" t="n">
+      <c r="M70" s="39" t="n">
         <v>1.625</v>
       </c>
       <c r="N70" s="28" t="n">
@@ -17780,11 +17811,11 @@
       <c r="V70" s="24" t="n"/>
       <c r="W70" s="26" t="n"/>
       <c r="X70" s="26" t="n"/>
-      <c r="Y70" s="25" t="n"/>
+      <c r="Y70" s="38" t="n"/>
       <c r="Z70" s="26" t="n"/>
       <c r="AA70" s="28" t="n"/>
       <c r="AB70" s="28" t="n"/>
-      <c r="AC70" s="30" t="n"/>
+      <c r="AC70" s="40" t="n"/>
       <c r="AD70" s="24" t="n"/>
       <c r="AE70" s="31" t="inlineStr">
         <is>
@@ -17915,11 +17946,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ70" s="25" t="n"/>
+      <c r="BJ70" s="38" t="n"/>
       <c r="BK70" s="26" t="n">
         <v>-160</v>
       </c>
-      <c r="BL70" s="27" t="n">
+      <c r="BL70" s="39" t="n">
         <v>1.625</v>
       </c>
       <c r="BM70" s="28" t="n">
@@ -17929,16 +17960,16 @@
         <v>0.61194</v>
       </c>
       <c r="BO70" s="28" t="n"/>
-      <c r="BP70" s="25" t="n"/>
-      <c r="BQ70" s="27" t="n"/>
+      <c r="BP70" s="38" t="n"/>
+      <c r="BQ70" s="39" t="n"/>
       <c r="BR70" s="28" t="n"/>
       <c r="BS70" s="28" t="n"/>
       <c r="BT70" s="28" t="n"/>
-      <c r="BU70" s="25" t="n"/>
+      <c r="BU70" s="38" t="n"/>
       <c r="BV70" s="29" t="n"/>
       <c r="BW70" s="24" t="n"/>
-      <c r="BX70" s="30" t="n"/>
-      <c r="BY70" s="27" t="n"/>
+      <c r="BX70" s="40" t="n"/>
+      <c r="BY70" s="39" t="n"/>
       <c r="BZ70" s="24" t="n"/>
       <c r="CA70" s="31" t="n"/>
     </row>
@@ -17988,7 +18019,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J71" s="25" t="n"/>
+      <c r="J71" s="38" t="n"/>
       <c r="K71" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17997,7 +18028,7 @@
       <c r="L71" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M71" s="27" t="n">
+      <c r="M71" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N71" s="28" t="n">
@@ -18029,11 +18060,11 @@
       <c r="V71" s="24" t="n"/>
       <c r="W71" s="26" t="n"/>
       <c r="X71" s="26" t="n"/>
-      <c r="Y71" s="25" t="n"/>
+      <c r="Y71" s="38" t="n"/>
       <c r="Z71" s="26" t="n"/>
       <c r="AA71" s="28" t="n"/>
       <c r="AB71" s="28" t="n"/>
-      <c r="AC71" s="30" t="n"/>
+      <c r="AC71" s="40" t="n"/>
       <c r="AD71" s="24" t="n"/>
       <c r="AE71" s="31" t="inlineStr">
         <is>
@@ -18164,11 +18195,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ71" s="25" t="n"/>
+      <c r="BJ71" s="38" t="n"/>
       <c r="BK71" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL71" s="27" t="n">
+      <c r="BL71" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM71" s="28" t="n">
@@ -18178,16 +18209,16 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO71" s="28" t="n"/>
-      <c r="BP71" s="25" t="n"/>
-      <c r="BQ71" s="27" t="n"/>
+      <c r="BP71" s="38" t="n"/>
+      <c r="BQ71" s="39" t="n"/>
       <c r="BR71" s="28" t="n"/>
       <c r="BS71" s="28" t="n"/>
       <c r="BT71" s="28" t="n"/>
-      <c r="BU71" s="25" t="n"/>
+      <c r="BU71" s="38" t="n"/>
       <c r="BV71" s="29" t="n"/>
       <c r="BW71" s="24" t="n"/>
-      <c r="BX71" s="30" t="n"/>
-      <c r="BY71" s="27" t="n"/>
+      <c r="BX71" s="40" t="n"/>
+      <c r="BY71" s="39" t="n"/>
       <c r="BZ71" s="24" t="n"/>
       <c r="CA71" s="31" t="n"/>
     </row>
@@ -18237,7 +18268,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J72" s="25" t="n"/>
+      <c r="J72" s="38" t="n"/>
       <c r="K72" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -18246,7 +18277,7 @@
       <c r="L72" s="26" t="n">
         <v>-115</v>
       </c>
-      <c r="M72" s="27" t="n">
+      <c r="M72" s="39" t="n">
         <v>1.869565</v>
       </c>
       <c r="N72" s="28" t="n">
@@ -18278,11 +18309,11 @@
       <c r="V72" s="24" t="n"/>
       <c r="W72" s="26" t="n"/>
       <c r="X72" s="26" t="n"/>
-      <c r="Y72" s="25" t="n"/>
+      <c r="Y72" s="38" t="n"/>
       <c r="Z72" s="26" t="n"/>
       <c r="AA72" s="28" t="n"/>
       <c r="AB72" s="28" t="n"/>
-      <c r="AC72" s="30" t="n"/>
+      <c r="AC72" s="40" t="n"/>
       <c r="AD72" s="24" t="n"/>
       <c r="AE72" s="31" t="inlineStr">
         <is>
@@ -18413,11 +18444,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ72" s="25" t="n"/>
+      <c r="BJ72" s="38" t="n"/>
       <c r="BK72" s="26" t="n">
         <v>-115</v>
       </c>
-      <c r="BL72" s="27" t="n">
+      <c r="BL72" s="39" t="n">
         <v>1.869565</v>
       </c>
       <c r="BM72" s="28" t="n">
@@ -18427,16 +18458,16 @@
         <v>0.532338</v>
       </c>
       <c r="BO72" s="28" t="n"/>
-      <c r="BP72" s="25" t="n"/>
-      <c r="BQ72" s="27" t="n"/>
+      <c r="BP72" s="38" t="n"/>
+      <c r="BQ72" s="39" t="n"/>
       <c r="BR72" s="28" t="n"/>
       <c r="BS72" s="28" t="n"/>
       <c r="BT72" s="28" t="n"/>
-      <c r="BU72" s="25" t="n"/>
+      <c r="BU72" s="38" t="n"/>
       <c r="BV72" s="29" t="n"/>
       <c r="BW72" s="24" t="n"/>
-      <c r="BX72" s="30" t="n"/>
-      <c r="BY72" s="27" t="n"/>
+      <c r="BX72" s="40" t="n"/>
+      <c r="BY72" s="39" t="n"/>
       <c r="BZ72" s="24" t="n"/>
       <c r="CA72" s="31" t="n"/>
     </row>
@@ -18486,7 +18517,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J73" s="25" t="n"/>
+      <c r="J73" s="38" t="n"/>
       <c r="K73" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -18495,7 +18526,7 @@
       <c r="L73" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="M73" s="27" t="n">
+      <c r="M73" s="39" t="n">
         <v>1.854701</v>
       </c>
       <c r="N73" s="28" t="n">
@@ -18527,11 +18558,11 @@
       <c r="V73" s="24" t="n"/>
       <c r="W73" s="26" t="n"/>
       <c r="X73" s="26" t="n"/>
-      <c r="Y73" s="25" t="n"/>
+      <c r="Y73" s="38" t="n"/>
       <c r="Z73" s="26" t="n"/>
       <c r="AA73" s="28" t="n"/>
       <c r="AB73" s="28" t="n"/>
-      <c r="AC73" s="30" t="n"/>
+      <c r="AC73" s="40" t="n"/>
       <c r="AD73" s="24" t="n"/>
       <c r="AE73" s="31" t="inlineStr">
         <is>
@@ -18662,11 +18693,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ73" s="25" t="n"/>
+      <c r="BJ73" s="38" t="n"/>
       <c r="BK73" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="BL73" s="27" t="n">
+      <c r="BL73" s="39" t="n">
         <v>1.854701</v>
       </c>
       <c r="BM73" s="28" t="n">
@@ -18676,16 +18707,16 @@
         <v>0.537313</v>
       </c>
       <c r="BO73" s="28" t="n"/>
-      <c r="BP73" s="25" t="n"/>
-      <c r="BQ73" s="27" t="n"/>
+      <c r="BP73" s="38" t="n"/>
+      <c r="BQ73" s="39" t="n"/>
       <c r="BR73" s="28" t="n"/>
       <c r="BS73" s="28" t="n"/>
       <c r="BT73" s="28" t="n"/>
-      <c r="BU73" s="25" t="n"/>
+      <c r="BU73" s="38" t="n"/>
       <c r="BV73" s="29" t="n"/>
       <c r="BW73" s="24" t="n"/>
-      <c r="BX73" s="30" t="n"/>
-      <c r="BY73" s="27" t="n"/>
+      <c r="BX73" s="40" t="n"/>
+      <c r="BY73" s="39" t="n"/>
       <c r="BZ73" s="24" t="n"/>
       <c r="CA73" s="31" t="n"/>
     </row>
@@ -18735,7 +18766,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J74" s="25" t="n"/>
+      <c r="J74" s="38" t="n"/>
       <c r="K74" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -18744,7 +18775,7 @@
       <c r="L74" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="M74" s="27" t="n">
+      <c r="M74" s="39" t="n">
         <v>1.694444</v>
       </c>
       <c r="N74" s="28" t="n">
@@ -18776,11 +18807,11 @@
       <c r="V74" s="24" t="n"/>
       <c r="W74" s="26" t="n"/>
       <c r="X74" s="26" t="n"/>
-      <c r="Y74" s="25" t="n"/>
+      <c r="Y74" s="38" t="n"/>
       <c r="Z74" s="26" t="n"/>
       <c r="AA74" s="28" t="n"/>
       <c r="AB74" s="28" t="n"/>
-      <c r="AC74" s="30" t="n"/>
+      <c r="AC74" s="40" t="n"/>
       <c r="AD74" s="24" t="n"/>
       <c r="AE74" s="31" t="inlineStr">
         <is>
@@ -18911,11 +18942,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ74" s="25" t="n"/>
+      <c r="BJ74" s="38" t="n"/>
       <c r="BK74" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="BL74" s="27" t="n">
+      <c r="BL74" s="39" t="n">
         <v>1.694444</v>
       </c>
       <c r="BM74" s="28" t="n">
@@ -18925,16 +18956,16 @@
         <v>0.5870649999999999</v>
       </c>
       <c r="BO74" s="28" t="n"/>
-      <c r="BP74" s="25" t="n"/>
-      <c r="BQ74" s="27" t="n"/>
+      <c r="BP74" s="38" t="n"/>
+      <c r="BQ74" s="39" t="n"/>
       <c r="BR74" s="28" t="n"/>
       <c r="BS74" s="28" t="n"/>
       <c r="BT74" s="28" t="n"/>
-      <c r="BU74" s="25" t="n"/>
+      <c r="BU74" s="38" t="n"/>
       <c r="BV74" s="29" t="n"/>
       <c r="BW74" s="24" t="n"/>
-      <c r="BX74" s="30" t="n"/>
-      <c r="BY74" s="27" t="n"/>
+      <c r="BX74" s="40" t="n"/>
+      <c r="BY74" s="39" t="n"/>
       <c r="BZ74" s="24" t="n"/>
       <c r="CA74" s="31" t="n"/>
     </row>
@@ -18984,7 +19015,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J75" s="25" t="n"/>
+      <c r="J75" s="38" t="n"/>
       <c r="K75" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -18993,7 +19024,7 @@
       <c r="L75" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M75" s="27" t="n">
+      <c r="M75" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="N75" s="28" t="n">
@@ -19025,11 +19056,11 @@
       <c r="V75" s="24" t="n"/>
       <c r="W75" s="26" t="n"/>
       <c r="X75" s="26" t="n"/>
-      <c r="Y75" s="25" t="n"/>
+      <c r="Y75" s="38" t="n"/>
       <c r="Z75" s="26" t="n"/>
       <c r="AA75" s="28" t="n"/>
       <c r="AB75" s="28" t="n"/>
-      <c r="AC75" s="30" t="n"/>
+      <c r="AC75" s="40" t="n"/>
       <c r="AD75" s="24" t="n"/>
       <c r="AE75" s="31" t="inlineStr">
         <is>
@@ -19160,11 +19191,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ75" s="25" t="n"/>
+      <c r="BJ75" s="38" t="n"/>
       <c r="BK75" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL75" s="27" t="n">
+      <c r="BL75" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM75" s="28" t="n">
@@ -19174,16 +19205,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO75" s="28" t="n"/>
-      <c r="BP75" s="25" t="n"/>
-      <c r="BQ75" s="27" t="n"/>
+      <c r="BP75" s="38" t="n"/>
+      <c r="BQ75" s="39" t="n"/>
       <c r="BR75" s="28" t="n"/>
       <c r="BS75" s="28" t="n"/>
       <c r="BT75" s="28" t="n"/>
-      <c r="BU75" s="25" t="n"/>
+      <c r="BU75" s="38" t="n"/>
       <c r="BV75" s="29" t="n"/>
       <c r="BW75" s="24" t="n"/>
-      <c r="BX75" s="30" t="n"/>
-      <c r="BY75" s="27" t="n"/>
+      <c r="BX75" s="40" t="n"/>
+      <c r="BY75" s="39" t="n"/>
       <c r="BZ75" s="24" t="n"/>
       <c r="CA75" s="31" t="n"/>
     </row>
@@ -19233,7 +19264,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J76" s="25" t="n"/>
+      <c r="J76" s="38" t="n"/>
       <c r="K76" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -19242,7 +19273,7 @@
       <c r="L76" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M76" s="27" t="n">
+      <c r="M76" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="N76" s="28" t="n">
@@ -19274,11 +19305,11 @@
       <c r="V76" s="24" t="n"/>
       <c r="W76" s="26" t="n"/>
       <c r="X76" s="26" t="n"/>
-      <c r="Y76" s="25" t="n"/>
+      <c r="Y76" s="38" t="n"/>
       <c r="Z76" s="26" t="n"/>
       <c r="AA76" s="28" t="n"/>
       <c r="AB76" s="28" t="n"/>
-      <c r="AC76" s="30" t="n"/>
+      <c r="AC76" s="40" t="n"/>
       <c r="AD76" s="24" t="n"/>
       <c r="AE76" s="31" t="inlineStr">
         <is>
@@ -19409,11 +19440,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ76" s="25" t="n"/>
+      <c r="BJ76" s="38" t="n"/>
       <c r="BK76" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL76" s="27" t="n">
+      <c r="BL76" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="BM76" s="28" t="n">
@@ -19423,16 +19454,16 @@
         <v>0.492537</v>
       </c>
       <c r="BO76" s="28" t="n"/>
-      <c r="BP76" s="25" t="n"/>
-      <c r="BQ76" s="27" t="n"/>
+      <c r="BP76" s="38" t="n"/>
+      <c r="BQ76" s="39" t="n"/>
       <c r="BR76" s="28" t="n"/>
       <c r="BS76" s="28" t="n"/>
       <c r="BT76" s="28" t="n"/>
-      <c r="BU76" s="25" t="n"/>
+      <c r="BU76" s="38" t="n"/>
       <c r="BV76" s="29" t="n"/>
       <c r="BW76" s="24" t="n"/>
-      <c r="BX76" s="30" t="n"/>
-      <c r="BY76" s="27" t="n"/>
+      <c r="BX76" s="40" t="n"/>
+      <c r="BY76" s="39" t="n"/>
       <c r="BZ76" s="24" t="n"/>
       <c r="CA76" s="31" t="n"/>
     </row>
@@ -19482,7 +19513,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J77" s="25" t="n"/>
+      <c r="J77" s="38" t="n"/>
       <c r="K77" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -19491,7 +19522,7 @@
       <c r="L77" s="26" t="n">
         <v>-488</v>
       </c>
-      <c r="M77" s="27" t="n">
+      <c r="M77" s="39" t="n">
         <v>1.204918</v>
       </c>
       <c r="N77" s="28" t="n">
@@ -19523,11 +19554,11 @@
       <c r="V77" s="24" t="n"/>
       <c r="W77" s="26" t="n"/>
       <c r="X77" s="26" t="n"/>
-      <c r="Y77" s="25" t="n"/>
+      <c r="Y77" s="38" t="n"/>
       <c r="Z77" s="26" t="n"/>
       <c r="AA77" s="28" t="n"/>
       <c r="AB77" s="28" t="n"/>
-      <c r="AC77" s="30" t="n"/>
+      <c r="AC77" s="40" t="n"/>
       <c r="AD77" s="24" t="n"/>
       <c r="AE77" s="31" t="inlineStr">
         <is>
@@ -19658,11 +19689,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ77" s="25" t="n"/>
+      <c r="BJ77" s="38" t="n"/>
       <c r="BK77" s="26" t="n">
         <v>-488</v>
       </c>
-      <c r="BL77" s="27" t="n">
+      <c r="BL77" s="39" t="n">
         <v>1.204918</v>
       </c>
       <c r="BM77" s="28" t="n">
@@ -19672,16 +19703,16 @@
         <v>0.821782</v>
       </c>
       <c r="BO77" s="28" t="n"/>
-      <c r="BP77" s="25" t="n"/>
-      <c r="BQ77" s="27" t="n"/>
+      <c r="BP77" s="38" t="n"/>
+      <c r="BQ77" s="39" t="n"/>
       <c r="BR77" s="28" t="n"/>
       <c r="BS77" s="28" t="n"/>
       <c r="BT77" s="28" t="n"/>
-      <c r="BU77" s="25" t="n"/>
+      <c r="BU77" s="38" t="n"/>
       <c r="BV77" s="29" t="n"/>
       <c r="BW77" s="24" t="n"/>
-      <c r="BX77" s="30" t="n"/>
-      <c r="BY77" s="27" t="n"/>
+      <c r="BX77" s="40" t="n"/>
+      <c r="BY77" s="39" t="n"/>
       <c r="BZ77" s="24" t="n"/>
       <c r="CA77" s="31" t="n"/>
     </row>
@@ -19731,7 +19762,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J78" s="25" t="n"/>
+      <c r="J78" s="38" t="n"/>
       <c r="K78" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -19740,7 +19771,7 @@
       <c r="L78" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="M78" s="27" t="n">
+      <c r="M78" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="N78" s="28" t="n">
@@ -19772,11 +19803,11 @@
       <c r="V78" s="24" t="n"/>
       <c r="W78" s="26" t="n"/>
       <c r="X78" s="26" t="n"/>
-      <c r="Y78" s="25" t="n"/>
+      <c r="Y78" s="38" t="n"/>
       <c r="Z78" s="26" t="n"/>
       <c r="AA78" s="28" t="n"/>
       <c r="AB78" s="28" t="n"/>
-      <c r="AC78" s="30" t="n"/>
+      <c r="AC78" s="40" t="n"/>
       <c r="AD78" s="24" t="n"/>
       <c r="AE78" s="31" t="inlineStr">
         <is>
@@ -19907,11 +19938,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ78" s="25" t="n"/>
+      <c r="BJ78" s="38" t="n"/>
       <c r="BK78" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="BL78" s="27" t="n">
+      <c r="BL78" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="BM78" s="28" t="n">
@@ -19921,16 +19952,16 @@
         <v>0.39604</v>
       </c>
       <c r="BO78" s="28" t="n"/>
-      <c r="BP78" s="25" t="n"/>
-      <c r="BQ78" s="27" t="n"/>
+      <c r="BP78" s="38" t="n"/>
+      <c r="BQ78" s="39" t="n"/>
       <c r="BR78" s="28" t="n"/>
       <c r="BS78" s="28" t="n"/>
       <c r="BT78" s="28" t="n"/>
-      <c r="BU78" s="25" t="n"/>
+      <c r="BU78" s="38" t="n"/>
       <c r="BV78" s="29" t="n"/>
       <c r="BW78" s="24" t="n"/>
-      <c r="BX78" s="30" t="n"/>
-      <c r="BY78" s="27" t="n"/>
+      <c r="BX78" s="40" t="n"/>
+      <c r="BY78" s="39" t="n"/>
       <c r="BZ78" s="24" t="n"/>
       <c r="CA78" s="31" t="n"/>
     </row>
@@ -19980,7 +20011,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J79" s="25" t="n"/>
+      <c r="J79" s="38" t="n"/>
       <c r="K79" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -19989,7 +20020,7 @@
       <c r="L79" s="26" t="n">
         <v>-317</v>
       </c>
-      <c r="M79" s="27" t="n">
+      <c r="M79" s="39" t="n">
         <v>1.315457</v>
       </c>
       <c r="N79" s="28" t="n">
@@ -20021,11 +20052,11 @@
       <c r="V79" s="24" t="n"/>
       <c r="W79" s="26" t="n"/>
       <c r="X79" s="26" t="n"/>
-      <c r="Y79" s="25" t="n"/>
+      <c r="Y79" s="38" t="n"/>
       <c r="Z79" s="26" t="n"/>
       <c r="AA79" s="28" t="n"/>
       <c r="AB79" s="28" t="n"/>
-      <c r="AC79" s="30" t="n"/>
+      <c r="AC79" s="40" t="n"/>
       <c r="AD79" s="24" t="n"/>
       <c r="AE79" s="31" t="inlineStr">
         <is>
@@ -20156,11 +20187,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ79" s="25" t="n"/>
+      <c r="BJ79" s="38" t="n"/>
       <c r="BK79" s="26" t="n">
         <v>-317</v>
       </c>
-      <c r="BL79" s="27" t="n">
+      <c r="BL79" s="39" t="n">
         <v>1.315457</v>
       </c>
       <c r="BM79" s="28" t="n">
@@ -20170,16 +20201,16 @@
         <v>0.752475</v>
       </c>
       <c r="BO79" s="28" t="n"/>
-      <c r="BP79" s="25" t="n"/>
-      <c r="BQ79" s="27" t="n"/>
+      <c r="BP79" s="38" t="n"/>
+      <c r="BQ79" s="39" t="n"/>
       <c r="BR79" s="28" t="n"/>
       <c r="BS79" s="28" t="n"/>
       <c r="BT79" s="28" t="n"/>
-      <c r="BU79" s="25" t="n"/>
+      <c r="BU79" s="38" t="n"/>
       <c r="BV79" s="29" t="n"/>
       <c r="BW79" s="24" t="n"/>
-      <c r="BX79" s="30" t="n"/>
-      <c r="BY79" s="27" t="n"/>
+      <c r="BX79" s="40" t="n"/>
+      <c r="BY79" s="39" t="n"/>
       <c r="BZ79" s="24" t="n"/>
       <c r="CA79" s="31" t="n"/>
     </row>
@@ -20229,7 +20260,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J80" s="25" t="n"/>
+      <c r="J80" s="38" t="n"/>
       <c r="K80" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -20238,7 +20269,7 @@
       <c r="L80" s="26" t="n">
         <v>-456</v>
       </c>
-      <c r="M80" s="27" t="n">
+      <c r="M80" s="39" t="n">
         <v>1.219298</v>
       </c>
       <c r="N80" s="28" t="n">
@@ -20270,11 +20301,11 @@
       <c r="V80" s="24" t="n"/>
       <c r="W80" s="26" t="n"/>
       <c r="X80" s="26" t="n"/>
-      <c r="Y80" s="25" t="n"/>
+      <c r="Y80" s="38" t="n"/>
       <c r="Z80" s="26" t="n"/>
       <c r="AA80" s="28" t="n"/>
       <c r="AB80" s="28" t="n"/>
-      <c r="AC80" s="30" t="n"/>
+      <c r="AC80" s="40" t="n"/>
       <c r="AD80" s="24" t="n"/>
       <c r="AE80" s="31" t="inlineStr">
         <is>
@@ -20405,11 +20436,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ80" s="25" t="n"/>
+      <c r="BJ80" s="38" t="n"/>
       <c r="BK80" s="26" t="n">
         <v>-456</v>
       </c>
-      <c r="BL80" s="27" t="n">
+      <c r="BL80" s="39" t="n">
         <v>1.219298</v>
       </c>
       <c r="BM80" s="28" t="n">
@@ -20419,28 +20450,28 @@
         <v>0.811881</v>
       </c>
       <c r="BO80" s="28" t="n"/>
-      <c r="BP80" s="25" t="n"/>
-      <c r="BQ80" s="27" t="n"/>
+      <c r="BP80" s="38" t="n"/>
+      <c r="BQ80" s="39" t="n"/>
       <c r="BR80" s="28" t="n"/>
       <c r="BS80" s="28" t="n"/>
       <c r="BT80" s="28" t="n"/>
-      <c r="BU80" s="25" t="n"/>
+      <c r="BU80" s="38" t="n"/>
       <c r="BV80" s="29" t="n"/>
       <c r="BW80" s="24" t="n"/>
-      <c r="BX80" s="30" t="n"/>
-      <c r="BY80" s="27" t="n"/>
+      <c r="BX80" s="40" t="n"/>
+      <c r="BY80" s="39" t="n"/>
       <c r="BZ80" s="24" t="n"/>
       <c r="CA80" s="31" t="n"/>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>5b6cb66aed1b43a7</t>
+          <t>8f572bd4fec54325</t>
         </is>
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:04.119469Z</t>
+          <t>2026-07-20T16:32:49.855665Z</t>
         </is>
       </c>
       <c r="C81" s="24" t="inlineStr">
@@ -20478,7 +20509,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J81" s="25" t="n"/>
+      <c r="J81" s="38" t="n"/>
       <c r="K81" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -20487,24 +20518,24 @@
       <c r="L81" s="26" t="n">
         <v>144</v>
       </c>
-      <c r="M81" s="27" t="n">
+      <c r="M81" s="39" t="n">
         <v>2.44</v>
       </c>
       <c r="N81" s="28" t="n">
         <v>0.409836</v>
       </c>
       <c r="O81" s="28" t="n">
-        <v>0.555003</v>
+        <v>0.527501</v>
       </c>
       <c r="P81" s="28" t="n"/>
       <c r="Q81" s="28" t="n">
-        <v>0.145003</v>
+        <v>0.117501</v>
       </c>
       <c r="R81" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S81" s="29" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="T81" s="24" t="inlineStr">
         <is>
@@ -20519,11 +20550,11 @@
       <c r="V81" s="24" t="n"/>
       <c r="W81" s="26" t="n"/>
       <c r="X81" s="26" t="n"/>
-      <c r="Y81" s="25" t="n"/>
+      <c r="Y81" s="38" t="n"/>
       <c r="Z81" s="26" t="n"/>
       <c r="AA81" s="28" t="n"/>
       <c r="AB81" s="28" t="n"/>
-      <c r="AC81" s="30" t="n"/>
+      <c r="AC81" s="40" t="n"/>
       <c r="AD81" s="24" t="n"/>
       <c r="AE81" s="31" t="inlineStr">
         <is>
@@ -20646,7 +20677,7 @@
       </c>
       <c r="BH81" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:04.119469Z</t>
+          <t>2026-07-20T16:32:49.855665Z</t>
         </is>
       </c>
       <c r="BI81" s="24" t="inlineStr">
@@ -20654,11 +20685,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ81" s="25" t="n"/>
+      <c r="BJ81" s="38" t="n"/>
       <c r="BK81" s="26" t="n">
         <v>144</v>
       </c>
-      <c r="BL81" s="27" t="n">
+      <c r="BL81" s="39" t="n">
         <v>2.44</v>
       </c>
       <c r="BM81" s="28" t="n">
@@ -20666,28 +20697,28 @@
       </c>
       <c r="BN81" s="28" t="n"/>
       <c r="BO81" s="28" t="n"/>
-      <c r="BP81" s="25" t="n"/>
-      <c r="BQ81" s="27" t="n"/>
+      <c r="BP81" s="38" t="n"/>
+      <c r="BQ81" s="39" t="n"/>
       <c r="BR81" s="28" t="n"/>
       <c r="BS81" s="28" t="n"/>
       <c r="BT81" s="28" t="n"/>
-      <c r="BU81" s="25" t="n"/>
+      <c r="BU81" s="38" t="n"/>
       <c r="BV81" s="29" t="n"/>
       <c r="BW81" s="24" t="n"/>
-      <c r="BX81" s="30" t="n"/>
-      <c r="BY81" s="27" t="n"/>
+      <c r="BX81" s="40" t="n"/>
+      <c r="BY81" s="39" t="n"/>
       <c r="BZ81" s="24" t="n"/>
       <c r="CA81" s="31" t="n"/>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
         <is>
-          <t>6daddbd69a464322</t>
+          <t>04bc614189f44e85</t>
         </is>
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:04.354854Z</t>
+          <t>2026-07-20T16:32:50.077952Z</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
@@ -20725,7 +20756,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J82" s="25" t="n"/>
+      <c r="J82" s="38" t="n"/>
       <c r="K82" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -20734,24 +20765,24 @@
       <c r="L82" s="26" t="n">
         <v>186</v>
       </c>
-      <c r="M82" s="27" t="n">
+      <c r="M82" s="39" t="n">
         <v>2.86</v>
       </c>
       <c r="N82" s="28" t="n">
         <v>0.34965</v>
       </c>
       <c r="O82" s="28" t="n">
-        <v>0.567918</v>
+        <v>0.533959</v>
       </c>
       <c r="P82" s="28" t="n"/>
       <c r="Q82" s="28" t="n">
-        <v>0.217918</v>
+        <v>0.183959</v>
       </c>
       <c r="R82" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S82" s="29" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="T82" s="24" t="inlineStr">
         <is>
@@ -20766,11 +20797,11 @@
       <c r="V82" s="24" t="n"/>
       <c r="W82" s="26" t="n"/>
       <c r="X82" s="26" t="n"/>
-      <c r="Y82" s="25" t="n"/>
+      <c r="Y82" s="38" t="n"/>
       <c r="Z82" s="26" t="n"/>
       <c r="AA82" s="28" t="n"/>
       <c r="AB82" s="28" t="n"/>
-      <c r="AC82" s="30" t="n"/>
+      <c r="AC82" s="40" t="n"/>
       <c r="AD82" s="24" t="n"/>
       <c r="AE82" s="31" t="inlineStr">
         <is>
@@ -20893,7 +20924,7 @@
       </c>
       <c r="BH82" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:04.354854Z</t>
+          <t>2026-07-20T16:32:50.077952Z</t>
         </is>
       </c>
       <c r="BI82" s="24" t="inlineStr">
@@ -20901,11 +20932,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ82" s="25" t="n"/>
+      <c r="BJ82" s="38" t="n"/>
       <c r="BK82" s="26" t="n">
         <v>186</v>
       </c>
-      <c r="BL82" s="27" t="n">
+      <c r="BL82" s="39" t="n">
         <v>2.86</v>
       </c>
       <c r="BM82" s="28" t="n">
@@ -20913,38 +20944,38 @@
       </c>
       <c r="BN82" s="28" t="n"/>
       <c r="BO82" s="28" t="n"/>
-      <c r="BP82" s="25" t="n"/>
-      <c r="BQ82" s="27" t="n"/>
+      <c r="BP82" s="38" t="n"/>
+      <c r="BQ82" s="39" t="n"/>
       <c r="BR82" s="28" t="n"/>
       <c r="BS82" s="28" t="n"/>
       <c r="BT82" s="28" t="n"/>
-      <c r="BU82" s="25" t="n"/>
+      <c r="BU82" s="38" t="n"/>
       <c r="BV82" s="29" t="n"/>
       <c r="BW82" s="24" t="n"/>
-      <c r="BX82" s="30" t="n"/>
-      <c r="BY82" s="27" t="n"/>
+      <c r="BX82" s="40" t="n"/>
+      <c r="BY82" s="39" t="n"/>
       <c r="BZ82" s="24" t="n"/>
       <c r="CA82" s="31" t="n"/>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="24" t="inlineStr">
         <is>
-          <t>a90c13efd4db44fa</t>
+          <t>d4cef3f0c09a4253</t>
         </is>
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:04.555914Z</t>
+          <t>2026-07-20T16:32:50.272162Z</t>
         </is>
       </c>
       <c r="C83" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T22:00:00Z</t>
+          <t>2026-07-20T23:00:00Z</t>
         </is>
       </c>
       <c r="D83" s="24" t="inlineStr">
         <is>
-          <t>54693</t>
+          <t>54724</t>
         </is>
       </c>
       <c r="E83" s="24" t="inlineStr">
@@ -20954,12 +20985,12 @@
       </c>
       <c r="F83" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="G83" s="24" t="inlineStr">
         <is>
-          <t>RED Academy</t>
+          <t>RMD Gaming</t>
         </is>
       </c>
       <c r="H83" s="24" t="inlineStr">
@@ -20969,36 +21000,36 @@
       </c>
       <c r="I83" s="24" t="inlineStr">
         <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J83" s="25" t="n"/>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J83" s="38" t="n"/>
       <c r="K83" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L83" s="26" t="n">
-        <v>300</v>
-      </c>
-      <c r="M83" s="27" t="n">
-        <v>4</v>
+        <v>-144</v>
+      </c>
+      <c r="M83" s="39" t="n">
+        <v>1.694444</v>
       </c>
       <c r="N83" s="28" t="n">
-        <v>0.25</v>
+        <v>0.590164</v>
       </c>
       <c r="O83" s="28" t="n">
-        <v>0.674654</v>
+        <v>0.524075</v>
       </c>
       <c r="P83" s="28" t="n"/>
       <c r="Q83" s="28" t="n">
-        <v>0.424654</v>
+        <v>-0.065925</v>
       </c>
       <c r="R83" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S83" s="29" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="T83" s="24" t="inlineStr">
         <is>
@@ -21013,15 +21044,15 @@
       <c r="V83" s="24" t="n"/>
       <c r="W83" s="26" t="n"/>
       <c r="X83" s="26" t="n"/>
-      <c r="Y83" s="25" t="n"/>
+      <c r="Y83" s="38" t="n"/>
       <c r="Z83" s="26" t="n"/>
       <c r="AA83" s="28" t="n"/>
       <c r="AB83" s="28" t="n"/>
-      <c r="AC83" s="30" t="n"/>
+      <c r="AC83" s="40" t="n"/>
       <c r="AD83" s="24" t="n"/>
       <c r="AE83" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.2500 (aec-lol-reda-nerd-2026-07-20).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (aec-lol-tse-rmd-2026-07-20).</t>
         </is>
       </c>
       <c r="AF83" s="31" t="inlineStr">
@@ -21062,32 +21093,32 @@
       </c>
       <c r="AP83" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AQ83" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AR83" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AS83" s="24" t="inlineStr">
         <is>
-          <t>RED Academy</t>
+          <t>RMD Gaming</t>
         </is>
       </c>
       <c r="AT83" s="24" t="inlineStr">
         <is>
-          <t>RED Academy</t>
+          <t>RMD Gaming</t>
         </is>
       </c>
       <c r="AU83" s="24" t="inlineStr">
         <is>
-          <t>RED Academy</t>
+          <t>RMD Gaming</t>
         </is>
       </c>
       <c r="AV83" s="24" t="n"/>
@@ -21140,7 +21171,7 @@
       </c>
       <c r="BH83" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:04.555914Z</t>
+          <t>2026-07-20T16:32:50.272162Z</t>
         </is>
       </c>
       <c r="BI83" s="24" t="inlineStr">
@@ -21148,65 +21179,65 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ83" s="25" t="n"/>
+      <c r="BJ83" s="38" t="n"/>
       <c r="BK83" s="26" t="n">
-        <v>300</v>
-      </c>
-      <c r="BL83" s="27" t="n">
-        <v>4</v>
+        <v>-144</v>
+      </c>
+      <c r="BL83" s="39" t="n">
+        <v>1.694444</v>
       </c>
       <c r="BM83" s="28" t="n">
-        <v>0.25</v>
+        <v>0.590164</v>
       </c>
       <c r="BN83" s="28" t="n"/>
       <c r="BO83" s="28" t="n"/>
-      <c r="BP83" s="25" t="n"/>
-      <c r="BQ83" s="27" t="n"/>
+      <c r="BP83" s="38" t="n"/>
+      <c r="BQ83" s="39" t="n"/>
       <c r="BR83" s="28" t="n"/>
       <c r="BS83" s="28" t="n"/>
       <c r="BT83" s="28" t="n"/>
-      <c r="BU83" s="25" t="n"/>
+      <c r="BU83" s="38" t="n"/>
       <c r="BV83" s="29" t="n"/>
       <c r="BW83" s="24" t="n"/>
-      <c r="BX83" s="30" t="n"/>
-      <c r="BY83" s="27" t="n"/>
+      <c r="BX83" s="40" t="n"/>
+      <c r="BY83" s="39" t="n"/>
       <c r="BZ83" s="24" t="n"/>
       <c r="CA83" s="31" t="n"/>
     </row>
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="24" t="inlineStr">
         <is>
-          <t>3a2bf877040d4609</t>
+          <t>345e121461114afb</t>
         </is>
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:04.750645Z</t>
+          <t>2026-07-20T16:32:57.353876Z</t>
         </is>
       </c>
       <c r="C84" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T23:00:00Z</t>
+          <t>2026-07-20T17:00:00Z</t>
         </is>
       </c>
       <c r="D84" s="24" t="inlineStr">
         <is>
-          <t>54724</t>
+          <t>56113</t>
         </is>
       </c>
       <c r="E84" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F84" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="G84" s="24" t="inlineStr">
         <is>
-          <t>RMD Gaming</t>
+          <t>Endless Journey</t>
         </is>
       </c>
       <c r="H84" s="24" t="inlineStr">
@@ -21219,37 +21250,37 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J84" s="25" t="n"/>
+      <c r="J84" s="38" t="n"/>
       <c r="K84" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L84" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M84" s="27" t="n">
-        <v>1.694444</v>
+        <v>113</v>
+      </c>
+      <c r="M84" s="39" t="n">
+        <v>2.13</v>
       </c>
       <c r="N84" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.469484</v>
       </c>
       <c r="O84" s="28" t="n">
-        <v>0.54815</v>
+        <v>0.576217</v>
       </c>
       <c r="P84" s="28" t="n"/>
       <c r="Q84" s="28" t="n">
-        <v>-0.04185</v>
+        <v>0.106217</v>
       </c>
       <c r="R84" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S84" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T84" s="24" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>cs2-neutral-series-elo-v1</t>
         </is>
       </c>
       <c r="U84" s="24" t="inlineStr">
@@ -21260,15 +21291,15 @@
       <c r="V84" s="24" t="n"/>
       <c r="W84" s="26" t="n"/>
       <c r="X84" s="26" t="n"/>
-      <c r="Y84" s="25" t="n"/>
+      <c r="Y84" s="38" t="n"/>
       <c r="Z84" s="26" t="n"/>
       <c r="AA84" s="28" t="n"/>
       <c r="AB84" s="28" t="n"/>
-      <c r="AC84" s="30" t="n"/>
+      <c r="AC84" s="40" t="n"/>
       <c r="AD84" s="24" t="n"/>
       <c r="AE84" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (aec-lol-tse-rmd-2026-07-20).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (aec-cs2-ica-ej-2026-07-20).</t>
         </is>
       </c>
       <c r="AF84" s="31" t="inlineStr">
@@ -21309,32 +21340,32 @@
       </c>
       <c r="AP84" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AQ84" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AR84" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AS84" s="24" t="inlineStr">
         <is>
-          <t>RMD Gaming</t>
+          <t>Endless Journey</t>
         </is>
       </c>
       <c r="AT84" s="24" t="inlineStr">
         <is>
-          <t>RMD Gaming</t>
+          <t>Endless Journey</t>
         </is>
       </c>
       <c r="AU84" s="24" t="inlineStr">
         <is>
-          <t>RMD Gaming</t>
+          <t>Endless Journey</t>
         </is>
       </c>
       <c r="AV84" s="24" t="n"/>
@@ -21352,7 +21383,7 @@
       </c>
       <c r="BA84" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
         </is>
       </c>
       <c r="BB84" s="24" t="inlineStr">
@@ -21362,12 +21393,12 @@
       </c>
       <c r="BC84" s="24" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>cs2-neutral-series-elo-v1</t>
         </is>
       </c>
       <c r="BD84" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
         </is>
       </c>
       <c r="BE84" s="24" t="inlineStr">
@@ -21387,7 +21418,7 @@
       </c>
       <c r="BH84" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:04.750645Z</t>
+          <t>2026-07-20T16:32:57.353876Z</t>
         </is>
       </c>
       <c r="BI84" s="24" t="inlineStr">
@@ -21395,65 +21426,65 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ84" s="25" t="n"/>
+      <c r="BJ84" s="38" t="n"/>
       <c r="BK84" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL84" s="27" t="n">
-        <v>1.694444</v>
+        <v>113</v>
+      </c>
+      <c r="BL84" s="39" t="n">
+        <v>2.13</v>
       </c>
       <c r="BM84" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.469484</v>
       </c>
       <c r="BN84" s="28" t="n"/>
       <c r="BO84" s="28" t="n"/>
-      <c r="BP84" s="25" t="n"/>
-      <c r="BQ84" s="27" t="n"/>
+      <c r="BP84" s="38" t="n"/>
+      <c r="BQ84" s="39" t="n"/>
       <c r="BR84" s="28" t="n"/>
       <c r="BS84" s="28" t="n"/>
       <c r="BT84" s="28" t="n"/>
-      <c r="BU84" s="25" t="n"/>
+      <c r="BU84" s="38" t="n"/>
       <c r="BV84" s="29" t="n"/>
       <c r="BW84" s="24" t="n"/>
-      <c r="BX84" s="30" t="n"/>
-      <c r="BY84" s="27" t="n"/>
+      <c r="BX84" s="40" t="n"/>
+      <c r="BY84" s="39" t="n"/>
       <c r="BZ84" s="24" t="n"/>
       <c r="CA84" s="31" t="n"/>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>f15dccef86584b5d</t>
+          <t>26f9b7dd6b974bf6</t>
         </is>
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:04.952889Z</t>
+          <t>2026-07-20T16:32:57.577880Z</t>
         </is>
       </c>
       <c r="C85" s="24" t="inlineStr">
         <is>
-          <t>2026-07-21T00:00:00Z</t>
+          <t>2026-07-20T21:00:00Z</t>
         </is>
       </c>
       <c r="D85" s="24" t="inlineStr">
         <is>
-          <t>54745</t>
+          <t>54669</t>
         </is>
       </c>
       <c r="E85" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F85" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>QUINTESSÊNCIA</t>
         </is>
       </c>
       <c r="G85" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>MIBR Academy</t>
         </is>
       </c>
       <c r="H85" s="24" t="inlineStr">
@@ -21463,40 +21494,40 @@
       </c>
       <c r="I85" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J85" s="25" t="n"/>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J85" s="38" t="n"/>
       <c r="K85" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L85" s="26" t="n">
-        <v>245</v>
-      </c>
-      <c r="M85" s="27" t="n">
-        <v>3.45</v>
+        <v>-223</v>
+      </c>
+      <c r="M85" s="39" t="n">
+        <v>1.44843</v>
       </c>
       <c r="N85" s="28" t="n">
-        <v>0.289855</v>
+        <v>0.690402</v>
       </c>
       <c r="O85" s="28" t="n">
-        <v>0.586418</v>
+        <v>0.580016</v>
       </c>
       <c r="P85" s="28" t="n"/>
       <c r="Q85" s="28" t="n">
-        <v>0.296418</v>
+        <v>-0.109984</v>
       </c>
       <c r="R85" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S85" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T85" s="24" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>cs2-neutral-series-elo-v1</t>
         </is>
       </c>
       <c r="U85" s="24" t="inlineStr">
@@ -21507,15 +21538,15 @@
       <c r="V85" s="24" t="n"/>
       <c r="W85" s="26" t="n"/>
       <c r="X85" s="26" t="n"/>
-      <c r="Y85" s="25" t="n"/>
+      <c r="Y85" s="38" t="n"/>
       <c r="Z85" s="26" t="n"/>
       <c r="AA85" s="28" t="n"/>
       <c r="AB85" s="28" t="n"/>
-      <c r="AC85" s="30" t="n"/>
+      <c r="AC85" s="40" t="n"/>
       <c r="AD85" s="24" t="n"/>
       <c r="AE85" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.2900 (aec-lol-est-pnga-2026-07-21).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (aec-cs2-mibra-quin-2026-07-20).</t>
         </is>
       </c>
       <c r="AF85" s="31" t="inlineStr">
@@ -21556,32 +21587,32 @@
       </c>
       <c r="AP85" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>QUINTESSÊNCIA</t>
         </is>
       </c>
       <c r="AQ85" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>QUINTESSÊNCIA</t>
         </is>
       </c>
       <c r="AR85" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>QUINTESSÊNCIA</t>
         </is>
       </c>
       <c r="AS85" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>MIBR Academy</t>
         </is>
       </c>
       <c r="AT85" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>MIBR Academy</t>
         </is>
       </c>
       <c r="AU85" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>MIBR Academy</t>
         </is>
       </c>
       <c r="AV85" s="24" t="n"/>
@@ -21599,7 +21630,7 @@
       </c>
       <c r="BA85" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
         </is>
       </c>
       <c r="BB85" s="24" t="inlineStr">
@@ -21609,12 +21640,12 @@
       </c>
       <c r="BC85" s="24" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>cs2-neutral-series-elo-v1</t>
         </is>
       </c>
       <c r="BD85" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
         </is>
       </c>
       <c r="BE85" s="24" t="inlineStr">
@@ -21634,7 +21665,7 @@
       </c>
       <c r="BH85" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:04.952889Z</t>
+          <t>2026-07-20T16:32:57.577880Z</t>
         </is>
       </c>
       <c r="BI85" s="24" t="inlineStr">
@@ -21642,50 +21673,50 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ85" s="25" t="n"/>
+      <c r="BJ85" s="38" t="n"/>
       <c r="BK85" s="26" t="n">
-        <v>245</v>
-      </c>
-      <c r="BL85" s="27" t="n">
-        <v>3.45</v>
+        <v>-223</v>
+      </c>
+      <c r="BL85" s="39" t="n">
+        <v>1.44843</v>
       </c>
       <c r="BM85" s="28" t="n">
-        <v>0.289855</v>
+        <v>0.690402</v>
       </c>
       <c r="BN85" s="28" t="n"/>
       <c r="BO85" s="28" t="n"/>
-      <c r="BP85" s="25" t="n"/>
-      <c r="BQ85" s="27" t="n"/>
+      <c r="BP85" s="38" t="n"/>
+      <c r="BQ85" s="39" t="n"/>
       <c r="BR85" s="28" t="n"/>
       <c r="BS85" s="28" t="n"/>
       <c r="BT85" s="28" t="n"/>
-      <c r="BU85" s="25" t="n"/>
+      <c r="BU85" s="38" t="n"/>
       <c r="BV85" s="29" t="n"/>
       <c r="BW85" s="24" t="n"/>
-      <c r="BX85" s="30" t="n"/>
-      <c r="BY85" s="27" t="n"/>
+      <c r="BX85" s="40" t="n"/>
+      <c r="BY85" s="39" t="n"/>
       <c r="BZ85" s="24" t="n"/>
       <c r="CA85" s="31" t="n"/>
     </row>
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="24" t="inlineStr">
         <is>
-          <t>26f5ce8f779549de</t>
+          <t>1a2e4cd0bc214362</t>
         </is>
       </c>
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:26:44.609761Z</t>
+          <t>2026-07-20T16:32:57.772821Z</t>
         </is>
       </c>
       <c r="C86" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T17:00:00Z</t>
+          <t>2026-07-20T21:00:00Z</t>
         </is>
       </c>
       <c r="D86" s="24" t="inlineStr">
         <is>
-          <t>56113</t>
+          <t>54672</t>
         </is>
       </c>
       <c r="E86" s="24" t="inlineStr">
@@ -21695,12 +21726,12 @@
       </c>
       <c r="F86" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>METANOIA WOLVES</t>
         </is>
       </c>
       <c r="G86" s="24" t="inlineStr">
         <is>
-          <t>Endless Journey</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="H86" s="24" t="inlineStr">
@@ -21710,30 +21741,30 @@
       </c>
       <c r="I86" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J86" s="25" t="n"/>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J86" s="38" t="n"/>
       <c r="K86" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L86" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="M86" s="27" t="n">
-        <v>1.925926</v>
+        <v>-144</v>
+      </c>
+      <c r="M86" s="39" t="n">
+        <v>1.694444</v>
       </c>
       <c r="N86" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.590164</v>
       </c>
       <c r="O86" s="28" t="n">
-        <v>0.652434</v>
+        <v>0.692542</v>
       </c>
       <c r="P86" s="28" t="n"/>
       <c r="Q86" s="28" t="n">
-        <v>0.132434</v>
+        <v>0.102542</v>
       </c>
       <c r="R86" s="26" t="n">
         <v>100</v>
@@ -21754,15 +21785,15 @@
       <c r="V86" s="24" t="n"/>
       <c r="W86" s="26" t="n"/>
       <c r="X86" s="26" t="n"/>
-      <c r="Y86" s="25" t="n"/>
+      <c r="Y86" s="38" t="n"/>
       <c r="Z86" s="26" t="n"/>
       <c r="AA86" s="28" t="n"/>
       <c r="AB86" s="28" t="n"/>
-      <c r="AC86" s="30" t="n"/>
+      <c r="AC86" s="40" t="n"/>
       <c r="AD86" s="24" t="n"/>
       <c r="AE86" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (aec-cs2-ica-ej-2026-07-20).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (aec-cs2-reda-mw-2026-07-20).</t>
         </is>
       </c>
       <c r="AF86" s="31" t="inlineStr">
@@ -21803,32 +21834,32 @@
       </c>
       <c r="AP86" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>METANOIA WOLVES</t>
         </is>
       </c>
       <c r="AQ86" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>METANOIA WOLVES</t>
         </is>
       </c>
       <c r="AR86" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>METANOIA WOLVES</t>
         </is>
       </c>
       <c r="AS86" s="24" t="inlineStr">
         <is>
-          <t>Endless Journey</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="AT86" s="24" t="inlineStr">
         <is>
-          <t>Endless Journey</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="AU86" s="24" t="inlineStr">
         <is>
-          <t>Endless Journey</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="AV86" s="24" t="n"/>
@@ -21881,7 +21912,7 @@
       </c>
       <c r="BH86" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:26:44.609761Z</t>
+          <t>2026-07-20T16:32:57.772821Z</t>
         </is>
       </c>
       <c r="BI86" s="24" t="inlineStr">
@@ -21889,1018 +21920,30 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ86" s="25" t="n"/>
+      <c r="BJ86" s="38" t="n"/>
       <c r="BK86" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="BL86" s="27" t="n">
-        <v>1.925926</v>
+        <v>-144</v>
+      </c>
+      <c r="BL86" s="39" t="n">
+        <v>1.694444</v>
       </c>
       <c r="BM86" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.590164</v>
       </c>
       <c r="BN86" s="28" t="n"/>
       <c r="BO86" s="28" t="n"/>
-      <c r="BP86" s="25" t="n"/>
-      <c r="BQ86" s="27" t="n"/>
+      <c r="BP86" s="38" t="n"/>
+      <c r="BQ86" s="39" t="n"/>
       <c r="BR86" s="28" t="n"/>
       <c r="BS86" s="28" t="n"/>
       <c r="BT86" s="28" t="n"/>
-      <c r="BU86" s="25" t="n"/>
+      <c r="BU86" s="38" t="n"/>
       <c r="BV86" s="29" t="n"/>
       <c r="BW86" s="24" t="n"/>
-      <c r="BX86" s="30" t="n"/>
-      <c r="BY86" s="27" t="n"/>
+      <c r="BX86" s="40" t="n"/>
+      <c r="BY86" s="39" t="n"/>
       <c r="BZ86" s="24" t="n"/>
       <c r="CA86" s="31" t="n"/>
-    </row>
-    <row r="87" ht="36" customHeight="1">
-      <c r="A87" s="24" t="inlineStr">
-        <is>
-          <t>56fd16b43e1349fc</t>
-        </is>
-      </c>
-      <c r="B87" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:44.830487Z</t>
-        </is>
-      </c>
-      <c r="C87" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T19:00:00Z</t>
-        </is>
-      </c>
-      <c r="D87" s="24" t="inlineStr">
-        <is>
-          <t>56757</t>
-        </is>
-      </c>
-      <c r="E87" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F87" s="24" t="inlineStr">
-        <is>
-          <t>MAGICOS</t>
-        </is>
-      </c>
-      <c r="G87" s="24" t="inlineStr">
-        <is>
-          <t>Blitzkrieg</t>
-        </is>
-      </c>
-      <c r="H87" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I87" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J87" s="25" t="n"/>
-      <c r="K87" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L87" s="26" t="n">
-        <v>669</v>
-      </c>
-      <c r="M87" s="27" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="N87" s="28" t="n">
-        <v>0.130039</v>
-      </c>
-      <c r="O87" s="28" t="n">
-        <v>0.598244</v>
-      </c>
-      <c r="P87" s="28" t="n"/>
-      <c r="Q87" s="28" t="n">
-        <v>0.468244</v>
-      </c>
-      <c r="R87" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S87" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T87" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="U87" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V87" s="24" t="n"/>
-      <c r="W87" s="26" t="n"/>
-      <c r="X87" s="26" t="n"/>
-      <c r="Y87" s="25" t="n"/>
-      <c r="Z87" s="26" t="n"/>
-      <c r="AA87" s="28" t="n"/>
-      <c r="AB87" s="28" t="n"/>
-      <c r="AC87" s="30" t="n"/>
-      <c r="AD87" s="24" t="n"/>
-      <c r="AE87" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.1300 (aec-cs2-mag-bk-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF87" s="31" t="inlineStr">
-        <is>
-          <t>Research baseline; zero-unit shadow until qualified.</t>
-        </is>
-      </c>
-      <c r="AG87" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH87" s="24" t="n"/>
-      <c r="AI87" s="31" t="n"/>
-      <c r="AJ87" s="31" t="n"/>
-      <c r="AK87" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL87" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM87" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN87" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO87" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP87" s="24" t="inlineStr">
-        <is>
-          <t>MAGICOS</t>
-        </is>
-      </c>
-      <c r="AQ87" s="24" t="inlineStr">
-        <is>
-          <t>MAGICOS</t>
-        </is>
-      </c>
-      <c r="AR87" s="24" t="inlineStr">
-        <is>
-          <t>MAGICOS</t>
-        </is>
-      </c>
-      <c r="AS87" s="24" t="inlineStr">
-        <is>
-          <t>Blitzkrieg</t>
-        </is>
-      </c>
-      <c r="AT87" s="24" t="inlineStr">
-        <is>
-          <t>Blitzkrieg</t>
-        </is>
-      </c>
-      <c r="AU87" s="24" t="inlineStr">
-        <is>
-          <t>Blitzkrieg</t>
-        </is>
-      </c>
-      <c r="AV87" s="24" t="n"/>
-      <c r="AW87" s="24" t="n"/>
-      <c r="AX87" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY87" s="24" t="n"/>
-      <c r="AZ87" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA87" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BB87" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC87" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD87" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BE87" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF87" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG87" s="24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="BH87" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:44.830487Z</t>
-        </is>
-      </c>
-      <c r="BI87" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ87" s="25" t="n"/>
-      <c r="BK87" s="26" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL87" s="27" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="BM87" s="28" t="n">
-        <v>0.130039</v>
-      </c>
-      <c r="BN87" s="28" t="n"/>
-      <c r="BO87" s="28" t="n"/>
-      <c r="BP87" s="25" t="n"/>
-      <c r="BQ87" s="27" t="n"/>
-      <c r="BR87" s="28" t="n"/>
-      <c r="BS87" s="28" t="n"/>
-      <c r="BT87" s="28" t="n"/>
-      <c r="BU87" s="25" t="n"/>
-      <c r="BV87" s="29" t="n"/>
-      <c r="BW87" s="24" t="n"/>
-      <c r="BX87" s="30" t="n"/>
-      <c r="BY87" s="27" t="n"/>
-      <c r="BZ87" s="24" t="n"/>
-      <c r="CA87" s="31" t="n"/>
-    </row>
-    <row r="88" ht="36" customHeight="1">
-      <c r="A88" s="24" t="inlineStr">
-        <is>
-          <t>016345fa98e04c4d</t>
-        </is>
-      </c>
-      <c r="B88" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:45.030222Z</t>
-        </is>
-      </c>
-      <c r="C88" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T19:00:00Z</t>
-        </is>
-      </c>
-      <c r="D88" s="24" t="inlineStr">
-        <is>
-          <t>54667</t>
-        </is>
-      </c>
-      <c r="E88" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F88" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="G88" s="24" t="inlineStr">
-        <is>
-          <t>HATERS</t>
-        </is>
-      </c>
-      <c r="H88" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I88" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J88" s="25" t="n"/>
-      <c r="K88" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L88" s="26" t="n">
-        <v>335</v>
-      </c>
-      <c r="M88" s="27" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="N88" s="28" t="n">
-        <v>0.229885</v>
-      </c>
-      <c r="O88" s="28" t="n">
-        <v>0.558097</v>
-      </c>
-      <c r="P88" s="28" t="n"/>
-      <c r="Q88" s="28" t="n">
-        <v>0.328097</v>
-      </c>
-      <c r="R88" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S88" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T88" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="U88" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V88" s="24" t="n"/>
-      <c r="W88" s="26" t="n"/>
-      <c r="X88" s="26" t="n"/>
-      <c r="Y88" s="25" t="n"/>
-      <c r="Z88" s="26" t="n"/>
-      <c r="AA88" s="28" t="n"/>
-      <c r="AB88" s="28" t="n"/>
-      <c r="AC88" s="30" t="n"/>
-      <c r="AD88" s="24" t="n"/>
-      <c r="AE88" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.2300 (aec-cs2-hat-paina-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF88" s="31" t="inlineStr">
-        <is>
-          <t>Research baseline; zero-unit shadow until qualified.</t>
-        </is>
-      </c>
-      <c r="AG88" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH88" s="24" t="n"/>
-      <c r="AI88" s="31" t="n"/>
-      <c r="AJ88" s="31" t="n"/>
-      <c r="AK88" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL88" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM88" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN88" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO88" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP88" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AQ88" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AR88" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AS88" s="24" t="inlineStr">
-        <is>
-          <t>HATERS</t>
-        </is>
-      </c>
-      <c r="AT88" s="24" t="inlineStr">
-        <is>
-          <t>HATERS</t>
-        </is>
-      </c>
-      <c r="AU88" s="24" t="inlineStr">
-        <is>
-          <t>HATERS</t>
-        </is>
-      </c>
-      <c r="AV88" s="24" t="n"/>
-      <c r="AW88" s="24" t="n"/>
-      <c r="AX88" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY88" s="24" t="n"/>
-      <c r="AZ88" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA88" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BB88" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC88" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD88" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BE88" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF88" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG88" s="24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="BH88" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:45.030222Z</t>
-        </is>
-      </c>
-      <c r="BI88" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ88" s="25" t="n"/>
-      <c r="BK88" s="26" t="n">
-        <v>335</v>
-      </c>
-      <c r="BL88" s="27" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="BM88" s="28" t="n">
-        <v>0.229885</v>
-      </c>
-      <c r="BN88" s="28" t="n"/>
-      <c r="BO88" s="28" t="n"/>
-      <c r="BP88" s="25" t="n"/>
-      <c r="BQ88" s="27" t="n"/>
-      <c r="BR88" s="28" t="n"/>
-      <c r="BS88" s="28" t="n"/>
-      <c r="BT88" s="28" t="n"/>
-      <c r="BU88" s="25" t="n"/>
-      <c r="BV88" s="29" t="n"/>
-      <c r="BW88" s="24" t="n"/>
-      <c r="BX88" s="30" t="n"/>
-      <c r="BY88" s="27" t="n"/>
-      <c r="BZ88" s="24" t="n"/>
-      <c r="CA88" s="31" t="n"/>
-    </row>
-    <row r="89" ht="36" customHeight="1">
-      <c r="A89" s="24" t="inlineStr">
-        <is>
-          <t>817f81c59de8400e</t>
-        </is>
-      </c>
-      <c r="B89" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:45.236193Z</t>
-        </is>
-      </c>
-      <c r="C89" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D89" s="24" t="inlineStr">
-        <is>
-          <t>54669</t>
-        </is>
-      </c>
-      <c r="E89" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F89" s="24" t="inlineStr">
-        <is>
-          <t>QUINTESSÊNCIA</t>
-        </is>
-      </c>
-      <c r="G89" s="24" t="inlineStr">
-        <is>
-          <t>MIBR Academy</t>
-        </is>
-      </c>
-      <c r="H89" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I89" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J89" s="25" t="n"/>
-      <c r="K89" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L89" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M89" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N89" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O89" s="28" t="n">
-        <v>0.660032</v>
-      </c>
-      <c r="P89" s="28" t="n"/>
-      <c r="Q89" s="28" t="n">
-        <v>-0.029968</v>
-      </c>
-      <c r="R89" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T89" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="U89" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V89" s="24" t="n"/>
-      <c r="W89" s="26" t="n"/>
-      <c r="X89" s="26" t="n"/>
-      <c r="Y89" s="25" t="n"/>
-      <c r="Z89" s="26" t="n"/>
-      <c r="AA89" s="28" t="n"/>
-      <c r="AB89" s="28" t="n"/>
-      <c r="AC89" s="30" t="n"/>
-      <c r="AD89" s="24" t="n"/>
-      <c r="AE89" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (aec-cs2-mibra-quin-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF89" s="31" t="inlineStr">
-        <is>
-          <t>Research baseline; zero-unit shadow until qualified.</t>
-        </is>
-      </c>
-      <c r="AG89" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH89" s="24" t="n"/>
-      <c r="AI89" s="31" t="n"/>
-      <c r="AJ89" s="31" t="n"/>
-      <c r="AK89" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL89" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM89" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN89" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO89" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP89" s="24" t="inlineStr">
-        <is>
-          <t>QUINTESSÊNCIA</t>
-        </is>
-      </c>
-      <c r="AQ89" s="24" t="inlineStr">
-        <is>
-          <t>QUINTESSÊNCIA</t>
-        </is>
-      </c>
-      <c r="AR89" s="24" t="inlineStr">
-        <is>
-          <t>QUINTESSÊNCIA</t>
-        </is>
-      </c>
-      <c r="AS89" s="24" t="inlineStr">
-        <is>
-          <t>MIBR Academy</t>
-        </is>
-      </c>
-      <c r="AT89" s="24" t="inlineStr">
-        <is>
-          <t>MIBR Academy</t>
-        </is>
-      </c>
-      <c r="AU89" s="24" t="inlineStr">
-        <is>
-          <t>MIBR Academy</t>
-        </is>
-      </c>
-      <c r="AV89" s="24" t="n"/>
-      <c r="AW89" s="24" t="n"/>
-      <c r="AX89" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY89" s="24" t="n"/>
-      <c r="AZ89" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA89" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BB89" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC89" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD89" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BE89" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF89" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG89" s="24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="BH89" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:45.236193Z</t>
-        </is>
-      </c>
-      <c r="BI89" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ89" s="25" t="n"/>
-      <c r="BK89" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL89" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM89" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN89" s="28" t="n"/>
-      <c r="BO89" s="28" t="n"/>
-      <c r="BP89" s="25" t="n"/>
-      <c r="BQ89" s="27" t="n"/>
-      <c r="BR89" s="28" t="n"/>
-      <c r="BS89" s="28" t="n"/>
-      <c r="BT89" s="28" t="n"/>
-      <c r="BU89" s="25" t="n"/>
-      <c r="BV89" s="29" t="n"/>
-      <c r="BW89" s="24" t="n"/>
-      <c r="BX89" s="30" t="n"/>
-      <c r="BY89" s="27" t="n"/>
-      <c r="BZ89" s="24" t="n"/>
-      <c r="CA89" s="31" t="n"/>
-    </row>
-    <row r="90" ht="36" customHeight="1">
-      <c r="A90" s="24" t="inlineStr">
-        <is>
-          <t>14ea1c3a676f493a</t>
-        </is>
-      </c>
-      <c r="B90" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:45.443663Z</t>
-        </is>
-      </c>
-      <c r="C90" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D90" s="24" t="inlineStr">
-        <is>
-          <t>54672</t>
-        </is>
-      </c>
-      <c r="E90" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F90" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="G90" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="H90" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I90" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J90" s="25" t="n"/>
-      <c r="K90" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L90" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M90" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N90" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O90" s="28" t="n">
-        <v>0.885084</v>
-      </c>
-      <c r="P90" s="28" t="n"/>
-      <c r="Q90" s="28" t="n">
-        <v>0.295084</v>
-      </c>
-      <c r="R90" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S90" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T90" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="U90" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V90" s="24" t="n"/>
-      <c r="W90" s="26" t="n"/>
-      <c r="X90" s="26" t="n"/>
-      <c r="Y90" s="25" t="n"/>
-      <c r="Z90" s="26" t="n"/>
-      <c r="AA90" s="28" t="n"/>
-      <c r="AB90" s="28" t="n"/>
-      <c r="AC90" s="30" t="n"/>
-      <c r="AD90" s="24" t="n"/>
-      <c r="AE90" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (aec-cs2-reda-mw-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF90" s="31" t="inlineStr">
-        <is>
-          <t>Research baseline; zero-unit shadow until qualified.</t>
-        </is>
-      </c>
-      <c r="AG90" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH90" s="24" t="n"/>
-      <c r="AI90" s="31" t="n"/>
-      <c r="AJ90" s="31" t="n"/>
-      <c r="AK90" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL90" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM90" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN90" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO90" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP90" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="AQ90" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="AR90" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="AS90" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="AT90" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="AU90" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="AV90" s="24" t="n"/>
-      <c r="AW90" s="24" t="n"/>
-      <c r="AX90" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY90" s="24" t="n"/>
-      <c r="AZ90" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA90" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BB90" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC90" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD90" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BE90" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF90" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG90" s="24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="BH90" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:45.443663Z</t>
-        </is>
-      </c>
-      <c r="BI90" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ90" s="25" t="n"/>
-      <c r="BK90" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL90" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM90" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN90" s="28" t="n"/>
-      <c r="BO90" s="28" t="n"/>
-      <c r="BP90" s="25" t="n"/>
-      <c r="BQ90" s="27" t="n"/>
-      <c r="BR90" s="28" t="n"/>
-      <c r="BS90" s="28" t="n"/>
-      <c r="BT90" s="28" t="n"/>
-      <c r="BU90" s="25" t="n"/>
-      <c r="BV90" s="29" t="n"/>
-      <c r="BW90" s="24" t="n"/>
-      <c r="BX90" s="30" t="n"/>
-      <c r="BY90" s="27" t="n"/>
-      <c r="BZ90" s="24" t="n"/>
-      <c r="CA90" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0###"/>
-    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,38 +217,11 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -327,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA86" headerRowCount="1">
-  <autoFilter ref="A1:CA86"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA85" headerRowCount="1">
+  <autoFilter ref="A1:CA85"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -765,23 +738,22 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$86)</f>
+        <f>COUNTA('Picks'!$A$2:$A$85)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$86,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$85,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$86,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$85,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"win")+COUNTIFS('Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"win")+COUNTIFS('Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -806,23 +778,22 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$86,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$85,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$85,"&gt;0",'Picks'!$V$2:$V$85,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$85,"&gt;0",'Picks'!$V$2:$V$85,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="32">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"win")/(COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"win")+COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"loss")),0)</f>
+      <c r="E7" s="7">
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$85,"&gt;0",'Picks'!$V$2:$V$85,"win")/(COUNTIFS('Picks'!$BX$2:$BX$85,"&gt;0",'Picks'!$V$2:$V$85,"win")+COUNTIFS('Picks'!$BX$2:$BX$85,"&gt;0",'Picks'!$V$2:$V$85,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="32">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$86)/SUM('Picks'!$BX$2:$BX$86),0)</f>
+      <c r="G7" s="7">
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$85)/SUM('Picks'!$BX$2:$BX$85),0)</f>
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -846,24 +817,23 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="33">
-        <f>SUM('Picks'!$BY$2:$BY$86)</f>
+      <c r="A10" s="8">
+        <f>SUM('Picks'!$BY$2:$BY$85)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$86,"&lt;&gt;",'Picks'!$AB$2:$AB$86),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$85,"&lt;&gt;",'Picks'!$AB$2:$AB$85),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$86,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$86,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$85,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$85,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="33">
-        <f>SUMIFS('Picks'!$AC$2:$AC$86,'Picks'!$AM$2:$AM$86,"QUALIFIED_SHADOW_CALL")</f>
+      <c r="G10" s="8">
+        <f>SUMIFS('Picks'!$AC$2:$AC$85,'Picks'!$AM$2:$AM$85,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -915,27 +885,27 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$86,$A14,'Picks'!$U$2:$U$86,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A14,'Picks'!$U$2:$U$85,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$86,$A14,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A14,'Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$86,$A14,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A14,'Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="14">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$86,'Picks'!$H$2:$H$86,$A14)</f>
+      <c r="F14" s="15">
+        <f>SUMIFS('Picks'!$BY$2:$BY$85,'Picks'!$H$2:$H$85,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$86,'Picks'!$H$2:$H$86,$A14,'Picks'!$U$2:$U$86,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$85,'Picks'!$H$2:$H$85,$A14,'Picks'!$U$2:$U$85,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -946,27 +916,27 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$86,$A15,'Picks'!$U$2:$U$86,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A15,'Picks'!$U$2:$U$85,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$86,$A15,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A15,'Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$86,$A15,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A15,'Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="19">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="37">
-        <f>SUMIFS('Picks'!$BY$2:$BY$86,'Picks'!$H$2:$H$86,$A15)</f>
+      <c r="F15" s="20">
+        <f>SUMIFS('Picks'!$BY$2:$BY$85,'Picks'!$H$2:$H$85,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$86,'Picks'!$H$2:$H$86,$A15,'Picks'!$U$2:$U$86,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$85,'Picks'!$H$2:$H$85,$A15,'Picks'!$U$2:$U$85,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -977,31 +947,30 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$86,$A16,'Picks'!$U$2:$U$86,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A16,'Picks'!$U$2:$U$85,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$86,$A16,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A16,'Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$86,$A16,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$85,$A16,'Picks'!$U$2:$U$85,"settled",'Picks'!$V$2:$V$85,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="14">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$86,'Picks'!$H$2:$H$86,$A16)</f>
+      <c r="F16" s="15">
+        <f>SUMIFS('Picks'!$BY$2:$BY$85,'Picks'!$H$2:$H$85,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$86,'Picks'!$H$2:$H$86,$A16,'Picks'!$U$2:$U$86,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$85,'Picks'!$H$2:$H$85,$A16,'Picks'!$U$2:$U$85,"settled"),0)</f>
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
@@ -1027,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA86"/>
+  <dimension ref="A1:CA85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1554,7 +1523,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="38" t="n"/>
+      <c r="J2" s="25" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1563,7 +1532,7 @@
       <c r="L2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M2" s="39" t="n">
+      <c r="M2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1603,11 +1572,11 @@
       <c r="X2" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="Y2" s="38" t="n"/>
+      <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="40" t="n">
+      <c r="AC2" s="30" t="n">
         <v>1.755</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1744,11 +1713,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="38" t="n"/>
+      <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL2" s="39" t="n">
+      <c r="BL2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1758,18 +1727,18 @@
         <v>0.455446</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="38" t="n"/>
-      <c r="BQ2" s="39" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="38" t="n"/>
+      <c r="BU2" s="25" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="40" t="n">
+      <c r="BX2" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="39" t="n">
+      <c r="BY2" s="27" t="n">
         <v>1.17</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1829,7 +1798,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="38" t="n"/>
+      <c r="J3" s="25" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1838,7 +1807,7 @@
       <c r="L3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M3" s="39" t="n">
+      <c r="M3" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1878,11 +1847,11 @@
       <c r="X3" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y3" s="38" t="n"/>
+      <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="40" t="n">
+      <c r="AC3" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -2019,11 +1988,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="38" t="n"/>
+      <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL3" s="39" t="n">
+      <c r="BL3" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2033,18 +2002,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="38" t="n"/>
-      <c r="BQ3" s="39" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="38" t="n"/>
+      <c r="BU3" s="25" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="40" t="n">
+      <c r="BX3" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="39" t="n">
+      <c r="BY3" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2104,7 +2073,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="25" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2113,7 +2082,7 @@
       <c r="L4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M4" s="39" t="n">
+      <c r="M4" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2153,11 +2122,11 @@
       <c r="X4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="38" t="n"/>
+      <c r="Y4" s="25" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="40" t="n">
+      <c r="AC4" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2294,11 +2263,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="38" t="n"/>
+      <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL4" s="39" t="n">
+      <c r="BL4" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2308,18 +2277,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="38" t="n"/>
-      <c r="BQ4" s="39" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="38" t="n"/>
+      <c r="BU4" s="25" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="40" t="n">
+      <c r="BX4" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" s="39" t="n">
+      <c r="BY4" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
@@ -2379,7 +2348,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="25" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2388,7 +2357,7 @@
       <c r="L5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M5" s="39" t="n">
+      <c r="M5" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2428,11 +2397,11 @@
       <c r="X5" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y5" s="38" t="n"/>
+      <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="40" t="n">
+      <c r="AC5" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2569,11 +2538,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="38" t="n"/>
+      <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL5" s="39" t="n">
+      <c r="BL5" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2583,18 +2552,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="38" t="n"/>
-      <c r="BQ5" s="39" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="38" t="n"/>
+      <c r="BU5" s="25" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="40" t="n">
+      <c r="BX5" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" s="39" t="n">
+      <c r="BY5" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
@@ -2654,7 +2623,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="25" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2663,7 +2632,7 @@
       <c r="L6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M6" s="39" t="n">
+      <c r="M6" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2703,11 +2672,11 @@
       <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="38" t="n"/>
+      <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="40" t="n">
+      <c r="AC6" s="30" t="n">
         <v>1.2019</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2844,11 +2813,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="38" t="n"/>
+      <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL6" s="39" t="n">
+      <c r="BL6" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2858,18 +2827,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="38" t="n"/>
-      <c r="BQ6" s="39" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="38" t="n"/>
+      <c r="BU6" s="25" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="40" t="n">
+      <c r="BX6" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" s="39" t="n">
+      <c r="BY6" s="27" t="n">
         <v>0.961538</v>
       </c>
       <c r="BZ6" s="24" t="inlineStr">
@@ -2929,7 +2898,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="25" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2938,7 +2907,7 @@
       <c r="L7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M7" s="39" t="n">
+      <c r="M7" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2978,11 +2947,11 @@
       <c r="X7" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" s="38" t="n"/>
+      <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="40" t="n">
+      <c r="AC7" s="30" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3119,11 +3088,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="38" t="n"/>
+      <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL7" s="39" t="n">
+      <c r="BL7" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3133,18 +3102,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="38" t="n"/>
-      <c r="BQ7" s="39" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="38" t="n"/>
+      <c r="BU7" s="25" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="40" t="n">
+      <c r="BX7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" s="39" t="n">
+      <c r="BY7" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ7" s="24" t="inlineStr">
@@ -3204,7 +3173,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="25" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3213,7 +3182,7 @@
       <c r="L8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M8" s="39" t="n">
+      <c r="M8" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3253,11 +3222,11 @@
       <c r="X8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y8" s="38" t="n"/>
+      <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="40" t="n">
+      <c r="AC8" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3394,11 +3363,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="38" t="n"/>
+      <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL8" s="39" t="n">
+      <c r="BL8" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3408,18 +3377,18 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="38" t="n"/>
-      <c r="BQ8" s="39" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="38" t="n"/>
+      <c r="BU8" s="25" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="40" t="n">
+      <c r="BX8" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" s="39" t="n">
+      <c r="BY8" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ8" s="24" t="inlineStr">
@@ -3479,7 +3448,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="25" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3488,7 +3457,7 @@
       <c r="L9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M9" s="39" t="n">
+      <c r="M9" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3528,11 +3497,11 @@
       <c r="X9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="38" t="n"/>
+      <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="40" t="n">
+      <c r="AC9" s="30" t="n">
         <v>0.9804</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
@@ -3669,11 +3638,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="38" t="n"/>
+      <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL9" s="39" t="n">
+      <c r="BL9" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3683,18 +3652,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="38" t="n"/>
-      <c r="BQ9" s="39" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="38" t="n"/>
+      <c r="BU9" s="25" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="40" t="n">
+      <c r="BX9" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" s="39" t="n">
+      <c r="BY9" s="27" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ9" s="24" t="inlineStr">
@@ -3754,7 +3723,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J10" s="38" t="n"/>
+      <c r="J10" s="25" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3763,7 +3732,7 @@
       <c r="L10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M10" s="39" t="n">
+      <c r="M10" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3803,11 +3772,11 @@
       <c r="X10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y10" s="38" t="n"/>
+      <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="40" t="n">
+      <c r="AC10" s="30" t="n">
         <v>1.2681</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -3944,11 +3913,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="38" t="n"/>
+      <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL10" s="39" t="n">
+      <c r="BL10" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -3958,18 +3927,18 @@
         <v>0.577114</v>
       </c>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="38" t="n"/>
-      <c r="BQ10" s="39" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="38" t="n"/>
+      <c r="BU10" s="25" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="40" t="n">
+      <c r="BX10" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" s="39" t="n">
+      <c r="BY10" s="27" t="n">
         <v>0.724638</v>
       </c>
       <c r="BZ10" s="24" t="inlineStr">
@@ -4029,7 +3998,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="25" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4038,7 +4007,7 @@
       <c r="L11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M11" s="39" t="n">
+      <c r="M11" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -4078,11 +4047,11 @@
       <c r="X11" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="38" t="n"/>
+      <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="40" t="n">
+      <c r="AC11" s="30" t="n">
         <v>1.275</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4219,11 +4188,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="38" t="n"/>
+      <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL11" s="39" t="n">
+      <c r="BL11" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4233,18 +4202,18 @@
         <v>0.492537</v>
       </c>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="38" t="n"/>
-      <c r="BQ11" s="39" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="38" t="n"/>
+      <c r="BU11" s="25" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="40" t="n">
+      <c r="BX11" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" s="39" t="n">
+      <c r="BY11" s="27" t="n">
         <v>1.02</v>
       </c>
       <c r="BZ11" s="24" t="inlineStr">
@@ -4304,7 +4273,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="25" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4313,7 +4282,7 @@
       <c r="L12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M12" s="39" t="n">
+      <c r="M12" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4353,11 +4322,11 @@
       <c r="X12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" s="38" t="n"/>
+      <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="40" t="n">
+      <c r="AC12" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
@@ -4494,11 +4463,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="38" t="n"/>
+      <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL12" s="39" t="n">
+      <c r="BL12" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4508,18 +4477,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="38" t="n"/>
-      <c r="BQ12" s="39" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="38" t="n"/>
+      <c r="BU12" s="25" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="40" t="n">
+      <c r="BX12" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" s="39" t="n">
+      <c r="BY12" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ12" s="24" t="inlineStr">
@@ -4579,7 +4548,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J13" s="38" t="n"/>
+      <c r="J13" s="25" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4588,7 +4557,7 @@
       <c r="L13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M13" s="39" t="n">
+      <c r="M13" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4628,11 +4597,11 @@
       <c r="X13" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" s="38" t="n"/>
+      <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="40" t="n">
+      <c r="AC13" s="30" t="n">
         <v>1.2255</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
@@ -4769,11 +4738,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="38" t="n"/>
+      <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL13" s="39" t="n">
+      <c r="BL13" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4783,18 +4752,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="38" t="n"/>
-      <c r="BQ13" s="39" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="38" t="n"/>
+      <c r="BU13" s="25" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="40" t="n">
+      <c r="BX13" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY13" s="39" t="n">
+      <c r="BY13" s="27" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ13" s="24" t="inlineStr">
@@ -4854,7 +4823,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J14" s="38" t="n"/>
+      <c r="J14" s="25" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4863,7 +4832,7 @@
       <c r="L14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M14" s="39" t="n">
+      <c r="M14" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -4903,11 +4872,11 @@
       <c r="X14" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="38" t="n"/>
+      <c r="Y14" s="25" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="40" t="n">
+      <c r="AC14" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -5044,11 +5013,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="38" t="n"/>
+      <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL14" s="39" t="n">
+      <c r="BL14" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -5058,18 +5027,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="38" t="n"/>
-      <c r="BQ14" s="39" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="38" t="n"/>
+      <c r="BU14" s="25" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="40" t="n">
+      <c r="BX14" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY14" s="39" t="n">
+      <c r="BY14" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ14" s="24" t="inlineStr">
@@ -5129,7 +5098,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="38" t="n"/>
+      <c r="J15" s="25" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5138,7 +5107,7 @@
       <c r="L15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M15" s="39" t="n">
+      <c r="M15" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -5178,11 +5147,11 @@
       <c r="X15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="38" t="n"/>
+      <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="40" t="n">
+      <c r="AC15" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
@@ -5319,11 +5288,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="38" t="n"/>
+      <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL15" s="39" t="n">
+      <c r="BL15" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5333,18 +5302,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="38" t="n"/>
-      <c r="BQ15" s="39" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="38" t="n"/>
+      <c r="BU15" s="25" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="40" t="n">
+      <c r="BX15" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY15" s="39" t="n">
+      <c r="BY15" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ15" s="24" t="inlineStr">
@@ -5404,7 +5373,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J16" s="38" t="n"/>
+      <c r="J16" s="25" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5413,7 +5382,7 @@
       <c r="L16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M16" s="39" t="n">
+      <c r="M16" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5453,11 +5422,11 @@
       <c r="X16" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" s="38" t="n"/>
+      <c r="Y16" s="25" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="40" t="n">
+      <c r="AC16" s="30" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
@@ -5594,11 +5563,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="38" t="n"/>
+      <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL16" s="39" t="n">
+      <c r="BL16" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5608,18 +5577,18 @@
         <v>0.522388</v>
       </c>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="38" t="n"/>
-      <c r="BQ16" s="39" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="38" t="n"/>
+      <c r="BU16" s="25" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="40" t="n">
+      <c r="BX16" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY16" s="39" t="n">
+      <c r="BY16" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ16" s="24" t="inlineStr">
@@ -5679,7 +5648,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="38" t="n"/>
+      <c r="J17" s="25" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5688,7 +5657,7 @@
       <c r="L17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M17" s="39" t="n">
+      <c r="M17" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5728,11 +5697,11 @@
       <c r="X17" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y17" s="38" t="n"/>
+      <c r="Y17" s="25" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="40" t="n">
+      <c r="AC17" s="30" t="n">
         <v>0.9258999999999999</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
@@ -5869,11 +5838,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ17" s="38" t="n"/>
+      <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL17" s="39" t="n">
+      <c r="BL17" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -5883,18 +5852,18 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="38" t="n"/>
-      <c r="BQ17" s="39" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="38" t="n"/>
+      <c r="BU17" s="25" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="40" t="n">
+      <c r="BX17" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY17" s="39" t="n">
+      <c r="BY17" s="27" t="n">
         <v>0.925926</v>
       </c>
       <c r="BZ17" s="24" t="inlineStr">
@@ -5954,7 +5923,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="38" t="n"/>
+      <c r="J18" s="25" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5963,7 +5932,7 @@
       <c r="L18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="M18" s="39" t="n">
+      <c r="M18" s="27" t="n">
         <v>2.11</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -6003,11 +5972,11 @@
       <c r="X18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y18" s="38" t="n"/>
+      <c r="Y18" s="25" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="40" t="n">
+      <c r="AC18" s="30" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
@@ -6144,11 +6113,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ18" s="38" t="n"/>
+      <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="BL18" s="39" t="n">
+      <c r="BL18" s="27" t="n">
         <v>2.11</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -6158,18 +6127,18 @@
         <v>0.472637</v>
       </c>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="38" t="n"/>
-      <c r="BQ18" s="39" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="38" t="n"/>
+      <c r="BU18" s="25" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="40" t="n">
+      <c r="BX18" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" s="39" t="n">
+      <c r="BY18" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ18" s="24" t="inlineStr">
@@ -6229,7 +6198,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="38" t="n"/>
+      <c r="J19" s="25" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6238,7 +6207,7 @@
       <c r="L19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M19" s="39" t="n">
+      <c r="M19" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -6278,11 +6247,11 @@
       <c r="X19" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y19" s="38" t="n"/>
+      <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="40" t="n">
+      <c r="AC19" s="30" t="n">
         <v>1.2</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
@@ -6419,11 +6388,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ19" s="38" t="n"/>
+      <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL19" s="39" t="n">
+      <c r="BL19" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -6433,18 +6402,18 @@
         <v>0.552239</v>
       </c>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="38" t="n"/>
-      <c r="BQ19" s="39" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="38" t="n"/>
+      <c r="BU19" s="25" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="40" t="n">
+      <c r="BX19" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY19" s="39" t="n">
+      <c r="BY19" s="27" t="n">
         <v>0.8</v>
       </c>
       <c r="BZ19" s="24" t="inlineStr">
@@ -6504,7 +6473,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J20" s="38" t="n"/>
+      <c r="J20" s="25" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6513,7 +6482,7 @@
       <c r="L20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="M20" s="39" t="n">
+      <c r="M20" s="27" t="n">
         <v>2.06</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6553,11 +6522,11 @@
       <c r="X20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y20" s="38" t="n"/>
+      <c r="Y20" s="25" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="40" t="n">
+      <c r="AC20" s="30" t="n">
         <v>0.795</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
@@ -6694,11 +6663,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ20" s="38" t="n"/>
+      <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="BL20" s="39" t="n">
+      <c r="BL20" s="27" t="n">
         <v>2.06</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -6708,18 +6677,18 @@
         <v>0.482587</v>
       </c>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="38" t="n"/>
-      <c r="BQ20" s="39" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="38" t="n"/>
+      <c r="BU20" s="25" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="40" t="n">
+      <c r="BX20" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" s="39" t="n">
+      <c r="BY20" s="27" t="n">
         <v>1.06</v>
       </c>
       <c r="BZ20" s="24" t="inlineStr">
@@ -6779,7 +6748,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J21" s="38" t="n"/>
+      <c r="J21" s="25" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6788,7 +6757,7 @@
       <c r="L21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M21" s="39" t="n">
+      <c r="M21" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
@@ -6830,11 +6799,11 @@
       <c r="X21" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y21" s="38" t="n"/>
+      <c r="Y21" s="25" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="40" t="n">
+      <c r="AC21" s="30" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
@@ -6893,11 +6862,11 @@
         </is>
       </c>
       <c r="BI21" s="24" t="n"/>
-      <c r="BJ21" s="38" t="n"/>
+      <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL21" s="39" t="n">
+      <c r="BL21" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
@@ -6907,16 +6876,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="38" t="n"/>
-      <c r="BQ21" s="39" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="38" t="n"/>
+      <c r="BU21" s="25" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="40" t="n"/>
-      <c r="BY21" s="39" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
     </row>
@@ -6966,7 +6935,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="38" t="n"/>
+      <c r="J22" s="25" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6975,7 +6944,7 @@
       <c r="L22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M22" s="39" t="n">
+      <c r="M22" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N22" s="28" t="n">
@@ -7017,11 +6986,11 @@
       <c r="X22" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y22" s="38" t="n"/>
+      <c r="Y22" s="25" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="40" t="n">
+      <c r="AC22" s="30" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
@@ -7080,11 +7049,11 @@
         </is>
       </c>
       <c r="BI22" s="24" t="n"/>
-      <c r="BJ22" s="38" t="n"/>
+      <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL22" s="39" t="n">
+      <c r="BL22" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM22" s="28" t="n">
@@ -7094,16 +7063,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="38" t="n"/>
-      <c r="BQ22" s="39" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="38" t="n"/>
+      <c r="BU22" s="25" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="40" t="n"/>
-      <c r="BY22" s="39" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
     </row>
@@ -7153,7 +7122,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J23" s="38" t="n"/>
+      <c r="J23" s="25" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7162,7 +7131,7 @@
       <c r="L23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M23" s="39" t="n">
+      <c r="M23" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="N23" s="28" t="n">
@@ -7204,11 +7173,11 @@
       <c r="X23" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y23" s="38" t="n"/>
+      <c r="Y23" s="25" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="40" t="n">
+      <c r="AC23" s="30" t="n">
         <v>1.2411</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
@@ -7267,11 +7236,11 @@
         </is>
       </c>
       <c r="BI23" s="24" t="n"/>
-      <c r="BJ23" s="38" t="n"/>
+      <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL23" s="39" t="n">
+      <c r="BL23" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM23" s="28" t="n">
@@ -7281,16 +7250,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="38" t="n"/>
-      <c r="BQ23" s="39" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="38" t="n"/>
+      <c r="BU23" s="25" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="40" t="n"/>
-      <c r="BY23" s="39" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
     </row>
@@ -7340,7 +7309,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="38" t="n"/>
+      <c r="J24" s="25" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7349,7 +7318,7 @@
       <c r="L24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M24" s="39" t="n">
+      <c r="M24" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N24" s="28" t="n">
@@ -7391,11 +7360,11 @@
       <c r="X24" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" s="38" t="n"/>
+      <c r="Y24" s="25" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="40" t="n">
+      <c r="AC24" s="30" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -7454,11 +7423,11 @@
         </is>
       </c>
       <c r="BI24" s="24" t="n"/>
-      <c r="BJ24" s="38" t="n"/>
+      <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL24" s="39" t="n">
+      <c r="BL24" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM24" s="28" t="n">
@@ -7468,16 +7437,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="38" t="n"/>
-      <c r="BQ24" s="39" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="38" t="n"/>
+      <c r="BU24" s="25" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="40" t="n"/>
-      <c r="BY24" s="39" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
     </row>
@@ -7527,7 +7496,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J25" s="38" t="n"/>
+      <c r="J25" s="25" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7536,7 +7505,7 @@
       <c r="L25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M25" s="39" t="n">
+      <c r="M25" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
@@ -7578,11 +7547,11 @@
       <c r="X25" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" s="38" t="n"/>
+      <c r="Y25" s="25" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="40" t="n">
+      <c r="AC25" s="30" t="n">
         <v>1.3</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
@@ -7641,11 +7610,11 @@
         </is>
       </c>
       <c r="BI25" s="24" t="n"/>
-      <c r="BJ25" s="38" t="n"/>
+      <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL25" s="39" t="n">
+      <c r="BL25" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
@@ -7655,16 +7624,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="38" t="n"/>
-      <c r="BQ25" s="39" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="38" t="n"/>
+      <c r="BU25" s="25" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="40" t="n"/>
-      <c r="BY25" s="39" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
     </row>
@@ -7714,7 +7683,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J26" s="38" t="n"/>
+      <c r="J26" s="25" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7723,7 +7692,7 @@
       <c r="L26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M26" s="39" t="n">
+      <c r="M26" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N26" s="28" t="n">
@@ -7765,11 +7734,11 @@
       <c r="X26" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26" s="38" t="n"/>
+      <c r="Y26" s="25" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="40" t="n">
+      <c r="AC26" s="30" t="n">
         <v>0.9615</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
@@ -7828,11 +7797,11 @@
         </is>
       </c>
       <c r="BI26" s="24" t="n"/>
-      <c r="BJ26" s="38" t="n"/>
+      <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL26" s="39" t="n">
+      <c r="BL26" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM26" s="28" t="n">
@@ -7842,16 +7811,16 @@
         <v>0.507463</v>
       </c>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="38" t="n"/>
-      <c r="BQ26" s="39" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="38" t="n"/>
+      <c r="BU26" s="25" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="40" t="n"/>
-      <c r="BY26" s="39" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
       <c r="BZ26" s="24" t="n"/>
       <c r="CA26" s="31" t="n"/>
     </row>
@@ -7901,7 +7870,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="38" t="n"/>
+      <c r="J27" s="25" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7910,7 +7879,7 @@
       <c r="L27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="M27" s="39" t="n">
+      <c r="M27" s="27" t="n">
         <v>2.2</v>
       </c>
       <c r="N27" s="28" t="n">
@@ -7952,11 +7921,11 @@
       <c r="X27" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" s="38" t="n"/>
+      <c r="Y27" s="25" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="40" t="n">
+      <c r="AC27" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
@@ -8015,11 +7984,11 @@
         </is>
       </c>
       <c r="BI27" s="24" t="n"/>
-      <c r="BJ27" s="38" t="n"/>
+      <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="BL27" s="39" t="n">
+      <c r="BL27" s="27" t="n">
         <v>2.2</v>
       </c>
       <c r="BM27" s="28" t="n">
@@ -8029,16 +7998,16 @@
         <v>0.452736</v>
       </c>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="38" t="n"/>
-      <c r="BQ27" s="39" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="38" t="n"/>
+      <c r="BU27" s="25" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="40" t="n"/>
-      <c r="BY27" s="39" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
       <c r="BZ27" s="24" t="n"/>
       <c r="CA27" s="31" t="n"/>
     </row>
@@ -8088,7 +8057,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="38" t="n"/>
+      <c r="J28" s="25" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -8097,7 +8066,7 @@
       <c r="L28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="39" t="n">
+      <c r="M28" s="27" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -8139,11 +8108,11 @@
       <c r="X28" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="38" t="n"/>
+      <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="40" t="n">
+      <c r="AC28" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
@@ -8202,11 +8171,11 @@
         </is>
       </c>
       <c r="BI28" s="24" t="n"/>
-      <c r="BJ28" s="38" t="n"/>
+      <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL28" s="39" t="n">
+      <c r="BL28" s="27" t="n">
         <v>2</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -8216,16 +8185,16 @@
         <v>0.497512</v>
       </c>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="38" t="n"/>
-      <c r="BQ28" s="39" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="38" t="n"/>
+      <c r="BU28" s="25" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="40" t="n"/>
-      <c r="BY28" s="39" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
       <c r="BZ28" s="24" t="n"/>
       <c r="CA28" s="31" t="n"/>
     </row>
@@ -8275,7 +8244,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J29" s="38" t="n"/>
+      <c r="J29" s="25" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8284,7 +8253,7 @@
       <c r="L29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M29" s="39" t="n">
+      <c r="M29" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -8324,11 +8293,11 @@
       <c r="X29" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y29" s="38" t="n"/>
+      <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="40" t="n">
+      <c r="AC29" s="30" t="n">
         <v>1.35</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
@@ -8465,11 +8434,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ29" s="38" t="n"/>
+      <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL29" s="39" t="n">
+      <c r="BL29" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -8479,18 +8448,18 @@
         <v>0.477612</v>
       </c>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="38" t="n"/>
-      <c r="BQ29" s="39" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="38" t="n"/>
+      <c r="BU29" s="25" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="40" t="n">
+      <c r="BX29" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY29" s="39" t="n">
+      <c r="BY29" s="27" t="n">
         <v>1.08</v>
       </c>
       <c r="BZ29" s="24" t="inlineStr">
@@ -8550,7 +8519,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J30" s="38" t="n"/>
+      <c r="J30" s="25" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8559,7 +8528,7 @@
       <c r="L30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M30" s="39" t="n">
+      <c r="M30" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -8599,11 +8568,11 @@
       <c r="X30" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y30" s="38" t="n"/>
+      <c r="Y30" s="25" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="40" t="n">
+      <c r="AC30" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
@@ -8740,11 +8709,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ30" s="38" t="n"/>
+      <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL30" s="39" t="n">
+      <c r="BL30" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -8754,18 +8723,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="38" t="n"/>
-      <c r="BQ30" s="39" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="38" t="n"/>
+      <c r="BU30" s="25" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="40" t="n">
+      <c r="BX30" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY30" s="39" t="n">
+      <c r="BY30" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ30" s="24" t="inlineStr">
@@ -8825,7 +8794,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="38" t="n"/>
+      <c r="J31" s="25" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8834,7 +8803,7 @@
       <c r="L31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="M31" s="39" t="n">
+      <c r="M31" s="27" t="n">
         <v>2.3</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -8874,11 +8843,11 @@
       <c r="X31" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y31" s="38" t="n"/>
+      <c r="Y31" s="25" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="40" t="n">
+      <c r="AC31" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
@@ -9015,11 +8984,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ31" s="38" t="n"/>
+      <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="BL31" s="39" t="n">
+      <c r="BL31" s="27" t="n">
         <v>2.3</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -9029,18 +8998,18 @@
         <v>0.432836</v>
       </c>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="38" t="n"/>
-      <c r="BQ31" s="39" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="38" t="n"/>
+      <c r="BU31" s="25" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="40" t="n">
+      <c r="BX31" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY31" s="39" t="n">
+      <c r="BY31" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ31" s="24" t="inlineStr">
@@ -9100,7 +9069,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J32" s="38" t="n"/>
+      <c r="J32" s="25" t="n"/>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9109,7 +9078,7 @@
       <c r="L32" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M32" s="39" t="n">
+      <c r="M32" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="N32" s="28" t="n">
@@ -9149,11 +9118,11 @@
       <c r="X32" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y32" s="38" t="n"/>
+      <c r="Y32" s="25" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="40" t="n">
+      <c r="AC32" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD32" s="24" t="inlineStr">
@@ -9290,11 +9259,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ32" s="38" t="n"/>
+      <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL32" s="39" t="n">
+      <c r="BL32" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="BM32" s="28" t="n">
@@ -9304,16 +9273,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="38" t="n"/>
-      <c r="BQ32" s="39" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
       <c r="BR32" s="28" t="n"/>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="38" t="n"/>
+      <c r="BU32" s="25" t="n"/>
       <c r="BV32" s="29" t="n"/>
       <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="40" t="n"/>
-      <c r="BY32" s="39" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
       <c r="BZ32" s="24" t="n"/>
       <c r="CA32" s="31" t="n"/>
     </row>
@@ -9363,7 +9332,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J33" s="38" t="n"/>
+      <c r="J33" s="25" t="n"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9372,7 +9341,7 @@
       <c r="L33" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M33" s="39" t="n">
+      <c r="M33" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="N33" s="28" t="n">
@@ -9412,11 +9381,11 @@
       <c r="X33" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y33" s="38" t="n"/>
+      <c r="Y33" s="25" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="40" t="n">
+      <c r="AC33" s="30" t="n">
         <v>-1.75</v>
       </c>
       <c r="AD33" s="24" t="inlineStr">
@@ -9553,11 +9522,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ33" s="38" t="n"/>
+      <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL33" s="39" t="n">
+      <c r="BL33" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="BM33" s="28" t="n">
@@ -9567,16 +9536,16 @@
         <v>0.457711</v>
       </c>
       <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="38" t="n"/>
-      <c r="BQ33" s="39" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
       <c r="BR33" s="28" t="n"/>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="38" t="n"/>
+      <c r="BU33" s="25" t="n"/>
       <c r="BV33" s="29" t="n"/>
       <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="40" t="n"/>
-      <c r="BY33" s="39" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
       <c r="BZ33" s="24" t="n"/>
       <c r="CA33" s="31" t="n"/>
     </row>
@@ -9626,7 +9595,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J34" s="38" t="n"/>
+      <c r="J34" s="25" t="n"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9635,7 +9604,7 @@
       <c r="L34" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="M34" s="39" t="n">
+      <c r="M34" s="27" t="n">
         <v>1.854701</v>
       </c>
       <c r="N34" s="28" t="n">
@@ -9675,11 +9644,11 @@
       <c r="X34" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y34" s="38" t="n"/>
+      <c r="Y34" s="25" t="n"/>
       <c r="Z34" s="26" t="n"/>
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="40" t="n">
+      <c r="AC34" s="30" t="n">
         <v>0.8547</v>
       </c>
       <c r="AD34" s="24" t="inlineStr">
@@ -9816,11 +9785,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ34" s="38" t="n"/>
+      <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="BL34" s="39" t="n">
+      <c r="BL34" s="27" t="n">
         <v>1.854701</v>
       </c>
       <c r="BM34" s="28" t="n">
@@ -9830,16 +9799,16 @@
         <v>0.537313</v>
       </c>
       <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="38" t="n"/>
-      <c r="BQ34" s="39" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
       <c r="BR34" s="28" t="n"/>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="38" t="n"/>
+      <c r="BU34" s="25" t="n"/>
       <c r="BV34" s="29" t="n"/>
       <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="40" t="n"/>
-      <c r="BY34" s="39" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
       <c r="BZ34" s="24" t="n"/>
       <c r="CA34" s="31" t="n"/>
     </row>
@@ -9889,7 +9858,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J35" s="38" t="n"/>
+      <c r="J35" s="25" t="n"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9898,7 +9867,7 @@
       <c r="L35" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M35" s="39" t="n">
+      <c r="M35" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="N35" s="28" t="n">
@@ -9938,11 +9907,11 @@
       <c r="X35" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y35" s="38" t="n"/>
+      <c r="Y35" s="25" t="n"/>
       <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="40" t="n">
+      <c r="AC35" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD35" s="24" t="inlineStr">
@@ -10079,11 +10048,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ35" s="38" t="n"/>
+      <c r="BJ35" s="25" t="n"/>
       <c r="BK35" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL35" s="39" t="n">
+      <c r="BL35" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="BM35" s="28" t="n">
@@ -10093,16 +10062,16 @@
         <v>0.457711</v>
       </c>
       <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="38" t="n"/>
-      <c r="BQ35" s="39" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
       <c r="BR35" s="28" t="n"/>
       <c r="BS35" s="28" t="n"/>
       <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="38" t="n"/>
+      <c r="BU35" s="25" t="n"/>
       <c r="BV35" s="29" t="n"/>
       <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="40" t="n"/>
-      <c r="BY35" s="39" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
       <c r="BZ35" s="24" t="n"/>
       <c r="CA35" s="31" t="n"/>
     </row>
@@ -10152,7 +10121,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J36" s="38" t="n"/>
+      <c r="J36" s="25" t="n"/>
       <c r="K36" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10161,7 +10130,7 @@
       <c r="L36" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M36" s="39" t="n">
+      <c r="M36" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N36" s="28" t="n">
@@ -10201,11 +10170,11 @@
       <c r="X36" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y36" s="38" t="n"/>
+      <c r="Y36" s="25" t="n"/>
       <c r="Z36" s="26" t="n"/>
       <c r="AA36" s="28" t="n"/>
       <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="40" t="n">
+      <c r="AC36" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD36" s="24" t="inlineStr">
@@ -10342,11 +10311,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ36" s="38" t="n"/>
+      <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL36" s="39" t="n">
+      <c r="BL36" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM36" s="28" t="n">
@@ -10356,16 +10325,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="38" t="n"/>
-      <c r="BQ36" s="39" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
       <c r="BR36" s="28" t="n"/>
       <c r="BS36" s="28" t="n"/>
       <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="38" t="n"/>
+      <c r="BU36" s="25" t="n"/>
       <c r="BV36" s="29" t="n"/>
       <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="40" t="n"/>
-      <c r="BY36" s="39" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
       <c r="BZ36" s="24" t="n"/>
       <c r="CA36" s="31" t="n"/>
     </row>
@@ -10415,7 +10384,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J37" s="38" t="n"/>
+      <c r="J37" s="25" t="n"/>
       <c r="K37" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10424,7 +10393,7 @@
       <c r="L37" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="M37" s="39" t="n">
+      <c r="M37" s="27" t="n">
         <v>1.819672</v>
       </c>
       <c r="N37" s="28" t="n">
@@ -10464,11 +10433,11 @@
       <c r="X37" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y37" s="38" t="n"/>
+      <c r="Y37" s="25" t="n"/>
       <c r="Z37" s="26" t="n"/>
       <c r="AA37" s="28" t="n"/>
       <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="40" t="n">
+      <c r="AC37" s="30" t="n">
         <v>1.4344</v>
       </c>
       <c r="AD37" s="24" t="inlineStr">
@@ -10605,11 +10574,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ37" s="38" t="n"/>
+      <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="BL37" s="39" t="n">
+      <c r="BL37" s="27" t="n">
         <v>1.819672</v>
       </c>
       <c r="BM37" s="28" t="n">
@@ -10619,16 +10588,16 @@
         <v>0.547264</v>
       </c>
       <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="38" t="n"/>
-      <c r="BQ37" s="39" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
       <c r="BR37" s="28" t="n"/>
       <c r="BS37" s="28" t="n"/>
       <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="38" t="n"/>
+      <c r="BU37" s="25" t="n"/>
       <c r="BV37" s="29" t="n"/>
       <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="40" t="n"/>
-      <c r="BY37" s="39" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
       <c r="BZ37" s="24" t="n"/>
       <c r="CA37" s="31" t="n"/>
     </row>
@@ -10678,7 +10647,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J38" s="38" t="n"/>
+      <c r="J38" s="25" t="n"/>
       <c r="K38" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10687,7 +10656,7 @@
       <c r="L38" s="26" t="n">
         <v>115</v>
       </c>
-      <c r="M38" s="39" t="n">
+      <c r="M38" s="27" t="n">
         <v>2.15</v>
       </c>
       <c r="N38" s="28" t="n">
@@ -10727,11 +10696,11 @@
       <c r="X38" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y38" s="38" t="n"/>
+      <c r="Y38" s="25" t="n"/>
       <c r="Z38" s="26" t="n"/>
       <c r="AA38" s="28" t="n"/>
       <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="40" t="n">
+      <c r="AC38" s="30" t="n">
         <v>0.8625</v>
       </c>
       <c r="AD38" s="24" t="inlineStr">
@@ -10868,11 +10837,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ38" s="38" t="n"/>
+      <c r="BJ38" s="25" t="n"/>
       <c r="BK38" s="26" t="n">
         <v>115</v>
       </c>
-      <c r="BL38" s="39" t="n">
+      <c r="BL38" s="27" t="n">
         <v>2.15</v>
       </c>
       <c r="BM38" s="28" t="n">
@@ -10882,16 +10851,16 @@
         <v>0.462687</v>
       </c>
       <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="38" t="n"/>
-      <c r="BQ38" s="39" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
       <c r="BR38" s="28" t="n"/>
       <c r="BS38" s="28" t="n"/>
       <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="38" t="n"/>
+      <c r="BU38" s="25" t="n"/>
       <c r="BV38" s="29" t="n"/>
       <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="40" t="n"/>
-      <c r="BY38" s="39" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
       <c r="BZ38" s="24" t="n"/>
       <c r="CA38" s="31" t="n"/>
     </row>
@@ -10941,7 +10910,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J39" s="38" t="n"/>
+      <c r="J39" s="25" t="n"/>
       <c r="K39" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10950,7 +10919,7 @@
       <c r="L39" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="M39" s="39" t="n">
+      <c r="M39" s="27" t="n">
         <v>1.666667</v>
       </c>
       <c r="N39" s="28" t="n">
@@ -10990,11 +10959,11 @@
       <c r="X39" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y39" s="38" t="n"/>
+      <c r="Y39" s="25" t="n"/>
       <c r="Z39" s="26" t="n"/>
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="40" t="n">
+      <c r="AC39" s="30" t="n">
         <v>1</v>
       </c>
       <c r="AD39" s="24" t="inlineStr">
@@ -11131,11 +11100,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ39" s="38" t="n"/>
+      <c r="BJ39" s="25" t="n"/>
       <c r="BK39" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="BL39" s="39" t="n">
+      <c r="BL39" s="27" t="n">
         <v>1.666667</v>
       </c>
       <c r="BM39" s="28" t="n">
@@ -11145,16 +11114,16 @@
         <v>0.597015</v>
       </c>
       <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="38" t="n"/>
-      <c r="BQ39" s="39" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n"/>
       <c r="BR39" s="28" t="n"/>
       <c r="BS39" s="28" t="n"/>
       <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="38" t="n"/>
+      <c r="BU39" s="25" t="n"/>
       <c r="BV39" s="29" t="n"/>
       <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="40" t="n"/>
-      <c r="BY39" s="39" t="n"/>
+      <c r="BX39" s="30" t="n"/>
+      <c r="BY39" s="27" t="n"/>
       <c r="BZ39" s="24" t="n"/>
       <c r="CA39" s="31" t="n"/>
     </row>
@@ -11204,7 +11173,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J40" s="38" t="n"/>
+      <c r="J40" s="25" t="n"/>
       <c r="K40" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11213,7 +11182,7 @@
       <c r="L40" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M40" s="39" t="n">
+      <c r="M40" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="N40" s="28" t="n">
@@ -11253,11 +11222,11 @@
       <c r="X40" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y40" s="38" t="n"/>
+      <c r="Y40" s="25" t="n"/>
       <c r="Z40" s="26" t="n"/>
       <c r="AA40" s="28" t="n"/>
       <c r="AB40" s="28" t="n"/>
-      <c r="AC40" s="40" t="n">
+      <c r="AC40" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD40" s="24" t="inlineStr">
@@ -11394,11 +11363,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ40" s="38" t="n"/>
+      <c r="BJ40" s="25" t="n"/>
       <c r="BK40" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL40" s="39" t="n">
+      <c r="BL40" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM40" s="28" t="n">
@@ -11408,16 +11377,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO40" s="28" t="n"/>
-      <c r="BP40" s="38" t="n"/>
-      <c r="BQ40" s="39" t="n"/>
+      <c r="BP40" s="25" t="n"/>
+      <c r="BQ40" s="27" t="n"/>
       <c r="BR40" s="28" t="n"/>
       <c r="BS40" s="28" t="n"/>
       <c r="BT40" s="28" t="n"/>
-      <c r="BU40" s="38" t="n"/>
+      <c r="BU40" s="25" t="n"/>
       <c r="BV40" s="29" t="n"/>
       <c r="BW40" s="24" t="n"/>
-      <c r="BX40" s="40" t="n"/>
-      <c r="BY40" s="39" t="n"/>
+      <c r="BX40" s="30" t="n"/>
+      <c r="BY40" s="27" t="n"/>
       <c r="BZ40" s="24" t="n"/>
       <c r="CA40" s="31" t="n"/>
     </row>
@@ -11467,7 +11436,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J41" s="38" t="n"/>
+      <c r="J41" s="25" t="n"/>
       <c r="K41" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11476,7 +11445,7 @@
       <c r="L41" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="M41" s="39" t="n">
+      <c r="M41" s="27" t="n">
         <v>1.613497</v>
       </c>
       <c r="N41" s="28" t="n">
@@ -11516,11 +11485,11 @@
       <c r="X41" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y41" s="38" t="n"/>
+      <c r="Y41" s="25" t="n"/>
       <c r="Z41" s="26" t="n"/>
       <c r="AA41" s="28" t="n"/>
       <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="40" t="n">
+      <c r="AC41" s="30" t="n">
         <v>0.9202</v>
       </c>
       <c r="AD41" s="24" t="inlineStr">
@@ -11657,11 +11626,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ41" s="38" t="n"/>
+      <c r="BJ41" s="25" t="n"/>
       <c r="BK41" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="BL41" s="39" t="n">
+      <c r="BL41" s="27" t="n">
         <v>1.613497</v>
       </c>
       <c r="BM41" s="28" t="n">
@@ -11671,16 +11640,16 @@
         <v>0.616915</v>
       </c>
       <c r="BO41" s="28" t="n"/>
-      <c r="BP41" s="38" t="n"/>
-      <c r="BQ41" s="39" t="n"/>
+      <c r="BP41" s="25" t="n"/>
+      <c r="BQ41" s="27" t="n"/>
       <c r="BR41" s="28" t="n"/>
       <c r="BS41" s="28" t="n"/>
       <c r="BT41" s="28" t="n"/>
-      <c r="BU41" s="38" t="n"/>
+      <c r="BU41" s="25" t="n"/>
       <c r="BV41" s="29" t="n"/>
       <c r="BW41" s="24" t="n"/>
-      <c r="BX41" s="40" t="n"/>
-      <c r="BY41" s="39" t="n"/>
+      <c r="BX41" s="30" t="n"/>
+      <c r="BY41" s="27" t="n"/>
       <c r="BZ41" s="24" t="n"/>
       <c r="CA41" s="31" t="n"/>
     </row>
@@ -11730,7 +11699,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J42" s="38" t="n"/>
+      <c r="J42" s="25" t="n"/>
       <c r="K42" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11739,7 +11708,7 @@
       <c r="L42" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M42" s="39" t="n">
+      <c r="M42" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="N42" s="28" t="n">
@@ -11779,11 +11748,11 @@
       <c r="X42" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y42" s="38" t="n"/>
+      <c r="Y42" s="25" t="n"/>
       <c r="Z42" s="26" t="n"/>
       <c r="AA42" s="28" t="n"/>
       <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="40" t="n">
+      <c r="AC42" s="30" t="n">
         <v>0.6757</v>
       </c>
       <c r="AD42" s="24" t="inlineStr">
@@ -11920,11 +11889,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ42" s="38" t="n"/>
+      <c r="BJ42" s="25" t="n"/>
       <c r="BK42" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL42" s="39" t="n">
+      <c r="BL42" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM42" s="28" t="n">
@@ -11934,16 +11903,16 @@
         <v>0.522388</v>
       </c>
       <c r="BO42" s="28" t="n"/>
-      <c r="BP42" s="38" t="n"/>
-      <c r="BQ42" s="39" t="n"/>
+      <c r="BP42" s="25" t="n"/>
+      <c r="BQ42" s="27" t="n"/>
       <c r="BR42" s="28" t="n"/>
       <c r="BS42" s="28" t="n"/>
       <c r="BT42" s="28" t="n"/>
-      <c r="BU42" s="38" t="n"/>
+      <c r="BU42" s="25" t="n"/>
       <c r="BV42" s="29" t="n"/>
       <c r="BW42" s="24" t="n"/>
-      <c r="BX42" s="40" t="n"/>
-      <c r="BY42" s="39" t="n"/>
+      <c r="BX42" s="30" t="n"/>
+      <c r="BY42" s="27" t="n"/>
       <c r="BZ42" s="24" t="n"/>
       <c r="CA42" s="31" t="n"/>
     </row>
@@ -11993,7 +11962,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J43" s="38" t="n"/>
+      <c r="J43" s="25" t="n"/>
       <c r="K43" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12002,7 +11971,7 @@
       <c r="L43" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M43" s="39" t="n">
+      <c r="M43" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N43" s="28" t="n">
@@ -12042,11 +12011,11 @@
       <c r="X43" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y43" s="38" t="n"/>
+      <c r="Y43" s="25" t="n"/>
       <c r="Z43" s="26" t="n"/>
       <c r="AA43" s="28" t="n"/>
       <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="40" t="n">
+      <c r="AC43" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD43" s="24" t="inlineStr">
@@ -12183,11 +12152,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ43" s="38" t="n"/>
+      <c r="BJ43" s="25" t="n"/>
       <c r="BK43" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL43" s="39" t="n">
+      <c r="BL43" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM43" s="28" t="n">
@@ -12197,16 +12166,16 @@
         <v>0.517413</v>
       </c>
       <c r="BO43" s="28" t="n"/>
-      <c r="BP43" s="38" t="n"/>
-      <c r="BQ43" s="39" t="n"/>
+      <c r="BP43" s="25" t="n"/>
+      <c r="BQ43" s="27" t="n"/>
       <c r="BR43" s="28" t="n"/>
       <c r="BS43" s="28" t="n"/>
       <c r="BT43" s="28" t="n"/>
-      <c r="BU43" s="38" t="n"/>
+      <c r="BU43" s="25" t="n"/>
       <c r="BV43" s="29" t="n"/>
       <c r="BW43" s="24" t="n"/>
-      <c r="BX43" s="40" t="n"/>
-      <c r="BY43" s="39" t="n"/>
+      <c r="BX43" s="30" t="n"/>
+      <c r="BY43" s="27" t="n"/>
       <c r="BZ43" s="24" t="n"/>
       <c r="CA43" s="31" t="n"/>
     </row>
@@ -12256,7 +12225,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J44" s="38" t="n"/>
+      <c r="J44" s="25" t="n"/>
       <c r="K44" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12265,7 +12234,7 @@
       <c r="L44" s="26" t="n">
         <v>-400</v>
       </c>
-      <c r="M44" s="39" t="n">
+      <c r="M44" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="N44" s="28" t="n">
@@ -12305,11 +12274,11 @@
       <c r="X44" s="26" t="n">
         <v>90</v>
       </c>
-      <c r="Y44" s="38" t="n"/>
+      <c r="Y44" s="25" t="n"/>
       <c r="Z44" s="26" t="n"/>
       <c r="AA44" s="28" t="n"/>
       <c r="AB44" s="28" t="n"/>
-      <c r="AC44" s="40" t="n">
+      <c r="AC44" s="30" t="n">
         <v>0.5</v>
       </c>
       <c r="AD44" s="24" t="inlineStr">
@@ -12446,11 +12415,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ44" s="38" t="n"/>
+      <c r="BJ44" s="25" t="n"/>
       <c r="BK44" s="26" t="n">
         <v>-400</v>
       </c>
-      <c r="BL44" s="39" t="n">
+      <c r="BL44" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="BM44" s="28" t="n">
@@ -12460,16 +12429,16 @@
         <v>0.792079</v>
       </c>
       <c r="BO44" s="28" t="n"/>
-      <c r="BP44" s="38" t="n"/>
-      <c r="BQ44" s="39" t="n"/>
+      <c r="BP44" s="25" t="n"/>
+      <c r="BQ44" s="27" t="n"/>
       <c r="BR44" s="28" t="n"/>
       <c r="BS44" s="28" t="n"/>
       <c r="BT44" s="28" t="n"/>
-      <c r="BU44" s="38" t="n"/>
+      <c r="BU44" s="25" t="n"/>
       <c r="BV44" s="29" t="n"/>
       <c r="BW44" s="24" t="n"/>
-      <c r="BX44" s="40" t="n"/>
-      <c r="BY44" s="39" t="n"/>
+      <c r="BX44" s="30" t="n"/>
+      <c r="BY44" s="27" t="n"/>
       <c r="BZ44" s="24" t="n"/>
       <c r="CA44" s="31" t="n"/>
     </row>
@@ -12519,7 +12488,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J45" s="38" t="n"/>
+      <c r="J45" s="25" t="n"/>
       <c r="K45" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12528,7 +12497,7 @@
       <c r="L45" s="26" t="n">
         <v>-426</v>
       </c>
-      <c r="M45" s="39" t="n">
+      <c r="M45" s="27" t="n">
         <v>1.234742</v>
       </c>
       <c r="N45" s="28" t="n">
@@ -12568,11 +12537,11 @@
       <c r="X45" s="26" t="n">
         <v>93</v>
       </c>
-      <c r="Y45" s="38" t="n"/>
+      <c r="Y45" s="25" t="n"/>
       <c r="Z45" s="26" t="n"/>
       <c r="AA45" s="28" t="n"/>
       <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="40" t="n">
+      <c r="AC45" s="30" t="n">
         <v>0.4695</v>
       </c>
       <c r="AD45" s="24" t="inlineStr">
@@ -12709,11 +12678,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ45" s="38" t="n"/>
+      <c r="BJ45" s="25" t="n"/>
       <c r="BK45" s="26" t="n">
         <v>-426</v>
       </c>
-      <c r="BL45" s="39" t="n">
+      <c r="BL45" s="27" t="n">
         <v>1.234742</v>
       </c>
       <c r="BM45" s="28" t="n">
@@ -12723,16 +12692,16 @@
         <v>0.80198</v>
       </c>
       <c r="BO45" s="28" t="n"/>
-      <c r="BP45" s="38" t="n"/>
-      <c r="BQ45" s="39" t="n"/>
+      <c r="BP45" s="25" t="n"/>
+      <c r="BQ45" s="27" t="n"/>
       <c r="BR45" s="28" t="n"/>
       <c r="BS45" s="28" t="n"/>
       <c r="BT45" s="28" t="n"/>
-      <c r="BU45" s="38" t="n"/>
+      <c r="BU45" s="25" t="n"/>
       <c r="BV45" s="29" t="n"/>
       <c r="BW45" s="24" t="n"/>
-      <c r="BX45" s="40" t="n"/>
-      <c r="BY45" s="39" t="n"/>
+      <c r="BX45" s="30" t="n"/>
+      <c r="BY45" s="27" t="n"/>
       <c r="BZ45" s="24" t="n"/>
       <c r="CA45" s="31" t="n"/>
     </row>
@@ -12782,7 +12751,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J46" s="38" t="n"/>
+      <c r="J46" s="25" t="n"/>
       <c r="K46" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12791,7 +12760,7 @@
       <c r="L46" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="M46" s="39" t="n">
+      <c r="M46" s="27" t="n">
         <v>1.641026</v>
       </c>
       <c r="N46" s="28" t="n">
@@ -12831,11 +12800,11 @@
       <c r="X46" s="26" t="n">
         <v>72</v>
       </c>
-      <c r="Y46" s="38" t="n"/>
+      <c r="Y46" s="25" t="n"/>
       <c r="Z46" s="26" t="n"/>
       <c r="AA46" s="28" t="n"/>
       <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="40" t="n">
+      <c r="AC46" s="30" t="n">
         <v>0.8013</v>
       </c>
       <c r="AD46" s="24" t="inlineStr">
@@ -12972,11 +12941,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ46" s="38" t="n"/>
+      <c r="BJ46" s="25" t="n"/>
       <c r="BK46" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="BL46" s="39" t="n">
+      <c r="BL46" s="27" t="n">
         <v>1.641026</v>
       </c>
       <c r="BM46" s="28" t="n">
@@ -12986,16 +12955,16 @@
         <v>0.6039600000000001</v>
       </c>
       <c r="BO46" s="28" t="n"/>
-      <c r="BP46" s="38" t="n"/>
-      <c r="BQ46" s="39" t="n"/>
+      <c r="BP46" s="25" t="n"/>
+      <c r="BQ46" s="27" t="n"/>
       <c r="BR46" s="28" t="n"/>
       <c r="BS46" s="28" t="n"/>
       <c r="BT46" s="28" t="n"/>
-      <c r="BU46" s="38" t="n"/>
+      <c r="BU46" s="25" t="n"/>
       <c r="BV46" s="29" t="n"/>
       <c r="BW46" s="24" t="n"/>
-      <c r="BX46" s="40" t="n"/>
-      <c r="BY46" s="39" t="n"/>
+      <c r="BX46" s="30" t="n"/>
+      <c r="BY46" s="27" t="n"/>
       <c r="BZ46" s="24" t="n"/>
       <c r="CA46" s="31" t="n"/>
     </row>
@@ -13045,7 +13014,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J47" s="38" t="n"/>
+      <c r="J47" s="25" t="n"/>
       <c r="K47" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -13054,7 +13023,7 @@
       <c r="L47" s="26" t="n">
         <v>-354</v>
       </c>
-      <c r="M47" s="39" t="n">
+      <c r="M47" s="27" t="n">
         <v>1.282486</v>
       </c>
       <c r="N47" s="28" t="n">
@@ -13092,11 +13061,11 @@
       <c r="X47" s="26" t="n">
         <v>110</v>
       </c>
-      <c r="Y47" s="38" t="n"/>
+      <c r="Y47" s="25" t="n"/>
       <c r="Z47" s="26" t="n"/>
       <c r="AA47" s="28" t="n"/>
       <c r="AB47" s="28" t="n"/>
-      <c r="AC47" s="40" t="n">
+      <c r="AC47" s="30" t="n">
         <v>0.4944</v>
       </c>
       <c r="AD47" s="24" t="inlineStr">
@@ -13157,11 +13126,11 @@
       <c r="BG47" s="24" t="n"/>
       <c r="BH47" s="24" t="n"/>
       <c r="BI47" s="24" t="n"/>
-      <c r="BJ47" s="38" t="n"/>
+      <c r="BJ47" s="25" t="n"/>
       <c r="BK47" s="26" t="n">
         <v>-354</v>
       </c>
-      <c r="BL47" s="39" t="n">
+      <c r="BL47" s="27" t="n">
         <v>1.282486</v>
       </c>
       <c r="BM47" s="28" t="n">
@@ -13171,16 +13140,16 @@
         <v>0.779736</v>
       </c>
       <c r="BO47" s="28" t="n"/>
-      <c r="BP47" s="38" t="n"/>
-      <c r="BQ47" s="39" t="n"/>
+      <c r="BP47" s="25" t="n"/>
+      <c r="BQ47" s="27" t="n"/>
       <c r="BR47" s="28" t="n"/>
       <c r="BS47" s="28" t="n"/>
       <c r="BT47" s="28" t="n"/>
-      <c r="BU47" s="38" t="n"/>
+      <c r="BU47" s="25" t="n"/>
       <c r="BV47" s="29" t="n"/>
       <c r="BW47" s="24" t="n"/>
-      <c r="BX47" s="40" t="n"/>
-      <c r="BY47" s="39" t="n"/>
+      <c r="BX47" s="30" t="n"/>
+      <c r="BY47" s="27" t="n"/>
       <c r="BZ47" s="24" t="n"/>
       <c r="CA47" s="31" t="n"/>
     </row>
@@ -13230,7 +13199,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J48" s="38" t="n"/>
+      <c r="J48" s="25" t="n"/>
       <c r="K48" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13239,7 +13208,7 @@
       <c r="L48" s="26" t="n">
         <v>-194</v>
       </c>
-      <c r="M48" s="39" t="n">
+      <c r="M48" s="27" t="n">
         <v>1.515464</v>
       </c>
       <c r="N48" s="28" t="n">
@@ -13281,11 +13250,11 @@
       <c r="X48" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y48" s="38" t="n"/>
+      <c r="Y48" s="25" t="n"/>
       <c r="Z48" s="26" t="n"/>
       <c r="AA48" s="28" t="n"/>
       <c r="AB48" s="28" t="n"/>
-      <c r="AC48" s="40" t="n">
+      <c r="AC48" s="30" t="n">
         <v>0.6443</v>
       </c>
       <c r="AD48" s="24" t="inlineStr">
@@ -13344,11 +13313,11 @@
         </is>
       </c>
       <c r="BI48" s="24" t="n"/>
-      <c r="BJ48" s="38" t="n"/>
+      <c r="BJ48" s="25" t="n"/>
       <c r="BK48" s="26" t="n">
         <v>-194</v>
       </c>
-      <c r="BL48" s="39" t="n">
+      <c r="BL48" s="27" t="n">
         <v>1.515464</v>
       </c>
       <c r="BM48" s="28" t="n">
@@ -13358,16 +13327,16 @@
         <v>0.656716</v>
       </c>
       <c r="BO48" s="28" t="n"/>
-      <c r="BP48" s="38" t="n"/>
-      <c r="BQ48" s="39" t="n"/>
+      <c r="BP48" s="25" t="n"/>
+      <c r="BQ48" s="27" t="n"/>
       <c r="BR48" s="28" t="n"/>
       <c r="BS48" s="28" t="n"/>
       <c r="BT48" s="28" t="n"/>
-      <c r="BU48" s="38" t="n"/>
+      <c r="BU48" s="25" t="n"/>
       <c r="BV48" s="29" t="n"/>
       <c r="BW48" s="24" t="n"/>
-      <c r="BX48" s="40" t="n"/>
-      <c r="BY48" s="39" t="n"/>
+      <c r="BX48" s="30" t="n"/>
+      <c r="BY48" s="27" t="n"/>
       <c r="BZ48" s="24" t="n"/>
       <c r="CA48" s="31" t="n"/>
     </row>
@@ -13417,7 +13386,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J49" s="38" t="n"/>
+      <c r="J49" s="25" t="n"/>
       <c r="K49" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13426,7 +13395,7 @@
       <c r="L49" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="M49" s="39" t="n">
+      <c r="M49" s="27" t="n">
         <v>1.819672</v>
       </c>
       <c r="N49" s="28" t="n">
@@ -13468,11 +13437,11 @@
       <c r="X49" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y49" s="38" t="n"/>
+      <c r="Y49" s="25" t="n"/>
       <c r="Z49" s="26" t="n"/>
       <c r="AA49" s="28" t="n"/>
       <c r="AB49" s="28" t="n"/>
-      <c r="AC49" s="40" t="n">
+      <c r="AC49" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD49" s="24" t="inlineStr">
@@ -13531,11 +13500,11 @@
         </is>
       </c>
       <c r="BI49" s="24" t="n"/>
-      <c r="BJ49" s="38" t="n"/>
+      <c r="BJ49" s="25" t="n"/>
       <c r="BK49" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="BL49" s="39" t="n">
+      <c r="BL49" s="27" t="n">
         <v>1.819672</v>
       </c>
       <c r="BM49" s="28" t="n">
@@ -13545,16 +13514,16 @@
         <v>0.547264</v>
       </c>
       <c r="BO49" s="28" t="n"/>
-      <c r="BP49" s="38" t="n"/>
-      <c r="BQ49" s="39" t="n"/>
+      <c r="BP49" s="25" t="n"/>
+      <c r="BQ49" s="27" t="n"/>
       <c r="BR49" s="28" t="n"/>
       <c r="BS49" s="28" t="n"/>
       <c r="BT49" s="28" t="n"/>
-      <c r="BU49" s="38" t="n"/>
+      <c r="BU49" s="25" t="n"/>
       <c r="BV49" s="29" t="n"/>
       <c r="BW49" s="24" t="n"/>
-      <c r="BX49" s="40" t="n"/>
-      <c r="BY49" s="39" t="n"/>
+      <c r="BX49" s="30" t="n"/>
+      <c r="BY49" s="27" t="n"/>
       <c r="BZ49" s="24" t="n"/>
       <c r="CA49" s="31" t="n"/>
     </row>
@@ -13604,7 +13573,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J50" s="38" t="n"/>
+      <c r="J50" s="25" t="n"/>
       <c r="K50" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13613,7 +13582,7 @@
       <c r="L50" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M50" s="39" t="n">
+      <c r="M50" s="27" t="n">
         <v>1.884956</v>
       </c>
       <c r="N50" s="28" t="n">
@@ -13655,11 +13624,11 @@
       <c r="X50" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y50" s="38" t="n"/>
+      <c r="Y50" s="25" t="n"/>
       <c r="Z50" s="26" t="n"/>
       <c r="AA50" s="28" t="n"/>
       <c r="AB50" s="28" t="n"/>
-      <c r="AC50" s="40" t="n">
+      <c r="AC50" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD50" s="24" t="inlineStr">
@@ -13718,11 +13687,11 @@
         </is>
       </c>
       <c r="BI50" s="24" t="n"/>
-      <c r="BJ50" s="38" t="n"/>
+      <c r="BJ50" s="25" t="n"/>
       <c r="BK50" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL50" s="39" t="n">
+      <c r="BL50" s="27" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM50" s="28" t="n">
@@ -13732,16 +13701,16 @@
         <v>0.527363</v>
       </c>
       <c r="BO50" s="28" t="n"/>
-      <c r="BP50" s="38" t="n"/>
-      <c r="BQ50" s="39" t="n"/>
+      <c r="BP50" s="25" t="n"/>
+      <c r="BQ50" s="27" t="n"/>
       <c r="BR50" s="28" t="n"/>
       <c r="BS50" s="28" t="n"/>
       <c r="BT50" s="28" t="n"/>
-      <c r="BU50" s="38" t="n"/>
+      <c r="BU50" s="25" t="n"/>
       <c r="BV50" s="29" t="n"/>
       <c r="BW50" s="24" t="n"/>
-      <c r="BX50" s="40" t="n"/>
-      <c r="BY50" s="39" t="n"/>
+      <c r="BX50" s="30" t="n"/>
+      <c r="BY50" s="27" t="n"/>
       <c r="BZ50" s="24" t="n"/>
       <c r="CA50" s="31" t="n"/>
     </row>
@@ -13791,7 +13760,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J51" s="38" t="n"/>
+      <c r="J51" s="25" t="n"/>
       <c r="K51" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13800,7 +13769,7 @@
       <c r="L51" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M51" s="39" t="n">
+      <c r="M51" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N51" s="28" t="n">
@@ -13842,11 +13811,11 @@
       <c r="X51" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y51" s="38" t="n"/>
+      <c r="Y51" s="25" t="n"/>
       <c r="Z51" s="26" t="n"/>
       <c r="AA51" s="28" t="n"/>
       <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="40" t="n">
+      <c r="AC51" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD51" s="24" t="inlineStr">
@@ -13905,11 +13874,11 @@
         </is>
       </c>
       <c r="BI51" s="24" t="n"/>
-      <c r="BJ51" s="38" t="n"/>
+      <c r="BJ51" s="25" t="n"/>
       <c r="BK51" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL51" s="39" t="n">
+      <c r="BL51" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM51" s="28" t="n">
@@ -13919,16 +13888,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO51" s="28" t="n"/>
-      <c r="BP51" s="38" t="n"/>
-      <c r="BQ51" s="39" t="n"/>
+      <c r="BP51" s="25" t="n"/>
+      <c r="BQ51" s="27" t="n"/>
       <c r="BR51" s="28" t="n"/>
       <c r="BS51" s="28" t="n"/>
       <c r="BT51" s="28" t="n"/>
-      <c r="BU51" s="38" t="n"/>
+      <c r="BU51" s="25" t="n"/>
       <c r="BV51" s="29" t="n"/>
       <c r="BW51" s="24" t="n"/>
-      <c r="BX51" s="40" t="n"/>
-      <c r="BY51" s="39" t="n"/>
+      <c r="BX51" s="30" t="n"/>
+      <c r="BY51" s="27" t="n"/>
       <c r="BZ51" s="24" t="n"/>
       <c r="CA51" s="31" t="n"/>
     </row>
@@ -13978,7 +13947,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J52" s="38" t="n"/>
+      <c r="J52" s="25" t="n"/>
       <c r="K52" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -13987,7 +13956,7 @@
       <c r="L52" s="26" t="n">
         <v>-174</v>
       </c>
-      <c r="M52" s="39" t="n">
+      <c r="M52" s="27" t="n">
         <v>1.574713</v>
       </c>
       <c r="N52" s="28" t="n">
@@ -14029,11 +13998,11 @@
       <c r="X52" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y52" s="38" t="n"/>
+      <c r="Y52" s="25" t="n"/>
       <c r="Z52" s="26" t="n"/>
       <c r="AA52" s="28" t="n"/>
       <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="40" t="n">
+      <c r="AC52" s="30" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD52" s="24" t="inlineStr">
@@ -14092,11 +14061,11 @@
         </is>
       </c>
       <c r="BI52" s="24" t="n"/>
-      <c r="BJ52" s="38" t="n"/>
+      <c r="BJ52" s="25" t="n"/>
       <c r="BK52" s="26" t="n">
         <v>-174</v>
       </c>
-      <c r="BL52" s="39" t="n">
+      <c r="BL52" s="27" t="n">
         <v>1.574713</v>
       </c>
       <c r="BM52" s="28" t="n">
@@ -14106,16 +14075,16 @@
         <v>0.631841</v>
       </c>
       <c r="BO52" s="28" t="n"/>
-      <c r="BP52" s="38" t="n"/>
-      <c r="BQ52" s="39" t="n"/>
+      <c r="BP52" s="25" t="n"/>
+      <c r="BQ52" s="27" t="n"/>
       <c r="BR52" s="28" t="n"/>
       <c r="BS52" s="28" t="n"/>
       <c r="BT52" s="28" t="n"/>
-      <c r="BU52" s="38" t="n"/>
+      <c r="BU52" s="25" t="n"/>
       <c r="BV52" s="29" t="n"/>
       <c r="BW52" s="24" t="n"/>
-      <c r="BX52" s="40" t="n"/>
-      <c r="BY52" s="39" t="n"/>
+      <c r="BX52" s="30" t="n"/>
+      <c r="BY52" s="27" t="n"/>
       <c r="BZ52" s="24" t="n"/>
       <c r="CA52" s="31" t="n"/>
     </row>
@@ -14165,7 +14134,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J53" s="38" t="n"/>
+      <c r="J53" s="25" t="n"/>
       <c r="K53" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14174,7 +14143,7 @@
       <c r="L53" s="26" t="n">
         <v>-376</v>
       </c>
-      <c r="M53" s="39" t="n">
+      <c r="M53" s="27" t="n">
         <v>1.265957</v>
       </c>
       <c r="N53" s="28" t="n">
@@ -14214,11 +14183,11 @@
       <c r="X53" s="26" t="n">
         <v>92</v>
       </c>
-      <c r="Y53" s="38" t="n"/>
+      <c r="Y53" s="25" t="n"/>
       <c r="Z53" s="26" t="n"/>
       <c r="AA53" s="28" t="n"/>
       <c r="AB53" s="28" t="n"/>
-      <c r="AC53" s="40" t="n">
+      <c r="AC53" s="30" t="n">
         <v>0.1995</v>
       </c>
       <c r="AD53" s="24" t="inlineStr">
@@ -14265,11 +14234,11 @@
         </is>
       </c>
       <c r="BI53" s="24" t="n"/>
-      <c r="BJ53" s="38" t="n"/>
+      <c r="BJ53" s="25" t="n"/>
       <c r="BK53" s="26" t="n">
         <v>-376</v>
       </c>
-      <c r="BL53" s="39" t="n">
+      <c r="BL53" s="27" t="n">
         <v>1.265957</v>
       </c>
       <c r="BM53" s="28" t="n">
@@ -14279,16 +14248,16 @@
         <v>0.782178</v>
       </c>
       <c r="BO53" s="28" t="n"/>
-      <c r="BP53" s="38" t="n"/>
-      <c r="BQ53" s="39" t="n"/>
+      <c r="BP53" s="25" t="n"/>
+      <c r="BQ53" s="27" t="n"/>
       <c r="BR53" s="28" t="n"/>
       <c r="BS53" s="28" t="n"/>
       <c r="BT53" s="28" t="n"/>
-      <c r="BU53" s="38" t="n"/>
+      <c r="BU53" s="25" t="n"/>
       <c r="BV53" s="29" t="n"/>
       <c r="BW53" s="24" t="n"/>
-      <c r="BX53" s="40" t="n"/>
-      <c r="BY53" s="39" t="n"/>
+      <c r="BX53" s="30" t="n"/>
+      <c r="BY53" s="27" t="n"/>
       <c r="BZ53" s="24" t="n"/>
       <c r="CA53" s="31" t="n"/>
     </row>
@@ -14338,7 +14307,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J54" s="38" t="n"/>
+      <c r="J54" s="25" t="n"/>
       <c r="K54" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14347,7 +14316,7 @@
       <c r="L54" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M54" s="39" t="n">
+      <c r="M54" s="27" t="n">
         <v>1.884956</v>
       </c>
       <c r="N54" s="28" t="n">
@@ -14387,11 +14356,11 @@
       <c r="X54" s="26" t="n">
         <v>96</v>
       </c>
-      <c r="Y54" s="38" t="n"/>
+      <c r="Y54" s="25" t="n"/>
       <c r="Z54" s="26" t="n"/>
       <c r="AA54" s="28" t="n"/>
       <c r="AB54" s="28" t="n"/>
-      <c r="AC54" s="40" t="n">
+      <c r="AC54" s="30" t="n">
         <v>0.4425</v>
       </c>
       <c r="AD54" s="24" t="inlineStr">
@@ -14438,11 +14407,11 @@
         </is>
       </c>
       <c r="BI54" s="24" t="n"/>
-      <c r="BJ54" s="38" t="n"/>
+      <c r="BJ54" s="25" t="n"/>
       <c r="BK54" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL54" s="39" t="n">
+      <c r="BL54" s="27" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM54" s="28" t="n">
@@ -14452,16 +14421,16 @@
         <v>0.524752</v>
       </c>
       <c r="BO54" s="28" t="n"/>
-      <c r="BP54" s="38" t="n"/>
-      <c r="BQ54" s="39" t="n"/>
+      <c r="BP54" s="25" t="n"/>
+      <c r="BQ54" s="27" t="n"/>
       <c r="BR54" s="28" t="n"/>
       <c r="BS54" s="28" t="n"/>
       <c r="BT54" s="28" t="n"/>
-      <c r="BU54" s="38" t="n"/>
+      <c r="BU54" s="25" t="n"/>
       <c r="BV54" s="29" t="n"/>
       <c r="BW54" s="24" t="n"/>
-      <c r="BX54" s="40" t="n"/>
-      <c r="BY54" s="39" t="n"/>
+      <c r="BX54" s="30" t="n"/>
+      <c r="BY54" s="27" t="n"/>
       <c r="BZ54" s="24" t="n"/>
       <c r="CA54" s="31" t="n"/>
     </row>
@@ -14511,7 +14480,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J55" s="38" t="n"/>
+      <c r="J55" s="25" t="n"/>
       <c r="K55" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14520,7 +14489,7 @@
       <c r="L55" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="M55" s="39" t="n">
+      <c r="M55" s="27" t="n">
         <v>1.561798</v>
       </c>
       <c r="N55" s="28" t="n">
@@ -14560,11 +14529,11 @@
       <c r="X55" s="26" t="n">
         <v>83</v>
       </c>
-      <c r="Y55" s="38" t="n"/>
+      <c r="Y55" s="25" t="n"/>
       <c r="Z55" s="26" t="n"/>
       <c r="AA55" s="28" t="n"/>
       <c r="AB55" s="28" t="n"/>
-      <c r="AC55" s="40" t="n">
+      <c r="AC55" s="30" t="n">
         <v>-2</v>
       </c>
       <c r="AD55" s="24" t="inlineStr">
@@ -14611,11 +14580,11 @@
         </is>
       </c>
       <c r="BI55" s="24" t="n"/>
-      <c r="BJ55" s="38" t="n"/>
+      <c r="BJ55" s="25" t="n"/>
       <c r="BK55" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="BL55" s="39" t="n">
+      <c r="BL55" s="27" t="n">
         <v>1.561798</v>
       </c>
       <c r="BM55" s="28" t="n">
@@ -14625,16 +14594,16 @@
         <v>0.633663</v>
       </c>
       <c r="BO55" s="28" t="n"/>
-      <c r="BP55" s="38" t="n"/>
-      <c r="BQ55" s="39" t="n"/>
+      <c r="BP55" s="25" t="n"/>
+      <c r="BQ55" s="27" t="n"/>
       <c r="BR55" s="28" t="n"/>
       <c r="BS55" s="28" t="n"/>
       <c r="BT55" s="28" t="n"/>
-      <c r="BU55" s="38" t="n"/>
+      <c r="BU55" s="25" t="n"/>
       <c r="BV55" s="29" t="n"/>
       <c r="BW55" s="24" t="n"/>
-      <c r="BX55" s="40" t="n"/>
-      <c r="BY55" s="39" t="n"/>
+      <c r="BX55" s="30" t="n"/>
+      <c r="BY55" s="27" t="n"/>
       <c r="BZ55" s="24" t="n"/>
       <c r="CA55" s="31" t="n"/>
     </row>
@@ -14684,7 +14653,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J56" s="38" t="n"/>
+      <c r="J56" s="25" t="n"/>
       <c r="K56" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14693,7 +14662,7 @@
       <c r="L56" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="M56" s="39" t="n">
+      <c r="M56" s="27" t="n">
         <v>1.613497</v>
       </c>
       <c r="N56" s="28" t="n">
@@ -14735,11 +14704,11 @@
       <c r="X56" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y56" s="38" t="n"/>
+      <c r="Y56" s="25" t="n"/>
       <c r="Z56" s="26" t="n"/>
       <c r="AA56" s="28" t="n"/>
       <c r="AB56" s="28" t="n"/>
-      <c r="AC56" s="40" t="n">
+      <c r="AC56" s="30" t="n">
         <v>0.9202</v>
       </c>
       <c r="AD56" s="24" t="inlineStr">
@@ -14798,11 +14767,11 @@
         </is>
       </c>
       <c r="BI56" s="24" t="n"/>
-      <c r="BJ56" s="38" t="n"/>
+      <c r="BJ56" s="25" t="n"/>
       <c r="BK56" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="BL56" s="39" t="n">
+      <c r="BL56" s="27" t="n">
         <v>1.613497</v>
       </c>
       <c r="BM56" s="28" t="n">
@@ -14812,16 +14781,16 @@
         <v>0.616915</v>
       </c>
       <c r="BO56" s="28" t="n"/>
-      <c r="BP56" s="38" t="n"/>
-      <c r="BQ56" s="39" t="n"/>
+      <c r="BP56" s="25" t="n"/>
+      <c r="BQ56" s="27" t="n"/>
       <c r="BR56" s="28" t="n"/>
       <c r="BS56" s="28" t="n"/>
       <c r="BT56" s="28" t="n"/>
-      <c r="BU56" s="38" t="n"/>
+      <c r="BU56" s="25" t="n"/>
       <c r="BV56" s="29" t="n"/>
       <c r="BW56" s="24" t="n"/>
-      <c r="BX56" s="40" t="n"/>
-      <c r="BY56" s="39" t="n"/>
+      <c r="BX56" s="30" t="n"/>
+      <c r="BY56" s="27" t="n"/>
       <c r="BZ56" s="24" t="n"/>
       <c r="CA56" s="31" t="n"/>
     </row>
@@ -14871,7 +14840,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J57" s="38" t="n"/>
+      <c r="J57" s="25" t="n"/>
       <c r="K57" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -14880,7 +14849,7 @@
       <c r="L57" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M57" s="39" t="n">
+      <c r="M57" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="N57" s="28" t="n">
@@ -14922,11 +14891,11 @@
       <c r="X57" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y57" s="38" t="n"/>
+      <c r="Y57" s="25" t="n"/>
       <c r="Z57" s="26" t="n"/>
       <c r="AA57" s="28" t="n"/>
       <c r="AB57" s="28" t="n"/>
-      <c r="AC57" s="40" t="n">
+      <c r="AC57" s="30" t="n">
         <v>0.6757</v>
       </c>
       <c r="AD57" s="24" t="inlineStr">
@@ -14985,11 +14954,11 @@
         </is>
       </c>
       <c r="BI57" s="24" t="n"/>
-      <c r="BJ57" s="38" t="n"/>
+      <c r="BJ57" s="25" t="n"/>
       <c r="BK57" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL57" s="39" t="n">
+      <c r="BL57" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM57" s="28" t="n">
@@ -14999,16 +14968,16 @@
         <v>0.522388</v>
       </c>
       <c r="BO57" s="28" t="n"/>
-      <c r="BP57" s="38" t="n"/>
-      <c r="BQ57" s="39" t="n"/>
+      <c r="BP57" s="25" t="n"/>
+      <c r="BQ57" s="27" t="n"/>
       <c r="BR57" s="28" t="n"/>
       <c r="BS57" s="28" t="n"/>
       <c r="BT57" s="28" t="n"/>
-      <c r="BU57" s="38" t="n"/>
+      <c r="BU57" s="25" t="n"/>
       <c r="BV57" s="29" t="n"/>
       <c r="BW57" s="24" t="n"/>
-      <c r="BX57" s="40" t="n"/>
-      <c r="BY57" s="39" t="n"/>
+      <c r="BX57" s="30" t="n"/>
+      <c r="BY57" s="27" t="n"/>
       <c r="BZ57" s="24" t="n"/>
       <c r="CA57" s="31" t="n"/>
     </row>
@@ -15058,7 +15027,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J58" s="38" t="n"/>
+      <c r="J58" s="25" t="n"/>
       <c r="K58" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -15067,7 +15036,7 @@
       <c r="L58" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M58" s="39" t="n">
+      <c r="M58" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="N58" s="28" t="n">
@@ -15109,11 +15078,11 @@
       <c r="X58" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y58" s="38" t="n"/>
+      <c r="Y58" s="25" t="n"/>
       <c r="Z58" s="26" t="n"/>
       <c r="AA58" s="28" t="n"/>
       <c r="AB58" s="28" t="n"/>
-      <c r="AC58" s="40" t="n">
+      <c r="AC58" s="30" t="n">
         <v>1.087</v>
       </c>
       <c r="AD58" s="24" t="inlineStr">
@@ -15172,11 +15141,11 @@
         </is>
       </c>
       <c r="BI58" s="24" t="n"/>
-      <c r="BJ58" s="38" t="n"/>
+      <c r="BJ58" s="25" t="n"/>
       <c r="BK58" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL58" s="39" t="n">
+      <c r="BL58" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM58" s="28" t="n">
@@ -15186,16 +15155,16 @@
         <v>0.577114</v>
       </c>
       <c r="BO58" s="28" t="n"/>
-      <c r="BP58" s="38" t="n"/>
-      <c r="BQ58" s="39" t="n"/>
+      <c r="BP58" s="25" t="n"/>
+      <c r="BQ58" s="27" t="n"/>
       <c r="BR58" s="28" t="n"/>
       <c r="BS58" s="28" t="n"/>
       <c r="BT58" s="28" t="n"/>
-      <c r="BU58" s="38" t="n"/>
+      <c r="BU58" s="25" t="n"/>
       <c r="BV58" s="29" t="n"/>
       <c r="BW58" s="24" t="n"/>
-      <c r="BX58" s="40" t="n"/>
-      <c r="BY58" s="39" t="n"/>
+      <c r="BX58" s="30" t="n"/>
+      <c r="BY58" s="27" t="n"/>
       <c r="BZ58" s="24" t="n"/>
       <c r="CA58" s="31" t="n"/>
     </row>
@@ -15245,7 +15214,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J59" s="38" t="n"/>
+      <c r="J59" s="25" t="n"/>
       <c r="K59" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -15254,7 +15223,7 @@
       <c r="L59" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="M59" s="39" t="n">
+      <c r="M59" s="27" t="n">
         <v>1.561798</v>
       </c>
       <c r="N59" s="28" t="n">
@@ -15296,11 +15265,11 @@
       <c r="X59" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y59" s="38" t="n"/>
+      <c r="Y59" s="25" t="n"/>
       <c r="Z59" s="26" t="n"/>
       <c r="AA59" s="28" t="n"/>
       <c r="AB59" s="28" t="n"/>
-      <c r="AC59" s="40" t="n">
+      <c r="AC59" s="30" t="n">
         <v>0.5618</v>
       </c>
       <c r="AD59" s="24" t="inlineStr">
@@ -15359,11 +15328,11 @@
         </is>
       </c>
       <c r="BI59" s="24" t="n"/>
-      <c r="BJ59" s="38" t="n"/>
+      <c r="BJ59" s="25" t="n"/>
       <c r="BK59" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="BL59" s="39" t="n">
+      <c r="BL59" s="27" t="n">
         <v>1.561798</v>
       </c>
       <c r="BM59" s="28" t="n">
@@ -15373,16 +15342,16 @@
         <v>0.636816</v>
       </c>
       <c r="BO59" s="28" t="n"/>
-      <c r="BP59" s="38" t="n"/>
-      <c r="BQ59" s="39" t="n"/>
+      <c r="BP59" s="25" t="n"/>
+      <c r="BQ59" s="27" t="n"/>
       <c r="BR59" s="28" t="n"/>
       <c r="BS59" s="28" t="n"/>
       <c r="BT59" s="28" t="n"/>
-      <c r="BU59" s="38" t="n"/>
+      <c r="BU59" s="25" t="n"/>
       <c r="BV59" s="29" t="n"/>
       <c r="BW59" s="24" t="n"/>
-      <c r="BX59" s="40" t="n"/>
-      <c r="BY59" s="39" t="n"/>
+      <c r="BX59" s="30" t="n"/>
+      <c r="BY59" s="27" t="n"/>
       <c r="BZ59" s="24" t="n"/>
       <c r="CA59" s="31" t="n"/>
     </row>
@@ -15432,7 +15401,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J60" s="38" t="n"/>
+      <c r="J60" s="25" t="n"/>
       <c r="K60" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -15441,7 +15410,7 @@
       <c r="L60" s="26" t="n">
         <v>-669</v>
       </c>
-      <c r="M60" s="39" t="n">
+      <c r="M60" s="27" t="n">
         <v>1.149477</v>
       </c>
       <c r="N60" s="28" t="n">
@@ -15481,11 +15450,11 @@
       <c r="X60" s="26" t="n">
         <v>101</v>
       </c>
-      <c r="Y60" s="38" t="n"/>
+      <c r="Y60" s="25" t="n"/>
       <c r="Z60" s="26" t="n"/>
       <c r="AA60" s="28" t="n"/>
       <c r="AB60" s="28" t="n"/>
-      <c r="AC60" s="40" t="n">
+      <c r="AC60" s="30" t="n">
         <v>0.299</v>
       </c>
       <c r="AD60" s="24" t="inlineStr">
@@ -15532,11 +15501,11 @@
         </is>
       </c>
       <c r="BI60" s="24" t="n"/>
-      <c r="BJ60" s="38" t="n"/>
+      <c r="BJ60" s="25" t="n"/>
       <c r="BK60" s="26" t="n">
         <v>-669</v>
       </c>
-      <c r="BL60" s="39" t="n">
+      <c r="BL60" s="27" t="n">
         <v>1.149477</v>
       </c>
       <c r="BM60" s="28" t="n">
@@ -15546,16 +15515,16 @@
         <v>0.861386</v>
       </c>
       <c r="BO60" s="28" t="n"/>
-      <c r="BP60" s="38" t="n"/>
-      <c r="BQ60" s="39" t="n"/>
+      <c r="BP60" s="25" t="n"/>
+      <c r="BQ60" s="27" t="n"/>
       <c r="BR60" s="28" t="n"/>
       <c r="BS60" s="28" t="n"/>
       <c r="BT60" s="28" t="n"/>
-      <c r="BU60" s="38" t="n"/>
+      <c r="BU60" s="25" t="n"/>
       <c r="BV60" s="29" t="n"/>
       <c r="BW60" s="24" t="n"/>
-      <c r="BX60" s="40" t="n"/>
-      <c r="BY60" s="39" t="n"/>
+      <c r="BX60" s="30" t="n"/>
+      <c r="BY60" s="27" t="n"/>
       <c r="BZ60" s="24" t="n"/>
       <c r="CA60" s="31" t="n"/>
     </row>
@@ -15605,7 +15574,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J61" s="38" t="n"/>
+      <c r="J61" s="25" t="n"/>
       <c r="K61" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -15614,7 +15583,7 @@
       <c r="L61" s="26" t="n">
         <v>-355</v>
       </c>
-      <c r="M61" s="39" t="n">
+      <c r="M61" s="27" t="n">
         <v>1.28169</v>
       </c>
       <c r="N61" s="28" t="n">
@@ -15654,11 +15623,11 @@
       <c r="X61" s="26" t="n">
         <v>74</v>
       </c>
-      <c r="Y61" s="38" t="n"/>
+      <c r="Y61" s="25" t="n"/>
       <c r="Z61" s="26" t="n"/>
       <c r="AA61" s="28" t="n"/>
       <c r="AB61" s="28" t="n"/>
-      <c r="AC61" s="40" t="n">
+      <c r="AC61" s="30" t="n">
         <v>0.5634</v>
       </c>
       <c r="AD61" s="24" t="inlineStr">
@@ -15705,11 +15674,11 @@
         </is>
       </c>
       <c r="BI61" s="24" t="n"/>
-      <c r="BJ61" s="38" t="n"/>
+      <c r="BJ61" s="25" t="n"/>
       <c r="BK61" s="26" t="n">
         <v>-355</v>
       </c>
-      <c r="BL61" s="39" t="n">
+      <c r="BL61" s="27" t="n">
         <v>1.28169</v>
       </c>
       <c r="BM61" s="28" t="n">
@@ -15719,16 +15688,16 @@
         <v>0.772277</v>
       </c>
       <c r="BO61" s="28" t="n"/>
-      <c r="BP61" s="38" t="n"/>
-      <c r="BQ61" s="39" t="n"/>
+      <c r="BP61" s="25" t="n"/>
+      <c r="BQ61" s="27" t="n"/>
       <c r="BR61" s="28" t="n"/>
       <c r="BS61" s="28" t="n"/>
       <c r="BT61" s="28" t="n"/>
-      <c r="BU61" s="38" t="n"/>
+      <c r="BU61" s="25" t="n"/>
       <c r="BV61" s="29" t="n"/>
       <c r="BW61" s="24" t="n"/>
-      <c r="BX61" s="40" t="n"/>
-      <c r="BY61" s="39" t="n"/>
+      <c r="BX61" s="30" t="n"/>
+      <c r="BY61" s="27" t="n"/>
       <c r="BZ61" s="24" t="n"/>
       <c r="CA61" s="31" t="n"/>
     </row>
@@ -15778,7 +15747,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J62" s="38" t="n"/>
+      <c r="J62" s="25" t="n"/>
       <c r="K62" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -15787,7 +15756,7 @@
       <c r="L62" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="M62" s="39" t="n">
+      <c r="M62" s="27" t="n">
         <v>2.13</v>
       </c>
       <c r="N62" s="28" t="n">
@@ -15819,11 +15788,11 @@
       <c r="V62" s="24" t="n"/>
       <c r="W62" s="26" t="n"/>
       <c r="X62" s="26" t="n"/>
-      <c r="Y62" s="38" t="n"/>
+      <c r="Y62" s="25" t="n"/>
       <c r="Z62" s="26" t="n"/>
       <c r="AA62" s="28" t="n"/>
       <c r="AB62" s="28" t="n"/>
-      <c r="AC62" s="40" t="n"/>
+      <c r="AC62" s="30" t="n"/>
       <c r="AD62" s="24" t="n"/>
       <c r="AE62" s="31" t="inlineStr">
         <is>
@@ -15954,11 +15923,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ62" s="38" t="n"/>
+      <c r="BJ62" s="25" t="n"/>
       <c r="BK62" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="BL62" s="39" t="n">
+      <c r="BL62" s="27" t="n">
         <v>2.13</v>
       </c>
       <c r="BM62" s="28" t="n">
@@ -15968,16 +15937,16 @@
         <v>0.467662</v>
       </c>
       <c r="BO62" s="28" t="n"/>
-      <c r="BP62" s="38" t="n"/>
-      <c r="BQ62" s="39" t="n"/>
+      <c r="BP62" s="25" t="n"/>
+      <c r="BQ62" s="27" t="n"/>
       <c r="BR62" s="28" t="n"/>
       <c r="BS62" s="28" t="n"/>
       <c r="BT62" s="28" t="n"/>
-      <c r="BU62" s="38" t="n"/>
+      <c r="BU62" s="25" t="n"/>
       <c r="BV62" s="29" t="n"/>
       <c r="BW62" s="24" t="n"/>
-      <c r="BX62" s="40" t="n"/>
-      <c r="BY62" s="39" t="n"/>
+      <c r="BX62" s="30" t="n"/>
+      <c r="BY62" s="27" t="n"/>
       <c r="BZ62" s="24" t="n"/>
       <c r="CA62" s="31" t="n"/>
     </row>
@@ -16027,7 +15996,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J63" s="38" t="n"/>
+      <c r="J63" s="25" t="n"/>
       <c r="K63" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16036,7 +16005,7 @@
       <c r="L63" s="26" t="n">
         <v>125</v>
       </c>
-      <c r="M63" s="39" t="n">
+      <c r="M63" s="27" t="n">
         <v>2.25</v>
       </c>
       <c r="N63" s="28" t="n">
@@ -16068,11 +16037,11 @@
       <c r="V63" s="24" t="n"/>
       <c r="W63" s="26" t="n"/>
       <c r="X63" s="26" t="n"/>
-      <c r="Y63" s="38" t="n"/>
+      <c r="Y63" s="25" t="n"/>
       <c r="Z63" s="26" t="n"/>
       <c r="AA63" s="28" t="n"/>
       <c r="AB63" s="28" t="n"/>
-      <c r="AC63" s="40" t="n"/>
+      <c r="AC63" s="30" t="n"/>
       <c r="AD63" s="24" t="n"/>
       <c r="AE63" s="31" t="inlineStr">
         <is>
@@ -16203,11 +16172,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ63" s="38" t="n"/>
+      <c r="BJ63" s="25" t="n"/>
       <c r="BK63" s="26" t="n">
         <v>125</v>
       </c>
-      <c r="BL63" s="39" t="n">
+      <c r="BL63" s="27" t="n">
         <v>2.25</v>
       </c>
       <c r="BM63" s="28" t="n">
@@ -16217,16 +16186,16 @@
         <v>0.442786</v>
       </c>
       <c r="BO63" s="28" t="n"/>
-      <c r="BP63" s="38" t="n"/>
-      <c r="BQ63" s="39" t="n"/>
+      <c r="BP63" s="25" t="n"/>
+      <c r="BQ63" s="27" t="n"/>
       <c r="BR63" s="28" t="n"/>
       <c r="BS63" s="28" t="n"/>
       <c r="BT63" s="28" t="n"/>
-      <c r="BU63" s="38" t="n"/>
+      <c r="BU63" s="25" t="n"/>
       <c r="BV63" s="29" t="n"/>
       <c r="BW63" s="24" t="n"/>
-      <c r="BX63" s="40" t="n"/>
-      <c r="BY63" s="39" t="n"/>
+      <c r="BX63" s="30" t="n"/>
+      <c r="BY63" s="27" t="n"/>
       <c r="BZ63" s="24" t="n"/>
       <c r="CA63" s="31" t="n"/>
     </row>
@@ -16276,7 +16245,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J64" s="38" t="n"/>
+      <c r="J64" s="25" t="n"/>
       <c r="K64" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16285,7 +16254,7 @@
       <c r="L64" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M64" s="39" t="n">
+      <c r="M64" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N64" s="28" t="n">
@@ -16317,11 +16286,11 @@
       <c r="V64" s="24" t="n"/>
       <c r="W64" s="26" t="n"/>
       <c r="X64" s="26" t="n"/>
-      <c r="Y64" s="38" t="n"/>
+      <c r="Y64" s="25" t="n"/>
       <c r="Z64" s="26" t="n"/>
       <c r="AA64" s="28" t="n"/>
       <c r="AB64" s="28" t="n"/>
-      <c r="AC64" s="40" t="n"/>
+      <c r="AC64" s="30" t="n"/>
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
@@ -16452,11 +16421,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ64" s="38" t="n"/>
+      <c r="BJ64" s="25" t="n"/>
       <c r="BK64" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL64" s="39" t="n">
+      <c r="BL64" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM64" s="28" t="n">
@@ -16466,16 +16435,16 @@
         <v>0.517413</v>
       </c>
       <c r="BO64" s="28" t="n"/>
-      <c r="BP64" s="38" t="n"/>
-      <c r="BQ64" s="39" t="n"/>
+      <c r="BP64" s="25" t="n"/>
+      <c r="BQ64" s="27" t="n"/>
       <c r="BR64" s="28" t="n"/>
       <c r="BS64" s="28" t="n"/>
       <c r="BT64" s="28" t="n"/>
-      <c r="BU64" s="38" t="n"/>
+      <c r="BU64" s="25" t="n"/>
       <c r="BV64" s="29" t="n"/>
       <c r="BW64" s="24" t="n"/>
-      <c r="BX64" s="40" t="n"/>
-      <c r="BY64" s="39" t="n"/>
+      <c r="BX64" s="30" t="n"/>
+      <c r="BY64" s="27" t="n"/>
       <c r="BZ64" s="24" t="n"/>
       <c r="CA64" s="31" t="n"/>
     </row>
@@ -16525,7 +16494,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J65" s="38" t="n"/>
+      <c r="J65" s="25" t="n"/>
       <c r="K65" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16534,7 +16503,7 @@
       <c r="L65" s="26" t="n">
         <v>-147</v>
       </c>
-      <c r="M65" s="39" t="n">
+      <c r="M65" s="27" t="n">
         <v>1.680272</v>
       </c>
       <c r="N65" s="28" t="n">
@@ -16566,11 +16535,11 @@
       <c r="V65" s="24" t="n"/>
       <c r="W65" s="26" t="n"/>
       <c r="X65" s="26" t="n"/>
-      <c r="Y65" s="38" t="n"/>
+      <c r="Y65" s="25" t="n"/>
       <c r="Z65" s="26" t="n"/>
       <c r="AA65" s="28" t="n"/>
       <c r="AB65" s="28" t="n"/>
-      <c r="AC65" s="40" t="n"/>
+      <c r="AC65" s="30" t="n"/>
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
@@ -16701,11 +16670,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ65" s="38" t="n"/>
+      <c r="BJ65" s="25" t="n"/>
       <c r="BK65" s="26" t="n">
         <v>-147</v>
       </c>
-      <c r="BL65" s="39" t="n">
+      <c r="BL65" s="27" t="n">
         <v>1.680272</v>
       </c>
       <c r="BM65" s="28" t="n">
@@ -16715,16 +16684,16 @@
         <v>0.59204</v>
       </c>
       <c r="BO65" s="28" t="n"/>
-      <c r="BP65" s="38" t="n"/>
-      <c r="BQ65" s="39" t="n"/>
+      <c r="BP65" s="25" t="n"/>
+      <c r="BQ65" s="27" t="n"/>
       <c r="BR65" s="28" t="n"/>
       <c r="BS65" s="28" t="n"/>
       <c r="BT65" s="28" t="n"/>
-      <c r="BU65" s="38" t="n"/>
+      <c r="BU65" s="25" t="n"/>
       <c r="BV65" s="29" t="n"/>
       <c r="BW65" s="24" t="n"/>
-      <c r="BX65" s="40" t="n"/>
-      <c r="BY65" s="39" t="n"/>
+      <c r="BX65" s="30" t="n"/>
+      <c r="BY65" s="27" t="n"/>
       <c r="BZ65" s="24" t="n"/>
       <c r="CA65" s="31" t="n"/>
     </row>
@@ -16774,7 +16743,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J66" s="38" t="n"/>
+      <c r="J66" s="25" t="n"/>
       <c r="K66" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16783,7 +16752,7 @@
       <c r="L66" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M66" s="39" t="n">
+      <c r="M66" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="N66" s="28" t="n">
@@ -16815,11 +16784,11 @@
       <c r="V66" s="24" t="n"/>
       <c r="W66" s="26" t="n"/>
       <c r="X66" s="26" t="n"/>
-      <c r="Y66" s="38" t="n"/>
+      <c r="Y66" s="25" t="n"/>
       <c r="Z66" s="26" t="n"/>
       <c r="AA66" s="28" t="n"/>
       <c r="AB66" s="28" t="n"/>
-      <c r="AC66" s="40" t="n"/>
+      <c r="AC66" s="30" t="n"/>
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
@@ -16950,11 +16919,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ66" s="38" t="n"/>
+      <c r="BJ66" s="25" t="n"/>
       <c r="BK66" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL66" s="39" t="n">
+      <c r="BL66" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM66" s="28" t="n">
@@ -16964,16 +16933,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO66" s="28" t="n"/>
-      <c r="BP66" s="38" t="n"/>
-      <c r="BQ66" s="39" t="n"/>
+      <c r="BP66" s="25" t="n"/>
+      <c r="BQ66" s="27" t="n"/>
       <c r="BR66" s="28" t="n"/>
       <c r="BS66" s="28" t="n"/>
       <c r="BT66" s="28" t="n"/>
-      <c r="BU66" s="38" t="n"/>
+      <c r="BU66" s="25" t="n"/>
       <c r="BV66" s="29" t="n"/>
       <c r="BW66" s="24" t="n"/>
-      <c r="BX66" s="40" t="n"/>
-      <c r="BY66" s="39" t="n"/>
+      <c r="BX66" s="30" t="n"/>
+      <c r="BY66" s="27" t="n"/>
       <c r="BZ66" s="24" t="n"/>
       <c r="CA66" s="31" t="n"/>
     </row>
@@ -17023,7 +16992,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J67" s="38" t="n"/>
+      <c r="J67" s="25" t="n"/>
       <c r="K67" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17032,7 +17001,7 @@
       <c r="L67" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M67" s="39" t="n">
+      <c r="M67" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N67" s="28" t="n">
@@ -17064,11 +17033,11 @@
       <c r="V67" s="24" t="n"/>
       <c r="W67" s="26" t="n"/>
       <c r="X67" s="26" t="n"/>
-      <c r="Y67" s="38" t="n"/>
+      <c r="Y67" s="25" t="n"/>
       <c r="Z67" s="26" t="n"/>
       <c r="AA67" s="28" t="n"/>
       <c r="AB67" s="28" t="n"/>
-      <c r="AC67" s="40" t="n"/>
+      <c r="AC67" s="30" t="n"/>
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
@@ -17199,11 +17168,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ67" s="38" t="n"/>
+      <c r="BJ67" s="25" t="n"/>
       <c r="BK67" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL67" s="39" t="n">
+      <c r="BL67" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM67" s="28" t="n">
@@ -17213,16 +17182,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO67" s="28" t="n"/>
-      <c r="BP67" s="38" t="n"/>
-      <c r="BQ67" s="39" t="n"/>
+      <c r="BP67" s="25" t="n"/>
+      <c r="BQ67" s="27" t="n"/>
       <c r="BR67" s="28" t="n"/>
       <c r="BS67" s="28" t="n"/>
       <c r="BT67" s="28" t="n"/>
-      <c r="BU67" s="38" t="n"/>
+      <c r="BU67" s="25" t="n"/>
       <c r="BV67" s="29" t="n"/>
       <c r="BW67" s="24" t="n"/>
-      <c r="BX67" s="40" t="n"/>
-      <c r="BY67" s="39" t="n"/>
+      <c r="BX67" s="30" t="n"/>
+      <c r="BY67" s="27" t="n"/>
       <c r="BZ67" s="24" t="n"/>
       <c r="CA67" s="31" t="n"/>
     </row>
@@ -17272,7 +17241,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J68" s="38" t="n"/>
+      <c r="J68" s="25" t="n"/>
       <c r="K68" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17281,7 +17250,7 @@
       <c r="L68" s="26" t="n">
         <v>-199</v>
       </c>
-      <c r="M68" s="39" t="n">
+      <c r="M68" s="27" t="n">
         <v>1.502513</v>
       </c>
       <c r="N68" s="28" t="n">
@@ -17313,11 +17282,11 @@
       <c r="V68" s="24" t="n"/>
       <c r="W68" s="26" t="n"/>
       <c r="X68" s="26" t="n"/>
-      <c r="Y68" s="38" t="n"/>
+      <c r="Y68" s="25" t="n"/>
       <c r="Z68" s="26" t="n"/>
       <c r="AA68" s="28" t="n"/>
       <c r="AB68" s="28" t="n"/>
-      <c r="AC68" s="40" t="n"/>
+      <c r="AC68" s="30" t="n"/>
       <c r="AD68" s="24" t="n"/>
       <c r="AE68" s="31" t="inlineStr">
         <is>
@@ -17448,11 +17417,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ68" s="38" t="n"/>
+      <c r="BJ68" s="25" t="n"/>
       <c r="BK68" s="26" t="n">
         <v>-199</v>
       </c>
-      <c r="BL68" s="39" t="n">
+      <c r="BL68" s="27" t="n">
         <v>1.502513</v>
       </c>
       <c r="BM68" s="28" t="n">
@@ -17462,16 +17431,16 @@
         <v>0.6616919999999999</v>
       </c>
       <c r="BO68" s="28" t="n"/>
-      <c r="BP68" s="38" t="n"/>
-      <c r="BQ68" s="39" t="n"/>
+      <c r="BP68" s="25" t="n"/>
+      <c r="BQ68" s="27" t="n"/>
       <c r="BR68" s="28" t="n"/>
       <c r="BS68" s="28" t="n"/>
       <c r="BT68" s="28" t="n"/>
-      <c r="BU68" s="38" t="n"/>
+      <c r="BU68" s="25" t="n"/>
       <c r="BV68" s="29" t="n"/>
       <c r="BW68" s="24" t="n"/>
-      <c r="BX68" s="40" t="n"/>
-      <c r="BY68" s="39" t="n"/>
+      <c r="BX68" s="30" t="n"/>
+      <c r="BY68" s="27" t="n"/>
       <c r="BZ68" s="24" t="n"/>
       <c r="CA68" s="31" t="n"/>
     </row>
@@ -17521,7 +17490,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J69" s="38" t="n"/>
+      <c r="J69" s="25" t="n"/>
       <c r="K69" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17530,7 +17499,7 @@
       <c r="L69" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M69" s="39" t="n">
+      <c r="M69" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="N69" s="28" t="n">
@@ -17562,11 +17531,11 @@
       <c r="V69" s="24" t="n"/>
       <c r="W69" s="26" t="n"/>
       <c r="X69" s="26" t="n"/>
-      <c r="Y69" s="38" t="n"/>
+      <c r="Y69" s="25" t="n"/>
       <c r="Z69" s="26" t="n"/>
       <c r="AA69" s="28" t="n"/>
       <c r="AB69" s="28" t="n"/>
-      <c r="AC69" s="40" t="n"/>
+      <c r="AC69" s="30" t="n"/>
       <c r="AD69" s="24" t="n"/>
       <c r="AE69" s="31" t="inlineStr">
         <is>
@@ -17697,11 +17666,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ69" s="38" t="n"/>
+      <c r="BJ69" s="25" t="n"/>
       <c r="BK69" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL69" s="39" t="n">
+      <c r="BL69" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM69" s="28" t="n">
@@ -17711,16 +17680,16 @@
         <v>0.522388</v>
       </c>
       <c r="BO69" s="28" t="n"/>
-      <c r="BP69" s="38" t="n"/>
-      <c r="BQ69" s="39" t="n"/>
+      <c r="BP69" s="25" t="n"/>
+      <c r="BQ69" s="27" t="n"/>
       <c r="BR69" s="28" t="n"/>
       <c r="BS69" s="28" t="n"/>
       <c r="BT69" s="28" t="n"/>
-      <c r="BU69" s="38" t="n"/>
+      <c r="BU69" s="25" t="n"/>
       <c r="BV69" s="29" t="n"/>
       <c r="BW69" s="24" t="n"/>
-      <c r="BX69" s="40" t="n"/>
-      <c r="BY69" s="39" t="n"/>
+      <c r="BX69" s="30" t="n"/>
+      <c r="BY69" s="27" t="n"/>
       <c r="BZ69" s="24" t="n"/>
       <c r="CA69" s="31" t="n"/>
     </row>
@@ -17770,7 +17739,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J70" s="38" t="n"/>
+      <c r="J70" s="25" t="n"/>
       <c r="K70" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17779,7 +17748,7 @@
       <c r="L70" s="26" t="n">
         <v>-160</v>
       </c>
-      <c r="M70" s="39" t="n">
+      <c r="M70" s="27" t="n">
         <v>1.625</v>
       </c>
       <c r="N70" s="28" t="n">
@@ -17811,11 +17780,11 @@
       <c r="V70" s="24" t="n"/>
       <c r="W70" s="26" t="n"/>
       <c r="X70" s="26" t="n"/>
-      <c r="Y70" s="38" t="n"/>
+      <c r="Y70" s="25" t="n"/>
       <c r="Z70" s="26" t="n"/>
       <c r="AA70" s="28" t="n"/>
       <c r="AB70" s="28" t="n"/>
-      <c r="AC70" s="40" t="n"/>
+      <c r="AC70" s="30" t="n"/>
       <c r="AD70" s="24" t="n"/>
       <c r="AE70" s="31" t="inlineStr">
         <is>
@@ -17946,11 +17915,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ70" s="38" t="n"/>
+      <c r="BJ70" s="25" t="n"/>
       <c r="BK70" s="26" t="n">
         <v>-160</v>
       </c>
-      <c r="BL70" s="39" t="n">
+      <c r="BL70" s="27" t="n">
         <v>1.625</v>
       </c>
       <c r="BM70" s="28" t="n">
@@ -17960,16 +17929,16 @@
         <v>0.61194</v>
       </c>
       <c r="BO70" s="28" t="n"/>
-      <c r="BP70" s="38" t="n"/>
-      <c r="BQ70" s="39" t="n"/>
+      <c r="BP70" s="25" t="n"/>
+      <c r="BQ70" s="27" t="n"/>
       <c r="BR70" s="28" t="n"/>
       <c r="BS70" s="28" t="n"/>
       <c r="BT70" s="28" t="n"/>
-      <c r="BU70" s="38" t="n"/>
+      <c r="BU70" s="25" t="n"/>
       <c r="BV70" s="29" t="n"/>
       <c r="BW70" s="24" t="n"/>
-      <c r="BX70" s="40" t="n"/>
-      <c r="BY70" s="39" t="n"/>
+      <c r="BX70" s="30" t="n"/>
+      <c r="BY70" s="27" t="n"/>
       <c r="BZ70" s="24" t="n"/>
       <c r="CA70" s="31" t="n"/>
     </row>
@@ -18019,7 +17988,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J71" s="38" t="n"/>
+      <c r="J71" s="25" t="n"/>
       <c r="K71" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -18028,7 +17997,7 @@
       <c r="L71" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M71" s="39" t="n">
+      <c r="M71" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N71" s="28" t="n">
@@ -18060,11 +18029,11 @@
       <c r="V71" s="24" t="n"/>
       <c r="W71" s="26" t="n"/>
       <c r="X71" s="26" t="n"/>
-      <c r="Y71" s="38" t="n"/>
+      <c r="Y71" s="25" t="n"/>
       <c r="Z71" s="26" t="n"/>
       <c r="AA71" s="28" t="n"/>
       <c r="AB71" s="28" t="n"/>
-      <c r="AC71" s="40" t="n"/>
+      <c r="AC71" s="30" t="n"/>
       <c r="AD71" s="24" t="n"/>
       <c r="AE71" s="31" t="inlineStr">
         <is>
@@ -18195,11 +18164,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ71" s="38" t="n"/>
+      <c r="BJ71" s="25" t="n"/>
       <c r="BK71" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL71" s="39" t="n">
+      <c r="BL71" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM71" s="28" t="n">
@@ -18209,16 +18178,16 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO71" s="28" t="n"/>
-      <c r="BP71" s="38" t="n"/>
-      <c r="BQ71" s="39" t="n"/>
+      <c r="BP71" s="25" t="n"/>
+      <c r="BQ71" s="27" t="n"/>
       <c r="BR71" s="28" t="n"/>
       <c r="BS71" s="28" t="n"/>
       <c r="BT71" s="28" t="n"/>
-      <c r="BU71" s="38" t="n"/>
+      <c r="BU71" s="25" t="n"/>
       <c r="BV71" s="29" t="n"/>
       <c r="BW71" s="24" t="n"/>
-      <c r="BX71" s="40" t="n"/>
-      <c r="BY71" s="39" t="n"/>
+      <c r="BX71" s="30" t="n"/>
+      <c r="BY71" s="27" t="n"/>
       <c r="BZ71" s="24" t="n"/>
       <c r="CA71" s="31" t="n"/>
     </row>
@@ -18268,7 +18237,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J72" s="38" t="n"/>
+      <c r="J72" s="25" t="n"/>
       <c r="K72" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -18277,7 +18246,7 @@
       <c r="L72" s="26" t="n">
         <v>-115</v>
       </c>
-      <c r="M72" s="39" t="n">
+      <c r="M72" s="27" t="n">
         <v>1.869565</v>
       </c>
       <c r="N72" s="28" t="n">
@@ -18309,11 +18278,11 @@
       <c r="V72" s="24" t="n"/>
       <c r="W72" s="26" t="n"/>
       <c r="X72" s="26" t="n"/>
-      <c r="Y72" s="38" t="n"/>
+      <c r="Y72" s="25" t="n"/>
       <c r="Z72" s="26" t="n"/>
       <c r="AA72" s="28" t="n"/>
       <c r="AB72" s="28" t="n"/>
-      <c r="AC72" s="40" t="n"/>
+      <c r="AC72" s="30" t="n"/>
       <c r="AD72" s="24" t="n"/>
       <c r="AE72" s="31" t="inlineStr">
         <is>
@@ -18444,11 +18413,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ72" s="38" t="n"/>
+      <c r="BJ72" s="25" t="n"/>
       <c r="BK72" s="26" t="n">
         <v>-115</v>
       </c>
-      <c r="BL72" s="39" t="n">
+      <c r="BL72" s="27" t="n">
         <v>1.869565</v>
       </c>
       <c r="BM72" s="28" t="n">
@@ -18458,16 +18427,16 @@
         <v>0.532338</v>
       </c>
       <c r="BO72" s="28" t="n"/>
-      <c r="BP72" s="38" t="n"/>
-      <c r="BQ72" s="39" t="n"/>
+      <c r="BP72" s="25" t="n"/>
+      <c r="BQ72" s="27" t="n"/>
       <c r="BR72" s="28" t="n"/>
       <c r="BS72" s="28" t="n"/>
       <c r="BT72" s="28" t="n"/>
-      <c r="BU72" s="38" t="n"/>
+      <c r="BU72" s="25" t="n"/>
       <c r="BV72" s="29" t="n"/>
       <c r="BW72" s="24" t="n"/>
-      <c r="BX72" s="40" t="n"/>
-      <c r="BY72" s="39" t="n"/>
+      <c r="BX72" s="30" t="n"/>
+      <c r="BY72" s="27" t="n"/>
       <c r="BZ72" s="24" t="n"/>
       <c r="CA72" s="31" t="n"/>
     </row>
@@ -18517,7 +18486,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J73" s="38" t="n"/>
+      <c r="J73" s="25" t="n"/>
       <c r="K73" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -18526,7 +18495,7 @@
       <c r="L73" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="M73" s="39" t="n">
+      <c r="M73" s="27" t="n">
         <v>1.854701</v>
       </c>
       <c r="N73" s="28" t="n">
@@ -18558,11 +18527,11 @@
       <c r="V73" s="24" t="n"/>
       <c r="W73" s="26" t="n"/>
       <c r="X73" s="26" t="n"/>
-      <c r="Y73" s="38" t="n"/>
+      <c r="Y73" s="25" t="n"/>
       <c r="Z73" s="26" t="n"/>
       <c r="AA73" s="28" t="n"/>
       <c r="AB73" s="28" t="n"/>
-      <c r="AC73" s="40" t="n"/>
+      <c r="AC73" s="30" t="n"/>
       <c r="AD73" s="24" t="n"/>
       <c r="AE73" s="31" t="inlineStr">
         <is>
@@ -18693,11 +18662,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ73" s="38" t="n"/>
+      <c r="BJ73" s="25" t="n"/>
       <c r="BK73" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="BL73" s="39" t="n">
+      <c r="BL73" s="27" t="n">
         <v>1.854701</v>
       </c>
       <c r="BM73" s="28" t="n">
@@ -18707,16 +18676,16 @@
         <v>0.537313</v>
       </c>
       <c r="BO73" s="28" t="n"/>
-      <c r="BP73" s="38" t="n"/>
-      <c r="BQ73" s="39" t="n"/>
+      <c r="BP73" s="25" t="n"/>
+      <c r="BQ73" s="27" t="n"/>
       <c r="BR73" s="28" t="n"/>
       <c r="BS73" s="28" t="n"/>
       <c r="BT73" s="28" t="n"/>
-      <c r="BU73" s="38" t="n"/>
+      <c r="BU73" s="25" t="n"/>
       <c r="BV73" s="29" t="n"/>
       <c r="BW73" s="24" t="n"/>
-      <c r="BX73" s="40" t="n"/>
-      <c r="BY73" s="39" t="n"/>
+      <c r="BX73" s="30" t="n"/>
+      <c r="BY73" s="27" t="n"/>
       <c r="BZ73" s="24" t="n"/>
       <c r="CA73" s="31" t="n"/>
     </row>
@@ -18766,7 +18735,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J74" s="38" t="n"/>
+      <c r="J74" s="25" t="n"/>
       <c r="K74" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -18775,7 +18744,7 @@
       <c r="L74" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="M74" s="39" t="n">
+      <c r="M74" s="27" t="n">
         <v>1.694444</v>
       </c>
       <c r="N74" s="28" t="n">
@@ -18807,11 +18776,11 @@
       <c r="V74" s="24" t="n"/>
       <c r="W74" s="26" t="n"/>
       <c r="X74" s="26" t="n"/>
-      <c r="Y74" s="38" t="n"/>
+      <c r="Y74" s="25" t="n"/>
       <c r="Z74" s="26" t="n"/>
       <c r="AA74" s="28" t="n"/>
       <c r="AB74" s="28" t="n"/>
-      <c r="AC74" s="40" t="n"/>
+      <c r="AC74" s="30" t="n"/>
       <c r="AD74" s="24" t="n"/>
       <c r="AE74" s="31" t="inlineStr">
         <is>
@@ -18942,11 +18911,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ74" s="38" t="n"/>
+      <c r="BJ74" s="25" t="n"/>
       <c r="BK74" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="BL74" s="39" t="n">
+      <c r="BL74" s="27" t="n">
         <v>1.694444</v>
       </c>
       <c r="BM74" s="28" t="n">
@@ -18956,16 +18925,16 @@
         <v>0.5870649999999999</v>
       </c>
       <c r="BO74" s="28" t="n"/>
-      <c r="BP74" s="38" t="n"/>
-      <c r="BQ74" s="39" t="n"/>
+      <c r="BP74" s="25" t="n"/>
+      <c r="BQ74" s="27" t="n"/>
       <c r="BR74" s="28" t="n"/>
       <c r="BS74" s="28" t="n"/>
       <c r="BT74" s="28" t="n"/>
-      <c r="BU74" s="38" t="n"/>
+      <c r="BU74" s="25" t="n"/>
       <c r="BV74" s="29" t="n"/>
       <c r="BW74" s="24" t="n"/>
-      <c r="BX74" s="40" t="n"/>
-      <c r="BY74" s="39" t="n"/>
+      <c r="BX74" s="30" t="n"/>
+      <c r="BY74" s="27" t="n"/>
       <c r="BZ74" s="24" t="n"/>
       <c r="CA74" s="31" t="n"/>
     </row>
@@ -19015,7 +18984,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J75" s="38" t="n"/>
+      <c r="J75" s="25" t="n"/>
       <c r="K75" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -19024,7 +18993,7 @@
       <c r="L75" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M75" s="39" t="n">
+      <c r="M75" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="N75" s="28" t="n">
@@ -19056,11 +19025,11 @@
       <c r="V75" s="24" t="n"/>
       <c r="W75" s="26" t="n"/>
       <c r="X75" s="26" t="n"/>
-      <c r="Y75" s="38" t="n"/>
+      <c r="Y75" s="25" t="n"/>
       <c r="Z75" s="26" t="n"/>
       <c r="AA75" s="28" t="n"/>
       <c r="AB75" s="28" t="n"/>
-      <c r="AC75" s="40" t="n"/>
+      <c r="AC75" s="30" t="n"/>
       <c r="AD75" s="24" t="n"/>
       <c r="AE75" s="31" t="inlineStr">
         <is>
@@ -19191,11 +19160,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ75" s="38" t="n"/>
+      <c r="BJ75" s="25" t="n"/>
       <c r="BK75" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL75" s="39" t="n">
+      <c r="BL75" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM75" s="28" t="n">
@@ -19205,16 +19174,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO75" s="28" t="n"/>
-      <c r="BP75" s="38" t="n"/>
-      <c r="BQ75" s="39" t="n"/>
+      <c r="BP75" s="25" t="n"/>
+      <c r="BQ75" s="27" t="n"/>
       <c r="BR75" s="28" t="n"/>
       <c r="BS75" s="28" t="n"/>
       <c r="BT75" s="28" t="n"/>
-      <c r="BU75" s="38" t="n"/>
+      <c r="BU75" s="25" t="n"/>
       <c r="BV75" s="29" t="n"/>
       <c r="BW75" s="24" t="n"/>
-      <c r="BX75" s="40" t="n"/>
-      <c r="BY75" s="39" t="n"/>
+      <c r="BX75" s="30" t="n"/>
+      <c r="BY75" s="27" t="n"/>
       <c r="BZ75" s="24" t="n"/>
       <c r="CA75" s="31" t="n"/>
     </row>
@@ -19264,7 +19233,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J76" s="38" t="n"/>
+      <c r="J76" s="25" t="n"/>
       <c r="K76" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -19273,7 +19242,7 @@
       <c r="L76" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M76" s="39" t="n">
+      <c r="M76" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="N76" s="28" t="n">
@@ -19305,11 +19274,11 @@
       <c r="V76" s="24" t="n"/>
       <c r="W76" s="26" t="n"/>
       <c r="X76" s="26" t="n"/>
-      <c r="Y76" s="38" t="n"/>
+      <c r="Y76" s="25" t="n"/>
       <c r="Z76" s="26" t="n"/>
       <c r="AA76" s="28" t="n"/>
       <c r="AB76" s="28" t="n"/>
-      <c r="AC76" s="40" t="n"/>
+      <c r="AC76" s="30" t="n"/>
       <c r="AD76" s="24" t="n"/>
       <c r="AE76" s="31" t="inlineStr">
         <is>
@@ -19440,11 +19409,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ76" s="38" t="n"/>
+      <c r="BJ76" s="25" t="n"/>
       <c r="BK76" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL76" s="39" t="n">
+      <c r="BL76" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="BM76" s="28" t="n">
@@ -19454,16 +19423,16 @@
         <v>0.492537</v>
       </c>
       <c r="BO76" s="28" t="n"/>
-      <c r="BP76" s="38" t="n"/>
-      <c r="BQ76" s="39" t="n"/>
+      <c r="BP76" s="25" t="n"/>
+      <c r="BQ76" s="27" t="n"/>
       <c r="BR76" s="28" t="n"/>
       <c r="BS76" s="28" t="n"/>
       <c r="BT76" s="28" t="n"/>
-      <c r="BU76" s="38" t="n"/>
+      <c r="BU76" s="25" t="n"/>
       <c r="BV76" s="29" t="n"/>
       <c r="BW76" s="24" t="n"/>
-      <c r="BX76" s="40" t="n"/>
-      <c r="BY76" s="39" t="n"/>
+      <c r="BX76" s="30" t="n"/>
+      <c r="BY76" s="27" t="n"/>
       <c r="BZ76" s="24" t="n"/>
       <c r="CA76" s="31" t="n"/>
     </row>
@@ -19513,7 +19482,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J77" s="38" t="n"/>
+      <c r="J77" s="25" t="n"/>
       <c r="K77" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -19522,7 +19491,7 @@
       <c r="L77" s="26" t="n">
         <v>-488</v>
       </c>
-      <c r="M77" s="39" t="n">
+      <c r="M77" s="27" t="n">
         <v>1.204918</v>
       </c>
       <c r="N77" s="28" t="n">
@@ -19554,11 +19523,11 @@
       <c r="V77" s="24" t="n"/>
       <c r="W77" s="26" t="n"/>
       <c r="X77" s="26" t="n"/>
-      <c r="Y77" s="38" t="n"/>
+      <c r="Y77" s="25" t="n"/>
       <c r="Z77" s="26" t="n"/>
       <c r="AA77" s="28" t="n"/>
       <c r="AB77" s="28" t="n"/>
-      <c r="AC77" s="40" t="n"/>
+      <c r="AC77" s="30" t="n"/>
       <c r="AD77" s="24" t="n"/>
       <c r="AE77" s="31" t="inlineStr">
         <is>
@@ -19689,11 +19658,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ77" s="38" t="n"/>
+      <c r="BJ77" s="25" t="n"/>
       <c r="BK77" s="26" t="n">
         <v>-488</v>
       </c>
-      <c r="BL77" s="39" t="n">
+      <c r="BL77" s="27" t="n">
         <v>1.204918</v>
       </c>
       <c r="BM77" s="28" t="n">
@@ -19703,16 +19672,16 @@
         <v>0.821782</v>
       </c>
       <c r="BO77" s="28" t="n"/>
-      <c r="BP77" s="38" t="n"/>
-      <c r="BQ77" s="39" t="n"/>
+      <c r="BP77" s="25" t="n"/>
+      <c r="BQ77" s="27" t="n"/>
       <c r="BR77" s="28" t="n"/>
       <c r="BS77" s="28" t="n"/>
       <c r="BT77" s="28" t="n"/>
-      <c r="BU77" s="38" t="n"/>
+      <c r="BU77" s="25" t="n"/>
       <c r="BV77" s="29" t="n"/>
       <c r="BW77" s="24" t="n"/>
-      <c r="BX77" s="40" t="n"/>
-      <c r="BY77" s="39" t="n"/>
+      <c r="BX77" s="30" t="n"/>
+      <c r="BY77" s="27" t="n"/>
       <c r="BZ77" s="24" t="n"/>
       <c r="CA77" s="31" t="n"/>
     </row>
@@ -19762,7 +19731,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J78" s="38" t="n"/>
+      <c r="J78" s="25" t="n"/>
       <c r="K78" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -19771,7 +19740,7 @@
       <c r="L78" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="M78" s="39" t="n">
+      <c r="M78" s="27" t="n">
         <v>2.5</v>
       </c>
       <c r="N78" s="28" t="n">
@@ -19803,11 +19772,11 @@
       <c r="V78" s="24" t="n"/>
       <c r="W78" s="26" t="n"/>
       <c r="X78" s="26" t="n"/>
-      <c r="Y78" s="38" t="n"/>
+      <c r="Y78" s="25" t="n"/>
       <c r="Z78" s="26" t="n"/>
       <c r="AA78" s="28" t="n"/>
       <c r="AB78" s="28" t="n"/>
-      <c r="AC78" s="40" t="n"/>
+      <c r="AC78" s="30" t="n"/>
       <c r="AD78" s="24" t="n"/>
       <c r="AE78" s="31" t="inlineStr">
         <is>
@@ -19938,11 +19907,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ78" s="38" t="n"/>
+      <c r="BJ78" s="25" t="n"/>
       <c r="BK78" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="BL78" s="39" t="n">
+      <c r="BL78" s="27" t="n">
         <v>2.5</v>
       </c>
       <c r="BM78" s="28" t="n">
@@ -19952,16 +19921,16 @@
         <v>0.39604</v>
       </c>
       <c r="BO78" s="28" t="n"/>
-      <c r="BP78" s="38" t="n"/>
-      <c r="BQ78" s="39" t="n"/>
+      <c r="BP78" s="25" t="n"/>
+      <c r="BQ78" s="27" t="n"/>
       <c r="BR78" s="28" t="n"/>
       <c r="BS78" s="28" t="n"/>
       <c r="BT78" s="28" t="n"/>
-      <c r="BU78" s="38" t="n"/>
+      <c r="BU78" s="25" t="n"/>
       <c r="BV78" s="29" t="n"/>
       <c r="BW78" s="24" t="n"/>
-      <c r="BX78" s="40" t="n"/>
-      <c r="BY78" s="39" t="n"/>
+      <c r="BX78" s="30" t="n"/>
+      <c r="BY78" s="27" t="n"/>
       <c r="BZ78" s="24" t="n"/>
       <c r="CA78" s="31" t="n"/>
     </row>
@@ -20011,7 +19980,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J79" s="38" t="n"/>
+      <c r="J79" s="25" t="n"/>
       <c r="K79" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -20020,7 +19989,7 @@
       <c r="L79" s="26" t="n">
         <v>-317</v>
       </c>
-      <c r="M79" s="39" t="n">
+      <c r="M79" s="27" t="n">
         <v>1.315457</v>
       </c>
       <c r="N79" s="28" t="n">
@@ -20052,11 +20021,11 @@
       <c r="V79" s="24" t="n"/>
       <c r="W79" s="26" t="n"/>
       <c r="X79" s="26" t="n"/>
-      <c r="Y79" s="38" t="n"/>
+      <c r="Y79" s="25" t="n"/>
       <c r="Z79" s="26" t="n"/>
       <c r="AA79" s="28" t="n"/>
       <c r="AB79" s="28" t="n"/>
-      <c r="AC79" s="40" t="n"/>
+      <c r="AC79" s="30" t="n"/>
       <c r="AD79" s="24" t="n"/>
       <c r="AE79" s="31" t="inlineStr">
         <is>
@@ -20187,11 +20156,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ79" s="38" t="n"/>
+      <c r="BJ79" s="25" t="n"/>
       <c r="BK79" s="26" t="n">
         <v>-317</v>
       </c>
-      <c r="BL79" s="39" t="n">
+      <c r="BL79" s="27" t="n">
         <v>1.315457</v>
       </c>
       <c r="BM79" s="28" t="n">
@@ -20201,16 +20170,16 @@
         <v>0.752475</v>
       </c>
       <c r="BO79" s="28" t="n"/>
-      <c r="BP79" s="38" t="n"/>
-      <c r="BQ79" s="39" t="n"/>
+      <c r="BP79" s="25" t="n"/>
+      <c r="BQ79" s="27" t="n"/>
       <c r="BR79" s="28" t="n"/>
       <c r="BS79" s="28" t="n"/>
       <c r="BT79" s="28" t="n"/>
-      <c r="BU79" s="38" t="n"/>
+      <c r="BU79" s="25" t="n"/>
       <c r="BV79" s="29" t="n"/>
       <c r="BW79" s="24" t="n"/>
-      <c r="BX79" s="40" t="n"/>
-      <c r="BY79" s="39" t="n"/>
+      <c r="BX79" s="30" t="n"/>
+      <c r="BY79" s="27" t="n"/>
       <c r="BZ79" s="24" t="n"/>
       <c r="CA79" s="31" t="n"/>
     </row>
@@ -20260,7 +20229,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J80" s="38" t="n"/>
+      <c r="J80" s="25" t="n"/>
       <c r="K80" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -20269,7 +20238,7 @@
       <c r="L80" s="26" t="n">
         <v>-456</v>
       </c>
-      <c r="M80" s="39" t="n">
+      <c r="M80" s="27" t="n">
         <v>1.219298</v>
       </c>
       <c r="N80" s="28" t="n">
@@ -20301,11 +20270,11 @@
       <c r="V80" s="24" t="n"/>
       <c r="W80" s="26" t="n"/>
       <c r="X80" s="26" t="n"/>
-      <c r="Y80" s="38" t="n"/>
+      <c r="Y80" s="25" t="n"/>
       <c r="Z80" s="26" t="n"/>
       <c r="AA80" s="28" t="n"/>
       <c r="AB80" s="28" t="n"/>
-      <c r="AC80" s="40" t="n"/>
+      <c r="AC80" s="30" t="n"/>
       <c r="AD80" s="24" t="n"/>
       <c r="AE80" s="31" t="inlineStr">
         <is>
@@ -20436,11 +20405,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ80" s="38" t="n"/>
+      <c r="BJ80" s="25" t="n"/>
       <c r="BK80" s="26" t="n">
         <v>-456</v>
       </c>
-      <c r="BL80" s="39" t="n">
+      <c r="BL80" s="27" t="n">
         <v>1.219298</v>
       </c>
       <c r="BM80" s="28" t="n">
@@ -20450,28 +20419,28 @@
         <v>0.811881</v>
       </c>
       <c r="BO80" s="28" t="n"/>
-      <c r="BP80" s="38" t="n"/>
-      <c r="BQ80" s="39" t="n"/>
+      <c r="BP80" s="25" t="n"/>
+      <c r="BQ80" s="27" t="n"/>
       <c r="BR80" s="28" t="n"/>
       <c r="BS80" s="28" t="n"/>
       <c r="BT80" s="28" t="n"/>
-      <c r="BU80" s="38" t="n"/>
+      <c r="BU80" s="25" t="n"/>
       <c r="BV80" s="29" t="n"/>
       <c r="BW80" s="24" t="n"/>
-      <c r="BX80" s="40" t="n"/>
-      <c r="BY80" s="39" t="n"/>
+      <c r="BX80" s="30" t="n"/>
+      <c r="BY80" s="27" t="n"/>
       <c r="BZ80" s="24" t="n"/>
       <c r="CA80" s="31" t="n"/>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>8f572bd4fec54325</t>
+          <t>1a48e42752fa4d4d</t>
         </is>
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:49.855665Z</t>
+          <t>2026-07-20T16:43:23.198474Z</t>
         </is>
       </c>
       <c r="C81" s="24" t="inlineStr">
@@ -20509,7 +20478,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J81" s="38" t="n"/>
+      <c r="J81" s="25" t="n"/>
       <c r="K81" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -20518,24 +20487,24 @@
       <c r="L81" s="26" t="n">
         <v>144</v>
       </c>
-      <c r="M81" s="39" t="n">
+      <c r="M81" s="27" t="n">
         <v>2.44</v>
       </c>
       <c r="N81" s="28" t="n">
         <v>0.409836</v>
       </c>
       <c r="O81" s="28" t="n">
-        <v>0.527501</v>
+        <v>0.597574</v>
       </c>
       <c r="P81" s="28" t="n"/>
       <c r="Q81" s="28" t="n">
-        <v>0.117501</v>
+        <v>0.187574</v>
       </c>
       <c r="R81" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S81" s="29" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="T81" s="24" t="inlineStr">
         <is>
@@ -20550,11 +20519,11 @@
       <c r="V81" s="24" t="n"/>
       <c r="W81" s="26" t="n"/>
       <c r="X81" s="26" t="n"/>
-      <c r="Y81" s="38" t="n"/>
+      <c r="Y81" s="25" t="n"/>
       <c r="Z81" s="26" t="n"/>
       <c r="AA81" s="28" t="n"/>
       <c r="AB81" s="28" t="n"/>
-      <c r="AC81" s="40" t="n"/>
+      <c r="AC81" s="30" t="n"/>
       <c r="AD81" s="24" t="n"/>
       <c r="AE81" s="31" t="inlineStr">
         <is>
@@ -20642,7 +20611,7 @@
       </c>
       <c r="BA81" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
         </is>
       </c>
       <c r="BB81" s="24" t="inlineStr">
@@ -20657,7 +20626,7 @@
       </c>
       <c r="BD81" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
         </is>
       </c>
       <c r="BE81" s="24" t="inlineStr">
@@ -20677,7 +20646,7 @@
       </c>
       <c r="BH81" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:49.855665Z</t>
+          <t>2026-07-20T16:43:23.198474Z</t>
         </is>
       </c>
       <c r="BI81" s="24" t="inlineStr">
@@ -20685,11 +20654,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ81" s="38" t="n"/>
+      <c r="BJ81" s="25" t="n"/>
       <c r="BK81" s="26" t="n">
         <v>144</v>
       </c>
-      <c r="BL81" s="39" t="n">
+      <c r="BL81" s="27" t="n">
         <v>2.44</v>
       </c>
       <c r="BM81" s="28" t="n">
@@ -20697,28 +20666,28 @@
       </c>
       <c r="BN81" s="28" t="n"/>
       <c r="BO81" s="28" t="n"/>
-      <c r="BP81" s="38" t="n"/>
-      <c r="BQ81" s="39" t="n"/>
+      <c r="BP81" s="25" t="n"/>
+      <c r="BQ81" s="27" t="n"/>
       <c r="BR81" s="28" t="n"/>
       <c r="BS81" s="28" t="n"/>
       <c r="BT81" s="28" t="n"/>
-      <c r="BU81" s="38" t="n"/>
+      <c r="BU81" s="25" t="n"/>
       <c r="BV81" s="29" t="n"/>
       <c r="BW81" s="24" t="n"/>
-      <c r="BX81" s="40" t="n"/>
-      <c r="BY81" s="39" t="n"/>
+      <c r="BX81" s="30" t="n"/>
+      <c r="BY81" s="27" t="n"/>
       <c r="BZ81" s="24" t="n"/>
       <c r="CA81" s="31" t="n"/>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
         <is>
-          <t>04bc614189f44e85</t>
+          <t>c8a2ce99ec2b4bb4</t>
         </is>
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:50.077952Z</t>
+          <t>2026-07-20T16:43:23.412348Z</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
@@ -20753,10 +20722,10 @@
       </c>
       <c r="I82" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J82" s="38" t="n"/>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J82" s="25" t="n"/>
       <c r="K82" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -20765,24 +20734,24 @@
       <c r="L82" s="26" t="n">
         <v>186</v>
       </c>
-      <c r="M82" s="39" t="n">
+      <c r="M82" s="27" t="n">
         <v>2.86</v>
       </c>
       <c r="N82" s="28" t="n">
         <v>0.34965</v>
       </c>
       <c r="O82" s="28" t="n">
-        <v>0.533959</v>
+        <v>0.597891</v>
       </c>
       <c r="P82" s="28" t="n"/>
       <c r="Q82" s="28" t="n">
-        <v>0.183959</v>
+        <v>0.247891</v>
       </c>
       <c r="R82" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S82" s="29" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="T82" s="24" t="inlineStr">
         <is>
@@ -20797,11 +20766,11 @@
       <c r="V82" s="24" t="n"/>
       <c r="W82" s="26" t="n"/>
       <c r="X82" s="26" t="n"/>
-      <c r="Y82" s="38" t="n"/>
+      <c r="Y82" s="25" t="n"/>
       <c r="Z82" s="26" t="n"/>
       <c r="AA82" s="28" t="n"/>
       <c r="AB82" s="28" t="n"/>
-      <c r="AC82" s="40" t="n"/>
+      <c r="AC82" s="30" t="n"/>
       <c r="AD82" s="24" t="n"/>
       <c r="AE82" s="31" t="inlineStr">
         <is>
@@ -20889,7 +20858,7 @@
       </c>
       <c r="BA82" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
         </is>
       </c>
       <c r="BB82" s="24" t="inlineStr">
@@ -20904,7 +20873,7 @@
       </c>
       <c r="BD82" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
         </is>
       </c>
       <c r="BE82" s="24" t="inlineStr">
@@ -20924,7 +20893,7 @@
       </c>
       <c r="BH82" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:50.077952Z</t>
+          <t>2026-07-20T16:43:23.412348Z</t>
         </is>
       </c>
       <c r="BI82" s="24" t="inlineStr">
@@ -20932,11 +20901,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ82" s="38" t="n"/>
+      <c r="BJ82" s="25" t="n"/>
       <c r="BK82" s="26" t="n">
         <v>186</v>
       </c>
-      <c r="BL82" s="39" t="n">
+      <c r="BL82" s="27" t="n">
         <v>2.86</v>
       </c>
       <c r="BM82" s="28" t="n">
@@ -20944,28 +20913,28 @@
       </c>
       <c r="BN82" s="28" t="n"/>
       <c r="BO82" s="28" t="n"/>
-      <c r="BP82" s="38" t="n"/>
-      <c r="BQ82" s="39" t="n"/>
+      <c r="BP82" s="25" t="n"/>
+      <c r="BQ82" s="27" t="n"/>
       <c r="BR82" s="28" t="n"/>
       <c r="BS82" s="28" t="n"/>
       <c r="BT82" s="28" t="n"/>
-      <c r="BU82" s="38" t="n"/>
+      <c r="BU82" s="25" t="n"/>
       <c r="BV82" s="29" t="n"/>
       <c r="BW82" s="24" t="n"/>
-      <c r="BX82" s="40" t="n"/>
-      <c r="BY82" s="39" t="n"/>
+      <c r="BX82" s="30" t="n"/>
+      <c r="BY82" s="27" t="n"/>
       <c r="BZ82" s="24" t="n"/>
       <c r="CA82" s="31" t="n"/>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="24" t="inlineStr">
         <is>
-          <t>d4cef3f0c09a4253</t>
+          <t>59e23c595c724c2d</t>
         </is>
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:50.272162Z</t>
+          <t>2026-07-20T16:43:23.600706Z</t>
         </is>
       </c>
       <c r="C83" s="24" t="inlineStr">
@@ -21000,10 +20969,10 @@
       </c>
       <c r="I83" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J83" s="38" t="n"/>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J83" s="25" t="n"/>
       <c r="K83" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -21012,24 +20981,24 @@
       <c r="L83" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="M83" s="39" t="n">
+      <c r="M83" s="27" t="n">
         <v>1.694444</v>
       </c>
       <c r="N83" s="28" t="n">
         <v>0.590164</v>
       </c>
       <c r="O83" s="28" t="n">
-        <v>0.524075</v>
+        <v>0.537815</v>
       </c>
       <c r="P83" s="28" t="n"/>
       <c r="Q83" s="28" t="n">
-        <v>-0.065925</v>
+        <v>-0.052185</v>
       </c>
       <c r="R83" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S83" s="29" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="T83" s="24" t="inlineStr">
         <is>
@@ -21044,11 +21013,11 @@
       <c r="V83" s="24" t="n"/>
       <c r="W83" s="26" t="n"/>
       <c r="X83" s="26" t="n"/>
-      <c r="Y83" s="38" t="n"/>
+      <c r="Y83" s="25" t="n"/>
       <c r="Z83" s="26" t="n"/>
       <c r="AA83" s="28" t="n"/>
       <c r="AB83" s="28" t="n"/>
-      <c r="AC83" s="40" t="n"/>
+      <c r="AC83" s="30" t="n"/>
       <c r="AD83" s="24" t="n"/>
       <c r="AE83" s="31" t="inlineStr">
         <is>
@@ -21136,7 +21105,7 @@
       </c>
       <c r="BA83" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
         </is>
       </c>
       <c r="BB83" s="24" t="inlineStr">
@@ -21151,7 +21120,7 @@
       </c>
       <c r="BD83" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
         </is>
       </c>
       <c r="BE83" s="24" t="inlineStr">
@@ -21171,7 +21140,7 @@
       </c>
       <c r="BH83" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:50.272162Z</t>
+          <t>2026-07-20T16:43:23.600706Z</t>
         </is>
       </c>
       <c r="BI83" s="24" t="inlineStr">
@@ -21179,11 +21148,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ83" s="38" t="n"/>
+      <c r="BJ83" s="25" t="n"/>
       <c r="BK83" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="BL83" s="39" t="n">
+      <c r="BL83" s="27" t="n">
         <v>1.694444</v>
       </c>
       <c r="BM83" s="28" t="n">
@@ -21191,38 +21160,38 @@
       </c>
       <c r="BN83" s="28" t="n"/>
       <c r="BO83" s="28" t="n"/>
-      <c r="BP83" s="38" t="n"/>
-      <c r="BQ83" s="39" t="n"/>
+      <c r="BP83" s="25" t="n"/>
+      <c r="BQ83" s="27" t="n"/>
       <c r="BR83" s="28" t="n"/>
       <c r="BS83" s="28" t="n"/>
       <c r="BT83" s="28" t="n"/>
-      <c r="BU83" s="38" t="n"/>
+      <c r="BU83" s="25" t="n"/>
       <c r="BV83" s="29" t="n"/>
       <c r="BW83" s="24" t="n"/>
-      <c r="BX83" s="40" t="n"/>
-      <c r="BY83" s="39" t="n"/>
+      <c r="BX83" s="30" t="n"/>
+      <c r="BY83" s="27" t="n"/>
       <c r="BZ83" s="24" t="n"/>
       <c r="CA83" s="31" t="n"/>
     </row>
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="24" t="inlineStr">
         <is>
-          <t>345e121461114afb</t>
+          <t>13b3d8aeb7054f14</t>
         </is>
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:57.353876Z</t>
+          <t>2026-07-20T16:43:29.969000Z</t>
         </is>
       </c>
       <c r="C84" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T17:00:00Z</t>
+          <t>2026-07-20T21:00:00Z</t>
         </is>
       </c>
       <c r="D84" s="24" t="inlineStr">
         <is>
-          <t>56113</t>
+          <t>54669</t>
         </is>
       </c>
       <c r="E84" s="24" t="inlineStr">
@@ -21232,12 +21201,12 @@
       </c>
       <c r="F84" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>QUINTESSÊNCIA</t>
         </is>
       </c>
       <c r="G84" s="24" t="inlineStr">
         <is>
-          <t>Endless Journey</t>
+          <t>MIBR Academy</t>
         </is>
       </c>
       <c r="H84" s="24" t="inlineStr">
@@ -21247,33 +21216,33 @@
       </c>
       <c r="I84" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J84" s="38" t="n"/>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J84" s="25" t="n"/>
       <c r="K84" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L84" s="26" t="n">
-        <v>113</v>
-      </c>
-      <c r="M84" s="39" t="n">
-        <v>2.13</v>
+        <v>-223</v>
+      </c>
+      <c r="M84" s="27" t="n">
+        <v>1.44843</v>
       </c>
       <c r="N84" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.690402</v>
       </c>
       <c r="O84" s="28" t="n">
-        <v>0.576217</v>
+        <v>0.5805439999999999</v>
       </c>
       <c r="P84" s="28" t="n"/>
       <c r="Q84" s="28" t="n">
-        <v>0.106217</v>
+        <v>-0.109456</v>
       </c>
       <c r="R84" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S84" s="29" t="n">
         <v>1.25</v>
@@ -21291,15 +21260,15 @@
       <c r="V84" s="24" t="n"/>
       <c r="W84" s="26" t="n"/>
       <c r="X84" s="26" t="n"/>
-      <c r="Y84" s="38" t="n"/>
+      <c r="Y84" s="25" t="n"/>
       <c r="Z84" s="26" t="n"/>
       <c r="AA84" s="28" t="n"/>
       <c r="AB84" s="28" t="n"/>
-      <c r="AC84" s="40" t="n"/>
+      <c r="AC84" s="30" t="n"/>
       <c r="AD84" s="24" t="n"/>
       <c r="AE84" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (aec-cs2-ica-ej-2026-07-20).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (aec-cs2-mibra-quin-2026-07-20).</t>
         </is>
       </c>
       <c r="AF84" s="31" t="inlineStr">
@@ -21340,32 +21309,32 @@
       </c>
       <c r="AP84" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>QUINTESSÊNCIA</t>
         </is>
       </c>
       <c r="AQ84" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>QUINTESSÊNCIA</t>
         </is>
       </c>
       <c r="AR84" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>QUINTESSÊNCIA</t>
         </is>
       </c>
       <c r="AS84" s="24" t="inlineStr">
         <is>
-          <t>Endless Journey</t>
+          <t>MIBR Academy</t>
         </is>
       </c>
       <c r="AT84" s="24" t="inlineStr">
         <is>
-          <t>Endless Journey</t>
+          <t>MIBR Academy</t>
         </is>
       </c>
       <c r="AU84" s="24" t="inlineStr">
         <is>
-          <t>Endless Journey</t>
+          <t>MIBR Academy</t>
         </is>
       </c>
       <c r="AV84" s="24" t="n"/>
@@ -21383,7 +21352,7 @@
       </c>
       <c r="BA84" s="24" t="inlineStr">
         <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+          <t>8ec29f8dd1985b5dbc96c1339c99e2a2129c4afa4af6efce101e4f76d99dce85</t>
         </is>
       </c>
       <c r="BB84" s="24" t="inlineStr">
@@ -21398,7 +21367,7 @@
       </c>
       <c r="BD84" s="24" t="inlineStr">
         <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+          <t>8ec29f8dd1985b5dbc96c1339c99e2a2129c4afa4af6efce101e4f76d99dce85</t>
         </is>
       </c>
       <c r="BE84" s="24" t="inlineStr">
@@ -21418,7 +21387,7 @@
       </c>
       <c r="BH84" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:57.353876Z</t>
+          <t>2026-07-20T16:43:29.969000Z</t>
         </is>
       </c>
       <c r="BI84" s="24" t="inlineStr">
@@ -21426,40 +21395,40 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ84" s="38" t="n"/>
+      <c r="BJ84" s="25" t="n"/>
       <c r="BK84" s="26" t="n">
-        <v>113</v>
-      </c>
-      <c r="BL84" s="39" t="n">
-        <v>2.13</v>
+        <v>-223</v>
+      </c>
+      <c r="BL84" s="27" t="n">
+        <v>1.44843</v>
       </c>
       <c r="BM84" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.690402</v>
       </c>
       <c r="BN84" s="28" t="n"/>
       <c r="BO84" s="28" t="n"/>
-      <c r="BP84" s="38" t="n"/>
-      <c r="BQ84" s="39" t="n"/>
+      <c r="BP84" s="25" t="n"/>
+      <c r="BQ84" s="27" t="n"/>
       <c r="BR84" s="28" t="n"/>
       <c r="BS84" s="28" t="n"/>
       <c r="BT84" s="28" t="n"/>
-      <c r="BU84" s="38" t="n"/>
+      <c r="BU84" s="25" t="n"/>
       <c r="BV84" s="29" t="n"/>
       <c r="BW84" s="24" t="n"/>
-      <c r="BX84" s="40" t="n"/>
-      <c r="BY84" s="39" t="n"/>
+      <c r="BX84" s="30" t="n"/>
+      <c r="BY84" s="27" t="n"/>
       <c r="BZ84" s="24" t="n"/>
       <c r="CA84" s="31" t="n"/>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>26f9b7dd6b974bf6</t>
+          <t>b56aaa797c2a4200</t>
         </is>
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:57.577880Z</t>
+          <t>2026-07-20T16:43:30.199856Z</t>
         </is>
       </c>
       <c r="C85" s="24" t="inlineStr">
@@ -21469,7 +21438,7 @@
       </c>
       <c r="D85" s="24" t="inlineStr">
         <is>
-          <t>54669</t>
+          <t>54672</t>
         </is>
       </c>
       <c r="E85" s="24" t="inlineStr">
@@ -21479,12 +21448,12 @@
       </c>
       <c r="F85" s="24" t="inlineStr">
         <is>
-          <t>QUINTESSÊNCIA</t>
+          <t>METANOIA WOLVES</t>
         </is>
       </c>
       <c r="G85" s="24" t="inlineStr">
         <is>
-          <t>MIBR Academy</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="H85" s="24" t="inlineStr">
@@ -21497,33 +21466,33 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J85" s="38" t="n"/>
+      <c r="J85" s="25" t="n"/>
       <c r="K85" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L85" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M85" s="39" t="n">
-        <v>1.44843</v>
+        <v>-144</v>
+      </c>
+      <c r="M85" s="27" t="n">
+        <v>1.694444</v>
       </c>
       <c r="N85" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.590164</v>
       </c>
       <c r="O85" s="28" t="n">
-        <v>0.580016</v>
+        <v>0.719007</v>
       </c>
       <c r="P85" s="28" t="n"/>
       <c r="Q85" s="28" t="n">
-        <v>-0.109984</v>
+        <v>0.129007</v>
       </c>
       <c r="R85" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S85" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T85" s="24" t="inlineStr">
         <is>
@@ -21538,15 +21507,15 @@
       <c r="V85" s="24" t="n"/>
       <c r="W85" s="26" t="n"/>
       <c r="X85" s="26" t="n"/>
-      <c r="Y85" s="38" t="n"/>
+      <c r="Y85" s="25" t="n"/>
       <c r="Z85" s="26" t="n"/>
       <c r="AA85" s="28" t="n"/>
       <c r="AB85" s="28" t="n"/>
-      <c r="AC85" s="40" t="n"/>
+      <c r="AC85" s="30" t="n"/>
       <c r="AD85" s="24" t="n"/>
       <c r="AE85" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (aec-cs2-mibra-quin-2026-07-20).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (aec-cs2-reda-mw-2026-07-20).</t>
         </is>
       </c>
       <c r="AF85" s="31" t="inlineStr">
@@ -21587,32 +21556,32 @@
       </c>
       <c r="AP85" s="24" t="inlineStr">
         <is>
-          <t>QUINTESSÊNCIA</t>
+          <t>METANOIA WOLVES</t>
         </is>
       </c>
       <c r="AQ85" s="24" t="inlineStr">
         <is>
-          <t>QUINTESSÊNCIA</t>
+          <t>METANOIA WOLVES</t>
         </is>
       </c>
       <c r="AR85" s="24" t="inlineStr">
         <is>
-          <t>QUINTESSÊNCIA</t>
+          <t>METANOIA WOLVES</t>
         </is>
       </c>
       <c r="AS85" s="24" t="inlineStr">
         <is>
-          <t>MIBR Academy</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="AT85" s="24" t="inlineStr">
         <is>
-          <t>MIBR Academy</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="AU85" s="24" t="inlineStr">
         <is>
-          <t>MIBR Academy</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="AV85" s="24" t="n"/>
@@ -21630,7 +21599,7 @@
       </c>
       <c r="BA85" s="24" t="inlineStr">
         <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+          <t>8ec29f8dd1985b5dbc96c1339c99e2a2129c4afa4af6efce101e4f76d99dce85</t>
         </is>
       </c>
       <c r="BB85" s="24" t="inlineStr">
@@ -21645,7 +21614,7 @@
       </c>
       <c r="BD85" s="24" t="inlineStr">
         <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+          <t>8ec29f8dd1985b5dbc96c1339c99e2a2129c4afa4af6efce101e4f76d99dce85</t>
         </is>
       </c>
       <c r="BE85" s="24" t="inlineStr">
@@ -21665,7 +21634,7 @@
       </c>
       <c r="BH85" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:57.577880Z</t>
+          <t>2026-07-20T16:43:30.199856Z</t>
         </is>
       </c>
       <c r="BI85" s="24" t="inlineStr">
@@ -21673,277 +21642,30 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ85" s="38" t="n"/>
+      <c r="BJ85" s="25" t="n"/>
       <c r="BK85" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL85" s="39" t="n">
-        <v>1.44843</v>
+        <v>-144</v>
+      </c>
+      <c r="BL85" s="27" t="n">
+        <v>1.694444</v>
       </c>
       <c r="BM85" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.590164</v>
       </c>
       <c r="BN85" s="28" t="n"/>
       <c r="BO85" s="28" t="n"/>
-      <c r="BP85" s="38" t="n"/>
-      <c r="BQ85" s="39" t="n"/>
+      <c r="BP85" s="25" t="n"/>
+      <c r="BQ85" s="27" t="n"/>
       <c r="BR85" s="28" t="n"/>
       <c r="BS85" s="28" t="n"/>
       <c r="BT85" s="28" t="n"/>
-      <c r="BU85" s="38" t="n"/>
+      <c r="BU85" s="25" t="n"/>
       <c r="BV85" s="29" t="n"/>
       <c r="BW85" s="24" t="n"/>
-      <c r="BX85" s="40" t="n"/>
-      <c r="BY85" s="39" t="n"/>
+      <c r="BX85" s="30" t="n"/>
+      <c r="BY85" s="27" t="n"/>
       <c r="BZ85" s="24" t="n"/>
       <c r="CA85" s="31" t="n"/>
-    </row>
-    <row r="86" ht="36" customHeight="1">
-      <c r="A86" s="24" t="inlineStr">
-        <is>
-          <t>1a2e4cd0bc214362</t>
-        </is>
-      </c>
-      <c r="B86" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:32:57.772821Z</t>
-        </is>
-      </c>
-      <c r="C86" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D86" s="24" t="inlineStr">
-        <is>
-          <t>54672</t>
-        </is>
-      </c>
-      <c r="E86" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F86" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="G86" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="H86" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I86" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J86" s="38" t="n"/>
-      <c r="K86" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L86" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M86" s="39" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N86" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O86" s="28" t="n">
-        <v>0.692542</v>
-      </c>
-      <c r="P86" s="28" t="n"/>
-      <c r="Q86" s="28" t="n">
-        <v>0.102542</v>
-      </c>
-      <c r="R86" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S86" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T86" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="U86" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V86" s="24" t="n"/>
-      <c r="W86" s="26" t="n"/>
-      <c r="X86" s="26" t="n"/>
-      <c r="Y86" s="38" t="n"/>
-      <c r="Z86" s="26" t="n"/>
-      <c r="AA86" s="28" t="n"/>
-      <c r="AB86" s="28" t="n"/>
-      <c r="AC86" s="40" t="n"/>
-      <c r="AD86" s="24" t="n"/>
-      <c r="AE86" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (aec-cs2-reda-mw-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF86" s="31" t="inlineStr">
-        <is>
-          <t>Research baseline; zero-unit shadow until qualified.</t>
-        </is>
-      </c>
-      <c r="AG86" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH86" s="24" t="n"/>
-      <c r="AI86" s="31" t="n"/>
-      <c r="AJ86" s="31" t="n"/>
-      <c r="AK86" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL86" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM86" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN86" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO86" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP86" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="AQ86" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="AR86" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="AS86" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="AT86" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="AU86" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="AV86" s="24" t="n"/>
-      <c r="AW86" s="24" t="n"/>
-      <c r="AX86" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY86" s="24" t="n"/>
-      <c r="AZ86" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA86" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BB86" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC86" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD86" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BE86" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF86" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG86" s="24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="BH86" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:32:57.772821Z</t>
-        </is>
-      </c>
-      <c r="BI86" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ86" s="38" t="n"/>
-      <c r="BK86" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL86" s="39" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM86" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN86" s="28" t="n"/>
-      <c r="BO86" s="28" t="n"/>
-      <c r="BP86" s="38" t="n"/>
-      <c r="BQ86" s="39" t="n"/>
-      <c r="BR86" s="28" t="n"/>
-      <c r="BS86" s="28" t="n"/>
-      <c r="BT86" s="28" t="n"/>
-      <c r="BU86" s="38" t="n"/>
-      <c r="BV86" s="29" t="n"/>
-      <c r="BW86" s="24" t="n"/>
-      <c r="BX86" s="40" t="n"/>
-      <c r="BY86" s="39" t="n"/>
-      <c r="BZ86" s="24" t="n"/>
-      <c r="CA86" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -20435,12 +20435,12 @@
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>1a48e42752fa4d4d</t>
+          <t>9a9d4b57a88e423c</t>
         </is>
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:43:23.198474Z</t>
+          <t>2026-07-20T16:47:44.302889Z</t>
         </is>
       </c>
       <c r="C81" s="24" t="inlineStr">
@@ -20646,7 +20646,7 @@
       </c>
       <c r="BH81" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:43:23.198474Z</t>
+          <t>2026-07-20T16:47:44.302889Z</t>
         </is>
       </c>
       <c r="BI81" s="24" t="inlineStr">
@@ -20682,12 +20682,12 @@
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
         <is>
-          <t>c8a2ce99ec2b4bb4</t>
+          <t>3317c6b205ce46df</t>
         </is>
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:43:23.412348Z</t>
+          <t>2026-07-20T16:47:44.584921Z</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
@@ -20707,14 +20707,14 @@
       </c>
       <c r="F82" s="24" t="inlineStr">
         <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="G82" s="24" t="inlineStr">
+        <is>
           <t>INTZ e-Sports</t>
         </is>
       </c>
-      <c r="G82" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
       <c r="H82" s="24" t="inlineStr">
         <is>
           <t>moneyline</t>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="I82" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J82" s="25" t="n"/>
@@ -20815,32 +20815,32 @@
       </c>
       <c r="AP82" s="24" t="inlineStr">
         <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AQ82" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AR82" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AS82" s="24" t="inlineStr">
+        <is>
           <t>INTZ e-Sports</t>
         </is>
       </c>
-      <c r="AQ82" s="24" t="inlineStr">
+      <c r="AT82" s="24" t="inlineStr">
         <is>
           <t>INTZ e-Sports</t>
         </is>
       </c>
-      <c r="AR82" s="24" t="inlineStr">
+      <c r="AU82" s="24" t="inlineStr">
         <is>
           <t>INTZ e-Sports</t>
-        </is>
-      </c>
-      <c r="AS82" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AT82" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AU82" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
         </is>
       </c>
       <c r="AV82" s="24" t="n"/>
@@ -20893,7 +20893,7 @@
       </c>
       <c r="BH82" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:43:23.412348Z</t>
+          <t>2026-07-20T16:47:44.584921Z</t>
         </is>
       </c>
       <c r="BI82" s="24" t="inlineStr">
@@ -20929,12 +20929,12 @@
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="24" t="inlineStr">
         <is>
-          <t>59e23c595c724c2d</t>
+          <t>e255a57d46ac4478</t>
         </is>
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:43:23.600706Z</t>
+          <t>2026-07-20T16:47:44.797663Z</t>
         </is>
       </c>
       <c r="C83" s="24" t="inlineStr">
@@ -20954,14 +20954,14 @@
       </c>
       <c r="F83" s="24" t="inlineStr">
         <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
           <t>Team Solid</t>
         </is>
       </c>
-      <c r="G83" s="24" t="inlineStr">
-        <is>
-          <t>RMD Gaming</t>
-        </is>
-      </c>
       <c r="H83" s="24" t="inlineStr">
         <is>
           <t>moneyline</t>
@@ -20969,7 +20969,7 @@
       </c>
       <c r="I83" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J83" s="25" t="n"/>
@@ -21062,32 +21062,32 @@
       </c>
       <c r="AP83" s="24" t="inlineStr">
         <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ83" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AR83" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AS83" s="24" t="inlineStr">
+        <is>
           <t>Team Solid</t>
         </is>
       </c>
-      <c r="AQ83" s="24" t="inlineStr">
+      <c r="AT83" s="24" t="inlineStr">
         <is>
           <t>Team Solid</t>
         </is>
       </c>
-      <c r="AR83" s="24" t="inlineStr">
+      <c r="AU83" s="24" t="inlineStr">
         <is>
           <t>Team Solid</t>
-        </is>
-      </c>
-      <c r="AS83" s="24" t="inlineStr">
-        <is>
-          <t>RMD Gaming</t>
-        </is>
-      </c>
-      <c r="AT83" s="24" t="inlineStr">
-        <is>
-          <t>RMD Gaming</t>
-        </is>
-      </c>
-      <c r="AU83" s="24" t="inlineStr">
-        <is>
-          <t>RMD Gaming</t>
         </is>
       </c>
       <c r="AV83" s="24" t="n"/>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="BH83" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:43:23.600706Z</t>
+          <t>2026-07-20T16:47:44.797663Z</t>
         </is>
       </c>
       <c r="BI83" s="24" t="inlineStr">
@@ -21176,12 +21176,12 @@
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="24" t="inlineStr">
         <is>
-          <t>13b3d8aeb7054f14</t>
+          <t>5eb5e85b3a8f4197</t>
         </is>
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:43:29.969000Z</t>
+          <t>2026-07-20T16:47:49.894690Z</t>
         </is>
       </c>
       <c r="C84" s="24" t="inlineStr">
@@ -21387,7 +21387,7 @@
       </c>
       <c r="BH84" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:43:29.969000Z</t>
+          <t>2026-07-20T16:47:49.894690Z</t>
         </is>
       </c>
       <c r="BI84" s="24" t="inlineStr">
@@ -21423,12 +21423,12 @@
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>b56aaa797c2a4200</t>
+          <t>081d51f5bea5463a</t>
         </is>
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:43:30.199856Z</t>
+          <t>2026-07-20T16:47:50.137639Z</t>
         </is>
       </c>
       <c r="C85" s="24" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="BH85" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:43:30.199856Z</t>
+          <t>2026-07-20T16:47:50.137639Z</t>
         </is>
       </c>
       <c r="BI85" s="24" t="inlineStr">

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -842,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB141"/>
+  <dimension ref="A1:CB154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1429,7 +1429,7 @@
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1705,7 +1705,7 @@
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1981,7 +1981,7 @@
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -2257,7 +2257,7 @@
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -2533,7 +2533,7 @@
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2809,7 +2809,7 @@
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -3085,7 +3085,7 @@
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -3361,7 +3361,7 @@
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -3913,7 +3913,7 @@
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -4189,7 +4189,7 @@
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -4465,7 +4465,7 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -4741,7 +4741,7 @@
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -4954,7 +4954,11 @@
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL15" t="n">
         <v>3</v>
       </c>
@@ -4991,7 +4995,7 @@
       <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -5188,7 +5192,11 @@
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL16" t="n">
         <v>3</v>
       </c>
@@ -5225,7 +5233,7 @@
       <c r="AW16" t="inlineStr"/>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -5422,7 +5430,11 @@
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL17" t="n">
         <v>3</v>
       </c>
@@ -5459,7 +5471,7 @@
       <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -5656,7 +5668,11 @@
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL18" t="n">
         <v>3</v>
       </c>
@@ -5693,7 +5709,7 @@
       <c r="AW18" t="inlineStr"/>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -5890,7 +5906,11 @@
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL19" t="n">
         <v>3</v>
       </c>
@@ -5927,7 +5947,7 @@
       <c r="AW19" t="inlineStr"/>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -6124,7 +6144,11 @@
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL20" t="n">
         <v>3</v>
       </c>
@@ -6161,7 +6185,7 @@
       <c r="AW20" t="inlineStr"/>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -6358,7 +6382,11 @@
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL21" t="n">
         <v>3</v>
       </c>
@@ -6395,7 +6423,7 @@
       <c r="AW21" t="inlineStr"/>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -6592,7 +6620,11 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL22" t="n">
         <v>3</v>
       </c>
@@ -6629,7 +6661,7 @@
       <c r="AW22" t="inlineStr"/>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -6889,7 +6921,7 @@
       <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -7165,7 +7197,7 @@
       <c r="AW24" t="inlineStr"/>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -7441,7 +7473,7 @@
       <c r="AW25" t="inlineStr"/>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -7717,7 +7749,7 @@
       <c r="AW26" t="inlineStr"/>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -7981,7 +8013,7 @@
       <c r="AW27" t="inlineStr"/>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -8245,7 +8277,7 @@
       <c r="AW28" t="inlineStr"/>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -8509,7 +8541,7 @@
       <c r="AW29" t="inlineStr"/>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -8773,7 +8805,7 @@
       <c r="AW30" t="inlineStr"/>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -9037,7 +9069,7 @@
       <c r="AW31" t="inlineStr"/>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -9301,7 +9333,7 @@
       <c r="AW32" t="inlineStr"/>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -9565,7 +9597,7 @@
       <c r="AW33" t="inlineStr"/>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -9829,7 +9861,7 @@
       <c r="AW34" t="inlineStr"/>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -10093,7 +10125,7 @@
       <c r="AW35" t="inlineStr"/>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -10357,7 +10389,7 @@
       <c r="AW36" t="inlineStr"/>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -10621,7 +10653,7 @@
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -10885,7 +10917,7 @@
       <c r="AW38" t="inlineStr"/>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -11149,7 +11181,7 @@
       <c r="AW39" t="inlineStr"/>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -11413,7 +11445,7 @@
       <c r="AW40" t="inlineStr"/>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -11608,7 +11640,7 @@
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL41" t="n">
@@ -11647,7 +11679,7 @@
       <c r="AW41" t="inlineStr"/>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>learned</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -11832,7 +11864,11 @@
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL42" t="n">
         <v>3</v>
       </c>
@@ -11869,7 +11905,7 @@
       <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -12066,7 +12102,11 @@
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL43" t="n">
         <v>3</v>
       </c>
@@ -12103,7 +12143,7 @@
       <c r="AW43" t="inlineStr"/>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -12300,7 +12340,11 @@
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL44" t="n">
         <v>3</v>
       </c>
@@ -12337,7 +12381,7 @@
       <c r="AW44" t="inlineStr"/>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -12534,7 +12578,11 @@
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL45" t="n">
         <v>3</v>
       </c>
@@ -12571,7 +12619,7 @@
       <c r="AW45" t="inlineStr"/>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -12768,7 +12816,11 @@
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL46" t="n">
         <v>3</v>
       </c>
@@ -12805,7 +12857,7 @@
       <c r="AW46" t="inlineStr"/>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -13000,7 +13052,11 @@
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL47" t="n">
         <v>3</v>
       </c>
@@ -13037,7 +13093,7 @@
       <c r="AW47" t="inlineStr"/>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -13224,7 +13280,11 @@
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL48" t="n">
         <v>3</v>
       </c>
@@ -13261,7 +13321,7 @@
       <c r="AW48" t="inlineStr"/>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -13448,7 +13508,11 @@
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
-      <c r="AK49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL49" t="n">
         <v>3</v>
       </c>
@@ -13485,7 +13549,7 @@
       <c r="AW49" t="inlineStr"/>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -13674,7 +13738,11 @@
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="inlineStr"/>
-      <c r="AK50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL50" t="n">
         <v>3</v>
       </c>
@@ -13711,7 +13779,7 @@
       <c r="AW50" t="inlineStr"/>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -13908,7 +13976,11 @@
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL51" t="n">
         <v>3</v>
       </c>
@@ -13945,7 +14017,7 @@
       <c r="AW51" t="inlineStr"/>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -14142,7 +14214,11 @@
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="inlineStr"/>
       <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL52" t="n">
         <v>3</v>
       </c>
@@ -14179,7 +14255,7 @@
       <c r="AW52" t="inlineStr"/>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -14376,7 +14452,11 @@
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL53" t="n">
         <v>3</v>
       </c>
@@ -14413,7 +14493,7 @@
       <c r="AW53" t="inlineStr"/>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -14608,7 +14688,11 @@
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL54" t="n">
         <v>3</v>
       </c>
@@ -14645,7 +14729,7 @@
       <c r="AW54" t="inlineStr"/>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -14832,7 +14916,11 @@
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
       <c r="AL55" t="n">
         <v>3</v>
       </c>
@@ -14869,7 +14957,7 @@
       <c r="AW55" t="inlineStr"/>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -15121,7 +15209,7 @@
       <c r="AW56" t="inlineStr"/>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -15385,7 +15473,7 @@
       <c r="AW57" t="inlineStr"/>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -15649,7 +15737,7 @@
       <c r="AW58" t="inlineStr"/>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -15913,7 +16001,7 @@
       <c r="AW59" t="inlineStr"/>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -16177,7 +16265,7 @@
       <c r="AW60" t="inlineStr"/>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -16441,7 +16529,7 @@
       <c r="AW61" t="inlineStr"/>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -16705,7 +16793,7 @@
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -16969,7 +17057,7 @@
       <c r="AW63" t="inlineStr"/>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -17233,7 +17321,7 @@
       <c r="AW64" t="inlineStr"/>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -17497,7 +17585,7 @@
       <c r="AW65" t="inlineStr"/>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -17761,7 +17849,7 @@
       <c r="AW66" t="inlineStr"/>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -18025,7 +18113,7 @@
       <c r="AW67" t="inlineStr"/>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -18289,7 +18377,7 @@
       <c r="AW68" t="inlineStr"/>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -18553,7 +18641,7 @@
       <c r="AW69" t="inlineStr"/>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -18817,7 +18905,7 @@
       <c r="AW70" t="inlineStr"/>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -19081,7 +19169,7 @@
       <c r="AW71" t="inlineStr"/>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -19345,7 +19433,7 @@
       <c r="AW72" t="inlineStr"/>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -19609,7 +19697,7 @@
       <c r="AW73" t="inlineStr"/>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -19873,7 +19961,7 @@
       <c r="AW74" t="inlineStr"/>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -20068,7 +20156,7 @@
       <c r="AJ75" t="inlineStr"/>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL75" t="n">
@@ -20123,7 +20211,7 @@
       <c r="AW75" t="inlineStr"/>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -20318,7 +20406,7 @@
       <c r="AJ76" t="inlineStr"/>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL76" t="n">
@@ -20373,7 +20461,7 @@
       <c r="AW76" t="inlineStr"/>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -20582,7 +20670,7 @@
       <c r="AJ77" t="inlineStr"/>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL77" t="n">
@@ -20637,7 +20725,7 @@
       <c r="AW77" t="inlineStr"/>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -20844,7 +20932,7 @@
       <c r="AJ78" t="inlineStr"/>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL78" t="n">
@@ -20899,7 +20987,7 @@
       <c r="AW78" t="inlineStr"/>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -21106,7 +21194,7 @@
       <c r="AJ79" t="inlineStr"/>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL79" t="n">
@@ -21161,7 +21249,7 @@
       <c r="AW79" t="inlineStr"/>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -21368,7 +21456,7 @@
       <c r="AJ80" t="inlineStr"/>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL80" t="n">
@@ -21423,7 +21511,7 @@
       <c r="AW80" t="inlineStr"/>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -21630,7 +21718,7 @@
       <c r="AJ81" t="inlineStr"/>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL81" t="n">
@@ -21685,7 +21773,7 @@
       <c r="AW81" t="inlineStr"/>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -21892,7 +21980,7 @@
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL82" t="n">
@@ -21947,7 +22035,7 @@
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -22154,7 +22242,7 @@
       <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL83" t="n">
@@ -22209,7 +22297,7 @@
       <c r="AW83" t="inlineStr"/>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -22416,7 +22504,7 @@
       <c r="AJ84" t="inlineStr"/>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL84" t="n">
@@ -22471,7 +22559,7 @@
       <c r="AW84" t="inlineStr"/>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -22678,7 +22766,7 @@
       <c r="AJ85" t="inlineStr"/>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL85" t="n">
@@ -22733,7 +22821,7 @@
       <c r="AW85" t="inlineStr"/>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -22940,7 +23028,7 @@
       <c r="AJ86" t="inlineStr"/>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL86" t="n">
@@ -22995,7 +23083,7 @@
       <c r="AW86" t="inlineStr"/>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -23188,7 +23276,7 @@
       <c r="AJ87" t="inlineStr"/>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL87" t="n">
@@ -23243,7 +23331,7 @@
       <c r="AW87" t="inlineStr"/>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -23436,7 +23524,7 @@
       <c r="AJ88" t="inlineStr"/>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL88" t="n">
@@ -23491,7 +23579,7 @@
       <c r="AW88" t="inlineStr"/>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -23684,7 +23772,7 @@
       <c r="AJ89" t="inlineStr"/>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL89" t="n">
@@ -23739,7 +23827,7 @@
       <c r="AW89" t="inlineStr"/>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -23932,7 +24020,7 @@
       <c r="AJ90" t="inlineStr"/>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL90" t="n">
@@ -23987,7 +24075,7 @@
       <c r="AW90" t="inlineStr"/>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -27379,7 +27467,7 @@
       <c r="AW103" t="inlineStr"/>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -27586,7 +27674,7 @@
       <c r="AJ104" t="inlineStr"/>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL104" t="n">
@@ -27641,7 +27729,7 @@
       <c r="AW104" t="inlineStr"/>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -27848,7 +27936,7 @@
       <c r="AJ105" t="inlineStr"/>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL105" t="n">
@@ -27903,7 +27991,7 @@
       <c r="AW105" t="inlineStr"/>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -28110,7 +28198,7 @@
       <c r="AJ106" t="inlineStr"/>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL106" t="n">
@@ -28165,7 +28253,7 @@
       <c r="AW106" t="inlineStr"/>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -28358,7 +28446,7 @@
       <c r="AJ107" t="inlineStr"/>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL107" t="n">
@@ -28413,7 +28501,7 @@
       <c r="AW107" t="inlineStr"/>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -28606,7 +28694,7 @@
       <c r="AJ108" t="inlineStr"/>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL108" t="n">
@@ -28661,7 +28749,7 @@
       <c r="AW108" t="inlineStr"/>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -28854,7 +28942,7 @@
       <c r="AJ109" t="inlineStr"/>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL109" t="n">
@@ -28909,7 +28997,7 @@
       <c r="AW109" t="inlineStr"/>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -29157,7 +29245,7 @@
       <c r="AW110" t="inlineStr"/>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -29405,7 +29493,7 @@
       <c r="AW111" t="inlineStr"/>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -29653,7 +29741,7 @@
       <c r="AW112" t="inlineStr"/>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -29901,7 +29989,7 @@
       <c r="AW113" t="inlineStr"/>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -30149,7 +30237,7 @@
       <c r="AW114" t="inlineStr"/>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -30397,7 +30485,7 @@
       <c r="AW115" t="inlineStr"/>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -30645,7 +30733,7 @@
       <c r="AW116" t="inlineStr"/>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -30893,7 +30981,7 @@
       <c r="AW117" t="inlineStr"/>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -31389,7 +31477,7 @@
       <c r="AW119" t="inlineStr"/>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -33373,7 +33461,7 @@
       <c r="AW127" t="inlineStr"/>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -33621,7 +33709,7 @@
       <c r="AW128" t="inlineStr"/>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -33869,7 +33957,7 @@
       <c r="AW129" t="inlineStr"/>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -34117,7 +34205,7 @@
       <c r="AW130" t="inlineStr"/>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -34365,7 +34453,7 @@
       <c r="AW131" t="inlineStr"/>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -34613,7 +34701,7 @@
       <c r="AW132" t="inlineStr"/>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -34861,7 +34949,7 @@
       <c r="AW133" t="inlineStr"/>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -35109,7 +35197,7 @@
       <c r="AW134" t="inlineStr"/>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -35357,7 +35445,7 @@
       <c r="AW135" t="inlineStr"/>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -35607,7 +35695,7 @@
       <c r="AW136" t="inlineStr"/>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -35857,7 +35945,7 @@
       <c r="AW137" t="inlineStr"/>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -36107,7 +36195,7 @@
       <c r="AW138" t="inlineStr"/>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -36355,7 +36443,7 @@
       <c r="AW139" t="inlineStr"/>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>statistical_model</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -36931,6 +37019,3478 @@
       <c r="CA141" t="inlineStr"/>
       <c r="CB141" t="inlineStr"/>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>48c8669ffc2149cc</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-07-18T17:37:17.255201Z</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-07-19T12:15:00-0400</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>401816171</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.549576</v>
+      </c>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="n">
+        <v>0.039772</v>
+      </c>
+      <c r="R142" t="n">
+        <v>39</v>
+      </c>
+      <c r="S142" t="n">
+        <v>1</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W142" t="n">
+        <v>3</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y142" t="inlineStr"/>
+      <c r="Z142" t="inlineStr"/>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr"/>
+      <c r="AC142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:34.426330Z</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5100; executable ask 0.5100 (aec-mlb-cws-tor-2026-07-19).</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr"/>
+      <c r="AI142" t="inlineStr"/>
+      <c r="AJ142" t="inlineStr"/>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN142" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>mlb-cws</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>mlb-tor</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr"/>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD142" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE142" t="inlineStr">
+        <is>
+          <t>50f6dab0538e7f4a</t>
+        </is>
+      </c>
+      <c r="BF142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG142" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH142" t="inlineStr">
+        <is>
+          <t>2026-07-18T17:36:34.425604Z</t>
+        </is>
+      </c>
+      <c r="BI142" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ142" t="inlineStr"/>
+      <c r="BK142" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.507463</v>
+      </c>
+      <c r="BO142" t="inlineStr"/>
+      <c r="BP142" t="inlineStr"/>
+      <c r="BQ142" t="inlineStr"/>
+      <c r="BR142" t="inlineStr"/>
+      <c r="BS142" t="inlineStr"/>
+      <c r="BT142" t="inlineStr"/>
+      <c r="BU142" t="inlineStr"/>
+      <c r="BV142" t="inlineStr"/>
+      <c r="BW142" t="inlineStr"/>
+      <c r="BX142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ142" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:34.426330Z</t>
+        </is>
+      </c>
+      <c r="CA142" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
+      <c r="CB142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>5290104d16c8463b</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-07-18T17:37:17.255201Z</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-07-19T13:35:00-0400</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>401816173</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>-111</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1.900901</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.526066</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.606009</v>
+      </c>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="n">
+        <v>0.079943</v>
+      </c>
+      <c r="R143" t="n">
+        <v>79</v>
+      </c>
+      <c r="S143" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W143" t="n">
+        <v>6</v>
+      </c>
+      <c r="X143" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y143" t="inlineStr"/>
+      <c r="Z143" t="inlineStr"/>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:34.633018Z</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5100; executable ask 0.5250 (aec-mlb-nym-phi-2026-07-19).</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr"/>
+      <c r="AI143" t="inlineStr"/>
+      <c r="AJ143" t="inlineStr"/>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL143" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN143" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>mlb-nym</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>mlb-phi</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr"/>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD143" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE143" t="inlineStr">
+        <is>
+          <t>ce93768fc5c8be02</t>
+        </is>
+      </c>
+      <c r="BF143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG143" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH143" t="inlineStr">
+        <is>
+          <t>2026-07-18T17:36:34.787099Z</t>
+        </is>
+      </c>
+      <c r="BI143" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ143" t="inlineStr"/>
+      <c r="BK143" t="n">
+        <v>-111</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>1.900901</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.526066</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.522388</v>
+      </c>
+      <c r="BO143" t="inlineStr"/>
+      <c r="BP143" t="inlineStr"/>
+      <c r="BQ143" t="inlineStr"/>
+      <c r="BR143" t="inlineStr"/>
+      <c r="BS143" t="inlineStr"/>
+      <c r="BT143" t="inlineStr"/>
+      <c r="BU143" t="inlineStr"/>
+      <c r="BV143" t="inlineStr"/>
+      <c r="BW143" t="inlineStr"/>
+      <c r="BX143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ143" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:34.633018Z</t>
+        </is>
+      </c>
+      <c r="CA143" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
+      <c r="CB143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>7a4271bd40494914</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-07-18T17:37:17.255201Z</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-07-19T13:35:00-0400</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>401816175</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M144" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0.550576</v>
+      </c>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="n">
+        <v>0.031345</v>
+      </c>
+      <c r="R144" t="n">
+        <v>31</v>
+      </c>
+      <c r="S144" t="n">
+        <v>1</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W144" t="n">
+        <v>1</v>
+      </c>
+      <c r="X144" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y144" t="inlineStr"/>
+      <c r="Z144" t="inlineStr"/>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:34.820097Z</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5100; executable ask 0.5200 (aec-mlb-tb-bos-2026-07-19).</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr"/>
+      <c r="AI144" t="inlineStr"/>
+      <c r="AJ144" t="inlineStr"/>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN144" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>mlb-tb</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>mlb-bos</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr"/>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE144" t="inlineStr">
+        <is>
+          <t>1e50d689e0ba0748</t>
+        </is>
+      </c>
+      <c r="BF144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG144" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH144" t="inlineStr">
+        <is>
+          <t>2026-07-18T17:36:36.879504Z</t>
+        </is>
+      </c>
+      <c r="BI144" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ144" t="inlineStr"/>
+      <c r="BK144" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM144" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN144" t="n">
+        <v>0.5148509999999999</v>
+      </c>
+      <c r="BO144" t="inlineStr"/>
+      <c r="BP144" t="inlineStr"/>
+      <c r="BQ144" t="inlineStr"/>
+      <c r="BR144" t="inlineStr"/>
+      <c r="BS144" t="inlineStr"/>
+      <c r="BT144" t="inlineStr"/>
+      <c r="BU144" t="inlineStr"/>
+      <c r="BV144" t="inlineStr"/>
+      <c r="BW144" t="inlineStr"/>
+      <c r="BX144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY144" t="n">
+        <v>0.925926</v>
+      </c>
+      <c r="BZ144" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:34.820097Z</t>
+        </is>
+      </c>
+      <c r="CA144" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
+      <c r="CB144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>6c30433f6943459a</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-07-18T17:37:17.255201Z</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-07-19T13:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>401816174</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>111</v>
+      </c>
+      <c r="M145" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0.473934</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0.564072</v>
+      </c>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="n">
+        <v>0.090138</v>
+      </c>
+      <c r="R145" t="n">
+        <v>90</v>
+      </c>
+      <c r="S145" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W145" t="n">
+        <v>7</v>
+      </c>
+      <c r="X145" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y145" t="inlineStr"/>
+      <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.008100Z</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5100; executable ask 0.4750 (aec-mlb-pit-cle-2026-07-19).</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr"/>
+      <c r="AI145" t="inlineStr"/>
+      <c r="AJ145" t="inlineStr"/>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL145" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN145" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>mlb-pit</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>mlb-cle</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr"/>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD145" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE145" t="inlineStr">
+        <is>
+          <t>5e36475e8b7bf75d</t>
+        </is>
+      </c>
+      <c r="BF145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG145" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH145" t="inlineStr">
+        <is>
+          <t>2026-07-18T17:36:37.946655Z</t>
+        </is>
+      </c>
+      <c r="BI145" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ145" t="inlineStr"/>
+      <c r="BK145" t="n">
+        <v>111</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>0.473934</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>0.472637</v>
+      </c>
+      <c r="BO145" t="inlineStr"/>
+      <c r="BP145" t="inlineStr"/>
+      <c r="BQ145" t="inlineStr"/>
+      <c r="BR145" t="inlineStr"/>
+      <c r="BS145" t="inlineStr"/>
+      <c r="BT145" t="inlineStr"/>
+      <c r="BU145" t="inlineStr"/>
+      <c r="BV145" t="inlineStr"/>
+      <c r="BW145" t="inlineStr"/>
+      <c r="BX145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ145" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.008100Z</t>
+        </is>
+      </c>
+      <c r="CA145" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
+      <c r="CB145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>a96ea6dd6b144441</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-07-18T17:37:17.255201Z</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-07-19T14:10:00-0400</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>401816178</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>-125</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0.555556</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0.607169</v>
+      </c>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="n">
+        <v>0.051613</v>
+      </c>
+      <c r="R146" t="n">
+        <v>51</v>
+      </c>
+      <c r="S146" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W146" t="n">
+        <v>1</v>
+      </c>
+      <c r="X146" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y146" t="inlineStr"/>
+      <c r="Z146" t="inlineStr"/>
+      <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="inlineStr"/>
+      <c r="AC146" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.195059Z</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5100; executable ask 0.5550 (aec-mlb-mia-mil-2026-07-19).</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr"/>
+      <c r="AI146" t="inlineStr"/>
+      <c r="AJ146" t="inlineStr"/>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL146" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN146" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>mlb-mia</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr"/>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD146" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE146" t="inlineStr">
+        <is>
+          <t>a0d9b1134dce1744</t>
+        </is>
+      </c>
+      <c r="BF146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG146" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH146" t="inlineStr">
+        <is>
+          <t>2026-07-18T17:36:41.204729Z</t>
+        </is>
+      </c>
+      <c r="BI146" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ146" t="inlineStr"/>
+      <c r="BK146" t="n">
+        <v>-125</v>
+      </c>
+      <c r="BL146" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>0.555556</v>
+      </c>
+      <c r="BN146" t="n">
+        <v>0.552239</v>
+      </c>
+      <c r="BO146" t="inlineStr"/>
+      <c r="BP146" t="inlineStr"/>
+      <c r="BQ146" t="inlineStr"/>
+      <c r="BR146" t="inlineStr"/>
+      <c r="BS146" t="inlineStr"/>
+      <c r="BT146" t="inlineStr"/>
+      <c r="BU146" t="inlineStr"/>
+      <c r="BV146" t="inlineStr"/>
+      <c r="BW146" t="inlineStr"/>
+      <c r="BX146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY146" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BZ146" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.195059Z</t>
+        </is>
+      </c>
+      <c r="CA146" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
+      <c r="CB146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>04b8c864fb464dd7</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-07-18T17:37:17.255201Z</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-07-19T14:10:00-0400</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>401816180</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>106</v>
+      </c>
+      <c r="M147" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0.485437</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0.520865</v>
+      </c>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="n">
+        <v>0.035428</v>
+      </c>
+      <c r="R147" t="n">
+        <v>35</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W147" t="n">
+        <v>19</v>
+      </c>
+      <c r="X147" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr"/>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
+      <c r="AC147" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.380420Z</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5100; executable ask 0.4850 (aec-mlb-sd-kc-2026-07-19).</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr"/>
+      <c r="AI147" t="inlineStr"/>
+      <c r="AJ147" t="inlineStr"/>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL147" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN147" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>mlb-sd</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>mlb-kc</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr"/>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD147" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE147" t="inlineStr">
+        <is>
+          <t>b9e5139f50e614b7</t>
+        </is>
+      </c>
+      <c r="BF147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG147" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH147" t="inlineStr">
+        <is>
+          <t>2026-07-18T17:36:40.632965Z</t>
+        </is>
+      </c>
+      <c r="BI147" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ147" t="inlineStr"/>
+      <c r="BK147" t="n">
+        <v>106</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>0.485437</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>0.482587</v>
+      </c>
+      <c r="BO147" t="inlineStr"/>
+      <c r="BP147" t="inlineStr"/>
+      <c r="BQ147" t="inlineStr"/>
+      <c r="BR147" t="inlineStr"/>
+      <c r="BS147" t="inlineStr"/>
+      <c r="BT147" t="inlineStr"/>
+      <c r="BU147" t="inlineStr"/>
+      <c r="BV147" t="inlineStr"/>
+      <c r="BW147" t="inlineStr"/>
+      <c r="BX147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY147" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BZ147" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.380420Z</t>
+        </is>
+      </c>
+      <c r="CA147" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
+      <c r="CB147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>542e7a0dbfec4eb5</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:50:34.398508Z</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-07-20T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>401816188</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>115</v>
+      </c>
+      <c r="M148" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0.465116</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0.5726869999999999</v>
+      </c>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="n">
+        <v>0.107571</v>
+      </c>
+      <c r="R148" t="n">
+        <v>100</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W148" t="n">
+        <v>4</v>
+      </c>
+      <c r="X148" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y148" t="inlineStr"/>
+      <c r="Z148" t="inlineStr"/>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="inlineStr"/>
+      <c r="AC148" t="n">
+        <v>1.4375</v>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>2026-07-21T03:22:54.737922Z</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.4650 (aec-mlb-min-cle-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr"/>
+      <c r="AI148" t="inlineStr"/>
+      <c r="AJ148" t="inlineStr"/>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN148" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>mlb-min</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>mlb-cle</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr"/>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD148" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE148" t="inlineStr">
+        <is>
+          <t>2170ac399ced5417</t>
+        </is>
+      </c>
+      <c r="BF148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG148" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH148" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:49:43.428041Z</t>
+        </is>
+      </c>
+      <c r="BI148" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ148" t="inlineStr"/>
+      <c r="BK148" t="n">
+        <v>115</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>0.465116</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>0.462687</v>
+      </c>
+      <c r="BO148" t="inlineStr"/>
+      <c r="BP148" t="inlineStr"/>
+      <c r="BQ148" t="inlineStr"/>
+      <c r="BR148" t="inlineStr"/>
+      <c r="BS148" t="inlineStr"/>
+      <c r="BT148" t="inlineStr"/>
+      <c r="BU148" t="inlineStr"/>
+      <c r="BV148" t="inlineStr"/>
+      <c r="BW148" t="inlineStr"/>
+      <c r="BX148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY148" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BZ148" t="inlineStr">
+        <is>
+          <t>2026-07-21T03:22:54.737922Z</t>
+        </is>
+      </c>
+      <c r="CA148" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
+      <c r="CB148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>554be71d308247ed</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:50:34.398508Z</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>401816189</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M149" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0.578558</v>
+      </c>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="n">
+        <v>0.059327</v>
+      </c>
+      <c r="R149" t="n">
+        <v>50</v>
+      </c>
+      <c r="S149" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W149" t="n">
+        <v>5</v>
+      </c>
+      <c r="X149" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y149" t="inlineStr"/>
+      <c r="Z149" t="inlineStr"/>
+      <c r="AA149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr"/>
+      <c r="AC149" t="n">
+        <v>1.1574</v>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>2026-07-21T03:22:55.055992Z</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-pit-nyy-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr"/>
+      <c r="AI149" t="inlineStr"/>
+      <c r="AJ149" t="inlineStr"/>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN149" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>mlb-pit</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>mlb-nyy</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr"/>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD149" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE149" t="inlineStr">
+        <is>
+          <t>38ab7db5a3798f0c</t>
+        </is>
+      </c>
+      <c r="BF149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG149" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH149" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:49:45.032018Z</t>
+        </is>
+      </c>
+      <c r="BI149" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ149" t="inlineStr"/>
+      <c r="BK149" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>0.517413</v>
+      </c>
+      <c r="BO149" t="inlineStr"/>
+      <c r="BP149" t="inlineStr"/>
+      <c r="BQ149" t="inlineStr"/>
+      <c r="BR149" t="inlineStr"/>
+      <c r="BS149" t="inlineStr"/>
+      <c r="BT149" t="inlineStr"/>
+      <c r="BU149" t="inlineStr"/>
+      <c r="BV149" t="inlineStr"/>
+      <c r="BW149" t="inlineStr"/>
+      <c r="BX149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY149" t="n">
+        <v>0.925926</v>
+      </c>
+      <c r="BZ149" t="inlineStr">
+        <is>
+          <t>2026-07-21T03:22:55.055992Z</t>
+        </is>
+      </c>
+      <c r="CA149" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
+      <c r="CB149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>af79b4620f7a4af3</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:50:34.398508Z</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>401816193</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>-106</v>
+      </c>
+      <c r="M150" t="n">
+        <v>1.943396</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0.514563</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0.566967</v>
+      </c>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="n">
+        <v>0.052404</v>
+      </c>
+      <c r="R150" t="n">
+        <v>46</v>
+      </c>
+      <c r="S150" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W150" t="n">
+        <v>8</v>
+      </c>
+      <c r="X150" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y150" t="inlineStr"/>
+      <c r="Z150" t="inlineStr"/>
+      <c r="AA150" t="inlineStr"/>
+      <c r="AB150" t="inlineStr"/>
+      <c r="AC150" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>2026-07-21T04:41:10.971771Z</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5150 (aec-mlb-det-chc-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr"/>
+      <c r="AI150" t="inlineStr"/>
+      <c r="AJ150" t="inlineStr"/>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN150" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>mlb-det</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>mlb-chc</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr"/>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD150" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE150" t="inlineStr">
+        <is>
+          <t>b84afb2c70e14d93</t>
+        </is>
+      </c>
+      <c r="BF150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG150" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH150" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:49:55.275935Z</t>
+        </is>
+      </c>
+      <c r="BI150" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ150" t="inlineStr"/>
+      <c r="BK150" t="n">
+        <v>-106</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>1.943396</v>
+      </c>
+      <c r="BM150" t="n">
+        <v>0.514563</v>
+      </c>
+      <c r="BN150" t="n">
+        <v>0.5124379999999999</v>
+      </c>
+      <c r="BO150" t="inlineStr"/>
+      <c r="BP150" t="inlineStr"/>
+      <c r="BQ150" t="inlineStr"/>
+      <c r="BR150" t="inlineStr"/>
+      <c r="BS150" t="inlineStr"/>
+      <c r="BT150" t="inlineStr"/>
+      <c r="BU150" t="inlineStr"/>
+      <c r="BV150" t="inlineStr"/>
+      <c r="BW150" t="inlineStr"/>
+      <c r="BX150" t="inlineStr"/>
+      <c r="BY150" t="inlineStr"/>
+      <c r="BZ150" t="inlineStr"/>
+      <c r="CA150" t="inlineStr"/>
+      <c r="CB150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>283f71257d594ea5</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:50:37.639352Z</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>401892393</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>150</v>
+      </c>
+      <c r="M151" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0.751217</v>
+      </c>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="n">
+        <v>0.351217</v>
+      </c>
+      <c r="R151" t="n">
+        <v>100</v>
+      </c>
+      <c r="S151" t="n">
+        <v>2</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W151" t="n">
+        <v>99</v>
+      </c>
+      <c r="X151" t="n">
+        <v>98</v>
+      </c>
+      <c r="Y151" t="inlineStr"/>
+      <c r="Z151" t="inlineStr"/>
+      <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>2026-07-21T03:22:55.455883Z</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5051; executable ask 0.4000 (aec-wnba-ny-dal-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr"/>
+      <c r="AI151" t="inlineStr"/>
+      <c r="AJ151" t="inlineStr"/>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN151" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>wnba-dal</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr"/>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD151" t="inlineStr">
+        <is>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+        </is>
+      </c>
+      <c r="BE151" t="inlineStr">
+        <is>
+          <t>3b474aa853a60d81</t>
+        </is>
+      </c>
+      <c r="BF151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG151" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH151" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:50:05.640054Z</t>
+        </is>
+      </c>
+      <c r="BI151" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ151" t="inlineStr"/>
+      <c r="BK151" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM151" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN151" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="BO151" t="inlineStr"/>
+      <c r="BP151" t="inlineStr"/>
+      <c r="BQ151" t="inlineStr"/>
+      <c r="BR151" t="inlineStr"/>
+      <c r="BS151" t="inlineStr"/>
+      <c r="BT151" t="inlineStr"/>
+      <c r="BU151" t="inlineStr"/>
+      <c r="BV151" t="inlineStr"/>
+      <c r="BW151" t="inlineStr"/>
+      <c r="BX151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ151" t="inlineStr">
+        <is>
+          <t>2026-07-21T03:22:55.455883Z</t>
+        </is>
+      </c>
+      <c r="CA151" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
+      <c r="CB151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>0f1add5fb76a4ae7</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:28:21.625948Z</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-07-21T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>401816208</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>-111</v>
+      </c>
+      <c r="M152" t="n">
+        <v>1.900901</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0.526066</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0.566967</v>
+      </c>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="n">
+        <v>0.040901</v>
+      </c>
+      <c r="R152" t="n">
+        <v>40</v>
+      </c>
+      <c r="S152" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr"/>
+      <c r="W152" t="inlineStr"/>
+      <c r="X152" t="inlineStr"/>
+      <c r="Y152" t="inlineStr"/>
+      <c r="Z152" t="inlineStr"/>
+      <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="inlineStr"/>
+      <c r="AD152" t="inlineStr"/>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5250 (aec-mlb-det-chc-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr"/>
+      <c r="AI152" t="inlineStr"/>
+      <c r="AJ152" t="inlineStr"/>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN152" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>mlb-det</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>mlb-chc</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr"/>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD152" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE152" t="inlineStr">
+        <is>
+          <t>ac77cab6921e81d4</t>
+        </is>
+      </c>
+      <c r="BF152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG152" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH152" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:27:54.312105Z</t>
+        </is>
+      </c>
+      <c r="BI152" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ152" t="inlineStr"/>
+      <c r="BK152" t="n">
+        <v>-111</v>
+      </c>
+      <c r="BL152" t="n">
+        <v>1.900901</v>
+      </c>
+      <c r="BM152" t="n">
+        <v>0.526066</v>
+      </c>
+      <c r="BN152" t="n">
+        <v>0.522388</v>
+      </c>
+      <c r="BO152" t="inlineStr"/>
+      <c r="BP152" t="inlineStr"/>
+      <c r="BQ152" t="inlineStr"/>
+      <c r="BR152" t="inlineStr"/>
+      <c r="BS152" t="inlineStr"/>
+      <c r="BT152" t="inlineStr"/>
+      <c r="BU152" t="inlineStr"/>
+      <c r="BV152" t="inlineStr"/>
+      <c r="BW152" t="inlineStr"/>
+      <c r="BX152" t="inlineStr"/>
+      <c r="BY152" t="inlineStr"/>
+      <c r="BZ152" t="inlineStr"/>
+      <c r="CA152" t="inlineStr"/>
+      <c r="CB152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>5d159d03a1244f92</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:28:21.625948Z</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-07-21T20:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>401816212</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>-102</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1.980392</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0.5563709999999999</v>
+      </c>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="n">
+        <v>0.051421</v>
+      </c>
+      <c r="R153" t="n">
+        <v>46</v>
+      </c>
+      <c r="S153" t="n">
+        <v>1</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr"/>
+      <c r="W153" t="inlineStr"/>
+      <c r="X153" t="inlineStr"/>
+      <c r="Y153" t="inlineStr"/>
+      <c r="Z153" t="inlineStr"/>
+      <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="inlineStr"/>
+      <c r="AD153" t="inlineStr"/>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5050 (aec-mlb-wsh-col-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr"/>
+      <c r="AI153" t="inlineStr"/>
+      <c r="AJ153" t="inlineStr"/>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL153" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN153" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>mlb-wsh</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>mlb-col</t>
+        </is>
+      </c>
+      <c r="AT153" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr"/>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD153" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE153" t="inlineStr">
+        <is>
+          <t>398815bb9dc03ea8</t>
+        </is>
+      </c>
+      <c r="BF153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG153" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH153" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:27:57.788476Z</t>
+        </is>
+      </c>
+      <c r="BI153" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ153" t="inlineStr"/>
+      <c r="BK153" t="n">
+        <v>-102</v>
+      </c>
+      <c r="BL153" t="n">
+        <v>1.980392</v>
+      </c>
+      <c r="BM153" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="BN153" t="n">
+        <v>0.502488</v>
+      </c>
+      <c r="BO153" t="inlineStr"/>
+      <c r="BP153" t="inlineStr"/>
+      <c r="BQ153" t="inlineStr"/>
+      <c r="BR153" t="inlineStr"/>
+      <c r="BS153" t="inlineStr"/>
+      <c r="BT153" t="inlineStr"/>
+      <c r="BU153" t="inlineStr"/>
+      <c r="BV153" t="inlineStr"/>
+      <c r="BW153" t="inlineStr"/>
+      <c r="BX153" t="inlineStr"/>
+      <c r="BY153" t="inlineStr"/>
+      <c r="BZ153" t="inlineStr"/>
+      <c r="CA153" t="inlineStr"/>
+      <c r="CB153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>8386d51ccef24cb5</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:28:21.625948Z</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>401816213</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M154" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0.58189</v>
+      </c>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="n">
+        <v>0.022419</v>
+      </c>
+      <c r="R154" t="n">
+        <v>31</v>
+      </c>
+      <c r="S154" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr"/>
+      <c r="W154" t="inlineStr"/>
+      <c r="X154" t="inlineStr"/>
+      <c r="Y154" t="inlineStr"/>
+      <c r="Z154" t="inlineStr"/>
+      <c r="AA154" t="inlineStr"/>
+      <c r="AB154" t="inlineStr"/>
+      <c r="AC154" t="inlineStr"/>
+      <c r="AD154" t="inlineStr"/>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5600 (aec-mlb-ath-az-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr"/>
+      <c r="AI154" t="inlineStr"/>
+      <c r="AJ154" t="inlineStr"/>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN154" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>mlb-ath</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>mlb-ari</t>
+        </is>
+      </c>
+      <c r="AT154" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr"/>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD154" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE154" t="inlineStr">
+        <is>
+          <t>9892b2a76fbe9db3</t>
+        </is>
+      </c>
+      <c r="BF154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG154" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH154" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:28:01.055923Z</t>
+        </is>
+      </c>
+      <c r="BI154" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ154" t="inlineStr"/>
+      <c r="BK154" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>0.557214</v>
+      </c>
+      <c r="BO154" t="inlineStr"/>
+      <c r="BP154" t="inlineStr"/>
+      <c r="BQ154" t="inlineStr"/>
+      <c r="BR154" t="inlineStr"/>
+      <c r="BS154" t="inlineStr"/>
+      <c r="BT154" t="inlineStr"/>
+      <c r="BU154" t="inlineStr"/>
+      <c r="BV154" t="inlineStr"/>
+      <c r="BW154" t="inlineStr"/>
+      <c r="BX154" t="inlineStr"/>
+      <c r="BY154" t="inlineStr"/>
+      <c r="BZ154" t="inlineStr"/>
+      <c r="CA154" t="inlineStr"/>
+      <c r="CB154" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -842,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB154"/>
+  <dimension ref="A1:CB176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40491,6 +40491,5592 @@
       <c r="CA154" t="inlineStr"/>
       <c r="CB154" t="inlineStr"/>
     </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>9d66d2c6b69d4f27</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:28:21.625948Z</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-07-21T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>401816210</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M155" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0.640995</v>
+      </c>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="n">
+        <v>0.07018000000000001</v>
+      </c>
+      <c r="R155" t="n">
+        <v>55</v>
+      </c>
+      <c r="S155" t="n">
+        <v>2</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr"/>
+      <c r="W155" t="inlineStr"/>
+      <c r="X155" t="inlineStr"/>
+      <c r="Y155" t="inlineStr"/>
+      <c r="Z155" t="inlineStr"/>
+      <c r="AA155" t="inlineStr"/>
+      <c r="AB155" t="inlineStr"/>
+      <c r="AC155" t="inlineStr"/>
+      <c r="AD155" t="inlineStr"/>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5700 (aec-mlb-nym-mil-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr"/>
+      <c r="AI155" t="inlineStr"/>
+      <c r="AJ155" t="inlineStr"/>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN155" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>mlb-nym</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AT155" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr"/>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD155" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE155" t="inlineStr">
+        <is>
+          <t>b3842f29fc9906ce</t>
+        </is>
+      </c>
+      <c r="BF155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG155" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH155" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:27:49.015557Z</t>
+        </is>
+      </c>
+      <c r="BI155" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ155" t="inlineStr"/>
+      <c r="BK155" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>0.567164</v>
+      </c>
+      <c r="BO155" t="inlineStr"/>
+      <c r="BP155" t="inlineStr"/>
+      <c r="BQ155" t="inlineStr"/>
+      <c r="BR155" t="inlineStr"/>
+      <c r="BS155" t="inlineStr"/>
+      <c r="BT155" t="inlineStr"/>
+      <c r="BU155" t="inlineStr"/>
+      <c r="BV155" t="inlineStr"/>
+      <c r="BW155" t="inlineStr"/>
+      <c r="BX155" t="inlineStr"/>
+      <c r="BY155" t="inlineStr"/>
+      <c r="BZ155" t="inlineStr"/>
+      <c r="CA155" t="inlineStr"/>
+      <c r="CB155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>3781ba4200414486</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:28:21.625948Z</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>401816214</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>-106</v>
+      </c>
+      <c r="M156" t="n">
+        <v>1.943396</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0.514563</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0.592852</v>
+      </c>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="n">
+        <v>0.078289</v>
+      </c>
+      <c r="R156" t="n">
+        <v>59</v>
+      </c>
+      <c r="S156" t="n">
+        <v>1</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr"/>
+      <c r="W156" t="inlineStr"/>
+      <c r="X156" t="inlineStr"/>
+      <c r="Y156" t="inlineStr"/>
+      <c r="Z156" t="inlineStr"/>
+      <c r="AA156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr"/>
+      <c r="AC156" t="inlineStr"/>
+      <c r="AD156" t="inlineStr"/>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5150 (aec-mlb-cin-sea-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr"/>
+      <c r="AI156" t="inlineStr"/>
+      <c r="AJ156" t="inlineStr"/>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN156" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>mlb-cin</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>mlb-sea</t>
+        </is>
+      </c>
+      <c r="AT156" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr"/>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD156" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE156" t="inlineStr">
+        <is>
+          <t>5c7208cbf934ad36</t>
+        </is>
+      </c>
+      <c r="BF156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG156" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH156" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:28:02.507970Z</t>
+        </is>
+      </c>
+      <c r="BI156" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ156" t="inlineStr"/>
+      <c r="BK156" t="n">
+        <v>-106</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>1.943396</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>0.514563</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>0.5124379999999999</v>
+      </c>
+      <c r="BO156" t="inlineStr"/>
+      <c r="BP156" t="inlineStr"/>
+      <c r="BQ156" t="inlineStr"/>
+      <c r="BR156" t="inlineStr"/>
+      <c r="BS156" t="inlineStr"/>
+      <c r="BT156" t="inlineStr"/>
+      <c r="BU156" t="inlineStr"/>
+      <c r="BV156" t="inlineStr"/>
+      <c r="BW156" t="inlineStr"/>
+      <c r="BX156" t="inlineStr"/>
+      <c r="BY156" t="inlineStr"/>
+      <c r="BZ156" t="inlineStr"/>
+      <c r="CA156" t="inlineStr"/>
+      <c r="CB156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>e6c6805e8ee84709</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:04.732597Z</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-07-21T10:45:00Z</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>54950</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>144</v>
+      </c>
+      <c r="M157" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0.7499980000000001</v>
+      </c>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="n">
+        <v>0.339998</v>
+      </c>
+      <c r="R157" t="n">
+        <v>100</v>
+      </c>
+      <c r="S157" t="n">
+        <v>2</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W157" t="n">
+        <v>0</v>
+      </c>
+      <c r="X157" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y157" t="inlineStr"/>
+      <c r="Z157" t="inlineStr"/>
+      <c r="AA157" t="inlineStr"/>
+      <c r="AB157" t="inlineStr"/>
+      <c r="AC157" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>2026-07-21T16:22:44.126888Z</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (aec-lol-t1-krx-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr"/>
+      <c r="AI157" t="inlineStr"/>
+      <c r="AJ157" t="inlineStr"/>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN157" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr"/>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD157" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH157" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:04.732597Z</t>
+        </is>
+      </c>
+      <c r="BI157" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ157" t="inlineStr"/>
+      <c r="BK157" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN157" t="inlineStr"/>
+      <c r="BO157" t="inlineStr"/>
+      <c r="BP157" t="inlineStr"/>
+      <c r="BQ157" t="inlineStr"/>
+      <c r="BR157" t="inlineStr"/>
+      <c r="BS157" t="inlineStr"/>
+      <c r="BT157" t="inlineStr"/>
+      <c r="BU157" t="inlineStr"/>
+      <c r="BV157" t="inlineStr"/>
+      <c r="BW157" t="inlineStr"/>
+      <c r="BX157" t="inlineStr"/>
+      <c r="BY157" t="inlineStr"/>
+      <c r="BZ157" t="inlineStr"/>
+      <c r="CA157" t="inlineStr"/>
+      <c r="CB157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>afb2b4ca2d694387</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:04.942524Z</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-07-21T11:30:00Z</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>54961</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>DN SOOPers</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>194</v>
+      </c>
+      <c r="M158" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="R158" t="n">
+        <v>100</v>
+      </c>
+      <c r="S158" t="n">
+        <v>2</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W158" t="n">
+        <v>1</v>
+      </c>
+      <c r="X158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y158" t="inlineStr"/>
+      <c r="Z158" t="inlineStr"/>
+      <c r="AA158" t="inlineStr"/>
+      <c r="AB158" t="inlineStr"/>
+      <c r="AC158" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>2026-07-21T16:22:45.719452Z</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3400 (aec-lol-hle-dns-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr"/>
+      <c r="AI158" t="inlineStr"/>
+      <c r="AJ158" t="inlineStr"/>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL158" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN158" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>DN SOOPers</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>DN SOOPers</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>DN SOOPers</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AT158" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr"/>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD158" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH158" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:04.942524Z</t>
+        </is>
+      </c>
+      <c r="BI158" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ158" t="inlineStr"/>
+      <c r="BK158" t="n">
+        <v>194</v>
+      </c>
+      <c r="BL158" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="BN158" t="inlineStr"/>
+      <c r="BO158" t="inlineStr"/>
+      <c r="BP158" t="inlineStr"/>
+      <c r="BQ158" t="inlineStr"/>
+      <c r="BR158" t="inlineStr"/>
+      <c r="BS158" t="inlineStr"/>
+      <c r="BT158" t="inlineStr"/>
+      <c r="BU158" t="inlineStr"/>
+      <c r="BV158" t="inlineStr"/>
+      <c r="BW158" t="inlineStr"/>
+      <c r="BX158" t="inlineStr"/>
+      <c r="BY158" t="inlineStr"/>
+      <c r="BZ158" t="inlineStr"/>
+      <c r="CA158" t="inlineStr"/>
+      <c r="CB158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>e269074c55f34c0a</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:05.151435Z</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-07-21T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>56853</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0.650242</v>
+      </c>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="n">
+        <v>0.060242</v>
+      </c>
+      <c r="R159" t="n">
+        <v>60</v>
+      </c>
+      <c r="S159" t="n">
+        <v>2</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W159" t="n">
+        <v>1</v>
+      </c>
+      <c r="X159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y159" t="inlineStr"/>
+      <c r="Z159" t="inlineStr"/>
+      <c r="AA159" t="inlineStr"/>
+      <c r="AB159" t="inlineStr"/>
+      <c r="AC159" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:34:55.003704Z</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (aec-lol-tlnp-ijc-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr"/>
+      <c r="AI159" t="inlineStr"/>
+      <c r="AJ159" t="inlineStr"/>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL159" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN159" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AT159" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr"/>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD159" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH159" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:05.151435Z</t>
+        </is>
+      </c>
+      <c r="BI159" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ159" t="inlineStr"/>
+      <c r="BK159" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN159" t="inlineStr"/>
+      <c r="BO159" t="inlineStr"/>
+      <c r="BP159" t="inlineStr"/>
+      <c r="BQ159" t="inlineStr"/>
+      <c r="BR159" t="inlineStr"/>
+      <c r="BS159" t="inlineStr"/>
+      <c r="BT159" t="inlineStr"/>
+      <c r="BU159" t="inlineStr"/>
+      <c r="BV159" t="inlineStr"/>
+      <c r="BW159" t="inlineStr"/>
+      <c r="BX159" t="inlineStr"/>
+      <c r="BY159" t="inlineStr"/>
+      <c r="BZ159" t="inlineStr"/>
+      <c r="CA159" t="inlineStr"/>
+      <c r="CB159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>998d5fc8f8714168</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:05.359328Z</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-07-21T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>57016</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>113</v>
+      </c>
+      <c r="M160" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0.503502</v>
+      </c>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="n">
+        <v>0.033502</v>
+      </c>
+      <c r="R160" t="n">
+        <v>33</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W160" t="n">
+        <v>1</v>
+      </c>
+      <c r="X160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y160" t="inlineStr"/>
+      <c r="Z160" t="inlineStr"/>
+      <c r="AA160" t="inlineStr"/>
+      <c r="AB160" t="inlineStr"/>
+      <c r="AC160" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:34:56.687478Z</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4700 (aec-lol-piv-bam-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr"/>
+      <c r="AI160" t="inlineStr"/>
+      <c r="AJ160" t="inlineStr"/>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL160" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN160" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="AT160" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr"/>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD160" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH160" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:05.359328Z</t>
+        </is>
+      </c>
+      <c r="BI160" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ160" t="inlineStr"/>
+      <c r="BK160" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN160" t="inlineStr"/>
+      <c r="BO160" t="inlineStr"/>
+      <c r="BP160" t="inlineStr"/>
+      <c r="BQ160" t="inlineStr"/>
+      <c r="BR160" t="inlineStr"/>
+      <c r="BS160" t="inlineStr"/>
+      <c r="BT160" t="inlineStr"/>
+      <c r="BU160" t="inlineStr"/>
+      <c r="BV160" t="inlineStr"/>
+      <c r="BW160" t="inlineStr"/>
+      <c r="BX160" t="inlineStr"/>
+      <c r="BY160" t="inlineStr"/>
+      <c r="BZ160" t="inlineStr"/>
+      <c r="CA160" t="inlineStr"/>
+      <c r="CB160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>d3b95e0bdd404503</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:05.574126Z</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-07-21T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>56856</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M161" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0.748054</v>
+      </c>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="n">
+        <v>0.08805399999999999</v>
+      </c>
+      <c r="R161" t="n">
+        <v>88</v>
+      </c>
+      <c r="S161" t="n">
+        <v>2</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W161" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y161" t="inlineStr"/>
+      <c r="Z161" t="inlineStr"/>
+      <c r="AA161" t="inlineStr"/>
+      <c r="AB161" t="inlineStr"/>
+      <c r="AC161" t="n">
+        <v>1.0309</v>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:34:58.112054Z</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (aec-lol-gal-jl-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr"/>
+      <c r="AI161" t="inlineStr"/>
+      <c r="AJ161" t="inlineStr"/>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN161" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="AT161" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr"/>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD161" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH161" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:05.574126Z</t>
+        </is>
+      </c>
+      <c r="BI161" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ161" t="inlineStr"/>
+      <c r="BK161" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN161" t="inlineStr"/>
+      <c r="BO161" t="inlineStr"/>
+      <c r="BP161" t="inlineStr"/>
+      <c r="BQ161" t="inlineStr"/>
+      <c r="BR161" t="inlineStr"/>
+      <c r="BS161" t="inlineStr"/>
+      <c r="BT161" t="inlineStr"/>
+      <c r="BU161" t="inlineStr"/>
+      <c r="BV161" t="inlineStr"/>
+      <c r="BW161" t="inlineStr"/>
+      <c r="BX161" t="inlineStr"/>
+      <c r="BY161" t="inlineStr"/>
+      <c r="BZ161" t="inlineStr"/>
+      <c r="CA161" t="inlineStr"/>
+      <c r="CB161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>4c1c4e9366e14623</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:05.910492Z</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>55205</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M162" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0.731785</v>
+      </c>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="n">
+        <v>0.061785</v>
+      </c>
+      <c r="R162" t="n">
+        <v>61</v>
+      </c>
+      <c r="S162" t="n">
+        <v>2</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W162" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y162" t="inlineStr"/>
+      <c r="Z162" t="inlineStr"/>
+      <c r="AA162" t="inlineStr"/>
+      <c r="AB162" t="inlineStr"/>
+      <c r="AC162" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:34:59.516440Z</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (aec-lol-pnga-rmd-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr"/>
+      <c r="AI162" t="inlineStr"/>
+      <c r="AJ162" t="inlineStr"/>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL162" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN162" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AT162" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr"/>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD162" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH162" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:05.910492Z</t>
+        </is>
+      </c>
+      <c r="BI162" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ162" t="inlineStr"/>
+      <c r="BK162" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN162" t="inlineStr"/>
+      <c r="BO162" t="inlineStr"/>
+      <c r="BP162" t="inlineStr"/>
+      <c r="BQ162" t="inlineStr"/>
+      <c r="BR162" t="inlineStr"/>
+      <c r="BS162" t="inlineStr"/>
+      <c r="BT162" t="inlineStr"/>
+      <c r="BU162" t="inlineStr"/>
+      <c r="BV162" t="inlineStr"/>
+      <c r="BW162" t="inlineStr"/>
+      <c r="BX162" t="inlineStr"/>
+      <c r="BY162" t="inlineStr"/>
+      <c r="BZ162" t="inlineStr"/>
+      <c r="CA162" t="inlineStr"/>
+      <c r="CB162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>db9ff36a2ee94b8c</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:06.130324Z</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-07-21T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>55206</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>212</v>
+      </c>
+      <c r="M163" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0.320513</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0.59232</v>
+      </c>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="n">
+        <v>0.27232</v>
+      </c>
+      <c r="R163" t="n">
+        <v>100</v>
+      </c>
+      <c r="S163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W163" t="n">
+        <v>1</v>
+      </c>
+      <c r="X163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y163" t="inlineStr"/>
+      <c r="Z163" t="inlineStr"/>
+      <c r="AA163" t="inlineStr"/>
+      <c r="AB163" t="inlineStr"/>
+      <c r="AC163" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:35:00.880867Z</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3200 (aec-lol-kbm-est-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr"/>
+      <c r="AI163" t="inlineStr"/>
+      <c r="AJ163" t="inlineStr"/>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN163" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AT163" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr"/>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD163" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH163" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:06.130324Z</t>
+        </is>
+      </c>
+      <c r="BI163" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ163" t="inlineStr"/>
+      <c r="BK163" t="n">
+        <v>212</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>0.320513</v>
+      </c>
+      <c r="BN163" t="inlineStr"/>
+      <c r="BO163" t="inlineStr"/>
+      <c r="BP163" t="inlineStr"/>
+      <c r="BQ163" t="inlineStr"/>
+      <c r="BR163" t="inlineStr"/>
+      <c r="BS163" t="inlineStr"/>
+      <c r="BT163" t="inlineStr"/>
+      <c r="BU163" t="inlineStr"/>
+      <c r="BV163" t="inlineStr"/>
+      <c r="BW163" t="inlineStr"/>
+      <c r="BX163" t="inlineStr"/>
+      <c r="BY163" t="inlineStr"/>
+      <c r="BZ163" t="inlineStr"/>
+      <c r="CA163" t="inlineStr"/>
+      <c r="CB163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>c1f4d33246924874</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:06.360899Z</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-07-22T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>55996</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M164" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0.748396</v>
+      </c>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="n">
+        <v>0.07839599999999999</v>
+      </c>
+      <c r="R164" t="n">
+        <v>78</v>
+      </c>
+      <c r="S164" t="n">
+        <v>2</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr"/>
+      <c r="W164" t="inlineStr"/>
+      <c r="X164" t="inlineStr"/>
+      <c r="Y164" t="inlineStr"/>
+      <c r="Z164" t="inlineStr"/>
+      <c r="AA164" t="inlineStr"/>
+      <c r="AB164" t="inlineStr"/>
+      <c r="AC164" t="inlineStr"/>
+      <c r="AD164" t="inlineStr"/>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (aec-lol-tes-we-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr"/>
+      <c r="AI164" t="inlineStr"/>
+      <c r="AJ164" t="inlineStr"/>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL164" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN164" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="AT164" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr"/>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD164" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG164" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH164" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:06.360899Z</t>
+        </is>
+      </c>
+      <c r="BI164" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ164" t="inlineStr"/>
+      <c r="BK164" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN164" t="inlineStr"/>
+      <c r="BO164" t="inlineStr"/>
+      <c r="BP164" t="inlineStr"/>
+      <c r="BQ164" t="inlineStr"/>
+      <c r="BR164" t="inlineStr"/>
+      <c r="BS164" t="inlineStr"/>
+      <c r="BT164" t="inlineStr"/>
+      <c r="BU164" t="inlineStr"/>
+      <c r="BV164" t="inlineStr"/>
+      <c r="BW164" t="inlineStr"/>
+      <c r="BX164" t="inlineStr"/>
+      <c r="BY164" t="inlineStr"/>
+      <c r="BZ164" t="inlineStr"/>
+      <c r="CA164" t="inlineStr"/>
+      <c r="CB164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>a2bb4ba4e2f84c70</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:06.595624Z</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-07-22T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>56056</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>FALKE Esports</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>UB Alma Mater</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>203</v>
+      </c>
+      <c r="M165" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0.64693</v>
+      </c>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="R165" t="n">
+        <v>100</v>
+      </c>
+      <c r="S165" t="n">
+        <v>2</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr"/>
+      <c r="W165" t="inlineStr"/>
+      <c r="X165" t="inlineStr"/>
+      <c r="Y165" t="inlineStr"/>
+      <c r="Z165" t="inlineStr"/>
+      <c r="AA165" t="inlineStr"/>
+      <c r="AB165" t="inlineStr"/>
+      <c r="AC165" t="inlineStr"/>
+      <c r="AD165" t="inlineStr"/>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3300 (aec-lol-ub-flk-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr"/>
+      <c r="AI165" t="inlineStr"/>
+      <c r="AJ165" t="inlineStr"/>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL165" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN165" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>FALKE Esports</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>FALKE Esports</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>FALKE Esports</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>UB Alma Mater</t>
+        </is>
+      </c>
+      <c r="AT165" t="inlineStr">
+        <is>
+          <t>UB Alma Mater</t>
+        </is>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>UB Alma Mater</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr"/>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD165" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH165" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:06.595624Z</t>
+        </is>
+      </c>
+      <c r="BI165" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ165" t="inlineStr"/>
+      <c r="BK165" t="n">
+        <v>203</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="BN165" t="inlineStr"/>
+      <c r="BO165" t="inlineStr"/>
+      <c r="BP165" t="inlineStr"/>
+      <c r="BQ165" t="inlineStr"/>
+      <c r="BR165" t="inlineStr"/>
+      <c r="BS165" t="inlineStr"/>
+      <c r="BT165" t="inlineStr"/>
+      <c r="BU165" t="inlineStr"/>
+      <c r="BV165" t="inlineStr"/>
+      <c r="BW165" t="inlineStr"/>
+      <c r="BX165" t="inlineStr"/>
+      <c r="BY165" t="inlineStr"/>
+      <c r="BZ165" t="inlineStr"/>
+      <c r="CA165" t="inlineStr"/>
+      <c r="CB165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>88825e98cdf14a2c</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:06.831199Z</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-07-22T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>56127</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M166" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0.6951349999999999</v>
+      </c>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="n">
+        <v>0.105135</v>
+      </c>
+      <c r="R166" t="n">
+        <v>100</v>
+      </c>
+      <c r="S166" t="n">
+        <v>2</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr"/>
+      <c r="W166" t="inlineStr"/>
+      <c r="X166" t="inlineStr"/>
+      <c r="Y166" t="inlineStr"/>
+      <c r="Z166" t="inlineStr"/>
+      <c r="AA166" t="inlineStr"/>
+      <c r="AB166" t="inlineStr"/>
+      <c r="AC166" t="inlineStr"/>
+      <c r="AD166" t="inlineStr"/>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (aec-lol-bar-ucam-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr"/>
+      <c r="AI166" t="inlineStr"/>
+      <c r="AJ166" t="inlineStr"/>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN166" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AT166" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr"/>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD166" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG166" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH166" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:06.831199Z</t>
+        </is>
+      </c>
+      <c r="BI166" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ166" t="inlineStr"/>
+      <c r="BK166" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN166" t="inlineStr"/>
+      <c r="BO166" t="inlineStr"/>
+      <c r="BP166" t="inlineStr"/>
+      <c r="BQ166" t="inlineStr"/>
+      <c r="BR166" t="inlineStr"/>
+      <c r="BS166" t="inlineStr"/>
+      <c r="BT166" t="inlineStr"/>
+      <c r="BU166" t="inlineStr"/>
+      <c r="BV166" t="inlineStr"/>
+      <c r="BW166" t="inlineStr"/>
+      <c r="BX166" t="inlineStr"/>
+      <c r="BY166" t="inlineStr"/>
+      <c r="BZ166" t="inlineStr"/>
+      <c r="CA166" t="inlineStr"/>
+      <c r="CB166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>03582afc01c14b32</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:42:00.190701Z</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-07-21T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>54926</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>NIP</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>M80</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>108</v>
+      </c>
+      <c r="M167" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0.721453</v>
+      </c>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="n">
+        <v>0.240684</v>
+      </c>
+      <c r="R167" t="n">
+        <v>100</v>
+      </c>
+      <c r="S167" t="n">
+        <v>2</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W167" t="n">
+        <v>1</v>
+      </c>
+      <c r="X167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y167" t="inlineStr"/>
+      <c r="Z167" t="inlineStr"/>
+      <c r="AA167" t="inlineStr"/>
+      <c r="AB167" t="inlineStr"/>
+      <c r="AC167" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>2026-07-21T16:22:48.604482Z</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4800 (aec-cs2-m80-nip-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr"/>
+      <c r="AI167" t="inlineStr"/>
+      <c r="AJ167" t="inlineStr"/>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL167" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN167" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>NIP</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>NIP</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>NIP</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>M80</t>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr">
+        <is>
+          <t>M80</t>
+        </is>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>M80</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr"/>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>98da4a80b7f318a7919e5e7e0ea665d52be3fd1d2c2ae7cd25aead8acbac7a16</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD167" t="inlineStr">
+        <is>
+          <t>9dbde86ab8062ac73a51c94b0ad431573ac8b755ccd742d86794849a749958c7</t>
+        </is>
+      </c>
+      <c r="BE167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG167" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH167" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:42:00.190701Z</t>
+        </is>
+      </c>
+      <c r="BI167" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ167" t="inlineStr"/>
+      <c r="BK167" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM167" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN167" t="inlineStr"/>
+      <c r="BO167" t="inlineStr"/>
+      <c r="BP167" t="inlineStr"/>
+      <c r="BQ167" t="inlineStr"/>
+      <c r="BR167" t="inlineStr"/>
+      <c r="BS167" t="inlineStr"/>
+      <c r="BT167" t="inlineStr"/>
+      <c r="BU167" t="inlineStr"/>
+      <c r="BV167" t="inlineStr"/>
+      <c r="BW167" t="inlineStr"/>
+      <c r="BX167" t="inlineStr"/>
+      <c r="BY167" t="inlineStr"/>
+      <c r="BZ167" t="inlineStr"/>
+      <c r="CA167" t="inlineStr"/>
+      <c r="CB167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>9cccd398c3f94f4a</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:42:02.062138Z</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-07-21T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>56760</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>ALKA GAMING</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Procyon Gaming</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M168" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0.780802</v>
+      </c>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="n">
+        <v>0.209987</v>
+      </c>
+      <c r="R168" t="n">
+        <v>100</v>
+      </c>
+      <c r="S168" t="n">
+        <v>2</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W168" t="n">
+        <v>1</v>
+      </c>
+      <c r="X168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y168" t="inlineStr"/>
+      <c r="Z168" t="inlineStr"/>
+      <c r="AA168" t="inlineStr"/>
+      <c r="AB168" t="inlineStr"/>
+      <c r="AC168" t="n">
+        <v>1.5038</v>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:35:05.485250Z</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (aec-cs2-pcy-alka-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr"/>
+      <c r="AI168" t="inlineStr"/>
+      <c r="AJ168" t="inlineStr"/>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN168" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>ALKA GAMING</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>ALKA GAMING</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>ALKA GAMING</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>Procyon Gaming</t>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr">
+        <is>
+          <t>Procyon Gaming</t>
+        </is>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>Procyon Gaming</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr"/>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>98da4a80b7f318a7919e5e7e0ea665d52be3fd1d2c2ae7cd25aead8acbac7a16</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD168" t="inlineStr">
+        <is>
+          <t>9dbde86ab8062ac73a51c94b0ad431573ac8b755ccd742d86794849a749958c7</t>
+        </is>
+      </c>
+      <c r="BE168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG168" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH168" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:42:02.062138Z</t>
+        </is>
+      </c>
+      <c r="BI168" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ168" t="inlineStr"/>
+      <c r="BK168" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN168" t="inlineStr"/>
+      <c r="BO168" t="inlineStr"/>
+      <c r="BP168" t="inlineStr"/>
+      <c r="BQ168" t="inlineStr"/>
+      <c r="BR168" t="inlineStr"/>
+      <c r="BS168" t="inlineStr"/>
+      <c r="BT168" t="inlineStr"/>
+      <c r="BU168" t="inlineStr"/>
+      <c r="BV168" t="inlineStr"/>
+      <c r="BW168" t="inlineStr"/>
+      <c r="BX168" t="inlineStr"/>
+      <c r="BY168" t="inlineStr"/>
+      <c r="BZ168" t="inlineStr"/>
+      <c r="CA168" t="inlineStr"/>
+      <c r="CB168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>c60fe3cbab604f77</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:33:49.469667Z</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-07-22T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>56056</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>FALKE Esports</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>UB Alma Mater</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>223</v>
+      </c>
+      <c r="M169" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0.549502</v>
+      </c>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="n">
+        <v>0.239904</v>
+      </c>
+      <c r="R169" t="n">
+        <v>100</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr"/>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr"/>
+      <c r="Y169" t="inlineStr"/>
+      <c r="Z169" t="inlineStr"/>
+      <c r="AA169" t="inlineStr"/>
+      <c r="AB169" t="inlineStr"/>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-lol-ub-flk-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr"/>
+      <c r="AI169" t="inlineStr"/>
+      <c r="AJ169" t="inlineStr"/>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN169" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>FALKE Esports</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>FALKE Esports</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>FALKE Esports</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>UB Alma Mater</t>
+        </is>
+      </c>
+      <c r="AT169" t="inlineStr">
+        <is>
+          <t>UB Alma Mater</t>
+        </is>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>UB Alma Mater</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr"/>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD169" t="inlineStr">
+        <is>
+          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+        </is>
+      </c>
+      <c r="BE169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG169" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH169" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:33:26.514025Z</t>
+        </is>
+      </c>
+      <c r="BI169" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ169" t="inlineStr"/>
+      <c r="BK169" t="n">
+        <v>223</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="BN169" t="inlineStr"/>
+      <c r="BO169" t="inlineStr"/>
+      <c r="BP169" t="inlineStr"/>
+      <c r="BQ169" t="inlineStr"/>
+      <c r="BR169" t="inlineStr"/>
+      <c r="BS169" t="inlineStr"/>
+      <c r="BT169" t="inlineStr"/>
+      <c r="BU169" t="inlineStr"/>
+      <c r="BV169" t="inlineStr"/>
+      <c r="BW169" t="inlineStr"/>
+      <c r="BX169" t="inlineStr"/>
+      <c r="BY169" t="inlineStr"/>
+      <c r="BZ169" t="inlineStr"/>
+      <c r="CA169" t="inlineStr"/>
+      <c r="CB169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>a66ab58a0dec4c09</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:33:49.469667Z</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-07-22T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>58172</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M170" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0.651459</v>
+      </c>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="n">
+        <v>0.031687</v>
+      </c>
+      <c r="R170" t="n">
+        <v>36</v>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr"/>
+      <c r="W170" t="inlineStr"/>
+      <c r="X170" t="inlineStr"/>
+      <c r="Y170" t="inlineStr"/>
+      <c r="Z170" t="inlineStr"/>
+      <c r="AA170" t="inlineStr"/>
+      <c r="AB170" t="inlineStr"/>
+      <c r="AC170" t="inlineStr"/>
+      <c r="AD170" t="inlineStr"/>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-khk-use-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr"/>
+      <c r="AI170" t="inlineStr"/>
+      <c r="AJ170" t="inlineStr"/>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN170" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AT170" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr"/>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD170" t="inlineStr">
+        <is>
+          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+        </is>
+      </c>
+      <c r="BE170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG170" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH170" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:33:33.988461Z</t>
+        </is>
+      </c>
+      <c r="BI170" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ170" t="inlineStr"/>
+      <c r="BK170" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN170" t="inlineStr"/>
+      <c r="BO170" t="inlineStr"/>
+      <c r="BP170" t="inlineStr"/>
+      <c r="BQ170" t="inlineStr"/>
+      <c r="BR170" t="inlineStr"/>
+      <c r="BS170" t="inlineStr"/>
+      <c r="BT170" t="inlineStr"/>
+      <c r="BU170" t="inlineStr"/>
+      <c r="BV170" t="inlineStr"/>
+      <c r="BW170" t="inlineStr"/>
+      <c r="BX170" t="inlineStr"/>
+      <c r="BY170" t="inlineStr"/>
+      <c r="BZ170" t="inlineStr"/>
+      <c r="CA170" t="inlineStr"/>
+      <c r="CB170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>dce9764f932b4769</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:33:49.469667Z</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-07-22T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>56127</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M171" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0.689025</v>
+      </c>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="n">
+        <v>0.08902500000000001</v>
+      </c>
+      <c r="R171" t="n">
+        <v>65</v>
+      </c>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr"/>
+      <c r="W171" t="inlineStr"/>
+      <c r="X171" t="inlineStr"/>
+      <c r="Y171" t="inlineStr"/>
+      <c r="Z171" t="inlineStr"/>
+      <c r="AA171" t="inlineStr"/>
+      <c r="AB171" t="inlineStr"/>
+      <c r="AC171" t="inlineStr"/>
+      <c r="AD171" t="inlineStr"/>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-bar-ucam-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr"/>
+      <c r="AI171" t="inlineStr"/>
+      <c r="AJ171" t="inlineStr"/>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN171" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>NO_CALL_EXPOSURE_LIMIT</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AT171" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr"/>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD171" t="inlineStr">
+        <is>
+          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+        </is>
+      </c>
+      <c r="BE171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG171" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH171" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:33:34.731546Z</t>
+        </is>
+      </c>
+      <c r="BI171" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ171" t="inlineStr"/>
+      <c r="BK171" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN171" t="inlineStr"/>
+      <c r="BO171" t="inlineStr"/>
+      <c r="BP171" t="inlineStr"/>
+      <c r="BQ171" t="inlineStr"/>
+      <c r="BR171" t="inlineStr"/>
+      <c r="BS171" t="inlineStr"/>
+      <c r="BT171" t="inlineStr"/>
+      <c r="BU171" t="inlineStr"/>
+      <c r="BV171" t="inlineStr"/>
+      <c r="BW171" t="inlineStr"/>
+      <c r="BX171" t="inlineStr"/>
+      <c r="BY171" t="inlineStr"/>
+      <c r="BZ171" t="inlineStr"/>
+      <c r="CA171" t="inlineStr"/>
+      <c r="CB171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>aec53b15dbe44fd4</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:33:49.469667Z</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-07-22T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>56132</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M172" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N172" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0.625647</v>
+      </c>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="n">
+        <v>0.086476</v>
+      </c>
+      <c r="R172" t="n">
+        <v>63</v>
+      </c>
+      <c r="S172" t="n">
+        <v>0</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr"/>
+      <c r="W172" t="inlineStr"/>
+      <c r="X172" t="inlineStr"/>
+      <c r="Y172" t="inlineStr"/>
+      <c r="Z172" t="inlineStr"/>
+      <c r="AA172" t="inlineStr"/>
+      <c r="AB172" t="inlineStr"/>
+      <c r="AC172" t="inlineStr"/>
+      <c r="AD172" t="inlineStr"/>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-kbm-itz-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr"/>
+      <c r="AI172" t="inlineStr"/>
+      <c r="AJ172" t="inlineStr"/>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN172" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>NO_CALL_EXPOSURE_LIMIT</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr"/>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD172" t="inlineStr">
+        <is>
+          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+        </is>
+      </c>
+      <c r="BE172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG172" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH172" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:33:43.868094Z</t>
+        </is>
+      </c>
+      <c r="BI172" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ172" t="inlineStr"/>
+      <c r="BK172" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN172" t="inlineStr"/>
+      <c r="BO172" t="inlineStr"/>
+      <c r="BP172" t="inlineStr"/>
+      <c r="BQ172" t="inlineStr"/>
+      <c r="BR172" t="inlineStr"/>
+      <c r="BS172" t="inlineStr"/>
+      <c r="BT172" t="inlineStr"/>
+      <c r="BU172" t="inlineStr"/>
+      <c r="BV172" t="inlineStr"/>
+      <c r="BW172" t="inlineStr"/>
+      <c r="BX172" t="inlineStr"/>
+      <c r="BY172" t="inlineStr"/>
+      <c r="BZ172" t="inlineStr"/>
+      <c r="CA172" t="inlineStr"/>
+      <c r="CB172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ab20860ab7904fa7</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:33:49.469667Z</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-07-22T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>56138</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>138</v>
+      </c>
+      <c r="M173" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0.589489</v>
+      </c>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="n">
+        <v>0.169321</v>
+      </c>
+      <c r="R173" t="n">
+        <v>100</v>
+      </c>
+      <c r="S173" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr"/>
+      <c r="W173" t="inlineStr"/>
+      <c r="X173" t="inlineStr"/>
+      <c r="Y173" t="inlineStr"/>
+      <c r="Z173" t="inlineStr"/>
+      <c r="AA173" t="inlineStr"/>
+      <c r="AB173" t="inlineStr"/>
+      <c r="AC173" t="inlineStr"/>
+      <c r="AD173" t="inlineStr"/>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-nerd-7rex-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr"/>
+      <c r="AI173" t="inlineStr"/>
+      <c r="AJ173" t="inlineStr"/>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL173" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN173" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AT173" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr"/>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD173" t="inlineStr">
+        <is>
+          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+        </is>
+      </c>
+      <c r="BE173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG173" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH173" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:33:47.942599Z</t>
+        </is>
+      </c>
+      <c r="BI173" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ173" t="inlineStr"/>
+      <c r="BK173" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM173" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN173" t="inlineStr"/>
+      <c r="BO173" t="inlineStr"/>
+      <c r="BP173" t="inlineStr"/>
+      <c r="BQ173" t="inlineStr"/>
+      <c r="BR173" t="inlineStr"/>
+      <c r="BS173" t="inlineStr"/>
+      <c r="BT173" t="inlineStr"/>
+      <c r="BU173" t="inlineStr"/>
+      <c r="BV173" t="inlineStr"/>
+      <c r="BW173" t="inlineStr"/>
+      <c r="BX173" t="inlineStr"/>
+      <c r="BY173" t="inlineStr"/>
+      <c r="BZ173" t="inlineStr"/>
+      <c r="CA173" t="inlineStr"/>
+      <c r="CB173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2f0b6b58fffe4726</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:34:34.693145Z</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-07-22T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>56051</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Spirit Academy</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>138</v>
+      </c>
+      <c r="M174" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0.583304</v>
+      </c>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="n">
+        <v>0.163136</v>
+      </c>
+      <c r="R174" t="n">
+        <v>100</v>
+      </c>
+      <c r="S174" t="n">
+        <v>0</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>dota2-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr"/>
+      <c r="W174" t="inlineStr"/>
+      <c r="X174" t="inlineStr"/>
+      <c r="Y174" t="inlineStr"/>
+      <c r="Z174" t="inlineStr"/>
+      <c r="AA174" t="inlineStr"/>
+      <c r="AB174" t="inlineStr"/>
+      <c r="AC174" t="inlineStr"/>
+      <c r="AD174" t="inlineStr"/>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-dota2-stx-tsa-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr"/>
+      <c r="AI174" t="inlineStr"/>
+      <c r="AJ174" t="inlineStr"/>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN174" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>Spirit Academy</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>Spirit Academy</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>Spirit Academy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AT174" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr"/>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>60cc774ad3002a7529570909940337a5af5782c2461438910bdcad9e470f34dd</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>dota2-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD174" t="inlineStr">
+        <is>
+          <t>60cc774ad3002a7529570909940337a5af5782c2461438910bdcad9e470f34dd</t>
+        </is>
+      </c>
+      <c r="BE174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG174" t="inlineStr">
+        <is>
+          <t>dota2-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH174" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:34:33.179770Z</t>
+        </is>
+      </c>
+      <c r="BI174" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ174" t="inlineStr"/>
+      <c r="BK174" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM174" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN174" t="inlineStr"/>
+      <c r="BO174" t="inlineStr"/>
+      <c r="BP174" t="inlineStr"/>
+      <c r="BQ174" t="inlineStr"/>
+      <c r="BR174" t="inlineStr"/>
+      <c r="BS174" t="inlineStr"/>
+      <c r="BT174" t="inlineStr"/>
+      <c r="BU174" t="inlineStr"/>
+      <c r="BV174" t="inlineStr"/>
+      <c r="BW174" t="inlineStr"/>
+      <c r="BX174" t="inlineStr"/>
+      <c r="BY174" t="inlineStr"/>
+      <c r="BZ174" t="inlineStr"/>
+      <c r="CA174" t="inlineStr"/>
+      <c r="CB174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>fb6f6e039a3b4ee2</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:34:34.693145Z</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-07-22T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>56146</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>150</v>
+      </c>
+      <c r="M175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0.625394</v>
+      </c>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="n">
+        <v>0.225394</v>
+      </c>
+      <c r="R175" t="n">
+        <v>100</v>
+      </c>
+      <c r="S175" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>dota2-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr"/>
+      <c r="W175" t="inlineStr"/>
+      <c r="X175" t="inlineStr"/>
+      <c r="Y175" t="inlineStr"/>
+      <c r="Z175" t="inlineStr"/>
+      <c r="AA175" t="inlineStr"/>
+      <c r="AB175" t="inlineStr"/>
+      <c r="AC175" t="inlineStr"/>
+      <c r="AD175" t="inlineStr"/>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-z10-lvlup-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr"/>
+      <c r="AI175" t="inlineStr"/>
+      <c r="AJ175" t="inlineStr"/>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL175" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN175" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AT175" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr"/>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>60cc774ad3002a7529570909940337a5af5782c2461438910bdcad9e470f34dd</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>dota2-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD175" t="inlineStr">
+        <is>
+          <t>60cc774ad3002a7529570909940337a5af5782c2461438910bdcad9e470f34dd</t>
+        </is>
+      </c>
+      <c r="BE175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG175" t="inlineStr">
+        <is>
+          <t>dota2-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH175" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:34:33.944559Z</t>
+        </is>
+      </c>
+      <c r="BI175" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ175" t="inlineStr"/>
+      <c r="BK175" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN175" t="inlineStr"/>
+      <c r="BO175" t="inlineStr"/>
+      <c r="BP175" t="inlineStr"/>
+      <c r="BQ175" t="inlineStr"/>
+      <c r="BR175" t="inlineStr"/>
+      <c r="BS175" t="inlineStr"/>
+      <c r="BT175" t="inlineStr"/>
+      <c r="BU175" t="inlineStr"/>
+      <c r="BV175" t="inlineStr"/>
+      <c r="BW175" t="inlineStr"/>
+      <c r="BX175" t="inlineStr"/>
+      <c r="BY175" t="inlineStr"/>
+      <c r="BZ175" t="inlineStr"/>
+      <c r="CA175" t="inlineStr"/>
+      <c r="CB175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>f4d2f718f0ad4a06</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:34:34.693145Z</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-07-22T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>56149</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>163</v>
+      </c>
+      <c r="M176" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="n">
+        <v>0.119772</v>
+      </c>
+      <c r="R176" t="n">
+        <v>100</v>
+      </c>
+      <c r="S176" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>dota2-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr"/>
+      <c r="W176" t="inlineStr"/>
+      <c r="X176" t="inlineStr"/>
+      <c r="Y176" t="inlineStr"/>
+      <c r="Z176" t="inlineStr"/>
+      <c r="AA176" t="inlineStr"/>
+      <c r="AB176" t="inlineStr"/>
+      <c r="AC176" t="inlineStr"/>
+      <c r="AD176" t="inlineStr"/>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-dota2-pckcp-tje-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr"/>
+      <c r="AI176" t="inlineStr"/>
+      <c r="AJ176" t="inlineStr"/>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN176" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AT176" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr"/>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>60cc774ad3002a7529570909940337a5af5782c2461438910bdcad9e470f34dd</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr">
+        <is>
+          <t>dota2-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD176" t="inlineStr">
+        <is>
+          <t>60cc774ad3002a7529570909940337a5af5782c2461438910bdcad9e470f34dd</t>
+        </is>
+      </c>
+      <c r="BE176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG176" t="inlineStr">
+        <is>
+          <t>dota2-neutral-series-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH176" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:34:34.692223Z</t>
+        </is>
+      </c>
+      <c r="BI176" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ176" t="inlineStr"/>
+      <c r="BK176" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL176" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM176" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN176" t="inlineStr"/>
+      <c r="BO176" t="inlineStr"/>
+      <c r="BP176" t="inlineStr"/>
+      <c r="BQ176" t="inlineStr"/>
+      <c r="BR176" t="inlineStr"/>
+      <c r="BS176" t="inlineStr"/>
+      <c r="BT176" t="inlineStr"/>
+      <c r="BU176" t="inlineStr"/>
+      <c r="BV176" t="inlineStr"/>
+      <c r="BW176" t="inlineStr"/>
+      <c r="BX176" t="inlineStr"/>
+      <c r="BY176" t="inlineStr"/>
+      <c r="BZ176" t="inlineStr"/>
+      <c r="CA176" t="inlineStr"/>
+      <c r="CB176" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -1805,11 +1805,11 @@
         <v>0.65035</v>
       </c>
       <c r="O4" t="n">
-        <v>0.567916</v>
+        <v>0.537085</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>-0.08243399999999999</v>
+        <v>-0.113265</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -2053,11 +2053,11 @@
         <v>0.640288</v>
       </c>
       <c r="O5" t="n">
-        <v>0.57491</v>
+        <v>0.471633</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>-0.06537800000000001</v>
+        <v>-0.168655</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>-0.180511</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>dota2-neutral-series-elo-v2</t>
+          <t>dota2-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -3795,11 +3795,11 @@
         <v>0.420168</v>
       </c>
       <c r="O12" t="n">
-        <v>0.583304</v>
+        <v>0.5</v>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>0.163136</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>100</v>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>dota2-neutral-series-elo-v2</t>
+          <t>dota2-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -4043,11 +4043,11 @@
         <v>0.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0.625394</v>
+        <v>0.5</v>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
-        <v>0.225394</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>100</v>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>dota2-neutral-series-elo-v2</t>
+          <t>dota2-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
-        <v>0.119772</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>100</v>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>dota2-neutral-series-elo-v2</t>
+          <t>dota2-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="n">
-        <v>-0.169967</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>dota2-neutral-series-elo-v2</t>
+          <t>dota2-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -7267,11 +7267,11 @@
         <v>0.539171</v>
       </c>
       <c r="O26" t="n">
-        <v>0.625647</v>
+        <v>0.700126</v>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
-        <v>0.086476</v>
+        <v>0.160955</v>
       </c>
       <c r="R26" t="n">
         <v>63</v>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -7515,11 +7515,11 @@
         <v>0.619772</v>
       </c>
       <c r="O27" t="n">
-        <v>0.651459</v>
+        <v>0.769629</v>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
-        <v>0.031687</v>
+        <v>0.149857</v>
       </c>
       <c r="R27" t="n">
         <v>36</v>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -7763,11 +7763,11 @@
         <v>0.6997</v>
       </c>
       <c r="O28" t="n">
-        <v>0.6156779999999999</v>
+        <v>0.651112</v>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="n">
-        <v>-0.084022</v>
+        <v>-0.048588</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -8011,11 +8011,11 @@
         <v>0.309598</v>
       </c>
       <c r="O29" t="n">
-        <v>0.549502</v>
+        <v>0.600415</v>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="n">
-        <v>0.239904</v>
+        <v>0.290817</v>
       </c>
       <c r="R29" t="n">
         <v>100</v>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -8259,11 +8259,11 @@
         <v>0.420168</v>
       </c>
       <c r="O30" t="n">
-        <v>0.589489</v>
+        <v>0.589971</v>
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
-        <v>0.169321</v>
+        <v>0.169803</v>
       </c>
       <c r="R30" t="n">
         <v>100</v>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -8507,11 +8507,11 @@
         <v>0.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0.689025</v>
+        <v>0.662969</v>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
-        <v>0.08902500000000001</v>
+        <v>0.062969</v>
       </c>
       <c r="R31" t="n">
         <v>65</v>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -8755,11 +8755,11 @@
         <v>0.54955</v>
       </c>
       <c r="O32" t="n">
-        <v>0.501696</v>
+        <v>0.556402</v>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="n">
-        <v>-0.047854</v>
+        <v>0.006852</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -9003,11 +9003,11 @@
         <v>0.669967</v>
       </c>
       <c r="O33" t="n">
-        <v>0.612384</v>
+        <v>0.7733100000000001</v>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="n">
-        <v>-0.057583</v>
+        <v>0.103343</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -10023,11 +10023,11 @@
         <v>0.579832</v>
       </c>
       <c r="O37" t="n">
-        <v>0.577373</v>
+        <v>0.5</v>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="n">
-        <v>-0.002627</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -10037,7 +10037,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>dota2-neutral-series-elo-v1</t>
+          <t>dota2-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -13429,11 +13429,11 @@
         <v>0.6997</v>
       </c>
       <c r="O50" t="n">
-        <v>0.704201</v>
+        <v>0.6887720000000001</v>
       </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="n">
-        <v>0.004201</v>
+        <v>-0.010928</v>
       </c>
       <c r="R50" t="n">
         <v>4</v>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -13691,11 +13691,11 @@
         <v>0.659864</v>
       </c>
       <c r="O51" t="n">
-        <v>0.603723</v>
+        <v>0.5767600000000001</v>
       </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="n">
-        <v>-0.056277</v>
+        <v>-0.083104</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -13705,7 +13705,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
@@ -13953,11 +13953,11 @@
         <v>0.320513</v>
       </c>
       <c r="O52" t="n">
-        <v>0.59232</v>
+        <v>0.563621</v>
       </c>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
-        <v>0.27232</v>
+        <v>0.243108</v>
       </c>
       <c r="R52" t="n">
         <v>100</v>
@@ -13967,7 +13967,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -14215,11 +14215,11 @@
         <v>0.669967</v>
       </c>
       <c r="O53" t="n">
-        <v>0.731785</v>
+        <v>0.753541</v>
       </c>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="n">
-        <v>0.061785</v>
+        <v>0.083574</v>
       </c>
       <c r="R53" t="n">
         <v>61</v>
@@ -14229,7 +14229,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -14477,11 +14477,11 @@
         <v>0.659864</v>
       </c>
       <c r="O54" t="n">
-        <v>0.748054</v>
+        <v>0.8542149999999999</v>
       </c>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="n">
-        <v>0.08805399999999999</v>
+        <v>0.194351</v>
       </c>
       <c r="R54" t="n">
         <v>88</v>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -14739,11 +14739,11 @@
         <v>0.469484</v>
       </c>
       <c r="O55" t="n">
-        <v>0.503502</v>
+        <v>0.5</v>
       </c>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="n">
-        <v>0.033502</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>33</v>
@@ -14753,7 +14753,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -15001,11 +15001,11 @@
         <v>0.65035</v>
       </c>
       <c r="O56" t="n">
-        <v>0.650024</v>
+        <v>0.616388</v>
       </c>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="n">
-        <v>2.4e-05</v>
+        <v>-0.033962</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -15263,11 +15263,11 @@
         <v>0.590164</v>
       </c>
       <c r="O57" t="n">
-        <v>0.650242</v>
+        <v>0.615103</v>
       </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="n">
-        <v>0.060242</v>
+        <v>0.024939</v>
       </c>
       <c r="R57" t="n">
         <v>60</v>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -15525,11 +15525,11 @@
         <v>0.340136</v>
       </c>
       <c r="O58" t="n">
-        <v>0.75</v>
+        <v>0.958215</v>
       </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="n">
-        <v>0.41</v>
+        <v>0.618079</v>
       </c>
       <c r="R58" t="n">
         <v>100</v>
@@ -15539,7 +15539,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -15787,11 +15787,11 @@
         <v>0.409836</v>
       </c>
       <c r="O59" t="n">
-        <v>0.7499980000000001</v>
+        <v>0.933732</v>
       </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="n">
-        <v>0.339998</v>
+        <v>0.523896</v>
       </c>
       <c r="R59" t="n">
         <v>100</v>
@@ -15801,7 +15801,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -3055,7 +3055,7 @@
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>-0.070815</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>valorant-neutral-series-elo-v2</t>
+          <t>valorant-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>-0.059471</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>valorant-neutral-series-elo-v2</t>
+          <t>valorant-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>valorant-neutral-series-elo-v1</t>
+          <t>valorant-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9513,7 +9513,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>valorant-neutral-series-elo-v1</t>
+          <t>valorant-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9775,7 +9775,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>valorant-neutral-series-elo-v1</t>
+          <t>valorant-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CB126" headerRowCount="1">
-  <autoFilter ref="A1:CB126"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CB137" headerRowCount="1">
+  <autoFilter ref="A1:CB137"/>
   <tableColumns count="80">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -739,19 +739,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$126)</f>
+        <f>COUNTA('Picks'!$A$2:$A$137)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$126,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$137,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$126,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$137,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$126,"settled",'Picks'!$V$2:$V$126,"win")+COUNTIFS('Picks'!$U$2:$U$126,"settled",'Picks'!$V$2:$V$126,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")+COUNTIFS('Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -779,19 +779,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$126,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$137,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$126,"&gt;0",'Picks'!$V$2:$V$126,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$126,"&gt;0",'Picks'!$V$2:$V$126,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$126,"&gt;0",'Picks'!$V$2:$V$126,"win")/(COUNTIFS('Picks'!$BX$2:$BX$126,"&gt;0",'Picks'!$V$2:$V$126,"win")+COUNTIFS('Picks'!$BX$2:$BX$126,"&gt;0",'Picks'!$V$2:$V$126,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"win")/(COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"win")+COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$126)/SUM('Picks'!$BX$2:$BX$126),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$137)/SUM('Picks'!$BX$2:$BX$137),0)</f>
         <v/>
       </c>
     </row>
@@ -819,19 +819,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$126)</f>
+        <f>SUM('Picks'!$BY$2:$BY$137)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$126,"&lt;&gt;",'Picks'!$AB$2:$AB$126),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$137,"&lt;&gt;",'Picks'!$AB$2:$AB$137),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$126,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$126,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$137,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$137,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$126,'Picks'!$AM$2:$AM$126,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$137,'Picks'!$AM$2:$AM$137,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -886,15 +886,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$126,$A14,'Picks'!$U$2:$U$126,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$126,$A14,'Picks'!$U$2:$U$126,"settled",'Picks'!$V$2:$V$126,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$126,$A14,'Picks'!$U$2:$U$126,"settled",'Picks'!$V$2:$V$126,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -902,11 +902,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$126,'Picks'!$H$2:$H$126,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$137,'Picks'!$H$2:$H$137,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$126,'Picks'!$H$2:$H$126,$A14,'Picks'!$U$2:$U$126,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$137,'Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -917,15 +917,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$126,$A15,'Picks'!$U$2:$U$126,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$126,$A15,'Picks'!$U$2:$U$126,"settled",'Picks'!$V$2:$V$126,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$126,$A15,'Picks'!$U$2:$U$126,"settled",'Picks'!$V$2:$V$126,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -933,11 +933,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$126,'Picks'!$H$2:$H$126,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$137,'Picks'!$H$2:$H$137,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$126,'Picks'!$H$2:$H$126,$A15,'Picks'!$U$2:$U$126,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$137,'Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -948,15 +948,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$126,$A16,'Picks'!$U$2:$U$126,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$126,$A16,'Picks'!$U$2:$U$126,"settled",'Picks'!$V$2:$V$126,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$126,$A16,'Picks'!$U$2:$U$126,"settled",'Picks'!$V$2:$V$126,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -964,11 +964,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$126,'Picks'!$H$2:$H$126,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$137,'Picks'!$H$2:$H$137,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$126,'Picks'!$H$2:$H$126,$A16,'Picks'!$U$2:$U$126,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$137,'Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -997,7 +997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CB126"/>
+  <dimension ref="A1:CB137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -33748,6 +33748,2734 @@
       <c r="CA126" s="31" t="n"/>
       <c r="CB126" s="24" t="n"/>
     </row>
+    <row r="127" ht="36" customHeight="1">
+      <c r="A127" s="24" t="inlineStr">
+        <is>
+          <t>d487a54363744159</t>
+        </is>
+      </c>
+      <c r="B127" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C127" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D127" s="24" t="inlineStr">
+        <is>
+          <t>55954</t>
+        </is>
+      </c>
+      <c r="E127" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F127" s="24" t="inlineStr">
+        <is>
+          <t>EDward Gaming</t>
+        </is>
+      </c>
+      <c r="G127" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="H127" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I127" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J127" s="25" t="n"/>
+      <c r="K127" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L127" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M127" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N127" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O127" s="28" t="n">
+        <v>0.528201</v>
+      </c>
+      <c r="P127" s="28" t="n"/>
+      <c r="Q127" s="28" t="n">
+        <v>-0.021349</v>
+      </c>
+      <c r="R127" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="S127" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T127" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U127" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V127" s="24" t="n"/>
+      <c r="W127" s="26" t="n"/>
+      <c r="X127" s="26" t="n"/>
+      <c r="Y127" s="25" t="n"/>
+      <c r="Z127" s="26" t="n"/>
+      <c r="AA127" s="28" t="n"/>
+      <c r="AB127" s="28" t="n"/>
+      <c r="AC127" s="30" t="n"/>
+      <c r="AD127" s="24" t="n"/>
+      <c r="AE127" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-lgd-edg-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF127" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG127" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH127" s="24" t="n"/>
+      <c r="AI127" s="31" t="n"/>
+      <c r="AJ127" s="31" t="n"/>
+      <c r="AK127" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL127" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM127" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN127" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO127" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP127" s="24" t="inlineStr">
+        <is>
+          <t>EDward Gaming</t>
+        </is>
+      </c>
+      <c r="AQ127" s="24" t="inlineStr">
+        <is>
+          <t>EDward Gaming</t>
+        </is>
+      </c>
+      <c r="AR127" s="24" t="inlineStr">
+        <is>
+          <t>EDward Gaming</t>
+        </is>
+      </c>
+      <c r="AS127" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AT127" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AU127" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AV127" s="24" t="n"/>
+      <c r="AW127" s="24" t="n"/>
+      <c r="AX127" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY127" s="24" t="n"/>
+      <c r="AZ127" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA127" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB127" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC127" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD127" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE127" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF127" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG127" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH127" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:02.737464Z</t>
+        </is>
+      </c>
+      <c r="BI127" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ127" s="25" t="n"/>
+      <c r="BK127" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL127" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM127" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN127" s="28" t="n"/>
+      <c r="BO127" s="28" t="n"/>
+      <c r="BP127" s="25" t="n"/>
+      <c r="BQ127" s="27" t="n"/>
+      <c r="BR127" s="28" t="n"/>
+      <c r="BS127" s="28" t="n"/>
+      <c r="BT127" s="28" t="n"/>
+      <c r="BU127" s="25" t="n"/>
+      <c r="BV127" s="29" t="n"/>
+      <c r="BW127" s="24" t="n"/>
+      <c r="BX127" s="30" t="n"/>
+      <c r="BY127" s="27" t="n"/>
+      <c r="BZ127" s="24" t="n"/>
+      <c r="CA127" s="31" t="n"/>
+      <c r="CB127" s="24" t="n"/>
+    </row>
+    <row r="128" ht="36" customHeight="1">
+      <c r="A128" s="24" t="inlineStr">
+        <is>
+          <t>53088914289f4187</t>
+        </is>
+      </c>
+      <c r="B128" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C128" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D128" s="24" t="inlineStr">
+        <is>
+          <t>55996</t>
+        </is>
+      </c>
+      <c r="E128" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F128" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="G128" s="24" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="H128" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I128" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J128" s="25" t="n"/>
+      <c r="K128" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L128" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M128" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N128" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O128" s="28" t="n">
+        <v>0.636655</v>
+      </c>
+      <c r="P128" s="28" t="n"/>
+      <c r="Q128" s="28" t="n">
+        <v>-0.053747</v>
+      </c>
+      <c r="R128" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T128" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U128" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V128" s="24" t="n"/>
+      <c r="W128" s="26" t="n"/>
+      <c r="X128" s="26" t="n"/>
+      <c r="Y128" s="25" t="n"/>
+      <c r="Z128" s="26" t="n"/>
+      <c r="AA128" s="28" t="n"/>
+      <c r="AB128" s="28" t="n"/>
+      <c r="AC128" s="30" t="n"/>
+      <c r="AD128" s="24" t="n"/>
+      <c r="AE128" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-tes-we-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF128" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG128" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH128" s="24" t="n"/>
+      <c r="AI128" s="31" t="n"/>
+      <c r="AJ128" s="31" t="n"/>
+      <c r="AK128" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL128" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM128" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN128" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO128" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP128" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AQ128" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AR128" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AS128" s="24" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="AT128" s="24" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="AU128" s="24" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="AV128" s="24" t="n"/>
+      <c r="AW128" s="24" t="n"/>
+      <c r="AX128" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY128" s="24" t="n"/>
+      <c r="AZ128" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA128" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB128" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC128" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD128" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE128" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF128" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG128" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH128" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:03.510789Z</t>
+        </is>
+      </c>
+      <c r="BI128" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ128" s="25" t="n"/>
+      <c r="BK128" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL128" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM128" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN128" s="28" t="n"/>
+      <c r="BO128" s="28" t="n"/>
+      <c r="BP128" s="25" t="n"/>
+      <c r="BQ128" s="27" t="n"/>
+      <c r="BR128" s="28" t="n"/>
+      <c r="BS128" s="28" t="n"/>
+      <c r="BT128" s="28" t="n"/>
+      <c r="BU128" s="25" t="n"/>
+      <c r="BV128" s="29" t="n"/>
+      <c r="BW128" s="24" t="n"/>
+      <c r="BX128" s="30" t="n"/>
+      <c r="BY128" s="27" t="n"/>
+      <c r="BZ128" s="24" t="n"/>
+      <c r="CA128" s="31" t="n"/>
+      <c r="CB128" s="24" t="n"/>
+    </row>
+    <row r="129" ht="36" customHeight="1">
+      <c r="A129" s="24" t="inlineStr">
+        <is>
+          <t>71faf50807664dea</t>
+        </is>
+      </c>
+      <c r="B129" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C129" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D129" s="24" t="inlineStr">
+        <is>
+          <t>56126</t>
+        </is>
+      </c>
+      <c r="E129" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F129" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="G129" s="24" t="inlineStr">
+        <is>
+          <t>HMBLE</t>
+        </is>
+      </c>
+      <c r="H129" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I129" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J129" s="25" t="n"/>
+      <c r="K129" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L129" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M129" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N129" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O129" s="28" t="n">
+        <v>0.575556</v>
+      </c>
+      <c r="P129" s="28" t="n"/>
+      <c r="Q129" s="28" t="n">
+        <v>-0.124144</v>
+      </c>
+      <c r="R129" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T129" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U129" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V129" s="24" t="n"/>
+      <c r="W129" s="26" t="n"/>
+      <c r="X129" s="26" t="n"/>
+      <c r="Y129" s="25" t="n"/>
+      <c r="Z129" s="26" t="n"/>
+      <c r="AA129" s="28" t="n"/>
+      <c r="AB129" s="28" t="n"/>
+      <c r="AC129" s="30" t="n"/>
+      <c r="AD129" s="24" t="n"/>
+      <c r="AE129" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-hmble-gmb-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF129" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG129" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH129" s="24" t="n"/>
+      <c r="AI129" s="31" t="n"/>
+      <c r="AJ129" s="31" t="n"/>
+      <c r="AK129" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL129" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM129" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN129" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO129" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP129" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AQ129" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AR129" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AS129" s="24" t="inlineStr">
+        <is>
+          <t>HMBLE</t>
+        </is>
+      </c>
+      <c r="AT129" s="24" t="inlineStr">
+        <is>
+          <t>HMBLE</t>
+        </is>
+      </c>
+      <c r="AU129" s="24" t="inlineStr">
+        <is>
+          <t>HMBLE</t>
+        </is>
+      </c>
+      <c r="AV129" s="24" t="n"/>
+      <c r="AW129" s="24" t="n"/>
+      <c r="AX129" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY129" s="24" t="n"/>
+      <c r="AZ129" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA129" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB129" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC129" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD129" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE129" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF129" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG129" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH129" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:10.295865Z</t>
+        </is>
+      </c>
+      <c r="BI129" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ129" s="25" t="n"/>
+      <c r="BK129" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL129" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM129" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN129" s="28" t="n"/>
+      <c r="BO129" s="28" t="n"/>
+      <c r="BP129" s="25" t="n"/>
+      <c r="BQ129" s="27" t="n"/>
+      <c r="BR129" s="28" t="n"/>
+      <c r="BS129" s="28" t="n"/>
+      <c r="BT129" s="28" t="n"/>
+      <c r="BU129" s="25" t="n"/>
+      <c r="BV129" s="29" t="n"/>
+      <c r="BW129" s="24" t="n"/>
+      <c r="BX129" s="30" t="n"/>
+      <c r="BY129" s="27" t="n"/>
+      <c r="BZ129" s="24" t="n"/>
+      <c r="CA129" s="31" t="n"/>
+      <c r="CB129" s="24" t="n"/>
+    </row>
+    <row r="130" ht="36" customHeight="1">
+      <c r="A130" s="24" t="inlineStr">
+        <is>
+          <t>f003875538a34221</t>
+        </is>
+      </c>
+      <c r="B130" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C130" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D130" s="24" t="inlineStr">
+        <is>
+          <t>58172</t>
+        </is>
+      </c>
+      <c r="E130" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F130" s="24" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="G130" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="H130" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I130" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J130" s="25" t="n"/>
+      <c r="K130" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L130" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M130" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N130" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O130" s="28" t="n">
+        <v>0.634815</v>
+      </c>
+      <c r="P130" s="28" t="n"/>
+      <c r="Q130" s="28" t="n">
+        <v>0.015043</v>
+      </c>
+      <c r="R130" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="S130" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T130" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U130" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V130" s="24" t="n"/>
+      <c r="W130" s="26" t="n"/>
+      <c r="X130" s="26" t="n"/>
+      <c r="Y130" s="25" t="n"/>
+      <c r="Z130" s="26" t="n"/>
+      <c r="AA130" s="28" t="n"/>
+      <c r="AB130" s="28" t="n"/>
+      <c r="AC130" s="30" t="n"/>
+      <c r="AD130" s="24" t="n"/>
+      <c r="AE130" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-khk-use-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF130" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG130" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH130" s="24" t="n"/>
+      <c r="AI130" s="31" t="n"/>
+      <c r="AJ130" s="31" t="n"/>
+      <c r="AK130" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL130" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM130" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN130" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO130" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP130" s="24" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AQ130" s="24" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AR130" s="24" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AS130" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AT130" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AU130" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AV130" s="24" t="n"/>
+      <c r="AW130" s="24" t="n"/>
+      <c r="AX130" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY130" s="24" t="n"/>
+      <c r="AZ130" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA130" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB130" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC130" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD130" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE130" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF130" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG130" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH130" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:11.065754Z</t>
+        </is>
+      </c>
+      <c r="BI130" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ130" s="25" t="n"/>
+      <c r="BK130" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL130" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM130" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN130" s="28" t="n"/>
+      <c r="BO130" s="28" t="n"/>
+      <c r="BP130" s="25" t="n"/>
+      <c r="BQ130" s="27" t="n"/>
+      <c r="BR130" s="28" t="n"/>
+      <c r="BS130" s="28" t="n"/>
+      <c r="BT130" s="28" t="n"/>
+      <c r="BU130" s="25" t="n"/>
+      <c r="BV130" s="29" t="n"/>
+      <c r="BW130" s="24" t="n"/>
+      <c r="BX130" s="30" t="n"/>
+      <c r="BY130" s="27" t="n"/>
+      <c r="BZ130" s="24" t="n"/>
+      <c r="CA130" s="31" t="n"/>
+      <c r="CB130" s="24" t="n"/>
+    </row>
+    <row r="131" ht="36" customHeight="1">
+      <c r="A131" s="24" t="inlineStr">
+        <is>
+          <t>b3933a7255314a9c</t>
+        </is>
+      </c>
+      <c r="B131" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C131" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="D131" s="24" t="inlineStr">
+        <is>
+          <t>56127</t>
+        </is>
+      </c>
+      <c r="E131" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F131" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="G131" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="H131" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I131" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J131" s="25" t="n"/>
+      <c r="K131" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L131" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M131" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N131" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O131" s="28" t="n">
+        <v>0.581485</v>
+      </c>
+      <c r="P131" s="28" t="n"/>
+      <c r="Q131" s="28" t="n">
+        <v>-0.018515</v>
+      </c>
+      <c r="R131" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="S131" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T131" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U131" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V131" s="24" t="n"/>
+      <c r="W131" s="26" t="n"/>
+      <c r="X131" s="26" t="n"/>
+      <c r="Y131" s="25" t="n"/>
+      <c r="Z131" s="26" t="n"/>
+      <c r="AA131" s="28" t="n"/>
+      <c r="AB131" s="28" t="n"/>
+      <c r="AC131" s="30" t="n"/>
+      <c r="AD131" s="24" t="n"/>
+      <c r="AE131" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-bar-ucam-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF131" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG131" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH131" s="24" t="n"/>
+      <c r="AI131" s="31" t="n"/>
+      <c r="AJ131" s="31" t="n"/>
+      <c r="AK131" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL131" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM131" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN131" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO131" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP131" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AQ131" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AR131" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AS131" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AT131" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AU131" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AV131" s="24" t="n"/>
+      <c r="AW131" s="24" t="n"/>
+      <c r="AX131" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY131" s="24" t="n"/>
+      <c r="AZ131" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA131" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB131" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC131" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD131" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE131" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF131" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG131" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH131" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:11.800383Z</t>
+        </is>
+      </c>
+      <c r="BI131" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ131" s="25" t="n"/>
+      <c r="BK131" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL131" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM131" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN131" s="28" t="n"/>
+      <c r="BO131" s="28" t="n"/>
+      <c r="BP131" s="25" t="n"/>
+      <c r="BQ131" s="27" t="n"/>
+      <c r="BR131" s="28" t="n"/>
+      <c r="BS131" s="28" t="n"/>
+      <c r="BT131" s="28" t="n"/>
+      <c r="BU131" s="25" t="n"/>
+      <c r="BV131" s="29" t="n"/>
+      <c r="BW131" s="24" t="n"/>
+      <c r="BX131" s="30" t="n"/>
+      <c r="BY131" s="27" t="n"/>
+      <c r="BZ131" s="24" t="n"/>
+      <c r="CA131" s="31" t="n"/>
+      <c r="CB131" s="24" t="n"/>
+    </row>
+    <row r="132" ht="36" customHeight="1">
+      <c r="A132" s="24" t="inlineStr">
+        <is>
+          <t>69fb3791da444f92</t>
+        </is>
+      </c>
+      <c r="B132" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C132" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D132" s="24" t="inlineStr">
+        <is>
+          <t>56129</t>
+        </is>
+      </c>
+      <c r="E132" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F132" s="24" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="G132" s="24" t="inlineStr">
+        <is>
+          <t>TITANS</t>
+        </is>
+      </c>
+      <c r="H132" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I132" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J132" s="25" t="n"/>
+      <c r="K132" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L132" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M132" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N132" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="O132" s="28" t="n">
+        <v>0.514184</v>
+      </c>
+      <c r="P132" s="28" t="n"/>
+      <c r="Q132" s="28" t="n">
+        <v>0.08499900000000001</v>
+      </c>
+      <c r="R132" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S132" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T132" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U132" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V132" s="24" t="n"/>
+      <c r="W132" s="26" t="n"/>
+      <c r="X132" s="26" t="n"/>
+      <c r="Y132" s="25" t="n"/>
+      <c r="Z132" s="26" t="n"/>
+      <c r="AA132" s="28" t="n"/>
+      <c r="AB132" s="28" t="n"/>
+      <c r="AC132" s="30" t="n"/>
+      <c r="AD132" s="24" t="n"/>
+      <c r="AE132" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-tts-eko-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF132" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG132" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH132" s="24" t="n"/>
+      <c r="AI132" s="31" t="n"/>
+      <c r="AJ132" s="31" t="n"/>
+      <c r="AK132" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL132" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM132" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN132" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO132" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP132" s="24" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="AQ132" s="24" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="AR132" s="24" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="AS132" s="24" t="inlineStr">
+        <is>
+          <t>TITANS</t>
+        </is>
+      </c>
+      <c r="AT132" s="24" t="inlineStr">
+        <is>
+          <t>TITANS</t>
+        </is>
+      </c>
+      <c r="AU132" s="24" t="inlineStr">
+        <is>
+          <t>TITANS</t>
+        </is>
+      </c>
+      <c r="AV132" s="24" t="n"/>
+      <c r="AW132" s="24" t="n"/>
+      <c r="AX132" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY132" s="24" t="n"/>
+      <c r="AZ132" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA132" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB132" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC132" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD132" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE132" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF132" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG132" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH132" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:13.396220Z</t>
+        </is>
+      </c>
+      <c r="BI132" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ132" s="25" t="n"/>
+      <c r="BK132" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="BL132" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM132" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="BN132" s="28" t="n"/>
+      <c r="BO132" s="28" t="n"/>
+      <c r="BP132" s="25" t="n"/>
+      <c r="BQ132" s="27" t="n"/>
+      <c r="BR132" s="28" t="n"/>
+      <c r="BS132" s="28" t="n"/>
+      <c r="BT132" s="28" t="n"/>
+      <c r="BU132" s="25" t="n"/>
+      <c r="BV132" s="29" t="n"/>
+      <c r="BW132" s="24" t="n"/>
+      <c r="BX132" s="30" t="n"/>
+      <c r="BY132" s="27" t="n"/>
+      <c r="BZ132" s="24" t="n"/>
+      <c r="CA132" s="31" t="n"/>
+      <c r="CB132" s="24" t="n"/>
+    </row>
+    <row r="133" ht="36" customHeight="1">
+      <c r="A133" s="24" t="inlineStr">
+        <is>
+          <t>acbde024ef4d41db</t>
+        </is>
+      </c>
+      <c r="B133" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C133" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D133" s="24" t="inlineStr">
+        <is>
+          <t>56130</t>
+        </is>
+      </c>
+      <c r="E133" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F133" s="24" t="inlineStr">
+        <is>
+          <t>Aeterna Esports</t>
+        </is>
+      </c>
+      <c r="G133" s="24" t="inlineStr">
+        <is>
+          <t>P11 Esports</t>
+        </is>
+      </c>
+      <c r="H133" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I133" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J133" s="25" t="n"/>
+      <c r="K133" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L133" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M133" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N133" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O133" s="28" t="n">
+        <v>0.518543</v>
+      </c>
+      <c r="P133" s="28" t="n"/>
+      <c r="Q133" s="28" t="n">
+        <v>-0.101229</v>
+      </c>
+      <c r="R133" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T133" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U133" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V133" s="24" t="n"/>
+      <c r="W133" s="26" t="n"/>
+      <c r="X133" s="26" t="n"/>
+      <c r="Y133" s="25" t="n"/>
+      <c r="Z133" s="26" t="n"/>
+      <c r="AA133" s="28" t="n"/>
+      <c r="AB133" s="28" t="n"/>
+      <c r="AC133" s="30" t="n"/>
+      <c r="AD133" s="24" t="n"/>
+      <c r="AE133" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-p11-aee-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF133" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG133" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH133" s="24" t="n"/>
+      <c r="AI133" s="31" t="n"/>
+      <c r="AJ133" s="31" t="n"/>
+      <c r="AK133" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL133" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM133" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN133" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO133" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP133" s="24" t="inlineStr">
+        <is>
+          <t>Aeterna Esports</t>
+        </is>
+      </c>
+      <c r="AQ133" s="24" t="inlineStr">
+        <is>
+          <t>Aeterna Esports</t>
+        </is>
+      </c>
+      <c r="AR133" s="24" t="inlineStr">
+        <is>
+          <t>Aeterna Esports</t>
+        </is>
+      </c>
+      <c r="AS133" s="24" t="inlineStr">
+        <is>
+          <t>P11 Esports</t>
+        </is>
+      </c>
+      <c r="AT133" s="24" t="inlineStr">
+        <is>
+          <t>P11 Esports</t>
+        </is>
+      </c>
+      <c r="AU133" s="24" t="inlineStr">
+        <is>
+          <t>P11 Esports</t>
+        </is>
+      </c>
+      <c r="AV133" s="24" t="n"/>
+      <c r="AW133" s="24" t="n"/>
+      <c r="AX133" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY133" s="24" t="n"/>
+      <c r="AZ133" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA133" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB133" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC133" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD133" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE133" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF133" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG133" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH133" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:18.687465Z</t>
+        </is>
+      </c>
+      <c r="BI133" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ133" s="25" t="n"/>
+      <c r="BK133" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL133" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM133" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN133" s="28" t="n"/>
+      <c r="BO133" s="28" t="n"/>
+      <c r="BP133" s="25" t="n"/>
+      <c r="BQ133" s="27" t="n"/>
+      <c r="BR133" s="28" t="n"/>
+      <c r="BS133" s="28" t="n"/>
+      <c r="BT133" s="28" t="n"/>
+      <c r="BU133" s="25" t="n"/>
+      <c r="BV133" s="29" t="n"/>
+      <c r="BW133" s="24" t="n"/>
+      <c r="BX133" s="30" t="n"/>
+      <c r="BY133" s="27" t="n"/>
+      <c r="BZ133" s="24" t="n"/>
+      <c r="CA133" s="31" t="n"/>
+      <c r="CB133" s="24" t="n"/>
+    </row>
+    <row r="134" ht="36" customHeight="1">
+      <c r="A134" s="24" t="inlineStr">
+        <is>
+          <t>af7e142ab3744a4a</t>
+        </is>
+      </c>
+      <c r="B134" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C134" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D134" s="24" t="inlineStr">
+        <is>
+          <t>56132</t>
+        </is>
+      </c>
+      <c r="E134" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F134" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="G134" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="H134" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I134" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J134" s="25" t="n"/>
+      <c r="K134" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L134" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M134" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N134" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O134" s="28" t="n">
+        <v>0.600063</v>
+      </c>
+      <c r="P134" s="28" t="n"/>
+      <c r="Q134" s="28" t="n">
+        <v>0.09025900000000001</v>
+      </c>
+      <c r="R134" s="26" t="n">
+        <v>65</v>
+      </c>
+      <c r="S134" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T134" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U134" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V134" s="24" t="n"/>
+      <c r="W134" s="26" t="n"/>
+      <c r="X134" s="26" t="n"/>
+      <c r="Y134" s="25" t="n"/>
+      <c r="Z134" s="26" t="n"/>
+      <c r="AA134" s="28" t="n"/>
+      <c r="AB134" s="28" t="n"/>
+      <c r="AC134" s="30" t="n"/>
+      <c r="AD134" s="24" t="n"/>
+      <c r="AE134" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-kbm-itz-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF134" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG134" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH134" s="24" t="n"/>
+      <c r="AI134" s="31" t="n"/>
+      <c r="AJ134" s="31" t="n"/>
+      <c r="AK134" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL134" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM134" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN134" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO134" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP134" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AQ134" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AR134" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AS134" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AT134" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AU134" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AV134" s="24" t="n"/>
+      <c r="AW134" s="24" t="n"/>
+      <c r="AX134" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY134" s="24" t="n"/>
+      <c r="AZ134" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA134" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB134" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC134" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD134" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE134" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF134" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG134" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH134" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:20.981406Z</t>
+        </is>
+      </c>
+      <c r="BI134" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ134" s="25" t="n"/>
+      <c r="BK134" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL134" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM134" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN134" s="28" t="n"/>
+      <c r="BO134" s="28" t="n"/>
+      <c r="BP134" s="25" t="n"/>
+      <c r="BQ134" s="27" t="n"/>
+      <c r="BR134" s="28" t="n"/>
+      <c r="BS134" s="28" t="n"/>
+      <c r="BT134" s="28" t="n"/>
+      <c r="BU134" s="25" t="n"/>
+      <c r="BV134" s="29" t="n"/>
+      <c r="BW134" s="24" t="n"/>
+      <c r="BX134" s="30" t="n"/>
+      <c r="BY134" s="27" t="n"/>
+      <c r="BZ134" s="24" t="n"/>
+      <c r="CA134" s="31" t="n"/>
+      <c r="CB134" s="24" t="n"/>
+    </row>
+    <row r="135" ht="36" customHeight="1">
+      <c r="A135" s="24" t="inlineStr">
+        <is>
+          <t>cb95d785b47c4574</t>
+        </is>
+      </c>
+      <c r="B135" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C135" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D135" s="24" t="inlineStr">
+        <is>
+          <t>56138</t>
+        </is>
+      </c>
+      <c r="E135" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F135" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="G135" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="H135" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I135" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J135" s="25" t="n"/>
+      <c r="K135" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L135" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M135" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N135" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O135" s="28" t="n">
+        <v>0.5449850000000001</v>
+      </c>
+      <c r="P135" s="28" t="n"/>
+      <c r="Q135" s="28" t="n">
+        <v>0.124817</v>
+      </c>
+      <c r="R135" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S135" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T135" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U135" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V135" s="24" t="n"/>
+      <c r="W135" s="26" t="n"/>
+      <c r="X135" s="26" t="n"/>
+      <c r="Y135" s="25" t="n"/>
+      <c r="Z135" s="26" t="n"/>
+      <c r="AA135" s="28" t="n"/>
+      <c r="AB135" s="28" t="n"/>
+      <c r="AC135" s="30" t="n"/>
+      <c r="AD135" s="24" t="n"/>
+      <c r="AE135" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-nerd-7rex-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF135" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG135" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH135" s="24" t="n"/>
+      <c r="AI135" s="31" t="n"/>
+      <c r="AJ135" s="31" t="n"/>
+      <c r="AK135" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL135" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM135" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN135" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO135" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP135" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AQ135" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AR135" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AS135" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AT135" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AU135" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AV135" s="24" t="n"/>
+      <c r="AW135" s="24" t="n"/>
+      <c r="AX135" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY135" s="24" t="n"/>
+      <c r="AZ135" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA135" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB135" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC135" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD135" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE135" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF135" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG135" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH135" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:24.819172Z</t>
+        </is>
+      </c>
+      <c r="BI135" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ135" s="25" t="n"/>
+      <c r="BK135" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL135" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM135" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN135" s="28" t="n"/>
+      <c r="BO135" s="28" t="n"/>
+      <c r="BP135" s="25" t="n"/>
+      <c r="BQ135" s="27" t="n"/>
+      <c r="BR135" s="28" t="n"/>
+      <c r="BS135" s="28" t="n"/>
+      <c r="BT135" s="28" t="n"/>
+      <c r="BU135" s="25" t="n"/>
+      <c r="BV135" s="29" t="n"/>
+      <c r="BW135" s="24" t="n"/>
+      <c r="BX135" s="30" t="n"/>
+      <c r="BY135" s="27" t="n"/>
+      <c r="BZ135" s="24" t="n"/>
+      <c r="CA135" s="31" t="n"/>
+      <c r="CB135" s="24" t="n"/>
+    </row>
+    <row r="136" ht="36" customHeight="1">
+      <c r="A136" s="24" t="inlineStr">
+        <is>
+          <t>8af698b4ee2c496c</t>
+        </is>
+      </c>
+      <c r="B136" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C136" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D136" s="24" t="inlineStr">
+        <is>
+          <t>56810</t>
+        </is>
+      </c>
+      <c r="E136" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F136" s="24" t="inlineStr">
+        <is>
+          <t>Anyone's Legend</t>
+        </is>
+      </c>
+      <c r="G136" s="24" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="H136" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I136" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J136" s="25" t="n"/>
+      <c r="K136" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L136" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M136" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N136" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O136" s="28" t="n">
+        <v>0.529047</v>
+      </c>
+      <c r="P136" s="28" t="n"/>
+      <c r="Q136" s="28" t="n">
+        <v>-0.050785</v>
+      </c>
+      <c r="R136" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T136" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U136" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V136" s="24" t="n"/>
+      <c r="W136" s="26" t="n"/>
+      <c r="X136" s="26" t="n"/>
+      <c r="Y136" s="25" t="n"/>
+      <c r="Z136" s="26" t="n"/>
+      <c r="AA136" s="28" t="n"/>
+      <c r="AB136" s="28" t="n"/>
+      <c r="AC136" s="30" t="n"/>
+      <c r="AD136" s="24" t="n"/>
+      <c r="AE136" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-jdg-al-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF136" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG136" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH136" s="24" t="n"/>
+      <c r="AI136" s="31" t="n"/>
+      <c r="AJ136" s="31" t="n"/>
+      <c r="AK136" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM136" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN136" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO136" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP136" s="24" t="inlineStr">
+        <is>
+          <t>Anyone's Legend</t>
+        </is>
+      </c>
+      <c r="AQ136" s="24" t="inlineStr">
+        <is>
+          <t>Anyone's Legend</t>
+        </is>
+      </c>
+      <c r="AR136" s="24" t="inlineStr">
+        <is>
+          <t>Anyone's Legend</t>
+        </is>
+      </c>
+      <c r="AS136" s="24" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="AT136" s="24" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="AU136" s="24" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="AV136" s="24" t="n"/>
+      <c r="AW136" s="24" t="n"/>
+      <c r="AX136" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY136" s="24" t="n"/>
+      <c r="AZ136" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA136" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB136" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC136" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD136" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE136" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF136" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG136" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH136" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:27.088741Z</t>
+        </is>
+      </c>
+      <c r="BI136" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ136" s="25" t="n"/>
+      <c r="BK136" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL136" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM136" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN136" s="28" t="n"/>
+      <c r="BO136" s="28" t="n"/>
+      <c r="BP136" s="25" t="n"/>
+      <c r="BQ136" s="27" t="n"/>
+      <c r="BR136" s="28" t="n"/>
+      <c r="BS136" s="28" t="n"/>
+      <c r="BT136" s="28" t="n"/>
+      <c r="BU136" s="25" t="n"/>
+      <c r="BV136" s="29" t="n"/>
+      <c r="BW136" s="24" t="n"/>
+      <c r="BX136" s="30" t="n"/>
+      <c r="BY136" s="27" t="n"/>
+      <c r="BZ136" s="24" t="n"/>
+      <c r="CA136" s="31" t="n"/>
+      <c r="CB136" s="24" t="n"/>
+    </row>
+    <row r="137" ht="36" customHeight="1">
+      <c r="A137" s="24" t="inlineStr">
+        <is>
+          <t>2fc0c6b918364ae8</t>
+        </is>
+      </c>
+      <c r="B137" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C137" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D137" s="24" t="inlineStr">
+        <is>
+          <t>57088</t>
+        </is>
+      </c>
+      <c r="E137" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F137" s="24" t="inlineStr">
+        <is>
+          <t>Dynasty</t>
+        </is>
+      </c>
+      <c r="G137" s="24" t="inlineStr">
+        <is>
+          <t>Myth Esports</t>
+        </is>
+      </c>
+      <c r="H137" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I137" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J137" s="25" t="n"/>
+      <c r="K137" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L137" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M137" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N137" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O137" s="28" t="n">
+        <v>0.501096</v>
+      </c>
+      <c r="P137" s="28" t="n"/>
+      <c r="Q137" s="28" t="n">
+        <v>0.080928</v>
+      </c>
+      <c r="R137" s="26" t="n">
+        <v>60</v>
+      </c>
+      <c r="S137" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T137" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U137" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V137" s="24" t="n"/>
+      <c r="W137" s="26" t="n"/>
+      <c r="X137" s="26" t="n"/>
+      <c r="Y137" s="25" t="n"/>
+      <c r="Z137" s="26" t="n"/>
+      <c r="AA137" s="28" t="n"/>
+      <c r="AB137" s="28" t="n"/>
+      <c r="AC137" s="30" t="n"/>
+      <c r="AD137" s="24" t="n"/>
+      <c r="AE137" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-myth-dyn-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF137" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG137" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH137" s="24" t="n"/>
+      <c r="AI137" s="31" t="n"/>
+      <c r="AJ137" s="31" t="n"/>
+      <c r="AK137" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL137" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM137" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN137" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO137" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP137" s="24" t="inlineStr">
+        <is>
+          <t>Dynasty</t>
+        </is>
+      </c>
+      <c r="AQ137" s="24" t="inlineStr">
+        <is>
+          <t>Dynasty</t>
+        </is>
+      </c>
+      <c r="AR137" s="24" t="inlineStr">
+        <is>
+          <t>Dynasty</t>
+        </is>
+      </c>
+      <c r="AS137" s="24" t="inlineStr">
+        <is>
+          <t>Myth Esports</t>
+        </is>
+      </c>
+      <c r="AT137" s="24" t="inlineStr">
+        <is>
+          <t>Myth Esports</t>
+        </is>
+      </c>
+      <c r="AU137" s="24" t="inlineStr">
+        <is>
+          <t>Myth Esports</t>
+        </is>
+      </c>
+      <c r="AV137" s="24" t="n"/>
+      <c r="AW137" s="24" t="n"/>
+      <c r="AX137" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY137" s="24" t="n"/>
+      <c r="AZ137" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA137" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB137" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC137" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD137" s="24" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE137" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF137" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG137" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH137" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:33.061872Z</t>
+        </is>
+      </c>
+      <c r="BI137" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ137" s="25" t="n"/>
+      <c r="BK137" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL137" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM137" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN137" s="28" t="n"/>
+      <c r="BO137" s="28" t="n"/>
+      <c r="BP137" s="25" t="n"/>
+      <c r="BQ137" s="27" t="n"/>
+      <c r="BR137" s="28" t="n"/>
+      <c r="BS137" s="28" t="n"/>
+      <c r="BT137" s="28" t="n"/>
+      <c r="BU137" s="25" t="n"/>
+      <c r="BV137" s="29" t="n"/>
+      <c r="BW137" s="24" t="n"/>
+      <c r="BX137" s="30" t="n"/>
+      <c r="BY137" s="27" t="n"/>
+      <c r="BZ137" s="24" t="n"/>
+      <c r="CA137" s="31" t="n"/>
+      <c r="CB137" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CB137" headerRowCount="1">
-  <autoFilter ref="A1:CB137"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CB117" headerRowCount="1">
+  <autoFilter ref="A1:CB117"/>
   <tableColumns count="80">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -739,19 +739,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$137)</f>
+        <f>COUNTA('Picks'!$A$2:$A$117)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$137,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$117,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$137,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")+COUNTIFS('Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")+COUNTIFS('Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -779,19 +779,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$137,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$117,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"win")/(COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"win")+COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"win")/(COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"win")+COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$137)/SUM('Picks'!$BX$2:$BX$137),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$117)/SUM('Picks'!$BX$2:$BX$117),0)</f>
         <v/>
       </c>
     </row>
@@ -819,19 +819,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$137)</f>
+        <f>SUM('Picks'!$BY$2:$BY$117)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$137,"&lt;&gt;",'Picks'!$AB$2:$AB$137),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$117,"&lt;&gt;",'Picks'!$AB$2:$AB$117),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$137,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$137,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$117,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$137,'Picks'!$AM$2:$AM$137,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$117,'Picks'!$AM$2:$AM$117,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -886,15 +886,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -902,11 +902,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$137,'Picks'!$H$2:$H$137,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$117,'Picks'!$H$2:$H$117,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$137,'Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$117,'Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -917,15 +917,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -933,11 +933,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$137,'Picks'!$H$2:$H$137,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$117,'Picks'!$H$2:$H$117,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$137,'Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$117,'Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -948,15 +948,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -964,11 +964,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$137,'Picks'!$H$2:$H$137,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$117,'Picks'!$H$2:$H$117,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$137,'Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$117,'Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -997,7 +997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CB137"/>
+  <dimension ref="A1:CB117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -29001,37 +29001,37 @@
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="24" t="inlineStr">
         <is>
-          <t>1abb899dd64e4da4</t>
+          <t>4901d34aa34e4eec</t>
         </is>
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:16:38.961882Z</t>
+          <t>2026-07-22T05:16:51.311842Z</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T15:00:00-0400</t>
+          <t>2026-07-22T14:10:00-0400</t>
         </is>
       </c>
       <c r="D108" s="24" t="inlineStr">
         <is>
-          <t>401857086</t>
+          <t>401816225</t>
         </is>
       </c>
       <c r="E108" s="24" t="inlineStr">
         <is>
-          <t>WNBA</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="F108" s="24" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="G108" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="H108" s="24" t="inlineStr">
@@ -29051,30 +29051,30 @@
         </is>
       </c>
       <c r="L108" s="26" t="n">
-        <v>-127</v>
+        <v>-138</v>
       </c>
       <c r="M108" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.724638</v>
       </c>
       <c r="N108" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.579832</v>
       </c>
       <c r="O108" s="28" t="n">
-        <v>0.506317</v>
+        <v>0.659782</v>
       </c>
       <c r="P108" s="28" t="n"/>
       <c r="Q108" s="28" t="n">
-        <v>-0.053154</v>
+        <v>0.07994999999999999</v>
       </c>
       <c r="R108" s="26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="S108" s="29" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="T108" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v4</t>
+          <t>mlb-elo-trend-lr-v5</t>
         </is>
       </c>
       <c r="U108" s="24" t="inlineStr">
@@ -29093,7 +29093,7 @@
       <c r="AD108" s="24" t="n"/>
       <c r="AE108" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.5600 (aec-wnba-phx-la-2026-07-22).</t>
+          <t>Learned LR call at threshold 0.5998; executable ask 0.5800 (aec-mlb-nym-mil-2026-07-22).</t>
         </is>
       </c>
       <c r="AF108" s="31" t="inlineStr">
@@ -29111,7 +29111,7 @@
       <c r="AJ108" s="31" t="n"/>
       <c r="AK108" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL108" s="26" t="n">
@@ -29119,47 +29119,47 @@
       </c>
       <c r="AM108" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN108" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO108" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP108" s="24" t="inlineStr">
         <is>
-          <t>wnba-phx</t>
+          <t>mlb-nym</t>
         </is>
       </c>
       <c r="AQ108" s="24" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AR108" s="24" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AS108" s="24" t="inlineStr">
         <is>
-          <t>wnba-las</t>
+          <t>mlb-mil</t>
         </is>
       </c>
       <c r="AT108" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AU108" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AV108" s="24" t="n"/>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="BA108" s="24" t="inlineStr">
         <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB108" s="24" t="inlineStr">
@@ -29187,17 +29187,17 @@
       </c>
       <c r="BC108" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v4</t>
+          <t>mlb-elo-trend-lr-v5</t>
         </is>
       </c>
       <c r="BD108" s="24" t="inlineStr">
         <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BE108" s="24" t="inlineStr">
         <is>
-          <t>8dc26f367dd0a935</t>
+          <t>040d74b8467fee0f</t>
         </is>
       </c>
       <c r="BF108" s="24" t="inlineStr">
@@ -29207,12 +29207,12 @@
       </c>
       <c r="BG108" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v4</t>
+          <t>mlb-elo-trend-lr-v5</t>
         </is>
       </c>
       <c r="BH108" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:15:39.568650Z</t>
+          <t>2026-07-22T05:15:16.419329Z</t>
         </is>
       </c>
       <c r="BI108" s="24" t="inlineStr">
@@ -29222,16 +29222,16 @@
       </c>
       <c r="BJ108" s="25" t="n"/>
       <c r="BK108" s="26" t="n">
-        <v>-127</v>
+        <v>-138</v>
       </c>
       <c r="BL108" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.724638</v>
       </c>
       <c r="BM108" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.579832</v>
       </c>
       <c r="BN108" s="28" t="n">
-        <v>0.554455</v>
+        <v>0.577114</v>
       </c>
       <c r="BO108" s="28" t="n"/>
       <c r="BP108" s="25" t="n"/>
@@ -29251,37 +29251,37 @@
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="24" t="inlineStr">
         <is>
-          <t>ff31c4ff2f6c42db</t>
+          <t>69fb3791da444f92</t>
         </is>
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:16:38.961882Z</t>
+          <t>2026-07-22T05:19:52.182978Z</t>
         </is>
       </c>
       <c r="C109" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T15:00:00-0400</t>
+          <t>2026-07-22T18:00:00Z</t>
         </is>
       </c>
       <c r="D109" s="24" t="inlineStr">
         <is>
-          <t>401857087</t>
+          <t>56129</t>
         </is>
       </c>
       <c r="E109" s="24" t="inlineStr">
         <is>
-          <t>WNBA</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F109" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>EKO Esports</t>
         </is>
       </c>
       <c r="G109" s="24" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>TITANS</t>
         </is>
       </c>
       <c r="H109" s="24" t="inlineStr">
@@ -29291,7 +29291,7 @@
       </c>
       <c r="I109" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J109" s="25" t="n"/>
@@ -29301,30 +29301,30 @@
         </is>
       </c>
       <c r="L109" s="26" t="n">
-        <v>-426</v>
+        <v>133</v>
       </c>
       <c r="M109" s="27" t="n">
-        <v>1.234742</v>
+        <v>2.33</v>
       </c>
       <c r="N109" s="28" t="n">
-        <v>0.809886</v>
+        <v>0.429185</v>
       </c>
       <c r="O109" s="28" t="n">
-        <v>0.741409</v>
+        <v>0.514184</v>
       </c>
       <c r="P109" s="28" t="n"/>
       <c r="Q109" s="28" t="n">
-        <v>-0.068477</v>
+        <v>0.08499900000000001</v>
       </c>
       <c r="R109" s="26" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="S109" s="29" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="T109" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v4</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U109" s="24" t="inlineStr">
@@ -29343,12 +29343,12 @@
       <c r="AD109" s="24" t="n"/>
       <c r="AE109" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.8100 (aec-wnba-min-sea-2026-07-22).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-tts-eko-2026-07-22).</t>
         </is>
       </c>
       <c r="AF109" s="31" t="inlineStr">
         <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
         </is>
       </c>
       <c r="AG109" s="24" t="inlineStr">
@@ -29361,7 +29361,7 @@
       <c r="AJ109" s="31" t="n"/>
       <c r="AK109" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL109" s="26" t="n">
@@ -29369,47 +29369,47 @@
       </c>
       <c r="AM109" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN109" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO109" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP109" s="24" t="inlineStr">
         <is>
-          <t>wnba-min</t>
+          <t>EKO Esports</t>
         </is>
       </c>
       <c r="AQ109" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>EKO Esports</t>
         </is>
       </c>
       <c r="AR109" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>EKO Esports</t>
         </is>
       </c>
       <c r="AS109" s="24" t="inlineStr">
         <is>
-          <t>wnba-sea</t>
+          <t>TITANS</t>
         </is>
       </c>
       <c r="AT109" s="24" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>TITANS</t>
         </is>
       </c>
       <c r="AU109" s="24" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>TITANS</t>
         </is>
       </c>
       <c r="AV109" s="24" t="n"/>
@@ -29427,27 +29427,27 @@
       </c>
       <c r="BA109" s="24" t="inlineStr">
         <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB109" s="24" t="inlineStr">
         <is>
-          <t>learned_lr</t>
+          <t>neutral_elo</t>
         </is>
       </c>
       <c r="BC109" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v4</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="BD109" s="24" t="inlineStr">
         <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BE109" s="24" t="inlineStr">
         <is>
-          <t>e8704025c4f6d663</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BF109" s="24" t="inlineStr">
@@ -29457,12 +29457,12 @@
       </c>
       <c r="BG109" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v4</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="BH109" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:15:40.405611Z</t>
+          <t>2026-07-22T05:17:13.396220Z</t>
         </is>
       </c>
       <c r="BI109" s="24" t="inlineStr">
@@ -29472,17 +29472,15 @@
       </c>
       <c r="BJ109" s="25" t="n"/>
       <c r="BK109" s="26" t="n">
-        <v>-426</v>
+        <v>133</v>
       </c>
       <c r="BL109" s="27" t="n">
-        <v>1.234742</v>
+        <v>2.33</v>
       </c>
       <c r="BM109" s="28" t="n">
-        <v>0.809886</v>
-      </c>
-      <c r="BN109" s="28" t="n">
-        <v>0.80198</v>
-      </c>
+        <v>0.429185</v>
+      </c>
+      <c r="BN109" s="28" t="n"/>
       <c r="BO109" s="28" t="n"/>
       <c r="BP109" s="25" t="n"/>
       <c r="BQ109" s="27" t="n"/>
@@ -29501,37 +29499,37 @@
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="24" t="inlineStr">
         <is>
-          <t>faec2a24ca8841ee</t>
+          <t>af7e142ab3744a4a</t>
         </is>
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:16:38.961882Z</t>
+          <t>2026-07-22T05:19:52.182978Z</t>
         </is>
       </c>
       <c r="C110" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T19:00:00-0400</t>
+          <t>2026-07-22T20:00:00Z</t>
         </is>
       </c>
       <c r="D110" s="24" t="inlineStr">
         <is>
-          <t>401857088</t>
+          <t>56132</t>
         </is>
       </c>
       <c r="E110" s="24" t="inlineStr">
         <is>
-          <t>WNBA</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F110" s="24" t="inlineStr">
         <is>
-          <t>Chicago Sky</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="G110" s="24" t="inlineStr">
         <is>
-          <t>New York Liberty</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="H110" s="24" t="inlineStr">
@@ -29551,30 +29549,30 @@
         </is>
       </c>
       <c r="L110" s="26" t="n">
-        <v>-317</v>
+        <v>-104</v>
       </c>
       <c r="M110" s="27" t="n">
-        <v>1.315457</v>
+        <v>1.961538</v>
       </c>
       <c r="N110" s="28" t="n">
-        <v>0.760192</v>
+        <v>0.509804</v>
       </c>
       <c r="O110" s="28" t="n">
-        <v>0.61455</v>
+        <v>0.600063</v>
       </c>
       <c r="P110" s="28" t="n"/>
       <c r="Q110" s="28" t="n">
-        <v>-0.145642</v>
+        <v>0.09025900000000001</v>
       </c>
       <c r="R110" s="26" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S110" s="29" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="T110" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v4</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U110" s="24" t="inlineStr">
@@ -29593,12 +29591,12 @@
       <c r="AD110" s="24" t="n"/>
       <c r="AE110" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.7600 (aec-wnba-chi-ny-2026-07-22).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-kbm-itz-2026-07-22).</t>
         </is>
       </c>
       <c r="AF110" s="31" t="inlineStr">
         <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
         </is>
       </c>
       <c r="AG110" s="24" t="inlineStr">
@@ -29611,7 +29609,7 @@
       <c r="AJ110" s="31" t="n"/>
       <c r="AK110" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL110" s="26" t="n">
@@ -29619,47 +29617,47 @@
       </c>
       <c r="AM110" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN110" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO110" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP110" s="24" t="inlineStr">
         <is>
-          <t>wnba-chi</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AQ110" s="24" t="inlineStr">
         <is>
-          <t>Chicago Sky</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AR110" s="24" t="inlineStr">
         <is>
-          <t>Chicago Sky</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AS110" s="24" t="inlineStr">
         <is>
-          <t>wnba-nyl</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AT110" s="24" t="inlineStr">
         <is>
-          <t>New York Liberty</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AU110" s="24" t="inlineStr">
         <is>
-          <t>New York Liberty</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AV110" s="24" t="n"/>
@@ -29677,27 +29675,27 @@
       </c>
       <c r="BA110" s="24" t="inlineStr">
         <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB110" s="24" t="inlineStr">
         <is>
-          <t>learned_lr</t>
+          <t>neutral_elo</t>
         </is>
       </c>
       <c r="BC110" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v4</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="BD110" s="24" t="inlineStr">
         <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BE110" s="24" t="inlineStr">
         <is>
-          <t>b13fc19a9d17bb09</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BF110" s="24" t="inlineStr">
@@ -29707,12 +29705,12 @@
       </c>
       <c r="BG110" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v4</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="BH110" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:15:43.323657Z</t>
+          <t>2026-07-22T05:17:20.981406Z</t>
         </is>
       </c>
       <c r="BI110" s="24" t="inlineStr">
@@ -29722,17 +29720,15 @@
       </c>
       <c r="BJ110" s="25" t="n"/>
       <c r="BK110" s="26" t="n">
-        <v>-317</v>
+        <v>-104</v>
       </c>
       <c r="BL110" s="27" t="n">
-        <v>1.315457</v>
+        <v>1.961538</v>
       </c>
       <c r="BM110" s="28" t="n">
-        <v>0.760192</v>
-      </c>
-      <c r="BN110" s="28" t="n">
-        <v>0.752475</v>
-      </c>
+        <v>0.509804</v>
+      </c>
+      <c r="BN110" s="28" t="n"/>
       <c r="BO110" s="28" t="n"/>
       <c r="BP110" s="25" t="n"/>
       <c r="BQ110" s="27" t="n"/>
@@ -29751,37 +29747,37 @@
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="24" t="inlineStr">
         <is>
-          <t>f19789e645ed42fe</t>
+          <t>2fc0c6b918364ae8</t>
         </is>
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:16:38.961882Z</t>
+          <t>2026-07-22T05:19:52.182978Z</t>
         </is>
       </c>
       <c r="C111" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T19:30:00-0400</t>
+          <t>2026-07-23T17:00:00Z</t>
         </is>
       </c>
       <c r="D111" s="24" t="inlineStr">
         <is>
-          <t>401857089</t>
+          <t>57088</t>
         </is>
       </c>
       <c r="E111" s="24" t="inlineStr">
         <is>
-          <t>WNBA</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F111" s="24" t="inlineStr">
         <is>
-          <t>Las Vegas Aces</t>
+          <t>Dynasty</t>
         </is>
       </c>
       <c r="G111" s="24" t="inlineStr">
         <is>
-          <t>Washington Mystics</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="H111" s="24" t="inlineStr">
@@ -29801,30 +29797,30 @@
         </is>
       </c>
       <c r="L111" s="26" t="n">
-        <v>-233</v>
+        <v>138</v>
       </c>
       <c r="M111" s="27" t="n">
-        <v>1.429185</v>
+        <v>2.38</v>
       </c>
       <c r="N111" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.420168</v>
       </c>
       <c r="O111" s="28" t="n">
-        <v>0.577804</v>
+        <v>0.501096</v>
       </c>
       <c r="P111" s="28" t="n"/>
       <c r="Q111" s="28" t="n">
-        <v>-0.121896</v>
+        <v>0.080928</v>
       </c>
       <c r="R111" s="26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="S111" s="29" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="T111" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v4</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U111" s="24" t="inlineStr">
@@ -29843,12 +29839,12 @@
       <c r="AD111" s="24" t="n"/>
       <c r="AE111" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.7000 (aec-wnba-lv-wsh-2026-07-22).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-myth-dyn-2026-07-23).</t>
         </is>
       </c>
       <c r="AF111" s="31" t="inlineStr">
         <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
         </is>
       </c>
       <c r="AG111" s="24" t="inlineStr">
@@ -29861,7 +29857,7 @@
       <c r="AJ111" s="31" t="n"/>
       <c r="AK111" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL111" s="26" t="n">
@@ -29869,47 +29865,47 @@
       </c>
       <c r="AM111" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN111" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO111" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP111" s="24" t="inlineStr">
         <is>
-          <t>wnba-lva</t>
+          <t>Dynasty</t>
         </is>
       </c>
       <c r="AQ111" s="24" t="inlineStr">
         <is>
-          <t>Las Vegas Aces</t>
+          <t>Dynasty</t>
         </is>
       </c>
       <c r="AR111" s="24" t="inlineStr">
         <is>
-          <t>Las Vegas Aces</t>
+          <t>Dynasty</t>
         </is>
       </c>
       <c r="AS111" s="24" t="inlineStr">
         <is>
-          <t>wnba-was</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="AT111" s="24" t="inlineStr">
         <is>
-          <t>Washington Mystics</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="AU111" s="24" t="inlineStr">
         <is>
-          <t>Washington Mystics</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="AV111" s="24" t="n"/>
@@ -29927,27 +29923,27 @@
       </c>
       <c r="BA111" s="24" t="inlineStr">
         <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB111" s="24" t="inlineStr">
         <is>
-          <t>learned_lr</t>
+          <t>neutral_elo</t>
         </is>
       </c>
       <c r="BC111" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v4</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="BD111" s="24" t="inlineStr">
         <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BE111" s="24" t="inlineStr">
         <is>
-          <t>6a72fbb8276e803a</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BF111" s="24" t="inlineStr">
@@ -29957,12 +29953,12 @@
       </c>
       <c r="BG111" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v4</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="BH111" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:15:44.349117Z</t>
+          <t>2026-07-22T05:17:33.061872Z</t>
         </is>
       </c>
       <c r="BI111" s="24" t="inlineStr">
@@ -29972,17 +29968,15 @@
       </c>
       <c r="BJ111" s="25" t="n"/>
       <c r="BK111" s="26" t="n">
-        <v>-233</v>
+        <v>138</v>
       </c>
       <c r="BL111" s="27" t="n">
-        <v>1.429185</v>
+        <v>2.38</v>
       </c>
       <c r="BM111" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="BN111" s="28" t="n">
-        <v>0.693069</v>
-      </c>
+        <v>0.420168</v>
+      </c>
+      <c r="BN111" s="28" t="n"/>
       <c r="BO111" s="28" t="n"/>
       <c r="BP111" s="25" t="n"/>
       <c r="BQ111" s="27" t="n"/>
@@ -30001,22 +29995,22 @@
     <row r="112" ht="36" customHeight="1">
       <c r="A112" s="24" t="inlineStr">
         <is>
-          <t>6bb1f243f9d441f7</t>
+          <t>1f2e7b3cf1e34dce</t>
         </is>
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:16:38.961882Z</t>
+          <t>2026-07-22T05:34:16.990001Z</t>
         </is>
       </c>
       <c r="C112" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T20:00:00-0400</t>
+          <t>2026-07-22T15:00:00-0400</t>
         </is>
       </c>
       <c r="D112" s="24" t="inlineStr">
         <is>
-          <t>401857090</t>
+          <t>401857086</t>
         </is>
       </c>
       <c r="E112" s="24" t="inlineStr">
@@ -30026,12 +30020,12 @@
       </c>
       <c r="F112" s="24" t="inlineStr">
         <is>
-          <t>Connecticut Sun</t>
+          <t>Phoenix Mercury</t>
         </is>
       </c>
       <c r="G112" s="24" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Los Angeles Sparks</t>
         </is>
       </c>
       <c r="H112" s="24" t="inlineStr">
@@ -30051,26 +30045,26 @@
         </is>
       </c>
       <c r="L112" s="26" t="n">
-        <v>-400</v>
+        <v>-127</v>
       </c>
       <c r="M112" s="27" t="n">
-        <v>1.25</v>
+        <v>1.787402</v>
       </c>
       <c r="N112" s="28" t="n">
-        <v>0.8</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O112" s="28" t="n">
-        <v>0.74864</v>
+        <v>0.506317</v>
       </c>
       <c r="P112" s="28" t="n"/>
       <c r="Q112" s="28" t="n">
-        <v>-0.05136</v>
+        <v>-0.053154</v>
       </c>
       <c r="R112" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S112" s="29" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="T112" s="24" t="inlineStr">
         <is>
@@ -30093,7 +30087,7 @@
       <c r="AD112" s="24" t="n"/>
       <c r="AE112" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.8000 (aec-wnba-conn-ind-2026-07-22).</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5600 (aec-wnba-phx-la-2026-07-22).</t>
         </is>
       </c>
       <c r="AF112" s="31" t="inlineStr">
@@ -30134,32 +30128,32 @@
       </c>
       <c r="AP112" s="24" t="inlineStr">
         <is>
-          <t>wnba-con</t>
+          <t>wnba-phx</t>
         </is>
       </c>
       <c r="AQ112" s="24" t="inlineStr">
         <is>
-          <t>Connecticut Sun</t>
+          <t>Phoenix Mercury</t>
         </is>
       </c>
       <c r="AR112" s="24" t="inlineStr">
         <is>
-          <t>Connecticut Sun</t>
+          <t>Phoenix Mercury</t>
         </is>
       </c>
       <c r="AS112" s="24" t="inlineStr">
         <is>
-          <t>wnba-ind</t>
+          <t>wnba-las</t>
         </is>
       </c>
       <c r="AT112" s="24" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Los Angeles Sparks</t>
         </is>
       </c>
       <c r="AU112" s="24" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Los Angeles Sparks</t>
         </is>
       </c>
       <c r="AV112" s="24" t="n"/>
@@ -30197,7 +30191,7 @@
       </c>
       <c r="BE112" s="24" t="inlineStr">
         <is>
-          <t>8c0d6eee02b48cfb</t>
+          <t>8dc26f367dd0a935</t>
         </is>
       </c>
       <c r="BF112" s="24" t="inlineStr">
@@ -30212,7 +30206,7 @@
       </c>
       <c r="BH112" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:15:46.578897Z</t>
+          <t>2026-07-22T05:33:27.255086Z</t>
         </is>
       </c>
       <c r="BI112" s="24" t="inlineStr">
@@ -30222,16 +30216,16 @@
       </c>
       <c r="BJ112" s="25" t="n"/>
       <c r="BK112" s="26" t="n">
-        <v>-400</v>
+        <v>-127</v>
       </c>
       <c r="BL112" s="27" t="n">
-        <v>1.25</v>
+        <v>1.787402</v>
       </c>
       <c r="BM112" s="28" t="n">
-        <v>0.8</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN112" s="28" t="n">
-        <v>0.792079</v>
+        <v>0.554455</v>
       </c>
       <c r="BO112" s="28" t="n"/>
       <c r="BP112" s="25" t="n"/>
@@ -30251,22 +30245,22 @@
     <row r="113" ht="36" customHeight="1">
       <c r="A113" s="24" t="inlineStr">
         <is>
-          <t>d5eff2e71a884fac</t>
+          <t>0aaf95abdbce4f35</t>
         </is>
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:16:38.961882Z</t>
+          <t>2026-07-22T05:34:16.990001Z</t>
         </is>
       </c>
       <c r="C113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T22:00:00-0400</t>
+          <t>2026-07-22T15:00:00-0400</t>
         </is>
       </c>
       <c r="D113" s="24" t="inlineStr">
         <is>
-          <t>401857091</t>
+          <t>401857087</t>
         </is>
       </c>
       <c r="E113" s="24" t="inlineStr">
@@ -30276,12 +30270,12 @@
       </c>
       <c r="F113" s="24" t="inlineStr">
         <is>
-          <t>Dallas Wings</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="G113" s="24" t="inlineStr">
         <is>
-          <t>Portland Fire</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="H113" s="24" t="inlineStr">
@@ -30301,26 +30295,26 @@
         </is>
       </c>
       <c r="L113" s="26" t="n">
-        <v>-213</v>
+        <v>-426</v>
       </c>
       <c r="M113" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.234742</v>
       </c>
       <c r="N113" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.809886</v>
       </c>
       <c r="O113" s="28" t="n">
-        <v>0.614249</v>
+        <v>0.741409</v>
       </c>
       <c r="P113" s="28" t="n"/>
       <c r="Q113" s="28" t="n">
-        <v>-0.066262</v>
+        <v>-0.068477</v>
       </c>
       <c r="R113" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S113" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T113" s="24" t="inlineStr">
         <is>
@@ -30343,7 +30337,7 @@
       <c r="AD113" s="24" t="n"/>
       <c r="AE113" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.6800 (aec-wnba-dal-por-2026-07-22).</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8100 (aec-wnba-min-sea-2026-07-22).</t>
         </is>
       </c>
       <c r="AF113" s="31" t="inlineStr">
@@ -30384,32 +30378,32 @@
       </c>
       <c r="AP113" s="24" t="inlineStr">
         <is>
-          <t>wnba-dal</t>
+          <t>wnba-min</t>
         </is>
       </c>
       <c r="AQ113" s="24" t="inlineStr">
         <is>
-          <t>Dallas Wings</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="AR113" s="24" t="inlineStr">
         <is>
-          <t>Dallas Wings</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="AS113" s="24" t="inlineStr">
         <is>
-          <t>wnba-por</t>
+          <t>wnba-sea</t>
         </is>
       </c>
       <c r="AT113" s="24" t="inlineStr">
         <is>
-          <t>Portland Fire</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="AU113" s="24" t="inlineStr">
         <is>
-          <t>Portland Fire</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="AV113" s="24" t="n"/>
@@ -30447,7 +30441,7 @@
       </c>
       <c r="BE113" s="24" t="inlineStr">
         <is>
-          <t>f97350d4d81b330d</t>
+          <t>e8704025c4f6d663</t>
         </is>
       </c>
       <c r="BF113" s="24" t="inlineStr">
@@ -30462,7 +30456,7 @@
       </c>
       <c r="BH113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:15:47.716256Z</t>
+          <t>2026-07-22T05:33:28.200571Z</t>
         </is>
       </c>
       <c r="BI113" s="24" t="inlineStr">
@@ -30472,16 +30466,16 @@
       </c>
       <c r="BJ113" s="25" t="n"/>
       <c r="BK113" s="26" t="n">
-        <v>-213</v>
+        <v>-426</v>
       </c>
       <c r="BL113" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.234742</v>
       </c>
       <c r="BM113" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.809886</v>
       </c>
       <c r="BN113" s="28" t="n">
-        <v>0.6732669999999999</v>
+        <v>0.80198</v>
       </c>
       <c r="BO113" s="28" t="n"/>
       <c r="BP113" s="25" t="n"/>
@@ -30501,37 +30495,37 @@
     <row r="114" ht="36" customHeight="1">
       <c r="A114" s="24" t="inlineStr">
         <is>
-          <t>4901d34aa34e4eec</t>
+          <t>6a1584ce946d472c</t>
         </is>
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:16:51.311842Z</t>
+          <t>2026-07-22T05:34:16.990001Z</t>
         </is>
       </c>
       <c r="C114" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T14:10:00-0400</t>
+          <t>2026-07-22T19:00:00-0400</t>
         </is>
       </c>
       <c r="D114" s="24" t="inlineStr">
         <is>
-          <t>401816225</t>
+          <t>401857088</t>
         </is>
       </c>
       <c r="E114" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>WNBA</t>
         </is>
       </c>
       <c r="F114" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Chicago Sky</t>
         </is>
       </c>
       <c r="G114" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="H114" s="24" t="inlineStr">
@@ -30551,30 +30545,30 @@
         </is>
       </c>
       <c r="L114" s="26" t="n">
-        <v>-138</v>
+        <v>-317</v>
       </c>
       <c r="M114" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.315457</v>
       </c>
       <c r="N114" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.760192</v>
       </c>
       <c r="O114" s="28" t="n">
-        <v>0.659782</v>
+        <v>0.61455</v>
       </c>
       <c r="P114" s="28" t="n"/>
       <c r="Q114" s="28" t="n">
-        <v>0.07994999999999999</v>
+        <v>-0.145642</v>
       </c>
       <c r="R114" s="26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S114" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T114" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>wnba-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U114" s="24" t="inlineStr">
@@ -30593,7 +30587,7 @@
       <c r="AD114" s="24" t="n"/>
       <c r="AE114" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5998; executable ask 0.5800 (aec-mlb-nym-mil-2026-07-22).</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7600 (aec-wnba-chi-ny-2026-07-22).</t>
         </is>
       </c>
       <c r="AF114" s="31" t="inlineStr">
@@ -30611,7 +30605,7 @@
       <c r="AJ114" s="31" t="n"/>
       <c r="AK114" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL114" s="26" t="n">
@@ -30619,47 +30613,47 @@
       </c>
       <c r="AM114" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN114" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO114" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
         </is>
       </c>
       <c r="AP114" s="24" t="inlineStr">
         <is>
-          <t>mlb-nym</t>
+          <t>wnba-chi</t>
         </is>
       </c>
       <c r="AQ114" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Chicago Sky</t>
         </is>
       </c>
       <c r="AR114" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Chicago Sky</t>
         </is>
       </c>
       <c r="AS114" s="24" t="inlineStr">
         <is>
-          <t>mlb-mil</t>
+          <t>wnba-nyl</t>
         </is>
       </c>
       <c r="AT114" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="AU114" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="AV114" s="24" t="n"/>
@@ -30677,7 +30671,7 @@
       </c>
       <c r="BA114" s="24" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB114" s="24" t="inlineStr">
@@ -30687,17 +30681,17 @@
       </c>
       <c r="BC114" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>wnba-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD114" s="24" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BE114" s="24" t="inlineStr">
         <is>
-          <t>040d74b8467fee0f</t>
+          <t>b13fc19a9d17bb09</t>
         </is>
       </c>
       <c r="BF114" s="24" t="inlineStr">
@@ -30707,12 +30701,12 @@
       </c>
       <c r="BG114" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>wnba-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH114" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:15:16.419329Z</t>
+          <t>2026-07-22T05:33:31.746909Z</t>
         </is>
       </c>
       <c r="BI114" s="24" t="inlineStr">
@@ -30722,16 +30716,16 @@
       </c>
       <c r="BJ114" s="25" t="n"/>
       <c r="BK114" s="26" t="n">
-        <v>-138</v>
+        <v>-317</v>
       </c>
       <c r="BL114" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.315457</v>
       </c>
       <c r="BM114" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.760192</v>
       </c>
       <c r="BN114" s="28" t="n">
-        <v>0.577114</v>
+        <v>0.752475</v>
       </c>
       <c r="BO114" s="28" t="n"/>
       <c r="BP114" s="25" t="n"/>
@@ -30751,37 +30745,37 @@
     <row r="115" ht="36" customHeight="1">
       <c r="A115" s="24" t="inlineStr">
         <is>
-          <t>e4e6e2bca0434be6</t>
+          <t>34b5601b54554be6</t>
         </is>
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:16:51.311842Z</t>
+          <t>2026-07-22T05:34:16.990001Z</t>
         </is>
       </c>
       <c r="C115" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T14:10:00-0400</t>
+          <t>2026-07-22T19:30:00-0400</t>
         </is>
       </c>
       <c r="D115" s="24" t="inlineStr">
         <is>
-          <t>401816226</t>
+          <t>401857089</t>
         </is>
       </c>
       <c r="E115" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>WNBA</t>
         </is>
       </c>
       <c r="F115" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Las Vegas Aces</t>
         </is>
       </c>
       <c r="G115" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="H115" s="24" t="inlineStr">
@@ -30791,7 +30785,7 @@
       </c>
       <c r="I115" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J115" s="25" t="n"/>
@@ -30801,30 +30795,30 @@
         </is>
       </c>
       <c r="L115" s="26" t="n">
-        <v>108</v>
+        <v>-233</v>
       </c>
       <c r="M115" s="27" t="n">
-        <v>2.08</v>
+        <v>1.429185</v>
       </c>
       <c r="N115" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.6997</v>
       </c>
       <c r="O115" s="28" t="n">
-        <v>0.536487</v>
+        <v>0.577804</v>
       </c>
       <c r="P115" s="28" t="n"/>
       <c r="Q115" s="28" t="n">
-        <v>0.055718</v>
+        <v>-0.121896</v>
       </c>
       <c r="R115" s="26" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="S115" s="29" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="T115" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>wnba-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U115" s="24" t="inlineStr">
@@ -30843,7 +30837,7 @@
       <c r="AD115" s="24" t="n"/>
       <c r="AE115" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5998; executable ask 0.4800 (aec-mlb-sf-kc-2026-07-22).</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7000 (aec-wnba-lv-wsh-2026-07-22).</t>
         </is>
       </c>
       <c r="AF115" s="31" t="inlineStr">
@@ -30879,37 +30873,37 @@
       </c>
       <c r="AO115" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
         </is>
       </c>
       <c r="AP115" s="24" t="inlineStr">
         <is>
-          <t>mlb-sf</t>
+          <t>wnba-lva</t>
         </is>
       </c>
       <c r="AQ115" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Las Vegas Aces</t>
         </is>
       </c>
       <c r="AR115" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Las Vegas Aces</t>
         </is>
       </c>
       <c r="AS115" s="24" t="inlineStr">
         <is>
-          <t>mlb-kc</t>
+          <t>wnba-was</t>
         </is>
       </c>
       <c r="AT115" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="AU115" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="AV115" s="24" t="n"/>
@@ -30927,7 +30921,7 @@
       </c>
       <c r="BA115" s="24" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB115" s="24" t="inlineStr">
@@ -30937,17 +30931,17 @@
       </c>
       <c r="BC115" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>wnba-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD115" s="24" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BE115" s="24" t="inlineStr">
         <is>
-          <t>43b8d3b9460e78bb</t>
+          <t>6a72fbb8276e803a</t>
         </is>
       </c>
       <c r="BF115" s="24" t="inlineStr">
@@ -30957,12 +30951,12 @@
       </c>
       <c r="BG115" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>wnba-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH115" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:15:17.992482Z</t>
+          <t>2026-07-22T05:33:32.539689Z</t>
         </is>
       </c>
       <c r="BI115" s="24" t="inlineStr">
@@ -30972,16 +30966,16 @@
       </c>
       <c r="BJ115" s="25" t="n"/>
       <c r="BK115" s="26" t="n">
-        <v>108</v>
+        <v>-233</v>
       </c>
       <c r="BL115" s="27" t="n">
-        <v>2.08</v>
+        <v>1.429185</v>
       </c>
       <c r="BM115" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.6997</v>
       </c>
       <c r="BN115" s="28" t="n">
-        <v>0.477612</v>
+        <v>0.693069</v>
       </c>
       <c r="BO115" s="28" t="n"/>
       <c r="BP115" s="25" t="n"/>
@@ -31001,37 +30995,37 @@
     <row r="116" ht="36" customHeight="1">
       <c r="A116" s="24" t="inlineStr">
         <is>
-          <t>88f96bd269024674</t>
+          <t>898f7fac103e4ce0</t>
         </is>
       </c>
       <c r="B116" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:16:51.311842Z</t>
+          <t>2026-07-22T05:34:16.990001Z</t>
         </is>
       </c>
       <c r="C116" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T15:10:00-0400</t>
+          <t>2026-07-22T20:00:00-0400</t>
         </is>
       </c>
       <c r="D116" s="24" t="inlineStr">
         <is>
-          <t>401816227</t>
+          <t>401857090</t>
         </is>
       </c>
       <c r="E116" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>WNBA</t>
         </is>
       </c>
       <c r="F116" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Connecticut Sun</t>
         </is>
       </c>
       <c r="G116" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="H116" s="24" t="inlineStr">
@@ -31041,7 +31035,7 @@
       </c>
       <c r="I116" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J116" s="25" t="n"/>
@@ -31051,30 +31045,30 @@
         </is>
       </c>
       <c r="L116" s="26" t="n">
-        <v>-125</v>
+        <v>-400</v>
       </c>
       <c r="M116" s="27" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="N116" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.8</v>
       </c>
       <c r="O116" s="28" t="n">
-        <v>0.582201</v>
+        <v>0.74864</v>
       </c>
       <c r="P116" s="28" t="n"/>
       <c r="Q116" s="28" t="n">
-        <v>0.026645</v>
+        <v>-0.05136</v>
       </c>
       <c r="R116" s="26" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="S116" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T116" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>wnba-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U116" s="24" t="inlineStr">
@@ -31093,7 +31087,7 @@
       <c r="AD116" s="24" t="n"/>
       <c r="AE116" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5998; executable ask 0.5550 (aec-mlb-wsh-col-2026-07-22).</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8000 (aec-wnba-conn-ind-2026-07-22).</t>
         </is>
       </c>
       <c r="AF116" s="31" t="inlineStr">
@@ -31134,32 +31128,32 @@
       </c>
       <c r="AP116" s="24" t="inlineStr">
         <is>
-          <t>mlb-wsh</t>
+          <t>wnba-con</t>
         </is>
       </c>
       <c r="AQ116" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Connecticut Sun</t>
         </is>
       </c>
       <c r="AR116" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Connecticut Sun</t>
         </is>
       </c>
       <c r="AS116" s="24" t="inlineStr">
         <is>
-          <t>mlb-col</t>
+          <t>wnba-ind</t>
         </is>
       </c>
       <c r="AT116" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="AU116" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="AV116" s="24" t="n"/>
@@ -31177,7 +31171,7 @@
       </c>
       <c r="BA116" s="24" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB116" s="24" t="inlineStr">
@@ -31187,17 +31181,17 @@
       </c>
       <c r="BC116" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>wnba-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD116" s="24" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BE116" s="24" t="inlineStr">
         <is>
-          <t>960549af203ec676</t>
+          <t>8c0d6eee02b48cfb</t>
         </is>
       </c>
       <c r="BF116" s="24" t="inlineStr">
@@ -31207,12 +31201,12 @@
       </c>
       <c r="BG116" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>wnba-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH116" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:15:19.553900Z</t>
+          <t>2026-07-22T05:33:35.161413Z</t>
         </is>
       </c>
       <c r="BI116" s="24" t="inlineStr">
@@ -31222,16 +31216,16 @@
       </c>
       <c r="BJ116" s="25" t="n"/>
       <c r="BK116" s="26" t="n">
-        <v>-125</v>
+        <v>-400</v>
       </c>
       <c r="BL116" s="27" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="BM116" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.8</v>
       </c>
       <c r="BN116" s="28" t="n">
-        <v>0.552239</v>
+        <v>0.792079</v>
       </c>
       <c r="BO116" s="28" t="n"/>
       <c r="BP116" s="25" t="n"/>
@@ -31251,37 +31245,37 @@
     <row r="117" ht="36" customHeight="1">
       <c r="A117" s="24" t="inlineStr">
         <is>
-          <t>bc59f6161a554881</t>
+          <t>a30c6420c7f84fd4</t>
         </is>
       </c>
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:16:51.311842Z</t>
+          <t>2026-07-22T05:34:16.990001Z</t>
         </is>
       </c>
       <c r="C117" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T15:40:00-0400</t>
+          <t>2026-07-22T22:00:00-0400</t>
         </is>
       </c>
       <c r="D117" s="24" t="inlineStr">
         <is>
-          <t>401816228</t>
+          <t>401857091</t>
         </is>
       </c>
       <c r="E117" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>WNBA</t>
         </is>
       </c>
       <c r="F117" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="G117" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Portland Fire</t>
         </is>
       </c>
       <c r="H117" s="24" t="inlineStr">
@@ -31291,7 +31285,7 @@
       </c>
       <c r="I117" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J117" s="25" t="n"/>
@@ -31301,30 +31295,30 @@
         </is>
       </c>
       <c r="L117" s="26" t="n">
-        <v>-111</v>
+        <v>-213</v>
       </c>
       <c r="M117" s="27" t="n">
-        <v>1.900901</v>
+        <v>1.469484</v>
       </c>
       <c r="N117" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.680511</v>
       </c>
       <c r="O117" s="28" t="n">
-        <v>0.567213</v>
+        <v>0.614249</v>
       </c>
       <c r="P117" s="28" t="n"/>
       <c r="Q117" s="28" t="n">
-        <v>0.041147</v>
+        <v>-0.066262</v>
       </c>
       <c r="R117" s="26" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="S117" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T117" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>wnba-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U117" s="24" t="inlineStr">
@@ -31343,7 +31337,7 @@
       <c r="AD117" s="24" t="n"/>
       <c r="AE117" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5998; executable ask 0.5250 (aec-mlb-ath-az-2026-07-22).</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.6800 (aec-wnba-dal-por-2026-07-22).</t>
         </is>
       </c>
       <c r="AF117" s="31" t="inlineStr">
@@ -31384,32 +31378,32 @@
       </c>
       <c r="AP117" s="24" t="inlineStr">
         <is>
-          <t>mlb-ath</t>
+          <t>wnba-dal</t>
         </is>
       </c>
       <c r="AQ117" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="AR117" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="AS117" s="24" t="inlineStr">
         <is>
-          <t>mlb-ari</t>
+          <t>wnba-por</t>
         </is>
       </c>
       <c r="AT117" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Portland Fire</t>
         </is>
       </c>
       <c r="AU117" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Portland Fire</t>
         </is>
       </c>
       <c r="AV117" s="24" t="n"/>
@@ -31427,7 +31421,7 @@
       </c>
       <c r="BA117" s="24" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB117" s="24" t="inlineStr">
@@ -31437,17 +31431,17 @@
       </c>
       <c r="BC117" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>wnba-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD117" s="24" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BE117" s="24" t="inlineStr">
         <is>
-          <t>242ff1fbdbcd8c5d</t>
+          <t>f97350d4d81b330d</t>
         </is>
       </c>
       <c r="BF117" s="24" t="inlineStr">
@@ -31457,12 +31451,12 @@
       </c>
       <c r="BG117" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>wnba-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH117" s="24" t="inlineStr">
         <is>
-          <t>2026-07-22T05:15:21.160744Z</t>
+          <t>2026-07-22T05:33:36.553455Z</t>
         </is>
       </c>
       <c r="BI117" s="24" t="inlineStr">
@@ -31472,16 +31466,16 @@
       </c>
       <c r="BJ117" s="25" t="n"/>
       <c r="BK117" s="26" t="n">
-        <v>-111</v>
+        <v>-213</v>
       </c>
       <c r="BL117" s="27" t="n">
-        <v>1.900901</v>
+        <v>1.469484</v>
       </c>
       <c r="BM117" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.680511</v>
       </c>
       <c r="BN117" s="28" t="n">
-        <v>0.522388</v>
+        <v>0.6732669999999999</v>
       </c>
       <c r="BO117" s="28" t="n"/>
       <c r="BP117" s="25" t="n"/>
@@ -31498,4984 +31492,6 @@
       <c r="CA117" s="31" t="n"/>
       <c r="CB117" s="24" t="n"/>
     </row>
-    <row r="118" ht="36" customHeight="1">
-      <c r="A118" s="24" t="inlineStr">
-        <is>
-          <t>f540434db3a04178</t>
-        </is>
-      </c>
-      <c r="B118" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:16:51.311842Z</t>
-        </is>
-      </c>
-      <c r="C118" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T15:40:00-0400</t>
-        </is>
-      </c>
-      <c r="D118" s="24" t="inlineStr">
-        <is>
-          <t>401816229</t>
-        </is>
-      </c>
-      <c r="E118" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F118" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="G118" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="H118" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I118" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J118" s="25" t="n"/>
-      <c r="K118" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L118" s="26" t="n">
-        <v>-141</v>
-      </c>
-      <c r="M118" s="27" t="n">
-        <v>1.70922</v>
-      </c>
-      <c r="N118" s="28" t="n">
-        <v>0.585062</v>
-      </c>
-      <c r="O118" s="28" t="n">
-        <v>0.575998</v>
-      </c>
-      <c r="P118" s="28" t="n"/>
-      <c r="Q118" s="28" t="n">
-        <v>-0.009063999999999999</v>
-      </c>
-      <c r="R118" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="S118" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T118" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="U118" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V118" s="24" t="n"/>
-      <c r="W118" s="26" t="n"/>
-      <c r="X118" s="26" t="n"/>
-      <c r="Y118" s="25" t="n"/>
-      <c r="Z118" s="26" t="n"/>
-      <c r="AA118" s="28" t="n"/>
-      <c r="AB118" s="28" t="n"/>
-      <c r="AC118" s="30" t="n"/>
-      <c r="AD118" s="24" t="n"/>
-      <c r="AE118" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5998; executable ask 0.5850 (aec-mlb-cin-sea-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF118" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG118" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH118" s="24" t="n"/>
-      <c r="AI118" s="31" t="n"/>
-      <c r="AJ118" s="31" t="n"/>
-      <c r="AK118" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL118" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM118" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN118" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO118" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP118" s="24" t="inlineStr">
-        <is>
-          <t>mlb-cin</t>
-        </is>
-      </c>
-      <c r="AQ118" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="AR118" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="AS118" s="24" t="inlineStr">
-        <is>
-          <t>mlb-sea</t>
-        </is>
-      </c>
-      <c r="AT118" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="AU118" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="AV118" s="24" t="n"/>
-      <c r="AW118" s="24" t="n"/>
-      <c r="AX118" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY118" s="24" t="n"/>
-      <c r="AZ118" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA118" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BB118" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC118" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BD118" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BE118" s="24" t="inlineStr">
-        <is>
-          <t>32921750b3e5ccf3</t>
-        </is>
-      </c>
-      <c r="BF118" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG118" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BH118" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:15:22.757209Z</t>
-        </is>
-      </c>
-      <c r="BI118" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ118" s="25" t="n"/>
-      <c r="BK118" s="26" t="n">
-        <v>-141</v>
-      </c>
-      <c r="BL118" s="27" t="n">
-        <v>1.70922</v>
-      </c>
-      <c r="BM118" s="28" t="n">
-        <v>0.585062</v>
-      </c>
-      <c r="BN118" s="28" t="n">
-        <v>0.58209</v>
-      </c>
-      <c r="BO118" s="28" t="n"/>
-      <c r="BP118" s="25" t="n"/>
-      <c r="BQ118" s="27" t="n"/>
-      <c r="BR118" s="28" t="n"/>
-      <c r="BS118" s="28" t="n"/>
-      <c r="BT118" s="28" t="n"/>
-      <c r="BU118" s="25" t="n"/>
-      <c r="BV118" s="29" t="n"/>
-      <c r="BW118" s="24" t="n"/>
-      <c r="BX118" s="30" t="n"/>
-      <c r="BY118" s="27" t="n"/>
-      <c r="BZ118" s="24" t="n"/>
-      <c r="CA118" s="31" t="n"/>
-      <c r="CB118" s="24" t="n"/>
-    </row>
-    <row r="119" ht="36" customHeight="1">
-      <c r="A119" s="24" t="inlineStr">
-        <is>
-          <t>dca0731b48524fd1</t>
-        </is>
-      </c>
-      <c r="B119" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:16:51.311842Z</t>
-        </is>
-      </c>
-      <c r="C119" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T16:07:00-0400</t>
-        </is>
-      </c>
-      <c r="D119" s="24" t="inlineStr">
-        <is>
-          <t>401816230</t>
-        </is>
-      </c>
-      <c r="E119" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F119" s="24" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="G119" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="H119" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I119" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J119" s="25" t="n"/>
-      <c r="K119" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L119" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="M119" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="N119" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="O119" s="28" t="n">
-        <v>0.541133</v>
-      </c>
-      <c r="P119" s="28" t="n"/>
-      <c r="Q119" s="28" t="n">
-        <v>0.060364</v>
-      </c>
-      <c r="R119" s="26" t="n">
-        <v>50</v>
-      </c>
-      <c r="S119" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T119" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="U119" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V119" s="24" t="n"/>
-      <c r="W119" s="26" t="n"/>
-      <c r="X119" s="26" t="n"/>
-      <c r="Y119" s="25" t="n"/>
-      <c r="Z119" s="26" t="n"/>
-      <c r="AA119" s="28" t="n"/>
-      <c r="AB119" s="28" t="n"/>
-      <c r="AC119" s="30" t="n"/>
-      <c r="AD119" s="24" t="n"/>
-      <c r="AE119" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5998; executable ask 0.4800 (aec-mlb-stl-laa-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF119" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG119" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH119" s="24" t="n"/>
-      <c r="AI119" s="31" t="n"/>
-      <c r="AJ119" s="31" t="n"/>
-      <c r="AK119" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL119" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM119" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN119" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO119" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP119" s="24" t="inlineStr">
-        <is>
-          <t>mlb-stl</t>
-        </is>
-      </c>
-      <c r="AQ119" s="24" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="AR119" s="24" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="AS119" s="24" t="inlineStr">
-        <is>
-          <t>mlb-laa</t>
-        </is>
-      </c>
-      <c r="AT119" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="AU119" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="AV119" s="24" t="n"/>
-      <c r="AW119" s="24" t="n"/>
-      <c r="AX119" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY119" s="24" t="n"/>
-      <c r="AZ119" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA119" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BB119" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC119" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BD119" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BE119" s="24" t="inlineStr">
-        <is>
-          <t>93d479bfbaf74f9f</t>
-        </is>
-      </c>
-      <c r="BF119" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG119" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BH119" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:15:24.036482Z</t>
-        </is>
-      </c>
-      <c r="BI119" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ119" s="25" t="n"/>
-      <c r="BK119" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="BL119" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BM119" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="BN119" s="28" t="n">
-        <v>0.477612</v>
-      </c>
-      <c r="BO119" s="28" t="n"/>
-      <c r="BP119" s="25" t="n"/>
-      <c r="BQ119" s="27" t="n"/>
-      <c r="BR119" s="28" t="n"/>
-      <c r="BS119" s="28" t="n"/>
-      <c r="BT119" s="28" t="n"/>
-      <c r="BU119" s="25" t="n"/>
-      <c r="BV119" s="29" t="n"/>
-      <c r="BW119" s="24" t="n"/>
-      <c r="BX119" s="30" t="n"/>
-      <c r="BY119" s="27" t="n"/>
-      <c r="BZ119" s="24" t="n"/>
-      <c r="CA119" s="31" t="n"/>
-      <c r="CB119" s="24" t="n"/>
-    </row>
-    <row r="120" ht="36" customHeight="1">
-      <c r="A120" s="24" t="inlineStr">
-        <is>
-          <t>31056c3df290407d</t>
-        </is>
-      </c>
-      <c r="B120" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:16:51.311842Z</t>
-        </is>
-      </c>
-      <c r="C120" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T18:40:00-0400</t>
-        </is>
-      </c>
-      <c r="D120" s="24" t="inlineStr">
-        <is>
-          <t>401816217</t>
-        </is>
-      </c>
-      <c r="E120" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F120" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="G120" s="24" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="H120" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I120" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J120" s="25" t="n"/>
-      <c r="K120" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L120" s="26" t="n">
-        <v>-106</v>
-      </c>
-      <c r="M120" s="27" t="n">
-        <v>1.943396</v>
-      </c>
-      <c r="N120" s="28" t="n">
-        <v>0.514563</v>
-      </c>
-      <c r="O120" s="28" t="n">
-        <v>0.524041</v>
-      </c>
-      <c r="P120" s="28" t="n"/>
-      <c r="Q120" s="28" t="n">
-        <v>0.009478</v>
-      </c>
-      <c r="R120" s="26" t="n">
-        <v>25</v>
-      </c>
-      <c r="S120" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T120" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="U120" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V120" s="24" t="n"/>
-      <c r="W120" s="26" t="n"/>
-      <c r="X120" s="26" t="n"/>
-      <c r="Y120" s="25" t="n"/>
-      <c r="Z120" s="26" t="n"/>
-      <c r="AA120" s="28" t="n"/>
-      <c r="AB120" s="28" t="n"/>
-      <c r="AC120" s="30" t="n"/>
-      <c r="AD120" s="24" t="n"/>
-      <c r="AE120" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5998; executable ask 0.5150 (aec-mlb-lad-phi-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF120" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG120" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH120" s="24" t="n"/>
-      <c r="AI120" s="31" t="n"/>
-      <c r="AJ120" s="31" t="n"/>
-      <c r="AK120" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL120" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM120" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN120" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO120" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP120" s="24" t="inlineStr">
-        <is>
-          <t>mlb-lad</t>
-        </is>
-      </c>
-      <c r="AQ120" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="AR120" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="AS120" s="24" t="inlineStr">
-        <is>
-          <t>mlb-phi</t>
-        </is>
-      </c>
-      <c r="AT120" s="24" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="AU120" s="24" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="AV120" s="24" t="n"/>
-      <c r="AW120" s="24" t="n"/>
-      <c r="AX120" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY120" s="24" t="n"/>
-      <c r="AZ120" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA120" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BB120" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC120" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BD120" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BE120" s="24" t="inlineStr">
-        <is>
-          <t>eedb654608c6e00e</t>
-        </is>
-      </c>
-      <c r="BF120" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG120" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BH120" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:15:26.832141Z</t>
-        </is>
-      </c>
-      <c r="BI120" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ120" s="25" t="n"/>
-      <c r="BK120" s="26" t="n">
-        <v>-106</v>
-      </c>
-      <c r="BL120" s="27" t="n">
-        <v>1.943396</v>
-      </c>
-      <c r="BM120" s="28" t="n">
-        <v>0.514563</v>
-      </c>
-      <c r="BN120" s="28" t="n">
-        <v>0.5124379999999999</v>
-      </c>
-      <c r="BO120" s="28" t="n"/>
-      <c r="BP120" s="25" t="n"/>
-      <c r="BQ120" s="27" t="n"/>
-      <c r="BR120" s="28" t="n"/>
-      <c r="BS120" s="28" t="n"/>
-      <c r="BT120" s="28" t="n"/>
-      <c r="BU120" s="25" t="n"/>
-      <c r="BV120" s="29" t="n"/>
-      <c r="BW120" s="24" t="n"/>
-      <c r="BX120" s="30" t="n"/>
-      <c r="BY120" s="27" t="n"/>
-      <c r="BZ120" s="24" t="n"/>
-      <c r="CA120" s="31" t="n"/>
-      <c r="CB120" s="24" t="n"/>
-    </row>
-    <row r="121" ht="36" customHeight="1">
-      <c r="A121" s="24" t="inlineStr">
-        <is>
-          <t>0ee2e597d4fc41ee</t>
-        </is>
-      </c>
-      <c r="B121" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:16:51.311842Z</t>
-        </is>
-      </c>
-      <c r="C121" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T18:40:00-0400</t>
-        </is>
-      </c>
-      <c r="D121" s="24" t="inlineStr">
-        <is>
-          <t>401816218</t>
-        </is>
-      </c>
-      <c r="E121" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F121" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="G121" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="H121" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I121" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J121" s="25" t="n"/>
-      <c r="K121" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L121" s="26" t="n">
-        <v>-117</v>
-      </c>
-      <c r="M121" s="27" t="n">
-        <v>1.854701</v>
-      </c>
-      <c r="N121" s="28" t="n">
-        <v>0.539171</v>
-      </c>
-      <c r="O121" s="28" t="n">
-        <v>0.562938</v>
-      </c>
-      <c r="P121" s="28" t="n"/>
-      <c r="Q121" s="28" t="n">
-        <v>0.023767</v>
-      </c>
-      <c r="R121" s="26" t="n">
-        <v>32</v>
-      </c>
-      <c r="S121" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T121" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="U121" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V121" s="24" t="n"/>
-      <c r="W121" s="26" t="n"/>
-      <c r="X121" s="26" t="n"/>
-      <c r="Y121" s="25" t="n"/>
-      <c r="Z121" s="26" t="n"/>
-      <c r="AA121" s="28" t="n"/>
-      <c r="AB121" s="28" t="n"/>
-      <c r="AC121" s="30" t="n"/>
-      <c r="AD121" s="24" t="n"/>
-      <c r="AE121" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5998; executable ask 0.5400 (aec-mlb-min-cle-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF121" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG121" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH121" s="24" t="n"/>
-      <c r="AI121" s="31" t="n"/>
-      <c r="AJ121" s="31" t="n"/>
-      <c r="AK121" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL121" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM121" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN121" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO121" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP121" s="24" t="inlineStr">
-        <is>
-          <t>mlb-min</t>
-        </is>
-      </c>
-      <c r="AQ121" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AR121" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AS121" s="24" t="inlineStr">
-        <is>
-          <t>mlb-cle</t>
-        </is>
-      </c>
-      <c r="AT121" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="AU121" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="AV121" s="24" t="n"/>
-      <c r="AW121" s="24" t="n"/>
-      <c r="AX121" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY121" s="24" t="n"/>
-      <c r="AZ121" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA121" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BB121" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC121" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BD121" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BE121" s="24" t="inlineStr">
-        <is>
-          <t>393dce007d73d9d7</t>
-        </is>
-      </c>
-      <c r="BF121" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG121" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BH121" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:15:25.534232Z</t>
-        </is>
-      </c>
-      <c r="BI121" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ121" s="25" t="n"/>
-      <c r="BK121" s="26" t="n">
-        <v>-117</v>
-      </c>
-      <c r="BL121" s="27" t="n">
-        <v>1.854701</v>
-      </c>
-      <c r="BM121" s="28" t="n">
-        <v>0.539171</v>
-      </c>
-      <c r="BN121" s="28" t="n">
-        <v>0.537313</v>
-      </c>
-      <c r="BO121" s="28" t="n"/>
-      <c r="BP121" s="25" t="n"/>
-      <c r="BQ121" s="27" t="n"/>
-      <c r="BR121" s="28" t="n"/>
-      <c r="BS121" s="28" t="n"/>
-      <c r="BT121" s="28" t="n"/>
-      <c r="BU121" s="25" t="n"/>
-      <c r="BV121" s="29" t="n"/>
-      <c r="BW121" s="24" t="n"/>
-      <c r="BX121" s="30" t="n"/>
-      <c r="BY121" s="27" t="n"/>
-      <c r="BZ121" s="24" t="n"/>
-      <c r="CA121" s="31" t="n"/>
-      <c r="CB121" s="24" t="n"/>
-    </row>
-    <row r="122" ht="36" customHeight="1">
-      <c r="A122" s="24" t="inlineStr">
-        <is>
-          <t>34d5f305f56e41fa</t>
-        </is>
-      </c>
-      <c r="B122" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:16:51.311842Z</t>
-        </is>
-      </c>
-      <c r="C122" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T19:07:00-0400</t>
-        </is>
-      </c>
-      <c r="D122" s="24" t="inlineStr">
-        <is>
-          <t>401816221</t>
-        </is>
-      </c>
-      <c r="E122" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F122" s="24" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="G122" s="24" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays</t>
-        </is>
-      </c>
-      <c r="H122" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I122" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J122" s="25" t="n"/>
-      <c r="K122" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L122" s="26" t="n">
-        <v>-102</v>
-      </c>
-      <c r="M122" s="27" t="n">
-        <v>1.980392</v>
-      </c>
-      <c r="N122" s="28" t="n">
-        <v>0.50495</v>
-      </c>
-      <c r="O122" s="28" t="n">
-        <v>0.525517</v>
-      </c>
-      <c r="P122" s="28" t="n"/>
-      <c r="Q122" s="28" t="n">
-        <v>0.020567</v>
-      </c>
-      <c r="R122" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="S122" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T122" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="U122" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V122" s="24" t="n"/>
-      <c r="W122" s="26" t="n"/>
-      <c r="X122" s="26" t="n"/>
-      <c r="Y122" s="25" t="n"/>
-      <c r="Z122" s="26" t="n"/>
-      <c r="AA122" s="28" t="n"/>
-      <c r="AB122" s="28" t="n"/>
-      <c r="AC122" s="30" t="n"/>
-      <c r="AD122" s="24" t="n"/>
-      <c r="AE122" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5998; executable ask 0.5050 (aec-mlb-tb-tor-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF122" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG122" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH122" s="24" t="n"/>
-      <c r="AI122" s="31" t="n"/>
-      <c r="AJ122" s="31" t="n"/>
-      <c r="AK122" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL122" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM122" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN122" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO122" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP122" s="24" t="inlineStr">
-        <is>
-          <t>mlb-tb</t>
-        </is>
-      </c>
-      <c r="AQ122" s="24" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="AR122" s="24" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="AS122" s="24" t="inlineStr">
-        <is>
-          <t>mlb-tor</t>
-        </is>
-      </c>
-      <c r="AT122" s="24" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays</t>
-        </is>
-      </c>
-      <c r="AU122" s="24" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays</t>
-        </is>
-      </c>
-      <c r="AV122" s="24" t="n"/>
-      <c r="AW122" s="24" t="n"/>
-      <c r="AX122" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY122" s="24" t="n"/>
-      <c r="AZ122" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA122" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BB122" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC122" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BD122" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BE122" s="24" t="inlineStr">
-        <is>
-          <t>f56f42ed87469618</t>
-        </is>
-      </c>
-      <c r="BF122" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG122" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BH122" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:15:30.289706Z</t>
-        </is>
-      </c>
-      <c r="BI122" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ122" s="25" t="n"/>
-      <c r="BK122" s="26" t="n">
-        <v>-102</v>
-      </c>
-      <c r="BL122" s="27" t="n">
-        <v>1.980392</v>
-      </c>
-      <c r="BM122" s="28" t="n">
-        <v>0.50495</v>
-      </c>
-      <c r="BN122" s="28" t="n">
-        <v>0.502488</v>
-      </c>
-      <c r="BO122" s="28" t="n"/>
-      <c r="BP122" s="25" t="n"/>
-      <c r="BQ122" s="27" t="n"/>
-      <c r="BR122" s="28" t="n"/>
-      <c r="BS122" s="28" t="n"/>
-      <c r="BT122" s="28" t="n"/>
-      <c r="BU122" s="25" t="n"/>
-      <c r="BV122" s="29" t="n"/>
-      <c r="BW122" s="24" t="n"/>
-      <c r="BX122" s="30" t="n"/>
-      <c r="BY122" s="27" t="n"/>
-      <c r="BZ122" s="24" t="n"/>
-      <c r="CA122" s="31" t="n"/>
-      <c r="CB122" s="24" t="n"/>
-    </row>
-    <row r="123" ht="36" customHeight="1">
-      <c r="A123" s="24" t="inlineStr">
-        <is>
-          <t>b4fcab58b8344f72</t>
-        </is>
-      </c>
-      <c r="B123" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:16:51.311842Z</t>
-        </is>
-      </c>
-      <c r="C123" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T19:15:00-0400</t>
-        </is>
-      </c>
-      <c r="D123" s="24" t="inlineStr">
-        <is>
-          <t>401816220</t>
-        </is>
-      </c>
-      <c r="E123" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F123" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="G123" s="24" t="inlineStr">
-        <is>
-          <t>Atlanta Braves</t>
-        </is>
-      </c>
-      <c r="H123" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I123" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J123" s="25" t="n"/>
-      <c r="K123" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L123" s="26" t="n">
-        <v>-115</v>
-      </c>
-      <c r="M123" s="27" t="n">
-        <v>1.869565</v>
-      </c>
-      <c r="N123" s="28" t="n">
-        <v>0.534884</v>
-      </c>
-      <c r="O123" s="28" t="n">
-        <v>0.56238</v>
-      </c>
-      <c r="P123" s="28" t="n"/>
-      <c r="Q123" s="28" t="n">
-        <v>0.027496</v>
-      </c>
-      <c r="R123" s="26" t="n">
-        <v>34</v>
-      </c>
-      <c r="S123" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T123" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="U123" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V123" s="24" t="n"/>
-      <c r="W123" s="26" t="n"/>
-      <c r="X123" s="26" t="n"/>
-      <c r="Y123" s="25" t="n"/>
-      <c r="Z123" s="26" t="n"/>
-      <c r="AA123" s="28" t="n"/>
-      <c r="AB123" s="28" t="n"/>
-      <c r="AC123" s="30" t="n"/>
-      <c r="AD123" s="24" t="n"/>
-      <c r="AE123" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5998; executable ask 0.5350 (aec-mlb-sd-atl-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF123" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG123" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH123" s="24" t="n"/>
-      <c r="AI123" s="31" t="n"/>
-      <c r="AJ123" s="31" t="n"/>
-      <c r="AK123" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL123" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM123" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN123" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO123" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP123" s="24" t="inlineStr">
-        <is>
-          <t>mlb-sd</t>
-        </is>
-      </c>
-      <c r="AQ123" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="AR123" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="AS123" s="24" t="inlineStr">
-        <is>
-          <t>mlb-atl</t>
-        </is>
-      </c>
-      <c r="AT123" s="24" t="inlineStr">
-        <is>
-          <t>Atlanta Braves</t>
-        </is>
-      </c>
-      <c r="AU123" s="24" t="inlineStr">
-        <is>
-          <t>Atlanta Braves</t>
-        </is>
-      </c>
-      <c r="AV123" s="24" t="n"/>
-      <c r="AW123" s="24" t="n"/>
-      <c r="AX123" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY123" s="24" t="n"/>
-      <c r="AZ123" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA123" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BB123" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC123" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BD123" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BE123" s="24" t="inlineStr">
-        <is>
-          <t>627c014be49ce2cc</t>
-        </is>
-      </c>
-      <c r="BF123" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG123" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BH123" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:15:33.341547Z</t>
-        </is>
-      </c>
-      <c r="BI123" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ123" s="25" t="n"/>
-      <c r="BK123" s="26" t="n">
-        <v>-115</v>
-      </c>
-      <c r="BL123" s="27" t="n">
-        <v>1.869565</v>
-      </c>
-      <c r="BM123" s="28" t="n">
-        <v>0.534884</v>
-      </c>
-      <c r="BN123" s="28" t="n">
-        <v>0.532338</v>
-      </c>
-      <c r="BO123" s="28" t="n"/>
-      <c r="BP123" s="25" t="n"/>
-      <c r="BQ123" s="27" t="n"/>
-      <c r="BR123" s="28" t="n"/>
-      <c r="BS123" s="28" t="n"/>
-      <c r="BT123" s="28" t="n"/>
-      <c r="BU123" s="25" t="n"/>
-      <c r="BV123" s="29" t="n"/>
-      <c r="BW123" s="24" t="n"/>
-      <c r="BX123" s="30" t="n"/>
-      <c r="BY123" s="27" t="n"/>
-      <c r="BZ123" s="24" t="n"/>
-      <c r="CA123" s="31" t="n"/>
-      <c r="CB123" s="24" t="n"/>
-    </row>
-    <row r="124" ht="36" customHeight="1">
-      <c r="A124" s="24" t="inlineStr">
-        <is>
-          <t>4e16d18e1de148f9</t>
-        </is>
-      </c>
-      <c r="B124" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:16:51.311842Z</t>
-        </is>
-      </c>
-      <c r="C124" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T20:00:00-0400</t>
-        </is>
-      </c>
-      <c r="D124" s="24" t="inlineStr">
-        <is>
-          <t>401816223</t>
-        </is>
-      </c>
-      <c r="E124" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F124" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="G124" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="H124" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I124" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J124" s="25" t="n"/>
-      <c r="K124" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L124" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="M124" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="N124" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="O124" s="28" t="n">
-        <v>0.572578</v>
-      </c>
-      <c r="P124" s="28" t="n"/>
-      <c r="Q124" s="28" t="n">
-        <v>0.053347</v>
-      </c>
-      <c r="R124" s="26" t="n">
-        <v>47</v>
-      </c>
-      <c r="S124" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T124" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="U124" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V124" s="24" t="n"/>
-      <c r="W124" s="26" t="n"/>
-      <c r="X124" s="26" t="n"/>
-      <c r="Y124" s="25" t="n"/>
-      <c r="Z124" s="26" t="n"/>
-      <c r="AA124" s="28" t="n"/>
-      <c r="AB124" s="28" t="n"/>
-      <c r="AC124" s="30" t="n"/>
-      <c r="AD124" s="24" t="n"/>
-      <c r="AE124" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5998; executable ask 0.5200 (aec-mlb-det-chc-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF124" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG124" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH124" s="24" t="n"/>
-      <c r="AI124" s="31" t="n"/>
-      <c r="AJ124" s="31" t="n"/>
-      <c r="AK124" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL124" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM124" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN124" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO124" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP124" s="24" t="inlineStr">
-        <is>
-          <t>mlb-det</t>
-        </is>
-      </c>
-      <c r="AQ124" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="AR124" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="AS124" s="24" t="inlineStr">
-        <is>
-          <t>mlb-chc</t>
-        </is>
-      </c>
-      <c r="AT124" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AU124" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AV124" s="24" t="n"/>
-      <c r="AW124" s="24" t="n"/>
-      <c r="AX124" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY124" s="24" t="n"/>
-      <c r="AZ124" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA124" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BB124" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC124" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BD124" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BE124" s="24" t="inlineStr">
-        <is>
-          <t>0f9d81396238e01e</t>
-        </is>
-      </c>
-      <c r="BF124" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG124" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BH124" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:15:35.802323Z</t>
-        </is>
-      </c>
-      <c r="BI124" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ124" s="25" t="n"/>
-      <c r="BK124" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="BL124" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="BM124" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="BN124" s="28" t="n">
-        <v>0.517413</v>
-      </c>
-      <c r="BO124" s="28" t="n"/>
-      <c r="BP124" s="25" t="n"/>
-      <c r="BQ124" s="27" t="n"/>
-      <c r="BR124" s="28" t="n"/>
-      <c r="BS124" s="28" t="n"/>
-      <c r="BT124" s="28" t="n"/>
-      <c r="BU124" s="25" t="n"/>
-      <c r="BV124" s="29" t="n"/>
-      <c r="BW124" s="24" t="n"/>
-      <c r="BX124" s="30" t="n"/>
-      <c r="BY124" s="27" t="n"/>
-      <c r="BZ124" s="24" t="n"/>
-      <c r="CA124" s="31" t="n"/>
-      <c r="CB124" s="24" t="n"/>
-    </row>
-    <row r="125" ht="36" customHeight="1">
-      <c r="A125" s="24" t="inlineStr">
-        <is>
-          <t>4b55624768bd41b5</t>
-        </is>
-      </c>
-      <c r="B125" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:16:51.311842Z</t>
-        </is>
-      </c>
-      <c r="C125" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T20:05:00-0400</t>
-        </is>
-      </c>
-      <c r="D125" s="24" t="inlineStr">
-        <is>
-          <t>401816222</t>
-        </is>
-      </c>
-      <c r="E125" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F125" s="24" t="inlineStr">
-        <is>
-          <t>Chicago White Sox</t>
-        </is>
-      </c>
-      <c r="G125" s="24" t="inlineStr">
-        <is>
-          <t>Texas Rangers</t>
-        </is>
-      </c>
-      <c r="H125" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I125" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J125" s="25" t="n"/>
-      <c r="K125" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L125" s="26" t="n">
-        <v>-104</v>
-      </c>
-      <c r="M125" s="27" t="n">
-        <v>1.961538</v>
-      </c>
-      <c r="N125" s="28" t="n">
-        <v>0.509804</v>
-      </c>
-      <c r="O125" s="28" t="n">
-        <v>0.551837</v>
-      </c>
-      <c r="P125" s="28" t="n"/>
-      <c r="Q125" s="28" t="n">
-        <v>0.042033</v>
-      </c>
-      <c r="R125" s="26" t="n">
-        <v>41</v>
-      </c>
-      <c r="S125" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T125" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="U125" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V125" s="24" t="n"/>
-      <c r="W125" s="26" t="n"/>
-      <c r="X125" s="26" t="n"/>
-      <c r="Y125" s="25" t="n"/>
-      <c r="Z125" s="26" t="n"/>
-      <c r="AA125" s="28" t="n"/>
-      <c r="AB125" s="28" t="n"/>
-      <c r="AC125" s="30" t="n"/>
-      <c r="AD125" s="24" t="n"/>
-      <c r="AE125" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5998; executable ask 0.5100 (aec-mlb-cws-tex-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF125" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG125" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH125" s="24" t="n"/>
-      <c r="AI125" s="31" t="n"/>
-      <c r="AJ125" s="31" t="n"/>
-      <c r="AK125" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL125" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM125" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN125" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO125" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP125" s="24" t="inlineStr">
-        <is>
-          <t>mlb-cws</t>
-        </is>
-      </c>
-      <c r="AQ125" s="24" t="inlineStr">
-        <is>
-          <t>Chicago White Sox</t>
-        </is>
-      </c>
-      <c r="AR125" s="24" t="inlineStr">
-        <is>
-          <t>Chicago White Sox</t>
-        </is>
-      </c>
-      <c r="AS125" s="24" t="inlineStr">
-        <is>
-          <t>mlb-tex</t>
-        </is>
-      </c>
-      <c r="AT125" s="24" t="inlineStr">
-        <is>
-          <t>Texas Rangers</t>
-        </is>
-      </c>
-      <c r="AU125" s="24" t="inlineStr">
-        <is>
-          <t>Texas Rangers</t>
-        </is>
-      </c>
-      <c r="AV125" s="24" t="n"/>
-      <c r="AW125" s="24" t="n"/>
-      <c r="AX125" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY125" s="24" t="n"/>
-      <c r="AZ125" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA125" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BB125" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC125" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BD125" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BE125" s="24" t="inlineStr">
-        <is>
-          <t>02d53785b23e99bb</t>
-        </is>
-      </c>
-      <c r="BF125" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG125" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BH125" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:15:34.794476Z</t>
-        </is>
-      </c>
-      <c r="BI125" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ125" s="25" t="n"/>
-      <c r="BK125" s="26" t="n">
-        <v>-104</v>
-      </c>
-      <c r="BL125" s="27" t="n">
-        <v>1.961538</v>
-      </c>
-      <c r="BM125" s="28" t="n">
-        <v>0.509804</v>
-      </c>
-      <c r="BN125" s="28" t="n">
-        <v>0.507463</v>
-      </c>
-      <c r="BO125" s="28" t="n"/>
-      <c r="BP125" s="25" t="n"/>
-      <c r="BQ125" s="27" t="n"/>
-      <c r="BR125" s="28" t="n"/>
-      <c r="BS125" s="28" t="n"/>
-      <c r="BT125" s="28" t="n"/>
-      <c r="BU125" s="25" t="n"/>
-      <c r="BV125" s="29" t="n"/>
-      <c r="BW125" s="24" t="n"/>
-      <c r="BX125" s="30" t="n"/>
-      <c r="BY125" s="27" t="n"/>
-      <c r="BZ125" s="24" t="n"/>
-      <c r="CA125" s="31" t="n"/>
-      <c r="CB125" s="24" t="n"/>
-    </row>
-    <row r="126" ht="36" customHeight="1">
-      <c r="A126" s="24" t="inlineStr">
-        <is>
-          <t>3314e96647d04bfc</t>
-        </is>
-      </c>
-      <c r="B126" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:16:51.311842Z</t>
-        </is>
-      </c>
-      <c r="C126" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T20:10:00-0400</t>
-        </is>
-      </c>
-      <c r="D126" s="24" t="inlineStr">
-        <is>
-          <t>401816224</t>
-        </is>
-      </c>
-      <c r="E126" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F126" s="24" t="inlineStr">
-        <is>
-          <t>Miami Marlins</t>
-        </is>
-      </c>
-      <c r="G126" s="24" t="inlineStr">
-        <is>
-          <t>Houston Astros</t>
-        </is>
-      </c>
-      <c r="H126" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I126" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J126" s="25" t="n"/>
-      <c r="K126" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L126" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="M126" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="N126" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="O126" s="28" t="n">
-        <v>0.506759</v>
-      </c>
-      <c r="P126" s="28" t="n"/>
-      <c r="Q126" s="28" t="n">
-        <v>-0.012472</v>
-      </c>
-      <c r="R126" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="S126" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T126" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="U126" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V126" s="24" t="n"/>
-      <c r="W126" s="26" t="n"/>
-      <c r="X126" s="26" t="n"/>
-      <c r="Y126" s="25" t="n"/>
-      <c r="Z126" s="26" t="n"/>
-      <c r="AA126" s="28" t="n"/>
-      <c r="AB126" s="28" t="n"/>
-      <c r="AC126" s="30" t="n"/>
-      <c r="AD126" s="24" t="n"/>
-      <c r="AE126" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5998; executable ask 0.5200 (aec-mlb-mia-hou-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF126" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG126" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH126" s="24" t="n"/>
-      <c r="AI126" s="31" t="n"/>
-      <c r="AJ126" s="31" t="n"/>
-      <c r="AK126" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL126" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM126" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN126" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO126" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP126" s="24" t="inlineStr">
-        <is>
-          <t>mlb-mia</t>
-        </is>
-      </c>
-      <c r="AQ126" s="24" t="inlineStr">
-        <is>
-          <t>Miami Marlins</t>
-        </is>
-      </c>
-      <c r="AR126" s="24" t="inlineStr">
-        <is>
-          <t>Miami Marlins</t>
-        </is>
-      </c>
-      <c r="AS126" s="24" t="inlineStr">
-        <is>
-          <t>mlb-hou</t>
-        </is>
-      </c>
-      <c r="AT126" s="24" t="inlineStr">
-        <is>
-          <t>Houston Astros</t>
-        </is>
-      </c>
-      <c r="AU126" s="24" t="inlineStr">
-        <is>
-          <t>Houston Astros</t>
-        </is>
-      </c>
-      <c r="AV126" s="24" t="n"/>
-      <c r="AW126" s="24" t="n"/>
-      <c r="AX126" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY126" s="24" t="n"/>
-      <c r="AZ126" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA126" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BB126" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC126" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BD126" s="24" t="inlineStr">
-        <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
-        </is>
-      </c>
-      <c r="BE126" s="24" t="inlineStr">
-        <is>
-          <t>9f873ead80ec222a</t>
-        </is>
-      </c>
-      <c r="BF126" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG126" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v5</t>
-        </is>
-      </c>
-      <c r="BH126" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:15:37.308149Z</t>
-        </is>
-      </c>
-      <c r="BI126" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ126" s="25" t="n"/>
-      <c r="BK126" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="BL126" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="BM126" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="BN126" s="28" t="n">
-        <v>0.517413</v>
-      </c>
-      <c r="BO126" s="28" t="n"/>
-      <c r="BP126" s="25" t="n"/>
-      <c r="BQ126" s="27" t="n"/>
-      <c r="BR126" s="28" t="n"/>
-      <c r="BS126" s="28" t="n"/>
-      <c r="BT126" s="28" t="n"/>
-      <c r="BU126" s="25" t="n"/>
-      <c r="BV126" s="29" t="n"/>
-      <c r="BW126" s="24" t="n"/>
-      <c r="BX126" s="30" t="n"/>
-      <c r="BY126" s="27" t="n"/>
-      <c r="BZ126" s="24" t="n"/>
-      <c r="CA126" s="31" t="n"/>
-      <c r="CB126" s="24" t="n"/>
-    </row>
-    <row r="127" ht="36" customHeight="1">
-      <c r="A127" s="24" t="inlineStr">
-        <is>
-          <t>d487a54363744159</t>
-        </is>
-      </c>
-      <c r="B127" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:19:52.182978Z</t>
-        </is>
-      </c>
-      <c r="C127" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T09:00:00Z</t>
-        </is>
-      </c>
-      <c r="D127" s="24" t="inlineStr">
-        <is>
-          <t>55954</t>
-        </is>
-      </c>
-      <c r="E127" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F127" s="24" t="inlineStr">
-        <is>
-          <t>EDward Gaming</t>
-        </is>
-      </c>
-      <c r="G127" s="24" t="inlineStr">
-        <is>
-          <t>LGD Gaming</t>
-        </is>
-      </c>
-      <c r="H127" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I127" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J127" s="25" t="n"/>
-      <c r="K127" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L127" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="M127" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="N127" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="O127" s="28" t="n">
-        <v>0.528201</v>
-      </c>
-      <c r="P127" s="28" t="n"/>
-      <c r="Q127" s="28" t="n">
-        <v>-0.021349</v>
-      </c>
-      <c r="R127" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="S127" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T127" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U127" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V127" s="24" t="n"/>
-      <c r="W127" s="26" t="n"/>
-      <c r="X127" s="26" t="n"/>
-      <c r="Y127" s="25" t="n"/>
-      <c r="Z127" s="26" t="n"/>
-      <c r="AA127" s="28" t="n"/>
-      <c r="AB127" s="28" t="n"/>
-      <c r="AC127" s="30" t="n"/>
-      <c r="AD127" s="24" t="n"/>
-      <c r="AE127" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-lgd-edg-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF127" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG127" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH127" s="24" t="n"/>
-      <c r="AI127" s="31" t="n"/>
-      <c r="AJ127" s="31" t="n"/>
-      <c r="AK127" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL127" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM127" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN127" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO127" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP127" s="24" t="inlineStr">
-        <is>
-          <t>EDward Gaming</t>
-        </is>
-      </c>
-      <c r="AQ127" s="24" t="inlineStr">
-        <is>
-          <t>EDward Gaming</t>
-        </is>
-      </c>
-      <c r="AR127" s="24" t="inlineStr">
-        <is>
-          <t>EDward Gaming</t>
-        </is>
-      </c>
-      <c r="AS127" s="24" t="inlineStr">
-        <is>
-          <t>LGD Gaming</t>
-        </is>
-      </c>
-      <c r="AT127" s="24" t="inlineStr">
-        <is>
-          <t>LGD Gaming</t>
-        </is>
-      </c>
-      <c r="AU127" s="24" t="inlineStr">
-        <is>
-          <t>LGD Gaming</t>
-        </is>
-      </c>
-      <c r="AV127" s="24" t="n"/>
-      <c r="AW127" s="24" t="n"/>
-      <c r="AX127" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY127" s="24" t="n"/>
-      <c r="AZ127" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA127" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BB127" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC127" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD127" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BE127" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF127" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG127" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH127" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:17:02.737464Z</t>
-        </is>
-      </c>
-      <c r="BI127" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ127" s="25" t="n"/>
-      <c r="BK127" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="BL127" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="BM127" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="BN127" s="28" t="n"/>
-      <c r="BO127" s="28" t="n"/>
-      <c r="BP127" s="25" t="n"/>
-      <c r="BQ127" s="27" t="n"/>
-      <c r="BR127" s="28" t="n"/>
-      <c r="BS127" s="28" t="n"/>
-      <c r="BT127" s="28" t="n"/>
-      <c r="BU127" s="25" t="n"/>
-      <c r="BV127" s="29" t="n"/>
-      <c r="BW127" s="24" t="n"/>
-      <c r="BX127" s="30" t="n"/>
-      <c r="BY127" s="27" t="n"/>
-      <c r="BZ127" s="24" t="n"/>
-      <c r="CA127" s="31" t="n"/>
-      <c r="CB127" s="24" t="n"/>
-    </row>
-    <row r="128" ht="36" customHeight="1">
-      <c r="A128" s="24" t="inlineStr">
-        <is>
-          <t>53088914289f4187</t>
-        </is>
-      </c>
-      <c r="B128" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:19:52.182978Z</t>
-        </is>
-      </c>
-      <c r="C128" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D128" s="24" t="inlineStr">
-        <is>
-          <t>55996</t>
-        </is>
-      </c>
-      <c r="E128" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F128" s="24" t="inlineStr">
-        <is>
-          <t>Team WE</t>
-        </is>
-      </c>
-      <c r="G128" s="24" t="inlineStr">
-        <is>
-          <t>Top Esports</t>
-        </is>
-      </c>
-      <c r="H128" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I128" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J128" s="25" t="n"/>
-      <c r="K128" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L128" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M128" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N128" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O128" s="28" t="n">
-        <v>0.636655</v>
-      </c>
-      <c r="P128" s="28" t="n"/>
-      <c r="Q128" s="28" t="n">
-        <v>-0.053747</v>
-      </c>
-      <c r="R128" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T128" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U128" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V128" s="24" t="n"/>
-      <c r="W128" s="26" t="n"/>
-      <c r="X128" s="26" t="n"/>
-      <c r="Y128" s="25" t="n"/>
-      <c r="Z128" s="26" t="n"/>
-      <c r="AA128" s="28" t="n"/>
-      <c r="AB128" s="28" t="n"/>
-      <c r="AC128" s="30" t="n"/>
-      <c r="AD128" s="24" t="n"/>
-      <c r="AE128" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-tes-we-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF128" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG128" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH128" s="24" t="n"/>
-      <c r="AI128" s="31" t="n"/>
-      <c r="AJ128" s="31" t="n"/>
-      <c r="AK128" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL128" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM128" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN128" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO128" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP128" s="24" t="inlineStr">
-        <is>
-          <t>Team WE</t>
-        </is>
-      </c>
-      <c r="AQ128" s="24" t="inlineStr">
-        <is>
-          <t>Team WE</t>
-        </is>
-      </c>
-      <c r="AR128" s="24" t="inlineStr">
-        <is>
-          <t>Team WE</t>
-        </is>
-      </c>
-      <c r="AS128" s="24" t="inlineStr">
-        <is>
-          <t>Top Esports</t>
-        </is>
-      </c>
-      <c r="AT128" s="24" t="inlineStr">
-        <is>
-          <t>Top Esports</t>
-        </is>
-      </c>
-      <c r="AU128" s="24" t="inlineStr">
-        <is>
-          <t>Top Esports</t>
-        </is>
-      </c>
-      <c r="AV128" s="24" t="n"/>
-      <c r="AW128" s="24" t="n"/>
-      <c r="AX128" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY128" s="24" t="n"/>
-      <c r="AZ128" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA128" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BB128" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC128" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD128" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BE128" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF128" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG128" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH128" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:17:03.510789Z</t>
-        </is>
-      </c>
-      <c r="BI128" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ128" s="25" t="n"/>
-      <c r="BK128" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL128" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM128" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN128" s="28" t="n"/>
-      <c r="BO128" s="28" t="n"/>
-      <c r="BP128" s="25" t="n"/>
-      <c r="BQ128" s="27" t="n"/>
-      <c r="BR128" s="28" t="n"/>
-      <c r="BS128" s="28" t="n"/>
-      <c r="BT128" s="28" t="n"/>
-      <c r="BU128" s="25" t="n"/>
-      <c r="BV128" s="29" t="n"/>
-      <c r="BW128" s="24" t="n"/>
-      <c r="BX128" s="30" t="n"/>
-      <c r="BY128" s="27" t="n"/>
-      <c r="BZ128" s="24" t="n"/>
-      <c r="CA128" s="31" t="n"/>
-      <c r="CB128" s="24" t="n"/>
-    </row>
-    <row r="129" ht="36" customHeight="1">
-      <c r="A129" s="24" t="inlineStr">
-        <is>
-          <t>71faf50807664dea</t>
-        </is>
-      </c>
-      <c r="B129" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:19:52.182978Z</t>
-        </is>
-      </c>
-      <c r="C129" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D129" s="24" t="inlineStr">
-        <is>
-          <t>56126</t>
-        </is>
-      </c>
-      <c r="E129" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F129" s="24" t="inlineStr">
-        <is>
-          <t>GMBLERS ESPORTS</t>
-        </is>
-      </c>
-      <c r="G129" s="24" t="inlineStr">
-        <is>
-          <t>HMBLE</t>
-        </is>
-      </c>
-      <c r="H129" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I129" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J129" s="25" t="n"/>
-      <c r="K129" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L129" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="M129" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="N129" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="O129" s="28" t="n">
-        <v>0.575556</v>
-      </c>
-      <c r="P129" s="28" t="n"/>
-      <c r="Q129" s="28" t="n">
-        <v>-0.124144</v>
-      </c>
-      <c r="R129" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T129" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U129" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V129" s="24" t="n"/>
-      <c r="W129" s="26" t="n"/>
-      <c r="X129" s="26" t="n"/>
-      <c r="Y129" s="25" t="n"/>
-      <c r="Z129" s="26" t="n"/>
-      <c r="AA129" s="28" t="n"/>
-      <c r="AB129" s="28" t="n"/>
-      <c r="AC129" s="30" t="n"/>
-      <c r="AD129" s="24" t="n"/>
-      <c r="AE129" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-hmble-gmb-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF129" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG129" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH129" s="24" t="n"/>
-      <c r="AI129" s="31" t="n"/>
-      <c r="AJ129" s="31" t="n"/>
-      <c r="AK129" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL129" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM129" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN129" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO129" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP129" s="24" t="inlineStr">
-        <is>
-          <t>GMBLERS ESPORTS</t>
-        </is>
-      </c>
-      <c r="AQ129" s="24" t="inlineStr">
-        <is>
-          <t>GMBLERS ESPORTS</t>
-        </is>
-      </c>
-      <c r="AR129" s="24" t="inlineStr">
-        <is>
-          <t>GMBLERS ESPORTS</t>
-        </is>
-      </c>
-      <c r="AS129" s="24" t="inlineStr">
-        <is>
-          <t>HMBLE</t>
-        </is>
-      </c>
-      <c r="AT129" s="24" t="inlineStr">
-        <is>
-          <t>HMBLE</t>
-        </is>
-      </c>
-      <c r="AU129" s="24" t="inlineStr">
-        <is>
-          <t>HMBLE</t>
-        </is>
-      </c>
-      <c r="AV129" s="24" t="n"/>
-      <c r="AW129" s="24" t="n"/>
-      <c r="AX129" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY129" s="24" t="n"/>
-      <c r="AZ129" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA129" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BB129" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC129" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD129" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BE129" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF129" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG129" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH129" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:17:10.295865Z</t>
-        </is>
-      </c>
-      <c r="BI129" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ129" s="25" t="n"/>
-      <c r="BK129" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="BL129" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="BM129" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="BN129" s="28" t="n"/>
-      <c r="BO129" s="28" t="n"/>
-      <c r="BP129" s="25" t="n"/>
-      <c r="BQ129" s="27" t="n"/>
-      <c r="BR129" s="28" t="n"/>
-      <c r="BS129" s="28" t="n"/>
-      <c r="BT129" s="28" t="n"/>
-      <c r="BU129" s="25" t="n"/>
-      <c r="BV129" s="29" t="n"/>
-      <c r="BW129" s="24" t="n"/>
-      <c r="BX129" s="30" t="n"/>
-      <c r="BY129" s="27" t="n"/>
-      <c r="BZ129" s="24" t="n"/>
-      <c r="CA129" s="31" t="n"/>
-      <c r="CB129" s="24" t="n"/>
-    </row>
-    <row r="130" ht="36" customHeight="1">
-      <c r="A130" s="24" t="inlineStr">
-        <is>
-          <t>f003875538a34221</t>
-        </is>
-      </c>
-      <c r="B130" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:19:52.182978Z</t>
-        </is>
-      </c>
-      <c r="C130" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D130" s="24" t="inlineStr">
-        <is>
-          <t>58172</t>
-        </is>
-      </c>
-      <c r="E130" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F130" s="24" t="inlineStr">
-        <is>
-          <t>Unicorns Of Love Sexy Edition</t>
-        </is>
-      </c>
-      <c r="G130" s="24" t="inlineStr">
-        <is>
-          <t>Kaufland Hangry Knights</t>
-        </is>
-      </c>
-      <c r="H130" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I130" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J130" s="25" t="n"/>
-      <c r="K130" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L130" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="M130" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="N130" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="O130" s="28" t="n">
-        <v>0.634815</v>
-      </c>
-      <c r="P130" s="28" t="n"/>
-      <c r="Q130" s="28" t="n">
-        <v>0.015043</v>
-      </c>
-      <c r="R130" s="26" t="n">
-        <v>28</v>
-      </c>
-      <c r="S130" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T130" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U130" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V130" s="24" t="n"/>
-      <c r="W130" s="26" t="n"/>
-      <c r="X130" s="26" t="n"/>
-      <c r="Y130" s="25" t="n"/>
-      <c r="Z130" s="26" t="n"/>
-      <c r="AA130" s="28" t="n"/>
-      <c r="AB130" s="28" t="n"/>
-      <c r="AC130" s="30" t="n"/>
-      <c r="AD130" s="24" t="n"/>
-      <c r="AE130" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-khk-use-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF130" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG130" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH130" s="24" t="n"/>
-      <c r="AI130" s="31" t="n"/>
-      <c r="AJ130" s="31" t="n"/>
-      <c r="AK130" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL130" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM130" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN130" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO130" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP130" s="24" t="inlineStr">
-        <is>
-          <t>Unicorns Of Love Sexy Edition</t>
-        </is>
-      </c>
-      <c r="AQ130" s="24" t="inlineStr">
-        <is>
-          <t>Unicorns Of Love Sexy Edition</t>
-        </is>
-      </c>
-      <c r="AR130" s="24" t="inlineStr">
-        <is>
-          <t>Unicorns Of Love Sexy Edition</t>
-        </is>
-      </c>
-      <c r="AS130" s="24" t="inlineStr">
-        <is>
-          <t>Kaufland Hangry Knights</t>
-        </is>
-      </c>
-      <c r="AT130" s="24" t="inlineStr">
-        <is>
-          <t>Kaufland Hangry Knights</t>
-        </is>
-      </c>
-      <c r="AU130" s="24" t="inlineStr">
-        <is>
-          <t>Kaufland Hangry Knights</t>
-        </is>
-      </c>
-      <c r="AV130" s="24" t="n"/>
-      <c r="AW130" s="24" t="n"/>
-      <c r="AX130" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY130" s="24" t="n"/>
-      <c r="AZ130" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA130" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BB130" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC130" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD130" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BE130" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF130" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG130" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH130" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:17:11.065754Z</t>
-        </is>
-      </c>
-      <c r="BI130" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ130" s="25" t="n"/>
-      <c r="BK130" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="BL130" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="BM130" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="BN130" s="28" t="n"/>
-      <c r="BO130" s="28" t="n"/>
-      <c r="BP130" s="25" t="n"/>
-      <c r="BQ130" s="27" t="n"/>
-      <c r="BR130" s="28" t="n"/>
-      <c r="BS130" s="28" t="n"/>
-      <c r="BT130" s="28" t="n"/>
-      <c r="BU130" s="25" t="n"/>
-      <c r="BV130" s="29" t="n"/>
-      <c r="BW130" s="24" t="n"/>
-      <c r="BX130" s="30" t="n"/>
-      <c r="BY130" s="27" t="n"/>
-      <c r="BZ130" s="24" t="n"/>
-      <c r="CA130" s="31" t="n"/>
-      <c r="CB130" s="24" t="n"/>
-    </row>
-    <row r="131" ht="36" customHeight="1">
-      <c r="A131" s="24" t="inlineStr">
-        <is>
-          <t>b3933a7255314a9c</t>
-        </is>
-      </c>
-      <c r="B131" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:19:52.182978Z</t>
-        </is>
-      </c>
-      <c r="C131" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T17:30:00Z</t>
-        </is>
-      </c>
-      <c r="D131" s="24" t="inlineStr">
-        <is>
-          <t>56127</t>
-        </is>
-      </c>
-      <c r="E131" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F131" s="24" t="inlineStr">
-        <is>
-          <t>UCAM Esports Club</t>
-        </is>
-      </c>
-      <c r="G131" s="24" t="inlineStr">
-        <is>
-          <t>Barça eSports</t>
-        </is>
-      </c>
-      <c r="H131" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I131" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J131" s="25" t="n"/>
-      <c r="K131" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L131" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="M131" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="N131" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O131" s="28" t="n">
-        <v>0.581485</v>
-      </c>
-      <c r="P131" s="28" t="n"/>
-      <c r="Q131" s="28" t="n">
-        <v>-0.018515</v>
-      </c>
-      <c r="R131" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="S131" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T131" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U131" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V131" s="24" t="n"/>
-      <c r="W131" s="26" t="n"/>
-      <c r="X131" s="26" t="n"/>
-      <c r="Y131" s="25" t="n"/>
-      <c r="Z131" s="26" t="n"/>
-      <c r="AA131" s="28" t="n"/>
-      <c r="AB131" s="28" t="n"/>
-      <c r="AC131" s="30" t="n"/>
-      <c r="AD131" s="24" t="n"/>
-      <c r="AE131" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-bar-ucam-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF131" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG131" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH131" s="24" t="n"/>
-      <c r="AI131" s="31" t="n"/>
-      <c r="AJ131" s="31" t="n"/>
-      <c r="AK131" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL131" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM131" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN131" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO131" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP131" s="24" t="inlineStr">
-        <is>
-          <t>UCAM Esports Club</t>
-        </is>
-      </c>
-      <c r="AQ131" s="24" t="inlineStr">
-        <is>
-          <t>UCAM Esports Club</t>
-        </is>
-      </c>
-      <c r="AR131" s="24" t="inlineStr">
-        <is>
-          <t>UCAM Esports Club</t>
-        </is>
-      </c>
-      <c r="AS131" s="24" t="inlineStr">
-        <is>
-          <t>Barça eSports</t>
-        </is>
-      </c>
-      <c r="AT131" s="24" t="inlineStr">
-        <is>
-          <t>Barça eSports</t>
-        </is>
-      </c>
-      <c r="AU131" s="24" t="inlineStr">
-        <is>
-          <t>Barça eSports</t>
-        </is>
-      </c>
-      <c r="AV131" s="24" t="n"/>
-      <c r="AW131" s="24" t="n"/>
-      <c r="AX131" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY131" s="24" t="n"/>
-      <c r="AZ131" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA131" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BB131" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC131" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD131" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BE131" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF131" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG131" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH131" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:17:11.800383Z</t>
-        </is>
-      </c>
-      <c r="BI131" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ131" s="25" t="n"/>
-      <c r="BK131" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="BL131" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="BM131" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN131" s="28" t="n"/>
-      <c r="BO131" s="28" t="n"/>
-      <c r="BP131" s="25" t="n"/>
-      <c r="BQ131" s="27" t="n"/>
-      <c r="BR131" s="28" t="n"/>
-      <c r="BS131" s="28" t="n"/>
-      <c r="BT131" s="28" t="n"/>
-      <c r="BU131" s="25" t="n"/>
-      <c r="BV131" s="29" t="n"/>
-      <c r="BW131" s="24" t="n"/>
-      <c r="BX131" s="30" t="n"/>
-      <c r="BY131" s="27" t="n"/>
-      <c r="BZ131" s="24" t="n"/>
-      <c r="CA131" s="31" t="n"/>
-      <c r="CB131" s="24" t="n"/>
-    </row>
-    <row r="132" ht="36" customHeight="1">
-      <c r="A132" s="24" t="inlineStr">
-        <is>
-          <t>69fb3791da444f92</t>
-        </is>
-      </c>
-      <c r="B132" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:19:52.182978Z</t>
-        </is>
-      </c>
-      <c r="C132" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D132" s="24" t="inlineStr">
-        <is>
-          <t>56129</t>
-        </is>
-      </c>
-      <c r="E132" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F132" s="24" t="inlineStr">
-        <is>
-          <t>EKO Esports</t>
-        </is>
-      </c>
-      <c r="G132" s="24" t="inlineStr">
-        <is>
-          <t>TITANS</t>
-        </is>
-      </c>
-      <c r="H132" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I132" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J132" s="25" t="n"/>
-      <c r="K132" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L132" s="26" t="n">
-        <v>133</v>
-      </c>
-      <c r="M132" s="27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="N132" s="28" t="n">
-        <v>0.429185</v>
-      </c>
-      <c r="O132" s="28" t="n">
-        <v>0.514184</v>
-      </c>
-      <c r="P132" s="28" t="n"/>
-      <c r="Q132" s="28" t="n">
-        <v>0.08499900000000001</v>
-      </c>
-      <c r="R132" s="26" t="n">
-        <v>62</v>
-      </c>
-      <c r="S132" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T132" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U132" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V132" s="24" t="n"/>
-      <c r="W132" s="26" t="n"/>
-      <c r="X132" s="26" t="n"/>
-      <c r="Y132" s="25" t="n"/>
-      <c r="Z132" s="26" t="n"/>
-      <c r="AA132" s="28" t="n"/>
-      <c r="AB132" s="28" t="n"/>
-      <c r="AC132" s="30" t="n"/>
-      <c r="AD132" s="24" t="n"/>
-      <c r="AE132" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-tts-eko-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF132" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG132" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH132" s="24" t="n"/>
-      <c r="AI132" s="31" t="n"/>
-      <c r="AJ132" s="31" t="n"/>
-      <c r="AK132" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL132" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM132" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN132" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO132" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP132" s="24" t="inlineStr">
-        <is>
-          <t>EKO Esports</t>
-        </is>
-      </c>
-      <c r="AQ132" s="24" t="inlineStr">
-        <is>
-          <t>EKO Esports</t>
-        </is>
-      </c>
-      <c r="AR132" s="24" t="inlineStr">
-        <is>
-          <t>EKO Esports</t>
-        </is>
-      </c>
-      <c r="AS132" s="24" t="inlineStr">
-        <is>
-          <t>TITANS</t>
-        </is>
-      </c>
-      <c r="AT132" s="24" t="inlineStr">
-        <is>
-          <t>TITANS</t>
-        </is>
-      </c>
-      <c r="AU132" s="24" t="inlineStr">
-        <is>
-          <t>TITANS</t>
-        </is>
-      </c>
-      <c r="AV132" s="24" t="n"/>
-      <c r="AW132" s="24" t="n"/>
-      <c r="AX132" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY132" s="24" t="n"/>
-      <c r="AZ132" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA132" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BB132" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC132" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD132" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BE132" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF132" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG132" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH132" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:17:13.396220Z</t>
-        </is>
-      </c>
-      <c r="BI132" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ132" s="25" t="n"/>
-      <c r="BK132" s="26" t="n">
-        <v>133</v>
-      </c>
-      <c r="BL132" s="27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BM132" s="28" t="n">
-        <v>0.429185</v>
-      </c>
-      <c r="BN132" s="28" t="n"/>
-      <c r="BO132" s="28" t="n"/>
-      <c r="BP132" s="25" t="n"/>
-      <c r="BQ132" s="27" t="n"/>
-      <c r="BR132" s="28" t="n"/>
-      <c r="BS132" s="28" t="n"/>
-      <c r="BT132" s="28" t="n"/>
-      <c r="BU132" s="25" t="n"/>
-      <c r="BV132" s="29" t="n"/>
-      <c r="BW132" s="24" t="n"/>
-      <c r="BX132" s="30" t="n"/>
-      <c r="BY132" s="27" t="n"/>
-      <c r="BZ132" s="24" t="n"/>
-      <c r="CA132" s="31" t="n"/>
-      <c r="CB132" s="24" t="n"/>
-    </row>
-    <row r="133" ht="36" customHeight="1">
-      <c r="A133" s="24" t="inlineStr">
-        <is>
-          <t>acbde024ef4d41db</t>
-        </is>
-      </c>
-      <c r="B133" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:19:52.182978Z</t>
-        </is>
-      </c>
-      <c r="C133" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T19:00:00Z</t>
-        </is>
-      </c>
-      <c r="D133" s="24" t="inlineStr">
-        <is>
-          <t>56130</t>
-        </is>
-      </c>
-      <c r="E133" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F133" s="24" t="inlineStr">
-        <is>
-          <t>Aeterna Esports</t>
-        </is>
-      </c>
-      <c r="G133" s="24" t="inlineStr">
-        <is>
-          <t>P11 Esports</t>
-        </is>
-      </c>
-      <c r="H133" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I133" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J133" s="25" t="n"/>
-      <c r="K133" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L133" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="M133" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="N133" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="O133" s="28" t="n">
-        <v>0.518543</v>
-      </c>
-      <c r="P133" s="28" t="n"/>
-      <c r="Q133" s="28" t="n">
-        <v>-0.101229</v>
-      </c>
-      <c r="R133" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T133" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U133" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V133" s="24" t="n"/>
-      <c r="W133" s="26" t="n"/>
-      <c r="X133" s="26" t="n"/>
-      <c r="Y133" s="25" t="n"/>
-      <c r="Z133" s="26" t="n"/>
-      <c r="AA133" s="28" t="n"/>
-      <c r="AB133" s="28" t="n"/>
-      <c r="AC133" s="30" t="n"/>
-      <c r="AD133" s="24" t="n"/>
-      <c r="AE133" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-p11-aee-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF133" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG133" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH133" s="24" t="n"/>
-      <c r="AI133" s="31" t="n"/>
-      <c r="AJ133" s="31" t="n"/>
-      <c r="AK133" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL133" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM133" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN133" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO133" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP133" s="24" t="inlineStr">
-        <is>
-          <t>Aeterna Esports</t>
-        </is>
-      </c>
-      <c r="AQ133" s="24" t="inlineStr">
-        <is>
-          <t>Aeterna Esports</t>
-        </is>
-      </c>
-      <c r="AR133" s="24" t="inlineStr">
-        <is>
-          <t>Aeterna Esports</t>
-        </is>
-      </c>
-      <c r="AS133" s="24" t="inlineStr">
-        <is>
-          <t>P11 Esports</t>
-        </is>
-      </c>
-      <c r="AT133" s="24" t="inlineStr">
-        <is>
-          <t>P11 Esports</t>
-        </is>
-      </c>
-      <c r="AU133" s="24" t="inlineStr">
-        <is>
-          <t>P11 Esports</t>
-        </is>
-      </c>
-      <c r="AV133" s="24" t="n"/>
-      <c r="AW133" s="24" t="n"/>
-      <c r="AX133" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY133" s="24" t="n"/>
-      <c r="AZ133" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA133" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BB133" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC133" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD133" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BE133" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF133" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG133" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH133" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:17:18.687465Z</t>
-        </is>
-      </c>
-      <c r="BI133" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ133" s="25" t="n"/>
-      <c r="BK133" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="BL133" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="BM133" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="BN133" s="28" t="n"/>
-      <c r="BO133" s="28" t="n"/>
-      <c r="BP133" s="25" t="n"/>
-      <c r="BQ133" s="27" t="n"/>
-      <c r="BR133" s="28" t="n"/>
-      <c r="BS133" s="28" t="n"/>
-      <c r="BT133" s="28" t="n"/>
-      <c r="BU133" s="25" t="n"/>
-      <c r="BV133" s="29" t="n"/>
-      <c r="BW133" s="24" t="n"/>
-      <c r="BX133" s="30" t="n"/>
-      <c r="BY133" s="27" t="n"/>
-      <c r="BZ133" s="24" t="n"/>
-      <c r="CA133" s="31" t="n"/>
-      <c r="CB133" s="24" t="n"/>
-    </row>
-    <row r="134" ht="36" customHeight="1">
-      <c r="A134" s="24" t="inlineStr">
-        <is>
-          <t>af7e142ab3744a4a</t>
-        </is>
-      </c>
-      <c r="B134" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:19:52.182978Z</t>
-        </is>
-      </c>
-      <c r="C134" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D134" s="24" t="inlineStr">
-        <is>
-          <t>56132</t>
-        </is>
-      </c>
-      <c r="E134" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F134" s="24" t="inlineStr">
-        <is>
-          <t>INTZ e-Sports</t>
-        </is>
-      </c>
-      <c r="G134" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="H134" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I134" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J134" s="25" t="n"/>
-      <c r="K134" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L134" s="26" t="n">
-        <v>-104</v>
-      </c>
-      <c r="M134" s="27" t="n">
-        <v>1.961538</v>
-      </c>
-      <c r="N134" s="28" t="n">
-        <v>0.509804</v>
-      </c>
-      <c r="O134" s="28" t="n">
-        <v>0.600063</v>
-      </c>
-      <c r="P134" s="28" t="n"/>
-      <c r="Q134" s="28" t="n">
-        <v>0.09025900000000001</v>
-      </c>
-      <c r="R134" s="26" t="n">
-        <v>65</v>
-      </c>
-      <c r="S134" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T134" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U134" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V134" s="24" t="n"/>
-      <c r="W134" s="26" t="n"/>
-      <c r="X134" s="26" t="n"/>
-      <c r="Y134" s="25" t="n"/>
-      <c r="Z134" s="26" t="n"/>
-      <c r="AA134" s="28" t="n"/>
-      <c r="AB134" s="28" t="n"/>
-      <c r="AC134" s="30" t="n"/>
-      <c r="AD134" s="24" t="n"/>
-      <c r="AE134" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-kbm-itz-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF134" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG134" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH134" s="24" t="n"/>
-      <c r="AI134" s="31" t="n"/>
-      <c r="AJ134" s="31" t="n"/>
-      <c r="AK134" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL134" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM134" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN134" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO134" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP134" s="24" t="inlineStr">
-        <is>
-          <t>INTZ e-Sports</t>
-        </is>
-      </c>
-      <c r="AQ134" s="24" t="inlineStr">
-        <is>
-          <t>INTZ e-Sports</t>
-        </is>
-      </c>
-      <c r="AR134" s="24" t="inlineStr">
-        <is>
-          <t>INTZ e-Sports</t>
-        </is>
-      </c>
-      <c r="AS134" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="AT134" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="AU134" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="AV134" s="24" t="n"/>
-      <c r="AW134" s="24" t="n"/>
-      <c r="AX134" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY134" s="24" t="n"/>
-      <c r="AZ134" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA134" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BB134" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC134" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD134" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BE134" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF134" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG134" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH134" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:17:20.981406Z</t>
-        </is>
-      </c>
-      <c r="BI134" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ134" s="25" t="n"/>
-      <c r="BK134" s="26" t="n">
-        <v>-104</v>
-      </c>
-      <c r="BL134" s="27" t="n">
-        <v>1.961538</v>
-      </c>
-      <c r="BM134" s="28" t="n">
-        <v>0.509804</v>
-      </c>
-      <c r="BN134" s="28" t="n"/>
-      <c r="BO134" s="28" t="n"/>
-      <c r="BP134" s="25" t="n"/>
-      <c r="BQ134" s="27" t="n"/>
-      <c r="BR134" s="28" t="n"/>
-      <c r="BS134" s="28" t="n"/>
-      <c r="BT134" s="28" t="n"/>
-      <c r="BU134" s="25" t="n"/>
-      <c r="BV134" s="29" t="n"/>
-      <c r="BW134" s="24" t="n"/>
-      <c r="BX134" s="30" t="n"/>
-      <c r="BY134" s="27" t="n"/>
-      <c r="BZ134" s="24" t="n"/>
-      <c r="CA134" s="31" t="n"/>
-      <c r="CB134" s="24" t="n"/>
-    </row>
-    <row r="135" ht="36" customHeight="1">
-      <c r="A135" s="24" t="inlineStr">
-        <is>
-          <t>cb95d785b47c4574</t>
-        </is>
-      </c>
-      <c r="B135" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:19:52.182978Z</t>
-        </is>
-      </c>
-      <c r="C135" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T23:00:00Z</t>
-        </is>
-      </c>
-      <c r="D135" s="24" t="inlineStr">
-        <is>
-          <t>56138</t>
-        </is>
-      </c>
-      <c r="E135" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F135" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="G135" s="24" t="inlineStr">
-        <is>
-          <t>Ei Nerd Esports</t>
-        </is>
-      </c>
-      <c r="H135" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I135" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J135" s="25" t="n"/>
-      <c r="K135" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L135" s="26" t="n">
-        <v>138</v>
-      </c>
-      <c r="M135" s="27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="N135" s="28" t="n">
-        <v>0.420168</v>
-      </c>
-      <c r="O135" s="28" t="n">
-        <v>0.5449850000000001</v>
-      </c>
-      <c r="P135" s="28" t="n"/>
-      <c r="Q135" s="28" t="n">
-        <v>0.124817</v>
-      </c>
-      <c r="R135" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S135" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T135" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U135" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V135" s="24" t="n"/>
-      <c r="W135" s="26" t="n"/>
-      <c r="X135" s="26" t="n"/>
-      <c r="Y135" s="25" t="n"/>
-      <c r="Z135" s="26" t="n"/>
-      <c r="AA135" s="28" t="n"/>
-      <c r="AB135" s="28" t="n"/>
-      <c r="AC135" s="30" t="n"/>
-      <c r="AD135" s="24" t="n"/>
-      <c r="AE135" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-nerd-7rex-2026-07-22).</t>
-        </is>
-      </c>
-      <c r="AF135" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG135" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH135" s="24" t="n"/>
-      <c r="AI135" s="31" t="n"/>
-      <c r="AJ135" s="31" t="n"/>
-      <c r="AK135" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL135" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM135" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN135" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO135" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP135" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AQ135" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AR135" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AS135" s="24" t="inlineStr">
-        <is>
-          <t>Ei Nerd Esports</t>
-        </is>
-      </c>
-      <c r="AT135" s="24" t="inlineStr">
-        <is>
-          <t>Ei Nerd Esports</t>
-        </is>
-      </c>
-      <c r="AU135" s="24" t="inlineStr">
-        <is>
-          <t>Ei Nerd Esports</t>
-        </is>
-      </c>
-      <c r="AV135" s="24" t="n"/>
-      <c r="AW135" s="24" t="n"/>
-      <c r="AX135" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY135" s="24" t="n"/>
-      <c r="AZ135" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA135" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BB135" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC135" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD135" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BE135" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF135" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG135" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH135" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:17:24.819172Z</t>
-        </is>
-      </c>
-      <c r="BI135" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ135" s="25" t="n"/>
-      <c r="BK135" s="26" t="n">
-        <v>138</v>
-      </c>
-      <c r="BL135" s="27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BM135" s="28" t="n">
-        <v>0.420168</v>
-      </c>
-      <c r="BN135" s="28" t="n"/>
-      <c r="BO135" s="28" t="n"/>
-      <c r="BP135" s="25" t="n"/>
-      <c r="BQ135" s="27" t="n"/>
-      <c r="BR135" s="28" t="n"/>
-      <c r="BS135" s="28" t="n"/>
-      <c r="BT135" s="28" t="n"/>
-      <c r="BU135" s="25" t="n"/>
-      <c r="BV135" s="29" t="n"/>
-      <c r="BW135" s="24" t="n"/>
-      <c r="BX135" s="30" t="n"/>
-      <c r="BY135" s="27" t="n"/>
-      <c r="BZ135" s="24" t="n"/>
-      <c r="CA135" s="31" t="n"/>
-      <c r="CB135" s="24" t="n"/>
-    </row>
-    <row r="136" ht="36" customHeight="1">
-      <c r="A136" s="24" t="inlineStr">
-        <is>
-          <t>8af698b4ee2c496c</t>
-        </is>
-      </c>
-      <c r="B136" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:19:52.182978Z</t>
-        </is>
-      </c>
-      <c r="C136" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T09:00:00Z</t>
-        </is>
-      </c>
-      <c r="D136" s="24" t="inlineStr">
-        <is>
-          <t>56810</t>
-        </is>
-      </c>
-      <c r="E136" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F136" s="24" t="inlineStr">
-        <is>
-          <t>Anyone's Legend</t>
-        </is>
-      </c>
-      <c r="G136" s="24" t="inlineStr">
-        <is>
-          <t>JD Gaming</t>
-        </is>
-      </c>
-      <c r="H136" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I136" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J136" s="25" t="n"/>
-      <c r="K136" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L136" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="M136" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="N136" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="O136" s="28" t="n">
-        <v>0.529047</v>
-      </c>
-      <c r="P136" s="28" t="n"/>
-      <c r="Q136" s="28" t="n">
-        <v>-0.050785</v>
-      </c>
-      <c r="R136" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T136" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U136" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V136" s="24" t="n"/>
-      <c r="W136" s="26" t="n"/>
-      <c r="X136" s="26" t="n"/>
-      <c r="Y136" s="25" t="n"/>
-      <c r="Z136" s="26" t="n"/>
-      <c r="AA136" s="28" t="n"/>
-      <c r="AB136" s="28" t="n"/>
-      <c r="AC136" s="30" t="n"/>
-      <c r="AD136" s="24" t="n"/>
-      <c r="AE136" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-jdg-al-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF136" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG136" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH136" s="24" t="n"/>
-      <c r="AI136" s="31" t="n"/>
-      <c r="AJ136" s="31" t="n"/>
-      <c r="AK136" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL136" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM136" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN136" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO136" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP136" s="24" t="inlineStr">
-        <is>
-          <t>Anyone's Legend</t>
-        </is>
-      </c>
-      <c r="AQ136" s="24" t="inlineStr">
-        <is>
-          <t>Anyone's Legend</t>
-        </is>
-      </c>
-      <c r="AR136" s="24" t="inlineStr">
-        <is>
-          <t>Anyone's Legend</t>
-        </is>
-      </c>
-      <c r="AS136" s="24" t="inlineStr">
-        <is>
-          <t>JD Gaming</t>
-        </is>
-      </c>
-      <c r="AT136" s="24" t="inlineStr">
-        <is>
-          <t>JD Gaming</t>
-        </is>
-      </c>
-      <c r="AU136" s="24" t="inlineStr">
-        <is>
-          <t>JD Gaming</t>
-        </is>
-      </c>
-      <c r="AV136" s="24" t="n"/>
-      <c r="AW136" s="24" t="n"/>
-      <c r="AX136" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY136" s="24" t="n"/>
-      <c r="AZ136" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA136" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BB136" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC136" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD136" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BE136" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF136" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG136" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH136" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:17:27.088741Z</t>
-        </is>
-      </c>
-      <c r="BI136" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ136" s="25" t="n"/>
-      <c r="BK136" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="BL136" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="BM136" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="BN136" s="28" t="n"/>
-      <c r="BO136" s="28" t="n"/>
-      <c r="BP136" s="25" t="n"/>
-      <c r="BQ136" s="27" t="n"/>
-      <c r="BR136" s="28" t="n"/>
-      <c r="BS136" s="28" t="n"/>
-      <c r="BT136" s="28" t="n"/>
-      <c r="BU136" s="25" t="n"/>
-      <c r="BV136" s="29" t="n"/>
-      <c r="BW136" s="24" t="n"/>
-      <c r="BX136" s="30" t="n"/>
-      <c r="BY136" s="27" t="n"/>
-      <c r="BZ136" s="24" t="n"/>
-      <c r="CA136" s="31" t="n"/>
-      <c r="CB136" s="24" t="n"/>
-    </row>
-    <row r="137" ht="36" customHeight="1">
-      <c r="A137" s="24" t="inlineStr">
-        <is>
-          <t>2fc0c6b918364ae8</t>
-        </is>
-      </c>
-      <c r="B137" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:19:52.182978Z</t>
-        </is>
-      </c>
-      <c r="C137" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D137" s="24" t="inlineStr">
-        <is>
-          <t>57088</t>
-        </is>
-      </c>
-      <c r="E137" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F137" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="G137" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="H137" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I137" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J137" s="25" t="n"/>
-      <c r="K137" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L137" s="26" t="n">
-        <v>138</v>
-      </c>
-      <c r="M137" s="27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="N137" s="28" t="n">
-        <v>0.420168</v>
-      </c>
-      <c r="O137" s="28" t="n">
-        <v>0.501096</v>
-      </c>
-      <c r="P137" s="28" t="n"/>
-      <c r="Q137" s="28" t="n">
-        <v>0.080928</v>
-      </c>
-      <c r="R137" s="26" t="n">
-        <v>60</v>
-      </c>
-      <c r="S137" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T137" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U137" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V137" s="24" t="n"/>
-      <c r="W137" s="26" t="n"/>
-      <c r="X137" s="26" t="n"/>
-      <c r="Y137" s="25" t="n"/>
-      <c r="Z137" s="26" t="n"/>
-      <c r="AA137" s="28" t="n"/>
-      <c r="AB137" s="28" t="n"/>
-      <c r="AC137" s="30" t="n"/>
-      <c r="AD137" s="24" t="n"/>
-      <c r="AE137" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-myth-dyn-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF137" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG137" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH137" s="24" t="n"/>
-      <c r="AI137" s="31" t="n"/>
-      <c r="AJ137" s="31" t="n"/>
-      <c r="AK137" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL137" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM137" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN137" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO137" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP137" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="AQ137" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="AR137" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="AS137" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="AT137" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="AU137" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="AV137" s="24" t="n"/>
-      <c r="AW137" s="24" t="n"/>
-      <c r="AX137" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY137" s="24" t="n"/>
-      <c r="AZ137" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA137" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BB137" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC137" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD137" s="24" t="inlineStr">
-        <is>
-          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
-        </is>
-      </c>
-      <c r="BE137" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF137" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG137" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH137" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-22T05:17:33.061872Z</t>
-        </is>
-      </c>
-      <c r="BI137" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ137" s="25" t="n"/>
-      <c r="BK137" s="26" t="n">
-        <v>138</v>
-      </c>
-      <c r="BL137" s="27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BM137" s="28" t="n">
-        <v>0.420168</v>
-      </c>
-      <c r="BN137" s="28" t="n"/>
-      <c r="BO137" s="28" t="n"/>
-      <c r="BP137" s="25" t="n"/>
-      <c r="BQ137" s="27" t="n"/>
-      <c r="BR137" s="28" t="n"/>
-      <c r="BS137" s="28" t="n"/>
-      <c r="BT137" s="28" t="n"/>
-      <c r="BU137" s="25" t="n"/>
-      <c r="BV137" s="29" t="n"/>
-      <c r="BW137" s="24" t="n"/>
-      <c r="BX137" s="30" t="n"/>
-      <c r="BY137" s="27" t="n"/>
-      <c r="BZ137" s="24" t="n"/>
-      <c r="CA137" s="31" t="n"/>
-      <c r="CB137" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -8238,7 +8238,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -15666,7 +15666,7 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -18280,7 +18280,11 @@
           <t>shadow_qualified</t>
         </is>
       </c>
-      <c r="BA66" t="inlineStr"/>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
       <c r="BB66" t="inlineStr">
         <is>
           <t>identity</t>
@@ -18508,7 +18512,11 @@
           <t>shadow_qualified</t>
         </is>
       </c>
-      <c r="BA67" t="inlineStr"/>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
       <c r="BB67" t="inlineStr">
         <is>
           <t>identity</t>
@@ -18736,7 +18744,11 @@
           <t>shadow_qualified</t>
         </is>
       </c>
-      <c r="BA68" t="inlineStr"/>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
       <c r="BB68" t="inlineStr">
         <is>
           <t>identity</t>
@@ -18968,7 +18980,7 @@
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -19206,7 +19218,7 @@
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -19444,7 +19456,7 @@
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -19678,7 +19690,11 @@
           <t>shadow_qualified</t>
         </is>
       </c>
-      <c r="BA72" t="inlineStr"/>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
       <c r="BB72" t="inlineStr">
         <is>
           <t>identity</t>
@@ -19906,7 +19922,11 @@
           <t>shadow_qualified</t>
         </is>
       </c>
-      <c r="BA73" t="inlineStr"/>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
       <c r="BB73" t="inlineStr">
         <is>
           <t>identity</t>
@@ -20138,7 +20158,7 @@
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -20376,7 +20396,7 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -20614,7 +20634,7 @@
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -20852,7 +20872,7 @@
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -21090,7 +21110,7 @@
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -21328,7 +21348,7 @@
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
@@ -21566,7 +21586,7 @@
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -21804,7 +21824,7 @@
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
@@ -22042,7 +22062,7 @@
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
@@ -22280,7 +22300,7 @@
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -22518,7 +22538,7 @@
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -22756,7 +22776,7 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
@@ -22994,7 +23014,7 @@
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
@@ -23232,7 +23252,7 @@
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
@@ -23492,7 +23512,7 @@
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
@@ -23768,7 +23788,7 @@
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
@@ -24044,7 +24064,7 @@
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
@@ -24320,7 +24340,7 @@
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
@@ -24596,7 +24616,7 @@
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
@@ -24872,7 +24892,7 @@
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
@@ -25148,7 +25168,7 @@
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
@@ -25424,7 +25444,7 @@
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
@@ -25700,7 +25720,7 @@
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
@@ -25976,7 +25996,7 @@
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
@@ -26252,7 +26272,7 @@
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
@@ -26528,7 +26548,7 @@
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
@@ -26804,7 +26824,7 @@
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
@@ -27080,7 +27100,7 @@
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
@@ -27356,7 +27376,7 @@
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
@@ -27632,7 +27652,7 @@
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
@@ -27908,7 +27928,7 @@
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
@@ -28184,7 +28204,7 @@
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
@@ -28460,7 +28480,7 @@
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>6b38a269117f4c6c1ae1e324273c2f9b9d11b2c15d99242f39aa89882d15db32</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
@@ -28704,7 +28724,11 @@
           <t>shadow_qualified</t>
         </is>
       </c>
-      <c r="BA107" t="inlineStr"/>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
       <c r="BB107" t="inlineStr">
         <is>
           <t>identity</t>

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -8238,7 +8238,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -15666,7 +15666,7 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -20158,7 +20158,7 @@
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -20396,7 +20396,7 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -20872,7 +20872,7 @@
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -21348,7 +21348,7 @@
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
@@ -21586,7 +21586,7 @@
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
@@ -22062,7 +22062,7 @@
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
@@ -23252,7 +23252,7 @@
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
@@ -23512,7 +23512,7 @@
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
@@ -23788,7 +23788,7 @@
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
@@ -24616,7 +24616,7 @@
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
@@ -24892,7 +24892,7 @@
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
@@ -25168,7 +25168,7 @@
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
@@ -25720,7 +25720,7 @@
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
@@ -25996,7 +25996,7 @@
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
@@ -26272,7 +26272,7 @@
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
@@ -26548,7 +26548,7 @@
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
@@ -27100,7 +27100,7 @@
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
@@ -27376,7 +27376,7 @@
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
@@ -27928,7 +27928,7 @@
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
@@ -28204,7 +28204,7 @@
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
@@ -28964,7 +28964,7 @@
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -8238,7 +8238,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -15666,7 +15666,7 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -20158,7 +20158,7 @@
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -20396,7 +20396,7 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -20872,7 +20872,7 @@
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -21348,7 +21348,7 @@
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
@@ -21586,7 +21586,7 @@
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
@@ -22062,7 +22062,7 @@
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
@@ -23252,7 +23252,7 @@
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
@@ -23512,7 +23512,7 @@
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
@@ -23788,7 +23788,7 @@
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
@@ -24616,7 +24616,7 @@
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
@@ -24892,7 +24892,7 @@
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
@@ -25168,7 +25168,7 @@
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
@@ -25720,7 +25720,7 @@
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
@@ -25996,7 +25996,7 @@
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
@@ -26272,7 +26272,7 @@
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
@@ -26548,7 +26548,7 @@
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
@@ -27100,7 +27100,7 @@
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
@@ -27376,7 +27376,7 @@
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
@@ -27928,7 +27928,7 @@
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
@@ -28204,7 +28204,7 @@
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
@@ -28964,7 +28964,7 @@
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">

--- a/data/flat_picks.xlsx
+++ b/data/flat_picks.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CM154" headerRowCount="1">
-  <autoFilter ref="A1:CM154"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CM157" headerRowCount="1">
+  <autoFilter ref="A1:CM157"/>
   <tableColumns count="91">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -750,19 +750,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$154)</f>
+        <f>COUNTA('Picks'!$A$2:$A$157)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$154,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$157,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$154,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$157,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$154,"settled",'Picks'!$V$2:$V$154,"win")+COUNTIFS('Picks'!$U$2:$U$154,"settled",'Picks'!$V$2:$V$154,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$157,"settled",'Picks'!$V$2:$V$157,"win")+COUNTIFS('Picks'!$U$2:$U$157,"settled",'Picks'!$V$2:$V$157,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -790,19 +790,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$154,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$157,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$154,"&gt;0",'Picks'!$V$2:$V$154,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$154,"&gt;0",'Picks'!$V$2:$V$154,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$157,"&gt;0",'Picks'!$V$2:$V$157,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$157,"&gt;0",'Picks'!$V$2:$V$157,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$154,"&gt;0",'Picks'!$V$2:$V$154,"win")/(COUNTIFS('Picks'!$BX$2:$BX$154,"&gt;0",'Picks'!$V$2:$V$154,"win")+COUNTIFS('Picks'!$BX$2:$BX$154,"&gt;0",'Picks'!$V$2:$V$154,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$157,"&gt;0",'Picks'!$V$2:$V$157,"win")/(COUNTIFS('Picks'!$BX$2:$BX$157,"&gt;0",'Picks'!$V$2:$V$157,"win")+COUNTIFS('Picks'!$BX$2:$BX$157,"&gt;0",'Picks'!$V$2:$V$157,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$154)/SUM('Picks'!$BX$2:$BX$154),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$157)/SUM('Picks'!$BX$2:$BX$157),0)</f>
         <v/>
       </c>
     </row>
@@ -830,19 +830,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$154)</f>
+        <f>SUM('Picks'!$BY$2:$BY$157)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$154,"&lt;&gt;",'Picks'!$AB$2:$AB$154),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$157,"&lt;&gt;",'Picks'!$AB$2:$AB$157),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$154,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$154,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$157,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$157,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$154,'Picks'!$AM$2:$AM$154,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$157,'Picks'!$AM$2:$AM$157,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -897,15 +897,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$154,$A14,'Picks'!$U$2:$U$154,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$157,$A14,'Picks'!$U$2:$U$157,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$154,$A14,'Picks'!$U$2:$U$154,"settled",'Picks'!$V$2:$V$154,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$157,$A14,'Picks'!$U$2:$U$157,"settled",'Picks'!$V$2:$V$157,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$154,$A14,'Picks'!$U$2:$U$154,"settled",'Picks'!$V$2:$V$154,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$157,$A14,'Picks'!$U$2:$U$157,"settled",'Picks'!$V$2:$V$157,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -913,11 +913,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$154,'Picks'!$H$2:$H$154,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$157,'Picks'!$H$2:$H$157,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$154,'Picks'!$H$2:$H$154,$A14,'Picks'!$U$2:$U$154,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$157,'Picks'!$H$2:$H$157,$A14,'Picks'!$U$2:$U$157,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -928,15 +928,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$154,$A15,'Picks'!$U$2:$U$154,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$157,$A15,'Picks'!$U$2:$U$157,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$154,$A15,'Picks'!$U$2:$U$154,"settled",'Picks'!$V$2:$V$154,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$157,$A15,'Picks'!$U$2:$U$157,"settled",'Picks'!$V$2:$V$157,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$154,$A15,'Picks'!$U$2:$U$154,"settled",'Picks'!$V$2:$V$154,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$157,$A15,'Picks'!$U$2:$U$157,"settled",'Picks'!$V$2:$V$157,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -944,11 +944,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$154,'Picks'!$H$2:$H$154,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$157,'Picks'!$H$2:$H$157,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$154,'Picks'!$H$2:$H$154,$A15,'Picks'!$U$2:$U$154,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$157,'Picks'!$H$2:$H$157,$A15,'Picks'!$U$2:$U$157,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -959,15 +959,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$154,$A16,'Picks'!$U$2:$U$154,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$157,$A16,'Picks'!$U$2:$U$157,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$154,$A16,'Picks'!$U$2:$U$154,"settled",'Picks'!$V$2:$V$154,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$157,$A16,'Picks'!$U$2:$U$157,"settled",'Picks'!$V$2:$V$157,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$154,$A16,'Picks'!$U$2:$U$154,"settled",'Picks'!$V$2:$V$154,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$157,$A16,'Picks'!$U$2:$U$157,"settled",'Picks'!$V$2:$V$157,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -975,11 +975,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$154,'Picks'!$H$2:$H$154,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$157,'Picks'!$H$2:$H$157,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$154,'Picks'!$H$2:$H$154,$A16,'Picks'!$U$2:$U$154,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$157,'Picks'!$H$2:$H$157,$A16,'Picks'!$U$2:$U$157,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CM154"/>
+  <dimension ref="A1:CM157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -29591,22 +29591,22 @@
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="24" t="inlineStr">
         <is>
-          <t>e8fa5b9e3cfb4844</t>
+          <t>3e68c62def444eb1</t>
         </is>
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>2026-07-23T04:39:57.634876Z</t>
+          <t>2026-07-23T04:36:37.074229Z</t>
         </is>
       </c>
       <c r="C111" s="24" t="inlineStr">
         <is>
-          <t>2026-07-23T12:15:00-0400</t>
+          <t>2026-07-22T20:00:00-0400</t>
         </is>
       </c>
       <c r="D111" s="24" t="inlineStr">
         <is>
-          <t>401816233</t>
+          <t>401816223</t>
         </is>
       </c>
       <c r="E111" s="24" t="inlineStr">
@@ -29616,12 +29616,12 @@
       </c>
       <c r="F111" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="G111" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="H111" s="24" t="inlineStr">
@@ -29641,27 +29641,29 @@
         </is>
       </c>
       <c r="L111" s="26" t="n">
-        <v>-213</v>
+        <v>-110</v>
       </c>
       <c r="M111" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.909091</v>
       </c>
       <c r="N111" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.52381</v>
       </c>
       <c r="O111" s="28" t="n">
-        <v>0.563209</v>
-      </c>
-      <c r="P111" s="28" t="n"/>
+        <v>0.592436</v>
+      </c>
+      <c r="P111" s="28" t="n">
+        <v>0.05</v>
+      </c>
       <c r="Q111" s="28" t="n">
-        <v>-0.117302</v>
+        <v>0.06862600000000001</v>
       </c>
       <c r="R111" s="26" t="n">
+        <v>54</v>
+      </c>
+      <c r="S111" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="S111" s="29" t="n">
-        <v>1.25</v>
-      </c>
       <c r="T111" s="24" t="inlineStr">
         <is>
           <t>mlb-elo-trend-lr-v5</t>
@@ -29669,26 +29671,46 @@
       </c>
       <c r="U111" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V111" s="24" t="n"/>
-      <c r="W111" s="26" t="n"/>
-      <c r="X111" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V111" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W111" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X111" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y111" s="25" t="n"/>
-      <c r="Z111" s="26" t="n"/>
-      <c r="AA111" s="28" t="n"/>
-      <c r="AB111" s="28" t="n"/>
-      <c r="AC111" s="30" t="n"/>
-      <c r="AD111" s="24" t="n"/>
+      <c r="Z111" s="26" t="n">
+        <v>-110</v>
+      </c>
+      <c r="AA111" s="28" t="n">
+        <v>0.52381</v>
+      </c>
+      <c r="AB111" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T04:36:37.074229Z</t>
+        </is>
+      </c>
       <c r="AE111" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5750; executable ask 0.6800 (aec-mlb-sd-atl-2026-07-23).</t>
+          <t>Retroactive model run — features from team averages.</t>
         </is>
       </c>
       <c r="AF111" s="31" t="inlineStr">
         <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+          <t>Retroactive; features approximated from teammate averages, not point-in-time.</t>
         </is>
       </c>
       <c r="AG111" s="24" t="inlineStr">
@@ -29719,37 +29741,37 @@
       </c>
       <c r="AO111" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+          <t>NO_CALL_MISSING_FEATURES</t>
         </is>
       </c>
       <c r="AP111" s="24" t="inlineStr">
         <is>
-          <t>mlb-sd</t>
+          <t>mlb-detroittigers</t>
         </is>
       </c>
       <c r="AQ111" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AR111" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AS111" s="24" t="inlineStr">
         <is>
-          <t>mlb-atl</t>
+          <t>mlb-chicagocubs</t>
         </is>
       </c>
       <c r="AT111" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AU111" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AV111" s="24" t="n"/>
@@ -29787,7 +29809,7 @@
       </c>
       <c r="BE111" s="24" t="inlineStr">
         <is>
-          <t>38f426fb99fbe531</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BF111" s="24" t="inlineStr">
@@ -29802,31 +29824,29 @@
       </c>
       <c r="BH111" s="24" t="inlineStr">
         <is>
-          <t>2026-07-23T04:37:57.864733Z</t>
-        </is>
-      </c>
-      <c r="BI111" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
+          <t>2026-07-23T04:36:37.074229Z</t>
+        </is>
+      </c>
+      <c r="BI111" s="24" t="n"/>
       <c r="BJ111" s="25" t="n"/>
       <c r="BK111" s="26" t="n">
-        <v>-213</v>
+        <v>-110</v>
       </c>
       <c r="BL111" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.909091</v>
       </c>
       <c r="BM111" s="28" t="n">
-        <v>0.680511</v>
-      </c>
-      <c r="BN111" s="28" t="n">
-        <v>0.676617</v>
-      </c>
+        <v>0.52381</v>
+      </c>
+      <c r="BN111" s="28" t="n"/>
       <c r="BO111" s="28" t="n"/>
       <c r="BP111" s="25" t="n"/>
-      <c r="BQ111" s="27" t="n"/>
-      <c r="BR111" s="28" t="n"/>
+      <c r="BQ111" s="27" t="n">
+        <v>1.909091</v>
+      </c>
+      <c r="BR111" s="28" t="n">
+        <v>0.52381</v>
+      </c>
       <c r="BS111" s="28" t="n"/>
       <c r="BT111" s="28" t="n"/>
       <c r="BU111" s="25" t="n"/>
@@ -29852,22 +29872,22 @@
     <row r="112" ht="36" customHeight="1">
       <c r="A112" s="24" t="inlineStr">
         <is>
-          <t>e84d82d379dd4c40</t>
+          <t>9d4cc694127f432f</t>
         </is>
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>2026-07-23T04:39:57.634876Z</t>
+          <t>2026-07-23T04:36:37.074229Z</t>
         </is>
       </c>
       <c r="C112" s="24" t="inlineStr">
         <is>
-          <t>2026-07-23T13:10:00-0400</t>
+          <t>2026-07-22T20:05:00-0400</t>
         </is>
       </c>
       <c r="D112" s="24" t="inlineStr">
         <is>
-          <t>401816232</t>
+          <t>401816222</t>
         </is>
       </c>
       <c r="E112" s="24" t="inlineStr">
@@ -29877,12 +29897,12 @@
       </c>
       <c r="F112" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="G112" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="H112" s="24" t="inlineStr">
@@ -29902,26 +29922,28 @@
         </is>
       </c>
       <c r="L112" s="26" t="n">
-        <v>-127</v>
+        <v>-110</v>
       </c>
       <c r="M112" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.909091</v>
       </c>
       <c r="N112" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.52381</v>
       </c>
       <c r="O112" s="28" t="n">
-        <v>0.56856</v>
-      </c>
-      <c r="P112" s="28" t="n"/>
+        <v>0.549254</v>
+      </c>
+      <c r="P112" s="28" t="n">
+        <v>0.05</v>
+      </c>
       <c r="Q112" s="28" t="n">
-        <v>0.009089</v>
+        <v>0.025445</v>
       </c>
       <c r="R112" s="26" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="S112" s="29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T112" s="24" t="inlineStr">
         <is>
@@ -29930,26 +29952,46 @@
       </c>
       <c r="U112" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V112" s="24" t="n"/>
-      <c r="W112" s="26" t="n"/>
-      <c r="X112" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V112" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W112" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X112" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y112" s="25" t="n"/>
-      <c r="Z112" s="26" t="n"/>
-      <c r="AA112" s="28" t="n"/>
-      <c r="AB112" s="28" t="n"/>
-      <c r="AC112" s="30" t="n"/>
-      <c r="AD112" s="24" t="n"/>
+      <c r="Z112" s="26" t="n">
+        <v>-110</v>
+      </c>
+      <c r="AA112" s="28" t="n">
+        <v>0.52381</v>
+      </c>
+      <c r="AB112" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-23T04:36:37.074229Z</t>
+        </is>
+      </c>
       <c r="AE112" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5750; executable ask 0.5600 (aec-mlb-min-cle-2026-07-23).</t>
+          <t>Retroactive model run — features from team averages.</t>
         </is>
       </c>
       <c r="AF112" s="31" t="inlineStr">
         <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+          <t>Retroactive; features approximated from teammate averages, not point-in-time.</t>
         </is>
       </c>
       <c r="AG112" s="24" t="inlineStr">
@@ -29980,37 +30022,37 @@
       </c>
       <c r="AO112" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MISSING_FEATURES</t>
         </is>
       </c>
       <c r="AP112" s="24" t="inlineStr">
         <is>
-          <t>mlb-min</t>
+          <t>mlb-chicagowhitesox</t>
         </is>
       </c>
       <c r="AQ112" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="AR112" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="AS112" s="24" t="inlineStr">
         <is>
-          <t>mlb-cle</t>
+          <t>mlb-texasrangers</t>
         </is>
       </c>
       <c r="AT112" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AU112" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AV112" s="24" t="n"/>
@@ -30048,7 +30090,7 @@
       </c>
       <c r="BE112" s="24" t="inlineStr">
         <is>
-          <t>5dbbda2c13171b0e</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BF112" s="24" t="inlineStr">
@@ -30063,31 +30105,29 @@
       </c>
       <c r="BH112" s="24" t="inlineStr">
         <is>
-          <t>2026-07-23T04:37:59.025113Z</t>
-        </is>
-      </c>
-      <c r="BI112" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
+          <t>2026-07-23T04:36:37.074229Z</t>
+        </is>
+      </c>
+      <c r="BI112" s="24" t="n"/>
       <c r="BJ112" s="25" t="n"/>
       <c r="BK112" s="26" t="n">
-        <v>-127</v>
+        <v>-110</v>
       </c>
       <c r="BL112" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.909091</v>
       </c>
       <c r="BM112" s="28" t="n">
-        <v>0.5594710000000001</v>
-      </c>
-      <c r="BN112" s="28" t="n">
-        <v>0.557214</v>
-      </c>
+        <v>0.52381</v>
+      </c>
+      <c r="BN112" s="28" t="n"/>
       <c r="BO112" s="28" t="n"/>
       <c r="BP112" s="25" t="n"/>
-      <c r="BQ112" s="27" t="n"/>
-      <c r="BR112" s="28" t="n"/>
+      <c r="BQ112" s="27" t="n">
+        <v>1.909091</v>
+      </c>
+      <c r="BR112" s="28" t="n">
+        <v>0.52381</v>
+      </c>
       <c r="BS112" s="28" t="n"/>
       <c r="BT112" s="28" t="n"/>
       <c r="BU112" s="25" t="n"/>
@@ -30113,37 +30153,37 @@
     <row r="113" ht="36" customHeight="1">
       <c r="A113" s="24" t="inlineStr">
         <is>
-          <t>ba5da1760f694c90</t>
+          <t>a8c0022f56dd4d20</t>
         </is>
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-23T04:39:57.634876Z</t>
+          <t>2026-07-23T04:41:27.795424Z</t>
         </is>
       </c>
       <c r="C113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-23T15:07:00-0400</t>
+          <t>2026-07-23T14:00:00Z</t>
         </is>
       </c>
       <c r="D113" s="24" t="inlineStr">
         <is>
-          <t>401816234</t>
+          <t>59038</t>
         </is>
       </c>
       <c r="E113" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F113" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="G113" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>BET-M 33</t>
         </is>
       </c>
       <c r="H113" s="24" t="inlineStr">
@@ -30163,30 +30203,30 @@
         </is>
       </c>
       <c r="L113" s="26" t="n">
-        <v>-102</v>
+        <v>127</v>
       </c>
       <c r="M113" s="27" t="n">
-        <v>1.980392</v>
+        <v>2.27</v>
       </c>
       <c r="N113" s="28" t="n">
-        <v>0.50495</v>
+        <v>0.440529</v>
       </c>
       <c r="O113" s="28" t="n">
-        <v>0.528152</v>
+        <v>0.524292</v>
       </c>
       <c r="P113" s="28" t="n"/>
       <c r="Q113" s="28" t="n">
-        <v>0.023202</v>
+        <v>0.083763</v>
       </c>
       <c r="R113" s="26" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="S113" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T113" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>cs2-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U113" s="24" t="inlineStr">
@@ -30205,12 +30245,12 @@
       <c r="AD113" s="24" t="n"/>
       <c r="AE113" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5750; executable ask 0.5050 (aec-mlb-tb-tor-2026-07-23).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-33-sparta-2026-07-23).</t>
         </is>
       </c>
       <c r="AF113" s="31" t="inlineStr">
         <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
         </is>
       </c>
       <c r="AG113" s="24" t="inlineStr">
@@ -30223,7 +30263,7 @@
       <c r="AJ113" s="31" t="n"/>
       <c r="AK113" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL113" s="26" t="n">
@@ -30231,47 +30271,47 @@
       </c>
       <c r="AM113" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN113" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO113" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP113" s="24" t="inlineStr">
         <is>
-          <t>mlb-tb</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AQ113" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AR113" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AS113" s="24" t="inlineStr">
         <is>
-          <t>mlb-tor</t>
+          <t>BET-M 33</t>
         </is>
       </c>
       <c r="AT113" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>BET-M 33</t>
         </is>
       </c>
       <c r="AU113" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>BET-M 33</t>
         </is>
       </c>
       <c r="AV113" s="24" t="n"/>
@@ -30289,27 +30329,27 @@
       </c>
       <c r="BA113" s="24" t="inlineStr">
         <is>
-          <t>f4ba988a51fcfbc42f017c34f5d25f481de500c1e844165b98cf0acea10d1539</t>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
         </is>
       </c>
       <c r="BB113" s="24" t="inlineStr">
         <is>
-          <t>learned_lr</t>
+          <t>neutral_elo</t>
         </is>
       </c>
       <c r="BC113" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>cs2-tiered-elo-v3</t>
         </is>
       </c>
       <c r="BD113" s="24" t="inlineStr">
         <is>
-          <t>f4ba988a51fcfbc42f017c34f5d25f481de500c1e844165b98cf0acea10d1539</t>
+          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
         </is>
       </c>
       <c r="BE113" s="24" t="inlineStr">
         <is>
-          <t>30f1580a797cd317</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BF113" s="24" t="inlineStr">
@@ -30319,12 +30359,12 @@
       </c>
       <c r="BG113" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>cs2-tiered-elo-v3</t>
         </is>
       </c>
       <c r="BH113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-23T04:38:03.482132Z</t>
+          <t>2026-07-23T04:40:51.634148Z</t>
         </is>
       </c>
       <c r="BI113" s="24" t="inlineStr">
@@ -30334,17 +30374,15 @@
       </c>
       <c r="BJ113" s="25" t="n"/>
       <c r="BK113" s="26" t="n">
-        <v>-102</v>
+        <v>127</v>
       </c>
       <c r="BL113" s="27" t="n">
-        <v>1.980392</v>
+        <v>2.27</v>
       </c>
       <c r="BM113" s="28" t="n">
-        <v>0.50495</v>
-      </c>
-      <c r="BN113" s="28" t="n">
-        <v>0.502488</v>
-      </c>
+        <v>0.440529</v>
+      </c>
+      <c r="BN113" s="28" t="n"/>
       <c r="BO113" s="28" t="n"/>
       <c r="BP113" s="25" t="n"/>
       <c r="BQ113" s="27" t="n"/>
@@ -30374,37 +30412,37 @@
     <row r="114" ht="36" customHeight="1">
       <c r="A114" s="24" t="inlineStr">
         <is>
-          <t>2c08c142a9c14ee3</t>
+          <t>5d28c87374ab4e12</t>
         </is>
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>2026-07-23T04:39:57.634876Z</t>
+          <t>2026-07-23T04:41:27.795424Z</t>
         </is>
       </c>
       <c r="C114" s="24" t="inlineStr">
         <is>
-          <t>2026-07-23T17:15:00-0400</t>
+          <t>2026-07-23T15:00:00Z</t>
         </is>
       </c>
       <c r="D114" s="24" t="inlineStr">
         <is>
-          <t>401881162</t>
+          <t>56958</t>
         </is>
       </c>
       <c r="E114" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F114" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>paiN</t>
         </is>
       </c>
       <c r="G114" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="H114" s="24" t="inlineStr">
@@ -30424,30 +30462,30 @@
         </is>
       </c>
       <c r="L114" s="26" t="n">
-        <v>-113</v>
+        <v>133</v>
       </c>
       <c r="M114" s="27" t="n">
-        <v>1.884956</v>
+        <v>2.33</v>
       </c>
       <c r="N114" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.429185</v>
       </c>
       <c r="O114" s="28" t="n">
-        <v>0.538243</v>
+        <v>0.524605</v>
       </c>
       <c r="P114" s="28" t="n"/>
       <c r="Q114" s="28" t="n">
-        <v>0.007727</v>
+        <v>0.09542</v>
       </c>
       <c r="R114" s="26" t="n">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="S114" s="29" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="T114" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v5</t>
+          <t>cs2-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U114" s="24" t="inlineStr">
@@ -30466,12 +30504,12 @@
       <c r="AD114" s="24" t="n"/>
       <c r="AE114" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5750; executable ask 0.5300 (aec-mlb-az-stl-2026-07-23).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-cs2-m8-pain-2026-07-23).</t>
         </is>
       </c>
       <c r="AF114" s="31" t="inlineStr">
         <is>
-          <t>Learned model; promotio